--- a/data/ORS.MI.xlsx
+++ b/data/ORS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1141" uniqueCount="1141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1142" uniqueCount="1142">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -56,109 +56,109 @@
     <t xml:space="preserve">7.82472562789917</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93818616867065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90171527862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03948974609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92603015899658</t>
+    <t xml:space="preserve">7.93818521499634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90171670913696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03948783874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92602872848511</t>
   </si>
   <si>
     <t xml:space="preserve">7.86119413375854</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8206729888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93413352966309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02328109741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08811569213867</t>
+    <t xml:space="preserve">7.82067251205444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93413400650024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02328014373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08811378479004</t>
   </si>
   <si>
     <t xml:space="preserve">8.1448450088501</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69910764694214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80446434020996</t>
+    <t xml:space="preserve">7.69910860061646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80446481704712</t>
   </si>
   <si>
     <t xml:space="preserve">7.97465467453003</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01112461090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01517677307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79230880737305</t>
+    <t xml:space="preserve">8.01112365722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01517581939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79230785369873</t>
   </si>
   <si>
     <t xml:space="preserve">7.82877779006958</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34745311737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84093427658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90981960296631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85714149475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78015089035034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84498596191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97870683670044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88550662994385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95034265518188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00302028656006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0192289352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91792488098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10027313232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10432434082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18536758422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20157527923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11242961883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07595825195312</t>
+    <t xml:space="preserve">8.34745407104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84093332290649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90982103347778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85714197158813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78015232086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8449854850769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97870779037476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88550710678101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95034170150757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00301837921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01922798156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9179253578186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1002721786499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10432243347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1853666305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20157432556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11242866516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07595920562744</t>
   </si>
   <si>
     <t xml:space="preserve">8.03138542175293</t>
@@ -179,10 +179,10 @@
     <t xml:space="preserve">8.2583065032959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4203929901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67162609100342</t>
+    <t xml:space="preserve">8.42039203643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67162704467773</t>
   </si>
   <si>
     <t xml:space="preserve">8.55816650390625</t>
@@ -191,34 +191,34 @@
     <t xml:space="preserve">8.42849731445312</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52429008483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45921897888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50802230834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60562896728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5324239730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61376285552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67069911956787</t>
+    <t xml:space="preserve">8.52428913116455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45921802520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50802040100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60562801361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53242492675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61376190185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67070007324219</t>
   </si>
   <si>
     <t xml:space="preserve">8.87404632568359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79270648956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90658092498779</t>
+    <t xml:space="preserve">8.7927074432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90657997131348</t>
   </si>
   <si>
     <t xml:space="preserve">8.86591243743896</t>
@@ -233,10 +233,10 @@
     <t xml:space="preserve">8.78457260131836</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74390506744385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91471576690674</t>
+    <t xml:space="preserve">8.74390316009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91471481323242</t>
   </si>
   <si>
     <t xml:space="preserve">8.92284965515137</t>
@@ -245,10 +245,10 @@
     <t xml:space="preserve">9.10992813110352</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07739353179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11806201934814</t>
+    <t xml:space="preserve">9.077392578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11806297302246</t>
   </si>
   <si>
     <t xml:space="preserve">9.1343297958374</t>
@@ -257,16 +257,16 @@
     <t xml:space="preserve">9.15059757232666</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15873241424561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73576927185059</t>
+    <t xml:space="preserve">9.15873050689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7357702255249</t>
   </si>
   <si>
     <t xml:space="preserve">8.6788330078125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85777759552002</t>
+    <t xml:space="preserve">8.85777854919434</t>
   </si>
   <si>
     <t xml:space="preserve">8.72763633728027</t>
@@ -275,7 +275,7 @@
     <t xml:space="preserve">8.70323467254639</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66256713867188</t>
+    <t xml:space="preserve">8.66256618499756</t>
   </si>
   <si>
     <t xml:space="preserve">8.69510078430176</t>
@@ -284,7 +284,7 @@
     <t xml:space="preserve">8.6218957901001</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80084133148193</t>
+    <t xml:space="preserve">8.80084037780762</t>
   </si>
   <si>
     <t xml:space="preserve">8.77643966674805</t>
@@ -293,55 +293,55 @@
     <t xml:space="preserve">8.68696689605713</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54869079589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54055786132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58122825622559</t>
+    <t xml:space="preserve">8.54869174957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54055690765381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58122730255127</t>
   </si>
   <si>
     <t xml:space="preserve">8.46735286712646</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51615524291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49988651275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45108413696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63003063201904</t>
+    <t xml:space="preserve">8.51615428924561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49988842010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45108318328857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63002967834473</t>
   </si>
   <si>
     <t xml:space="preserve">8.80897521972656</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89031314849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.930983543396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9635181427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05299091339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30514144897461</t>
+    <t xml:space="preserve">8.89031410217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93098449707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96351718902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0529899597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30514049530029</t>
   </si>
   <si>
     <t xml:space="preserve">9.10179424285889</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1912670135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35394287109375</t>
+    <t xml:space="preserve">9.19126605987549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35394382476807</t>
   </si>
   <si>
     <t xml:space="preserve">9.4759521484375</t>
@@ -359,28 +359,28 @@
     <t xml:space="preserve">9.71996688842773</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85824394226074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0046520233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.240535736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.24866771698</t>
+    <t xml:space="preserve">9.85824489593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0046539306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2405347824097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2486696243286</t>
   </si>
   <si>
     <t xml:space="preserve">10.3381414413452</t>
   </si>
   <si>
-    <t xml:space="preserve">10.598424911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4276151657104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4032106399536</t>
+    <t xml:space="preserve">10.5984258651733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4276142120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4032115936279</t>
   </si>
   <si>
     <t xml:space="preserve">10.5252199172974</t>
@@ -392,31 +392,31 @@
     <t xml:space="preserve">10.5658893585205</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5821571350098</t>
+    <t xml:space="preserve">10.5821561813354</t>
   </si>
   <si>
     <t xml:space="preserve">10.7773704528809</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9807167053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8749771118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6553630828857</t>
+    <t xml:space="preserve">10.9807157516479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8749761581421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6553640365601</t>
   </si>
   <si>
     <t xml:space="preserve">10.6797637939453</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5740232467651</t>
+    <t xml:space="preserve">10.5740242004395</t>
   </si>
   <si>
     <t xml:space="preserve">10.5170860290527</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5414886474609</t>
+    <t xml:space="preserve">10.5414876937866</t>
   </si>
   <si>
     <t xml:space="preserve">10.5577564239502</t>
@@ -428,46 +428,46 @@
     <t xml:space="preserve">10.8180389404297</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6878976821899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7611017227173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6472282409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8993768692017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.883111000061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.671630859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7367000579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0051193237305</t>
+    <t xml:space="preserve">10.6878967285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.761100769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6472291946411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8993797302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8831100463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6716289520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7367010116577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0051183700562</t>
   </si>
   <si>
     <t xml:space="preserve">11.0213871002197</t>
   </si>
   <si>
-    <t xml:space="preserve">11.184063911438</t>
+    <t xml:space="preserve">11.1840648651123</t>
   </si>
   <si>
     <t xml:space="preserve">11.4036769866943</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3955450057983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3386077880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3223400115967</t>
+    <t xml:space="preserve">11.3955430984497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3386068344116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.322338104248</t>
   </si>
   <si>
     <t xml:space="preserve">11.330472946167</t>
@@ -476,13 +476,13 @@
     <t xml:space="preserve">11.3630094528198</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0783243179321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6065607070923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8424415588379</t>
+    <t xml:space="preserve">11.0783224105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.606559753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8424425125122</t>
   </si>
   <si>
     <t xml:space="preserve">10.8505754470825</t>
@@ -491,79 +491,79 @@
     <t xml:space="preserve">10.6390943527222</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4113464355469</t>
+    <t xml:space="preserve">10.4113454818726</t>
   </si>
   <si>
     <t xml:space="preserve">10.2080011367798</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2730712890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2324018478394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.321873664856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3706769943237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3300075531006</t>
+    <t xml:space="preserve">10.2730703353882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2323999404907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3218746185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.370677947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3300065994263</t>
   </si>
   <si>
     <t xml:space="preserve">10.3056058883667</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2568054199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1835975646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4845514297485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3625431060791</t>
+    <t xml:space="preserve">10.2568044662476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1835966110229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4845523834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3625421524048</t>
   </si>
   <si>
     <t xml:space="preserve">10.4438819885254</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8587083816528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9237804412842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0376539230347</t>
+    <t xml:space="preserve">10.8587074279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9237794876099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0376529693604</t>
   </si>
   <si>
     <t xml:space="preserve">11.0620565414429</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1027240753174</t>
+    <t xml:space="preserve">11.1027250289917</t>
   </si>
   <si>
     <t xml:space="preserve">11.1433944702148</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1759300231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1352596282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0701894760132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.118992805481</t>
+    <t xml:space="preserve">11.175929069519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1352605819702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0701904296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1189937591553</t>
   </si>
   <si>
     <t xml:space="preserve">11.1515274047852</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2247323989868</t>
+    <t xml:space="preserve">11.2247314453125</t>
   </si>
   <si>
     <t xml:space="preserve">11.0457878112793</t>
@@ -575,7 +575,7 @@
     <t xml:space="preserve">10.1347951889038</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36161136627197</t>
+    <t xml:space="preserve">8.36161231994629</t>
   </si>
   <si>
     <t xml:space="preserve">8.01999092102051</t>
@@ -584,25 +584,25 @@
     <t xml:space="preserve">8.10946273803711</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3941478729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21520233154297</t>
+    <t xml:space="preserve">8.39414691925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21520328521729</t>
   </si>
   <si>
     <t xml:space="preserve">8.3372106552124</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3128080368042</t>
+    <t xml:space="preserve">8.31280899047852</t>
   </si>
   <si>
     <t xml:space="preserve">8.18266773223877</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34534645080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23960399627686</t>
+    <t xml:space="preserve">8.34534454345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23960494995117</t>
   </si>
   <si>
     <t xml:space="preserve">8.49175548553467</t>
@@ -611,31 +611,31 @@
     <t xml:space="preserve">8.5893611907959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76017189025879</t>
+    <t xml:space="preserve">8.76017284393311</t>
   </si>
   <si>
     <t xml:space="preserve">8.29654216766357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25587368011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17453479766846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19080066680908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23147106170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28027248382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14199829101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15826606750488</t>
+    <t xml:space="preserve">8.25587177276611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17453289031982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1908016204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23147010803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2802734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14199924468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15826511383057</t>
   </si>
   <si>
     <t xml:space="preserve">8.16639995574951</t>
@@ -647,25 +647,25 @@
     <t xml:space="preserve">8.05252552032471</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89798355102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85731220245361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93051719665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90611505508423</t>
+    <t xml:space="preserve">7.89798307418823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85731315612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93051671981812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90611553192139</t>
   </si>
   <si>
     <t xml:space="preserve">7.93865251541138</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8491792678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.808509349823</t>
+    <t xml:space="preserve">7.84917974472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80850887298584</t>
   </si>
   <si>
     <t xml:space="preserve">7.62956476211548</t>
@@ -674,22 +674,22 @@
     <t xml:space="preserve">7.57262754440308</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48315477371216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66616725921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60516357421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54009342193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52382469177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.479088306427</t>
+    <t xml:space="preserve">7.48315572738647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66616678237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60516309738159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54009246826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52382326126099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47908735275269</t>
   </si>
   <si>
     <t xml:space="preserve">7.61329698562622</t>
@@ -698,13 +698,13 @@
     <t xml:space="preserve">7.54822492599487</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56449413299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50755643844604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46688604354858</t>
+    <t xml:space="preserve">7.56449365615845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5075569152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4668869972229</t>
   </si>
   <si>
     <t xml:space="preserve">7.49128913879395</t>
@@ -713,13 +713,13 @@
     <t xml:space="preserve">7.49942302703857</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31234407424927</t>
+    <t xml:space="preserve">7.31234502792358</t>
   </si>
   <si>
     <t xml:space="preserve">7.27980804443359</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37741565704346</t>
+    <t xml:space="preserve">7.37741422653198</t>
   </si>
   <si>
     <t xml:space="preserve">7.38554906845093</t>
@@ -731,109 +731,109 @@
     <t xml:space="preserve">7.3204779624939</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34487867355347</t>
+    <t xml:space="preserve">7.34487915039062</t>
   </si>
   <si>
     <t xml:space="preserve">7.28794193267822</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04392623901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15779972076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39368295669556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42621850967407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40181684494019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30421113967896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36114740371704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20660305023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35301351547241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.336745262146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27167367935181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23100519180298</t>
+    <t xml:space="preserve">7.04392671585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15780019760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39368343353271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42621898651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40181636810303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3042106628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36114835739136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20660400390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35301208496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33674669265747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27167463302612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23100471496582</t>
   </si>
   <si>
     <t xml:space="preserve">7.32861185073853</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26354074478149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23913908004761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22287130355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24727249145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44248628616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25540781021118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18220281600952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29607534408569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16593408584595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1415319442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05206060409546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07646131515503</t>
+    <t xml:space="preserve">7.26354122161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23913955688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22287178039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24727344512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44248533248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25540637969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18220138549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29607582092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16593456268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14153337478638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0520601272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07646179199219</t>
   </si>
   <si>
     <t xml:space="preserve">7.0357928276062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01952457427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87311410903931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67790269851685</t>
+    <t xml:space="preserve">7.01952505111694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87311458587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.677903175354</t>
   </si>
   <si>
     <t xml:space="preserve">6.85124731063843</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93379211425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26397275924683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14840984344482</t>
+    <t xml:space="preserve">6.93379163742065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26397323608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14841032028198</t>
   </si>
   <si>
     <t xml:space="preserve">7.09888315200806</t>
@@ -842,16 +842,16 @@
     <t xml:space="preserve">7.18142795562744</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16491842269897</t>
+    <t xml:space="preserve">7.16491889953613</t>
   </si>
   <si>
     <t xml:space="preserve">7.14015579223633</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2144455909729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1731743812561</t>
+    <t xml:space="preserve">7.21444654464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17317342758179</t>
   </si>
   <si>
     <t xml:space="preserve">6.97506427764893</t>
@@ -860,10 +860,10 @@
     <t xml:space="preserve">6.84299325942993</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60361289978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62012147903442</t>
+    <t xml:space="preserve">6.60361194610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62012100219727</t>
   </si>
   <si>
     <t xml:space="preserve">6.67790222167969</t>
@@ -872,13 +872,13 @@
     <t xml:space="preserve">6.80997467041016</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54582977294922</t>
+    <t xml:space="preserve">6.54583072662354</t>
   </si>
   <si>
     <t xml:space="preserve">6.31470394134521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32295846939087</t>
+    <t xml:space="preserve">6.32295894622803</t>
   </si>
   <si>
     <t xml:space="preserve">6.34772253036499</t>
@@ -890,16 +890,16 @@
     <t xml:space="preserve">6.39724922180176</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4715404510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28168535232544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22390413284302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09183168411255</t>
+    <t xml:space="preserve">6.47153997421265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28168678283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22390460968018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09183216094971</t>
   </si>
   <si>
     <t xml:space="preserve">5.90197801589966</t>
@@ -908,16 +908,16 @@
     <t xml:space="preserve">5.9597601890564</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9927773475647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20739507675171</t>
+    <t xml:space="preserve">5.99277782440186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20739555358887</t>
   </si>
   <si>
     <t xml:space="preserve">6.14135980606079</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19088697433472</t>
+    <t xml:space="preserve">6.19088649749756</t>
   </si>
   <si>
     <t xml:space="preserve">6.14961338043213</t>
@@ -926,7 +926,7 @@
     <t xml:space="preserve">6.07532358169556</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25692224502563</t>
+    <t xml:space="preserve">6.25692272186279</t>
   </si>
   <si>
     <t xml:space="preserve">6.00928735733032</t>
@@ -938,10 +938,10 @@
     <t xml:space="preserve">6.12485027313232</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13310480117798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2734317779541</t>
+    <t xml:space="preserve">6.13310527801514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27343082427979</t>
   </si>
   <si>
     <t xml:space="preserve">6.44677591323853</t>
@@ -950,13 +950,13 @@
     <t xml:space="preserve">6.55408525466919</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51281213760376</t>
+    <t xml:space="preserve">6.51281261444092</t>
   </si>
   <si>
     <t xml:space="preserve">6.36423110961914</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2404146194458</t>
+    <t xml:space="preserve">6.24041366577148</t>
   </si>
   <si>
     <t xml:space="preserve">6.21564960479736</t>
@@ -968,16 +968,16 @@
     <t xml:space="preserve">6.24866771697998</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11659574508667</t>
+    <t xml:space="preserve">6.11659622192383</t>
   </si>
   <si>
     <t xml:space="preserve">6.10834074020386</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05055904388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89372396469116</t>
+    <t xml:space="preserve">6.05055952072144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89372444152832</t>
   </si>
   <si>
     <t xml:space="preserve">5.778160572052</t>
@@ -986,7 +986,7 @@
     <t xml:space="preserve">5.6956148147583</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79466962814331</t>
+    <t xml:space="preserve">5.79466915130615</t>
   </si>
   <si>
     <t xml:space="preserve">5.80292367935181</t>
@@ -998,16 +998,16 @@
     <t xml:space="preserve">5.78641510009766</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73688697814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85245180130005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29819488525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1826319694519</t>
+    <t xml:space="preserve">5.73688745498657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85245132446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29819536209106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18263244628906</t>
   </si>
   <si>
     <t xml:space="preserve">6.15786790847778</t>
@@ -1019,7 +1019,7 @@
     <t xml:space="preserve">6.08357763290405</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81943321228027</t>
+    <t xml:space="preserve">5.81943416595459</t>
   </si>
   <si>
     <t xml:space="preserve">5.91848659515381</t>
@@ -1028,19 +1028,19 @@
     <t xml:space="preserve">5.86070537567139</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76165151596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75339698791504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81117868423462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70387029647827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74514245986938</t>
+    <t xml:space="preserve">5.76165246963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75339651107788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81117820739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70387077331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74514198303223</t>
   </si>
   <si>
     <t xml:space="preserve">5.83594226837158</t>
@@ -1052,34 +1052,34 @@
     <t xml:space="preserve">5.84419679641724</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94325113296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96801376342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87721538543701</t>
+    <t xml:space="preserve">5.94325065612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96801424026489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87721490859985</t>
   </si>
   <si>
     <t xml:space="preserve">5.88546943664551</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93499612808228</t>
+    <t xml:space="preserve">5.93499660491943</t>
   </si>
   <si>
     <t xml:space="preserve">6.02579593658447</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0670690536499</t>
+    <t xml:space="preserve">6.06706857681274</t>
   </si>
   <si>
     <t xml:space="preserve">6.3889946937561</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19914102554321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04230499267578</t>
+    <t xml:space="preserve">6.19914054870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04230451583862</t>
   </si>
   <si>
     <t xml:space="preserve">6.05881452560425</t>
@@ -1091,10 +1091,10 @@
     <t xml:space="preserve">6.17437744140625</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1760196685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29349851608276</t>
+    <t xml:space="preserve">6.17601919174194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29349803924561</t>
   </si>
   <si>
     <t xml:space="preserve">6.25993204116821</t>
@@ -1103,7 +1103,7 @@
     <t xml:space="preserve">6.20958423614502</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09210538864136</t>
+    <t xml:space="preserve">6.09210586547852</t>
   </si>
   <si>
     <t xml:space="preserve">6.10888910293579</t>
@@ -1133,16 +1133,16 @@
     <t xml:space="preserve">6.12567138671875</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1928014755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42775917053223</t>
+    <t xml:space="preserve">6.19280195236206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42775964736938</t>
   </si>
   <si>
     <t xml:space="preserve">6.71306467056274</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64593410491943</t>
+    <t xml:space="preserve">6.64593458175659</t>
   </si>
   <si>
     <t xml:space="preserve">6.69628238677979</t>
@@ -1154,13 +1154,13 @@
     <t xml:space="preserve">6.7298469543457</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62915086746216</t>
+    <t xml:space="preserve">6.629150390625</t>
   </si>
   <si>
     <t xml:space="preserve">6.56202030181885</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54523754119873</t>
+    <t xml:space="preserve">6.54523801803589</t>
   </si>
   <si>
     <t xml:space="preserve">6.67949914932251</t>
@@ -1184,49 +1184,49 @@
     <t xml:space="preserve">6.36062908172607</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67253875732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55506086349487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68932247161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62219095230103</t>
+    <t xml:space="preserve">5.67253923416138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55506038665771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68932199478149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62219190597534</t>
   </si>
   <si>
     <t xml:space="preserve">5.53827810287476</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43758201599121</t>
+    <t xml:space="preserve">5.43758249282837</t>
   </si>
   <si>
     <t xml:space="preserve">5.45436525344849</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60540866851807</t>
+    <t xml:space="preserve">5.60540819168091</t>
   </si>
   <si>
     <t xml:space="preserve">5.5214958190918</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50471305847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48793029785156</t>
+    <t xml:space="preserve">5.50471258163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48792934417725</t>
   </si>
   <si>
     <t xml:space="preserve">5.35366868972778</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3704514503479</t>
+    <t xml:space="preserve">5.37045049667358</t>
   </si>
   <si>
     <t xml:space="preserve">5.42079925537109</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28653812408447</t>
+    <t xml:space="preserve">5.28653860092163</t>
   </si>
   <si>
     <t xml:space="preserve">5.30332088470459</t>
@@ -1235,19 +1235,19 @@
     <t xml:space="preserve">5.26975584030151</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38723373413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32010316848755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65575695037842</t>
+    <t xml:space="preserve">5.38723421096802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32010364532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65575647354126</t>
   </si>
   <si>
     <t xml:space="preserve">5.75645303726196</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70610427856445</t>
+    <t xml:space="preserve">5.70610475540161</t>
   </si>
   <si>
     <t xml:space="preserve">5.72288703918457</t>
@@ -1256,7 +1256,7 @@
     <t xml:space="preserve">5.73967027664185</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63897466659546</t>
+    <t xml:space="preserve">5.6389741897583</t>
   </si>
   <si>
     <t xml:space="preserve">5.57184410095215</t>
@@ -1271,19 +1271,19 @@
     <t xml:space="preserve">5.21940803527832</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16905975341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13549375534058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10192918777466</t>
+    <t xml:space="preserve">5.16906023025513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13549327850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1019287109375</t>
   </si>
   <si>
     <t xml:space="preserve">4.95088481903076</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03479814529419</t>
+    <t xml:space="preserve">5.03479862213135</t>
   </si>
   <si>
     <t xml:space="preserve">5.15227651596069</t>
@@ -1295,22 +1295,22 @@
     <t xml:space="preserve">5.06836318969727</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08514642715454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23618984222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2529730796814</t>
+    <t xml:space="preserve">5.0851469039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23619031906128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25297212600708</t>
   </si>
   <si>
     <t xml:space="preserve">5.33688640594482</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79001808166504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77323532104492</t>
+    <t xml:space="preserve">5.79001760482788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77323579788208</t>
   </si>
   <si>
     <t xml:space="preserve">5.58862638473511</t>
@@ -1322,7 +1322,7 @@
     <t xml:space="preserve">4.79984140396118</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59844827651978</t>
+    <t xml:space="preserve">4.59844875335693</t>
   </si>
   <si>
     <t xml:space="preserve">4.36349201202393</t>
@@ -1331,19 +1331,19 @@
     <t xml:space="preserve">4.31314420700073</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19566488265991</t>
+    <t xml:space="preserve">4.19566535949707</t>
   </si>
   <si>
     <t xml:space="preserve">4.11175203323364</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02783870697021</t>
+    <t xml:space="preserve">4.02783823013306</t>
   </si>
   <si>
     <t xml:space="preserve">4.17049074172974</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06979608535767</t>
+    <t xml:space="preserve">4.06979513168335</t>
   </si>
   <si>
     <t xml:space="preserve">4.12014293670654</t>
@@ -1355,7 +1355,7 @@
     <t xml:space="preserve">4.17888164520264</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04462099075317</t>
+    <t xml:space="preserve">4.04462146759033</t>
   </si>
   <si>
     <t xml:space="preserve">4.15370845794678</t>
@@ -1370,16 +1370,16 @@
     <t xml:space="preserve">4.14531803131104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99427318572998</t>
+    <t xml:space="preserve">3.99427270889282</t>
   </si>
   <si>
     <t xml:space="preserve">4.09496927261353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98588132858276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27957820892334</t>
+    <t xml:space="preserve">3.98588180541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2795786857605</t>
   </si>
   <si>
     <t xml:space="preserve">4.22922992706299</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">4.03622961044312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12877893447876</t>
+    <t xml:space="preserve">4.12877941131592</t>
   </si>
   <si>
     <t xml:space="preserve">4.16283130645752</t>
@@ -1403,16 +1403,16 @@
     <t xml:space="preserve">4.00108432769775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20539617538452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3756537437439</t>
+    <t xml:space="preserve">4.20539569854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37565469741821</t>
   </si>
   <si>
     <t xml:space="preserve">4.21390867233276</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22242116928101</t>
+    <t xml:space="preserve">4.22242164611816</t>
   </si>
   <si>
     <t xml:space="preserve">4.25647354125977</t>
@@ -1424,13 +1424,13 @@
     <t xml:space="preserve">4.32457637786865</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30755090713501</t>
+    <t xml:space="preserve">4.30755138397217</t>
   </si>
   <si>
     <t xml:space="preserve">4.23944711685181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35862874984741</t>
+    <t xml:space="preserve">4.35862827301025</t>
   </si>
   <si>
     <t xml:space="preserve">4.51186180114746</t>
@@ -1448,13 +1448,13 @@
     <t xml:space="preserve">5.73772573471069</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5504412651062</t>
+    <t xml:space="preserve">5.55044078826904</t>
   </si>
   <si>
     <t xml:space="preserve">5.5844931602478</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56746768951416</t>
+    <t xml:space="preserve">5.567467212677</t>
   </si>
   <si>
     <t xml:space="preserve">5.41423416137695</t>
@@ -1466,10 +1466,10 @@
     <t xml:space="preserve">5.48233795166016</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44828605651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60151863098145</t>
+    <t xml:space="preserve">5.4482855796814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6015191078186</t>
   </si>
   <si>
     <t xml:space="preserve">5.66962242126465</t>
@@ -1478,37 +1478,37 @@
     <t xml:space="preserve">5.51638984680176</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70367479324341</t>
+    <t xml:space="preserve">5.70367431640625</t>
   </si>
   <si>
     <t xml:space="preserve">5.32910490036011</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27802705764771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43126106262207</t>
+    <t xml:space="preserve">5.27802658081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43126010894775</t>
   </si>
   <si>
     <t xml:space="preserve">5.31207847595215</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2269492149353</t>
+    <t xml:space="preserve">5.22694873809814</t>
   </si>
   <si>
     <t xml:space="preserve">5.00561237335205</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95453500747681</t>
+    <t xml:space="preserve">4.95453548431396</t>
   </si>
   <si>
     <t xml:space="preserve">4.93750905990601</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05668973922729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03966426849365</t>
+    <t xml:space="preserve">5.05669021606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03966474533081</t>
   </si>
   <si>
     <t xml:space="preserve">4.97156095504761</t>
@@ -1517,10 +1517,10 @@
     <t xml:space="preserve">4.8864312171936</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02263879776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92048263549805</t>
+    <t xml:space="preserve">5.02263832092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92048311233521</t>
   </si>
   <si>
     <t xml:space="preserve">4.9034571647644</t>
@@ -1529,16 +1529,16 @@
     <t xml:space="preserve">4.852379322052</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86940479278564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34613132476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24397563934326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36315631866455</t>
+    <t xml:space="preserve">4.8694052696228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34613037109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2439751625061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36315679550171</t>
   </si>
   <si>
     <t xml:space="preserve">5.38018274307251</t>
@@ -1550,31 +1550,31 @@
     <t xml:space="preserve">5.15884637832642</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10776853561401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98858642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0907416343689</t>
+    <t xml:space="preserve">5.10776805877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98858737945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09074211120605</t>
   </si>
   <si>
     <t xml:space="preserve">5.1928973197937</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17587184906006</t>
+    <t xml:space="preserve">5.1758713722229</t>
   </si>
   <si>
     <t xml:space="preserve">5.1418194770813</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07371616363525</t>
+    <t xml:space="preserve">5.07371664047241</t>
   </si>
   <si>
     <t xml:space="preserve">4.68212032318115</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5459132194519</t>
+    <t xml:space="preserve">4.54591369628906</t>
   </si>
   <si>
     <t xml:space="preserve">4.59699106216431</t>
@@ -1586,22 +1586,22 @@
     <t xml:space="preserve">4.63104295730591</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7842755317688</t>
+    <t xml:space="preserve">4.78427600860596</t>
   </si>
   <si>
     <t xml:space="preserve">4.767249584198</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8183274269104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80130195617676</t>
+    <t xml:space="preserve">4.81832790374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8013014793396</t>
   </si>
   <si>
     <t xml:space="preserve">5.39720869064331</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6185450553894</t>
+    <t xml:space="preserve">5.61854457855225</t>
   </si>
   <si>
     <t xml:space="preserve">5.4653115272522</t>
@@ -1610,19 +1610,19 @@
     <t xml:space="preserve">5.49936389923096</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63557052612305</t>
+    <t xml:space="preserve">5.63557100296021</t>
   </si>
   <si>
     <t xml:space="preserve">5.68664789199829</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65259695053101</t>
+    <t xml:space="preserve">5.65259647369385</t>
   </si>
   <si>
     <t xml:space="preserve">5.8569073677063</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8739333152771</t>
+    <t xml:space="preserve">5.87393283843994</t>
   </si>
   <si>
     <t xml:space="preserve">6.31660652160645</t>
@@ -1631,7 +1631,7 @@
     <t xml:space="preserve">6.33363246917725</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2995810508728</t>
+    <t xml:space="preserve">6.29958057403564</t>
   </si>
   <si>
     <t xml:space="preserve">6.35065841674805</t>
@@ -1643,25 +1643,25 @@
     <t xml:space="preserve">6.55496835708618</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69117593765259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79333209991455</t>
+    <t xml:space="preserve">6.69117641448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79333162307739</t>
   </si>
   <si>
     <t xml:space="preserve">7.15087509155273</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08277130126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8784613609314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77630519866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84440946578979</t>
+    <t xml:space="preserve">7.08277082443237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87846088409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77630567550659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84440898895264</t>
   </si>
   <si>
     <t xml:space="preserve">6.70820236206055</t>
@@ -1673,16 +1673,16 @@
     <t xml:space="preserve">6.53794288635254</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72522830963135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65712451934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91251230239868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8954873085022</t>
+    <t xml:space="preserve">6.72522783279419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6571249961853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91251277923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89548635482788</t>
   </si>
   <si>
     <t xml:space="preserve">6.96359014511108</t>
@@ -1691,13 +1691,13 @@
     <t xml:space="preserve">7.17302179336548</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05085372924805</t>
+    <t xml:space="preserve">7.05085325241089</t>
   </si>
   <si>
     <t xml:space="preserve">7.12066411972046</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57443189620972</t>
+    <t xml:space="preserve">7.57443284988403</t>
   </si>
   <si>
     <t xml:space="preserve">7.97584199905396</t>
@@ -1712,22 +1712,22 @@
     <t xml:space="preserve">7.99329423904419</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0107479095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94093799591064</t>
+    <t xml:space="preserve">8.01074695587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94093704223633</t>
   </si>
   <si>
     <t xml:space="preserve">8.13291454315186</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15036773681641</t>
+    <t xml:space="preserve">8.15036869049072</t>
   </si>
   <si>
     <t xml:space="preserve">8.16782093048096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18527317047119</t>
+    <t xml:space="preserve">8.18527412414551</t>
   </si>
   <si>
     <t xml:space="preserve">8.34234619140625</t>
@@ -1736,37 +1736,37 @@
     <t xml:space="preserve">8.11546325683594</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25508403778076</t>
+    <t xml:space="preserve">8.25508308410645</t>
   </si>
   <si>
     <t xml:space="preserve">8.08055782318115</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20272445678711</t>
+    <t xml:space="preserve">8.20272541046143</t>
   </si>
   <si>
     <t xml:space="preserve">7.95838928222656</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37725162506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32489395141602</t>
+    <t xml:space="preserve">8.37725257873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3248929977417</t>
   </si>
   <si>
     <t xml:space="preserve">8.81356716156006</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58668231964111</t>
+    <t xml:space="preserve">8.58668327331543</t>
   </si>
   <si>
     <t xml:space="preserve">8.53432559967041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69139766693115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60413551330566</t>
+    <t xml:space="preserve">8.69139862060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60413646697998</t>
   </si>
   <si>
     <t xml:space="preserve">8.72630405426025</t>
@@ -1775,25 +1775,25 @@
     <t xml:space="preserve">8.42960929870605</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28998947143555</t>
+    <t xml:space="preserve">8.28998851776123</t>
   </si>
   <si>
     <t xml:space="preserve">8.30744171142578</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04565334320068</t>
+    <t xml:space="preserve">8.04565238952637</t>
   </si>
   <si>
     <t xml:space="preserve">7.85367345809937</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41215705871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22017860412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44706249237061</t>
+    <t xml:space="preserve">8.41215801239014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22017765045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44706153869629</t>
   </si>
   <si>
     <t xml:space="preserve">8.3597993850708</t>
@@ -1814,7 +1814,7 @@
     <t xml:space="preserve">8.55177783966064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65649318695068</t>
+    <t xml:space="preserve">8.656494140625</t>
   </si>
   <si>
     <t xml:space="preserve">8.51687240600586</t>
@@ -1826,13 +1826,13 @@
     <t xml:space="preserve">8.49942016601562</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5692310333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99161815643311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59893321990967</t>
+    <t xml:space="preserve">8.56923007965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99161720275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59893417358398</t>
   </si>
   <si>
     <t xml:space="preserve">9.77345943450928</t>
@@ -1841,31 +1841,31 @@
     <t xml:space="preserve">9.8170919418335</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29351425170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46803951263428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55530166625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64256572723389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9043550491333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33714580535889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94798564910889</t>
+    <t xml:space="preserve">9.29351329803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46804046630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55530261993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64256477355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90435600280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33714485168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9479866027832</t>
   </si>
   <si>
     <t xml:space="preserve">9.86072254180908</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5151968002319</t>
+    <t xml:space="preserve">10.5151958465576</t>
   </si>
   <si>
     <t xml:space="preserve">10.4279327392578</t>
@@ -1874,13 +1874,13 @@
     <t xml:space="preserve">10.5588283538818</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6024589538574</t>
+    <t xml:space="preserve">10.6024580001831</t>
   </si>
   <si>
     <t xml:space="preserve">10.8206167221069</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7333545684814</t>
+    <t xml:space="preserve">10.7333536148071</t>
   </si>
   <si>
     <t xml:space="preserve">10.7769861221313</t>
@@ -1892,7 +1892,7 @@
     <t xml:space="preserve">10.3843011856079</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3406705856323</t>
+    <t xml:space="preserve">10.3406715393066</t>
   </si>
   <si>
     <t xml:space="preserve">10.2097749710083</t>
@@ -1907,7 +1907,7 @@
     <t xml:space="preserve">9.51167106628418</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72982788085938</t>
+    <t xml:space="preserve">9.72982883453369</t>
   </si>
   <si>
     <t xml:space="preserve">9.68619823455811</t>
@@ -1919,10 +1919,10 @@
     <t xml:space="preserve">9.42440795898438</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6496152877808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.562352180481</t>
+    <t xml:space="preserve">11.6496162414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5623531341553</t>
   </si>
   <si>
     <t xml:space="preserve">11.7805099487305</t>
@@ -1940,10 +1940,10 @@
     <t xml:space="preserve">12.3040895462036</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2604570388794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2168254852295</t>
+    <t xml:space="preserve">12.2604560852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2168245315552</t>
   </si>
   <si>
     <t xml:space="preserve">12.3913507461548</t>
@@ -1958,16 +1958,16 @@
     <t xml:space="preserve">11.6059837341309</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9515104293823</t>
+    <t xml:space="preserve">10.9515113830566</t>
   </si>
   <si>
     <t xml:space="preserve">12.0422992706299</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3005628585815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3441953659058</t>
+    <t xml:space="preserve">11.3005638122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3441944122314</t>
   </si>
   <si>
     <t xml:space="preserve">10.9951429367065</t>
@@ -1976,10 +1976,10 @@
     <t xml:space="preserve">10.4715642929077</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9078807830811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4314575195312</t>
+    <t xml:space="preserve">10.9078798294067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4314584732056</t>
   </si>
   <si>
     <t xml:space="preserve">11.0387735366821</t>
@@ -1991,25 +1991,25 @@
     <t xml:space="preserve">11.7456045150757</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5361728668213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5187215805054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6234359741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4489116668701</t>
+    <t xml:space="preserve">11.5361738204956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5187206268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6234369277954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4489107131958</t>
   </si>
   <si>
     <t xml:space="preserve">11.64089012146</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7281522750854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9201307296753</t>
+    <t xml:space="preserve">11.7281513214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.920129776001</t>
   </si>
   <si>
     <t xml:space="preserve">11.1173105239868</t>
@@ -2024,7 +2024,7 @@
     <t xml:space="preserve">10.7508068084717</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3319435119629</t>
+    <t xml:space="preserve">10.3319444656372</t>
   </si>
   <si>
     <t xml:space="preserve">10.1050596237183</t>
@@ -2036,10 +2036,10 @@
     <t xml:space="preserve">9.69297409057617</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7108907699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1408929824829</t>
+    <t xml:space="preserve">9.71089172363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1408939361572</t>
   </si>
   <si>
     <t xml:space="preserve">10.2663106918335</t>
@@ -2054,25 +2054,25 @@
     <t xml:space="preserve">10.1588106155396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0692253112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0871429443359</t>
+    <t xml:space="preserve">10.0692262649536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0871438980103</t>
   </si>
   <si>
     <t xml:space="preserve">10.4633951187134</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7858982086182</t>
+    <t xml:space="preserve">10.7858963012695</t>
   </si>
   <si>
     <t xml:space="preserve">10.5708961486816</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7142295837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7500638961792</t>
+    <t xml:space="preserve">10.7142305374146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7500629425049</t>
   </si>
   <si>
     <t xml:space="preserve">11.1621494293213</t>
@@ -2081,22 +2081,22 @@
     <t xml:space="preserve">10.8754816055298</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6425619125366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5888118743896</t>
+    <t xml:space="preserve">10.6425638198853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.588812828064</t>
   </si>
   <si>
     <t xml:space="preserve">10.5171461105347</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8575649261475</t>
+    <t xml:space="preserve">10.8575639724731</t>
   </si>
   <si>
     <t xml:space="preserve">10.9113149642944</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6067295074463</t>
+    <t xml:space="preserve">10.6067304611206</t>
   </si>
   <si>
     <t xml:space="preserve">10.6604795455933</t>
@@ -2105,22 +2105,22 @@
     <t xml:space="preserve">10.3021440505981</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4096441268921</t>
+    <t xml:space="preserve">10.4096450805664</t>
   </si>
   <si>
     <t xml:space="preserve">10.3558940887451</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6783962249756</t>
+    <t xml:space="preserve">10.6783971786499</t>
   </si>
   <si>
     <t xml:space="preserve">10.4275617599487</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5350618362427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1800661087036</t>
+    <t xml:space="preserve">10.535062789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1800651550293</t>
   </si>
   <si>
     <t xml:space="preserve">10.9829816818237</t>
@@ -2132,22 +2132,22 @@
     <t xml:space="preserve">11.3771505355835</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7354860305786</t>
+    <t xml:space="preserve">11.7354869842529</t>
   </si>
   <si>
     <t xml:space="preserve">11.9146537780762</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9325704574585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0221538543701</t>
+    <t xml:space="preserve">11.9325714111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0221548080444</t>
   </si>
   <si>
     <t xml:space="preserve">11.8788204193115</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2371559143066</t>
+    <t xml:space="preserve">12.2371549606323</t>
   </si>
   <si>
     <t xml:space="preserve">12.3267402648926</t>
@@ -2159,10 +2159,10 @@
     <t xml:space="preserve">12.0938215255737</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3984069824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2013216018677</t>
+    <t xml:space="preserve">12.3984079360962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.201322555542</t>
   </si>
   <si>
     <t xml:space="preserve">11.9863214492798</t>
@@ -2174,7 +2174,7 @@
     <t xml:space="preserve">12.6134080886841</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8463258743286</t>
+    <t xml:space="preserve">12.8463268280029</t>
   </si>
   <si>
     <t xml:space="preserve">12.810492515564</t>
@@ -2189,16 +2189,16 @@
     <t xml:space="preserve">13.4017457962036</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4375801086426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6884136199951</t>
+    <t xml:space="preserve">13.4375791549683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6884145736694</t>
   </si>
   <si>
     <t xml:space="preserve">13.9034156799316</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6559200286865</t>
+    <t xml:space="preserve">14.6559209823608</t>
   </si>
   <si>
     <t xml:space="preserve">14.2438344955444</t>
@@ -2207,7 +2207,7 @@
     <t xml:space="preserve">14.6380043029785</t>
   </si>
   <si>
-    <t xml:space="preserve">14.92467212677</t>
+    <t xml:space="preserve">14.9246711730957</t>
   </si>
   <si>
     <t xml:space="preserve">14.5125865936279</t>
@@ -2222,34 +2222,34 @@
     <t xml:space="preserve">14.5484189987183</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4946699142456</t>
+    <t xml:space="preserve">14.4946689605713</t>
   </si>
   <si>
     <t xml:space="preserve">14.2617511749268</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8888387680054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8171730041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3871688842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7634210586548</t>
+    <t xml:space="preserve">14.8888397216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8171720504761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.387167930603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7634191513062</t>
   </si>
   <si>
     <t xml:space="preserve">14.6200866699219</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9067544937134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1217546463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0321731567383</t>
+    <t xml:space="preserve">14.9067535400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1217555999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.032172203064</t>
   </si>
   <si>
     <t xml:space="preserve">14.7455034255981</t>
@@ -2258,22 +2258,22 @@
     <t xml:space="preserve">15.0500888824463</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0680046081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1038408279419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5305032730103</t>
+    <t xml:space="preserve">15.0680065155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1038398742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5305023193359</t>
   </si>
   <si>
     <t xml:space="preserve">14.7096710205078</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2080001831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6167478561401</t>
+    <t xml:space="preserve">14.2080011367798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6167469024658</t>
   </si>
   <si>
     <t xml:space="preserve">13.5092468261719</t>
@@ -2282,13 +2282,13 @@
     <t xml:space="preserve">13.0434112548828</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1688270568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9717435836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4700746536255</t>
+    <t xml:space="preserve">13.1688280105591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9717426300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4700736999512</t>
   </si>
   <si>
     <t xml:space="preserve">13.2404947280884</t>
@@ -2306,31 +2306,31 @@
     <t xml:space="preserve">13.4913301467896</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2225780487061</t>
+    <t xml:space="preserve">13.2225790023804</t>
   </si>
   <si>
     <t xml:space="preserve">13.2046613693237</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0613269805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0075778961182</t>
+    <t xml:space="preserve">13.0613279342651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0075769424438</t>
   </si>
   <si>
     <t xml:space="preserve">12.6313257217407</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0971612930298</t>
+    <t xml:space="preserve">13.0971603393555</t>
   </si>
   <si>
     <t xml:space="preserve">13.0792446136475</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8642435073853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9896593093872</t>
+    <t xml:space="preserve">12.8642425537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9896602630615</t>
   </si>
   <si>
     <t xml:space="preserve">12.9538269042969</t>
@@ -2345,16 +2345,16 @@
     <t xml:space="preserve">13.1150779724121</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1509122848511</t>
+    <t xml:space="preserve">13.1509113311768</t>
   </si>
   <si>
     <t xml:space="preserve">13.5271635055542</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3479948043823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.276328086853</t>
+    <t xml:space="preserve">13.3479957580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2763290405273</t>
   </si>
   <si>
     <t xml:space="preserve">12.7925758361816</t>
@@ -2366,22 +2366,22 @@
     <t xml:space="preserve">12.5238237380981</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5059080123901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4879894256592</t>
+    <t xml:space="preserve">12.5059070587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4879903793335</t>
   </si>
   <si>
     <t xml:space="preserve">12.3088226318359</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5417413711548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8284091949463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3804893493652</t>
+    <t xml:space="preserve">12.5417404174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8284101486206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3804903030396</t>
   </si>
   <si>
     <t xml:space="preserve">12.6671581268311</t>
@@ -2396,25 +2396,25 @@
     <t xml:space="preserve">12.7746591567993</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4342403411865</t>
+    <t xml:space="preserve">12.4342412948608</t>
   </si>
   <si>
     <t xml:space="preserve">11.9504880905151</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2192401885986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8250703811646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1117391586304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9684038162231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0400714874268</t>
+    <t xml:space="preserve">12.2192392349243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8250694274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1117382049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9684047698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0400705337524</t>
   </si>
   <si>
     <t xml:space="preserve">12.0042381286621</t>
@@ -2426,13 +2426,13 @@
     <t xml:space="preserve">12.7388257980347</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7421646118164</t>
+    <t xml:space="preserve">13.7421655654907</t>
   </si>
   <si>
     <t xml:space="preserve">13.7063312530518</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0825834274292</t>
+    <t xml:space="preserve">14.0825843811035</t>
   </si>
   <si>
     <t xml:space="preserve">14.0109167098999</t>
@@ -2450,7 +2450,7 @@
     <t xml:space="preserve">13.9392499923706</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6346635818481</t>
+    <t xml:space="preserve">13.6346645355225</t>
   </si>
   <si>
     <t xml:space="preserve">14.2796678543091</t>
@@ -2462,7 +2462,7 @@
     <t xml:space="preserve">13.9571657180786</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8496646881104</t>
+    <t xml:space="preserve">13.8496656417847</t>
   </si>
   <si>
     <t xml:space="preserve">13.9750833511353</t>
@@ -2471,7 +2471,7 @@
     <t xml:space="preserve">13.5450801849365</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4734134674072</t>
+    <t xml:space="preserve">13.4734125137329</t>
   </si>
   <si>
     <t xml:space="preserve">13.1867456436157</t>
@@ -2486,28 +2486,28 @@
     <t xml:space="preserve">12.7029914855957</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8429861068726</t>
+    <t xml:space="preserve">11.8429870605469</t>
   </si>
   <si>
     <t xml:space="preserve">11.7892360687256</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6817359924316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0759048461914</t>
+    <t xml:space="preserve">11.6817350387573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0759038925171</t>
   </si>
   <si>
     <t xml:space="preserve">11.5742359161377</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2159004211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3592348098755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4309024810791</t>
+    <t xml:space="preserve">11.2158994674683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3592338562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4309015274048</t>
   </si>
   <si>
     <t xml:space="preserve">11.3054838180542</t>
@@ -2516,13 +2516,13 @@
     <t xml:space="preserve">11.2875671386719</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6837844848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5179252624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2783527374268</t>
+    <t xml:space="preserve">11.683783531189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5179262161255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2783517837524</t>
   </si>
   <si>
     <t xml:space="preserve">11.1493520736694</t>
@@ -2534,7 +2534,7 @@
     <t xml:space="preserve">11.0756378173828</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9970712661743</t>
+    <t xml:space="preserve">11.9970722198486</t>
   </si>
   <si>
     <t xml:space="preserve">12.052357673645</t>
@@ -2543,7 +2543,7 @@
     <t xml:space="preserve">12.2735013961792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2182159423828</t>
+    <t xml:space="preserve">12.2182149887085</t>
   </si>
   <si>
     <t xml:space="preserve">12.4025020599365</t>
@@ -2555,7 +2555,7 @@
     <t xml:space="preserve">12.0707864761353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1629295349121</t>
+    <t xml:space="preserve">12.1629285812378</t>
   </si>
   <si>
     <t xml:space="preserve">12.1260719299316</t>
@@ -2570,13 +2570,13 @@
     <t xml:space="preserve">11.7759265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8312139511108</t>
+    <t xml:space="preserve">11.8312129974365</t>
   </si>
   <si>
     <t xml:space="preserve">11.9786424636841</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7206420898438</t>
+    <t xml:space="preserve">11.7206411361694</t>
   </si>
   <si>
     <t xml:space="preserve">11.868070602417</t>
@@ -2591,7 +2591,7 @@
     <t xml:space="preserve">11.4442110061646</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3520679473877</t>
+    <t xml:space="preserve">11.3520669937134</t>
   </si>
   <si>
     <t xml:space="preserve">11.3704957962036</t>
@@ -2609,7 +2609,7 @@
     <t xml:space="preserve">11.7022123336792</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5732126235962</t>
+    <t xml:space="preserve">11.5732116699219</t>
   </si>
   <si>
     <t xml:space="preserve">11.481068611145</t>
@@ -2618,7 +2618,7 @@
     <t xml:space="preserve">11.296781539917</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3152103424072</t>
+    <t xml:space="preserve">11.3152093887329</t>
   </si>
   <si>
     <t xml:space="preserve">11.5547828674316</t>
@@ -2627,7 +2627,7 @@
     <t xml:space="preserve">11.4257822036743</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3336391448975</t>
+    <t xml:space="preserve">11.3336381912231</t>
   </si>
   <si>
     <t xml:space="preserve">11.3889245986938</t>
@@ -2636,7 +2636,7 @@
     <t xml:space="preserve">11.4626398086548</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7943563461304</t>
+    <t xml:space="preserve">11.7943553924561</t>
   </si>
   <si>
     <t xml:space="preserve">12.1076431274414</t>
@@ -2666,7 +2666,7 @@
     <t xml:space="preserve">13.0290775299072</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2502212524414</t>
+    <t xml:space="preserve">13.2502222061157</t>
   </si>
   <si>
     <t xml:space="preserve">13.4160804748535</t>
@@ -2681,7 +2681,7 @@
     <t xml:space="preserve">12.6420755386353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8816471099854</t>
+    <t xml:space="preserve">12.8816480636597</t>
   </si>
   <si>
     <t xml:space="preserve">12.9185056686401</t>
@@ -2690,7 +2690,7 @@
     <t xml:space="preserve">13.194935798645</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1580781936646</t>
+    <t xml:space="preserve">13.1580772399902</t>
   </si>
   <si>
     <t xml:space="preserve">12.8079328536987</t>
@@ -2705,7 +2705,7 @@
     <t xml:space="preserve">12.5499315261841</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0843639373779</t>
+    <t xml:space="preserve">13.0843629837036</t>
   </si>
   <si>
     <t xml:space="preserve">13.3423643112183</t>
@@ -2723,13 +2723,13 @@
     <t xml:space="preserve">13.1027917861938</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3607931137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2133636474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5266523361206</t>
+    <t xml:space="preserve">13.3607940673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2133646011353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5266513824463</t>
   </si>
   <si>
     <t xml:space="preserve">13.6003665924072</t>
@@ -2747,28 +2747,28 @@
     <t xml:space="preserve">13.7846536636353</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0610837936401</t>
+    <t xml:space="preserve">14.0610828399658</t>
   </si>
   <si>
     <t xml:space="preserve">14.2637987136841</t>
   </si>
   <si>
-    <t xml:space="preserve">14.540228843689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6139430999756</t>
+    <t xml:space="preserve">14.5402297973633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6139440536499</t>
   </si>
   <si>
     <t xml:space="preserve">15.3695201873779</t>
   </si>
   <si>
-    <t xml:space="preserve">15.53537940979</t>
+    <t xml:space="preserve">15.5353784561157</t>
   </si>
   <si>
     <t xml:space="preserve">15.6275205612183</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5722341537476</t>
+    <t xml:space="preserve">15.5722360610962</t>
   </si>
   <si>
     <t xml:space="preserve">15.4063768386841</t>
@@ -2780,34 +2780,34 @@
     <t xml:space="preserve">15.295804977417</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2773771286011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4616641998291</t>
+    <t xml:space="preserve">15.2773761749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4616651535034</t>
   </si>
   <si>
     <t xml:space="preserve">15.6459493637085</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4432353973389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.664379119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7012367248535</t>
+    <t xml:space="preserve">15.4432344436646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6643781661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7012376785278</t>
   </si>
   <si>
     <t xml:space="preserve">15.6090936660767</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3326616287231</t>
+    <t xml:space="preserve">15.3326606750488</t>
   </si>
   <si>
     <t xml:space="preserve">15.2036619186401</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1668043136597</t>
+    <t xml:space="preserve">15.1668033599854</t>
   </si>
   <si>
     <t xml:space="preserve">14.8535175323486</t>
@@ -2828,22 +2828,22 @@
     <t xml:space="preserve">15.8302373886108</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7196636199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3879499435425</t>
+    <t xml:space="preserve">15.7196645736694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3879489898682</t>
   </si>
   <si>
     <t xml:space="preserve">15.5906648635864</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6828079223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7565231323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.738094329834</t>
+    <t xml:space="preserve">15.682806968689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7565221786499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7380933761597</t>
   </si>
   <si>
     <t xml:space="preserve">15.1483764648438</t>
@@ -2855,7 +2855,7 @@
     <t xml:space="preserve">15.1299476623535</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4800910949707</t>
+    <t xml:space="preserve">15.480092048645</t>
   </si>
   <si>
     <t xml:space="preserve">15.9223804473877</t>
@@ -2867,22 +2867,22 @@
     <t xml:space="preserve">16.0882377624512</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7749519348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8670930862427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7109384536743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6556520462036</t>
+    <t xml:space="preserve">15.7749509811401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.867094039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7109394073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6556529998779</t>
   </si>
   <si>
     <t xml:space="preserve">13.6372241973877</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1347980499268</t>
+    <t xml:space="preserve">14.1347990036011</t>
   </si>
   <si>
     <t xml:space="preserve">14.4480857849121</t>
@@ -2894,7 +2894,7 @@
     <t xml:space="preserve">14.0242261886597</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0795116424561</t>
+    <t xml:space="preserve">14.0795125961304</t>
   </si>
   <si>
     <t xml:space="preserve">14.0057973861694</t>
@@ -2915,7 +2915,7 @@
     <t xml:space="preserve">13.4897947311401</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6187944412231</t>
+    <t xml:space="preserve">13.6187953948975</t>
   </si>
   <si>
     <t xml:space="preserve">12.8263626098633</t>
@@ -2927,7 +2927,7 @@
     <t xml:space="preserve">13.2686500549316</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9369344711304</t>
+    <t xml:space="preserve">12.9369335174561</t>
   </si>
   <si>
     <t xml:space="preserve">12.9000768661499</t>
@@ -2936,10 +2936,10 @@
     <t xml:space="preserve">12.9922199249268</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0475063323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6973609924316</t>
+    <t xml:space="preserve">13.0475053787231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6973600387573</t>
   </si>
   <si>
     <t xml:space="preserve">12.6052179336548</t>
@@ -2951,7 +2951,7 @@
     <t xml:space="preserve">12.4209308624268</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4762163162231</t>
+    <t xml:space="preserve">12.4762172698975</t>
   </si>
   <si>
     <t xml:space="preserve">12.6236457824707</t>
@@ -3435,6 +3435,9 @@
   </si>
   <si>
     <t xml:space="preserve">18.6399993896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9200000762939</t>
   </si>
 </sst>
 </file>
@@ -68409,7 +68412,7 @@
     </row>
     <row r="2487">
       <c r="A2487" s="1" t="n">
-        <v>45940.6494444444</v>
+        <v>45940.2916666667</v>
       </c>
       <c r="B2487" t="n">
         <v>59492</v>
@@ -68430,6 +68433,32 @@
         <v>1140</v>
       </c>
       <c r="H2487" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2488">
+      <c r="A2488" s="1" t="n">
+        <v>45943.6495486111</v>
+      </c>
+      <c r="B2488" t="n">
+        <v>59931</v>
+      </c>
+      <c r="C2488" t="n">
+        <v>19.0200004577637</v>
+      </c>
+      <c r="D2488" t="n">
+        <v>18.6800003051758</v>
+      </c>
+      <c r="E2488" t="n">
+        <v>18.6800003051758</v>
+      </c>
+      <c r="F2488" t="n">
+        <v>18.9200000762939</v>
+      </c>
+      <c r="G2488" t="s">
+        <v>1141</v>
+      </c>
+      <c r="H2488" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ORS.MI.xlsx
+++ b/data/ORS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1142" uniqueCount="1142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1143" uniqueCount="1143">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,127 +38,127 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08406352996826</t>
+    <t xml:space="preserve">8.08406448364258</t>
   </si>
   <si>
     <t xml:space="preserve">ORS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98275804519653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06380081176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94223737716675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82472562789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93818521499634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90171670913696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03948783874512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92602872848511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86119413375854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82067251205444</t>
+    <t xml:space="preserve">7.98275852203369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06380176544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94223690032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82472467422485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93818616867065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9017162322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03948879241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92603063583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8611946105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82067203521729</t>
   </si>
   <si>
     <t xml:space="preserve">7.93413400650024</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02328014373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08811378479004</t>
+    <t xml:space="preserve">8.02328109741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08811473846436</t>
   </si>
   <si>
     <t xml:space="preserve">8.1448450088501</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69910860061646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80446481704712</t>
+    <t xml:space="preserve">7.69910669326782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8044638633728</t>
   </si>
   <si>
     <t xml:space="preserve">7.97465467453003</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01112365722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01517581939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79230785369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82877779006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34745407104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84093332290649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90982103347778</t>
+    <t xml:space="preserve">8.01112461090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01517677307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79230833053589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82877731323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34745311737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84093284606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90982055664062</t>
   </si>
   <si>
     <t xml:space="preserve">7.85714197158813</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78015232086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8449854850769</t>
+    <t xml:space="preserve">7.7801513671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84498643875122</t>
   </si>
   <si>
     <t xml:space="preserve">7.97870779037476</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88550710678101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95034170150757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00301837921143</t>
+    <t xml:space="preserve">7.88550615310669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95034313201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00302028656006</t>
   </si>
   <si>
     <t xml:space="preserve">8.01922798156738</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9179253578186</t>
+    <t xml:space="preserve">7.91792440414429</t>
   </si>
   <si>
     <t xml:space="preserve">8.1002721786499</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10432243347168</t>
+    <t xml:space="preserve">8.104323387146</t>
   </si>
   <si>
     <t xml:space="preserve">8.1853666305542</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20157432556152</t>
+    <t xml:space="preserve">8.20157527923584</t>
   </si>
   <si>
     <t xml:space="preserve">8.11242866516113</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07595920562744</t>
+    <t xml:space="preserve">8.07595825195312</t>
   </si>
   <si>
     <t xml:space="preserve">8.03138542175293</t>
@@ -176,7 +176,7 @@
     <t xml:space="preserve">8.12053298950195</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2583065032959</t>
+    <t xml:space="preserve">8.25830745697021</t>
   </si>
   <si>
     <t xml:space="preserve">8.42039203643799</t>
@@ -191,7 +191,7 @@
     <t xml:space="preserve">8.42849731445312</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52428913116455</t>
+    <t xml:space="preserve">8.52429008483887</t>
   </si>
   <si>
     <t xml:space="preserve">8.45921802520752</t>
@@ -203,43 +203,43 @@
     <t xml:space="preserve">8.60562801361084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53242492675781</t>
+    <t xml:space="preserve">8.5324239730835</t>
   </si>
   <si>
     <t xml:space="preserve">8.61376190185547</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67070007324219</t>
+    <t xml:space="preserve">8.67069911956787</t>
   </si>
   <si>
     <t xml:space="preserve">8.87404632568359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7927074432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90657997131348</t>
+    <t xml:space="preserve">8.79270553588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90658092498779</t>
   </si>
   <si>
     <t xml:space="preserve">8.86591243743896</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94725131988525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93911838531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78457260131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74390316009521</t>
+    <t xml:space="preserve">8.94725036621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93911743164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78457355499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74390411376953</t>
   </si>
   <si>
     <t xml:space="preserve">8.91471481323242</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92284965515137</t>
+    <t xml:space="preserve">8.92284870147705</t>
   </si>
   <si>
     <t xml:space="preserve">9.10992813110352</t>
@@ -251,85 +251,85 @@
     <t xml:space="preserve">9.11806297302246</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1343297958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15059757232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15873050689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7357702255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6788330078125</t>
+    <t xml:space="preserve">9.13432884216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15059852600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15873336791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73576927185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67883205413818</t>
   </si>
   <si>
     <t xml:space="preserve">8.85777854919434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72763633728027</t>
+    <t xml:space="preserve">8.72763538360596</t>
   </si>
   <si>
     <t xml:space="preserve">8.70323467254639</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66256618499756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69510078430176</t>
+    <t xml:space="preserve">8.66256523132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69510173797607</t>
   </si>
   <si>
     <t xml:space="preserve">8.6218957901001</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80084037780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77643966674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68696689605713</t>
+    <t xml:space="preserve">8.80084133148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77644062042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68696784973145</t>
   </si>
   <si>
     <t xml:space="preserve">8.54869174957275</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54055690765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58122730255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46735286712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51615428924561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49988842010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45108318328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63002967834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80897521972656</t>
+    <t xml:space="preserve">8.54055786132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58122825622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46735191345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51615715026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49988651275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45108509063721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63003063201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80897617340088</t>
   </si>
   <si>
     <t xml:space="preserve">8.89031410217285</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93098449707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96351718902588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0529899597168</t>
+    <t xml:space="preserve">8.93098258972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96351623535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05299091339111</t>
   </si>
   <si>
     <t xml:space="preserve">9.30514049530029</t>
@@ -338,7 +338,7 @@
     <t xml:space="preserve">9.10179424285889</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19126605987549</t>
+    <t xml:space="preserve">9.1912670135498</t>
   </si>
   <si>
     <t xml:space="preserve">9.35394382476807</t>
@@ -347,64 +347,64 @@
     <t xml:space="preserve">9.4759521484375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54915523529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5898265838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66303157806396</t>
+    <t xml:space="preserve">9.54915618896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58982563018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66303062438965</t>
   </si>
   <si>
     <t xml:space="preserve">9.71996688842773</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85824489593506</t>
+    <t xml:space="preserve">9.85824394226074</t>
   </si>
   <si>
     <t xml:space="preserve">10.0046539306641</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2405347824097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2486696243286</t>
+    <t xml:space="preserve">10.2405338287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2486686706543</t>
   </si>
   <si>
     <t xml:space="preserve">10.3381414413452</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5984258651733</t>
+    <t xml:space="preserve">10.598424911499</t>
   </si>
   <si>
     <t xml:space="preserve">10.4276142120361</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4032115936279</t>
+    <t xml:space="preserve">10.4032125473022</t>
   </si>
   <si>
     <t xml:space="preserve">10.5252199172974</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4601497650146</t>
+    <t xml:space="preserve">10.4601488113403</t>
   </si>
   <si>
     <t xml:space="preserve">10.5658893585205</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5821561813354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7773704528809</t>
+    <t xml:space="preserve">10.5821580886841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7773694992065</t>
   </si>
   <si>
     <t xml:space="preserve">10.9807157516479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8749761581421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6553640365601</t>
+    <t xml:space="preserve">10.8749771118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6553621292114</t>
   </si>
   <si>
     <t xml:space="preserve">10.6797637939453</t>
@@ -413,70 +413,70 @@
     <t xml:space="preserve">10.5740242004395</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5170860290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5414876937866</t>
+    <t xml:space="preserve">10.5170869827271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5414886474609</t>
   </si>
   <si>
     <t xml:space="preserve">10.5577564239502</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5089530944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8180389404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6878967285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.761100769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6472291946411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8993797302246</t>
+    <t xml:space="preserve">10.5089540481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.818039894104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6878976821899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7611026763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6472282409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.899377822876</t>
   </si>
   <si>
     <t xml:space="preserve">10.8831100463867</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6716289520264</t>
+    <t xml:space="preserve">10.6716299057007</t>
   </si>
   <si>
     <t xml:space="preserve">10.7367010116577</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0051183700562</t>
+    <t xml:space="preserve">11.0051193237305</t>
   </si>
   <si>
     <t xml:space="preserve">11.0213871002197</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1840648651123</t>
+    <t xml:space="preserve">11.1840629577637</t>
   </si>
   <si>
     <t xml:space="preserve">11.4036769866943</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3955430984497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3386068344116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.322338104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.330472946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3630094528198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0783224105835</t>
+    <t xml:space="preserve">11.395544052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3386077880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3223390579224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3304738998413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3630084991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0783243179321</t>
   </si>
   <si>
     <t xml:space="preserve">10.606559753418</t>
@@ -491,43 +491,43 @@
     <t xml:space="preserve">10.6390943527222</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4113454818726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2080011367798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2730703353882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2323999404907</t>
+    <t xml:space="preserve">10.4113464355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2080001831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2730712890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.232400894165</t>
   </si>
   <si>
     <t xml:space="preserve">10.3218746185303</t>
   </si>
   <si>
-    <t xml:space="preserve">10.370677947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3300065994263</t>
+    <t xml:space="preserve">10.3706769943237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3300085067749</t>
   </si>
   <si>
     <t xml:space="preserve">10.3056058883667</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2568044662476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1835966110229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4845523834229</t>
+    <t xml:space="preserve">10.2568035125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1835975646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4845504760742</t>
   </si>
   <si>
     <t xml:space="preserve">10.3625421524048</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4438819885254</t>
+    <t xml:space="preserve">10.4438810348511</t>
   </si>
   <si>
     <t xml:space="preserve">10.8587074279785</t>
@@ -536,19 +536,19 @@
     <t xml:space="preserve">10.9237794876099</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0376529693604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0620565414429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1027250289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1433944702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.175929069519</t>
+    <t xml:space="preserve">11.0376539230347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0620546340942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1027240753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1433935165405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1759300231934</t>
   </si>
   <si>
     <t xml:space="preserve">11.1352605819702</t>
@@ -557,151 +557,151 @@
     <t xml:space="preserve">11.0701904296875</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1189937591553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1515274047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2247314453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0457878112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5008182525635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1347951889038</t>
+    <t xml:space="preserve">11.118992805481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1515283584595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2247323989868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0457887649536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5008192062378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1347942352295</t>
   </si>
   <si>
     <t xml:space="preserve">8.36161231994629</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01999092102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10946273803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39414691925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21520328521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3372106552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31280899047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18266773223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34534454345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23960494995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49175548553467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5893611907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76017284393311</t>
+    <t xml:space="preserve">8.01998901367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10946369171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3941478729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2152042388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33721160888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31280994415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18266582489014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34534549713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23960399627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49175453186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58936023712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76017189025879</t>
   </si>
   <si>
     <t xml:space="preserve">8.29654216766357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25587177276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17453289031982</t>
+    <t xml:space="preserve">8.25587272644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17453384399414</t>
   </si>
   <si>
     <t xml:space="preserve">8.1908016204834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23147010803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2802734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14199924468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15826511383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16639995574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12166213989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05252552032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89798307418823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85731315612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93051671981812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90611553192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93865251541138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84917974472046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80850887298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62956476211548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57262754440308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48315572738647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66616678237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60516309738159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54009246826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52382326126099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47908735275269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61329698562622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54822492599487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56449365615845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5075569152832</t>
+    <t xml:space="preserve">8.23147106170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28027439117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14199733734131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15826606750488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16640090942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12166309356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05252647399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89798212051392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85731220245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93051719665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9061164855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93865156173706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8491792678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80851030349731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62956571578979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57262706756592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48315525054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66616773605347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60516357421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54009294509888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5238242149353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47908782958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61329650878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54822540283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56449413299561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50755548477173</t>
   </si>
   <si>
     <t xml:space="preserve">7.4668869972229</t>
@@ -710,43 +710,43 @@
     <t xml:space="preserve">7.49128913879395</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49942302703857</t>
+    <t xml:space="preserve">7.49942255020142</t>
   </si>
   <si>
     <t xml:space="preserve">7.31234502792358</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27980804443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37741422653198</t>
+    <t xml:space="preserve">7.27980852127075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3774151802063</t>
   </si>
   <si>
     <t xml:space="preserve">7.38554906845093</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36928129196167</t>
+    <t xml:space="preserve">7.36928033828735</t>
   </si>
   <si>
     <t xml:space="preserve">7.3204779624939</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34487915039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28794193267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04392671585083</t>
+    <t xml:space="preserve">7.34487962722778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28794240951538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04392528533936</t>
   </si>
   <si>
     <t xml:space="preserve">7.15780019760132</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39368343353271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42621898651123</t>
+    <t xml:space="preserve">7.3936824798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42621850967407</t>
   </si>
   <si>
     <t xml:space="preserve">7.40181636810303</t>
@@ -755,55 +755,55 @@
     <t xml:space="preserve">7.3042106628418</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36114835739136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20660400390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35301208496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33674669265747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27167463302612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23100471496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32861185073853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26354122161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23913955688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22287178039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24727344512939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44248533248901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25540637969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18220138549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29607582092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16593456268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14153337478638</t>
+    <t xml:space="preserve">7.3611478805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20660352706909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35301303863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33674573898315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27167367935181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23100566864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32861137390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26354026794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23913908004761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22287130355835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24727296829224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44248485565186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25540685653687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18220186233521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29607629776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16593408584595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14153242111206</t>
   </si>
   <si>
     <t xml:space="preserve">7.0520601272583</t>
@@ -815,13 +815,13 @@
     <t xml:space="preserve">7.0357928276062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01952505111694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87311458587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.677903175354</t>
+    <t xml:space="preserve">7.0195255279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87311410903931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67790365219116</t>
   </si>
   <si>
     <t xml:space="preserve">6.85124731063843</t>
@@ -830,10 +830,10 @@
     <t xml:space="preserve">6.93379163742065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26397323608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14841032028198</t>
+    <t xml:space="preserve">7.26397275924683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14840936660767</t>
   </si>
   <si>
     <t xml:space="preserve">7.09888315200806</t>
@@ -842,13 +842,13 @@
     <t xml:space="preserve">7.18142795562744</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16491889953613</t>
+    <t xml:space="preserve">7.16491937637329</t>
   </si>
   <si>
     <t xml:space="preserve">7.14015579223633</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21444654464722</t>
+    <t xml:space="preserve">7.21444606781006</t>
   </si>
   <si>
     <t xml:space="preserve">7.17317342758179</t>
@@ -860,46 +860,46 @@
     <t xml:space="preserve">6.84299325942993</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60361194610596</t>
+    <t xml:space="preserve">6.60361242294312</t>
   </si>
   <si>
     <t xml:space="preserve">6.62012100219727</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67790222167969</t>
+    <t xml:space="preserve">6.67790269851685</t>
   </si>
   <si>
     <t xml:space="preserve">6.80997467041016</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54583072662354</t>
+    <t xml:space="preserve">6.54583024978638</t>
   </si>
   <si>
     <t xml:space="preserve">6.31470394134521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32295894622803</t>
+    <t xml:space="preserve">6.32295846939087</t>
   </si>
   <si>
     <t xml:space="preserve">6.34772253036499</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38073968887329</t>
+    <t xml:space="preserve">6.38074016571045</t>
   </si>
   <si>
     <t xml:space="preserve">6.39724922180176</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47153997421265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28168678283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22390460968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09183216094971</t>
+    <t xml:space="preserve">6.4715404510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2816858291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22390413284302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09183263778687</t>
   </si>
   <si>
     <t xml:space="preserve">5.90197801589966</t>
@@ -908,214 +908,214 @@
     <t xml:space="preserve">5.9597601890564</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99277782440186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20739555358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14135980606079</t>
+    <t xml:space="preserve">5.9927773475647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20739507675171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14135932922363</t>
   </si>
   <si>
     <t xml:space="preserve">6.19088649749756</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14961338043213</t>
+    <t xml:space="preserve">6.14961290359497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0753231048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25692272186279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00928735733032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9845232963562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12485122680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13310480117798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27343082427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44677591323853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55408525466919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51281213760376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3642315864563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24041414260864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21565008163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23215913772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24866819381714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11659622192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10834074020386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05055952072144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89372396469116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77816104888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69561529159546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79466915130615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80292320251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82768821716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78641510009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73688745498657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85245180130005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29819536209106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1826319694519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15786838531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03405046463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08357715606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81943321228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91848707199097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86070537567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76165246963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75339651107788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8111777305603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70387077331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74514245986938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83594226837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71212482452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84419727325439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94325065612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96801471710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87721490859985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88546991348267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93499565124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02579545974731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06706857681274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38899421691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19914102554321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04230499267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05881452560425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95150566101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17437744140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17601919174194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29349803924561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25993251800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20958423614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0921049118042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10888910293579</t>
   </si>
   <si>
     <t xml:space="preserve">6.07532358169556</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25692272186279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00928735733032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9845232963562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12485027313232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13310527801514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27343082427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44677591323853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55408525466919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51281261444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36423110961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24041366577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21564960479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23215961456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24866771697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11659622192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10834074020386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05055952072144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89372444152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.778160572052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6956148147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79466915130615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80292367935181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82768774032593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78641510009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73688745498657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85245132446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29819536209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18263244628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15786790847778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03405046463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08357763290405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81943416595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91848659515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86070537567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76165246963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75339651107788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81117820739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70387077331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74514198303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83594226837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71212434768677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84419679641724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94325065612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96801424026489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87721490859985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88546943664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93499660491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02579593658447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06706857681274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3889946937561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19914054870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04230451583862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05881452560425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95150566101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17437744140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17601919174194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29349803924561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25993204116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20958423614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09210586547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10888910293579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0753231048584</t>
-  </si>
-  <si>
     <t xml:space="preserve">6.14245367050171</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0585412979126</t>
+    <t xml:space="preserve">6.05854082107544</t>
   </si>
   <si>
     <t xml:space="preserve">6.02497482299805</t>
@@ -1124,19 +1124,19 @@
     <t xml:space="preserve">5.97462749481201</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95784425735474</t>
+    <t xml:space="preserve">5.95784473419189</t>
   </si>
   <si>
     <t xml:space="preserve">6.15923690795898</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12567138671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19280195236206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42775964736938</t>
+    <t xml:space="preserve">6.12567090988159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19280242919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42775869369507</t>
   </si>
   <si>
     <t xml:space="preserve">6.71306467056274</t>
@@ -1151,25 +1151,25 @@
     <t xml:space="preserve">6.78019523620605</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7298469543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.629150390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56202030181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54523801803589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67949914932251</t>
+    <t xml:space="preserve">6.72984743118286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62915086746216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56202077865601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54523754119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67949867248535</t>
   </si>
   <si>
     <t xml:space="preserve">6.66271686553955</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57880306243896</t>
+    <t xml:space="preserve">6.57880353927612</t>
   </si>
   <si>
     <t xml:space="preserve">6.37741088867188</t>
@@ -1178,10 +1178,10 @@
     <t xml:space="preserve">6.34384632110596</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22636747360229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36062908172607</t>
+    <t xml:space="preserve">6.22636795043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36062860488892</t>
   </si>
   <si>
     <t xml:space="preserve">5.67253923416138</t>
@@ -1193,7 +1193,7 @@
     <t xml:space="preserve">5.68932199478149</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62219190597534</t>
+    <t xml:space="preserve">5.62219142913818</t>
   </si>
   <si>
     <t xml:space="preserve">5.53827810287476</t>
@@ -1202,43 +1202,43 @@
     <t xml:space="preserve">5.43758249282837</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45436525344849</t>
+    <t xml:space="preserve">5.45436573028564</t>
   </si>
   <si>
     <t xml:space="preserve">5.60540819168091</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5214958190918</t>
+    <t xml:space="preserve">5.52149534225464</t>
   </si>
   <si>
     <t xml:space="preserve">5.50471258163452</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48792934417725</t>
+    <t xml:space="preserve">5.4879298210144</t>
   </si>
   <si>
     <t xml:space="preserve">5.35366868972778</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37045049667358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42079925537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28653860092163</t>
+    <t xml:space="preserve">5.3704514503479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42079973220825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28653812408447</t>
   </si>
   <si>
     <t xml:space="preserve">5.30332088470459</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26975584030151</t>
+    <t xml:space="preserve">5.26975536346436</t>
   </si>
   <si>
     <t xml:space="preserve">5.38723421096802</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32010364532471</t>
+    <t xml:space="preserve">5.32010412216187</t>
   </si>
   <si>
     <t xml:space="preserve">5.65575647354126</t>
@@ -1253,7 +1253,7 @@
     <t xml:space="preserve">5.72288703918457</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73967027664185</t>
+    <t xml:space="preserve">5.739670753479</t>
   </si>
   <si>
     <t xml:space="preserve">5.6389741897583</t>
@@ -1262,16 +1262,16 @@
     <t xml:space="preserve">5.57184410095215</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18584203720093</t>
+    <t xml:space="preserve">5.18584156036377</t>
   </si>
   <si>
     <t xml:space="preserve">5.2026252746582</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21940803527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16906023025513</t>
+    <t xml:space="preserve">5.21940755844116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16905975341797</t>
   </si>
   <si>
     <t xml:space="preserve">5.13549327850342</t>
@@ -1283,7 +1283,7 @@
     <t xml:space="preserve">4.95088481903076</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03479862213135</t>
+    <t xml:space="preserve">5.03479909896851</t>
   </si>
   <si>
     <t xml:space="preserve">5.15227651596069</t>
@@ -1295,7 +1295,7 @@
     <t xml:space="preserve">5.06836318969727</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0851469039917</t>
+    <t xml:space="preserve">5.08514642715454</t>
   </si>
   <si>
     <t xml:space="preserve">5.23619031906128</t>
@@ -1304,16 +1304,16 @@
     <t xml:space="preserve">5.25297212600708</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33688640594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79001760482788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77323579788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58862638473511</t>
+    <t xml:space="preserve">5.33688688278198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79001808166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77323532104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58862590789795</t>
   </si>
   <si>
     <t xml:space="preserve">4.81662321090698</t>
@@ -1322,22 +1322,22 @@
     <t xml:space="preserve">4.79984140396118</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59844875335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36349201202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31314420700073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19566535949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11175203323364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02783823013306</t>
+    <t xml:space="preserve">4.59844827651978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36349153518677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31314373016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19566488265991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11175107955933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02783870697021</t>
   </si>
   <si>
     <t xml:space="preserve">4.17049074172974</t>
@@ -1352,7 +1352,7 @@
     <t xml:space="preserve">4.34670877456665</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17888164520264</t>
+    <t xml:space="preserve">4.17888212203979</t>
   </si>
   <si>
     <t xml:space="preserve">4.04462146759033</t>
@@ -1361,22 +1361,22 @@
     <t xml:space="preserve">4.15370845794678</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26279640197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16209983825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14531803131104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99427270889282</t>
+    <t xml:space="preserve">4.26279592514038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16210031509399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14531755447388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99427247047424</t>
   </si>
   <si>
     <t xml:space="preserve">4.09496927261353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98588180541992</t>
+    <t xml:space="preserve">3.98588156700134</t>
   </si>
   <si>
     <t xml:space="preserve">4.2795786857605</t>
@@ -1385,25 +1385,25 @@
     <t xml:space="preserve">4.22922992706299</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21244764328003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03622961044312</t>
+    <t xml:space="preserve">4.21244812011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03623008728027</t>
   </si>
   <si>
     <t xml:space="preserve">4.12877941131592</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16283130645752</t>
+    <t xml:space="preserve">4.1628303527832</t>
   </si>
   <si>
     <t xml:space="preserve">4.07770156860352</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00108432769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20539569854736</t>
+    <t xml:space="preserve">4.00108480453491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20539522171021</t>
   </si>
   <si>
     <t xml:space="preserve">4.37565469741821</t>
@@ -1418,22 +1418,22 @@
     <t xml:space="preserve">4.25647354125977</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24796056747437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32457637786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30755138397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23944711685181</t>
+    <t xml:space="preserve">4.24795961380005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32457685470581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30755090713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23944759368896</t>
   </si>
   <si>
     <t xml:space="preserve">4.35862827301025</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51186180114746</t>
+    <t xml:space="preserve">4.5118613243103</t>
   </si>
   <si>
     <t xml:space="preserve">5.5334153175354</t>
@@ -1448,7 +1448,7 @@
     <t xml:space="preserve">5.73772573471069</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55044078826904</t>
+    <t xml:space="preserve">5.5504412651062</t>
   </si>
   <si>
     <t xml:space="preserve">5.5844931602478</t>
@@ -1463,10 +1463,10 @@
     <t xml:space="preserve">5.2610011100769</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48233795166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4482855796814</t>
+    <t xml:space="preserve">5.482337474823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44828605651855</t>
   </si>
   <si>
     <t xml:space="preserve">5.6015191078186</t>
@@ -1475,43 +1475,43 @@
     <t xml:space="preserve">5.66962242126465</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51638984680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70367431640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32910490036011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27802658081055</t>
+    <t xml:space="preserve">5.5163893699646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70367383956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32910442352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27802705764771</t>
   </si>
   <si>
     <t xml:space="preserve">5.43126010894775</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31207847595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22694873809814</t>
+    <t xml:space="preserve">5.31207799911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2269492149353</t>
   </si>
   <si>
     <t xml:space="preserve">5.00561237335205</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95453548431396</t>
+    <t xml:space="preserve">4.95453500747681</t>
   </si>
   <si>
     <t xml:space="preserve">4.93750905990601</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05669021606445</t>
+    <t xml:space="preserve">5.05669069290161</t>
   </si>
   <si>
     <t xml:space="preserve">5.03966474533081</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97156095504761</t>
+    <t xml:space="preserve">4.97156143188477</t>
   </si>
   <si>
     <t xml:space="preserve">4.8864312171936</t>
@@ -1523,7 +1523,7 @@
     <t xml:space="preserve">4.92048311233521</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9034571647644</t>
+    <t xml:space="preserve">4.90345764160156</t>
   </si>
   <si>
     <t xml:space="preserve">4.852379322052</t>
@@ -1532,10 +1532,10 @@
     <t xml:space="preserve">4.8694052696228</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34613037109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2439751625061</t>
+    <t xml:space="preserve">5.34613084793091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24397468566895</t>
   </si>
   <si>
     <t xml:space="preserve">5.36315679550171</t>
@@ -1547,10 +1547,10 @@
     <t xml:space="preserve">5.2099232673645</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15884637832642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10776805877686</t>
+    <t xml:space="preserve">5.1588454246521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1077675819397</t>
   </si>
   <si>
     <t xml:space="preserve">4.98858737945557</t>
@@ -1559,19 +1559,19 @@
     <t xml:space="preserve">5.09074211120605</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1928973197937</t>
+    <t xml:space="preserve">5.19289779663086</t>
   </si>
   <si>
     <t xml:space="preserve">5.1758713722229</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1418194770813</t>
+    <t xml:space="preserve">5.14181995391846</t>
   </si>
   <si>
     <t xml:space="preserve">5.07371664047241</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68212032318115</t>
+    <t xml:space="preserve">4.68212080001831</t>
   </si>
   <si>
     <t xml:space="preserve">4.54591369628906</t>
@@ -1589,7 +1589,7 @@
     <t xml:space="preserve">4.78427600860596</t>
   </si>
   <si>
-    <t xml:space="preserve">4.767249584198</t>
+    <t xml:space="preserve">4.76725006103516</t>
   </si>
   <si>
     <t xml:space="preserve">4.81832790374756</t>
@@ -1598,13 +1598,13 @@
     <t xml:space="preserve">4.8013014793396</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39720869064331</t>
+    <t xml:space="preserve">5.39720821380615</t>
   </si>
   <si>
     <t xml:space="preserve">5.61854457855225</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4653115272522</t>
+    <t xml:space="preserve">5.46531200408936</t>
   </si>
   <si>
     <t xml:space="preserve">5.49936389923096</t>
@@ -1613,7 +1613,7 @@
     <t xml:space="preserve">5.63557100296021</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68664789199829</t>
+    <t xml:space="preserve">5.68664836883545</t>
   </si>
   <si>
     <t xml:space="preserve">5.65259647369385</t>
@@ -1622,7 +1622,7 @@
     <t xml:space="preserve">5.8569073677063</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87393283843994</t>
+    <t xml:space="preserve">5.8739333152771</t>
   </si>
   <si>
     <t xml:space="preserve">6.31660652160645</t>
@@ -1634,13 +1634,13 @@
     <t xml:space="preserve">6.29958057403564</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35065841674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43578767776489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55496835708618</t>
+    <t xml:space="preserve">6.35065793991089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43578720092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55496883392334</t>
   </si>
   <si>
     <t xml:space="preserve">6.69117641448975</t>
@@ -1649,10 +1649,10 @@
     <t xml:space="preserve">6.79333162307739</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15087509155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08277082443237</t>
+    <t xml:space="preserve">7.15087461471558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08277177810669</t>
   </si>
   <si>
     <t xml:space="preserve">6.87846088409424</t>
@@ -1661,13 +1661,13 @@
     <t xml:space="preserve">6.77630567550659</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84440898895264</t>
+    <t xml:space="preserve">6.84440946578979</t>
   </si>
   <si>
     <t xml:space="preserve">6.70820236206055</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75927972793579</t>
+    <t xml:space="preserve">6.75928020477295</t>
   </si>
   <si>
     <t xml:space="preserve">6.53794288635254</t>
@@ -1676,16 +1676,16 @@
     <t xml:space="preserve">6.72522783279419</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6571249961853</t>
+    <t xml:space="preserve">6.65712404251099</t>
   </si>
   <si>
     <t xml:space="preserve">6.91251277923584</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89548635482788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96359014511108</t>
+    <t xml:space="preserve">6.8954873085022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96359062194824</t>
   </si>
   <si>
     <t xml:space="preserve">7.17302179336548</t>
@@ -1694,19 +1694,19 @@
     <t xml:space="preserve">7.05085325241089</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12066411972046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57443284988403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97584199905396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0281982421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0631046295166</t>
+    <t xml:space="preserve">7.1206636428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57443237304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97584247589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02819919586182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06310558319092</t>
   </si>
   <si>
     <t xml:space="preserve">7.99329423904419</t>
@@ -1718,40 +1718,40 @@
     <t xml:space="preserve">7.94093704223633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13291454315186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15036869049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16782093048096</t>
+    <t xml:space="preserve">8.13291358947754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15036773681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16781997680664</t>
   </si>
   <si>
     <t xml:space="preserve">8.18527412414551</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34234619140625</t>
+    <t xml:space="preserve">8.34234714508057</t>
   </si>
   <si>
     <t xml:space="preserve">8.11546325683594</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25508308410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08055782318115</t>
+    <t xml:space="preserve">8.25508213043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08055686950684</t>
   </si>
   <si>
     <t xml:space="preserve">8.20272541046143</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95838928222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37725257873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3248929977417</t>
+    <t xml:space="preserve">7.95838832855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37725162506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32489395141602</t>
   </si>
   <si>
     <t xml:space="preserve">8.81356716156006</t>
@@ -1760,19 +1760,19 @@
     <t xml:space="preserve">8.58668327331543</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53432559967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69139862060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60413646697998</t>
+    <t xml:space="preserve">8.53432369232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69139957427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60413551330566</t>
   </si>
   <si>
     <t xml:space="preserve">8.72630405426025</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42960929870605</t>
+    <t xml:space="preserve">8.42961025238037</t>
   </si>
   <si>
     <t xml:space="preserve">8.28998851776123</t>
@@ -1784,64 +1784,64 @@
     <t xml:space="preserve">8.04565238952637</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85367345809937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41215801239014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22017765045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44706153869629</t>
+    <t xml:space="preserve">7.85367298126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41215705871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22017860412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44706249237061</t>
   </si>
   <si>
     <t xml:space="preserve">8.3597993850708</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09800910949707</t>
+    <t xml:space="preserve">8.09801006317139</t>
   </si>
   <si>
     <t xml:space="preserve">8.23763084411621</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48196792602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62158870697021</t>
+    <t xml:space="preserve">8.48196697235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6215877532959</t>
   </si>
   <si>
     <t xml:space="preserve">8.55177783966064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.656494140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51687240600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46451377868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49942016601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56923007965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99161720275879</t>
+    <t xml:space="preserve">8.65649318695068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51687335968018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46451473236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49941921234131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5692310333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99161815643311</t>
   </si>
   <si>
     <t xml:space="preserve">9.59893417358398</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77345943450928</t>
+    <t xml:space="preserve">9.77346038818359</t>
   </si>
   <si>
     <t xml:space="preserve">9.8170919418335</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29351329803467</t>
+    <t xml:space="preserve">9.29351425170898</t>
   </si>
   <si>
     <t xml:space="preserve">9.46804046630859</t>
@@ -1850,16 +1850,16 @@
     <t xml:space="preserve">9.55530261993408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64256477355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90435600280762</t>
+    <t xml:space="preserve">9.64256572723389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90435409545898</t>
   </si>
   <si>
     <t xml:space="preserve">9.33714485168457</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9479866027832</t>
+    <t xml:space="preserve">9.94798564910889</t>
   </si>
   <si>
     <t xml:space="preserve">9.86072254180908</t>
@@ -1877,10 +1877,10 @@
     <t xml:space="preserve">10.6024580001831</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8206167221069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7333536148071</t>
+    <t xml:space="preserve">10.8206176757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7333545684814</t>
   </si>
   <si>
     <t xml:space="preserve">10.7769861221313</t>
@@ -1889,16 +1889,16 @@
     <t xml:space="preserve">10.2970390319824</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3843011856079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3406715393066</t>
+    <t xml:space="preserve">10.3843002319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3406705856323</t>
   </si>
   <si>
     <t xml:space="preserve">10.2097749710083</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2534065246582</t>
+    <t xml:space="preserve">10.2534074783325</t>
   </si>
   <si>
     <t xml:space="preserve">10.0788812637329</t>
@@ -1907,16 +1907,16 @@
     <t xml:space="preserve">9.51167106628418</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72982883453369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68619823455811</t>
+    <t xml:space="preserve">9.72982788085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68619728088379</t>
   </si>
   <si>
     <t xml:space="preserve">8.98809337615967</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42440795898438</t>
+    <t xml:space="preserve">9.42440891265869</t>
   </si>
   <si>
     <t xml:space="preserve">11.6496162414551</t>
@@ -1928,22 +1928,22 @@
     <t xml:space="preserve">11.7805099487305</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9114046096802</t>
+    <t xml:space="preserve">11.9114036560059</t>
   </si>
   <si>
     <t xml:space="preserve">11.9550361633301</t>
   </si>
   <si>
-    <t xml:space="preserve">11.693247795105</t>
+    <t xml:space="preserve">11.6932458877563</t>
   </si>
   <si>
     <t xml:space="preserve">12.3040895462036</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2604560852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2168245315552</t>
+    <t xml:space="preserve">12.2604570388794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2168254852295</t>
   </si>
   <si>
     <t xml:space="preserve">12.3913507461548</t>
@@ -1955,7 +1955,7 @@
     <t xml:space="preserve">11.8677730560303</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6059837341309</t>
+    <t xml:space="preserve">11.6059846878052</t>
   </si>
   <si>
     <t xml:space="preserve">10.9515113830566</t>
@@ -1967,10 +1967,10 @@
     <t xml:space="preserve">11.3005638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3441944122314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9951429367065</t>
+    <t xml:space="preserve">11.3441953659058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9951438903809</t>
   </si>
   <si>
     <t xml:space="preserve">10.4715642929077</t>
@@ -1979,22 +1979,22 @@
     <t xml:space="preserve">10.9078798294067</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4314584732056</t>
+    <t xml:space="preserve">11.4314575195312</t>
   </si>
   <si>
     <t xml:space="preserve">11.0387735366821</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9899415969849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7456045150757</t>
+    <t xml:space="preserve">11.9899406433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.74560546875</t>
   </si>
   <si>
     <t xml:space="preserve">11.5361738204956</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5187206268311</t>
+    <t xml:space="preserve">11.5187215805054</t>
   </si>
   <si>
     <t xml:space="preserve">11.6234369277954</t>
@@ -2006,22 +2006,22 @@
     <t xml:space="preserve">11.64089012146</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7281513214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.920129776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1173105239868</t>
+    <t xml:space="preserve">11.7281522750854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9201307296753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1173114776611</t>
   </si>
   <si>
     <t xml:space="preserve">11.0998592376709</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8031644821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7508068084717</t>
+    <t xml:space="preserve">10.8031635284424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7508058547974</t>
   </si>
   <si>
     <t xml:space="preserve">10.3319444656372</t>
@@ -2030,16 +2030,16 @@
     <t xml:space="preserve">10.1050596237183</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81839179992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69297409057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71089172363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1408939361572</t>
+    <t xml:space="preserve">9.81839275360107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69297313690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7108907699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1408929824829</t>
   </si>
   <si>
     <t xml:space="preserve">10.2663106918335</t>
@@ -2051,19 +2051,19 @@
     <t xml:space="preserve">10.1229763031006</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1588106155396</t>
+    <t xml:space="preserve">10.1588096618652</t>
   </si>
   <si>
     <t xml:space="preserve">10.0692262649536</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0871438980103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4633951187134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7858963012695</t>
+    <t xml:space="preserve">10.0871429443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4633960723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7858972549438</t>
   </si>
   <si>
     <t xml:space="preserve">10.5708961486816</t>
@@ -2072,7 +2072,7 @@
     <t xml:space="preserve">10.7142305374146</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7500629425049</t>
+    <t xml:space="preserve">10.7500638961792</t>
   </si>
   <si>
     <t xml:space="preserve">11.1621494293213</t>
@@ -2081,34 +2081,34 @@
     <t xml:space="preserve">10.8754816055298</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6425638198853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.588812828064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5171461105347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8575639724731</t>
+    <t xml:space="preserve">10.6425628662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5888118743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5171451568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8575649261475</t>
   </si>
   <si>
     <t xml:space="preserve">10.9113149642944</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6067304611206</t>
+    <t xml:space="preserve">10.6067295074463</t>
   </si>
   <si>
     <t xml:space="preserve">10.6604795455933</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3021440505981</t>
+    <t xml:space="preserve">10.3021450042725</t>
   </si>
   <si>
     <t xml:space="preserve">10.4096450805664</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3558940887451</t>
+    <t xml:space="preserve">10.3558950424194</t>
   </si>
   <si>
     <t xml:space="preserve">10.6783971786499</t>
@@ -2120,7 +2120,7 @@
     <t xml:space="preserve">10.535062789917</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1800651550293</t>
+    <t xml:space="preserve">11.1800661087036</t>
   </si>
   <si>
     <t xml:space="preserve">10.9829816818237</t>
@@ -2138,7 +2138,7 @@
     <t xml:space="preserve">11.9146537780762</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9325714111328</t>
+    <t xml:space="preserve">11.9325704574585</t>
   </si>
   <si>
     <t xml:space="preserve">12.0221548080444</t>
@@ -2147,10 +2147,10 @@
     <t xml:space="preserve">11.8788204193115</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2371549606323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3267402648926</t>
+    <t xml:space="preserve">12.2371559143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3267393112183</t>
   </si>
   <si>
     <t xml:space="preserve">12.4521570205688</t>
@@ -2159,7 +2159,7 @@
     <t xml:space="preserve">12.0938215255737</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3984079360962</t>
+    <t xml:space="preserve">12.3984069824219</t>
   </si>
   <si>
     <t xml:space="preserve">12.201322555542</t>
@@ -2186,7 +2186,7 @@
     <t xml:space="preserve">13.258412361145</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4017457962036</t>
+    <t xml:space="preserve">13.4017467498779</t>
   </si>
   <si>
     <t xml:space="preserve">13.4375791549683</t>
@@ -2195,19 +2195,19 @@
     <t xml:space="preserve">13.6884145736694</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9034156799316</t>
+    <t xml:space="preserve">13.903416633606</t>
   </si>
   <si>
     <t xml:space="preserve">14.6559209823608</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2438344955444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6380043029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9246711730957</t>
+    <t xml:space="preserve">14.2438335418701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6380033493042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.92467212677</t>
   </si>
   <si>
     <t xml:space="preserve">14.5125865936279</t>
@@ -2228,16 +2228,16 @@
     <t xml:space="preserve">14.2617511749268</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8888397216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8171720504761</t>
+    <t xml:space="preserve">14.8888387680054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8171710968018</t>
   </si>
   <si>
     <t xml:space="preserve">14.387167930603</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7634191513062</t>
+    <t xml:space="preserve">14.7634201049805</t>
   </si>
   <si>
     <t xml:space="preserve">14.6200866699219</t>
@@ -2246,10 +2246,10 @@
     <t xml:space="preserve">14.9067535400391</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1217555999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.032172203064</t>
+    <t xml:space="preserve">15.1217546463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0321741104126</t>
   </si>
   <si>
     <t xml:space="preserve">14.7455034255981</t>
@@ -2288,13 +2288,13 @@
     <t xml:space="preserve">12.9717426300049</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4700736999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2404947280884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6525812149048</t>
+    <t xml:space="preserve">12.4700746536255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2404956817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6525802612305</t>
   </si>
   <si>
     <t xml:space="preserve">13.5809135437012</t>
@@ -2306,22 +2306,22 @@
     <t xml:space="preserve">13.4913301467896</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2225790023804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2046613693237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0613279342651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0075769424438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6313257217407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0971603393555</t>
+    <t xml:space="preserve">13.2225780487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2046604156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0613269805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0075778961182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6313247680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0971612930298</t>
   </si>
   <si>
     <t xml:space="preserve">13.0792446136475</t>
@@ -2357,13 +2357,13 @@
     <t xml:space="preserve">13.2763290405273</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7925758361816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5954914093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5238237380981</t>
+    <t xml:space="preserve">12.7925748825073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5954923629761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5238246917725</t>
   </si>
   <si>
     <t xml:space="preserve">12.5059070587158</t>
@@ -2375,10 +2375,10 @@
     <t xml:space="preserve">12.3088226318359</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5417404174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8284101486206</t>
+    <t xml:space="preserve">12.5417413711548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8284091949463</t>
   </si>
   <si>
     <t xml:space="preserve">12.3804903030396</t>
@@ -2396,10 +2396,10 @@
     <t xml:space="preserve">12.7746591567993</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4342412948608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9504880905151</t>
+    <t xml:space="preserve">12.4342403411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9504871368408</t>
   </si>
   <si>
     <t xml:space="preserve">12.2192392349243</t>
@@ -2414,7 +2414,7 @@
     <t xml:space="preserve">11.9684047698975</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0400705337524</t>
+    <t xml:space="preserve">12.0400714874268</t>
   </si>
   <si>
     <t xml:space="preserve">12.0042381286621</t>
@@ -2423,7 +2423,7 @@
     <t xml:space="preserve">12.255072593689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7388257980347</t>
+    <t xml:space="preserve">12.7388248443604</t>
   </si>
   <si>
     <t xml:space="preserve">13.7421655654907</t>
@@ -2432,10 +2432,10 @@
     <t xml:space="preserve">13.7063312530518</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0825843811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0109167098999</t>
+    <t xml:space="preserve">14.0825834274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0109157562256</t>
   </si>
   <si>
     <t xml:space="preserve">13.7242479324341</t>
@@ -2444,10 +2444,10 @@
     <t xml:space="preserve">14.0467500686646</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0646667480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9392499923706</t>
+    <t xml:space="preserve">14.0646657943726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9392490386963</t>
   </si>
   <si>
     <t xml:space="preserve">13.6346645355225</t>
@@ -2471,10 +2471,10 @@
     <t xml:space="preserve">13.5450801849365</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4734125137329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1867456436157</t>
+    <t xml:space="preserve">13.4734134674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1867446899414</t>
   </si>
   <si>
     <t xml:space="preserve">13.3838291168213</t>
@@ -2483,7 +2483,7 @@
     <t xml:space="preserve">13.5988302230835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7029914855957</t>
+    <t xml:space="preserve">12.70299243927</t>
   </si>
   <si>
     <t xml:space="preserve">11.8429870605469</t>
@@ -2492,16 +2492,16 @@
     <t xml:space="preserve">11.7892360687256</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6817350387573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0759038925171</t>
+    <t xml:space="preserve">11.6817359924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0759048461914</t>
   </si>
   <si>
     <t xml:space="preserve">11.5742359161377</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2158994674683</t>
+    <t xml:space="preserve">11.2159004211426</t>
   </si>
   <si>
     <t xml:space="preserve">11.3592338562012</t>
@@ -2510,7 +2510,7 @@
     <t xml:space="preserve">11.4309015274048</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3054838180542</t>
+    <t xml:space="preserve">11.3054828643799</t>
   </si>
   <si>
     <t xml:space="preserve">11.2875671386719</t>
@@ -3438,6 +3438,9 @@
   </si>
   <si>
     <t xml:space="preserve">18.9200000762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2800006866455</t>
   </si>
 </sst>
 </file>
@@ -68438,7 +68441,7 @@
     </row>
     <row r="2488">
       <c r="A2488" s="1" t="n">
-        <v>45943.6495486111</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B2488" t="n">
         <v>59931</v>
@@ -68459,6 +68462,32 @@
         <v>1141</v>
       </c>
       <c r="H2488" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" s="1" t="n">
+        <v>45944.6496296296</v>
+      </c>
+      <c r="B2489" t="n">
+        <v>56494</v>
+      </c>
+      <c r="C2489" t="n">
+        <v>18.8199996948242</v>
+      </c>
+      <c r="D2489" t="n">
+        <v>18.1399993896484</v>
+      </c>
+      <c r="E2489" t="n">
+        <v>18.8199996948242</v>
+      </c>
+      <c r="F2489" t="n">
+        <v>18.2800006866455</v>
+      </c>
+      <c r="G2489" t="s">
+        <v>1142</v>
+      </c>
+      <c r="H2489" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ORS.MI.xlsx
+++ b/data/ORS.MI.xlsx
@@ -38,70 +38,70 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08406448364258</t>
+    <t xml:space="preserve">8.08406352996826</t>
   </si>
   <si>
     <t xml:space="preserve">ORS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98275852203369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06380176544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94223690032959</t>
+    <t xml:space="preserve">7.98275804519653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06380271911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94223785400391</t>
   </si>
   <si>
     <t xml:space="preserve">7.82472467422485</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93818616867065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9017162322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03948879241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92603063583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8611946105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82067203521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93413400650024</t>
+    <t xml:space="preserve">7.93818521499634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90171527862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03948974609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92602872848511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86119508743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8206729888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93413257598877</t>
   </si>
   <si>
     <t xml:space="preserve">8.02328109741211</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08811473846436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1448450088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69910669326782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8044638633728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97465467453003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01112461090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01517677307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79230833053589</t>
+    <t xml:space="preserve">8.08811569213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14484596252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69910860061646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80446434020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97465562820435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0111255645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01517581939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79230785369873</t>
   </si>
   <si>
     <t xml:space="preserve">7.82877731323242</t>
@@ -110,28 +110,28 @@
     <t xml:space="preserve">8.34745311737061</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84093284606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90982055664062</t>
+    <t xml:space="preserve">7.84093332290649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90982103347778</t>
   </si>
   <si>
     <t xml:space="preserve">7.85714197158813</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7801513671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84498643875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97870779037476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88550615310669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95034313201904</t>
+    <t xml:space="preserve">7.78015184402466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8449854850769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9787073135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88550662994385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95034217834473</t>
   </si>
   <si>
     <t xml:space="preserve">8.00302028656006</t>
@@ -146,22 +146,22 @@
     <t xml:space="preserve">8.1002721786499</t>
   </si>
   <si>
-    <t xml:space="preserve">8.104323387146</t>
+    <t xml:space="preserve">8.10432434082031</t>
   </si>
   <si>
     <t xml:space="preserve">8.1853666305542</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20157527923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11242866516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07595825195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03138542175293</t>
+    <t xml:space="preserve">8.20157623291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11242961883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07596015930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03138446807861</t>
   </si>
   <si>
     <t xml:space="preserve">8.09622001647949</t>
@@ -170,13 +170,13 @@
     <t xml:space="preserve">8.17726230621338</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05569839477539</t>
+    <t xml:space="preserve">8.05569744110107</t>
   </si>
   <si>
     <t xml:space="preserve">8.12053298950195</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25830745697021</t>
+    <t xml:space="preserve">8.25830554962158</t>
   </si>
   <si>
     <t xml:space="preserve">8.42039203643799</t>
@@ -185,19 +185,19 @@
     <t xml:space="preserve">8.67162704467773</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55816650390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42849731445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52429008483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45921802520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50802040100098</t>
+    <t xml:space="preserve">8.55816555023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42849826812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52429103851318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4592170715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50802230834961</t>
   </si>
   <si>
     <t xml:space="preserve">8.60562801361084</t>
@@ -206,7 +206,7 @@
     <t xml:space="preserve">8.5324239730835</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61376190185547</t>
+    <t xml:space="preserve">8.61376094818115</t>
   </si>
   <si>
     <t xml:space="preserve">8.67069911956787</t>
@@ -215,25 +215,25 @@
     <t xml:space="preserve">8.87404632568359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79270553588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90658092498779</t>
+    <t xml:space="preserve">8.7927074432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90657997131348</t>
   </si>
   <si>
     <t xml:space="preserve">8.86591243743896</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94725036621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93911743164062</t>
+    <t xml:space="preserve">8.94725131988525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93911647796631</t>
   </si>
   <si>
     <t xml:space="preserve">8.78457355499268</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74390411376953</t>
+    <t xml:space="preserve">8.74390316009521</t>
   </si>
   <si>
     <t xml:space="preserve">8.91471481323242</t>
@@ -242,40 +242,40 @@
     <t xml:space="preserve">8.92284870147705</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10992813110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.077392578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11806297302246</t>
+    <t xml:space="preserve">9.10992908477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07739162445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11806106567383</t>
   </si>
   <si>
     <t xml:space="preserve">9.13432884216309</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15059852600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15873336791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73576927185059</t>
+    <t xml:space="preserve">9.15059757232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15873146057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7357702255249</t>
   </si>
   <si>
     <t xml:space="preserve">8.67883205413818</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85777854919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72763538360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70323467254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66256523132324</t>
+    <t xml:space="preserve">8.85777759552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72763633728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7032356262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66256713867188</t>
   </si>
   <si>
     <t xml:space="preserve">8.69510173797607</t>
@@ -287,52 +287,52 @@
     <t xml:space="preserve">8.80084133148193</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77644062042236</t>
+    <t xml:space="preserve">8.77643871307373</t>
   </si>
   <si>
     <t xml:space="preserve">8.68696784973145</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54869174957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54055786132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58122825622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46735191345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51615715026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49988651275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45108509063721</t>
+    <t xml:space="preserve">8.54869079589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54055690765381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58122730255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46735382080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51615619659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49988746643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45108413696289</t>
   </si>
   <si>
     <t xml:space="preserve">8.63003063201904</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80897617340088</t>
+    <t xml:space="preserve">8.80897521972656</t>
   </si>
   <si>
     <t xml:space="preserve">8.89031410217285</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93098258972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96351623535156</t>
+    <t xml:space="preserve">8.930983543396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9635181427002</t>
   </si>
   <si>
     <t xml:space="preserve">9.05299091339111</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30514049530029</t>
+    <t xml:space="preserve">9.30514144897461</t>
   </si>
   <si>
     <t xml:space="preserve">9.10179424285889</t>
@@ -341,7 +341,7 @@
     <t xml:space="preserve">9.1912670135498</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35394382476807</t>
+    <t xml:space="preserve">9.35394287109375</t>
   </si>
   <si>
     <t xml:space="preserve">9.4759521484375</t>
@@ -353,19 +353,19 @@
     <t xml:space="preserve">9.58982563018799</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66303062438965</t>
+    <t xml:space="preserve">9.66303157806396</t>
   </si>
   <si>
     <t xml:space="preserve">9.71996688842773</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85824394226074</t>
+    <t xml:space="preserve">9.85824298858643</t>
   </si>
   <si>
     <t xml:space="preserve">10.0046539306641</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2405338287354</t>
+    <t xml:space="preserve">10.2405347824097</t>
   </si>
   <si>
     <t xml:space="preserve">10.2486686706543</t>
@@ -377,10 +377,10 @@
     <t xml:space="preserve">10.598424911499</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4276142120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4032125473022</t>
+    <t xml:space="preserve">10.4276151657104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4032115936279</t>
   </si>
   <si>
     <t xml:space="preserve">10.5252199172974</t>
@@ -389,88 +389,88 @@
     <t xml:space="preserve">10.4601488113403</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5658893585205</t>
+    <t xml:space="preserve">10.5658903121948</t>
   </si>
   <si>
     <t xml:space="preserve">10.5821580886841</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7773694992065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9807157516479</t>
+    <t xml:space="preserve">10.7773714065552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9807167053223</t>
   </si>
   <si>
     <t xml:space="preserve">10.8749771118164</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6553621292114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6797637939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5740242004395</t>
+    <t xml:space="preserve">10.6553630828857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.679762840271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5740232467651</t>
   </si>
   <si>
     <t xml:space="preserve">10.5170869827271</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5414886474609</t>
+    <t xml:space="preserve">10.5414896011353</t>
   </si>
   <si>
     <t xml:space="preserve">10.5577564239502</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5089540481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.818039894104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6878976821899</t>
+    <t xml:space="preserve">10.5089530944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8180389404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6878967285156</t>
   </si>
   <si>
     <t xml:space="preserve">10.7611026763916</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6472282409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.899377822876</t>
+    <t xml:space="preserve">10.6472291946411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8993787765503</t>
   </si>
   <si>
     <t xml:space="preserve">10.8831100463867</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6716299057007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7367010116577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0051193237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0213871002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1840629577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4036769866943</t>
+    <t xml:space="preserve">10.6716289520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.736701965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0051183700562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0213861465454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.184063911438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4036779403687</t>
   </si>
   <si>
     <t xml:space="preserve">11.395544052124</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3386077880859</t>
+    <t xml:space="preserve">11.3386068344116</t>
   </si>
   <si>
     <t xml:space="preserve">11.3223390579224</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3304738998413</t>
+    <t xml:space="preserve">11.330472946167</t>
   </si>
   <si>
     <t xml:space="preserve">11.3630084991455</t>
@@ -482,16 +482,16 @@
     <t xml:space="preserve">10.606559753418</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8424425125122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8505754470825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6390943527222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4113464355469</t>
+    <t xml:space="preserve">10.8424406051636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8505744934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6390953063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4113454818726</t>
   </si>
   <si>
     <t xml:space="preserve">10.2080001831055</t>
@@ -512,7 +512,7 @@
     <t xml:space="preserve">10.3300085067749</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3056058883667</t>
+    <t xml:space="preserve">10.3056039810181</t>
   </si>
   <si>
     <t xml:space="preserve">10.2568035125732</t>
@@ -521,82 +521,82 @@
     <t xml:space="preserve">10.1835975646973</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4845504760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3625421524048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4438810348511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8587074279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9237794876099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0376539230347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0620546340942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1027240753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1433935165405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1759300231934</t>
+    <t xml:space="preserve">10.4845523834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3625431060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4438819885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8587083816528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9237804412842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0376529693604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0620555877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1027250289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1433944702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.175929069519</t>
   </si>
   <si>
     <t xml:space="preserve">11.1352605819702</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0701904296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.118992805481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1515283584595</t>
+    <t xml:space="preserve">11.0701894760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1189937591553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1515274047852</t>
   </si>
   <si>
     <t xml:space="preserve">11.2247323989868</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0457887649536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5008192062378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1347942352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36161231994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01998901367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10946369171143</t>
+    <t xml:space="preserve">11.0457878112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5008182525635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1347961425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36161136627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01998996734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10946273803711</t>
   </si>
   <si>
     <t xml:space="preserve">8.3941478729248</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2152042388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33721160888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31280994415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18266582489014</t>
+    <t xml:space="preserve">8.21520328521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33720970153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31280899047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18266677856445</t>
   </si>
   <si>
     <t xml:space="preserve">8.34534549713135</t>
@@ -611,13 +611,13 @@
     <t xml:space="preserve">8.58936023712158</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76017189025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29654216766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25587272644043</t>
+    <t xml:space="preserve">8.76017093658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29654121398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25587177276611</t>
   </si>
   <si>
     <t xml:space="preserve">8.17453384399414</t>
@@ -626,10 +626,10 @@
     <t xml:space="preserve">8.1908016204834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23147106170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28027439117432</t>
+    <t xml:space="preserve">8.23147201538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28027248382568</t>
   </si>
   <si>
     <t xml:space="preserve">8.14199733734131</t>
@@ -638,106 +638,106 @@
     <t xml:space="preserve">8.15826606750488</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16640090942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12166309356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05252647399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89798212051392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85731220245361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93051719665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9061164855957</t>
+    <t xml:space="preserve">8.16639995574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12166404724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05252552032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89798259735107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85731363296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93051767349243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90611600875854</t>
   </si>
   <si>
     <t xml:space="preserve">7.93865156173706</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8491792678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80851030349731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62956571578979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57262706756592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48315525054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66616773605347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60516357421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54009294509888</t>
+    <t xml:space="preserve">7.84917974472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80850982666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62956476211548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57262754440308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48315477371216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66616630554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60516405105591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54009246826172</t>
   </si>
   <si>
     <t xml:space="preserve">7.5238242149353</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47908782958984</t>
+    <t xml:space="preserve">7.47908735275269</t>
   </si>
   <si>
     <t xml:space="preserve">7.61329650878906</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54822540283203</t>
+    <t xml:space="preserve">7.54822635650635</t>
   </si>
   <si>
     <t xml:space="preserve">7.56449413299561</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50755548477173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4668869972229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49128913879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49942255020142</t>
+    <t xml:space="preserve">7.50755596160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46688747406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4912896156311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49942207336426</t>
   </si>
   <si>
     <t xml:space="preserve">7.31234502792358</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27980852127075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3774151802063</t>
+    <t xml:space="preserve">7.27980756759644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37741470336914</t>
   </si>
   <si>
     <t xml:space="preserve">7.38554906845093</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36928033828735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3204779624939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34487962722778</t>
+    <t xml:space="preserve">7.36928129196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32047748565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34487915039062</t>
   </si>
   <si>
     <t xml:space="preserve">7.28794240951538</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04392528533936</t>
+    <t xml:space="preserve">7.04392623901367</t>
   </si>
   <si>
     <t xml:space="preserve">7.15780019760132</t>
@@ -746,52 +746,52 @@
     <t xml:space="preserve">7.3936824798584</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42621850967407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40181636810303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3042106628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3611478805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20660352706909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35301303863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33674573898315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27167367935181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23100566864014</t>
+    <t xml:space="preserve">7.42621803283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40181732177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30420970916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36114740371704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20660400390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3530125617981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.336745262146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27167510986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23100471496582</t>
   </si>
   <si>
     <t xml:space="preserve">7.32861137390137</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26354026794434</t>
+    <t xml:space="preserve">7.26354122161865</t>
   </si>
   <si>
     <t xml:space="preserve">7.23913908004761</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22287130355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24727296829224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44248485565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25540685653687</t>
+    <t xml:space="preserve">7.22287178039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24727392196655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44248580932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25540781021118</t>
   </si>
   <si>
     <t xml:space="preserve">7.18220186233521</t>
@@ -806,7 +806,7 @@
     <t xml:space="preserve">7.14153242111206</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0520601272583</t>
+    <t xml:space="preserve">7.05206060409546</t>
   </si>
   <si>
     <t xml:space="preserve">7.07646179199219</t>
@@ -815,52 +815,52 @@
     <t xml:space="preserve">7.0357928276062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0195255279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87311410903931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67790365219116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85124731063843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93379163742065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26397275924683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14840936660767</t>
+    <t xml:space="preserve">7.01952505111694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87311553955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.677903175354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85124778747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93379211425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26397323608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14840984344482</t>
   </si>
   <si>
     <t xml:space="preserve">7.09888315200806</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18142795562744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16491937637329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14015579223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21444606781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17317342758179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97506427764893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84299325942993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60361242294312</t>
+    <t xml:space="preserve">7.1814284324646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16491842269897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14015626907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21444702148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1731743812561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97506475448608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84299278259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60361289978027</t>
   </si>
   <si>
     <t xml:space="preserve">6.62012100219727</t>
@@ -872,37 +872,37 @@
     <t xml:space="preserve">6.80997467041016</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54583024978638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31470394134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32295846939087</t>
+    <t xml:space="preserve">6.54583072662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31470346450806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32295799255371</t>
   </si>
   <si>
     <t xml:space="preserve">6.34772253036499</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38074016571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39724922180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4715404510498</t>
+    <t xml:space="preserve">6.38074064254761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3972487449646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47153997421265</t>
   </si>
   <si>
     <t xml:space="preserve">6.2816858291626</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22390413284302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09183263778687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90197801589966</t>
+    <t xml:space="preserve">6.22390460968018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09183216094971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9019775390625</t>
   </si>
   <si>
     <t xml:space="preserve">5.9597601890564</t>
@@ -920,7 +920,7 @@
     <t xml:space="preserve">6.19088649749756</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14961290359497</t>
+    <t xml:space="preserve">6.14961338043213</t>
   </si>
   <si>
     <t xml:space="preserve">6.0753231048584</t>
@@ -932,22 +932,22 @@
     <t xml:space="preserve">6.00928735733032</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9845232963562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12485122680664</t>
+    <t xml:space="preserve">5.98452281951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12485074996948</t>
   </si>
   <si>
     <t xml:space="preserve">6.13310480117798</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27343082427979</t>
+    <t xml:space="preserve">6.2734317779541</t>
   </si>
   <si>
     <t xml:space="preserve">6.44677591323853</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55408525466919</t>
+    <t xml:space="preserve">6.55408477783203</t>
   </si>
   <si>
     <t xml:space="preserve">6.51281213760376</t>
@@ -956,25 +956,25 @@
     <t xml:space="preserve">6.3642315864563</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24041414260864</t>
+    <t xml:space="preserve">6.24041318893433</t>
   </si>
   <si>
     <t xml:space="preserve">6.21565008163452</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23215913772583</t>
+    <t xml:space="preserve">6.23215866088867</t>
   </si>
   <si>
     <t xml:space="preserve">6.24866819381714</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11659622192383</t>
+    <t xml:space="preserve">6.11659574508667</t>
   </si>
   <si>
     <t xml:space="preserve">6.10834074020386</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05055952072144</t>
+    <t xml:space="preserve">6.05055999755859</t>
   </si>
   <si>
     <t xml:space="preserve">5.89372396469116</t>
@@ -983,16 +983,16 @@
     <t xml:space="preserve">5.77816104888916</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69561529159546</t>
+    <t xml:space="preserve">5.6956148147583</t>
   </si>
   <si>
     <t xml:space="preserve">5.79466915130615</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80292320251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82768821716309</t>
+    <t xml:space="preserve">5.80292367935181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82768774032593</t>
   </si>
   <si>
     <t xml:space="preserve">5.78641510009766</t>
@@ -1001,13 +1001,13 @@
     <t xml:space="preserve">5.73688745498657</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85245180130005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29819536209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1826319694519</t>
+    <t xml:space="preserve">5.85245132446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29819583892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18263244628906</t>
   </si>
   <si>
     <t xml:space="preserve">6.15786838531494</t>
@@ -1016,31 +1016,31 @@
     <t xml:space="preserve">6.03405046463013</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08357715606689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81943321228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91848707199097</t>
+    <t xml:space="preserve">6.08357763290405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81943368911743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91848659515381</t>
   </si>
   <si>
     <t xml:space="preserve">5.86070537567139</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76165246963501</t>
+    <t xml:space="preserve">5.76165199279785</t>
   </si>
   <si>
     <t xml:space="preserve">5.75339651107788</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8111777305603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70387077331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74514245986938</t>
+    <t xml:space="preserve">5.81117868423462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70387029647827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74514198303223</t>
   </si>
   <si>
     <t xml:space="preserve">5.83594226837158</t>
@@ -1049,22 +1049,22 @@
     <t xml:space="preserve">5.71212482452393</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84419727325439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94325065612793</t>
+    <t xml:space="preserve">5.84419679641724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94325113296509</t>
   </si>
   <si>
     <t xml:space="preserve">5.96801471710205</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87721490859985</t>
+    <t xml:space="preserve">5.87721538543701</t>
   </si>
   <si>
     <t xml:space="preserve">5.88546991348267</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93499565124512</t>
+    <t xml:space="preserve">5.93499660491943</t>
   </si>
   <si>
     <t xml:space="preserve">6.02579545974731</t>
@@ -1073,13 +1073,13 @@
     <t xml:space="preserve">6.06706857681274</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38899421691895</t>
+    <t xml:space="preserve">6.38899517059326</t>
   </si>
   <si>
     <t xml:space="preserve">6.19914102554321</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04230499267578</t>
+    <t xml:space="preserve">6.04230546951294</t>
   </si>
   <si>
     <t xml:space="preserve">6.05881452560425</t>
@@ -1103,7 +1103,7 @@
     <t xml:space="preserve">6.20958423614502</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0921049118042</t>
+    <t xml:space="preserve">6.09210538864136</t>
   </si>
   <si>
     <t xml:space="preserve">6.10888910293579</t>
@@ -1112,19 +1112,19 @@
     <t xml:space="preserve">6.07532358169556</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14245367050171</t>
+    <t xml:space="preserve">6.14245414733887</t>
   </si>
   <si>
     <t xml:space="preserve">6.05854082107544</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02497482299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97462749481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95784473419189</t>
+    <t xml:space="preserve">6.02497529983521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97462797164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95784425735474</t>
   </si>
   <si>
     <t xml:space="preserve">6.15923690795898</t>
@@ -1133,49 +1133,49 @@
     <t xml:space="preserve">6.12567090988159</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19280242919922</t>
+    <t xml:space="preserve">6.19280195236206</t>
   </si>
   <si>
     <t xml:space="preserve">6.42775869369507</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71306467056274</t>
+    <t xml:space="preserve">6.7130651473999</t>
   </si>
   <si>
     <t xml:space="preserve">6.64593458175659</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69628238677979</t>
+    <t xml:space="preserve">6.69628190994263</t>
   </si>
   <si>
     <t xml:space="preserve">6.78019523620605</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72984743118286</t>
+    <t xml:space="preserve">6.7298469543457</t>
   </si>
   <si>
     <t xml:space="preserve">6.62915086746216</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56202077865601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54523754119873</t>
+    <t xml:space="preserve">6.56202030181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54523801803589</t>
   </si>
   <si>
     <t xml:space="preserve">6.67949867248535</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66271686553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57880353927612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37741088867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34384632110596</t>
+    <t xml:space="preserve">6.66271638870239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57880306243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37741136550903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3438458442688</t>
   </si>
   <si>
     <t xml:space="preserve">6.22636795043945</t>
@@ -1184,46 +1184,46 @@
     <t xml:space="preserve">6.36062860488892</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67253923416138</t>
+    <t xml:space="preserve">5.67253875732422</t>
   </si>
   <si>
     <t xml:space="preserve">5.55506038665771</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68932199478149</t>
+    <t xml:space="preserve">5.68932294845581</t>
   </si>
   <si>
     <t xml:space="preserve">5.62219142913818</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53827810287476</t>
+    <t xml:space="preserve">5.5382776260376</t>
   </si>
   <si>
     <t xml:space="preserve">5.43758249282837</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45436573028564</t>
+    <t xml:space="preserve">5.45436525344849</t>
   </si>
   <si>
     <t xml:space="preserve">5.60540819168091</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52149534225464</t>
+    <t xml:space="preserve">5.5214958190918</t>
   </si>
   <si>
     <t xml:space="preserve">5.50471258163452</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4879298210144</t>
+    <t xml:space="preserve">5.48792934417725</t>
   </si>
   <si>
     <t xml:space="preserve">5.35366868972778</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3704514503479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42079973220825</t>
+    <t xml:space="preserve">5.37045097351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42079925537109</t>
   </si>
   <si>
     <t xml:space="preserve">5.28653812408447</t>
@@ -1232,13 +1232,13 @@
     <t xml:space="preserve">5.30332088470459</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26975536346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38723421096802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32010412216187</t>
+    <t xml:space="preserve">5.26975584030151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38723468780518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32010364532471</t>
   </si>
   <si>
     <t xml:space="preserve">5.65575647354126</t>
@@ -1253,40 +1253,40 @@
     <t xml:space="preserve">5.72288703918457</t>
   </si>
   <si>
-    <t xml:space="preserve">5.739670753479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6389741897583</t>
+    <t xml:space="preserve">5.73967027664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63897466659546</t>
   </si>
   <si>
     <t xml:space="preserve">5.57184410095215</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18584156036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2026252746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21940755844116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16905975341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13549327850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1019287109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95088481903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03479909896851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15227651596069</t>
+    <t xml:space="preserve">5.18584203720093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20262479782104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21940803527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16905927658081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13549423217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10192918777466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9508843421936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03479862213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15227699279785</t>
   </si>
   <si>
     <t xml:space="preserve">5.11871147155762</t>
@@ -1301,22 +1301,22 @@
     <t xml:space="preserve">5.23619031906128</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25297212600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33688688278198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79001808166504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77323532104492</t>
+    <t xml:space="preserve">5.25297260284424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33688640594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79001760482788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77323484420776</t>
   </si>
   <si>
     <t xml:space="preserve">5.58862590789795</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81662321090698</t>
+    <t xml:space="preserve">4.81662368774414</t>
   </si>
   <si>
     <t xml:space="preserve">4.79984140396118</t>
@@ -1334,25 +1334,25 @@
     <t xml:space="preserve">4.19566488265991</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11175107955933</t>
+    <t xml:space="preserve">4.11175155639648</t>
   </si>
   <si>
     <t xml:space="preserve">4.02783870697021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17049074172974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06979513168335</t>
+    <t xml:space="preserve">4.17049169540405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06979560852051</t>
   </si>
   <si>
     <t xml:space="preserve">4.12014293670654</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34670877456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17888212203979</t>
+    <t xml:space="preserve">4.34670829772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17888164520264</t>
   </si>
   <si>
     <t xml:space="preserve">4.04462146759033</t>
@@ -1370,31 +1370,31 @@
     <t xml:space="preserve">4.14531755447388</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99427247047424</t>
+    <t xml:space="preserve">3.9942729473114</t>
   </si>
   <si>
     <t xml:space="preserve">4.09496927261353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98588156700134</t>
+    <t xml:space="preserve">3.98588132858276</t>
   </si>
   <si>
     <t xml:space="preserve">4.2795786857605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22922992706299</t>
+    <t xml:space="preserve">4.22923040390015</t>
   </si>
   <si>
     <t xml:space="preserve">4.21244812011719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03623008728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12877941131592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1628303527832</t>
+    <t xml:space="preserve">4.03622961044312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12877893447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16283082962036</t>
   </si>
   <si>
     <t xml:space="preserve">4.07770156860352</t>
@@ -1403,46 +1403,46 @@
     <t xml:space="preserve">4.00108480453491</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20539522171021</t>
+    <t xml:space="preserve">4.20539569854736</t>
   </si>
   <si>
     <t xml:space="preserve">4.37565469741821</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21390867233276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22242164611816</t>
+    <t xml:space="preserve">4.21390819549561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22242212295532</t>
   </si>
   <si>
     <t xml:space="preserve">4.25647354125977</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24795961380005</t>
+    <t xml:space="preserve">4.24796009063721</t>
   </si>
   <si>
     <t xml:space="preserve">4.32457685470581</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30755090713501</t>
+    <t xml:space="preserve">4.30755043029785</t>
   </si>
   <si>
     <t xml:space="preserve">4.23944759368896</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35862827301025</t>
+    <t xml:space="preserve">4.35862874984741</t>
   </si>
   <si>
     <t xml:space="preserve">4.5118613243103</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5334153175354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9420371055603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8909592628479</t>
+    <t xml:space="preserve">5.53341484069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94203662872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89095973968506</t>
   </si>
   <si>
     <t xml:space="preserve">5.73772573471069</t>
@@ -1454,16 +1454,16 @@
     <t xml:space="preserve">5.5844931602478</t>
   </si>
   <si>
-    <t xml:space="preserve">5.567467212677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41423416137695</t>
+    <t xml:space="preserve">5.56746673583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41423368453979</t>
   </si>
   <si>
     <t xml:space="preserve">5.2610011100769</t>
   </si>
   <si>
-    <t xml:space="preserve">5.482337474823</t>
+    <t xml:space="preserve">5.48233795166016</t>
   </si>
   <si>
     <t xml:space="preserve">5.44828605651855</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">5.32910442352295</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27802705764771</t>
+    <t xml:space="preserve">5.27802658081055</t>
   </si>
   <si>
     <t xml:space="preserve">5.43126010894775</t>
@@ -1496,10 +1496,10 @@
     <t xml:space="preserve">5.2269492149353</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00561237335205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95453500747681</t>
+    <t xml:space="preserve">5.00561285018921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95453548431396</t>
   </si>
   <si>
     <t xml:space="preserve">4.93750905990601</t>
@@ -1508,13 +1508,13 @@
     <t xml:space="preserve">5.05669069290161</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03966474533081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97156143188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8864312171936</t>
+    <t xml:space="preserve">5.03966426849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97156095504761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88643169403076</t>
   </si>
   <si>
     <t xml:space="preserve">5.02263832092285</t>
@@ -1526,22 +1526,22 @@
     <t xml:space="preserve">4.90345764160156</t>
   </si>
   <si>
-    <t xml:space="preserve">4.852379322052</t>
+    <t xml:space="preserve">4.85237979888916</t>
   </si>
   <si>
     <t xml:space="preserve">4.8694052696228</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34613084793091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24397468566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36315679550171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38018274307251</t>
+    <t xml:space="preserve">5.34613037109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2439751625061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36315631866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38018226623535</t>
   </si>
   <si>
     <t xml:space="preserve">5.2099232673645</t>
@@ -1550,37 +1550,37 @@
     <t xml:space="preserve">5.1588454246521</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1077675819397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98858737945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09074211120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19289779663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1758713722229</t>
+    <t xml:space="preserve">5.10776805877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98858690261841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09074258804321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1928973197937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17587089538574</t>
   </si>
   <si>
     <t xml:space="preserve">5.14181995391846</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07371664047241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68212080001831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54591369628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59699106216431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57996559143066</t>
+    <t xml:space="preserve">5.07371616363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68212032318115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5459132194519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59699153900146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57996511459351</t>
   </si>
   <si>
     <t xml:space="preserve">4.63104295730591</t>
@@ -1595,13 +1595,13 @@
     <t xml:space="preserve">4.81832790374756</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8013014793396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39720821380615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61854457855225</t>
+    <t xml:space="preserve">4.80130195617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39720869064331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6185450553894</t>
   </si>
   <si>
     <t xml:space="preserve">5.46531200408936</t>
@@ -1616,7 +1616,7 @@
     <t xml:space="preserve">5.68664836883545</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65259647369385</t>
+    <t xml:space="preserve">5.65259695053101</t>
   </si>
   <si>
     <t xml:space="preserve">5.8569073677063</t>
@@ -1634,7 +1634,7 @@
     <t xml:space="preserve">6.29958057403564</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35065793991089</t>
+    <t xml:space="preserve">6.35065841674805</t>
   </si>
   <si>
     <t xml:space="preserve">6.43578720092773</t>
@@ -1649,25 +1649,25 @@
     <t xml:space="preserve">6.79333162307739</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15087461471558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08277177810669</t>
+    <t xml:space="preserve">7.15087509155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08277130126953</t>
   </si>
   <si>
     <t xml:space="preserve">6.87846088409424</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77630567550659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84440946578979</t>
+    <t xml:space="preserve">6.77630519866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84440898895264</t>
   </si>
   <si>
     <t xml:space="preserve">6.70820236206055</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75928020477295</t>
+    <t xml:space="preserve">6.75927972793579</t>
   </si>
   <si>
     <t xml:space="preserve">6.53794288635254</t>
@@ -1676,10 +1676,10 @@
     <t xml:space="preserve">6.72522783279419</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65712404251099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91251277923584</t>
+    <t xml:space="preserve">6.6571249961853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91251230239868</t>
   </si>
   <si>
     <t xml:space="preserve">6.8954873085022</t>
@@ -1691,7 +1691,7 @@
     <t xml:space="preserve">7.17302179336548</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05085325241089</t>
+    <t xml:space="preserve">7.05085372924805</t>
   </si>
   <si>
     <t xml:space="preserve">7.1206636428833</t>
@@ -1706,37 +1706,37 @@
     <t xml:space="preserve">8.02819919586182</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06310558319092</t>
+    <t xml:space="preserve">8.0631046295166</t>
   </si>
   <si>
     <t xml:space="preserve">7.99329423904419</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01074695587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94093704223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13291358947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15036773681641</t>
+    <t xml:space="preserve">8.0107479095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94093656539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13291454315186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15036869049072</t>
   </si>
   <si>
     <t xml:space="preserve">8.16781997680664</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18527412414551</t>
+    <t xml:space="preserve">8.18527317047119</t>
   </si>
   <si>
     <t xml:space="preserve">8.34234714508057</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11546325683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25508213043213</t>
+    <t xml:space="preserve">8.11546230316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25508308410645</t>
   </si>
   <si>
     <t xml:space="preserve">8.08055686950684</t>
@@ -1748,19 +1748,19 @@
     <t xml:space="preserve">7.95838832855225</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37725162506104</t>
+    <t xml:space="preserve">8.37725257873535</t>
   </si>
   <si>
     <t xml:space="preserve">8.32489395141602</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81356716156006</t>
+    <t xml:space="preserve">8.81356811523438</t>
   </si>
   <si>
     <t xml:space="preserve">8.58668327331543</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53432369232178</t>
+    <t xml:space="preserve">8.53432464599609</t>
   </si>
   <si>
     <t xml:space="preserve">8.69139957427979</t>
@@ -1772,7 +1772,7 @@
     <t xml:space="preserve">8.72630405426025</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42961025238037</t>
+    <t xml:space="preserve">8.42960929870605</t>
   </si>
   <si>
     <t xml:space="preserve">8.28998851776123</t>
@@ -1784,19 +1784,19 @@
     <t xml:space="preserve">8.04565238952637</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85367298126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41215705871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22017860412598</t>
+    <t xml:space="preserve">7.85367345809937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41215801239014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22017765045166</t>
   </si>
   <si>
     <t xml:space="preserve">8.44706249237061</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3597993850708</t>
+    <t xml:space="preserve">8.35979843139648</t>
   </si>
   <si>
     <t xml:space="preserve">8.09801006317139</t>
@@ -1817,34 +1817,34 @@
     <t xml:space="preserve">8.65649318695068</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51687335968018</t>
+    <t xml:space="preserve">8.51687240600586</t>
   </si>
   <si>
     <t xml:space="preserve">8.46451473236084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49941921234131</t>
+    <t xml:space="preserve">8.49942016601562</t>
   </si>
   <si>
     <t xml:space="preserve">8.5692310333252</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99161815643311</t>
+    <t xml:space="preserve">9.99161720275879</t>
   </si>
   <si>
     <t xml:space="preserve">9.59893417358398</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77346038818359</t>
+    <t xml:space="preserve">9.77345943450928</t>
   </si>
   <si>
     <t xml:space="preserve">9.8170919418335</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29351425170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46804046630859</t>
+    <t xml:space="preserve">9.29351234436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46803951263428</t>
   </si>
   <si>
     <t xml:space="preserve">9.55530261993408</t>
@@ -1853,16 +1853,16 @@
     <t xml:space="preserve">9.64256572723389</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90435409545898</t>
+    <t xml:space="preserve">9.9043550491333</t>
   </si>
   <si>
     <t xml:space="preserve">9.33714485168457</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94798564910889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86072254180908</t>
+    <t xml:space="preserve">9.9479866027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8607234954834</t>
   </si>
   <si>
     <t xml:space="preserve">10.5151958465576</t>
@@ -1874,22 +1874,22 @@
     <t xml:space="preserve">10.5588283538818</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6024580001831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8206176757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7333545684814</t>
+    <t xml:space="preserve">10.6024589538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8206167221069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7333536148071</t>
   </si>
   <si>
     <t xml:space="preserve">10.7769861221313</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2970390319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3843002319336</t>
+    <t xml:space="preserve">10.2970380783081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3843011856079</t>
   </si>
   <si>
     <t xml:space="preserve">10.3406705856323</t>
@@ -1898,58 +1898,58 @@
     <t xml:space="preserve">10.2097749710083</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2534074783325</t>
+    <t xml:space="preserve">10.2534065246582</t>
   </si>
   <si>
     <t xml:space="preserve">10.0788812637329</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51167106628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72982788085938</t>
+    <t xml:space="preserve">9.51167011260986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72982883453369</t>
   </si>
   <si>
     <t xml:space="preserve">9.68619728088379</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98809337615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42440891265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6496162414551</t>
+    <t xml:space="preserve">8.98809432983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42440795898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6496171951294</t>
   </si>
   <si>
     <t xml:space="preserve">11.5623531341553</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7805099487305</t>
+    <t xml:space="preserve">11.7805109024048</t>
   </si>
   <si>
     <t xml:space="preserve">11.9114036560059</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9550361633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6932458877563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3040895462036</t>
+    <t xml:space="preserve">11.9550352096558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.693247795105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3040885925293</t>
   </si>
   <si>
     <t xml:space="preserve">12.2604570388794</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2168254852295</t>
+    <t xml:space="preserve">12.2168245315552</t>
   </si>
   <si>
     <t xml:space="preserve">12.3913507461548</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7368783950806</t>
+    <t xml:space="preserve">11.7368793487549</t>
   </si>
   <si>
     <t xml:space="preserve">11.8677730560303</t>
@@ -1967,10 +1967,10 @@
     <t xml:space="preserve">11.3005638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3441953659058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9951438903809</t>
+    <t xml:space="preserve">11.3441944122314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9951429367065</t>
   </si>
   <si>
     <t xml:space="preserve">10.4715642929077</t>
@@ -1979,7 +1979,7 @@
     <t xml:space="preserve">10.9078798294067</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4314575195312</t>
+    <t xml:space="preserve">11.4314594268799</t>
   </si>
   <si>
     <t xml:space="preserve">11.0387735366821</t>
@@ -1988,55 +1988,55 @@
     <t xml:space="preserve">11.9899406433105</t>
   </si>
   <si>
-    <t xml:space="preserve">11.74560546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5361738204956</t>
+    <t xml:space="preserve">11.7456045150757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5361728668213</t>
   </si>
   <si>
     <t xml:space="preserve">11.5187215805054</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6234369277954</t>
+    <t xml:space="preserve">11.6234359741211</t>
   </si>
   <si>
     <t xml:space="preserve">11.4489107131958</t>
   </si>
   <si>
-    <t xml:space="preserve">11.64089012146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7281522750854</t>
+    <t xml:space="preserve">11.6408891677856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7281513214111</t>
   </si>
   <si>
     <t xml:space="preserve">11.9201307296753</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1173114776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0998592376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8031635284424</t>
+    <t xml:space="preserve">11.1173105239868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0998582839966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8031644821167</t>
   </si>
   <si>
     <t xml:space="preserve">10.7508058547974</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3319444656372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1050596237183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81839275360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69297313690186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7108907699585</t>
+    <t xml:space="preserve">10.3319435119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1050605773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81839179992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69297409057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71089172363281</t>
   </si>
   <si>
     <t xml:space="preserve">10.1408929824829</t>
@@ -2051,16 +2051,16 @@
     <t xml:space="preserve">10.1229763031006</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1588096618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0692262649536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0871429443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4633960723877</t>
+    <t xml:space="preserve">10.1588106155396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0692253112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0871438980103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4633951187134</t>
   </si>
   <si>
     <t xml:space="preserve">10.7858972549438</t>
@@ -2087,13 +2087,13 @@
     <t xml:space="preserve">10.5888118743896</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5171451568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8575649261475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9113149642944</t>
+    <t xml:space="preserve">10.5171461105347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8575639724731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9113159179688</t>
   </si>
   <si>
     <t xml:space="preserve">10.6067295074463</t>
@@ -2102,13 +2102,13 @@
     <t xml:space="preserve">10.6604795455933</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3021450042725</t>
+    <t xml:space="preserve">10.3021440505981</t>
   </si>
   <si>
     <t xml:space="preserve">10.4096450805664</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3558950424194</t>
+    <t xml:space="preserve">10.3558940887451</t>
   </si>
   <si>
     <t xml:space="preserve">10.6783971786499</t>
@@ -2120,16 +2120,16 @@
     <t xml:space="preserve">10.535062789917</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1800661087036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9829816818237</t>
+    <t xml:space="preserve">11.1800651550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9829807281494</t>
   </si>
   <si>
     <t xml:space="preserve">11.4846515655518</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3771505355835</t>
+    <t xml:space="preserve">11.3771514892578</t>
   </si>
   <si>
     <t xml:space="preserve">11.7354869842529</t>
@@ -2150,7 +2150,7 @@
     <t xml:space="preserve">12.2371559143066</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3267393112183</t>
+    <t xml:space="preserve">12.3267402648926</t>
   </si>
   <si>
     <t xml:space="preserve">12.4521570205688</t>
@@ -2159,7 +2159,7 @@
     <t xml:space="preserve">12.0938215255737</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3984069824219</t>
+    <t xml:space="preserve">12.3984079360962</t>
   </si>
   <si>
     <t xml:space="preserve">12.201322555542</t>
@@ -2174,10 +2174,10 @@
     <t xml:space="preserve">12.6134080886841</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8463268280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.810492515564</t>
+    <t xml:space="preserve">12.8463258743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8104934692383</t>
   </si>
   <si>
     <t xml:space="preserve">12.9179935455322</t>
@@ -2186,37 +2186,37 @@
     <t xml:space="preserve">13.258412361145</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4017467498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4375791549683</t>
+    <t xml:space="preserve">13.4017457962036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4375801086426</t>
   </si>
   <si>
     <t xml:space="preserve">13.6884145736694</t>
   </si>
   <si>
-    <t xml:space="preserve">13.903416633606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6559209823608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2438335418701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6380033493042</t>
+    <t xml:space="preserve">13.9034156799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6559200286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2438344955444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6380043029785</t>
   </si>
   <si>
     <t xml:space="preserve">14.92467212677</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5125865936279</t>
+    <t xml:space="preserve">14.5125875473022</t>
   </si>
   <si>
     <t xml:space="preserve">14.5663366317749</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7992544174194</t>
+    <t xml:space="preserve">14.7992553710938</t>
   </si>
   <si>
     <t xml:space="preserve">14.5484189987183</t>
@@ -2228,10 +2228,10 @@
     <t xml:space="preserve">14.2617511749268</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8888387680054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8171710968018</t>
+    <t xml:space="preserve">14.8888397216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8171730041504</t>
   </si>
   <si>
     <t xml:space="preserve">14.387167930603</t>
@@ -2240,7 +2240,7 @@
     <t xml:space="preserve">14.7634201049805</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6200866699219</t>
+    <t xml:space="preserve">14.6200857162476</t>
   </si>
   <si>
     <t xml:space="preserve">14.9067535400391</t>
@@ -2249,7 +2249,7 @@
     <t xml:space="preserve">15.1217546463013</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0321741104126</t>
+    <t xml:space="preserve">15.032172203064</t>
   </si>
   <si>
     <t xml:space="preserve">14.7455034255981</t>
@@ -2258,7 +2258,7 @@
     <t xml:space="preserve">15.0500888824463</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0680065155029</t>
+    <t xml:space="preserve">15.0680055618286</t>
   </si>
   <si>
     <t xml:space="preserve">15.1038398742676</t>
@@ -2267,34 +2267,34 @@
     <t xml:space="preserve">14.5305023193359</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7096710205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2080011367798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6167469024658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5092468261719</t>
+    <t xml:space="preserve">14.7096700668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2080001831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6167478561401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5092458724976</t>
   </si>
   <si>
     <t xml:space="preserve">13.0434112548828</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1688280105591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9717426300049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4700746536255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2404956817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6525802612305</t>
+    <t xml:space="preserve">13.1688270568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9717435836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4700736999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2404947280884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6525812149048</t>
   </si>
   <si>
     <t xml:space="preserve">13.5809135437012</t>
@@ -2306,19 +2306,19 @@
     <t xml:space="preserve">13.4913301467896</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2225780487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2046604156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0613269805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0075778961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6313247680664</t>
+    <t xml:space="preserve">13.2225790023804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2046613693237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0613279342651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0075769424438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6313257217407</t>
   </si>
   <si>
     <t xml:space="preserve">13.0971612930298</t>
@@ -2345,7 +2345,7 @@
     <t xml:space="preserve">13.1150779724121</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1509113311768</t>
+    <t xml:space="preserve">13.1509122848511</t>
   </si>
   <si>
     <t xml:space="preserve">13.5271635055542</t>
@@ -2354,13 +2354,13 @@
     <t xml:space="preserve">13.3479957580566</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2763290405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7925748825073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5954923629761</t>
+    <t xml:space="preserve">13.276328086853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7925758361816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5954914093018</t>
   </si>
   <si>
     <t xml:space="preserve">12.5238246917725</t>
@@ -2372,16 +2372,16 @@
     <t xml:space="preserve">12.4879903793335</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3088226318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5417413711548</t>
+    <t xml:space="preserve">12.3088216781616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5417404174805</t>
   </si>
   <si>
     <t xml:space="preserve">12.8284091949463</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3804903030396</t>
+    <t xml:space="preserve">12.3804893493652</t>
   </si>
   <si>
     <t xml:space="preserve">12.6671581268311</t>
@@ -2399,22 +2399,22 @@
     <t xml:space="preserve">12.4342403411865</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9504871368408</t>
+    <t xml:space="preserve">11.9504880905151</t>
   </si>
   <si>
     <t xml:space="preserve">12.2192392349243</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8250694274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1117382049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9684047698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0400714874268</t>
+    <t xml:space="preserve">11.8250703811646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1117391586304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9684038162231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0400705337524</t>
   </si>
   <si>
     <t xml:space="preserve">12.0042381286621</t>
@@ -2423,10 +2423,10 @@
     <t xml:space="preserve">12.255072593689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7388248443604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7421655654907</t>
+    <t xml:space="preserve">12.7388257980347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7421646118164</t>
   </si>
   <si>
     <t xml:space="preserve">13.7063312530518</t>
@@ -2435,7 +2435,7 @@
     <t xml:space="preserve">14.0825834274292</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0109157562256</t>
+    <t xml:space="preserve">14.0109176635742</t>
   </si>
   <si>
     <t xml:space="preserve">13.7242479324341</t>
@@ -2444,10 +2444,10 @@
     <t xml:space="preserve">14.0467500686646</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0646657943726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9392490386963</t>
+    <t xml:space="preserve">14.0646667480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9392499923706</t>
   </si>
   <si>
     <t xml:space="preserve">13.6346645355225</t>
@@ -2474,55 +2474,55 @@
     <t xml:space="preserve">13.4734134674072</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1867446899414</t>
+    <t xml:space="preserve">13.1867456436157</t>
   </si>
   <si>
     <t xml:space="preserve">13.3838291168213</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5988302230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.70299243927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8429870605469</t>
+    <t xml:space="preserve">13.5988311767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7029914855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8429861068726</t>
   </si>
   <si>
     <t xml:space="preserve">11.7892360687256</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6817359924316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0759048461914</t>
+    <t xml:space="preserve">11.6817350387573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0759038925171</t>
   </si>
   <si>
     <t xml:space="preserve">11.5742359161377</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2159004211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3592338562012</t>
+    <t xml:space="preserve">11.2158994674683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3592348098755</t>
   </si>
   <si>
     <t xml:space="preserve">11.4309015274048</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3054828643799</t>
+    <t xml:space="preserve">11.3054838180542</t>
   </si>
   <si>
     <t xml:space="preserve">11.2875671386719</t>
   </si>
   <si>
-    <t xml:space="preserve">11.683783531189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5179262161255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2783517837524</t>
+    <t xml:space="preserve">11.6837844848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5179252624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2783527374268</t>
   </si>
   <si>
     <t xml:space="preserve">11.1493520736694</t>
@@ -2534,7 +2534,7 @@
     <t xml:space="preserve">11.0756378173828</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9970722198486</t>
+    <t xml:space="preserve">11.9970712661743</t>
   </si>
   <si>
     <t xml:space="preserve">12.052357673645</t>
@@ -2543,7 +2543,7 @@
     <t xml:space="preserve">12.2735013961792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2182149887085</t>
+    <t xml:space="preserve">12.2182159423828</t>
   </si>
   <si>
     <t xml:space="preserve">12.4025020599365</t>
@@ -2555,7 +2555,7 @@
     <t xml:space="preserve">12.0707864761353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1629285812378</t>
+    <t xml:space="preserve">12.1629295349121</t>
   </si>
   <si>
     <t xml:space="preserve">12.1260719299316</t>
@@ -2570,13 +2570,13 @@
     <t xml:space="preserve">11.7759265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8312129974365</t>
+    <t xml:space="preserve">11.8312139511108</t>
   </si>
   <si>
     <t xml:space="preserve">11.9786424636841</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7206411361694</t>
+    <t xml:space="preserve">11.7206420898438</t>
   </si>
   <si>
     <t xml:space="preserve">11.868070602417</t>
@@ -2591,7 +2591,7 @@
     <t xml:space="preserve">11.4442110061646</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3520669937134</t>
+    <t xml:space="preserve">11.3520679473877</t>
   </si>
   <si>
     <t xml:space="preserve">11.3704957962036</t>
@@ -2609,7 +2609,7 @@
     <t xml:space="preserve">11.7022123336792</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5732116699219</t>
+    <t xml:space="preserve">11.5732126235962</t>
   </si>
   <si>
     <t xml:space="preserve">11.481068611145</t>
@@ -2618,7 +2618,7 @@
     <t xml:space="preserve">11.296781539917</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3152093887329</t>
+    <t xml:space="preserve">11.3152103424072</t>
   </si>
   <si>
     <t xml:space="preserve">11.5547828674316</t>
@@ -2627,7 +2627,7 @@
     <t xml:space="preserve">11.4257822036743</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3336381912231</t>
+    <t xml:space="preserve">11.3336391448975</t>
   </si>
   <si>
     <t xml:space="preserve">11.3889245986938</t>
@@ -2636,7 +2636,7 @@
     <t xml:space="preserve">11.4626398086548</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7943553924561</t>
+    <t xml:space="preserve">11.7943563461304</t>
   </si>
   <si>
     <t xml:space="preserve">12.1076431274414</t>
@@ -2666,7 +2666,7 @@
     <t xml:space="preserve">13.0290775299072</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2502222061157</t>
+    <t xml:space="preserve">13.2502212524414</t>
   </si>
   <si>
     <t xml:space="preserve">13.4160804748535</t>
@@ -2681,7 +2681,7 @@
     <t xml:space="preserve">12.6420755386353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8816480636597</t>
+    <t xml:space="preserve">12.8816471099854</t>
   </si>
   <si>
     <t xml:space="preserve">12.9185056686401</t>
@@ -2690,7 +2690,7 @@
     <t xml:space="preserve">13.194935798645</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1580772399902</t>
+    <t xml:space="preserve">13.1580781936646</t>
   </si>
   <si>
     <t xml:space="preserve">12.8079328536987</t>
@@ -2705,7 +2705,7 @@
     <t xml:space="preserve">12.5499315261841</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0843629837036</t>
+    <t xml:space="preserve">13.0843639373779</t>
   </si>
   <si>
     <t xml:space="preserve">13.3423643112183</t>
@@ -2723,13 +2723,13 @@
     <t xml:space="preserve">13.1027917861938</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3607940673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2133646011353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5266513824463</t>
+    <t xml:space="preserve">13.3607931137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2133636474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5266523361206</t>
   </si>
   <si>
     <t xml:space="preserve">13.6003665924072</t>
@@ -2747,28 +2747,28 @@
     <t xml:space="preserve">13.7846536636353</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0610828399658</t>
+    <t xml:space="preserve">14.0610837936401</t>
   </si>
   <si>
     <t xml:space="preserve">14.2637987136841</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5402297973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6139440536499</t>
+    <t xml:space="preserve">14.540228843689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6139430999756</t>
   </si>
   <si>
     <t xml:space="preserve">15.3695201873779</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5353784561157</t>
+    <t xml:space="preserve">15.53537940979</t>
   </si>
   <si>
     <t xml:space="preserve">15.6275205612183</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5722360610962</t>
+    <t xml:space="preserve">15.5722341537476</t>
   </si>
   <si>
     <t xml:space="preserve">15.4063768386841</t>
@@ -2780,34 +2780,34 @@
     <t xml:space="preserve">15.295804977417</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2773761749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4616651535034</t>
+    <t xml:space="preserve">15.2773771286011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4616641998291</t>
   </si>
   <si>
     <t xml:space="preserve">15.6459493637085</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4432344436646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6643781661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7012376785278</t>
+    <t xml:space="preserve">15.4432353973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.664379119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7012367248535</t>
   </si>
   <si>
     <t xml:space="preserve">15.6090936660767</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3326606750488</t>
+    <t xml:space="preserve">15.3326616287231</t>
   </si>
   <si>
     <t xml:space="preserve">15.2036619186401</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1668033599854</t>
+    <t xml:space="preserve">15.1668043136597</t>
   </si>
   <si>
     <t xml:space="preserve">14.8535175323486</t>
@@ -2828,22 +2828,22 @@
     <t xml:space="preserve">15.8302373886108</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7196645736694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3879489898682</t>
+    <t xml:space="preserve">15.7196636199951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3879499435425</t>
   </si>
   <si>
     <t xml:space="preserve">15.5906648635864</t>
   </si>
   <si>
-    <t xml:space="preserve">15.682806968689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7565221786499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7380933761597</t>
+    <t xml:space="preserve">15.6828079223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7565231323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.738094329834</t>
   </si>
   <si>
     <t xml:space="preserve">15.1483764648438</t>
@@ -2855,7 +2855,7 @@
     <t xml:space="preserve">15.1299476623535</t>
   </si>
   <si>
-    <t xml:space="preserve">15.480092048645</t>
+    <t xml:space="preserve">15.4800910949707</t>
   </si>
   <si>
     <t xml:space="preserve">15.9223804473877</t>
@@ -2867,22 +2867,22 @@
     <t xml:space="preserve">16.0882377624512</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7749509811401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.867094039917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7109394073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6556529998779</t>
+    <t xml:space="preserve">15.7749519348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8670930862427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7109384536743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6556520462036</t>
   </si>
   <si>
     <t xml:space="preserve">13.6372241973877</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1347990036011</t>
+    <t xml:space="preserve">14.1347980499268</t>
   </si>
   <si>
     <t xml:space="preserve">14.4480857849121</t>
@@ -2894,7 +2894,7 @@
     <t xml:space="preserve">14.0242261886597</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0795125961304</t>
+    <t xml:space="preserve">14.0795116424561</t>
   </si>
   <si>
     <t xml:space="preserve">14.0057973861694</t>
@@ -2915,7 +2915,7 @@
     <t xml:space="preserve">13.4897947311401</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6187953948975</t>
+    <t xml:space="preserve">13.6187944412231</t>
   </si>
   <si>
     <t xml:space="preserve">12.8263626098633</t>
@@ -2927,7 +2927,7 @@
     <t xml:space="preserve">13.2686500549316</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9369335174561</t>
+    <t xml:space="preserve">12.9369344711304</t>
   </si>
   <si>
     <t xml:space="preserve">12.9000768661499</t>
@@ -2936,10 +2936,10 @@
     <t xml:space="preserve">12.9922199249268</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0475053787231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6973600387573</t>
+    <t xml:space="preserve">13.0475063323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6973609924316</t>
   </si>
   <si>
     <t xml:space="preserve">12.6052179336548</t>
@@ -2951,7 +2951,7 @@
     <t xml:space="preserve">12.4209308624268</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4762172698975</t>
+    <t xml:space="preserve">12.4762163162231</t>
   </si>
   <si>
     <t xml:space="preserve">12.6236457824707</t>
@@ -68467,7 +68467,7 @@
     </row>
     <row r="2489">
       <c r="A2489" s="1" t="n">
-        <v>45944.6496296296</v>
+        <v>45944.2916666667</v>
       </c>
       <c r="B2489" t="n">
         <v>56494</v>
@@ -68488,6 +68488,32 @@
         <v>1142</v>
       </c>
       <c r="H2489" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2490">
+      <c r="A2490" s="1" t="n">
+        <v>45945.649375</v>
+      </c>
+      <c r="B2490" t="n">
+        <v>57290</v>
+      </c>
+      <c r="C2490" t="n">
+        <v>18.3999996185303</v>
+      </c>
+      <c r="D2490" t="n">
+        <v>18.0400009155273</v>
+      </c>
+      <c r="E2490" t="n">
+        <v>18.3799991607666</v>
+      </c>
+      <c r="F2490" t="n">
+        <v>18.0799999237061</v>
+      </c>
+      <c r="G2490" t="s">
+        <v>1121</v>
+      </c>
+      <c r="H2490" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ORS.MI.xlsx
+++ b/data/ORS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1143" uniqueCount="1143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1144" uniqueCount="1144">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,13 +44,13 @@
     <t xml:space="preserve">ORS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98275804519653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06380271911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94223785400391</t>
+    <t xml:space="preserve">7.98275899887085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06380081176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94223737716675</t>
   </si>
   <si>
     <t xml:space="preserve">7.82472467422485</t>
@@ -59,28 +59,28 @@
     <t xml:space="preserve">7.93818521499634</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90171527862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03948974609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92602872848511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86119508743286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8206729888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93413257598877</t>
+    <t xml:space="preserve">7.90171480178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03948879241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92602968215942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86119413375854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82067155838013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93413400650024</t>
   </si>
   <si>
     <t xml:space="preserve">8.02328109741211</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08811569213867</t>
+    <t xml:space="preserve">8.08811473846436</t>
   </si>
   <si>
     <t xml:space="preserve">8.14484596252441</t>
@@ -89,52 +89,52 @@
     <t xml:space="preserve">7.69910860061646</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80446434020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97465562820435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0111255645752</t>
+    <t xml:space="preserve">7.8044638633728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97465467453003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01112365722656</t>
   </si>
   <si>
     <t xml:space="preserve">8.01517581939697</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79230785369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82877731323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34745311737061</t>
+    <t xml:space="preserve">7.79230833053589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82877683639526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34745407104492</t>
   </si>
   <si>
     <t xml:space="preserve">7.84093332290649</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90982103347778</t>
+    <t xml:space="preserve">7.90982007980347</t>
   </si>
   <si>
     <t xml:space="preserve">7.85714197158813</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78015184402466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8449854850769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9787073135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88550662994385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95034217834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00302028656006</t>
+    <t xml:space="preserve">7.7801513671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84498643875122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97870779037476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88550615310669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95034170150757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00301933288574</t>
   </si>
   <si>
     <t xml:space="preserve">8.01922798156738</t>
@@ -143,28 +143,28 @@
     <t xml:space="preserve">7.91792440414429</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1002721786499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10432434082031</t>
+    <t xml:space="preserve">8.10027122497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10432243347168</t>
   </si>
   <si>
     <t xml:space="preserve">8.1853666305542</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20157623291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11242961883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07596015930176</t>
+    <t xml:space="preserve">8.20157432556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11242866516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07595920562744</t>
   </si>
   <si>
     <t xml:space="preserve">8.03138446807861</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09622001647949</t>
+    <t xml:space="preserve">8.09621906280518</t>
   </si>
   <si>
     <t xml:space="preserve">8.17726230621338</t>
@@ -173,31 +173,31 @@
     <t xml:space="preserve">8.05569744110107</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12053298950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25830554962158</t>
+    <t xml:space="preserve">8.12053203582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25830745697021</t>
   </si>
   <si>
     <t xml:space="preserve">8.42039203643799</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67162704467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55816555023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42849826812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52429103851318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4592170715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50802230834961</t>
+    <t xml:space="preserve">8.6716251373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55816650390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42849731445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52429008483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45921993255615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50802135467529</t>
   </si>
   <si>
     <t xml:space="preserve">8.60562801361084</t>
@@ -206,31 +206,31 @@
     <t xml:space="preserve">8.5324239730835</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61376094818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67069911956787</t>
+    <t xml:space="preserve">8.61376190185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67070007324219</t>
   </si>
   <si>
     <t xml:space="preserve">8.87404632568359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7927074432373</t>
+    <t xml:space="preserve">8.79270648956299</t>
   </si>
   <si>
     <t xml:space="preserve">8.90657997131348</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86591243743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94725131988525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93911647796631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78457355499268</t>
+    <t xml:space="preserve">8.86591148376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94724941253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93911743164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78457260131836</t>
   </si>
   <si>
     <t xml:space="preserve">8.74390316009521</t>
@@ -239,16 +239,16 @@
     <t xml:space="preserve">8.91471481323242</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92284870147705</t>
+    <t xml:space="preserve">8.92284965515137</t>
   </si>
   <si>
     <t xml:space="preserve">9.10992908477783</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07739162445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11806106567383</t>
+    <t xml:space="preserve">9.07739353179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11806201934814</t>
   </si>
   <si>
     <t xml:space="preserve">9.13432884216309</t>
@@ -257,25 +257,25 @@
     <t xml:space="preserve">9.15059757232666</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15873146057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7357702255249</t>
+    <t xml:space="preserve">9.15873050689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73576927185059</t>
   </si>
   <si>
     <t xml:space="preserve">8.67883205413818</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85777759552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72763633728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7032356262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66256713867188</t>
+    <t xml:space="preserve">8.8577766418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72763538360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70323467254639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66256618499756</t>
   </si>
   <si>
     <t xml:space="preserve">8.69510173797607</t>
@@ -284,37 +284,37 @@
     <t xml:space="preserve">8.6218957901001</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80084133148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77643871307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68696784973145</t>
+    <t xml:space="preserve">8.80084037780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77643966674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68696880340576</t>
   </si>
   <si>
     <t xml:space="preserve">8.54869079589844</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54055690765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58122730255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46735382080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51615619659424</t>
+    <t xml:space="preserve">8.54055881500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58122825622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46735191345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51615715026855</t>
   </si>
   <si>
     <t xml:space="preserve">8.49988746643066</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45108413696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63003063201904</t>
+    <t xml:space="preserve">8.45108318328857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63003158569336</t>
   </si>
   <si>
     <t xml:space="preserve">8.80897521972656</t>
@@ -326,28 +326,28 @@
     <t xml:space="preserve">8.930983543396</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9635181427002</t>
+    <t xml:space="preserve">8.96351718902588</t>
   </si>
   <si>
     <t xml:space="preserve">9.05299091339111</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30514144897461</t>
+    <t xml:space="preserve">9.30513954162598</t>
   </si>
   <si>
     <t xml:space="preserve">9.10179424285889</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1912670135498</t>
+    <t xml:space="preserve">9.19126605987549</t>
   </si>
   <si>
     <t xml:space="preserve">9.35394287109375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4759521484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54915618896484</t>
+    <t xml:space="preserve">9.47595119476318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54915523529053</t>
   </si>
   <si>
     <t xml:space="preserve">9.58982563018799</t>
@@ -359,28 +359,28 @@
     <t xml:space="preserve">9.71996688842773</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85824298858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0046539306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2405347824097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2486686706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3381414413452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.598424911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4276151657104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4032115936279</t>
+    <t xml:space="preserve">9.85824394226074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0046529769897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2405338287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2486696243286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3381404876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5984268188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4276142120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4032125473022</t>
   </si>
   <si>
     <t xml:space="preserve">10.5252199172974</t>
@@ -392,22 +392,22 @@
     <t xml:space="preserve">10.5658903121948</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5821580886841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7773714065552</t>
+    <t xml:space="preserve">10.5821561813354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7773704528809</t>
   </si>
   <si>
     <t xml:space="preserve">10.9807167053223</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8749771118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6553630828857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.679762840271</t>
+    <t xml:space="preserve">10.8749761581421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6553621292114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6797637939453</t>
   </si>
   <si>
     <t xml:space="preserve">10.5740232467651</t>
@@ -416,37 +416,37 @@
     <t xml:space="preserve">10.5170869827271</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5414896011353</t>
+    <t xml:space="preserve">10.5414886474609</t>
   </si>
   <si>
     <t xml:space="preserve">10.5577564239502</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5089530944824</t>
+    <t xml:space="preserve">10.5089521408081</t>
   </si>
   <si>
     <t xml:space="preserve">10.8180389404297</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6878967285156</t>
+    <t xml:space="preserve">10.6878976821899</t>
   </si>
   <si>
     <t xml:space="preserve">10.7611026763916</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6472291946411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8993787765503</t>
+    <t xml:space="preserve">10.6472301483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.899377822876</t>
   </si>
   <si>
     <t xml:space="preserve">10.8831100463867</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6716289520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.736701965332</t>
+    <t xml:space="preserve">10.671630859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7367010116577</t>
   </si>
   <si>
     <t xml:space="preserve">11.0051183700562</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">11.0213861465454</t>
   </si>
   <si>
-    <t xml:space="preserve">11.184063911438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4036779403687</t>
+    <t xml:space="preserve">11.1840648651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4036769866943</t>
   </si>
   <si>
     <t xml:space="preserve">11.395544052124</t>
@@ -470,25 +470,25 @@
     <t xml:space="preserve">11.3223390579224</t>
   </si>
   <si>
-    <t xml:space="preserve">11.330472946167</t>
+    <t xml:space="preserve">11.3304738998413</t>
   </si>
   <si>
     <t xml:space="preserve">11.3630084991455</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0783243179321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.606559753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8424406051636</t>
+    <t xml:space="preserve">11.0783233642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6065587997437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8424425125122</t>
   </si>
   <si>
     <t xml:space="preserve">10.8505744934082</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6390953063965</t>
+    <t xml:space="preserve">10.6390943527222</t>
   </si>
   <si>
     <t xml:space="preserve">10.4113454818726</t>
@@ -497,13 +497,13 @@
     <t xml:space="preserve">10.2080001831055</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2730712890625</t>
+    <t xml:space="preserve">10.2730703353882</t>
   </si>
   <si>
     <t xml:space="preserve">10.232400894165</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3218746185303</t>
+    <t xml:space="preserve">10.3218727111816</t>
   </si>
   <si>
     <t xml:space="preserve">10.3706769943237</t>
@@ -512,16 +512,16 @@
     <t xml:space="preserve">10.3300085067749</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3056039810181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2568035125732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1835975646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4845523834229</t>
+    <t xml:space="preserve">10.305606842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2568044662476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1835966110229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4845514297485</t>
   </si>
   <si>
     <t xml:space="preserve">10.3625431060791</t>
@@ -530,13 +530,13 @@
     <t xml:space="preserve">10.4438819885254</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8587083816528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9237804412842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0376529693604</t>
+    <t xml:space="preserve">10.8587074279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9237785339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0376539230347</t>
   </si>
   <si>
     <t xml:space="preserve">11.0620555877686</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">11.1433944702148</t>
   </si>
   <si>
-    <t xml:space="preserve">11.175929069519</t>
+    <t xml:space="preserve">11.1759281158447</t>
   </si>
   <si>
     <t xml:space="preserve">11.1352605819702</t>
@@ -557,7 +557,7 @@
     <t xml:space="preserve">11.0701894760132</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1189937591553</t>
+    <t xml:space="preserve">11.118992805481</t>
   </si>
   <si>
     <t xml:space="preserve">11.1515274047852</t>
@@ -566,13 +566,13 @@
     <t xml:space="preserve">11.2247323989868</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0457878112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5008182525635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1347961425781</t>
+    <t xml:space="preserve">11.045786857605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5008201599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1347942352295</t>
   </si>
   <si>
     <t xml:space="preserve">8.36161136627197</t>
@@ -581,43 +581,43 @@
     <t xml:space="preserve">8.01998996734619</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10946273803711</t>
+    <t xml:space="preserve">8.10946178436279</t>
   </si>
   <si>
     <t xml:space="preserve">8.3941478729248</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21520328521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33720970153809</t>
+    <t xml:space="preserve">8.21520233154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3372106552124</t>
   </si>
   <si>
     <t xml:space="preserve">8.31280899047852</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18266677856445</t>
+    <t xml:space="preserve">8.18266773223877</t>
   </si>
   <si>
     <t xml:space="preserve">8.34534549713135</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23960399627686</t>
+    <t xml:space="preserve">8.23960494995117</t>
   </si>
   <si>
     <t xml:space="preserve">8.49175453186035</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58936023712158</t>
+    <t xml:space="preserve">8.5893611907959</t>
   </si>
   <si>
     <t xml:space="preserve">8.76017093658447</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29654121398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25587177276611</t>
+    <t xml:space="preserve">8.29654216766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25587272644043</t>
   </si>
   <si>
     <t xml:space="preserve">8.17453384399414</t>
@@ -626,16 +626,16 @@
     <t xml:space="preserve">8.1908016204834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23147201538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28027248382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14199733734131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15826606750488</t>
+    <t xml:space="preserve">8.23147010803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2802734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14199924468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15826416015625</t>
   </si>
   <si>
     <t xml:space="preserve">8.16639995574951</t>
@@ -644,160 +644,160 @@
     <t xml:space="preserve">8.12166404724121</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05252552032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89798259735107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85731363296509</t>
+    <t xml:space="preserve">8.05252456665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89798307418823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85731410980225</t>
   </si>
   <si>
     <t xml:space="preserve">7.93051767349243</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90611600875854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93865156173706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84917974472046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80850982666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62956476211548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57262754440308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48315477371216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66616630554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60516405105591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54009246826172</t>
+    <t xml:space="preserve">7.9061164855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93865251541138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84917879104614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80851078033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62956523895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57262706756592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48315525054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66616725921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60516357421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54009342193604</t>
   </si>
   <si>
     <t xml:space="preserve">7.5238242149353</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47908735275269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61329650878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54822635650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56449413299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50755596160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46688747406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4912896156311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49942207336426</t>
+    <t xml:space="preserve">7.47908687591553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61329698562622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54822540283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56449365615845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50755548477173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4668869972229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49128913879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49942255020142</t>
   </si>
   <si>
     <t xml:space="preserve">7.31234502792358</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27980756759644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37741470336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38554906845093</t>
+    <t xml:space="preserve">7.27980804443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3774151802063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38554859161377</t>
   </si>
   <si>
     <t xml:space="preserve">7.36928129196167</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32047748565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34487915039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28794240951538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04392623901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15780019760132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3936824798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42621803283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40181732177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30420970916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36114740371704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20660400390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3530125617981</t>
+    <t xml:space="preserve">7.3204779624939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34487962722778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28794145584106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04392576217651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15780067443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39368295669556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4262170791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40181541442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3042106628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3611478805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20660448074341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35301399230957</t>
   </si>
   <si>
     <t xml:space="preserve">7.336745262146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27167510986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23100471496582</t>
+    <t xml:space="preserve">7.27167415618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23100519180298</t>
   </si>
   <si>
     <t xml:space="preserve">7.32861137390137</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26354122161865</t>
+    <t xml:space="preserve">7.26354026794434</t>
   </si>
   <si>
     <t xml:space="preserve">7.23913908004761</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22287178039551</t>
+    <t xml:space="preserve">7.22287130355835</t>
   </si>
   <si>
     <t xml:space="preserve">7.24727392196655</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44248580932617</t>
+    <t xml:space="preserve">7.44248628616333</t>
   </si>
   <si>
     <t xml:space="preserve">7.25540781021118</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18220186233521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29607629776001</t>
+    <t xml:space="preserve">7.18220233917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29607582092285</t>
   </si>
   <si>
     <t xml:space="preserve">7.16593408584595</t>
@@ -806,10 +806,10 @@
     <t xml:space="preserve">7.14153242111206</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05206060409546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07646179199219</t>
+    <t xml:space="preserve">7.05205965042114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07646226882935</t>
   </si>
   <si>
     <t xml:space="preserve">7.0357928276062</t>
@@ -818,73 +818,73 @@
     <t xml:space="preserve">7.01952505111694</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87311553955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.677903175354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85124778747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93379211425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26397323608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14840984344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09888315200806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1814284324646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16491842269897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14015626907349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21444702148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1731743812561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97506475448608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84299278259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60361289978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62012100219727</t>
+    <t xml:space="preserve">6.87311458587646</t>
   </si>
   <si>
     <t xml:space="preserve">6.67790269851685</t>
   </si>
   <si>
+    <t xml:space="preserve">6.85124683380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93379163742065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26397371292114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14840936660767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0988826751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18142795562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16491937637329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14015579223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21444606781006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17317390441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97506523132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84299373626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60361194610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62012147903442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67790222167969</t>
+  </si>
+  <si>
     <t xml:space="preserve">6.80997467041016</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54583072662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31470346450806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32295799255371</t>
+    <t xml:space="preserve">6.54583024978638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31470394134521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32295846939087</t>
   </si>
   <si>
     <t xml:space="preserve">6.34772253036499</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38074064254761</t>
+    <t xml:space="preserve">6.38073968887329</t>
   </si>
   <si>
     <t xml:space="preserve">6.3972487449646</t>
@@ -896,13 +896,13 @@
     <t xml:space="preserve">6.2816858291626</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22390460968018</t>
+    <t xml:space="preserve">6.22390413284302</t>
   </si>
   <si>
     <t xml:space="preserve">6.09183216094971</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9019775390625</t>
+    <t xml:space="preserve">5.90197849273682</t>
   </si>
   <si>
     <t xml:space="preserve">5.9597601890564</t>
@@ -923,229 +923,229 @@
     <t xml:space="preserve">6.14961338043213</t>
   </si>
   <si>
+    <t xml:space="preserve">6.07532358169556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25692319869995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00928688049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9845232963562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12485027313232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13310480117798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27343082427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44677591323853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55408525466919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51281261444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3642315864563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24041414260864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21564960479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23215961456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24866724014282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11659574508667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10834074020386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05055952072144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89372444152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.778160572052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69561529159546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79466962814331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80292320251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82768821716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78641510009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73688745498657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85245132446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29819536209106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1826319694519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15786838531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03405046463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08357763290405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81943321228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91848659515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86070537567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76165199279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75339698791504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81117820739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70387077331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74514198303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83594226837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71212387084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84419679641724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94325065612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96801424026489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8772144317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88546991348267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93499565124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02579641342163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06706809997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38899517059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19914054870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04230451583862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05881452560425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9515061378479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17437744140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17601919174194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29349803924561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25993251800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20958423614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09210538864136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10888910293579</t>
+  </si>
+  <si>
     <t xml:space="preserve">6.0753231048584</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25692272186279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00928735733032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98452281951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12485074996948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13310480117798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2734317779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44677591323853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55408477783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51281213760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3642315864563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24041318893433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21565008163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23215866088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24866819381714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11659574508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10834074020386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05055999755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89372396469116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77816104888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6956148147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79466915130615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80292367935181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82768774032593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78641510009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73688745498657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85245132446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29819583892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18263244628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15786838531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03405046463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08357763290405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81943368911743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91848659515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86070537567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76165199279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75339651107788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81117868423462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70387029647827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74514198303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83594226837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71212482452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84419679641724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94325113296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96801471710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87721538543701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88546991348267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93499660491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02579545974731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06706857681274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38899517059326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19914102554321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04230546951294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05881452560425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95150566101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17437744140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17601919174194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29349803924561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25993251800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20958423614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09210538864136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10888910293579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07532358169556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14245414733887</t>
+    <t xml:space="preserve">6.14245367050171</t>
   </si>
   <si>
     <t xml:space="preserve">6.05854082107544</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02497529983521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97462797164917</t>
+    <t xml:space="preserve">6.02497482299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97462749481201</t>
   </si>
   <si>
     <t xml:space="preserve">5.95784425735474</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15923690795898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12567090988159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19280195236206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42775869369507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7130651473999</t>
+    <t xml:space="preserve">6.15923738479614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12567186355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1928014755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42775917053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71306467056274</t>
   </si>
   <si>
     <t xml:space="preserve">6.64593458175659</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69628190994263</t>
+    <t xml:space="preserve">6.69628238677979</t>
   </si>
   <si>
     <t xml:space="preserve">6.78019523620605</t>
@@ -1157,7 +1157,7 @@
     <t xml:space="preserve">6.62915086746216</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56202030181885</t>
+    <t xml:space="preserve">6.56201982498169</t>
   </si>
   <si>
     <t xml:space="preserve">6.54523801803589</t>
@@ -1172,31 +1172,31 @@
     <t xml:space="preserve">6.57880306243896</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37741136550903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3438458442688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22636795043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36062860488892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67253875732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55506038665771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68932294845581</t>
+    <t xml:space="preserve">6.37741088867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34384632110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22636699676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36062908172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67253828048706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55506086349487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68932247161865</t>
   </si>
   <si>
     <t xml:space="preserve">5.62219142913818</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5382776260376</t>
+    <t xml:space="preserve">5.53827810287476</t>
   </si>
   <si>
     <t xml:space="preserve">5.43758249282837</t>
@@ -1205,22 +1205,22 @@
     <t xml:space="preserve">5.45436525344849</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60540819168091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5214958190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50471258163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48792934417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35366868972778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37045097351074</t>
+    <t xml:space="preserve">5.60540866851807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52149534225464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50471353530884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4879298210144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35366916656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3704514503479</t>
   </si>
   <si>
     <t xml:space="preserve">5.42079925537109</t>
@@ -1232,16 +1232,16 @@
     <t xml:space="preserve">5.30332088470459</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26975584030151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38723468780518</t>
+    <t xml:space="preserve">5.26975631713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38723421096802</t>
   </si>
   <si>
     <t xml:space="preserve">5.32010364532471</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65575647354126</t>
+    <t xml:space="preserve">5.65575695037842</t>
   </si>
   <si>
     <t xml:space="preserve">5.75645303726196</t>
@@ -1250,31 +1250,31 @@
     <t xml:space="preserve">5.70610475540161</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72288703918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73967027664185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63897466659546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57184410095215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18584203720093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20262479782104</t>
+    <t xml:space="preserve">5.72288656234741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.739670753479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6389741897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57184362411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18584156036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2026252746582</t>
   </si>
   <si>
     <t xml:space="preserve">5.21940803527832</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16905927658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13549423217773</t>
+    <t xml:space="preserve">5.16905975341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13549327850342</t>
   </si>
   <si>
     <t xml:space="preserve">5.10192918777466</t>
@@ -1283,19 +1283,19 @@
     <t xml:space="preserve">4.9508843421936</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03479862213135</t>
+    <t xml:space="preserve">5.03479814529419</t>
   </si>
   <si>
     <t xml:space="preserve">5.15227699279785</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11871147155762</t>
+    <t xml:space="preserve">5.11871194839478</t>
   </si>
   <si>
     <t xml:space="preserve">5.06836318969727</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08514642715454</t>
+    <t xml:space="preserve">5.08514595031738</t>
   </si>
   <si>
     <t xml:space="preserve">5.23619031906128</t>
@@ -1304,43 +1304,43 @@
     <t xml:space="preserve">5.25297260284424</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33688640594482</t>
+    <t xml:space="preserve">5.33688592910767</t>
   </si>
   <si>
     <t xml:space="preserve">5.79001760482788</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77323484420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58862590789795</t>
+    <t xml:space="preserve">5.77323532104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58862638473511</t>
   </si>
   <si>
     <t xml:space="preserve">4.81662368774414</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79984140396118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59844827651978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36349153518677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31314373016357</t>
+    <t xml:space="preserve">4.79984092712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59844875335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36349248886108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31314420700073</t>
   </si>
   <si>
     <t xml:space="preserve">4.19566488265991</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11175155639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02783870697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17049169540405</t>
+    <t xml:space="preserve">4.11175203323364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02783918380737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17049074172974</t>
   </si>
   <si>
     <t xml:space="preserve">4.06979560852051</t>
@@ -1349,28 +1349,28 @@
     <t xml:space="preserve">4.12014293670654</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34670829772949</t>
+    <t xml:space="preserve">4.34670925140381</t>
   </si>
   <si>
     <t xml:space="preserve">4.17888164520264</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04462146759033</t>
+    <t xml:space="preserve">4.04462099075317</t>
   </si>
   <si>
     <t xml:space="preserve">4.15370845794678</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26279592514038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16210031509399</t>
+    <t xml:space="preserve">4.26279640197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16209983825684</t>
   </si>
   <si>
     <t xml:space="preserve">4.14531755447388</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9942729473114</t>
+    <t xml:space="preserve">3.99427270889282</t>
   </si>
   <si>
     <t xml:space="preserve">4.09496927261353</t>
@@ -1379,22 +1379,22 @@
     <t xml:space="preserve">3.98588132858276</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2795786857605</t>
+    <t xml:space="preserve">4.27957820892334</t>
   </si>
   <si>
     <t xml:space="preserve">4.22923040390015</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21244812011719</t>
+    <t xml:space="preserve">4.21244764328003</t>
   </si>
   <si>
     <t xml:space="preserve">4.03622961044312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12877893447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16283082962036</t>
+    <t xml:space="preserve">4.12877941131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16283130645752</t>
   </si>
   <si>
     <t xml:space="preserve">4.07770156860352</t>
@@ -1403,16 +1403,16 @@
     <t xml:space="preserve">4.00108480453491</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20539569854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37565469741821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21390819549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22242212295532</t>
+    <t xml:space="preserve">4.20539617538452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37565422058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21390867233276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22242164611816</t>
   </si>
   <si>
     <t xml:space="preserve">4.25647354125977</t>
@@ -1424,28 +1424,28 @@
     <t xml:space="preserve">4.32457685470581</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30755043029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23944759368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35862874984741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5118613243103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53341484069824</t>
+    <t xml:space="preserve">4.30755090713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23944711685181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35862827301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51186180114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5334153175354</t>
   </si>
   <si>
     <t xml:space="preserve">5.94203662872314</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89095973968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73772573471069</t>
+    <t xml:space="preserve">5.8909592628479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73772621154785</t>
   </si>
   <si>
     <t xml:space="preserve">5.5504412651062</t>
@@ -1454,10 +1454,10 @@
     <t xml:space="preserve">5.5844931602478</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56746673583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41423368453979</t>
+    <t xml:space="preserve">5.56746768951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41423416137695</t>
   </si>
   <si>
     <t xml:space="preserve">5.2610011100769</t>
@@ -1469,43 +1469,43 @@
     <t xml:space="preserve">5.44828605651855</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6015191078186</t>
+    <t xml:space="preserve">5.60151863098145</t>
   </si>
   <si>
     <t xml:space="preserve">5.66962242126465</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5163893699646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70367383956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32910442352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27802658081055</t>
+    <t xml:space="preserve">5.51639032363892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70367431640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32910490036011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27802705764771</t>
   </si>
   <si>
     <t xml:space="preserve">5.43126010894775</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31207799911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2269492149353</t>
+    <t xml:space="preserve">5.31207847595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22694969177246</t>
   </si>
   <si>
     <t xml:space="preserve">5.00561285018921</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95453548431396</t>
+    <t xml:space="preserve">4.95453500747681</t>
   </si>
   <si>
     <t xml:space="preserve">4.93750905990601</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05669069290161</t>
+    <t xml:space="preserve">5.05669021606445</t>
   </si>
   <si>
     <t xml:space="preserve">5.03966426849365</t>
@@ -1514,58 +1514,58 @@
     <t xml:space="preserve">4.97156095504761</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88643169403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02263832092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92048311233521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90345764160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85237979888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8694052696228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34613037109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2439751625061</t>
+    <t xml:space="preserve">4.8864312171936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02263879776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92048263549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9034571647644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.852379322052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86940479278564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34613132476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24397563934326</t>
   </si>
   <si>
     <t xml:space="preserve">5.36315631866455</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38018226623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2099232673645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1588454246521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10776805877686</t>
+    <t xml:space="preserve">5.38018274307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20992374420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15884590148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10776853561401</t>
   </si>
   <si>
     <t xml:space="preserve">4.98858690261841</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09074258804321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1928973197937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17587089538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14181995391846</t>
+    <t xml:space="preserve">5.0907416343689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19289684295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17587184906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1418194770813</t>
   </si>
   <si>
     <t xml:space="preserve">5.07371616363525</t>
@@ -1574,28 +1574,28 @@
     <t xml:space="preserve">4.68212032318115</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5459132194519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59699153900146</t>
+    <t xml:space="preserve">4.54591369628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59699106216431</t>
   </si>
   <si>
     <t xml:space="preserve">4.57996511459351</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63104295730591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78427600860596</t>
+    <t xml:space="preserve">4.63104248046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7842755317688</t>
   </si>
   <si>
     <t xml:space="preserve">4.76725006103516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81832790374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80130195617676</t>
+    <t xml:space="preserve">4.8183274269104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8013014793396</t>
   </si>
   <si>
     <t xml:space="preserve">5.39720869064331</t>
@@ -1610,19 +1610,19 @@
     <t xml:space="preserve">5.49936389923096</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63557100296021</t>
+    <t xml:space="preserve">5.63557052612305</t>
   </si>
   <si>
     <t xml:space="preserve">5.68664836883545</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65259695053101</t>
+    <t xml:space="preserve">5.65259647369385</t>
   </si>
   <si>
     <t xml:space="preserve">5.8569073677063</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8739333152771</t>
+    <t xml:space="preserve">5.87393283843994</t>
   </si>
   <si>
     <t xml:space="preserve">6.31660652160645</t>
@@ -1631,19 +1631,19 @@
     <t xml:space="preserve">6.33363246917725</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29958057403564</t>
+    <t xml:space="preserve">6.2995810508728</t>
   </si>
   <si>
     <t xml:space="preserve">6.35065841674805</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43578720092773</t>
+    <t xml:space="preserve">6.43578767776489</t>
   </si>
   <si>
     <t xml:space="preserve">6.55496883392334</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69117641448975</t>
+    <t xml:space="preserve">6.69117593765259</t>
   </si>
   <si>
     <t xml:space="preserve">6.79333162307739</t>
@@ -1658,16 +1658,16 @@
     <t xml:space="preserve">6.87846088409424</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77630519866943</t>
+    <t xml:space="preserve">6.77630567550659</t>
   </si>
   <si>
     <t xml:space="preserve">6.84440898895264</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70820236206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75927972793579</t>
+    <t xml:space="preserve">6.70820188522339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75928020477295</t>
   </si>
   <si>
     <t xml:space="preserve">6.53794288635254</t>
@@ -1676,31 +1676,31 @@
     <t xml:space="preserve">6.72522783279419</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6571249961853</t>
+    <t xml:space="preserve">6.65712451934814</t>
   </si>
   <si>
     <t xml:space="preserve">6.91251230239868</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8954873085022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96359062194824</t>
+    <t xml:space="preserve">6.89548683166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96359014511108</t>
   </si>
   <si>
     <t xml:space="preserve">7.17302179336548</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05085372924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1206636428833</t>
+    <t xml:space="preserve">7.05085325241089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12066411972046</t>
   </si>
   <si>
     <t xml:space="preserve">7.57443237304688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97584247589111</t>
+    <t xml:space="preserve">7.97584199905396</t>
   </si>
   <si>
     <t xml:space="preserve">8.02819919586182</t>
@@ -1709,61 +1709,61 @@
     <t xml:space="preserve">8.0631046295166</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99329423904419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0107479095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94093656539917</t>
+    <t xml:space="preserve">7.99329328536987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01074695587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94093799591064</t>
   </si>
   <si>
     <t xml:space="preserve">8.13291454315186</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15036869049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16781997680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18527317047119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34234714508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11546230316162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25508308410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08055686950684</t>
+    <t xml:space="preserve">8.15036773681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16782093048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18527412414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34234619140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11546325683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25508403778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08055782318115</t>
   </si>
   <si>
     <t xml:space="preserve">8.20272541046143</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95838832855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37725257873535</t>
+    <t xml:space="preserve">7.95838928222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37725162506104</t>
   </si>
   <si>
     <t xml:space="preserve">8.32489395141602</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81356811523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58668327331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53432464599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69139957427979</t>
+    <t xml:space="preserve">8.81356716156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58668231964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53432559967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69139766693115</t>
   </si>
   <si>
     <t xml:space="preserve">8.60413551330566</t>
@@ -1772,16 +1772,16 @@
     <t xml:space="preserve">8.72630405426025</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42960929870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28998851776123</t>
+    <t xml:space="preserve">8.42961025238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28998947143555</t>
   </si>
   <si>
     <t xml:space="preserve">8.30744171142578</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04565238952637</t>
+    <t xml:space="preserve">8.04565334320068</t>
   </si>
   <si>
     <t xml:space="preserve">7.85367345809937</t>
@@ -1793,19 +1793,19 @@
     <t xml:space="preserve">8.22017765045166</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44706249237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35979843139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09801006317139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23763084411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48196697235107</t>
+    <t xml:space="preserve">8.44706153869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3597993850708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09800910949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23762989044189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48196792602539</t>
   </si>
   <si>
     <t xml:space="preserve">8.6215877532959</t>
@@ -1814,22 +1814,22 @@
     <t xml:space="preserve">8.55177783966064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65649318695068</t>
+    <t xml:space="preserve">8.656494140625</t>
   </si>
   <si>
     <t xml:space="preserve">8.51687240600586</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46451473236084</t>
+    <t xml:space="preserve">8.46451377868652</t>
   </si>
   <si>
     <t xml:space="preserve">8.49942016601562</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5692310333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99161720275879</t>
+    <t xml:space="preserve">8.56923007965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99161815643311</t>
   </si>
   <si>
     <t xml:space="preserve">9.59893417358398</t>
@@ -1841,10 +1841,10 @@
     <t xml:space="preserve">9.8170919418335</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29351234436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46803951263428</t>
+    <t xml:space="preserve">9.29351425170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46804046630859</t>
   </si>
   <si>
     <t xml:space="preserve">9.55530261993408</t>
@@ -1856,22 +1856,22 @@
     <t xml:space="preserve">9.9043550491333</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33714485168457</t>
+    <t xml:space="preserve">9.33714580535889</t>
   </si>
   <si>
     <t xml:space="preserve">9.9479866027832</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8607234954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5151958465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4279327392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5588283538818</t>
+    <t xml:space="preserve">9.86072254180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5151968002319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4279317855835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5588274002075</t>
   </si>
   <si>
     <t xml:space="preserve">10.6024589538574</t>
@@ -1880,13 +1880,13 @@
     <t xml:space="preserve">10.8206167221069</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7333536148071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7769861221313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2970380783081</t>
+    <t xml:space="preserve">10.7333545684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.776985168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2970390319824</t>
   </si>
   <si>
     <t xml:space="preserve">10.3843011856079</t>
@@ -1904,31 +1904,31 @@
     <t xml:space="preserve">10.0788812637329</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51167011260986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72982883453369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68619728088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98809432983398</t>
+    <t xml:space="preserve">9.51167106628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72982788085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68619823455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98809337615967</t>
   </si>
   <si>
     <t xml:space="preserve">9.42440795898438</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6496171951294</t>
+    <t xml:space="preserve">11.6496152877808</t>
   </si>
   <si>
     <t xml:space="preserve">11.5623531341553</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7805109024048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9114036560059</t>
+    <t xml:space="preserve">11.7805099487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9114046096802</t>
   </si>
   <si>
     <t xml:space="preserve">11.9550352096558</t>
@@ -1943,19 +1943,19 @@
     <t xml:space="preserve">12.2604570388794</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2168245315552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3913507461548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7368793487549</t>
+    <t xml:space="preserve">12.2168254852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3913516998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7368783950806</t>
   </si>
   <si>
     <t xml:space="preserve">11.8677730560303</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6059846878052</t>
+    <t xml:space="preserve">11.6059837341309</t>
   </si>
   <si>
     <t xml:space="preserve">10.9515113830566</t>
@@ -1967,7 +1967,7 @@
     <t xml:space="preserve">11.3005638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3441944122314</t>
+    <t xml:space="preserve">11.3441953659058</t>
   </si>
   <si>
     <t xml:space="preserve">10.9951429367065</t>
@@ -1979,19 +1979,19 @@
     <t xml:space="preserve">10.9078798294067</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4314594268799</t>
+    <t xml:space="preserve">11.4314584732056</t>
   </si>
   <si>
     <t xml:space="preserve">11.0387735366821</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9899406433105</t>
+    <t xml:space="preserve">11.9899415969849</t>
   </si>
   <si>
     <t xml:space="preserve">11.7456045150757</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5361728668213</t>
+    <t xml:space="preserve">11.5361738204956</t>
   </si>
   <si>
     <t xml:space="preserve">11.5187215805054</t>
@@ -2000,13 +2000,13 @@
     <t xml:space="preserve">11.6234359741211</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4489107131958</t>
+    <t xml:space="preserve">11.4489116668701</t>
   </si>
   <si>
     <t xml:space="preserve">11.6408891677856</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7281513214111</t>
+    <t xml:space="preserve">11.7281522750854</t>
   </si>
   <si>
     <t xml:space="preserve">11.9201307296753</t>
@@ -2015,19 +2015,19 @@
     <t xml:space="preserve">11.1173105239868</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0998582839966</t>
+    <t xml:space="preserve">11.0998592376709</t>
   </si>
   <si>
     <t xml:space="preserve">10.8031644821167</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7508058547974</t>
+    <t xml:space="preserve">10.7508068084717</t>
   </si>
   <si>
     <t xml:space="preserve">10.3319435119629</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1050605773926</t>
+    <t xml:space="preserve">10.1050596237183</t>
   </si>
   <si>
     <t xml:space="preserve">9.81839179992676</t>
@@ -2036,7 +2036,7 @@
     <t xml:space="preserve">9.69297409057617</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71089172363281</t>
+    <t xml:space="preserve">9.7108907699585</t>
   </si>
   <si>
     <t xml:space="preserve">10.1408929824829</t>
@@ -2054,7 +2054,7 @@
     <t xml:space="preserve">10.1588106155396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0692253112793</t>
+    <t xml:space="preserve">10.0692262649536</t>
   </si>
   <si>
     <t xml:space="preserve">10.0871438980103</t>
@@ -2063,13 +2063,13 @@
     <t xml:space="preserve">10.4633951187134</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7858972549438</t>
+    <t xml:space="preserve">10.7858982086182</t>
   </si>
   <si>
     <t xml:space="preserve">10.5708961486816</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7142305374146</t>
+    <t xml:space="preserve">10.7142295837402</t>
   </si>
   <si>
     <t xml:space="preserve">10.7500638961792</t>
@@ -2087,13 +2087,13 @@
     <t xml:space="preserve">10.5888118743896</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5171461105347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8575639724731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9113159179688</t>
+    <t xml:space="preserve">10.5171451568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8575649261475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9113149642944</t>
   </si>
   <si>
     <t xml:space="preserve">10.6067295074463</t>
@@ -2102,7 +2102,7 @@
     <t xml:space="preserve">10.6604795455933</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3021440505981</t>
+    <t xml:space="preserve">10.3021450042725</t>
   </si>
   <si>
     <t xml:space="preserve">10.4096450805664</t>
@@ -2111,7 +2111,7 @@
     <t xml:space="preserve">10.3558940887451</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6783971786499</t>
+    <t xml:space="preserve">10.6783962249756</t>
   </si>
   <si>
     <t xml:space="preserve">10.4275617599487</t>
@@ -2120,16 +2120,16 @@
     <t xml:space="preserve">10.535062789917</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1800651550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9829807281494</t>
+    <t xml:space="preserve">11.1800661087036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9829816818237</t>
   </si>
   <si>
     <t xml:space="preserve">11.4846515655518</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3771514892578</t>
+    <t xml:space="preserve">11.3771505355835</t>
   </si>
   <si>
     <t xml:space="preserve">11.7354869842529</t>
@@ -2141,7 +2141,7 @@
     <t xml:space="preserve">11.9325704574585</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0221548080444</t>
+    <t xml:space="preserve">12.0221538543701</t>
   </si>
   <si>
     <t xml:space="preserve">11.8788204193115</t>
@@ -2159,7 +2159,7 @@
     <t xml:space="preserve">12.0938215255737</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3984079360962</t>
+    <t xml:space="preserve">12.3984069824219</t>
   </si>
   <si>
     <t xml:space="preserve">12.201322555542</t>
@@ -2177,7 +2177,7 @@
     <t xml:space="preserve">12.8463258743286</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8104934692383</t>
+    <t xml:space="preserve">12.810492515564</t>
   </si>
   <si>
     <t xml:space="preserve">12.9179935455322</t>
@@ -2186,16 +2186,16 @@
     <t xml:space="preserve">13.258412361145</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4017457962036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4375801086426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6884145736694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9034156799316</t>
+    <t xml:space="preserve">13.4017467498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4375791549683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6884136199951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.903416633606</t>
   </si>
   <si>
     <t xml:space="preserve">14.6559200286865</t>
@@ -2204,91 +2204,91 @@
     <t xml:space="preserve">14.2438344955444</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6380043029785</t>
+    <t xml:space="preserve">14.6380033493042</t>
   </si>
   <si>
     <t xml:space="preserve">14.92467212677</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5125875473022</t>
+    <t xml:space="preserve">14.5125865936279</t>
   </si>
   <si>
     <t xml:space="preserve">14.5663366317749</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7992553710938</t>
+    <t xml:space="preserve">14.7992544174194</t>
   </si>
   <si>
     <t xml:space="preserve">14.5484189987183</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4946689605713</t>
+    <t xml:space="preserve">14.4946699142456</t>
   </si>
   <si>
     <t xml:space="preserve">14.2617511749268</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8888397216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8171730041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.387167930603</t>
+    <t xml:space="preserve">14.8888387680054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8171720504761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3871688842773</t>
   </si>
   <si>
     <t xml:space="preserve">14.7634201049805</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6200857162476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9067535400391</t>
+    <t xml:space="preserve">14.6200866699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9067544937134</t>
   </si>
   <si>
     <t xml:space="preserve">15.1217546463013</t>
   </si>
   <si>
-    <t xml:space="preserve">15.032172203064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7455034255981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0500888824463</t>
+    <t xml:space="preserve">15.0321731567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7455043792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.050087928772</t>
   </si>
   <si>
     <t xml:space="preserve">15.0680055618286</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1038398742676</t>
+    <t xml:space="preserve">15.1038408279419</t>
   </si>
   <si>
     <t xml:space="preserve">14.5305023193359</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7096700668335</t>
+    <t xml:space="preserve">14.7096710205078</t>
   </si>
   <si>
     <t xml:space="preserve">14.2080001831055</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6167478561401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5092458724976</t>
+    <t xml:space="preserve">13.6167469024658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5092468261719</t>
   </si>
   <si>
     <t xml:space="preserve">13.0434112548828</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1688270568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9717435836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4700736999512</t>
+    <t xml:space="preserve">13.1688280105591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9717426300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4700746536255</t>
   </si>
   <si>
     <t xml:space="preserve">13.2404947280884</t>
@@ -2306,22 +2306,22 @@
     <t xml:space="preserve">13.4913301467896</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2225790023804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2046613693237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0613279342651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0075769424438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6313257217407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0971612930298</t>
+    <t xml:space="preserve">13.2225780487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2046604156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0613269805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0075778961182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6313247680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0971603393555</t>
   </si>
   <si>
     <t xml:space="preserve">13.0792446136475</t>
@@ -2336,7 +2336,7 @@
     <t xml:space="preserve">12.9538269042969</t>
   </si>
   <si>
-    <t xml:space="preserve">12.720908164978</t>
+    <t xml:space="preserve">12.7209091186523</t>
   </si>
   <si>
     <t xml:space="preserve">12.5596580505371</t>
@@ -2351,7 +2351,7 @@
     <t xml:space="preserve">13.5271635055542</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3479957580566</t>
+    <t xml:space="preserve">13.3479948043823</t>
   </si>
   <si>
     <t xml:space="preserve">13.276328086853</t>
@@ -2360,22 +2360,22 @@
     <t xml:space="preserve">12.7925758361816</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5954914093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5238246917725</t>
+    <t xml:space="preserve">12.5954923629761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5238237380981</t>
   </si>
   <si>
     <t xml:space="preserve">12.5059070587158</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4879903793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3088216781616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5417404174805</t>
+    <t xml:space="preserve">12.4879894256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3088226318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5417413711548</t>
   </si>
   <si>
     <t xml:space="preserve">12.8284091949463</t>
@@ -2399,10 +2399,10 @@
     <t xml:space="preserve">12.4342403411865</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9504880905151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2192392349243</t>
+    <t xml:space="preserve">11.9504871368408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2192401885986</t>
   </si>
   <si>
     <t xml:space="preserve">11.8250703811646</t>
@@ -2411,10 +2411,10 @@
     <t xml:space="preserve">12.1117391586304</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9684038162231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0400705337524</t>
+    <t xml:space="preserve">11.9684047698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0400714874268</t>
   </si>
   <si>
     <t xml:space="preserve">12.0042381286621</t>
@@ -2423,7 +2423,7 @@
     <t xml:space="preserve">12.255072593689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7388257980347</t>
+    <t xml:space="preserve">12.7388248443604</t>
   </si>
   <si>
     <t xml:space="preserve">13.7421646118164</t>
@@ -2435,7 +2435,7 @@
     <t xml:space="preserve">14.0825834274292</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0109176635742</t>
+    <t xml:space="preserve">14.0109167098999</t>
   </si>
   <si>
     <t xml:space="preserve">13.7242479324341</t>
@@ -2444,10 +2444,10 @@
     <t xml:space="preserve">14.0467500686646</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0646667480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9392499923706</t>
+    <t xml:space="preserve">14.0646657943726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9392490386963</t>
   </si>
   <si>
     <t xml:space="preserve">13.6346645355225</t>
@@ -2462,7 +2462,7 @@
     <t xml:space="preserve">13.9571657180786</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8496656417847</t>
+    <t xml:space="preserve">13.8496646881104</t>
   </si>
   <si>
     <t xml:space="preserve">13.9750833511353</t>
@@ -2477,31 +2477,31 @@
     <t xml:space="preserve">13.1867456436157</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3838291168213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5988311767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7029914855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8429861068726</t>
+    <t xml:space="preserve">13.383828163147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5988302230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.70299243927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8429870605469</t>
   </si>
   <si>
     <t xml:space="preserve">11.7892360687256</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6817350387573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0759038925171</t>
+    <t xml:space="preserve">11.6817359924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0759048461914</t>
   </si>
   <si>
     <t xml:space="preserve">11.5742359161377</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2158994674683</t>
+    <t xml:space="preserve">11.2159004211426</t>
   </si>
   <si>
     <t xml:space="preserve">11.3592348098755</t>
@@ -2510,7 +2510,7 @@
     <t xml:space="preserve">11.4309015274048</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3054838180542</t>
+    <t xml:space="preserve">11.3054828643799</t>
   </si>
   <si>
     <t xml:space="preserve">11.2875671386719</t>
@@ -3441,6 +3441,9 @@
   </si>
   <si>
     <t xml:space="preserve">18.2800006866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1000003814697</t>
   </si>
 </sst>
 </file>
@@ -68493,7 +68496,7 @@
     </row>
     <row r="2490">
       <c r="A2490" s="1" t="n">
-        <v>45945.649375</v>
+        <v>45945.2916666667</v>
       </c>
       <c r="B2490" t="n">
         <v>57290</v>
@@ -68514,6 +68517,32 @@
         <v>1121</v>
       </c>
       <c r="H2490" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2491">
+      <c r="A2491" s="1" t="n">
+        <v>45946.6494444444</v>
+      </c>
+      <c r="B2491" t="n">
+        <v>35898</v>
+      </c>
+      <c r="C2491" t="n">
+        <v>18.1200008392334</v>
+      </c>
+      <c r="D2491" t="n">
+        <v>17.8199996948242</v>
+      </c>
+      <c r="E2491" t="n">
+        <v>18.0599994659424</v>
+      </c>
+      <c r="F2491" t="n">
+        <v>18.1000003814697</v>
+      </c>
+      <c r="G2491" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H2491" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ORS.MI.xlsx
+++ b/data/ORS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1144" uniqueCount="1144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1145" uniqueCount="1145">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,25 +38,25 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08406352996826</t>
+    <t xml:space="preserve">8.08406448364258</t>
   </si>
   <si>
     <t xml:space="preserve">ORS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98275804519653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06380081176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94223690032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82472467422485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93818616867065</t>
+    <t xml:space="preserve">7.98275947570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06380271911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94223737716675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82472515106201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93818521499634</t>
   </si>
   <si>
     <t xml:space="preserve">7.9017162322998</t>
@@ -65,46 +65,46 @@
     <t xml:space="preserve">8.03948879241943</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92602920532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86119365692139</t>
+    <t xml:space="preserve">7.92602968215942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86119413375854</t>
   </si>
   <si>
     <t xml:space="preserve">7.82067203521729</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93413352966309</t>
+    <t xml:space="preserve">7.93413305282593</t>
   </si>
   <si>
     <t xml:space="preserve">8.02328109741211</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08811473846436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14484691619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69910717010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80446243286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97465419769287</t>
+    <t xml:space="preserve">8.08811569213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1448450088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69910764694214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80446434020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97465515136719</t>
   </si>
   <si>
     <t xml:space="preserve">8.0111255645752</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01517581939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79230880737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82877826690674</t>
+    <t xml:space="preserve">8.01517677307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79230737686157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82877731323242</t>
   </si>
   <si>
     <t xml:space="preserve">8.34745311737061</t>
@@ -122,37 +122,37 @@
     <t xml:space="preserve">7.78015089035034</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84498596191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97870683670044</t>
+    <t xml:space="preserve">7.84498643875122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97870635986328</t>
   </si>
   <si>
     <t xml:space="preserve">7.88550758361816</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95034217834473</t>
+    <t xml:space="preserve">7.95034122467041</t>
   </si>
   <si>
     <t xml:space="preserve">8.00302028656006</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0192289352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91792488098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10027313232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.104323387146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1853666305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20157623291016</t>
+    <t xml:space="preserve">8.01922798156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91792440414429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1002721786499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10432434082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18536758422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20157527923584</t>
   </si>
   <si>
     <t xml:space="preserve">8.11242866516113</t>
@@ -161,43 +161,43 @@
     <t xml:space="preserve">8.07595825195312</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03138446807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09621906280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1772632598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05569744110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12053298950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25830554962158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42039203643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67162704467773</t>
+    <t xml:space="preserve">8.03138542175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09622001647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17726230621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05569839477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12053203582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2583065032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4203929901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67162609100342</t>
   </si>
   <si>
     <t xml:space="preserve">8.55816555023193</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42849636077881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52429008483887</t>
+    <t xml:space="preserve">8.42849731445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52429103851318</t>
   </si>
   <si>
     <t xml:space="preserve">8.45921897888184</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50802040100098</t>
+    <t xml:space="preserve">8.50802230834961</t>
   </si>
   <si>
     <t xml:space="preserve">8.60562801361084</t>
@@ -209,52 +209,52 @@
     <t xml:space="preserve">8.61376190185547</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67069911956787</t>
+    <t xml:space="preserve">8.67070007324219</t>
   </si>
   <si>
     <t xml:space="preserve">8.87404632568359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7927074432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90658187866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86591148376465</t>
+    <t xml:space="preserve">8.79270839691162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90658092498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86591243743896</t>
   </si>
   <si>
     <t xml:space="preserve">8.94725036621094</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93911743164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78457260131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74390316009521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91471481323242</t>
+    <t xml:space="preserve">8.93911647796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78457355499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74390506744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91471385955811</t>
   </si>
   <si>
     <t xml:space="preserve">8.92284870147705</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10992813110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07739162445068</t>
+    <t xml:space="preserve">9.10993003845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.077392578125</t>
   </si>
   <si>
     <t xml:space="preserve">9.11806297302246</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13432884216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15059852600098</t>
+    <t xml:space="preserve">9.1343297958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15059757232666</t>
   </si>
   <si>
     <t xml:space="preserve">9.15873146057129</t>
@@ -263,22 +263,22 @@
     <t xml:space="preserve">8.73576927185059</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67883205413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85777759552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72763538360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70323657989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66256618499756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69510173797607</t>
+    <t xml:space="preserve">8.67883110046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8577766418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72763729095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70323467254639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66256523132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69510078430176</t>
   </si>
   <si>
     <t xml:space="preserve">8.62189674377441</t>
@@ -287,10 +287,10 @@
     <t xml:space="preserve">8.80084133148193</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77643966674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68696880340576</t>
+    <t xml:space="preserve">8.77643871307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68696689605713</t>
   </si>
   <si>
     <t xml:space="preserve">8.54869079589844</t>
@@ -299,7 +299,7 @@
     <t xml:space="preserve">8.54055690765381</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58122730255127</t>
+    <t xml:space="preserve">8.58122825622559</t>
   </si>
   <si>
     <t xml:space="preserve">8.46735191345215</t>
@@ -308,25 +308,25 @@
     <t xml:space="preserve">8.51615619659424</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49988746643066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45108318328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63003158569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80897521972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89031410217285</t>
+    <t xml:space="preserve">8.49988842010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45108509063721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63003063201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80897617340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89031505584717</t>
   </si>
   <si>
     <t xml:space="preserve">8.93098258972168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96351909637451</t>
+    <t xml:space="preserve">8.9635181427002</t>
   </si>
   <si>
     <t xml:space="preserve">9.05299091339111</t>
@@ -335,22 +335,22 @@
     <t xml:space="preserve">9.30514144897461</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10179424285889</t>
+    <t xml:space="preserve">9.10179328918457</t>
   </si>
   <si>
     <t xml:space="preserve">9.1912670135498</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35394287109375</t>
+    <t xml:space="preserve">9.35394382476807</t>
   </si>
   <si>
     <t xml:space="preserve">9.4759521484375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54915618896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5898265838623</t>
+    <t xml:space="preserve">9.54915714263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58982563018799</t>
   </si>
   <si>
     <t xml:space="preserve">9.66303062438965</t>
@@ -362,19 +362,19 @@
     <t xml:space="preserve">9.85824394226074</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0046539306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2405347824097</t>
+    <t xml:space="preserve">10.0046529769897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2405338287354</t>
   </si>
   <si>
     <t xml:space="preserve">10.24866771698</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3381414413452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5984239578247</t>
+    <t xml:space="preserve">10.3381423950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5984268188477</t>
   </si>
   <si>
     <t xml:space="preserve">10.4276142120361</t>
@@ -383,25 +383,25 @@
     <t xml:space="preserve">10.4032115936279</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5252199172974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4601488113403</t>
+    <t xml:space="preserve">10.5252208709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4601497650146</t>
   </si>
   <si>
     <t xml:space="preserve">10.5658893585205</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5821580886841</t>
+    <t xml:space="preserve">10.5821571350098</t>
   </si>
   <si>
     <t xml:space="preserve">10.7773704528809</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9807176589966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8749761581421</t>
+    <t xml:space="preserve">10.9807167053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8749771118164</t>
   </si>
   <si>
     <t xml:space="preserve">10.6553630828857</t>
@@ -410,13 +410,13 @@
     <t xml:space="preserve">10.6797637939453</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5740251541138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5170869827271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5414886474609</t>
+    <t xml:space="preserve">10.5740242004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5170879364014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5414896011353</t>
   </si>
   <si>
     <t xml:space="preserve">10.5577564239502</t>
@@ -428,103 +428,103 @@
     <t xml:space="preserve">10.818039894104</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6878986358643</t>
+    <t xml:space="preserve">10.6878967285156</t>
   </si>
   <si>
     <t xml:space="preserve">10.7611026763916</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6472291946411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8993787765503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8831100463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6716299057007</t>
+    <t xml:space="preserve">10.6472282409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.899377822876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.883111000061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6716289520264</t>
   </si>
   <si>
     <t xml:space="preserve">10.7367000579834</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0051193237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0213861465454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1840648651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4036769866943</t>
+    <t xml:space="preserve">11.0051183700562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0213871002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1840629577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4036779403687</t>
   </si>
   <si>
     <t xml:space="preserve">11.395544052124</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3386058807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.322340965271</t>
+    <t xml:space="preserve">11.3386077880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3223400115967</t>
   </si>
   <si>
     <t xml:space="preserve">11.330472946167</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3630094528198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0783224105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6065587997437</t>
+    <t xml:space="preserve">11.3630084991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0783233642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.606559753418</t>
   </si>
   <si>
     <t xml:space="preserve">10.8424425125122</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8505754470825</t>
+    <t xml:space="preserve">10.8505744934082</t>
   </si>
   <si>
     <t xml:space="preserve">10.6390943527222</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4113464355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2080011367798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2730722427368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2323999404907</t>
+    <t xml:space="preserve">10.4113454818726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2080001831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2730712890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.232400894165</t>
   </si>
   <si>
     <t xml:space="preserve">10.321873664856</t>
   </si>
   <si>
-    <t xml:space="preserve">10.370677947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3300065994263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3056058883667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2568035125732</t>
+    <t xml:space="preserve">10.3706769943237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3300085067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3056049346924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2568044662476</t>
   </si>
   <si>
     <t xml:space="preserve">10.1835975646973</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4845533370972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3625421524048</t>
+    <t xml:space="preserve">10.4845514297485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3625431060791</t>
   </si>
   <si>
     <t xml:space="preserve">10.4438819885254</t>
@@ -536,13 +536,13 @@
     <t xml:space="preserve">10.9237794876099</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0376529693604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0620555877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.102725982666</t>
+    <t xml:space="preserve">11.037654876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0620565414429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1027250289917</t>
   </si>
   <si>
     <t xml:space="preserve">11.1433935165405</t>
@@ -551,16 +551,16 @@
     <t xml:space="preserve">11.175929069519</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1352596282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0701894760132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1189947128296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1515283584595</t>
+    <t xml:space="preserve">11.1352605819702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0701904296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.118992805481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1515293121338</t>
   </si>
   <si>
     <t xml:space="preserve">11.2247314453125</t>
@@ -578,40 +578,40 @@
     <t xml:space="preserve">8.36161231994629</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01999092102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10946178436279</t>
+    <t xml:space="preserve">8.01998996734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10946369171143</t>
   </si>
   <si>
     <t xml:space="preserve">8.3941478729248</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21520328521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33721160888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3128080368042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18266677856445</t>
+    <t xml:space="preserve">8.21520233154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3372106552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31280899047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18266773223877</t>
   </si>
   <si>
     <t xml:space="preserve">8.34534549713135</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23960399627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49175453186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5893611907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76017284393311</t>
+    <t xml:space="preserve">8.23960494995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49175357818604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58936023712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76017093658447</t>
   </si>
   <si>
     <t xml:space="preserve">8.29654216766357</t>
@@ -620,13 +620,13 @@
     <t xml:space="preserve">8.25587272644043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17453289031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19080066680908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23147106170654</t>
+    <t xml:space="preserve">8.17453384399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1908016204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23147201538086</t>
   </si>
   <si>
     <t xml:space="preserve">8.2802734375</t>
@@ -635,163 +635,163 @@
     <t xml:space="preserve">8.14199733734131</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1582670211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16640090942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12166404724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05252647399902</t>
+    <t xml:space="preserve">8.15826606750488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1663990020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12166309356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05252552032471</t>
   </si>
   <si>
     <t xml:space="preserve">7.89798259735107</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85731410980225</t>
+    <t xml:space="preserve">7.85731267929077</t>
   </si>
   <si>
     <t xml:space="preserve">7.93051719665527</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90611600875854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93865156173706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84917879104614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80851030349731</t>
+    <t xml:space="preserve">7.90611553192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93865060806274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84917974472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80850982666016</t>
   </si>
   <si>
     <t xml:space="preserve">7.62956476211548</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5726261138916</t>
+    <t xml:space="preserve">7.57262754440308</t>
   </si>
   <si>
     <t xml:space="preserve">7.48315620422363</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66616725921631</t>
+    <t xml:space="preserve">7.66616678237915</t>
   </si>
   <si>
     <t xml:space="preserve">7.60516309738159</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54009389877319</t>
+    <t xml:space="preserve">7.54009199142456</t>
   </si>
   <si>
     <t xml:space="preserve">7.52382469177246</t>
   </si>
   <si>
-    <t xml:space="preserve">7.479088306427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61329698562622</t>
+    <t xml:space="preserve">7.47908735275269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61329650878906</t>
   </si>
   <si>
     <t xml:space="preserve">7.54822635650635</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56449317932129</t>
+    <t xml:space="preserve">7.56449365615845</t>
   </si>
   <si>
     <t xml:space="preserve">7.50755596160889</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46688604354858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4912896156311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49942207336426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31234455108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27980899810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37741470336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38554906845093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36928129196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32047748565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34488010406494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28794145584106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04392528533936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15779972076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3936824798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42621803283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40181541442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3042106628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36114740371704</t>
+    <t xml:space="preserve">7.4668869972229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49129009246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49942255020142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31234502792358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27980852127075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37741422653198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38554859161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36928081512451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3204779624939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34487962722778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28794193267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04392671585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15780019760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39368295669556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42621755599976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40181684494019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30421018600464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3611478805542</t>
   </si>
   <si>
     <t xml:space="preserve">7.20660352706909</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35301303863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33674621582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27167510986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23100471496582</t>
+    <t xml:space="preserve">7.3530125617981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33674573898315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27167463302612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23100566864014</t>
   </si>
   <si>
     <t xml:space="preserve">7.32861137390137</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26354074478149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23914003372192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22287082672119</t>
+    <t xml:space="preserve">7.26354169845581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23913955688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22287130355835</t>
   </si>
   <si>
     <t xml:space="preserve">7.24727344512939</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44248628616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25540685653687</t>
+    <t xml:space="preserve">7.44248580932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25540828704834</t>
   </si>
   <si>
     <t xml:space="preserve">7.18220233917236</t>
@@ -800,40 +800,40 @@
     <t xml:space="preserve">7.29607534408569</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16593503952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14153242111206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05205965042114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07646322250366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03579235076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0195255279541</t>
+    <t xml:space="preserve">7.16593360900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1415319442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0520601272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07646226882935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03579330444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01952457427979</t>
   </si>
   <si>
     <t xml:space="preserve">6.87311458587646</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67790269851685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85124778747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93379211425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26397275924683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14840936660767</t>
+    <t xml:space="preserve">6.677903175354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85124683380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93379163742065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26397323608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14841032028198</t>
   </si>
   <si>
     <t xml:space="preserve">7.09888315200806</t>
@@ -842,28 +842,28 @@
     <t xml:space="preserve">7.18142890930176</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16491889953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14015579223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21444606781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17317390441895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97506427764893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84299325942993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60361242294312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62012147903442</t>
+    <t xml:space="preserve">7.16491842269897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14015626907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21444654464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1731743812561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97506475448608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84299278259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60361194610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62012100219727</t>
   </si>
   <si>
     <t xml:space="preserve">6.67790222167969</t>
@@ -875,52 +875,52 @@
     <t xml:space="preserve">6.54583072662354</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31470394134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32295894622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34772253036499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38074064254761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3972487449646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47153949737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28168535232544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22390365600586</t>
+    <t xml:space="preserve">6.31470346450806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32295846939087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34772300720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38074016571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39724969863892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47153997421265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2816858291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22390413284302</t>
   </si>
   <si>
     <t xml:space="preserve">6.09183168411255</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90197849273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9597601890564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99277687072754</t>
+    <t xml:space="preserve">5.90197801589966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95975971221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9927773475647</t>
   </si>
   <si>
     <t xml:space="preserve">6.20739507675171</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14135980606079</t>
+    <t xml:space="preserve">6.14135932922363</t>
   </si>
   <si>
     <t xml:space="preserve">6.19088649749756</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14961338043213</t>
+    <t xml:space="preserve">6.14961385726929</t>
   </si>
   <si>
     <t xml:space="preserve">6.07532358169556</t>
@@ -932,22 +932,22 @@
     <t xml:space="preserve">6.00928783416748</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9845232963562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12485074996948</t>
+    <t xml:space="preserve">5.98452377319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12485122680664</t>
   </si>
   <si>
     <t xml:space="preserve">6.13310480117798</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27343130111694</t>
+    <t xml:space="preserve">6.2734317779541</t>
   </si>
   <si>
     <t xml:space="preserve">6.44677591323853</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55408525466919</t>
+    <t xml:space="preserve">6.55408477783203</t>
   </si>
   <si>
     <t xml:space="preserve">6.51281213760376</t>
@@ -956,37 +956,37 @@
     <t xml:space="preserve">6.3642315864563</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24041366577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21565008163452</t>
+    <t xml:space="preserve">6.24041414260864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21564960479736</t>
   </si>
   <si>
     <t xml:space="preserve">6.23215961456299</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2486686706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11659622192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10834074020386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05055999755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89372444152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77816104888916</t>
+    <t xml:space="preserve">6.24866819381714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11659669876099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10834121704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05055952072144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89372396469116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.778160572052</t>
   </si>
   <si>
     <t xml:space="preserve">5.6956148147583</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79467010498047</t>
+    <t xml:space="preserve">5.79466915130615</t>
   </si>
   <si>
     <t xml:space="preserve">5.80292320251465</t>
@@ -998,16 +998,16 @@
     <t xml:space="preserve">5.78641510009766</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73688745498657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85245084762573</t>
+    <t xml:space="preserve">5.73688793182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85245132446289</t>
   </si>
   <si>
     <t xml:space="preserve">6.29819536209106</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18263244628906</t>
+    <t xml:space="preserve">6.1826319694519</t>
   </si>
   <si>
     <t xml:space="preserve">6.15786838531494</t>
@@ -1019,7 +1019,7 @@
     <t xml:space="preserve">6.08357763290405</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81943416595459</t>
+    <t xml:space="preserve">5.81943368911743</t>
   </si>
   <si>
     <t xml:space="preserve">5.91848659515381</t>
@@ -1034,22 +1034,22 @@
     <t xml:space="preserve">5.75339698791504</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8111777305603</t>
+    <t xml:space="preserve">5.81117820739746</t>
   </si>
   <si>
     <t xml:space="preserve">5.70387029647827</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74514293670654</t>
+    <t xml:space="preserve">5.74514245986938</t>
   </si>
   <si>
     <t xml:space="preserve">5.83594226837158</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71212434768677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84419727325439</t>
+    <t xml:space="preserve">5.71212482452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84419679641724</t>
   </si>
   <si>
     <t xml:space="preserve">5.94325065612793</t>
@@ -1058,7 +1058,7 @@
     <t xml:space="preserve">5.96801424026489</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87721490859985</t>
+    <t xml:space="preserve">5.87721538543701</t>
   </si>
   <si>
     <t xml:space="preserve">5.88546943664551</t>
@@ -1070,10 +1070,10 @@
     <t xml:space="preserve">6.02579593658447</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0670690536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38899421691895</t>
+    <t xml:space="preserve">6.06706857681274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38899517059326</t>
   </si>
   <si>
     <t xml:space="preserve">6.19914102554321</t>
@@ -1085,10 +1085,10 @@
     <t xml:space="preserve">6.05881404876709</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95150566101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17437696456909</t>
+    <t xml:space="preserve">5.95150518417358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17437744140625</t>
   </si>
   <si>
     <t xml:space="preserve">6.1760196685791</t>
@@ -1100,25 +1100,25 @@
     <t xml:space="preserve">6.25993251800537</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20958375930786</t>
+    <t xml:space="preserve">6.20958471298218</t>
   </si>
   <si>
     <t xml:space="preserve">6.09210538864136</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10888862609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14245319366455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0585412979126</t>
+    <t xml:space="preserve">6.10888910293579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14245367050171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05854034423828</t>
   </si>
   <si>
     <t xml:space="preserve">6.02497529983521</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97462749481201</t>
+    <t xml:space="preserve">5.97462797164917</t>
   </si>
   <si>
     <t xml:space="preserve">5.95784473419189</t>
@@ -1127,7 +1127,7 @@
     <t xml:space="preserve">6.15923643112183</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12567090988159</t>
+    <t xml:space="preserve">6.12567138671875</t>
   </si>
   <si>
     <t xml:space="preserve">6.1928014755249</t>
@@ -1136,40 +1136,40 @@
     <t xml:space="preserve">6.42775917053223</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7130651473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64593410491943</t>
+    <t xml:space="preserve">6.71306467056274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64593458175659</t>
   </si>
   <si>
     <t xml:space="preserve">6.69628190994263</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78019523620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72984743118286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.629150390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56202030181885</t>
+    <t xml:space="preserve">6.78019571304321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7298469543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62915086746216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56201982498169</t>
   </si>
   <si>
     <t xml:space="preserve">6.54523801803589</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67949914932251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66271686553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57880353927612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37741088867188</t>
+    <t xml:space="preserve">6.67949867248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66271638870239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57880306243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37741136550903</t>
   </si>
   <si>
     <t xml:space="preserve">6.34384632110596</t>
@@ -1184,22 +1184,22 @@
     <t xml:space="preserve">5.67253875732422</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55505990982056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68932247161865</t>
+    <t xml:space="preserve">5.55506038665771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68932294845581</t>
   </si>
   <si>
     <t xml:space="preserve">5.62219142913818</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53827810287476</t>
+    <t xml:space="preserve">5.5382776260376</t>
   </si>
   <si>
     <t xml:space="preserve">5.43758249282837</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45436477661133</t>
+    <t xml:space="preserve">5.45436573028564</t>
   </si>
   <si>
     <t xml:space="preserve">5.60540866851807</t>
@@ -1214,7 +1214,7 @@
     <t xml:space="preserve">5.48792934417725</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35366821289062</t>
+    <t xml:space="preserve">5.35366868972778</t>
   </si>
   <si>
     <t xml:space="preserve">5.37045097351074</t>
@@ -1223,13 +1223,13 @@
     <t xml:space="preserve">5.42079973220825</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28653764724731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30332040786743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26975584030151</t>
+    <t xml:space="preserve">5.28653812408447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30332136154175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26975536346436</t>
   </si>
   <si>
     <t xml:space="preserve">5.38723421096802</t>
@@ -1238,7 +1238,7 @@
     <t xml:space="preserve">5.32010364532471</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65575647354126</t>
+    <t xml:space="preserve">5.65575695037842</t>
   </si>
   <si>
     <t xml:space="preserve">5.75645351409912</t>
@@ -1250,43 +1250,43 @@
     <t xml:space="preserve">5.72288703918457</t>
   </si>
   <si>
-    <t xml:space="preserve">5.739670753479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63897466659546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57184362411499</t>
+    <t xml:space="preserve">5.73967027664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6389741897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57184410095215</t>
   </si>
   <si>
     <t xml:space="preserve">5.18584203720093</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2026252746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21940755844116</t>
+    <t xml:space="preserve">5.20262479782104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21940803527832</t>
   </si>
   <si>
     <t xml:space="preserve">5.16905975341797</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13549327850342</t>
+    <t xml:space="preserve">5.13549375534058</t>
   </si>
   <si>
     <t xml:space="preserve">5.10192918777466</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9508843421936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03479909896851</t>
+    <t xml:space="preserve">4.95088481903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03479862213135</t>
   </si>
   <si>
     <t xml:space="preserve">5.15227699279785</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11871099472046</t>
+    <t xml:space="preserve">5.11871147155762</t>
   </si>
   <si>
     <t xml:space="preserve">5.06836366653442</t>
@@ -1301,28 +1301,28 @@
     <t xml:space="preserve">5.25297260284424</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33688592910767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79001760482788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77323532104492</t>
+    <t xml:space="preserve">5.33688640594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79001712799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77323484420776</t>
   </si>
   <si>
     <t xml:space="preserve">5.58862638473511</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81662321090698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79984092712402</t>
+    <t xml:space="preserve">4.81662368774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79984140396118</t>
   </si>
   <si>
     <t xml:space="preserve">4.59844827651978</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36349201202393</t>
+    <t xml:space="preserve">4.36349153518677</t>
   </si>
   <si>
     <t xml:space="preserve">4.31314373016357</t>
@@ -1331,28 +1331,28 @@
     <t xml:space="preserve">4.19566535949707</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11175107955933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02783918380737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17049074172974</t>
+    <t xml:space="preserve">4.11175203323364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02783870697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17049121856689</t>
   </si>
   <si>
     <t xml:space="preserve">4.06979560852051</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12014245986938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34670925140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17888212203979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04462099075317</t>
+    <t xml:space="preserve">4.12014293670654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34670877456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17888164520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04462146759033</t>
   </si>
   <si>
     <t xml:space="preserve">4.15370845794678</t>
@@ -1361,40 +1361,40 @@
     <t xml:space="preserve">4.26279640197754</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16209936141968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14531707763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99427270889282</t>
+    <t xml:space="preserve">4.16209983825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14531755447388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9942729473114</t>
   </si>
   <si>
     <t xml:space="preserve">4.09496927261353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98588180541992</t>
+    <t xml:space="preserve">3.98588132858276</t>
   </si>
   <si>
     <t xml:space="preserve">4.2795786857605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2292308807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21244812011719</t>
+    <t xml:space="preserve">4.22922992706299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21244764328003</t>
   </si>
   <si>
     <t xml:space="preserve">4.03622961044312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1287784576416</t>
+    <t xml:space="preserve">4.12877941131592</t>
   </si>
   <si>
     <t xml:space="preserve">4.16283130645752</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07770156860352</t>
+    <t xml:space="preserve">4.07770204544067</t>
   </si>
   <si>
     <t xml:space="preserve">4.00108432769775</t>
@@ -1403,13 +1403,13 @@
     <t xml:space="preserve">4.20539569854736</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37565469741821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21390867233276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22242116928101</t>
+    <t xml:space="preserve">4.37565422058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21390819549561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22242212295532</t>
   </si>
   <si>
     <t xml:space="preserve">4.25647354125977</t>
@@ -1418,16 +1418,16 @@
     <t xml:space="preserve">4.24796009063721</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32457685470581</t>
+    <t xml:space="preserve">4.32457637786865</t>
   </si>
   <si>
     <t xml:space="preserve">4.30755090713501</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23944807052612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35862827301025</t>
+    <t xml:space="preserve">4.23944759368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35862874984741</t>
   </si>
   <si>
     <t xml:space="preserve">4.51186180114746</t>
@@ -1439,16 +1439,16 @@
     <t xml:space="preserve">5.94203662872314</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8909592628479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73772573471069</t>
+    <t xml:space="preserve">5.89095878601074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73772621154785</t>
   </si>
   <si>
     <t xml:space="preserve">5.5504412651062</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58449268341064</t>
+    <t xml:space="preserve">5.5844931602478</t>
   </si>
   <si>
     <t xml:space="preserve">5.567467212677</t>
@@ -1457,28 +1457,28 @@
     <t xml:space="preserve">5.41423416137695</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26100063323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48233795166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44828605651855</t>
+    <t xml:space="preserve">5.2610011100769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48233842849731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44828653335571</t>
   </si>
   <si>
     <t xml:space="preserve">5.60151863098145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66962242126465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5163893699646</t>
+    <t xml:space="preserve">5.66962289810181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51638889312744</t>
   </si>
   <si>
     <t xml:space="preserve">5.70367431640625</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32910490036011</t>
+    <t xml:space="preserve">5.32910442352295</t>
   </si>
   <si>
     <t xml:space="preserve">5.27802705764771</t>
@@ -1487,40 +1487,40 @@
     <t xml:space="preserve">5.43126010894775</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31207847595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2269492149353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00561285018921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95453548431396</t>
+    <t xml:space="preserve">5.31207895278931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22694873809814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00561237335205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95453500747681</t>
   </si>
   <si>
     <t xml:space="preserve">4.93750905990601</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05669069290161</t>
+    <t xml:space="preserve">5.05669021606445</t>
   </si>
   <si>
     <t xml:space="preserve">5.03966426849365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97156143188477</t>
+    <t xml:space="preserve">4.97156095504761</t>
   </si>
   <si>
     <t xml:space="preserve">4.8864312171936</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02263832092285</t>
+    <t xml:space="preserve">5.02263879776001</t>
   </si>
   <si>
     <t xml:space="preserve">4.92048311233521</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9034571647644</t>
+    <t xml:space="preserve">4.90345764160156</t>
   </si>
   <si>
     <t xml:space="preserve">4.852379322052</t>
@@ -1541,16 +1541,16 @@
     <t xml:space="preserve">5.38018226623535</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20992279052734</t>
+    <t xml:space="preserve">5.2099232673645</t>
   </si>
   <si>
     <t xml:space="preserve">5.1588454246521</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10776853561401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98858690261841</t>
+    <t xml:space="preserve">5.10776805877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98858642578125</t>
   </si>
   <si>
     <t xml:space="preserve">5.09074211120605</t>
@@ -1559,13 +1559,13 @@
     <t xml:space="preserve">5.1928973197937</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1758713722229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14182043075562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0737156867981</t>
+    <t xml:space="preserve">5.17587089538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1418194770813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07371664047241</t>
   </si>
   <si>
     <t xml:space="preserve">4.68212080001831</t>
@@ -1574,28 +1574,28 @@
     <t xml:space="preserve">4.54591369628906</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59699106216431</t>
+    <t xml:space="preserve">4.59699153900146</t>
   </si>
   <si>
     <t xml:space="preserve">4.57996559143066</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63104343414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7842755317688</t>
+    <t xml:space="preserve">4.63104295730591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78427600860596</t>
   </si>
   <si>
     <t xml:space="preserve">4.76725006103516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81832790374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80130243301392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39720821380615</t>
+    <t xml:space="preserve">4.8183274269104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8013014793396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39720869064331</t>
   </si>
   <si>
     <t xml:space="preserve">5.6185450553894</t>
@@ -1604,88 +1604,88 @@
     <t xml:space="preserve">5.46531200408936</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4993634223938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63557052612305</t>
+    <t xml:space="preserve">5.49936389923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63557100296021</t>
   </si>
   <si>
     <t xml:space="preserve">5.68664836883545</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65259647369385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85690784454346</t>
+    <t xml:space="preserve">5.65259695053101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85690689086914</t>
   </si>
   <si>
     <t xml:space="preserve">5.8739333152771</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3166069984436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3336329460144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29958057403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35065793991089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43578720092773</t>
+    <t xml:space="preserve">6.31660604476929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33363246917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2995810508728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35065841674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43578767776489</t>
   </si>
   <si>
     <t xml:space="preserve">6.55496883392334</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69117593765259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79333162307739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15087413787842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08277177810669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8784613609314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77630519866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84440946578979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70820236206055</t>
+    <t xml:space="preserve">6.69117641448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79333114624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15087461471558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08277130126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87846088409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77630567550659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84440898895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70820283889771</t>
   </si>
   <si>
     <t xml:space="preserve">6.75927972793579</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53794288635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72522830963135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65712451934814</t>
+    <t xml:space="preserve">6.5379433631897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72522783279419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6571249961853</t>
   </si>
   <si>
     <t xml:space="preserve">6.91251230239868</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89548778533936</t>
+    <t xml:space="preserve">6.8954873085022</t>
   </si>
   <si>
     <t xml:space="preserve">6.96359062194824</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17302131652832</t>
+    <t xml:space="preserve">7.17302227020264</t>
   </si>
   <si>
     <t xml:space="preserve">7.05085372924805</t>
@@ -1694,25 +1694,25 @@
     <t xml:space="preserve">7.1206636428833</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57443141937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9758415222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02819919586182</t>
+    <t xml:space="preserve">7.57443237304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97584247589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02820014953613</t>
   </si>
   <si>
     <t xml:space="preserve">8.0631046295166</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99329423904419</t>
+    <t xml:space="preserve">7.99329519271851</t>
   </si>
   <si>
     <t xml:space="preserve">8.0107479095459</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94093751907349</t>
+    <t xml:space="preserve">7.94093656539917</t>
   </si>
   <si>
     <t xml:space="preserve">8.13291454315186</t>
@@ -1727,16 +1727,16 @@
     <t xml:space="preserve">8.18527412414551</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34234809875488</t>
+    <t xml:space="preserve">8.34234714508057</t>
   </si>
   <si>
     <t xml:space="preserve">8.11546230316162</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25508403778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08055686950684</t>
+    <t xml:space="preserve">8.25508308410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08055782318115</t>
   </si>
   <si>
     <t xml:space="preserve">8.20272445678711</t>
@@ -1748,7 +1748,7 @@
     <t xml:space="preserve">8.37725162506104</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32489395141602</t>
+    <t xml:space="preserve">8.3248929977417</t>
   </si>
   <si>
     <t xml:space="preserve">8.81356716156006</t>
@@ -1757,10 +1757,10 @@
     <t xml:space="preserve">8.58668327331543</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53432559967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69139957427979</t>
+    <t xml:space="preserve">8.53432464599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69139862060547</t>
   </si>
   <si>
     <t xml:space="preserve">8.60413551330566</t>
@@ -1769,13 +1769,13 @@
     <t xml:space="preserve">8.72630405426025</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42960929870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28998851776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30744075775146</t>
+    <t xml:space="preserve">8.42961025238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28998756408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30744171142578</t>
   </si>
   <si>
     <t xml:space="preserve">8.04565238952637</t>
@@ -1784,16 +1784,16 @@
     <t xml:space="preserve">7.85367345809937</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41215801239014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22017860412598</t>
+    <t xml:space="preserve">8.41215705871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22017765045166</t>
   </si>
   <si>
     <t xml:space="preserve">8.44706249237061</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3597993850708</t>
+    <t xml:space="preserve">8.35979843139648</t>
   </si>
   <si>
     <t xml:space="preserve">8.09801006317139</t>
@@ -1802,31 +1802,31 @@
     <t xml:space="preserve">8.23763084411621</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48196697235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62158870697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55177688598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65649223327637</t>
+    <t xml:space="preserve">8.48196792602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6215877532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55177783966064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65649318695068</t>
   </si>
   <si>
     <t xml:space="preserve">8.51687335968018</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46451377868652</t>
+    <t xml:space="preserve">8.46451473236084</t>
   </si>
   <si>
     <t xml:space="preserve">8.49942016601562</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56923007965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99161815643311</t>
+    <t xml:space="preserve">8.5692310333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99161720275879</t>
   </si>
   <si>
     <t xml:space="preserve">9.59893417358398</t>
@@ -1835,10 +1835,10 @@
     <t xml:space="preserve">9.77346038818359</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8170919418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29351329803467</t>
+    <t xml:space="preserve">9.81709289550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29351234436035</t>
   </si>
   <si>
     <t xml:space="preserve">9.46804046630859</t>
@@ -1850,16 +1850,16 @@
     <t xml:space="preserve">9.64256572723389</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9043550491333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33714389801025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94798564910889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86072254180908</t>
+    <t xml:space="preserve">9.90435600280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33714580535889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9479866027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8607234954834</t>
   </si>
   <si>
     <t xml:space="preserve">10.5151958465576</t>
@@ -1868,34 +1868,34 @@
     <t xml:space="preserve">10.4279327392578</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5588274002075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6024589538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8206167221069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7333536148071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.776985168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2970380783081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3843002319336</t>
+    <t xml:space="preserve">10.5588283538818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6024580001831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8206176757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7333545684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7769861221313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2970390319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3843011856079</t>
   </si>
   <si>
     <t xml:space="preserve">10.3406705856323</t>
   </si>
   <si>
-    <t xml:space="preserve">10.209774017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2534074783325</t>
+    <t xml:space="preserve">10.2097749710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2534065246582</t>
   </si>
   <si>
     <t xml:space="preserve">10.0788812637329</t>
@@ -1904,37 +1904,37 @@
     <t xml:space="preserve">9.51167011260986</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72982788085938</t>
+    <t xml:space="preserve">9.72982883453369</t>
   </si>
   <si>
     <t xml:space="preserve">9.68619728088379</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98809337615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42440795898438</t>
+    <t xml:space="preserve">8.98809432983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42440891265869</t>
   </si>
   <si>
     <t xml:space="preserve">11.6496162414551</t>
   </si>
   <si>
-    <t xml:space="preserve">11.562352180481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7805099487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9114046096802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9550361633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6932468414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3040885925293</t>
+    <t xml:space="preserve">11.5623531341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7805109024048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9114036560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9550352096558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.693247795105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3040895462036</t>
   </si>
   <si>
     <t xml:space="preserve">12.2604570388794</t>
@@ -1946,16 +1946,16 @@
     <t xml:space="preserve">12.3913516998291</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7368774414062</t>
+    <t xml:space="preserve">11.7368783950806</t>
   </si>
   <si>
     <t xml:space="preserve">11.8677730560303</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6059837341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.951512336731</t>
+    <t xml:space="preserve">11.6059846878052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9515113830566</t>
   </si>
   <si>
     <t xml:space="preserve">12.0422992706299</t>
@@ -1967,13 +1967,13 @@
     <t xml:space="preserve">11.3441944122314</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9951429367065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.471565246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9078788757324</t>
+    <t xml:space="preserve">10.9951419830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4715642929077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9078798294067</t>
   </si>
   <si>
     <t xml:space="preserve">11.4314584732056</t>
@@ -1985,31 +1985,31 @@
     <t xml:space="preserve">11.9899406433105</t>
   </si>
   <si>
-    <t xml:space="preserve">11.74560546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5361738204956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5187215805054</t>
+    <t xml:space="preserve">11.7456045150757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5361728668213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5187206268311</t>
   </si>
   <si>
     <t xml:space="preserve">11.6234369277954</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4489097595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6408882141113</t>
+    <t xml:space="preserve">11.4489107131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.64089012146</t>
   </si>
   <si>
     <t xml:space="preserve">11.7281522750854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9201316833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1173114776611</t>
+    <t xml:space="preserve">11.920129776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1173105239868</t>
   </si>
   <si>
     <t xml:space="preserve">11.0998582839966</t>
@@ -2021,7 +2021,7 @@
     <t xml:space="preserve">10.7508058547974</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3319435119629</t>
+    <t xml:space="preserve">10.3319444656372</t>
   </si>
   <si>
     <t xml:space="preserve">10.1050596237183</t>
@@ -2036,7 +2036,7 @@
     <t xml:space="preserve">9.71089172363281</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1408939361572</t>
+    <t xml:space="preserve">10.1408929824829</t>
   </si>
   <si>
     <t xml:space="preserve">10.2663106918335</t>
@@ -2051,7 +2051,7 @@
     <t xml:space="preserve">10.1588106155396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0692262649536</t>
+    <t xml:space="preserve">10.0692253112793</t>
   </si>
   <si>
     <t xml:space="preserve">10.0871438980103</t>
@@ -2060,7 +2060,7 @@
     <t xml:space="preserve">10.4633951187134</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7858963012695</t>
+    <t xml:space="preserve">10.7858972549438</t>
   </si>
   <si>
     <t xml:space="preserve">10.5708961486816</t>
@@ -2069,7 +2069,7 @@
     <t xml:space="preserve">10.7142305374146</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7500629425049</t>
+    <t xml:space="preserve">10.7500638961792</t>
   </si>
   <si>
     <t xml:space="preserve">11.1621494293213</t>
@@ -2078,10 +2078,10 @@
     <t xml:space="preserve">10.8754816055298</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6425638198853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.588812828064</t>
+    <t xml:space="preserve">10.6425628662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5888118743896</t>
   </si>
   <si>
     <t xml:space="preserve">10.5171461105347</t>
@@ -2090,10 +2090,10 @@
     <t xml:space="preserve">10.8575639724731</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9113149642944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6067304611206</t>
+    <t xml:space="preserve">10.9113159179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6067295074463</t>
   </si>
   <si>
     <t xml:space="preserve">10.6604795455933</t>
@@ -2120,13 +2120,13 @@
     <t xml:space="preserve">11.1800651550293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9829816818237</t>
+    <t xml:space="preserve">10.9829807281494</t>
   </si>
   <si>
     <t xml:space="preserve">11.4846515655518</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3771505355835</t>
+    <t xml:space="preserve">11.3771514892578</t>
   </si>
   <si>
     <t xml:space="preserve">11.7354869842529</t>
@@ -2135,7 +2135,7 @@
     <t xml:space="preserve">11.9146537780762</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9325714111328</t>
+    <t xml:space="preserve">11.9325704574585</t>
   </si>
   <si>
     <t xml:space="preserve">12.0221548080444</t>
@@ -2144,7 +2144,7 @@
     <t xml:space="preserve">11.8788204193115</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2371549606323</t>
+    <t xml:space="preserve">12.2371559143066</t>
   </si>
   <si>
     <t xml:space="preserve">12.3267402648926</t>
@@ -2171,10 +2171,10 @@
     <t xml:space="preserve">12.6134080886841</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8463268280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.810492515564</t>
+    <t xml:space="preserve">12.8463258743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8104934692383</t>
   </si>
   <si>
     <t xml:space="preserve">12.9179935455322</t>
@@ -2186,7 +2186,7 @@
     <t xml:space="preserve">13.4017457962036</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4375791549683</t>
+    <t xml:space="preserve">13.4375801086426</t>
   </si>
   <si>
     <t xml:space="preserve">13.6884145736694</t>
@@ -2195,7 +2195,7 @@
     <t xml:space="preserve">13.9034156799316</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6559209823608</t>
+    <t xml:space="preserve">14.6559200286865</t>
   </si>
   <si>
     <t xml:space="preserve">14.2438344955444</t>
@@ -2204,16 +2204,16 @@
     <t xml:space="preserve">14.6380043029785</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9246711730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5125865936279</t>
+    <t xml:space="preserve">14.92467212677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5125875473022</t>
   </si>
   <si>
     <t xml:space="preserve">14.5663366317749</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7992544174194</t>
+    <t xml:space="preserve">14.7992553710938</t>
   </si>
   <si>
     <t xml:space="preserve">14.5484189987183</t>
@@ -2228,22 +2228,22 @@
     <t xml:space="preserve">14.8888397216797</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8171720504761</t>
+    <t xml:space="preserve">14.8171730041504</t>
   </si>
   <si>
     <t xml:space="preserve">14.387167930603</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7634191513062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6200866699219</t>
+    <t xml:space="preserve">14.7634201049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6200857162476</t>
   </si>
   <si>
     <t xml:space="preserve">14.9067535400391</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1217555999756</t>
+    <t xml:space="preserve">15.1217546463013</t>
   </si>
   <si>
     <t xml:space="preserve">15.032172203064</t>
@@ -2255,7 +2255,7 @@
     <t xml:space="preserve">15.0500888824463</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0680065155029</t>
+    <t xml:space="preserve">15.0680055618286</t>
   </si>
   <si>
     <t xml:space="preserve">15.1038398742676</t>
@@ -2264,25 +2264,25 @@
     <t xml:space="preserve">14.5305023193359</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7096710205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2080011367798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6167469024658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5092468261719</t>
+    <t xml:space="preserve">14.7096700668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2080001831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6167478561401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5092458724976</t>
   </si>
   <si>
     <t xml:space="preserve">13.0434112548828</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1688280105591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9717426300049</t>
+    <t xml:space="preserve">13.1688270568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9717435836792</t>
   </si>
   <si>
     <t xml:space="preserve">12.4700736999512</t>
@@ -2318,7 +2318,7 @@
     <t xml:space="preserve">12.6313257217407</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0971603393555</t>
+    <t xml:space="preserve">13.0971612930298</t>
   </si>
   <si>
     <t xml:space="preserve">13.0792446136475</t>
@@ -2342,7 +2342,7 @@
     <t xml:space="preserve">13.1150779724121</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1509113311768</t>
+    <t xml:space="preserve">13.1509122848511</t>
   </si>
   <si>
     <t xml:space="preserve">13.5271635055542</t>
@@ -2351,7 +2351,7 @@
     <t xml:space="preserve">13.3479957580566</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2763290405273</t>
+    <t xml:space="preserve">13.276328086853</t>
   </si>
   <si>
     <t xml:space="preserve">12.7925758361816</t>
@@ -2360,7 +2360,7 @@
     <t xml:space="preserve">12.5954914093018</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5238237380981</t>
+    <t xml:space="preserve">12.5238246917725</t>
   </si>
   <si>
     <t xml:space="preserve">12.5059070587158</t>
@@ -2369,16 +2369,16 @@
     <t xml:space="preserve">12.4879903793335</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3088226318359</t>
+    <t xml:space="preserve">12.3088216781616</t>
   </si>
   <si>
     <t xml:space="preserve">12.5417404174805</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8284101486206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3804903030396</t>
+    <t xml:space="preserve">12.8284091949463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3804893493652</t>
   </si>
   <si>
     <t xml:space="preserve">12.6671581268311</t>
@@ -2393,7 +2393,7 @@
     <t xml:space="preserve">12.7746591567993</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4342412948608</t>
+    <t xml:space="preserve">12.4342403411865</t>
   </si>
   <si>
     <t xml:space="preserve">11.9504880905151</t>
@@ -2402,13 +2402,13 @@
     <t xml:space="preserve">12.2192392349243</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8250694274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1117382049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9684047698975</t>
+    <t xml:space="preserve">11.8250703811646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1117391586304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9684038162231</t>
   </si>
   <si>
     <t xml:space="preserve">12.0400705337524</t>
@@ -2423,16 +2423,16 @@
     <t xml:space="preserve">12.7388257980347</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7421655654907</t>
+    <t xml:space="preserve">13.7421646118164</t>
   </si>
   <si>
     <t xml:space="preserve">13.7063312530518</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0825843811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0109167098999</t>
+    <t xml:space="preserve">14.0825834274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0109176635742</t>
   </si>
   <si>
     <t xml:space="preserve">13.7242479324341</t>
@@ -2468,7 +2468,7 @@
     <t xml:space="preserve">13.5450801849365</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4734125137329</t>
+    <t xml:space="preserve">13.4734134674072</t>
   </si>
   <si>
     <t xml:space="preserve">13.1867456436157</t>
@@ -2477,13 +2477,13 @@
     <t xml:space="preserve">13.3838291168213</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5988302230835</t>
+    <t xml:space="preserve">13.5988311767578</t>
   </si>
   <si>
     <t xml:space="preserve">12.7029914855957</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8429870605469</t>
+    <t xml:space="preserve">11.8429861068726</t>
   </si>
   <si>
     <t xml:space="preserve">11.7892360687256</t>
@@ -2501,7 +2501,7 @@
     <t xml:space="preserve">11.2158994674683</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3592338562012</t>
+    <t xml:space="preserve">11.3592348098755</t>
   </si>
   <si>
     <t xml:space="preserve">11.4309015274048</t>
@@ -2513,13 +2513,13 @@
     <t xml:space="preserve">11.2875671386719</t>
   </si>
   <si>
-    <t xml:space="preserve">11.683783531189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5179262161255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2783517837524</t>
+    <t xml:space="preserve">11.6837844848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5179252624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2783527374268</t>
   </si>
   <si>
     <t xml:space="preserve">11.1493520736694</t>
@@ -2531,7 +2531,7 @@
     <t xml:space="preserve">11.0756378173828</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9970722198486</t>
+    <t xml:space="preserve">11.9970712661743</t>
   </si>
   <si>
     <t xml:space="preserve">12.052357673645</t>
@@ -2540,7 +2540,7 @@
     <t xml:space="preserve">12.2735013961792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2182149887085</t>
+    <t xml:space="preserve">12.2182159423828</t>
   </si>
   <si>
     <t xml:space="preserve">12.4025020599365</t>
@@ -2552,7 +2552,7 @@
     <t xml:space="preserve">12.0707864761353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1629285812378</t>
+    <t xml:space="preserve">12.1629295349121</t>
   </si>
   <si>
     <t xml:space="preserve">12.1260719299316</t>
@@ -2567,13 +2567,13 @@
     <t xml:space="preserve">11.7759265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8312129974365</t>
+    <t xml:space="preserve">11.8312139511108</t>
   </si>
   <si>
     <t xml:space="preserve">11.9786424636841</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7206411361694</t>
+    <t xml:space="preserve">11.7206420898438</t>
   </si>
   <si>
     <t xml:space="preserve">11.868070602417</t>
@@ -2588,7 +2588,7 @@
     <t xml:space="preserve">11.4442110061646</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3520669937134</t>
+    <t xml:space="preserve">11.3520679473877</t>
   </si>
   <si>
     <t xml:space="preserve">11.3704957962036</t>
@@ -2606,7 +2606,7 @@
     <t xml:space="preserve">11.7022123336792</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5732116699219</t>
+    <t xml:space="preserve">11.5732126235962</t>
   </si>
   <si>
     <t xml:space="preserve">11.481068611145</t>
@@ -2615,7 +2615,7 @@
     <t xml:space="preserve">11.296781539917</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3152093887329</t>
+    <t xml:space="preserve">11.3152103424072</t>
   </si>
   <si>
     <t xml:space="preserve">11.5547828674316</t>
@@ -2624,7 +2624,7 @@
     <t xml:space="preserve">11.4257822036743</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3336381912231</t>
+    <t xml:space="preserve">11.3336391448975</t>
   </si>
   <si>
     <t xml:space="preserve">11.3889245986938</t>
@@ -2633,7 +2633,7 @@
     <t xml:space="preserve">11.4626398086548</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7943553924561</t>
+    <t xml:space="preserve">11.7943563461304</t>
   </si>
   <si>
     <t xml:space="preserve">12.1076431274414</t>
@@ -2663,7 +2663,7 @@
     <t xml:space="preserve">13.0290775299072</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2502222061157</t>
+    <t xml:space="preserve">13.2502212524414</t>
   </si>
   <si>
     <t xml:space="preserve">13.4160804748535</t>
@@ -2678,7 +2678,7 @@
     <t xml:space="preserve">12.6420755386353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8816480636597</t>
+    <t xml:space="preserve">12.8816471099854</t>
   </si>
   <si>
     <t xml:space="preserve">12.9185056686401</t>
@@ -2687,7 +2687,7 @@
     <t xml:space="preserve">13.194935798645</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1580772399902</t>
+    <t xml:space="preserve">13.1580781936646</t>
   </si>
   <si>
     <t xml:space="preserve">12.8079328536987</t>
@@ -2702,7 +2702,7 @@
     <t xml:space="preserve">12.5499315261841</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0843629837036</t>
+    <t xml:space="preserve">13.0843639373779</t>
   </si>
   <si>
     <t xml:space="preserve">13.3423643112183</t>
@@ -2720,13 +2720,13 @@
     <t xml:space="preserve">13.1027917861938</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3607940673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2133646011353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5266513824463</t>
+    <t xml:space="preserve">13.3607931137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2133636474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5266523361206</t>
   </si>
   <si>
     <t xml:space="preserve">13.6003665924072</t>
@@ -2744,28 +2744,28 @@
     <t xml:space="preserve">13.7846536636353</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0610828399658</t>
+    <t xml:space="preserve">14.0610837936401</t>
   </si>
   <si>
     <t xml:space="preserve">14.2637987136841</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5402297973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6139440536499</t>
+    <t xml:space="preserve">14.540228843689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6139430999756</t>
   </si>
   <si>
     <t xml:space="preserve">15.3695201873779</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5353784561157</t>
+    <t xml:space="preserve">15.53537940979</t>
   </si>
   <si>
     <t xml:space="preserve">15.6275205612183</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5722360610962</t>
+    <t xml:space="preserve">15.5722341537476</t>
   </si>
   <si>
     <t xml:space="preserve">15.4063768386841</t>
@@ -2777,34 +2777,34 @@
     <t xml:space="preserve">15.295804977417</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2773761749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4616651535034</t>
+    <t xml:space="preserve">15.2773771286011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4616641998291</t>
   </si>
   <si>
     <t xml:space="preserve">15.6459493637085</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4432344436646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6643781661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7012376785278</t>
+    <t xml:space="preserve">15.4432353973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.664379119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7012367248535</t>
   </si>
   <si>
     <t xml:space="preserve">15.6090936660767</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3326606750488</t>
+    <t xml:space="preserve">15.3326616287231</t>
   </si>
   <si>
     <t xml:space="preserve">15.2036619186401</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1668033599854</t>
+    <t xml:space="preserve">15.1668043136597</t>
   </si>
   <si>
     <t xml:space="preserve">14.8535175323486</t>
@@ -2825,22 +2825,22 @@
     <t xml:space="preserve">15.8302373886108</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7196645736694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3879489898682</t>
+    <t xml:space="preserve">15.7196636199951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3879499435425</t>
   </si>
   <si>
     <t xml:space="preserve">15.5906648635864</t>
   </si>
   <si>
-    <t xml:space="preserve">15.682806968689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7565221786499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7380933761597</t>
+    <t xml:space="preserve">15.6828079223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7565231323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.738094329834</t>
   </si>
   <si>
     <t xml:space="preserve">15.1483764648438</t>
@@ -2852,7 +2852,7 @@
     <t xml:space="preserve">15.1299476623535</t>
   </si>
   <si>
-    <t xml:space="preserve">15.480092048645</t>
+    <t xml:space="preserve">15.4800910949707</t>
   </si>
   <si>
     <t xml:space="preserve">15.9223804473877</t>
@@ -2864,22 +2864,22 @@
     <t xml:space="preserve">16.0882377624512</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7749509811401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.867094039917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7109394073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6556529998779</t>
+    <t xml:space="preserve">15.7749519348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8670930862427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7109384536743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6556520462036</t>
   </si>
   <si>
     <t xml:space="preserve">13.6372241973877</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1347990036011</t>
+    <t xml:space="preserve">14.1347980499268</t>
   </si>
   <si>
     <t xml:space="preserve">14.4480857849121</t>
@@ -2891,7 +2891,7 @@
     <t xml:space="preserve">14.0242261886597</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0795125961304</t>
+    <t xml:space="preserve">14.0795116424561</t>
   </si>
   <si>
     <t xml:space="preserve">14.0057973861694</t>
@@ -2912,7 +2912,7 @@
     <t xml:space="preserve">13.4897947311401</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6187953948975</t>
+    <t xml:space="preserve">13.6187944412231</t>
   </si>
   <si>
     <t xml:space="preserve">12.8263626098633</t>
@@ -2924,7 +2924,7 @@
     <t xml:space="preserve">13.2686500549316</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9369335174561</t>
+    <t xml:space="preserve">12.9369344711304</t>
   </si>
   <si>
     <t xml:space="preserve">12.9000768661499</t>
@@ -2933,10 +2933,10 @@
     <t xml:space="preserve">12.9922199249268</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0475053787231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6973600387573</t>
+    <t xml:space="preserve">13.0475063323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6973609924316</t>
   </si>
   <si>
     <t xml:space="preserve">12.6052179336548</t>
@@ -2948,7 +2948,7 @@
     <t xml:space="preserve">12.4209308624268</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4762172698975</t>
+    <t xml:space="preserve">12.4762163162231</t>
   </si>
   <si>
     <t xml:space="preserve">12.6236457824707</t>
@@ -3444,6 +3444,9 @@
   </si>
   <si>
     <t xml:space="preserve">17.9400005340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9799995422363</t>
   </si>
 </sst>
 </file>
@@ -68548,7 +68551,7 @@
     </row>
     <row r="2492">
       <c r="A2492" s="1" t="n">
-        <v>45947.6494212963</v>
+        <v>45947.2916666667</v>
       </c>
       <c r="B2492" t="n">
         <v>17681</v>
@@ -68569,6 +68572,32 @@
         <v>1143</v>
       </c>
       <c r="H2492" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2493">
+      <c r="A2493" s="1" t="n">
+        <v>45950.6494328704</v>
+      </c>
+      <c r="B2493" t="n">
+        <v>45089</v>
+      </c>
+      <c r="C2493" t="n">
+        <v>18.1800003051758</v>
+      </c>
+      <c r="D2493" t="n">
+        <v>17.8600006103516</v>
+      </c>
+      <c r="E2493" t="n">
+        <v>18.1399993896484</v>
+      </c>
+      <c r="F2493" t="n">
+        <v>17.9799995422363</v>
+      </c>
+      <c r="G2493" t="s">
+        <v>1144</v>
+      </c>
+      <c r="H2493" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ORS.MI.xlsx
+++ b/data/ORS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1145" uniqueCount="1145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1146" uniqueCount="1146">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,37 +44,37 @@
     <t xml:space="preserve">ORS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98275804519653</t>
+    <t xml:space="preserve">7.98275899887085</t>
   </si>
   <si>
     <t xml:space="preserve">8.06380176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94223833084106</t>
+    <t xml:space="preserve">7.94223642349243</t>
   </si>
   <si>
     <t xml:space="preserve">7.82472467422485</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93818712234497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90171670913696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03948783874512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92603063583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86119508743286</t>
+    <t xml:space="preserve">7.93818616867065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90171527862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03948974609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92602920532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86119413375854</t>
   </si>
   <si>
     <t xml:space="preserve">7.82067346572876</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93413305282593</t>
+    <t xml:space="preserve">7.93413400650024</t>
   </si>
   <si>
     <t xml:space="preserve">8.02328109741211</t>
@@ -83,25 +83,25 @@
     <t xml:space="preserve">8.08811378479004</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1448450088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69910717010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80446290969849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97465372085571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01112365722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01517486572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79230833053589</t>
+    <t xml:space="preserve">8.14484596252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69910860061646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8044638633728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97465562820435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01112461090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01517677307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79230785369873</t>
   </si>
   <si>
     <t xml:space="preserve">7.82877683639526</t>
@@ -110,61 +110,61 @@
     <t xml:space="preserve">8.34745311737061</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84093332290649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90982103347778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85714101791382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78015184402466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84498643875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97870683670044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88550710678101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95034170150757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00301837921143</t>
+    <t xml:space="preserve">7.84093427658081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90982055664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85714149475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7801513671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84498453140259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97870779037476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88550567626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95034265518188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00302028656006</t>
   </si>
   <si>
     <t xml:space="preserve">8.01922798156738</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9179253578186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10027122497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10432243347168</t>
+    <t xml:space="preserve">7.91792297363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1002721786499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10432434082031</t>
   </si>
   <si>
     <t xml:space="preserve">8.18536758422852</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20157432556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11242771148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07595729827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03138542175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09621906280518</t>
+    <t xml:space="preserve">8.20157527923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11242866516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07595920562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03138446807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09622001647949</t>
   </si>
   <si>
     <t xml:space="preserve">8.1772632598877</t>
@@ -182,16 +182,16 @@
     <t xml:space="preserve">8.4203929901123</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67162609100342</t>
+    <t xml:space="preserve">8.67162704467773</t>
   </si>
   <si>
     <t xml:space="preserve">8.55816650390625</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42849826812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52428913116455</t>
+    <t xml:space="preserve">8.42849731445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52429008483887</t>
   </si>
   <si>
     <t xml:space="preserve">8.45921993255615</t>
@@ -209,25 +209,25 @@
     <t xml:space="preserve">8.61376190185547</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67070007324219</t>
+    <t xml:space="preserve">8.67069911956787</t>
   </si>
   <si>
     <t xml:space="preserve">8.87404632568359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7927074432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90657997131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86591053009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94724941253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93911838531494</t>
+    <t xml:space="preserve">8.79270648956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90658092498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86591243743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94725036621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93911743164062</t>
   </si>
   <si>
     <t xml:space="preserve">8.78457355499268</t>
@@ -236,40 +236,40 @@
     <t xml:space="preserve">8.74390411376953</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91471481323242</t>
+    <t xml:space="preserve">8.91471385955811</t>
   </si>
   <si>
     <t xml:space="preserve">8.92284965515137</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10992813110352</t>
+    <t xml:space="preserve">9.10992908477783</t>
   </si>
   <si>
     <t xml:space="preserve">9.077392578125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11806297302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1343297958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15059661865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15873050689697</t>
+    <t xml:space="preserve">9.11806201934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13432884216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15059757232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15873146057129</t>
   </si>
   <si>
     <t xml:space="preserve">8.73576927185059</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67883396148682</t>
+    <t xml:space="preserve">8.67883110046387</t>
   </si>
   <si>
     <t xml:space="preserve">8.85777759552002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72763729095459</t>
+    <t xml:space="preserve">8.72763633728027</t>
   </si>
   <si>
     <t xml:space="preserve">8.7032356262207</t>
@@ -278,13 +278,13 @@
     <t xml:space="preserve">8.66256523132324</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69509983062744</t>
+    <t xml:space="preserve">8.69510173797607</t>
   </si>
   <si>
     <t xml:space="preserve">8.6218957901001</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80084133148193</t>
+    <t xml:space="preserve">8.80084228515625</t>
   </si>
   <si>
     <t xml:space="preserve">8.77643966674805</t>
@@ -293,79 +293,79 @@
     <t xml:space="preserve">8.68696689605713</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54869270324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54055881500244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58122730255127</t>
+    <t xml:space="preserve">8.54869079589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54055690765381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5812292098999</t>
   </si>
   <si>
     <t xml:space="preserve">8.46735286712646</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51615619659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49988746643066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45108318328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63003063201904</t>
+    <t xml:space="preserve">8.51615524291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49988842010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45108413696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63003158569336</t>
   </si>
   <si>
     <t xml:space="preserve">8.80897617340088</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89031410217285</t>
+    <t xml:space="preserve">8.89031314849854</t>
   </si>
   <si>
     <t xml:space="preserve">8.930983543396</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96351718902588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05299186706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30514049530029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10179328918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19126605987549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35394382476807</t>
+    <t xml:space="preserve">8.96351909637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0529899597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30514144897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10179424285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1912670135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35394287109375</t>
   </si>
   <si>
     <t xml:space="preserve">9.4759521484375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54915523529053</t>
+    <t xml:space="preserve">9.54915618896484</t>
   </si>
   <si>
     <t xml:space="preserve">9.58982563018799</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66303157806396</t>
+    <t xml:space="preserve">9.66303062438965</t>
   </si>
   <si>
     <t xml:space="preserve">9.71996688842773</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85824489593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0046529769897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.240535736084</t>
+    <t xml:space="preserve">9.85824394226074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0046520233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2405347824097</t>
   </si>
   <si>
     <t xml:space="preserve">10.2486686706543</t>
@@ -386,34 +386,34 @@
     <t xml:space="preserve">10.5252199172974</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4601488113403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5658903121948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5821561813354</t>
+    <t xml:space="preserve">10.4601497650146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5658893585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5821580886841</t>
   </si>
   <si>
     <t xml:space="preserve">10.7773704528809</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9807157516479</t>
+    <t xml:space="preserve">10.9807176589966</t>
   </si>
   <si>
     <t xml:space="preserve">10.8749761581421</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6553621292114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6797637939453</t>
+    <t xml:space="preserve">10.6553640365601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6797647476196</t>
   </si>
   <si>
     <t xml:space="preserve">10.5740242004395</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5170860290527</t>
+    <t xml:space="preserve">10.5170869827271</t>
   </si>
   <si>
     <t xml:space="preserve">10.5414876937866</t>
@@ -425,7 +425,7 @@
     <t xml:space="preserve">10.5089540481567</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8180379867554</t>
+    <t xml:space="preserve">10.818039894104</t>
   </si>
   <si>
     <t xml:space="preserve">10.6878967285156</t>
@@ -434,7 +434,7 @@
     <t xml:space="preserve">10.7611026763916</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6472282409668</t>
+    <t xml:space="preserve">10.6472272872925</t>
   </si>
   <si>
     <t xml:space="preserve">10.8993787765503</t>
@@ -443,10 +443,10 @@
     <t xml:space="preserve">10.8831100463867</t>
   </si>
   <si>
-    <t xml:space="preserve">10.671630859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7367000579834</t>
+    <t xml:space="preserve">10.6716299057007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.736701965332</t>
   </si>
   <si>
     <t xml:space="preserve">11.0051193237305</t>
@@ -458,7 +458,7 @@
     <t xml:space="preserve">11.184063911438</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4036769866943</t>
+    <t xml:space="preserve">11.4036779403687</t>
   </si>
   <si>
     <t xml:space="preserve">11.3955430984497</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">11.3386058807373</t>
   </si>
   <si>
-    <t xml:space="preserve">11.322338104248</t>
+    <t xml:space="preserve">11.3223390579224</t>
   </si>
   <si>
     <t xml:space="preserve">11.3304738998413</t>
@@ -476,43 +476,43 @@
     <t xml:space="preserve">11.3630084991455</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0783224105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.606559753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8424425125122</t>
+    <t xml:space="preserve">11.0783243179321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6065587997437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8424415588379</t>
   </si>
   <si>
     <t xml:space="preserve">10.8505744934082</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6390943527222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4113464355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2080011367798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2730703353882</t>
+    <t xml:space="preserve">10.6390933990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4113473892212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2080001831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2730712890625</t>
   </si>
   <si>
     <t xml:space="preserve">10.232400894165</t>
   </si>
   <si>
-    <t xml:space="preserve">10.321873664856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3706789016724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3300075531006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3056058883667</t>
+    <t xml:space="preserve">10.3218727111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.370677947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3300085067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3056039810181</t>
   </si>
   <si>
     <t xml:space="preserve">10.2568035125732</t>
@@ -521,112 +521,112 @@
     <t xml:space="preserve">10.1835975646973</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4845514297485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3625421524048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4438819885254</t>
+    <t xml:space="preserve">10.4845523834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3625431060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4438810348511</t>
   </si>
   <si>
     <t xml:space="preserve">10.8587083816528</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9237794876099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.037654876709</t>
+    <t xml:space="preserve">10.9237804412842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0376539230347</t>
   </si>
   <si>
     <t xml:space="preserve">11.0620565414429</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1027250289917</t>
+    <t xml:space="preserve">11.1027240753174</t>
   </si>
   <si>
     <t xml:space="preserve">11.1433944702148</t>
   </si>
   <si>
-    <t xml:space="preserve">11.175929069519</t>
+    <t xml:space="preserve">11.1759300231934</t>
   </si>
   <si>
     <t xml:space="preserve">11.1352615356445</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0701904296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.118992805481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1515283584595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2247323989868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0457878112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5008201599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1347942352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36161231994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01999092102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10946178436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3941478729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21520328521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33721160888672</t>
+    <t xml:space="preserve">11.0701894760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1189937591553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1515274047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2247333526611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0457859039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5008192062378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1347961425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36161327362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01998996734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10946273803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39414691925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21520233154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3372106552124</t>
   </si>
   <si>
     <t xml:space="preserve">8.31280899047852</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18266773223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34534549713135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23960304260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49175453186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58936214447021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76017189025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29654216766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25587368011475</t>
+    <t xml:space="preserve">8.18266677856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34534454345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23960399627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49175357818604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58935928344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76017093658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29654121398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25587272644043</t>
   </si>
   <si>
     <t xml:space="preserve">8.17453384399414</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1908016204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23147010803223</t>
+    <t xml:space="preserve">8.19080066680908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23147201538086</t>
   </si>
   <si>
     <t xml:space="preserve">8.2802734375</t>
@@ -635,7 +635,7 @@
     <t xml:space="preserve">8.14199829101562</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15826511383057</t>
+    <t xml:space="preserve">8.1582670211792</t>
   </si>
   <si>
     <t xml:space="preserve">8.16639995574951</t>
@@ -644,34 +644,34 @@
     <t xml:space="preserve">8.12166404724121</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05252647399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89798212051392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85731315612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93051767349243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90611553192139</t>
+    <t xml:space="preserve">8.05252456665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89798259735107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85731267929077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93051815032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9061164855957</t>
   </si>
   <si>
     <t xml:space="preserve">7.93865156173706</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84917879104614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80850982666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62956476211548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57262849807739</t>
+    <t xml:space="preserve">7.84918022155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80850839614868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62956523895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57262659072876</t>
   </si>
   <si>
     <t xml:space="preserve">7.48315572738647</t>
@@ -680,91 +680,91 @@
     <t xml:space="preserve">7.66616630554199</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60516309738159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54009246826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52382469177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47908735275269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61329793930054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54822492599487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56449413299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5075569152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46688652038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49128913879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49942302703857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31234407424927</t>
+    <t xml:space="preserve">7.60516405105591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54009294509888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5238242149353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.479088306427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6132960319519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54822635650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56449365615845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50755596160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4668869972229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4912896156311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49942255020142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31234550476074</t>
   </si>
   <si>
     <t xml:space="preserve">7.27980804443359</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37741374969482</t>
+    <t xml:space="preserve">7.37741565704346</t>
   </si>
   <si>
     <t xml:space="preserve">7.38554906845093</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36928129196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3204779624939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34487915039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28794240951538</t>
+    <t xml:space="preserve">7.36928033828735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32047748565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34487867355347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28794145584106</t>
   </si>
   <si>
     <t xml:space="preserve">7.04392623901367</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15780067443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3936824798584</t>
+    <t xml:space="preserve">7.15780019760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39368295669556</t>
   </si>
   <si>
     <t xml:space="preserve">7.42621755599976</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40181684494019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3042106628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3611478805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20660400390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3530125617981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.336745262146</t>
+    <t xml:space="preserve">7.40181636810303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30421018600464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36114740371704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20660352706909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35301351547241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33674621582031</t>
   </si>
   <si>
     <t xml:space="preserve">7.27167463302612</t>
@@ -776,49 +776,49 @@
     <t xml:space="preserve">7.32861137390137</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26354122161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23914051055908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22287130355835</t>
+    <t xml:space="preserve">7.26354169845581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23914003372192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22287082672119</t>
   </si>
   <si>
     <t xml:space="preserve">7.24727296829224</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44248628616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25540685653687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18220138549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29607534408569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16593408584595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14153337478638</t>
+    <t xml:space="preserve">7.44248580932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25540781021118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18220233917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29607582092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16593456268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14153289794922</t>
   </si>
   <si>
     <t xml:space="preserve">7.05205965042114</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0764627456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0357928276062</t>
+    <t xml:space="preserve">7.07646226882935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03579330444336</t>
   </si>
   <si>
     <t xml:space="preserve">7.01952505111694</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87311506271362</t>
+    <t xml:space="preserve">6.87311458587646</t>
   </si>
   <si>
     <t xml:space="preserve">6.67790269851685</t>
@@ -827,13 +827,13 @@
     <t xml:space="preserve">6.85124778747559</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93379211425781</t>
+    <t xml:space="preserve">6.93379163742065</t>
   </si>
   <si>
     <t xml:space="preserve">7.26397323608398</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14840984344482</t>
+    <t xml:space="preserve">7.14841032028198</t>
   </si>
   <si>
     <t xml:space="preserve">7.09888315200806</t>
@@ -845,10 +845,10 @@
     <t xml:space="preserve">7.16491842269897</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14015579223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21444654464722</t>
+    <t xml:space="preserve">7.14015674591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2144455909729</t>
   </si>
   <si>
     <t xml:space="preserve">7.1731743812561</t>
@@ -857,109 +857,109 @@
     <t xml:space="preserve">6.97506475448608</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84299278259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60361242294312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62012147903442</t>
+    <t xml:space="preserve">6.84299325942993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60361194610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62012100219727</t>
   </si>
   <si>
     <t xml:space="preserve">6.80997467041016</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54583072662354</t>
+    <t xml:space="preserve">6.54583024978638</t>
   </si>
   <si>
     <t xml:space="preserve">6.31470394134521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32295846939087</t>
+    <t xml:space="preserve">6.32295799255371</t>
   </si>
   <si>
     <t xml:space="preserve">6.34772300720215</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38074016571045</t>
+    <t xml:space="preserve">6.38073968887329</t>
   </si>
   <si>
     <t xml:space="preserve">6.39724922180176</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4715404510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28168630599976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22390413284302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09183168411255</t>
+    <t xml:space="preserve">6.47153997421265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28168535232544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22390460968018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09183216094971</t>
   </si>
   <si>
     <t xml:space="preserve">5.90197801589966</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95975971221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99277782440186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20739555358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14135980606079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19088649749756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14961385726929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0753231048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25692224502563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00928735733032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9845232963562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12485027313232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13310480117798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27343082427979</t>
+    <t xml:space="preserve">5.95976066589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9927773475647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20739507675171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14135932922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19088745117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14961338043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07532358169556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25692272186279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00928783416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98452281951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12485074996948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13310432434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27343130111694</t>
   </si>
   <si>
     <t xml:space="preserve">6.44677639007568</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55408525466919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51281213760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36423110961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24041366577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21564960479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23215961456299</t>
+    <t xml:space="preserve">6.55408477783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51281261444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3642315864563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24041414260864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21565008163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23216009140015</t>
   </si>
   <si>
     <t xml:space="preserve">6.24866819381714</t>
@@ -977,58 +977,58 @@
     <t xml:space="preserve">5.89372444152832</t>
   </si>
   <si>
-    <t xml:space="preserve">5.778160572052</t>
+    <t xml:space="preserve">5.77816152572632</t>
   </si>
   <si>
     <t xml:space="preserve">5.6956148147583</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79466915130615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80292367935181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82768774032593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78641510009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73688745498657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85245132446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29819583892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1826319694519</t>
+    <t xml:space="preserve">5.79467010498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80292415618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82768726348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78641557693481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73688793182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85245084762573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29819536209106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18263244628906</t>
   </si>
   <si>
     <t xml:space="preserve">6.15786790847778</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03405046463013</t>
+    <t xml:space="preserve">6.03404998779297</t>
   </si>
   <si>
     <t xml:space="preserve">6.08357763290405</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81943368911743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91848659515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86070585250854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76165246963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75339651107788</t>
+    <t xml:space="preserve">5.81943321228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91848707199097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86070537567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76165151596069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75339698791504</t>
   </si>
   <si>
     <t xml:space="preserve">5.81117820739746</t>
@@ -1037,22 +1037,22 @@
     <t xml:space="preserve">5.70387029647827</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74514245986938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83594179153442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71212482452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84419679641724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94325065612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96801424026489</t>
+    <t xml:space="preserve">5.74514293670654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83594226837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71212434768677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84419727325439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94325113296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96801471710205</t>
   </si>
   <si>
     <t xml:space="preserve">5.87721490859985</t>
@@ -1061,43 +1061,43 @@
     <t xml:space="preserve">5.88546943664551</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93499660491943</t>
+    <t xml:space="preserve">5.93499565124512</t>
   </si>
   <si>
     <t xml:space="preserve">6.02579593658447</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06706857681274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3889946937561</t>
+    <t xml:space="preserve">6.0670690536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38899517059326</t>
   </si>
   <si>
     <t xml:space="preserve">6.19914102554321</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04230451583862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05881500244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9515061378479</t>
+    <t xml:space="preserve">6.04230499267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05881452560425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95150566101074</t>
   </si>
   <si>
     <t xml:space="preserve">6.17437744140625</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17601871490479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29349803924561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25993204116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20958423614502</t>
+    <t xml:space="preserve">6.1760196685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29349851608276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25993251800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20958375930786</t>
   </si>
   <si>
     <t xml:space="preserve">6.09210586547852</t>
@@ -1106,82 +1106,82 @@
     <t xml:space="preserve">6.10888910293579</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14245367050171</t>
+    <t xml:space="preserve">6.14245414733887</t>
   </si>
   <si>
     <t xml:space="preserve">6.05854082107544</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02497482299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97462749481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95784473419189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15923738479614</t>
+    <t xml:space="preserve">6.02497529983521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97462797164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95784425735474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15923643112183</t>
   </si>
   <si>
     <t xml:space="preserve">6.12567138671875</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1928014755249</t>
+    <t xml:space="preserve">6.19280195236206</t>
   </si>
   <si>
     <t xml:space="preserve">6.42775917053223</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7130651473999</t>
+    <t xml:space="preserve">6.71306467056274</t>
   </si>
   <si>
     <t xml:space="preserve">6.64593458175659</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69628238677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78019523620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72984743118286</t>
+    <t xml:space="preserve">6.69628190994263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78019571304321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7298469543457</t>
   </si>
   <si>
     <t xml:space="preserve">6.62915086746216</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56201982498169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54523754119873</t>
+    <t xml:space="preserve">6.56202030181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54523801803589</t>
   </si>
   <si>
     <t xml:space="preserve">6.67949914932251</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66271686553955</t>
+    <t xml:space="preserve">6.66271638870239</t>
   </si>
   <si>
     <t xml:space="preserve">6.57880353927612</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37741088867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34384632110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22636747360229</t>
+    <t xml:space="preserve">6.37741136550903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34384679794312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22636795043945</t>
   </si>
   <si>
     <t xml:space="preserve">6.36062860488892</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67253828048706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55506086349487</t>
+    <t xml:space="preserve">5.67253875732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55506038665771</t>
   </si>
   <si>
     <t xml:space="preserve">5.68932247161865</t>
@@ -1193,7 +1193,7 @@
     <t xml:space="preserve">5.53827810287476</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43758249282837</t>
+    <t xml:space="preserve">5.43758201599121</t>
   </si>
   <si>
     <t xml:space="preserve">5.45436525344849</t>
@@ -1202,28 +1202,28 @@
     <t xml:space="preserve">5.60540819168091</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5214958190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50471353530884</t>
+    <t xml:space="preserve">5.52149534225464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50471305847168</t>
   </si>
   <si>
     <t xml:space="preserve">5.4879298210144</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35366916656494</t>
+    <t xml:space="preserve">5.35366821289062</t>
   </si>
   <si>
     <t xml:space="preserve">5.3704514503479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42079925537109</t>
+    <t xml:space="preserve">5.42079973220825</t>
   </si>
   <si>
     <t xml:space="preserve">5.28653812408447</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30332088470459</t>
+    <t xml:space="preserve">5.30332040786743</t>
   </si>
   <si>
     <t xml:space="preserve">5.26975584030151</t>
@@ -1241,7 +1241,7 @@
     <t xml:space="preserve">5.75645303726196</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70610523223877</t>
+    <t xml:space="preserve">5.70610475540161</t>
   </si>
   <si>
     <t xml:space="preserve">5.72288703918457</t>
@@ -1259,19 +1259,19 @@
     <t xml:space="preserve">5.18584156036377</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2026252746582</t>
+    <t xml:space="preserve">5.20262479782104</t>
   </si>
   <si>
     <t xml:space="preserve">5.21940803527832</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16905927658081</t>
+    <t xml:space="preserve">5.16905975341797</t>
   </si>
   <si>
     <t xml:space="preserve">5.13549327850342</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1019287109375</t>
+    <t xml:space="preserve">5.10192918777466</t>
   </si>
   <si>
     <t xml:space="preserve">4.9508843421936</t>
@@ -1283,28 +1283,28 @@
     <t xml:space="preserve">5.15227699279785</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11871147155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06836318969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08514642715454</t>
+    <t xml:space="preserve">5.11871194839478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06836366653442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08514595031738</t>
   </si>
   <si>
     <t xml:space="preserve">5.23619031906128</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25297212600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33688592910767</t>
+    <t xml:space="preserve">5.25297260284424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33688688278198</t>
   </si>
   <si>
     <t xml:space="preserve">5.79001760482788</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77323532104492</t>
+    <t xml:space="preserve">5.77323579788208</t>
   </si>
   <si>
     <t xml:space="preserve">5.58862638473511</t>
@@ -1316,10 +1316,10 @@
     <t xml:space="preserve">4.79984140396118</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59844827651978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36349248886108</t>
+    <t xml:space="preserve">4.59844779968262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36349201202393</t>
   </si>
   <si>
     <t xml:space="preserve">4.31314420700073</t>
@@ -1328,13 +1328,13 @@
     <t xml:space="preserve">4.19566535949707</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11175155639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02783870697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17049074172974</t>
+    <t xml:space="preserve">4.11175107955933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02783823013306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17049121856689</t>
   </si>
   <si>
     <t xml:space="preserve">4.06979560852051</t>
@@ -1343,16 +1343,16 @@
     <t xml:space="preserve">4.12014293670654</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34670925140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17888212203979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04462099075317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15370845794678</t>
+    <t xml:space="preserve">4.34670877456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17888164520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04462146759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15370798110962</t>
   </si>
   <si>
     <t xml:space="preserve">4.26279640197754</t>
@@ -1364,19 +1364,19 @@
     <t xml:space="preserve">4.14531755447388</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99427270889282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09496879577637</t>
+    <t xml:space="preserve">3.9942729473114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09496974945068</t>
   </si>
   <si>
     <t xml:space="preserve">3.98588132858276</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2795786857605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22923040390015</t>
+    <t xml:space="preserve">4.27957820892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22922992706299</t>
   </si>
   <si>
     <t xml:space="preserve">4.21244812011719</t>
@@ -1385,19 +1385,19 @@
     <t xml:space="preserve">4.03622961044312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12877941131592</t>
+    <t xml:space="preserve">4.12877893447876</t>
   </si>
   <si>
     <t xml:space="preserve">4.16283082962036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07770156860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00108432769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20539617538452</t>
+    <t xml:space="preserve">4.07770109176636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00108480453491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20539569854736</t>
   </si>
   <si>
     <t xml:space="preserve">4.37565422058105</t>
@@ -1406,22 +1406,22 @@
     <t xml:space="preserve">4.21390819549561</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22242116928101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25647401809692</t>
+    <t xml:space="preserve">4.22242212295532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25647354125977</t>
   </si>
   <si>
     <t xml:space="preserve">4.24796009063721</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32457685470581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30755090713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23944759368896</t>
+    <t xml:space="preserve">4.32457637786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30755138397217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23944711685181</t>
   </si>
   <si>
     <t xml:space="preserve">4.35862827301025</t>
@@ -1436,10 +1436,10 @@
     <t xml:space="preserve">5.94203662872314</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8909592628479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73772621154785</t>
+    <t xml:space="preserve">5.89095878601074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73772573471069</t>
   </si>
   <si>
     <t xml:space="preserve">5.5504412651062</t>
@@ -1448,10 +1448,10 @@
     <t xml:space="preserve">5.58449268341064</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56746768951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41423368453979</t>
+    <t xml:space="preserve">5.56746673583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41423416137695</t>
   </si>
   <si>
     <t xml:space="preserve">5.2610011100769</t>
@@ -1460,22 +1460,22 @@
     <t xml:space="preserve">5.48233795166016</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4482855796814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60151863098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66962242126465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51639032363892</t>
+    <t xml:space="preserve">5.44828605651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6015191078186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66962289810181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5163893699646</t>
   </si>
   <si>
     <t xml:space="preserve">5.70367431640625</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32910490036011</t>
+    <t xml:space="preserve">5.32910442352295</t>
   </si>
   <si>
     <t xml:space="preserve">5.27802705764771</t>
@@ -1487,28 +1487,28 @@
     <t xml:space="preserve">5.31207847595215</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2269492149353</t>
+    <t xml:space="preserve">5.22694969177246</t>
   </si>
   <si>
     <t xml:space="preserve">5.00561285018921</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95453500747681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93750953674316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05669021606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03966426849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97156143188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88643169403076</t>
+    <t xml:space="preserve">4.95453548431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93750905990601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05669069290161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03966522216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97156047821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88643074035645</t>
   </si>
   <si>
     <t xml:space="preserve">5.02263879776001</t>
@@ -1517,34 +1517,34 @@
     <t xml:space="preserve">4.92048311233521</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9034571647644</t>
+    <t xml:space="preserve">4.90345764160156</t>
   </si>
   <si>
     <t xml:space="preserve">4.852379322052</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8694052696228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34613084793091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2439751625061</t>
+    <t xml:space="preserve">4.86940574645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34613037109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24397468566895</t>
   </si>
   <si>
     <t xml:space="preserve">5.36315631866455</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38018274307251</t>
+    <t xml:space="preserve">5.38018226623535</t>
   </si>
   <si>
     <t xml:space="preserve">5.2099232673645</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15884590148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10776853561401</t>
+    <t xml:space="preserve">5.1588454246521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1077675819397</t>
   </si>
   <si>
     <t xml:space="preserve">4.98858690261841</t>
@@ -1553,34 +1553,34 @@
     <t xml:space="preserve">5.09074211120605</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19289684295654</t>
+    <t xml:space="preserve">5.1928973197937</t>
   </si>
   <si>
     <t xml:space="preserve">5.1758713722229</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1418194770813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07371664047241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68212032318115</t>
+    <t xml:space="preserve">5.14181995391846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07371616363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68212080001831</t>
   </si>
   <si>
     <t xml:space="preserve">4.54591369628906</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59699106216431</t>
+    <t xml:space="preserve">4.59699153900146</t>
   </si>
   <si>
     <t xml:space="preserve">4.57996511459351</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63104248046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7842755317688</t>
+    <t xml:space="preserve">4.63104295730591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78427600860596</t>
   </si>
   <si>
     <t xml:space="preserve">4.76725006103516</t>
@@ -1589,22 +1589,22 @@
     <t xml:space="preserve">4.8183274269104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80130195617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39720821380615</t>
+    <t xml:space="preserve">4.8013014793396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39720869064331</t>
   </si>
   <si>
     <t xml:space="preserve">5.61854457855225</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4653115272522</t>
+    <t xml:space="preserve">5.46531200408936</t>
   </si>
   <si>
     <t xml:space="preserve">5.49936389923096</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63557004928589</t>
+    <t xml:space="preserve">5.63557052612305</t>
   </si>
   <si>
     <t xml:space="preserve">5.68664836883545</t>
@@ -1616,49 +1616,49 @@
     <t xml:space="preserve">5.8569073677063</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87393283843994</t>
+    <t xml:space="preserve">5.87393379211426</t>
   </si>
   <si>
     <t xml:space="preserve">6.31660652160645</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3336329460144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2995810508728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35065841674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43578720092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55496883392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69117593765259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79333162307739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15087556838989</t>
+    <t xml:space="preserve">6.33363199234009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29958057403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35065793991089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43578767776489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55496835708618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69117641448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79333114624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15087509155273</t>
   </si>
   <si>
     <t xml:space="preserve">7.08277082443237</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87846040725708</t>
+    <t xml:space="preserve">6.87846088409424</t>
   </si>
   <si>
     <t xml:space="preserve">6.77630567550659</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84440898895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70820188522339</t>
+    <t xml:space="preserve">6.84440946578979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70820236206055</t>
   </si>
   <si>
     <t xml:space="preserve">6.75928020477295</t>
@@ -1670,31 +1670,31 @@
     <t xml:space="preserve">6.72522783279419</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65712404251099</t>
+    <t xml:space="preserve">6.65712451934814</t>
   </si>
   <si>
     <t xml:space="preserve">6.91251230239868</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89548683166504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96359062194824</t>
+    <t xml:space="preserve">6.8954873085022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9635910987854</t>
   </si>
   <si>
     <t xml:space="preserve">7.17302179336548</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05085277557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12066411972046</t>
+    <t xml:space="preserve">7.05085372924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1206636428833</t>
   </si>
   <si>
     <t xml:space="preserve">7.57443237304688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97584199905396</t>
+    <t xml:space="preserve">7.9758415222168</t>
   </si>
   <si>
     <t xml:space="preserve">8.02819919586182</t>
@@ -1706,34 +1706,34 @@
     <t xml:space="preserve">7.99329423904419</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01074695587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94093799591064</t>
+    <t xml:space="preserve">8.0107479095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94093751907349</t>
   </si>
   <si>
     <t xml:space="preserve">8.13291454315186</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15036678314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16782093048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18527317047119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34234714508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11546325683594</t>
+    <t xml:space="preserve">8.15036869049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16781997680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18527412414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34234809875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11546230316162</t>
   </si>
   <si>
     <t xml:space="preserve">8.25508403778076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08055686950684</t>
+    <t xml:space="preserve">8.08055782318115</t>
   </si>
   <si>
     <t xml:space="preserve">8.20272445678711</t>
@@ -1751,25 +1751,25 @@
     <t xml:space="preserve">8.81356716156006</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58668231964111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53432464599609</t>
+    <t xml:space="preserve">8.58668327331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53432559967041</t>
   </si>
   <si>
     <t xml:space="preserve">8.69139862060547</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60413455963135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72630500793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42960929870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28998947143555</t>
+    <t xml:space="preserve">8.60413551330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72630405426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42961025238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28998756408691</t>
   </si>
   <si>
     <t xml:space="preserve">8.30744171142578</t>
@@ -1778,7 +1778,7 @@
     <t xml:space="preserve">8.04565238952637</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85367345809937</t>
+    <t xml:space="preserve">7.85367441177368</t>
   </si>
   <si>
     <t xml:space="preserve">8.41215801239014</t>
@@ -1790,28 +1790,28 @@
     <t xml:space="preserve">8.44706249237061</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3597993850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09800910949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23762989044189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48196792602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6215877532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55177783966064</t>
+    <t xml:space="preserve">8.35979843139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09801006317139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23763084411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48196697235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62158870697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55177688598633</t>
   </si>
   <si>
     <t xml:space="preserve">8.65649318695068</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51687240600586</t>
+    <t xml:space="preserve">8.51687335968018</t>
   </si>
   <si>
     <t xml:space="preserve">8.46451377868652</t>
@@ -1832,13 +1832,13 @@
     <t xml:space="preserve">9.77345943450928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81709098815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29351425170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46803951263428</t>
+    <t xml:space="preserve">9.8170919418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29351329803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46804046630859</t>
   </si>
   <si>
     <t xml:space="preserve">9.55530261993408</t>
@@ -1850,25 +1850,25 @@
     <t xml:space="preserve">9.9043550491333</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33714580535889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9479866027832</t>
+    <t xml:space="preserve">9.33714485168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94798564910889</t>
   </si>
   <si>
     <t xml:space="preserve">9.86072254180908</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5151968002319</t>
+    <t xml:space="preserve">10.5151958465576</t>
   </si>
   <si>
     <t xml:space="preserve">10.4279327392578</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5588274002075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6024589538574</t>
+    <t xml:space="preserve">10.5588283538818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6024580001831</t>
   </si>
   <si>
     <t xml:space="preserve">10.8206167221069</t>
@@ -1880,13 +1880,13 @@
     <t xml:space="preserve">10.776985168457</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2970390319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3843011856079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.340669631958</t>
+    <t xml:space="preserve">10.2970380783081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3843002319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3406705856323</t>
   </si>
   <si>
     <t xml:space="preserve">10.2097749710083</t>
@@ -1898,40 +1898,40 @@
     <t xml:space="preserve">10.0788822174072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51167106628418</t>
+    <t xml:space="preserve">9.51167011260986</t>
   </si>
   <si>
     <t xml:space="preserve">9.72982883453369</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68619823455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98809242248535</t>
+    <t xml:space="preserve">9.68619728088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98809337615967</t>
   </si>
   <si>
     <t xml:space="preserve">9.42440795898438</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6496162414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.562352180481</t>
+    <t xml:space="preserve">11.6496152877808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5623531341553</t>
   </si>
   <si>
     <t xml:space="preserve">11.7805099487305</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9114036560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9550352096558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.693247795105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3040885925293</t>
+    <t xml:space="preserve">11.9114046096802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9550361633301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6932468414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3040895462036</t>
   </si>
   <si>
     <t xml:space="preserve">12.2604570388794</t>
@@ -1940,10 +1940,10 @@
     <t xml:space="preserve">12.2168254852295</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3913507461548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7368783950806</t>
+    <t xml:space="preserve">12.3913516998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7368774414062</t>
   </si>
   <si>
     <t xml:space="preserve">11.8677730560303</t>
@@ -1952,34 +1952,34 @@
     <t xml:space="preserve">11.6059837341309</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9515113830566</t>
+    <t xml:space="preserve">10.951512336731</t>
   </si>
   <si>
     <t xml:space="preserve">12.0422992706299</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3005647659302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3441953659058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9951429367065</t>
+    <t xml:space="preserve">11.3005638122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3441944122314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9951419830322</t>
   </si>
   <si>
     <t xml:space="preserve">10.4715642929077</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9078807830811</t>
+    <t xml:space="preserve">10.9078798294067</t>
   </si>
   <si>
     <t xml:space="preserve">11.4314584732056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0387735366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9899415969849</t>
+    <t xml:space="preserve">11.0387744903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9899406433105</t>
   </si>
   <si>
     <t xml:space="preserve">11.7456045150757</t>
@@ -1991,10 +1991,10 @@
     <t xml:space="preserve">11.5187206268311</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6234359741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4489107131958</t>
+    <t xml:space="preserve">11.6234369277954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4489097595215</t>
   </si>
   <si>
     <t xml:space="preserve">11.6408891677856</t>
@@ -2012,28 +2012,28 @@
     <t xml:space="preserve">11.0998582839966</t>
   </si>
   <si>
-    <t xml:space="preserve">10.803165435791</t>
+    <t xml:space="preserve">10.8031644821167</t>
   </si>
   <si>
     <t xml:space="preserve">10.7508058547974</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3319435119629</t>
+    <t xml:space="preserve">10.3319444656372</t>
   </si>
   <si>
     <t xml:space="preserve">10.1050596237183</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81839275360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69297313690186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7108907699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1408929824829</t>
+    <t xml:space="preserve">9.81839179992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69297409057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71089172363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1408939361572</t>
   </si>
   <si>
     <t xml:space="preserve">10.2663106918335</t>
@@ -2045,19 +2045,19 @@
     <t xml:space="preserve">10.1229763031006</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1588096618652</t>
+    <t xml:space="preserve">10.1588106155396</t>
   </si>
   <si>
     <t xml:space="preserve">10.0692262649536</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0871429443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4633960723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7858972549438</t>
+    <t xml:space="preserve">10.0871438980103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4633951187134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7858963012695</t>
   </si>
   <si>
     <t xml:space="preserve">10.5708961486816</t>
@@ -2066,7 +2066,7 @@
     <t xml:space="preserve">10.7142305374146</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7500638961792</t>
+    <t xml:space="preserve">10.7500629425049</t>
   </si>
   <si>
     <t xml:space="preserve">11.1621494293213</t>
@@ -2075,34 +2075,34 @@
     <t xml:space="preserve">10.8754816055298</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6425628662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5888118743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5171451568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8575649261475</t>
+    <t xml:space="preserve">10.6425638198853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.588812828064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5171461105347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8575639724731</t>
   </si>
   <si>
     <t xml:space="preserve">10.9113149642944</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6067295074463</t>
+    <t xml:space="preserve">10.6067304611206</t>
   </si>
   <si>
     <t xml:space="preserve">10.6604795455933</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3021450042725</t>
+    <t xml:space="preserve">10.3021440505981</t>
   </si>
   <si>
     <t xml:space="preserve">10.4096450805664</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3558950424194</t>
+    <t xml:space="preserve">10.3558940887451</t>
   </si>
   <si>
     <t xml:space="preserve">10.6783971786499</t>
@@ -2114,7 +2114,7 @@
     <t xml:space="preserve">10.535062789917</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1800661087036</t>
+    <t xml:space="preserve">11.1800651550293</t>
   </si>
   <si>
     <t xml:space="preserve">10.9829816818237</t>
@@ -2132,7 +2132,7 @@
     <t xml:space="preserve">11.9146537780762</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9325704574585</t>
+    <t xml:space="preserve">11.9325714111328</t>
   </si>
   <si>
     <t xml:space="preserve">12.0221548080444</t>
@@ -2141,10 +2141,10 @@
     <t xml:space="preserve">11.8788204193115</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2371559143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3267393112183</t>
+    <t xml:space="preserve">12.2371549606323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3267402648926</t>
   </si>
   <si>
     <t xml:space="preserve">12.4521570205688</t>
@@ -2153,7 +2153,7 @@
     <t xml:space="preserve">12.0938215255737</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3984069824219</t>
+    <t xml:space="preserve">12.3984079360962</t>
   </si>
   <si>
     <t xml:space="preserve">12.201322555542</t>
@@ -2180,7 +2180,7 @@
     <t xml:space="preserve">13.258412361145</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4017467498779</t>
+    <t xml:space="preserve">13.4017457962036</t>
   </si>
   <si>
     <t xml:space="preserve">13.4375791549683</t>
@@ -2189,19 +2189,19 @@
     <t xml:space="preserve">13.6884145736694</t>
   </si>
   <si>
-    <t xml:space="preserve">13.903416633606</t>
+    <t xml:space="preserve">13.9034156799316</t>
   </si>
   <si>
     <t xml:space="preserve">14.6559209823608</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2438335418701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6380033493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.92467212677</t>
+    <t xml:space="preserve">14.2438344955444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6380043029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9246711730957</t>
   </si>
   <si>
     <t xml:space="preserve">14.5125865936279</t>
@@ -2222,16 +2222,16 @@
     <t xml:space="preserve">14.2617511749268</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8888387680054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8171710968018</t>
+    <t xml:space="preserve">14.8888397216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8171720504761</t>
   </si>
   <si>
     <t xml:space="preserve">14.387167930603</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7634201049805</t>
+    <t xml:space="preserve">14.7634191513062</t>
   </si>
   <si>
     <t xml:space="preserve">14.6200866699219</t>
@@ -2240,10 +2240,10 @@
     <t xml:space="preserve">14.9067535400391</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1217546463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0321741104126</t>
+    <t xml:space="preserve">15.1217555999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.032172203064</t>
   </si>
   <si>
     <t xml:space="preserve">14.7455034255981</t>
@@ -2282,13 +2282,13 @@
     <t xml:space="preserve">12.9717426300049</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4700746536255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2404956817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6525802612305</t>
+    <t xml:space="preserve">12.4700736999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2404947280884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6525812149048</t>
   </si>
   <si>
     <t xml:space="preserve">13.5809135437012</t>
@@ -2300,22 +2300,22 @@
     <t xml:space="preserve">13.4913301467896</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2225780487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2046604156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0613269805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0075778961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6313247680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0971612930298</t>
+    <t xml:space="preserve">13.2225790023804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2046613693237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0613279342651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0075769424438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6313257217407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0971603393555</t>
   </si>
   <si>
     <t xml:space="preserve">13.0792446136475</t>
@@ -2351,13 +2351,13 @@
     <t xml:space="preserve">13.2763290405273</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7925748825073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5954923629761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5238246917725</t>
+    <t xml:space="preserve">12.7925758361816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5954914093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5238237380981</t>
   </si>
   <si>
     <t xml:space="preserve">12.5059070587158</t>
@@ -2369,10 +2369,10 @@
     <t xml:space="preserve">12.3088226318359</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5417413711548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8284091949463</t>
+    <t xml:space="preserve">12.5417404174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8284101486206</t>
   </si>
   <si>
     <t xml:space="preserve">12.3804903030396</t>
@@ -2390,10 +2390,10 @@
     <t xml:space="preserve">12.7746591567993</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4342403411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9504871368408</t>
+    <t xml:space="preserve">12.4342412948608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9504880905151</t>
   </si>
   <si>
     <t xml:space="preserve">12.2192392349243</t>
@@ -2408,7 +2408,7 @@
     <t xml:space="preserve">11.9684047698975</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0400714874268</t>
+    <t xml:space="preserve">12.0400705337524</t>
   </si>
   <si>
     <t xml:space="preserve">12.0042381286621</t>
@@ -2417,7 +2417,7 @@
     <t xml:space="preserve">12.255072593689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7388248443604</t>
+    <t xml:space="preserve">12.7388257980347</t>
   </si>
   <si>
     <t xml:space="preserve">13.7421655654907</t>
@@ -2426,10 +2426,10 @@
     <t xml:space="preserve">13.7063312530518</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0825834274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0109157562256</t>
+    <t xml:space="preserve">14.0825843811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0109167098999</t>
   </si>
   <si>
     <t xml:space="preserve">13.7242479324341</t>
@@ -2438,10 +2438,10 @@
     <t xml:space="preserve">14.0467500686646</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0646657943726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9392490386963</t>
+    <t xml:space="preserve">14.0646667480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9392499923706</t>
   </si>
   <si>
     <t xml:space="preserve">13.6346645355225</t>
@@ -2465,10 +2465,10 @@
     <t xml:space="preserve">13.5450801849365</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4734134674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1867446899414</t>
+    <t xml:space="preserve">13.4734125137329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1867456436157</t>
   </si>
   <si>
     <t xml:space="preserve">13.3838291168213</t>
@@ -2477,7 +2477,7 @@
     <t xml:space="preserve">13.5988302230835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.70299243927</t>
+    <t xml:space="preserve">12.7029914855957</t>
   </si>
   <si>
     <t xml:space="preserve">11.8429870605469</t>
@@ -2486,16 +2486,16 @@
     <t xml:space="preserve">11.7892360687256</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6817359924316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0759048461914</t>
+    <t xml:space="preserve">11.6817350387573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0759038925171</t>
   </si>
   <si>
     <t xml:space="preserve">11.5742359161377</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2159004211426</t>
+    <t xml:space="preserve">11.2158994674683</t>
   </si>
   <si>
     <t xml:space="preserve">11.3592338562012</t>
@@ -2504,7 +2504,7 @@
     <t xml:space="preserve">11.4309015274048</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3054828643799</t>
+    <t xml:space="preserve">11.3054838180542</t>
   </si>
   <si>
     <t xml:space="preserve">11.2875671386719</t>
@@ -3447,6 +3447,9 @@
   </si>
   <si>
     <t xml:space="preserve">18.4599990844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1800003051758</t>
   </si>
 </sst>
 </file>
@@ -68603,7 +68606,7 @@
     </row>
     <row r="2494">
       <c r="A2494" s="1" t="n">
-        <v>45951.6493055556</v>
+        <v>45951.2916666667</v>
       </c>
       <c r="B2494" t="n">
         <v>66507</v>
@@ -68624,6 +68627,32 @@
         <v>1144</v>
       </c>
       <c r="H2494" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2495">
+      <c r="A2495" s="1" t="n">
+        <v>45952.6494097222</v>
+      </c>
+      <c r="B2495" t="n">
+        <v>53876</v>
+      </c>
+      <c r="C2495" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="D2495" t="n">
+        <v>18.0599994659424</v>
+      </c>
+      <c r="E2495" t="n">
+        <v>18.4599990844727</v>
+      </c>
+      <c r="F2495" t="n">
+        <v>18.1800003051758</v>
+      </c>
+      <c r="G2495" t="s">
+        <v>1145</v>
+      </c>
+      <c r="H2495" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ORS.MI.xlsx
+++ b/data/ORS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1150" uniqueCount="1150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="1151">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,13 +44,13 @@
     <t xml:space="preserve">ORS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98275804519653</t>
+    <t xml:space="preserve">7.98275899887085</t>
   </si>
   <si>
     <t xml:space="preserve">8.06380176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94223737716675</t>
+    <t xml:space="preserve">7.94223642349243</t>
   </si>
   <si>
     <t xml:space="preserve">7.82472467422485</t>
@@ -59,76 +59,76 @@
     <t xml:space="preserve">7.93818521499634</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9017162322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03949069976807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92603015899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86119508743286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82067346572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93413305282593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02328109741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08811569213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14484596252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69910860061646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8044638633728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97465562820435</t>
+    <t xml:space="preserve">7.90171670913696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03948879241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92602968215942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86119413375854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82067155838013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93413400650024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02328205108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08811378479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14484691619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69910764694214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80446481704712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97465467453003</t>
   </si>
   <si>
     <t xml:space="preserve">8.01112461090088</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01517677307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79230785369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82877683639526</t>
+    <t xml:space="preserve">8.01517581939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79230737686157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82877779006958</t>
   </si>
   <si>
     <t xml:space="preserve">8.34745311737061</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84093332290649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90982055664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85714054107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78015041351318</t>
+    <t xml:space="preserve">7.84093523025513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90981912612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85714101791382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7801513671875</t>
   </si>
   <si>
     <t xml:space="preserve">7.8449854850769</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97870779037476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88550662994385</t>
+    <t xml:space="preserve">7.97870588302612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88550710678101</t>
   </si>
   <si>
     <t xml:space="preserve">7.95034265518188</t>
@@ -137,16 +137,16 @@
     <t xml:space="preserve">8.00301933288574</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01922798156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91792392730713</t>
+    <t xml:space="preserve">8.0192289352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91792440414429</t>
   </si>
   <si>
     <t xml:space="preserve">8.1002721786499</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10432434082031</t>
+    <t xml:space="preserve">8.10432243347168</t>
   </si>
   <si>
     <t xml:space="preserve">8.18536758422852</t>
@@ -158,7 +158,7 @@
     <t xml:space="preserve">8.11242866516113</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07595920562744</t>
+    <t xml:space="preserve">8.07595825195312</t>
   </si>
   <si>
     <t xml:space="preserve">8.03138446807861</t>
@@ -167,46 +167,46 @@
     <t xml:space="preserve">8.09621906280518</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1772632598877</t>
+    <t xml:space="preserve">8.17726230621338</t>
   </si>
   <si>
     <t xml:space="preserve">8.05569839477539</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12053298950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25830554962158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4203929901123</t>
+    <t xml:space="preserve">8.12053203582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2583065032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42039203643799</t>
   </si>
   <si>
     <t xml:space="preserve">8.67162704467773</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55816555023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42849731445312</t>
+    <t xml:space="preserve">8.55816650390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42849826812744</t>
   </si>
   <si>
     <t xml:space="preserve">8.52429008483887</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45921993255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50802135467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60562705993652</t>
+    <t xml:space="preserve">8.45921897888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50802040100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60562896728516</t>
   </si>
   <si>
     <t xml:space="preserve">8.5324239730835</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61376190185547</t>
+    <t xml:space="preserve">8.61376285552979</t>
   </si>
   <si>
     <t xml:space="preserve">8.67069911956787</t>
@@ -215,34 +215,34 @@
     <t xml:space="preserve">8.87404727935791</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7927074432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90658092498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86591148376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94725036621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93911647796631</t>
+    <t xml:space="preserve">8.79270648956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90657997131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86591243743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94725227355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93911838531494</t>
   </si>
   <si>
     <t xml:space="preserve">8.78457355499268</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7439022064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91471481323242</t>
+    <t xml:space="preserve">8.74390506744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91471385955811</t>
   </si>
   <si>
     <t xml:space="preserve">8.92284965515137</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10993003845215</t>
+    <t xml:space="preserve">9.10992813110352</t>
   </si>
   <si>
     <t xml:space="preserve">9.077392578125</t>
@@ -251,10 +251,10 @@
     <t xml:space="preserve">9.11806297302246</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1343297958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15059757232666</t>
+    <t xml:space="preserve">9.13433074951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15059661865234</t>
   </si>
   <si>
     <t xml:space="preserve">9.15873146057129</t>
@@ -266,13 +266,13 @@
     <t xml:space="preserve">8.6788330078125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85777759552002</t>
+    <t xml:space="preserve">8.8577766418457</t>
   </si>
   <si>
     <t xml:space="preserve">8.72763633728027</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70323657989502</t>
+    <t xml:space="preserve">8.70323467254639</t>
   </si>
   <si>
     <t xml:space="preserve">8.66256523132324</t>
@@ -281,10 +281,10 @@
     <t xml:space="preserve">8.69510173797607</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62189483642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80084133148193</t>
+    <t xml:space="preserve">8.62189674377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80084228515625</t>
   </si>
   <si>
     <t xml:space="preserve">8.77643966674805</t>
@@ -296,43 +296,43 @@
     <t xml:space="preserve">8.54869174957275</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54055690765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58122825622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46735191345215</t>
+    <t xml:space="preserve">8.54055786132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58122730255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46735286712646</t>
   </si>
   <si>
     <t xml:space="preserve">8.51615524291992</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49988746643066</t>
+    <t xml:space="preserve">8.49988651275635</t>
   </si>
   <si>
     <t xml:space="preserve">8.45108413696289</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63003063201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8089771270752</t>
+    <t xml:space="preserve">8.63003158569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80897617340088</t>
   </si>
   <si>
     <t xml:space="preserve">8.89031314849854</t>
   </si>
   <si>
-    <t xml:space="preserve">8.930983543396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9635181427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0529899597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30514049530029</t>
+    <t xml:space="preserve">8.93098449707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96351718902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05299091339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30514144897461</t>
   </si>
   <si>
     <t xml:space="preserve">9.1017951965332</t>
@@ -341,19 +341,19 @@
     <t xml:space="preserve">9.19126605987549</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35394477844238</t>
+    <t xml:space="preserve">9.35394287109375</t>
   </si>
   <si>
     <t xml:space="preserve">9.4759521484375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54915714263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58982467651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66303062438965</t>
+    <t xml:space="preserve">9.54915523529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58982563018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66303157806396</t>
   </si>
   <si>
     <t xml:space="preserve">9.71996688842773</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">9.85824298858643</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0046529769897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2405347824097</t>
+    <t xml:space="preserve">10.0046539306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.240535736084</t>
   </si>
   <si>
     <t xml:space="preserve">10.2486686706543</t>
@@ -374,7 +374,7 @@
     <t xml:space="preserve">10.3381414413452</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5984258651733</t>
+    <t xml:space="preserve">10.5984268188477</t>
   </si>
   <si>
     <t xml:space="preserve">10.4276151657104</t>
@@ -383,91 +383,91 @@
     <t xml:space="preserve">10.4032125473022</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5252208709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4601497650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5658893585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5821571350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7773714065552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9807176589966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8749761581421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6553630828857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6797647476196</t>
+    <t xml:space="preserve">10.5252199172974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.460150718689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5658903121948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5821561813354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7773694992065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9807157516479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8749771118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6553621292114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.679762840271</t>
   </si>
   <si>
     <t xml:space="preserve">10.5740232467651</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5170869827271</t>
+    <t xml:space="preserve">10.5170860290527</t>
   </si>
   <si>
     <t xml:space="preserve">10.5414886474609</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5577564239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5089540481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8180389404297</t>
+    <t xml:space="preserve">10.5577573776245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5089521408081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.818039894104</t>
   </si>
   <si>
     <t xml:space="preserve">10.6878976821899</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7611026763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6472272872925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8993797302246</t>
+    <t xml:space="preserve">10.761100769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6472282409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.899377822876</t>
   </si>
   <si>
     <t xml:space="preserve">10.883111000061</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6716318130493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7367010116577</t>
+    <t xml:space="preserve">10.6716299057007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.736701965332</t>
   </si>
   <si>
     <t xml:space="preserve">11.0051193237305</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0213861465454</t>
+    <t xml:space="preserve">11.0213851928711</t>
   </si>
   <si>
     <t xml:space="preserve">11.184063911438</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4036769866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3955430984497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3386077880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3223400115967</t>
+    <t xml:space="preserve">11.4036779403687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3955450057983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3386068344116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.322338104248</t>
   </si>
   <si>
     <t xml:space="preserve">11.3304738998413</t>
@@ -476,10 +476,10 @@
     <t xml:space="preserve">11.3630084991455</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0783243179321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6065587997437</t>
+    <t xml:space="preserve">11.0783233642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.606559753418</t>
   </si>
   <si>
     <t xml:space="preserve">10.8424406051636</t>
@@ -500,13 +500,13 @@
     <t xml:space="preserve">10.2730712890625</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2324018478394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3218746185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3706769943237</t>
+    <t xml:space="preserve">10.232400894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3218727111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3706760406494</t>
   </si>
   <si>
     <t xml:space="preserve">10.3300075531006</t>
@@ -515,10 +515,10 @@
     <t xml:space="preserve">10.3056058883667</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2568025588989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1835975646973</t>
+    <t xml:space="preserve">10.2568035125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1835966110229</t>
   </si>
   <si>
     <t xml:space="preserve">10.4845514297485</t>
@@ -527,7 +527,7 @@
     <t xml:space="preserve">10.3625431060791</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4438819885254</t>
+    <t xml:space="preserve">10.4438810348511</t>
   </si>
   <si>
     <t xml:space="preserve">10.8587083816528</t>
@@ -536,22 +536,22 @@
     <t xml:space="preserve">10.9237794876099</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0376529693604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0620555877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.102725982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1433944702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.175929069519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1352605819702</t>
+    <t xml:space="preserve">11.037654876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0620574951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1027240753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1433954238892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1759281158447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1352615356445</t>
   </si>
   <si>
     <t xml:space="preserve">11.0701904296875</t>
@@ -566,43 +566,43 @@
     <t xml:space="preserve">11.2247323989868</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0457859039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5008192062378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1347951889038</t>
+    <t xml:space="preserve">11.0457878112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5008182525635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1347942352295</t>
   </si>
   <si>
     <t xml:space="preserve">8.36161231994629</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01999092102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10946369171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39414691925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21520137786865</t>
+    <t xml:space="preserve">8.01998996734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10946178436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3941478729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21520328521729</t>
   </si>
   <si>
     <t xml:space="preserve">8.33721160888672</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31280899047852</t>
+    <t xml:space="preserve">8.3128080368042</t>
   </si>
   <si>
     <t xml:space="preserve">8.18266677856445</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34534454345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23960399627686</t>
+    <t xml:space="preserve">8.34534549713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23960494995117</t>
   </si>
   <si>
     <t xml:space="preserve">8.49175548553467</t>
@@ -611,19 +611,19 @@
     <t xml:space="preserve">8.58936023712158</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76017189025879</t>
+    <t xml:space="preserve">8.76017093658447</t>
   </si>
   <si>
     <t xml:space="preserve">8.29654216766357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25587272644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17453479766846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19079971313477</t>
+    <t xml:space="preserve">8.25587177276611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17453289031982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19080066680908</t>
   </si>
   <si>
     <t xml:space="preserve">8.23147106170654</t>
@@ -635,124 +635,124 @@
     <t xml:space="preserve">8.14199829101562</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1582670211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16639995574951</t>
+    <t xml:space="preserve">8.15826606750488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16640090942383</t>
   </si>
   <si>
     <t xml:space="preserve">8.12166309356689</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05252552032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89798259735107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85731267929077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93051815032959</t>
+    <t xml:space="preserve">8.05252647399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89798307418823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85731220245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93051671981812</t>
   </si>
   <si>
     <t xml:space="preserve">7.9061164855957</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93865251541138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84917831420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.808509349823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62956428527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57262754440308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48315572738647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66616630554199</t>
+    <t xml:space="preserve">7.93865156173706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84917879104614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80850982666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62956476211548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57262802124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48315477371216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66616582870483</t>
   </si>
   <si>
     <t xml:space="preserve">7.60516309738159</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54009294509888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5238242149353</t>
+    <t xml:space="preserve">7.54009342193604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52382469177246</t>
   </si>
   <si>
     <t xml:space="preserve">7.47908735275269</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61329793930054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54822540283203</t>
+    <t xml:space="preserve">7.61329698562622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54822635650635</t>
   </si>
   <si>
     <t xml:space="preserve">7.56449365615845</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50755596160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4668869972229</t>
+    <t xml:space="preserve">7.5075569152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46688556671143</t>
   </si>
   <si>
     <t xml:space="preserve">7.4912896156311</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49942255020142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31234502792358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27980899810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37741470336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38554906845093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36928081512451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3204779624939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34487867355347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28794288635254</t>
+    <t xml:space="preserve">7.4994215965271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31234407424927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27980661392212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3774151802063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38554954528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36928176879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32047700881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34487915039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28794240951538</t>
   </si>
   <si>
     <t xml:space="preserve">7.04392623901367</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15780067443848</t>
+    <t xml:space="preserve">7.15779972076416</t>
   </si>
   <si>
     <t xml:space="preserve">7.39368295669556</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42621755599976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40181636810303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30421113967896</t>
+    <t xml:space="preserve">7.42621803283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40181684494019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3042106628418</t>
   </si>
   <si>
     <t xml:space="preserve">7.3611478805542</t>
@@ -764,67 +764,67 @@
     <t xml:space="preserve">7.35301303863525</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33674573898315</t>
+    <t xml:space="preserve">7.33674621582031</t>
   </si>
   <si>
     <t xml:space="preserve">7.27167367935181</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23100423812866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32861232757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26354074478149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23913908004761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22287082672119</t>
+    <t xml:space="preserve">7.23100471496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32861137390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26354122161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23913955688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22287178039551</t>
   </si>
   <si>
     <t xml:space="preserve">7.24727296829224</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44248580932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25540685653687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18220186233521</t>
+    <t xml:space="preserve">7.44248628616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25540733337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18220233917236</t>
   </si>
   <si>
     <t xml:space="preserve">7.29607582092285</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16593503952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14153337478638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05205965042114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07646226882935</t>
+    <t xml:space="preserve">7.16593456268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14153242111206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0520601272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07646131515503</t>
   </si>
   <si>
     <t xml:space="preserve">7.0357928276062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01952457427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87311506271362</t>
+    <t xml:space="preserve">7.01952505111694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87311458587646</t>
   </si>
   <si>
     <t xml:space="preserve">6.677903175354</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85124778747559</t>
+    <t xml:space="preserve">6.85124683380127</t>
   </si>
   <si>
     <t xml:space="preserve">6.93379211425781</t>
@@ -833,25 +833,25 @@
     <t xml:space="preserve">7.26397275924683</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14841079711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09888362884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18142747879028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16491889953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14015626907349</t>
+    <t xml:space="preserve">7.14841032028198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0988826751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18142795562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16491842269897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14015579223633</t>
   </si>
   <si>
     <t xml:space="preserve">7.21444606781006</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17317390441895</t>
+    <t xml:space="preserve">7.1731743812561</t>
   </si>
   <si>
     <t xml:space="preserve">6.97506427764893</t>
@@ -863,16 +863,16 @@
     <t xml:space="preserve">6.60361242294312</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62012100219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67790269851685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80997514724731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54583072662354</t>
+    <t xml:space="preserve">6.62012147903442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67790222167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80997467041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54583024978638</t>
   </si>
   <si>
     <t xml:space="preserve">6.31470394134521</t>
@@ -881,13 +881,13 @@
     <t xml:space="preserve">6.32295846939087</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34772253036499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38074016571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39724922180176</t>
+    <t xml:space="preserve">6.34772300720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38073968887329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3972487449646</t>
   </si>
   <si>
     <t xml:space="preserve">6.4715404510498</t>
@@ -899,28 +899,28 @@
     <t xml:space="preserve">6.22390413284302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09183216094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9019775390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95976066589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9927773475647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20739603042603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14135885238647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19088697433472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14961290359497</t>
+    <t xml:space="preserve">6.09183168411255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90197801589966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9597601890564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99277782440186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20739555358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14135980606079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19088649749756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14961338043213</t>
   </si>
   <si>
     <t xml:space="preserve">6.07532405853271</t>
@@ -929,22 +929,22 @@
     <t xml:space="preserve">6.25692272186279</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00928735733032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98452377319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12485027313232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13310432434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27343130111694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44677639007568</t>
+    <t xml:space="preserve">6.00928783416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98452281951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12484979629517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13310480117798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2734317779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44677591323853</t>
   </si>
   <si>
     <t xml:space="preserve">6.55408525466919</t>
@@ -953,34 +953,34 @@
     <t xml:space="preserve">6.51281213760376</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36423110961914</t>
+    <t xml:space="preserve">6.3642315864563</t>
   </si>
   <si>
     <t xml:space="preserve">6.2404146194458</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21565008163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23216009140015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2486686706543</t>
+    <t xml:space="preserve">6.21564960479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23215961456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24866771697998</t>
   </si>
   <si>
     <t xml:space="preserve">6.11659574508667</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10834074020386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05055952072144</t>
+    <t xml:space="preserve">6.1083402633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05055904388428</t>
   </si>
   <si>
     <t xml:space="preserve">5.89372396469116</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77816104888916</t>
+    <t xml:space="preserve">5.778160572052</t>
   </si>
   <si>
     <t xml:space="preserve">5.6956148147583</t>
@@ -989,19 +989,19 @@
     <t xml:space="preserve">5.79466962814331</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80292415618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82768726348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78641510009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73688793182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85245132446289</t>
+    <t xml:space="preserve">5.80292367935181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82768774032593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78641557693481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73688745498657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85245180130005</t>
   </si>
   <si>
     <t xml:space="preserve">6.29819488525391</t>
@@ -1022,34 +1022,34 @@
     <t xml:space="preserve">5.81943321228027</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91848659515381</t>
+    <t xml:space="preserve">5.91848707199097</t>
   </si>
   <si>
     <t xml:space="preserve">5.86070537567139</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76165246963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75339698791504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81117820739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70386981964111</t>
+    <t xml:space="preserve">5.76165151596069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75339651107788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81117868423462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70387029647827</t>
   </si>
   <si>
     <t xml:space="preserve">5.74514245986938</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83594226837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71212387084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84419727325439</t>
+    <t xml:space="preserve">5.83594179153442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71212434768677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84419679641724</t>
   </si>
   <si>
     <t xml:space="preserve">5.94325065612793</t>
@@ -1064,10 +1064,10 @@
     <t xml:space="preserve">5.88546991348267</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93499565124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02579641342163</t>
+    <t xml:space="preserve">5.93499612808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02579593658447</t>
   </si>
   <si>
     <t xml:space="preserve">6.0670690536499</t>
@@ -1076,7 +1076,7 @@
     <t xml:space="preserve">6.38899421691895</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19914150238037</t>
+    <t xml:space="preserve">6.19914102554321</t>
   </si>
   <si>
     <t xml:space="preserve">6.04230451583862</t>
@@ -1085,73 +1085,73 @@
     <t xml:space="preserve">6.05881452560425</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95150566101074</t>
+    <t xml:space="preserve">5.95150518417358</t>
   </si>
   <si>
     <t xml:space="preserve">6.17437744140625</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17601919174194</t>
+    <t xml:space="preserve">6.1760196685791</t>
   </si>
   <si>
     <t xml:space="preserve">6.29349803924561</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25993299484253</t>
+    <t xml:space="preserve">6.25993204116821</t>
   </si>
   <si>
     <t xml:space="preserve">6.20958423614502</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09210586547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10888957977295</t>
+    <t xml:space="preserve">6.09210538864136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10888910293579</t>
   </si>
   <si>
     <t xml:space="preserve">6.07532358169556</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14245367050171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05854082107544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02497482299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97462797164917</t>
+    <t xml:space="preserve">6.14245319366455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05854034423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02497529983521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97462749481201</t>
   </si>
   <si>
     <t xml:space="preserve">5.95784425735474</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15923690795898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12567138671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19280195236206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42775964736938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71306419372559</t>
+    <t xml:space="preserve">6.15923738479614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12567186355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1928014755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42775869369507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71306467056274</t>
   </si>
   <si>
     <t xml:space="preserve">6.64593458175659</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69628190994263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78019571304321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7298469543457</t>
+    <t xml:space="preserve">6.69628238677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78019523620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72984743118286</t>
   </si>
   <si>
     <t xml:space="preserve">6.629150390625</t>
@@ -1160,13 +1160,13 @@
     <t xml:space="preserve">6.56202030181885</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54523801803589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67949867248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66271638870239</t>
+    <t xml:space="preserve">6.54523754119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67949914932251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66271686553955</t>
   </si>
   <si>
     <t xml:space="preserve">6.57880353927612</t>
@@ -1175,13 +1175,13 @@
     <t xml:space="preserve">6.37741088867188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34384679794312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22636747360229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36062812805176</t>
+    <t xml:space="preserve">6.34384632110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22636699676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36062908172607</t>
   </si>
   <si>
     <t xml:space="preserve">5.67253875732422</t>
@@ -1193,7 +1193,7 @@
     <t xml:space="preserve">5.68932247161865</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62219190597534</t>
+    <t xml:space="preserve">5.62219142913818</t>
   </si>
   <si>
     <t xml:space="preserve">5.53827810287476</t>
@@ -1202,19 +1202,19 @@
     <t xml:space="preserve">5.43758249282837</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45436573028564</t>
+    <t xml:space="preserve">5.45436525344849</t>
   </si>
   <si>
     <t xml:space="preserve">5.60540819168091</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52149534225464</t>
+    <t xml:space="preserve">5.5214958190918</t>
   </si>
   <si>
     <t xml:space="preserve">5.50471305847168</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4879298210144</t>
+    <t xml:space="preserve">5.48793029785156</t>
   </si>
   <si>
     <t xml:space="preserve">5.35366868972778</t>
@@ -1223,7 +1223,7 @@
     <t xml:space="preserve">5.37045097351074</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42079925537109</t>
+    <t xml:space="preserve">5.42079877853394</t>
   </si>
   <si>
     <t xml:space="preserve">5.28653860092163</t>
@@ -1232,10 +1232,10 @@
     <t xml:space="preserve">5.30332088470459</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26975536346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38723373413086</t>
+    <t xml:space="preserve">5.26975584030151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38723421096802</t>
   </si>
   <si>
     <t xml:space="preserve">5.32010364532471</t>
@@ -1244,43 +1244,43 @@
     <t xml:space="preserve">5.65575695037842</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75645351409912</t>
+    <t xml:space="preserve">5.75645303726196</t>
   </si>
   <si>
     <t xml:space="preserve">5.70610475540161</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72288656234741</t>
+    <t xml:space="preserve">5.72288703918457</t>
   </si>
   <si>
     <t xml:space="preserve">5.73967027664185</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63897466659546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57184362411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18584203720093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2026252746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21940755844116</t>
+    <t xml:space="preserve">5.6389741897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57184410095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18584156036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20262575149536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21940803527832</t>
   </si>
   <si>
     <t xml:space="preserve">5.16905975341797</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13549375534058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10192966461182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95088481903076</t>
+    <t xml:space="preserve">5.13549327850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1019287109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9508843421936</t>
   </si>
   <si>
     <t xml:space="preserve">5.03479814529419</t>
@@ -1289,7 +1289,7 @@
     <t xml:space="preserve">5.15227699279785</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11871147155762</t>
+    <t xml:space="preserve">5.11871194839478</t>
   </si>
   <si>
     <t xml:space="preserve">5.06836318969727</t>
@@ -1304,13 +1304,13 @@
     <t xml:space="preserve">5.25297260284424</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33688688278198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79001760482788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77323579788208</t>
+    <t xml:space="preserve">5.33688640594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79001808166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77323484420776</t>
   </si>
   <si>
     <t xml:space="preserve">5.58862638473511</t>
@@ -1319,10 +1319,10 @@
     <t xml:space="preserve">4.81662321090698</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79984140396118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59844827651978</t>
+    <t xml:space="preserve">4.79984092712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59844875335693</t>
   </si>
   <si>
     <t xml:space="preserve">4.36349201202393</t>
@@ -1331,13 +1331,13 @@
     <t xml:space="preserve">4.31314420700073</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19566535949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11175107955933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02783823013306</t>
+    <t xml:space="preserve">4.19566488265991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11175203323364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02783918380737</t>
   </si>
   <si>
     <t xml:space="preserve">4.17049074172974</t>
@@ -1349,13 +1349,13 @@
     <t xml:space="preserve">4.12014293670654</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34670877456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17888212203979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04462146759033</t>
+    <t xml:space="preserve">4.34670925140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17888164520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04462051391602</t>
   </si>
   <si>
     <t xml:space="preserve">4.15370798110962</t>
@@ -1370,7 +1370,7 @@
     <t xml:space="preserve">4.14531803131104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9942729473114</t>
+    <t xml:space="preserve">3.99427223205566</t>
   </si>
   <si>
     <t xml:space="preserve">4.09496927261353</t>
@@ -1385,7 +1385,7 @@
     <t xml:space="preserve">4.22922992706299</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21244812011719</t>
+    <t xml:space="preserve">4.21244764328003</t>
   </si>
   <si>
     <t xml:space="preserve">4.03622961044312</t>
@@ -1394,73 +1394,73 @@
     <t xml:space="preserve">4.12877893447876</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16283082962036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07770109176636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00108528137207</t>
+    <t xml:space="preserve">4.16283130645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07770156860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00108432769775</t>
   </si>
   <si>
     <t xml:space="preserve">4.20539569854736</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37565469741821</t>
+    <t xml:space="preserve">4.37565422058105</t>
   </si>
   <si>
     <t xml:space="preserve">4.21390867233276</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22242164611816</t>
+    <t xml:space="preserve">4.22242116928101</t>
   </si>
   <si>
     <t xml:space="preserve">4.25647354125977</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24796009063721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32457637786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30755138397217</t>
+    <t xml:space="preserve">4.24796056747437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32457685470581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30755090713501</t>
   </si>
   <si>
     <t xml:space="preserve">4.23944759368896</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35862827301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51186180114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53341579437256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9420371055603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89095878601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73772573471069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5504412651062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58449268341064</t>
+    <t xml:space="preserve">4.35862874984741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5118613243103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5334153175354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94203662872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8909592628479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73772621154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55044078826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5844931602478</t>
   </si>
   <si>
     <t xml:space="preserve">5.567467212677</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41423368453979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26100158691406</t>
+    <t xml:space="preserve">5.41423416137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2610011100769</t>
   </si>
   <si>
     <t xml:space="preserve">5.48233795166016</t>
@@ -1472,31 +1472,31 @@
     <t xml:space="preserve">5.6015191078186</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66962289810181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5163893699646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70367479324341</t>
+    <t xml:space="preserve">5.66962242126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51638984680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70367431640625</t>
   </si>
   <si>
     <t xml:space="preserve">5.32910442352295</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27802705764771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43126010894775</t>
+    <t xml:space="preserve">5.27802658081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43126058578491</t>
   </si>
   <si>
     <t xml:space="preserve">5.31207847595215</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22694969177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00561285018921</t>
+    <t xml:space="preserve">5.2269492149353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00561237335205</t>
   </si>
   <si>
     <t xml:space="preserve">4.95453500747681</t>
@@ -1505,22 +1505,22 @@
     <t xml:space="preserve">4.93750905990601</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05669069290161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03966474533081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97156047821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8864312171936</t>
+    <t xml:space="preserve">5.05668973922729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03966426849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97156095504761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88643074035645</t>
   </si>
   <si>
     <t xml:space="preserve">5.02263879776001</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92048358917236</t>
+    <t xml:space="preserve">4.92048263549805</t>
   </si>
   <si>
     <t xml:space="preserve">4.9034571647644</t>
@@ -1529,46 +1529,46 @@
     <t xml:space="preserve">4.852379322052</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8694052696228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34613037109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2439751625061</t>
+    <t xml:space="preserve">4.86940479278564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34613132476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24397563934326</t>
   </si>
   <si>
     <t xml:space="preserve">5.36315679550171</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38018226623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2099232673645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15884590148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1077675819397</t>
+    <t xml:space="preserve">5.38018321990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20992374420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15884637832642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10776805877686</t>
   </si>
   <si>
     <t xml:space="preserve">4.98858690261841</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09074211120605</t>
+    <t xml:space="preserve">5.0907416343689</t>
   </si>
   <si>
     <t xml:space="preserve">5.1928973197937</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1758713722229</t>
+    <t xml:space="preserve">5.17587184906006</t>
   </si>
   <si>
     <t xml:space="preserve">5.14181995391846</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0737156867981</t>
+    <t xml:space="preserve">5.07371616363525</t>
   </si>
   <si>
     <t xml:space="preserve">4.68212080001831</t>
@@ -1580,28 +1580,28 @@
     <t xml:space="preserve">4.59699106216431</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57996511459351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63104248046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78427648544312</t>
+    <t xml:space="preserve">4.57996559143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63104295730591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7842755317688</t>
   </si>
   <si>
     <t xml:space="preserve">4.76725006103516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81832790374756</t>
+    <t xml:space="preserve">4.8183274269104</t>
   </si>
   <si>
     <t xml:space="preserve">4.80130195617676</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39720821380615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61854457855225</t>
+    <t xml:space="preserve">5.39720869064331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6185450553894</t>
   </si>
   <si>
     <t xml:space="preserve">5.46531200408936</t>
@@ -1616,10 +1616,10 @@
     <t xml:space="preserve">5.68664836883545</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65259647369385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85690689086914</t>
+    <t xml:space="preserve">5.65259695053101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8569073677063</t>
   </si>
   <si>
     <t xml:space="preserve">5.8739333152771</t>
@@ -1628,10 +1628,10 @@
     <t xml:space="preserve">6.31660652160645</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33363199234009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29958009719849</t>
+    <t xml:space="preserve">6.33363246917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29958057403564</t>
   </si>
   <si>
     <t xml:space="preserve">6.35065841674805</t>
@@ -1643,22 +1643,22 @@
     <t xml:space="preserve">6.55496883392334</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69117641448975</t>
+    <t xml:space="preserve">6.69117593765259</t>
   </si>
   <si>
     <t xml:space="preserve">6.79333162307739</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15087461471558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08277034759521</t>
+    <t xml:space="preserve">7.15087509155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08277130126953</t>
   </si>
   <si>
     <t xml:space="preserve">6.87846088409424</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77630567550659</t>
+    <t xml:space="preserve">6.77630519866943</t>
   </si>
   <si>
     <t xml:space="preserve">6.84440898895264</t>
@@ -1667,10 +1667,10 @@
     <t xml:space="preserve">6.70820236206055</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75928020477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53794288635254</t>
+    <t xml:space="preserve">6.75927972793579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5379433631897</t>
   </si>
   <si>
     <t xml:space="preserve">6.72522783279419</t>
@@ -1682,28 +1682,28 @@
     <t xml:space="preserve">6.91251277923584</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8954873085022</t>
+    <t xml:space="preserve">6.89548683166504</t>
   </si>
   <si>
     <t xml:space="preserve">6.96359062194824</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17302131652832</t>
+    <t xml:space="preserve">7.17302179336548</t>
   </si>
   <si>
     <t xml:space="preserve">7.05085372924805</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1206636428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57443141937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9758415222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02819919586182</t>
+    <t xml:space="preserve">7.12066411972046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57443189620972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97584199905396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0281982421875</t>
   </si>
   <si>
     <t xml:space="preserve">8.0631046295166</t>
@@ -1715,37 +1715,37 @@
     <t xml:space="preserve">8.0107479095459</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94093751907349</t>
+    <t xml:space="preserve">7.94093799591064</t>
   </si>
   <si>
     <t xml:space="preserve">8.13291454315186</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15036869049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16781997680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18527412414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34234809875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11546230316162</t>
+    <t xml:space="preserve">8.15036773681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16782093048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18527317047119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34234619140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11546325683594</t>
   </si>
   <si>
     <t xml:space="preserve">8.25508403778076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08055686950684</t>
+    <t xml:space="preserve">8.08055782318115</t>
   </si>
   <si>
     <t xml:space="preserve">8.20272445678711</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95838832855225</t>
+    <t xml:space="preserve">7.95838928222656</t>
   </si>
   <si>
     <t xml:space="preserve">8.37725162506104</t>
@@ -1757,13 +1757,13 @@
     <t xml:space="preserve">8.81356716156006</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58668327331543</t>
+    <t xml:space="preserve">8.58668231964111</t>
   </si>
   <si>
     <t xml:space="preserve">8.53432559967041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69139957427979</t>
+    <t xml:space="preserve">8.69139766693115</t>
   </si>
   <si>
     <t xml:space="preserve">8.60413551330566</t>
@@ -1775,19 +1775,19 @@
     <t xml:space="preserve">8.42960929870605</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28998851776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30744075775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04565238952637</t>
+    <t xml:space="preserve">8.28998947143555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30744171142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04565334320068</t>
   </si>
   <si>
     <t xml:space="preserve">7.85367345809937</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41215801239014</t>
+    <t xml:space="preserve">8.41215705871582</t>
   </si>
   <si>
     <t xml:space="preserve">8.22017860412598</t>
@@ -1799,25 +1799,25 @@
     <t xml:space="preserve">8.3597993850708</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09801006317139</t>
+    <t xml:space="preserve">8.09800910949707</t>
   </si>
   <si>
     <t xml:space="preserve">8.23763084411621</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48196697235107</t>
+    <t xml:space="preserve">8.48196792602539</t>
   </si>
   <si>
     <t xml:space="preserve">8.62158870697021</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55177688598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65649223327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51687335968018</t>
+    <t xml:space="preserve">8.55177783966064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65649318695068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51687240600586</t>
   </si>
   <si>
     <t xml:space="preserve">8.46451377868652</t>
@@ -1826,28 +1826,28 @@
     <t xml:space="preserve">8.49942016601562</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56923007965088</t>
+    <t xml:space="preserve">8.5692310333252</t>
   </si>
   <si>
     <t xml:space="preserve">9.99161815643311</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59893417358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77346038818359</t>
+    <t xml:space="preserve">9.59893321990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77345943450928</t>
   </si>
   <si>
     <t xml:space="preserve">9.8170919418335</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29351329803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46804046630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55530261993408</t>
+    <t xml:space="preserve">9.29351425170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46803951263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55530166625977</t>
   </si>
   <si>
     <t xml:space="preserve">9.64256572723389</t>
@@ -1856,7 +1856,7 @@
     <t xml:space="preserve">9.9043550491333</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33714389801025</t>
+    <t xml:space="preserve">9.33714580535889</t>
   </si>
   <si>
     <t xml:space="preserve">9.94798564910889</t>
@@ -1865,13 +1865,13 @@
     <t xml:space="preserve">9.86072254180908</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5151958465576</t>
+    <t xml:space="preserve">10.5151968002319</t>
   </si>
   <si>
     <t xml:space="preserve">10.4279327392578</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5588274002075</t>
+    <t xml:space="preserve">10.5588283538818</t>
   </si>
   <si>
     <t xml:space="preserve">10.6024589538574</t>
@@ -1880,37 +1880,37 @@
     <t xml:space="preserve">10.8206167221069</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7333536148071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.776985168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2970380783081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3843002319336</t>
+    <t xml:space="preserve">10.7333545684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7769861221313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2970390319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3843011856079</t>
   </si>
   <si>
     <t xml:space="preserve">10.3406705856323</t>
   </si>
   <si>
-    <t xml:space="preserve">10.209774017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2534074783325</t>
+    <t xml:space="preserve">10.2097749710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2534065246582</t>
   </si>
   <si>
     <t xml:space="preserve">10.0788812637329</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51167011260986</t>
+    <t xml:space="preserve">9.51167106628418</t>
   </si>
   <si>
     <t xml:space="preserve">9.72982788085938</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68619728088379</t>
+    <t xml:space="preserve">9.68619823455811</t>
   </si>
   <si>
     <t xml:space="preserve">8.98809337615967</t>
@@ -1919,7 +1919,7 @@
     <t xml:space="preserve">9.42440795898438</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6496162414551</t>
+    <t xml:space="preserve">11.6496152877808</t>
   </si>
   <si>
     <t xml:space="preserve">11.562352180481</t>
@@ -1934,10 +1934,10 @@
     <t xml:space="preserve">11.9550361633301</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6932468414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3040885925293</t>
+    <t xml:space="preserve">11.693247795105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3040895462036</t>
   </si>
   <si>
     <t xml:space="preserve">12.2604570388794</t>
@@ -1946,10 +1946,10 @@
     <t xml:space="preserve">12.2168254852295</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3913516998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7368774414062</t>
+    <t xml:space="preserve">12.3913507461548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7368783950806</t>
   </si>
   <si>
     <t xml:space="preserve">11.8677730560303</t>
@@ -1958,70 +1958,70 @@
     <t xml:space="preserve">11.6059837341309</t>
   </si>
   <si>
-    <t xml:space="preserve">10.951512336731</t>
+    <t xml:space="preserve">10.9515104293823</t>
   </si>
   <si>
     <t xml:space="preserve">12.0422992706299</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3005638122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3441944122314</t>
+    <t xml:space="preserve">11.3005628585815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3441953659058</t>
   </si>
   <si>
     <t xml:space="preserve">10.9951429367065</t>
   </si>
   <si>
-    <t xml:space="preserve">10.471565246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9078788757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4314584732056</t>
+    <t xml:space="preserve">10.4715642929077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9078807830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4314575195312</t>
   </si>
   <si>
     <t xml:space="preserve">11.0387735366821</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9899406433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.74560546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5361738204956</t>
+    <t xml:space="preserve">11.9899415969849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7456045150757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5361728668213</t>
   </si>
   <si>
     <t xml:space="preserve">11.5187215805054</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6234369277954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4489097595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6408882141113</t>
+    <t xml:space="preserve">11.6234359741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4489116668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.64089012146</t>
   </si>
   <si>
     <t xml:space="preserve">11.7281522750854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9201316833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1173114776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0998582839966</t>
+    <t xml:space="preserve">11.9201307296753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1173105239868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0998592376709</t>
   </si>
   <si>
     <t xml:space="preserve">10.8031644821167</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7508058547974</t>
+    <t xml:space="preserve">10.7508068084717</t>
   </si>
   <si>
     <t xml:space="preserve">10.3319435119629</t>
@@ -2036,10 +2036,10 @@
     <t xml:space="preserve">9.69297409057617</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71089172363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1408939361572</t>
+    <t xml:space="preserve">9.7108907699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1408929824829</t>
   </si>
   <si>
     <t xml:space="preserve">10.2663106918335</t>
@@ -2054,25 +2054,25 @@
     <t xml:space="preserve">10.1588106155396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0692262649536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0871438980103</t>
+    <t xml:space="preserve">10.0692253112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0871429443359</t>
   </si>
   <si>
     <t xml:space="preserve">10.4633951187134</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7858963012695</t>
+    <t xml:space="preserve">10.7858982086182</t>
   </si>
   <si>
     <t xml:space="preserve">10.5708961486816</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7142305374146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7500629425049</t>
+    <t xml:space="preserve">10.7142295837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7500638961792</t>
   </si>
   <si>
     <t xml:space="preserve">11.1621494293213</t>
@@ -2081,22 +2081,22 @@
     <t xml:space="preserve">10.8754816055298</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6425638198853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.588812828064</t>
+    <t xml:space="preserve">10.6425619125366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5888118743896</t>
   </si>
   <si>
     <t xml:space="preserve">10.5171461105347</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8575639724731</t>
+    <t xml:space="preserve">10.8575649261475</t>
   </si>
   <si>
     <t xml:space="preserve">10.9113149642944</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6067304611206</t>
+    <t xml:space="preserve">10.6067295074463</t>
   </si>
   <si>
     <t xml:space="preserve">10.6604795455933</t>
@@ -2105,22 +2105,22 @@
     <t xml:space="preserve">10.3021440505981</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4096450805664</t>
+    <t xml:space="preserve">10.4096441268921</t>
   </si>
   <si>
     <t xml:space="preserve">10.3558940887451</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6783971786499</t>
+    <t xml:space="preserve">10.6783962249756</t>
   </si>
   <si>
     <t xml:space="preserve">10.4275617599487</t>
   </si>
   <si>
-    <t xml:space="preserve">10.535062789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1800651550293</t>
+    <t xml:space="preserve">10.5350618362427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1800661087036</t>
   </si>
   <si>
     <t xml:space="preserve">10.9829816818237</t>
@@ -2132,22 +2132,22 @@
     <t xml:space="preserve">11.3771505355835</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7354869842529</t>
+    <t xml:space="preserve">11.7354860305786</t>
   </si>
   <si>
     <t xml:space="preserve">11.9146537780762</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9325714111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0221548080444</t>
+    <t xml:space="preserve">11.9325704574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0221538543701</t>
   </si>
   <si>
     <t xml:space="preserve">11.8788204193115</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2371549606323</t>
+    <t xml:space="preserve">12.2371559143066</t>
   </si>
   <si>
     <t xml:space="preserve">12.3267402648926</t>
@@ -2159,10 +2159,10 @@
     <t xml:space="preserve">12.0938215255737</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3984079360962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.201322555542</t>
+    <t xml:space="preserve">12.3984069824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2013216018677</t>
   </si>
   <si>
     <t xml:space="preserve">11.9863214492798</t>
@@ -2174,7 +2174,7 @@
     <t xml:space="preserve">12.6134080886841</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8463268280029</t>
+    <t xml:space="preserve">12.8463258743286</t>
   </si>
   <si>
     <t xml:space="preserve">12.810492515564</t>
@@ -2189,16 +2189,16 @@
     <t xml:space="preserve">13.4017457962036</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4375791549683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6884145736694</t>
+    <t xml:space="preserve">13.4375801086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6884136199951</t>
   </si>
   <si>
     <t xml:space="preserve">13.9034156799316</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6559209823608</t>
+    <t xml:space="preserve">14.6559200286865</t>
   </si>
   <si>
     <t xml:space="preserve">14.2438344955444</t>
@@ -2207,7 +2207,7 @@
     <t xml:space="preserve">14.6380043029785</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9246711730957</t>
+    <t xml:space="preserve">14.92467212677</t>
   </si>
   <si>
     <t xml:space="preserve">14.5125865936279</t>
@@ -2222,34 +2222,34 @@
     <t xml:space="preserve">14.5484189987183</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4946689605713</t>
+    <t xml:space="preserve">14.4946699142456</t>
   </si>
   <si>
     <t xml:space="preserve">14.2617511749268</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8888397216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8171720504761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.387167930603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7634191513062</t>
+    <t xml:space="preserve">14.8888387680054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8171730041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3871688842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7634210586548</t>
   </si>
   <si>
     <t xml:space="preserve">14.6200866699219</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9067535400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1217555999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.032172203064</t>
+    <t xml:space="preserve">14.9067544937134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1217546463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0321731567383</t>
   </si>
   <si>
     <t xml:space="preserve">14.7455034255981</t>
@@ -2258,22 +2258,22 @@
     <t xml:space="preserve">15.0500888824463</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0680065155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1038398742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5305023193359</t>
+    <t xml:space="preserve">15.0680046081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1038408279419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5305032730103</t>
   </si>
   <si>
     <t xml:space="preserve">14.7096710205078</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2080011367798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6167469024658</t>
+    <t xml:space="preserve">14.2080001831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6167478561401</t>
   </si>
   <si>
     <t xml:space="preserve">13.5092468261719</t>
@@ -2282,13 +2282,13 @@
     <t xml:space="preserve">13.0434112548828</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1688280105591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9717426300049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4700736999512</t>
+    <t xml:space="preserve">13.1688270568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9717435836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4700746536255</t>
   </si>
   <si>
     <t xml:space="preserve">13.2404947280884</t>
@@ -2306,31 +2306,31 @@
     <t xml:space="preserve">13.4913301467896</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2225790023804</t>
+    <t xml:space="preserve">13.2225780487061</t>
   </si>
   <si>
     <t xml:space="preserve">13.2046613693237</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0613279342651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0075769424438</t>
+    <t xml:space="preserve">13.0613269805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0075778961182</t>
   </si>
   <si>
     <t xml:space="preserve">12.6313257217407</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0971603393555</t>
+    <t xml:space="preserve">13.0971612930298</t>
   </si>
   <si>
     <t xml:space="preserve">13.0792446136475</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8642425537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9896602630615</t>
+    <t xml:space="preserve">12.8642435073853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9896593093872</t>
   </si>
   <si>
     <t xml:space="preserve">12.9538269042969</t>
@@ -2345,16 +2345,16 @@
     <t xml:space="preserve">13.1150779724121</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1509113311768</t>
+    <t xml:space="preserve">13.1509122848511</t>
   </si>
   <si>
     <t xml:space="preserve">13.5271635055542</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3479957580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2763290405273</t>
+    <t xml:space="preserve">13.3479948043823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.276328086853</t>
   </si>
   <si>
     <t xml:space="preserve">12.7925758361816</t>
@@ -2366,22 +2366,22 @@
     <t xml:space="preserve">12.5238237380981</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5059070587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4879903793335</t>
+    <t xml:space="preserve">12.5059080123901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4879894256592</t>
   </si>
   <si>
     <t xml:space="preserve">12.3088226318359</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5417404174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8284101486206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3804903030396</t>
+    <t xml:space="preserve">12.5417413711548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8284091949463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3804893493652</t>
   </si>
   <si>
     <t xml:space="preserve">12.6671581268311</t>
@@ -2396,25 +2396,25 @@
     <t xml:space="preserve">12.7746591567993</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4342412948608</t>
+    <t xml:space="preserve">12.4342403411865</t>
   </si>
   <si>
     <t xml:space="preserve">11.9504880905151</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2192392349243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8250694274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1117382049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9684047698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0400705337524</t>
+    <t xml:space="preserve">12.2192401885986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8250703811646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1117391586304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9684038162231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0400714874268</t>
   </si>
   <si>
     <t xml:space="preserve">12.0042381286621</t>
@@ -2426,13 +2426,13 @@
     <t xml:space="preserve">12.7388257980347</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7421655654907</t>
+    <t xml:space="preserve">13.7421646118164</t>
   </si>
   <si>
     <t xml:space="preserve">13.7063312530518</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0825843811035</t>
+    <t xml:space="preserve">14.0825834274292</t>
   </si>
   <si>
     <t xml:space="preserve">14.0109167098999</t>
@@ -2450,7 +2450,7 @@
     <t xml:space="preserve">13.9392499923706</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6346645355225</t>
+    <t xml:space="preserve">13.6346635818481</t>
   </si>
   <si>
     <t xml:space="preserve">14.2796678543091</t>
@@ -2462,7 +2462,7 @@
     <t xml:space="preserve">13.9571657180786</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8496656417847</t>
+    <t xml:space="preserve">13.8496646881104</t>
   </si>
   <si>
     <t xml:space="preserve">13.9750833511353</t>
@@ -2471,7 +2471,7 @@
     <t xml:space="preserve">13.5450801849365</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4734125137329</t>
+    <t xml:space="preserve">13.4734134674072</t>
   </si>
   <si>
     <t xml:space="preserve">13.1867456436157</t>
@@ -2486,28 +2486,28 @@
     <t xml:space="preserve">12.7029914855957</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8429870605469</t>
+    <t xml:space="preserve">11.8429861068726</t>
   </si>
   <si>
     <t xml:space="preserve">11.7892360687256</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6817350387573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0759038925171</t>
+    <t xml:space="preserve">11.6817359924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0759048461914</t>
   </si>
   <si>
     <t xml:space="preserve">11.5742359161377</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2158994674683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3592338562012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4309015274048</t>
+    <t xml:space="preserve">11.2159004211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3592348098755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4309024810791</t>
   </si>
   <si>
     <t xml:space="preserve">11.3054838180542</t>
@@ -2516,13 +2516,13 @@
     <t xml:space="preserve">11.2875671386719</t>
   </si>
   <si>
-    <t xml:space="preserve">11.683783531189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5179262161255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2783517837524</t>
+    <t xml:space="preserve">11.6837844848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5179252624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2783527374268</t>
   </si>
   <si>
     <t xml:space="preserve">11.1493520736694</t>
@@ -2534,7 +2534,7 @@
     <t xml:space="preserve">11.0756378173828</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9970722198486</t>
+    <t xml:space="preserve">11.9970712661743</t>
   </si>
   <si>
     <t xml:space="preserve">12.052357673645</t>
@@ -2543,7 +2543,7 @@
     <t xml:space="preserve">12.2735013961792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2182149887085</t>
+    <t xml:space="preserve">12.2182159423828</t>
   </si>
   <si>
     <t xml:space="preserve">12.4025020599365</t>
@@ -2555,7 +2555,7 @@
     <t xml:space="preserve">12.0707864761353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1629285812378</t>
+    <t xml:space="preserve">12.1629295349121</t>
   </si>
   <si>
     <t xml:space="preserve">12.1260719299316</t>
@@ -2570,13 +2570,13 @@
     <t xml:space="preserve">11.7759265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8312129974365</t>
+    <t xml:space="preserve">11.8312139511108</t>
   </si>
   <si>
     <t xml:space="preserve">11.9786424636841</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7206411361694</t>
+    <t xml:space="preserve">11.7206420898438</t>
   </si>
   <si>
     <t xml:space="preserve">11.868070602417</t>
@@ -2591,7 +2591,7 @@
     <t xml:space="preserve">11.4442110061646</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3520669937134</t>
+    <t xml:space="preserve">11.3520679473877</t>
   </si>
   <si>
     <t xml:space="preserve">11.3704957962036</t>
@@ -2609,7 +2609,7 @@
     <t xml:space="preserve">11.7022123336792</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5732116699219</t>
+    <t xml:space="preserve">11.5732126235962</t>
   </si>
   <si>
     <t xml:space="preserve">11.481068611145</t>
@@ -2618,7 +2618,7 @@
     <t xml:space="preserve">11.296781539917</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3152093887329</t>
+    <t xml:space="preserve">11.3152103424072</t>
   </si>
   <si>
     <t xml:space="preserve">11.5547828674316</t>
@@ -2627,7 +2627,7 @@
     <t xml:space="preserve">11.4257822036743</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3336381912231</t>
+    <t xml:space="preserve">11.3336391448975</t>
   </si>
   <si>
     <t xml:space="preserve">11.3889245986938</t>
@@ -2636,7 +2636,7 @@
     <t xml:space="preserve">11.4626398086548</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7943553924561</t>
+    <t xml:space="preserve">11.7943563461304</t>
   </si>
   <si>
     <t xml:space="preserve">12.1076431274414</t>
@@ -2666,7 +2666,7 @@
     <t xml:space="preserve">13.0290775299072</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2502222061157</t>
+    <t xml:space="preserve">13.2502212524414</t>
   </si>
   <si>
     <t xml:space="preserve">13.4160804748535</t>
@@ -2681,7 +2681,7 @@
     <t xml:space="preserve">12.6420755386353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8816480636597</t>
+    <t xml:space="preserve">12.8816471099854</t>
   </si>
   <si>
     <t xml:space="preserve">12.9185056686401</t>
@@ -2690,7 +2690,7 @@
     <t xml:space="preserve">13.194935798645</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1580772399902</t>
+    <t xml:space="preserve">13.1580781936646</t>
   </si>
   <si>
     <t xml:space="preserve">12.8079328536987</t>
@@ -2705,7 +2705,7 @@
     <t xml:space="preserve">12.5499315261841</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0843629837036</t>
+    <t xml:space="preserve">13.0843639373779</t>
   </si>
   <si>
     <t xml:space="preserve">13.3423643112183</t>
@@ -2723,13 +2723,13 @@
     <t xml:space="preserve">13.1027917861938</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3607940673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2133646011353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5266513824463</t>
+    <t xml:space="preserve">13.3607931137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2133636474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5266523361206</t>
   </si>
   <si>
     <t xml:space="preserve">13.6003665924072</t>
@@ -2747,28 +2747,28 @@
     <t xml:space="preserve">13.7846536636353</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0610828399658</t>
+    <t xml:space="preserve">14.0610837936401</t>
   </si>
   <si>
     <t xml:space="preserve">14.2637987136841</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5402297973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6139440536499</t>
+    <t xml:space="preserve">14.540228843689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6139430999756</t>
   </si>
   <si>
     <t xml:space="preserve">15.3695201873779</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5353784561157</t>
+    <t xml:space="preserve">15.53537940979</t>
   </si>
   <si>
     <t xml:space="preserve">15.6275205612183</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5722360610962</t>
+    <t xml:space="preserve">15.5722341537476</t>
   </si>
   <si>
     <t xml:space="preserve">15.4063768386841</t>
@@ -2780,34 +2780,34 @@
     <t xml:space="preserve">15.295804977417</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2773761749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4616651535034</t>
+    <t xml:space="preserve">15.2773771286011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4616641998291</t>
   </si>
   <si>
     <t xml:space="preserve">15.6459493637085</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4432344436646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6643781661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7012376785278</t>
+    <t xml:space="preserve">15.4432353973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.664379119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7012367248535</t>
   </si>
   <si>
     <t xml:space="preserve">15.6090936660767</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3326606750488</t>
+    <t xml:space="preserve">15.3326616287231</t>
   </si>
   <si>
     <t xml:space="preserve">15.2036619186401</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1668033599854</t>
+    <t xml:space="preserve">15.1668043136597</t>
   </si>
   <si>
     <t xml:space="preserve">14.8535175323486</t>
@@ -2828,22 +2828,22 @@
     <t xml:space="preserve">15.8302373886108</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7196645736694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3879489898682</t>
+    <t xml:space="preserve">15.7196636199951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3879499435425</t>
   </si>
   <si>
     <t xml:space="preserve">15.5906648635864</t>
   </si>
   <si>
-    <t xml:space="preserve">15.682806968689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7565221786499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7380933761597</t>
+    <t xml:space="preserve">15.6828079223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7565231323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.738094329834</t>
   </si>
   <si>
     <t xml:space="preserve">15.1483764648438</t>
@@ -2855,7 +2855,7 @@
     <t xml:space="preserve">15.1299476623535</t>
   </si>
   <si>
-    <t xml:space="preserve">15.480092048645</t>
+    <t xml:space="preserve">15.4800910949707</t>
   </si>
   <si>
     <t xml:space="preserve">15.9223804473877</t>
@@ -2867,22 +2867,22 @@
     <t xml:space="preserve">16.0882377624512</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7749509811401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.867094039917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7109394073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6556529998779</t>
+    <t xml:space="preserve">15.7749519348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8670930862427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7109384536743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6556520462036</t>
   </si>
   <si>
     <t xml:space="preserve">13.6372241973877</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1347990036011</t>
+    <t xml:space="preserve">14.1347980499268</t>
   </si>
   <si>
     <t xml:space="preserve">14.4480857849121</t>
@@ -2894,7 +2894,7 @@
     <t xml:space="preserve">14.0242261886597</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0795125961304</t>
+    <t xml:space="preserve">14.0795116424561</t>
   </si>
   <si>
     <t xml:space="preserve">14.0057973861694</t>
@@ -2915,7 +2915,7 @@
     <t xml:space="preserve">13.4897947311401</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6187953948975</t>
+    <t xml:space="preserve">13.6187944412231</t>
   </si>
   <si>
     <t xml:space="preserve">12.8263626098633</t>
@@ -2927,7 +2927,7 @@
     <t xml:space="preserve">13.2686500549316</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9369335174561</t>
+    <t xml:space="preserve">12.9369344711304</t>
   </si>
   <si>
     <t xml:space="preserve">12.9000768661499</t>
@@ -2936,10 +2936,10 @@
     <t xml:space="preserve">12.9922199249268</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0475053787231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6973600387573</t>
+    <t xml:space="preserve">13.0475063323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6973609924316</t>
   </si>
   <si>
     <t xml:space="preserve">12.6052179336548</t>
@@ -2951,7 +2951,7 @@
     <t xml:space="preserve">12.4209308624268</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4762172698975</t>
+    <t xml:space="preserve">12.4762163162231</t>
   </si>
   <si>
     <t xml:space="preserve">12.6236457824707</t>
@@ -3462,6 +3462,9 @@
   </si>
   <si>
     <t xml:space="preserve">18.5200004577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5400009155273</t>
   </si>
 </sst>
 </file>
@@ -68696,7 +68699,7 @@
     </row>
     <row r="2497">
       <c r="A2497" s="1" t="n">
-        <v>45954.6493981481</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B2497" t="n">
         <v>25166</v>
@@ -68717,6 +68720,32 @@
         <v>1149</v>
       </c>
       <c r="H2497" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2498">
+      <c r="A2498" s="1" t="n">
+        <v>45957.6909722222</v>
+      </c>
+      <c r="B2498" t="n">
+        <v>15401</v>
+      </c>
+      <c r="C2498" t="n">
+        <v>18.6800003051758</v>
+      </c>
+      <c r="D2498" t="n">
+        <v>18.3999996185303</v>
+      </c>
+      <c r="E2498" t="n">
+        <v>18.6000003814697</v>
+      </c>
+      <c r="F2498" t="n">
+        <v>18.5400009155273</v>
+      </c>
+      <c r="G2498" t="s">
+        <v>1150</v>
+      </c>
+      <c r="H2498" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ORS.MI.xlsx
+++ b/data/ORS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="1151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1152" uniqueCount="1152">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,52 +44,52 @@
     <t xml:space="preserve">ORS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98275899887085</t>
+    <t xml:space="preserve">7.98275995254517</t>
   </si>
   <si>
     <t xml:space="preserve">8.06380176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94223642349243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82472467422485</t>
+    <t xml:space="preserve">7.94223785400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82472515106201</t>
   </si>
   <si>
     <t xml:space="preserve">7.93818521499634</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90171670913696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03948879241943</t>
+    <t xml:space="preserve">7.90171527862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03948974609375</t>
   </si>
   <si>
     <t xml:space="preserve">7.92602968215942</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86119413375854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82067155838013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93413400650024</t>
+    <t xml:space="preserve">7.86119365692139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82067203521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93413352966309</t>
   </si>
   <si>
     <t xml:space="preserve">8.02328205108643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08811378479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14484691619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69910764694214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80446481704712</t>
+    <t xml:space="preserve">8.08811569213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14484596252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69910669326782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80446434020996</t>
   </si>
   <si>
     <t xml:space="preserve">7.97465467453003</t>
@@ -104,16 +104,16 @@
     <t xml:space="preserve">7.79230737686157</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82877779006958</t>
+    <t xml:space="preserve">7.82877731323242</t>
   </si>
   <si>
     <t xml:space="preserve">8.34745311737061</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84093523025513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90981912612915</t>
+    <t xml:space="preserve">7.84093236923218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90982103347778</t>
   </si>
   <si>
     <t xml:space="preserve">7.85714101791382</t>
@@ -122,22 +122,22 @@
     <t xml:space="preserve">7.7801513671875</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8449854850769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97870588302612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88550710678101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95034265518188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00301933288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0192289352417</t>
+    <t xml:space="preserve">7.84498596191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97870635986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88550662994385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95034122467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00302124023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01922798156738</t>
   </si>
   <si>
     <t xml:space="preserve">7.91792440414429</t>
@@ -146,13 +146,13 @@
     <t xml:space="preserve">8.1002721786499</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10432243347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18536758422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20157527923584</t>
+    <t xml:space="preserve">8.104323387146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1853666305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20157623291016</t>
   </si>
   <si>
     <t xml:space="preserve">8.11242866516113</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">8.07595825195312</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03138446807861</t>
+    <t xml:space="preserve">8.03138542175293</t>
   </si>
   <si>
     <t xml:space="preserve">8.09621906280518</t>
@@ -170,133 +170,133 @@
     <t xml:space="preserve">8.17726230621338</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05569839477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12053203582764</t>
+    <t xml:space="preserve">8.05569744110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12053298950195</t>
   </si>
   <si>
     <t xml:space="preserve">8.2583065032959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42039203643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67162704467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55816650390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42849826812744</t>
+    <t xml:space="preserve">8.4203929901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6716251373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55816555023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42849731445312</t>
   </si>
   <si>
     <t xml:space="preserve">8.52429008483887</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45921897888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50802040100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60562896728516</t>
+    <t xml:space="preserve">8.45921993255615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50802230834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60562801361084</t>
   </si>
   <si>
     <t xml:space="preserve">8.5324239730835</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61376285552979</t>
+    <t xml:space="preserve">8.61376190185547</t>
   </si>
   <si>
     <t xml:space="preserve">8.67069911956787</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87404727935791</t>
+    <t xml:space="preserve">8.87404537200928</t>
   </si>
   <si>
     <t xml:space="preserve">8.79270648956299</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90657997131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86591243743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94725227355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93911838531494</t>
+    <t xml:space="preserve">8.90658092498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86591339111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94725036621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93911647796631</t>
   </si>
   <si>
     <t xml:space="preserve">8.78457355499268</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74390506744385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91471385955811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92284965515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10992813110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.077392578125</t>
+    <t xml:space="preserve">8.74390411376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91471576690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92284870147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10992908477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07739353179932</t>
   </si>
   <si>
     <t xml:space="preserve">9.11806297302246</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13433074951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15059661865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15873146057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7357702255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6788330078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8577766418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72763633728027</t>
+    <t xml:space="preserve">9.1343297958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15059852600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15873241424561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73576927185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67883205413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85777759552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72763538360596</t>
   </si>
   <si>
     <t xml:space="preserve">8.70323467254639</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66256523132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69510173797607</t>
+    <t xml:space="preserve">8.66256618499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69510078430176</t>
   </si>
   <si>
     <t xml:space="preserve">8.62189674377441</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80084228515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77643966674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68696784973145</t>
+    <t xml:space="preserve">8.80084133148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77643871307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68696689605713</t>
   </si>
   <si>
     <t xml:space="preserve">8.54869174957275</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54055786132812</t>
+    <t xml:space="preserve">8.54055690765381</t>
   </si>
   <si>
     <t xml:space="preserve">8.58122730255127</t>
@@ -305,40 +305,40 @@
     <t xml:space="preserve">8.46735286712646</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51615524291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49988651275635</t>
+    <t xml:space="preserve">8.51615715026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49988746643066</t>
   </si>
   <si>
     <t xml:space="preserve">8.45108413696289</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63003158569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80897617340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89031314849854</t>
+    <t xml:space="preserve">8.63002967834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80897521972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89031505584717</t>
   </si>
   <si>
     <t xml:space="preserve">8.93098449707031</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96351718902588</t>
+    <t xml:space="preserve">8.9635181427002</t>
   </si>
   <si>
     <t xml:space="preserve">9.05299091339111</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30514144897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1017951965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19126605987549</t>
+    <t xml:space="preserve">9.30514049530029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10179424285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19126510620117</t>
   </si>
   <si>
     <t xml:space="preserve">9.35394287109375</t>
@@ -347,34 +347,34 @@
     <t xml:space="preserve">9.4759521484375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54915523529053</t>
+    <t xml:space="preserve">9.54915618896484</t>
   </si>
   <si>
     <t xml:space="preserve">9.58982563018799</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66303157806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71996688842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85824298858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0046539306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.240535736084</t>
+    <t xml:space="preserve">9.66303253173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71996784210205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85824203491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0046529769897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2405366897583</t>
   </si>
   <si>
     <t xml:space="preserve">10.2486686706543</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3381414413452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5984268188477</t>
+    <t xml:space="preserve">10.3381404876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5984258651733</t>
   </si>
   <si>
     <t xml:space="preserve">10.4276151657104</t>
@@ -386,7 +386,7 @@
     <t xml:space="preserve">10.5252199172974</t>
   </si>
   <si>
-    <t xml:space="preserve">10.460150718689</t>
+    <t xml:space="preserve">10.460147857666</t>
   </si>
   <si>
     <t xml:space="preserve">10.5658903121948</t>
@@ -401,37 +401,37 @@
     <t xml:space="preserve">10.9807157516479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8749771118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6553621292114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.679762840271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5740232467651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5170860290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5414886474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5577573776245</t>
+    <t xml:space="preserve">10.8749761581421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6553630828857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6797637939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5740242004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5170869827271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5414876937866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5577564239502</t>
   </si>
   <si>
     <t xml:space="preserve">10.5089521408081</t>
   </si>
   <si>
-    <t xml:space="preserve">10.818039894104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6878976821899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.761100769043</t>
+    <t xml:space="preserve">10.8180389404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6878967285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7611026763916</t>
   </si>
   <si>
     <t xml:space="preserve">10.6472282409668</t>
@@ -440,7 +440,7 @@
     <t xml:space="preserve">10.899377822876</t>
   </si>
   <si>
-    <t xml:space="preserve">10.883111000061</t>
+    <t xml:space="preserve">10.8831100463867</t>
   </si>
   <si>
     <t xml:space="preserve">10.6716299057007</t>
@@ -449,46 +449,46 @@
     <t xml:space="preserve">10.736701965332</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0051193237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0213851928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.184063911438</t>
+    <t xml:space="preserve">11.0051183700562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0213861465454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1840648651123</t>
   </si>
   <si>
     <t xml:space="preserve">11.4036779403687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3955450057983</t>
+    <t xml:space="preserve">11.3955430984497</t>
   </si>
   <si>
     <t xml:space="preserve">11.3386068344116</t>
   </si>
   <si>
-    <t xml:space="preserve">11.322338104248</t>
+    <t xml:space="preserve">11.3223400115967</t>
   </si>
   <si>
     <t xml:space="preserve">11.3304738998413</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3630084991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0783233642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.606559753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8424406051636</t>
+    <t xml:space="preserve">11.3630094528198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0783243179321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6065587997437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8424425125122</t>
   </si>
   <si>
     <t xml:space="preserve">10.8505744934082</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6390943527222</t>
+    <t xml:space="preserve">10.6390953063965</t>
   </si>
   <si>
     <t xml:space="preserve">10.4113464355469</t>
@@ -497,31 +497,31 @@
     <t xml:space="preserve">10.2080011367798</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2730712890625</t>
+    <t xml:space="preserve">10.2730703353882</t>
   </si>
   <si>
     <t xml:space="preserve">10.232400894165</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3218727111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3706760406494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3300075531006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3056058883667</t>
+    <t xml:space="preserve">10.3218746185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3706769943237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3300085067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3056049346924</t>
   </si>
   <si>
     <t xml:space="preserve">10.2568035125732</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1835966110229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4845514297485</t>
+    <t xml:space="preserve">10.1835994720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4845504760742</t>
   </si>
   <si>
     <t xml:space="preserve">10.3625431060791</t>
@@ -530,73 +530,73 @@
     <t xml:space="preserve">10.4438810348511</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8587083816528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9237794876099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.037654876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0620574951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1027240753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1433954238892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1759281158447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1352615356445</t>
+    <t xml:space="preserve">10.8587074279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9237804412842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0376529693604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0620546340942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1027250289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1433944702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.175929069519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1352605819702</t>
   </si>
   <si>
     <t xml:space="preserve">11.0701904296875</t>
   </si>
   <si>
-    <t xml:space="preserve">11.118992805481</t>
+    <t xml:space="preserve">11.1189937591553</t>
   </si>
   <si>
     <t xml:space="preserve">11.1515274047852</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2247323989868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0457878112793</t>
+    <t xml:space="preserve">11.2247333526611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.045786857605</t>
   </si>
   <si>
     <t xml:space="preserve">10.5008182525635</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1347942352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36161231994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01998996734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10946178436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3941478729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21520328521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33721160888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3128080368042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18266677856445</t>
+    <t xml:space="preserve">10.1347961425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36161136627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01999092102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10946273803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39414691925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21520233154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33720970153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31280994415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18266773223877</t>
   </si>
   <si>
     <t xml:space="preserve">8.34534549713135</t>
@@ -614,88 +614,88 @@
     <t xml:space="preserve">8.76017093658447</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29654216766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25587177276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17453289031982</t>
+    <t xml:space="preserve">8.29654121398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25587272644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17453384399414</t>
   </si>
   <si>
     <t xml:space="preserve">8.19080066680908</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23147106170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2802734375</t>
+    <t xml:space="preserve">8.23147010803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28027248382568</t>
   </si>
   <si>
     <t xml:space="preserve">8.14199829101562</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15826606750488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16640090942383</t>
+    <t xml:space="preserve">8.15826511383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16639995574951</t>
   </si>
   <si>
     <t xml:space="preserve">8.12166309356689</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05252647399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89798307418823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85731220245361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93051671981812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9061164855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93865156173706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84917879104614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80850982666016</t>
+    <t xml:space="preserve">8.05252552032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89798259735107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85731410980225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93051862716675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90611553192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93865251541138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8491792678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.808509349823</t>
   </si>
   <si>
     <t xml:space="preserve">7.62956476211548</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57262802124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48315477371216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66616582870483</t>
+    <t xml:space="preserve">7.57262754440308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48315525054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66616678237915</t>
   </si>
   <si>
     <t xml:space="preserve">7.60516309738159</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54009342193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52382469177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47908735275269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61329698562622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54822635650635</t>
+    <t xml:space="preserve">7.54009294509888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52382326126099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47908782958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61329746246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54822587966919</t>
   </si>
   <si>
     <t xml:space="preserve">7.56449365615845</t>
@@ -704,97 +704,97 @@
     <t xml:space="preserve">7.5075569152832</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46688556671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4912896156311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4994215965271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31234407424927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27980661392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3774151802063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38554954528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36928176879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32047700881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34487915039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28794240951538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04392623901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15779972076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39368295669556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42621803283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40181684494019</t>
+    <t xml:space="preserve">7.46688652038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49129009246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49942207336426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31234550476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27980899810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37741470336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38554859161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36928129196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32047748565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34487962722778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28794193267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04392576217651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15780115127563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3936824798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42621850967407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40181636810303</t>
   </si>
   <si>
     <t xml:space="preserve">7.3042106628418</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3611478805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20660352706909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35301303863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33674621582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27167367935181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23100471496582</t>
+    <t xml:space="preserve">7.36114740371704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20660400390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35301351547241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33674573898315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27167415618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23100519180298</t>
   </si>
   <si>
     <t xml:space="preserve">7.32861137390137</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26354122161865</t>
+    <t xml:space="preserve">7.26354074478149</t>
   </si>
   <si>
     <t xml:space="preserve">7.23913955688477</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22287178039551</t>
+    <t xml:space="preserve">7.22287225723267</t>
   </si>
   <si>
     <t xml:space="preserve">7.24727296829224</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44248628616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25540733337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18220233917236</t>
+    <t xml:space="preserve">7.44248580932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25540781021118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18220186233521</t>
   </si>
   <si>
     <t xml:space="preserve">7.29607582092285</t>
@@ -809,13 +809,13 @@
     <t xml:space="preserve">7.0520601272583</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07646131515503</t>
+    <t xml:space="preserve">7.0764627456665</t>
   </si>
   <si>
     <t xml:space="preserve">7.0357928276062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01952505111694</t>
+    <t xml:space="preserve">7.01952457427979</t>
   </si>
   <si>
     <t xml:space="preserve">6.87311458587646</t>
@@ -824,37 +824,37 @@
     <t xml:space="preserve">6.677903175354</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85124683380127</t>
+    <t xml:space="preserve">6.85124731063843</t>
   </si>
   <si>
     <t xml:space="preserve">6.93379211425781</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26397275924683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14841032028198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0988826751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18142795562744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16491842269897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14015579223633</t>
+    <t xml:space="preserve">7.26397371292114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14840936660767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09888315200806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18142890930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16491937637329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14015626907349</t>
   </si>
   <si>
     <t xml:space="preserve">7.21444606781006</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1731743812561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97506427764893</t>
+    <t xml:space="preserve">7.17317390441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97506475448608</t>
   </si>
   <si>
     <t xml:space="preserve">6.84299325942993</t>
@@ -863,7 +863,7 @@
     <t xml:space="preserve">6.60361242294312</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62012147903442</t>
+    <t xml:space="preserve">6.62012100219727</t>
   </si>
   <si>
     <t xml:space="preserve">6.67790222167969</t>
@@ -875,28 +875,28 @@
     <t xml:space="preserve">6.54583024978638</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31470394134521</t>
+    <t xml:space="preserve">6.31470441818237</t>
   </si>
   <si>
     <t xml:space="preserve">6.32295846939087</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34772300720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38073968887329</t>
+    <t xml:space="preserve">6.34772205352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38074016571045</t>
   </si>
   <si>
     <t xml:space="preserve">6.3972487449646</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4715404510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28168535232544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22390413284302</t>
+    <t xml:space="preserve">6.47153997421265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2816858291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22390365600586</t>
   </si>
   <si>
     <t xml:space="preserve">6.09183168411255</t>
@@ -908,10 +908,10 @@
     <t xml:space="preserve">5.9597601890564</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99277782440186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20739555358887</t>
+    <t xml:space="preserve">5.9927773475647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20739507675171</t>
   </si>
   <si>
     <t xml:space="preserve">6.14135980606079</t>
@@ -920,28 +920,28 @@
     <t xml:space="preserve">6.19088649749756</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14961338043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07532405853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25692272186279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00928783416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98452281951904</t>
+    <t xml:space="preserve">6.14961385726929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07532358169556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25692367553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00928735733032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9845232963562</t>
   </si>
   <si>
     <t xml:space="preserve">6.12484979629517</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13310480117798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2734317779541</t>
+    <t xml:space="preserve">6.13310432434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27343130111694</t>
   </si>
   <si>
     <t xml:space="preserve">6.44677591323853</t>
@@ -953,67 +953,67 @@
     <t xml:space="preserve">6.51281213760376</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3642315864563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2404146194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21564960479736</t>
+    <t xml:space="preserve">6.36423110961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24041366577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21565008163452</t>
   </si>
   <si>
     <t xml:space="preserve">6.23215961456299</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24866771697998</t>
+    <t xml:space="preserve">6.24866819381714</t>
   </si>
   <si>
     <t xml:space="preserve">6.11659574508667</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1083402633667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05055904388428</t>
+    <t xml:space="preserve">6.10834074020386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05055952072144</t>
   </si>
   <si>
     <t xml:space="preserve">5.89372396469116</t>
   </si>
   <si>
-    <t xml:space="preserve">5.778160572052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6956148147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79466962814331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80292367935181</t>
+    <t xml:space="preserve">5.77816104888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69561529159546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79466915130615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80292320251465</t>
   </si>
   <si>
     <t xml:space="preserve">5.82768774032593</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78641557693481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73688745498657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85245180130005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29819488525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1826319694519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15786790847778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03404998779297</t>
+    <t xml:space="preserve">5.78641510009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73688793182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85245132446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29819536209106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18263244628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15786838531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03405046463013</t>
   </si>
   <si>
     <t xml:space="preserve">6.08357763290405</t>
@@ -1022,70 +1022,70 @@
     <t xml:space="preserve">5.81943321228027</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91848707199097</t>
+    <t xml:space="preserve">5.91848659515381</t>
   </si>
   <si>
     <t xml:space="preserve">5.86070537567139</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76165151596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75339651107788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81117868423462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70387029647827</t>
+    <t xml:space="preserve">5.76165199279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75339698791504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8111777305603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70387077331543</t>
   </si>
   <si>
     <t xml:space="preserve">5.74514245986938</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83594179153442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71212434768677</t>
+    <t xml:space="preserve">5.83594226837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71212482452393</t>
   </si>
   <si>
     <t xml:space="preserve">5.84419679641724</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94325065612793</t>
+    <t xml:space="preserve">5.94325113296509</t>
   </si>
   <si>
     <t xml:space="preserve">5.96801424026489</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87721538543701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88546991348267</t>
+    <t xml:space="preserve">5.8772144317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88546943664551</t>
   </si>
   <si>
     <t xml:space="preserve">5.93499612808228</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02579593658447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0670690536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38899421691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19914102554321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04230451583862</t>
+    <t xml:space="preserve">6.02579641342163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06706857681274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3889946937561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19914054870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04230499267578</t>
   </si>
   <si>
     <t xml:space="preserve">6.05881452560425</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95150518417358</t>
+    <t xml:space="preserve">5.95150566101074</t>
   </si>
   <si>
     <t xml:space="preserve">6.17437744140625</t>
@@ -1097,7 +1097,7 @@
     <t xml:space="preserve">6.29349803924561</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25993204116821</t>
+    <t xml:space="preserve">6.25993251800537</t>
   </si>
   <si>
     <t xml:space="preserve">6.20958423614502</t>
@@ -1109,25 +1109,25 @@
     <t xml:space="preserve">6.10888910293579</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07532358169556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14245319366455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05854034423828</t>
+    <t xml:space="preserve">6.0753231048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14245367050171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05854082107544</t>
   </si>
   <si>
     <t xml:space="preserve">6.02497529983521</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97462749481201</t>
+    <t xml:space="preserve">5.97462701797485</t>
   </si>
   <si>
     <t xml:space="preserve">5.95784425735474</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15923738479614</t>
+    <t xml:space="preserve">6.15923690795898</t>
   </si>
   <si>
     <t xml:space="preserve">6.12567186355591</t>
@@ -1136,7 +1136,7 @@
     <t xml:space="preserve">6.1928014755249</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42775869369507</t>
+    <t xml:space="preserve">6.42775917053223</t>
   </si>
   <si>
     <t xml:space="preserve">6.71306467056274</t>
@@ -1145,16 +1145,16 @@
     <t xml:space="preserve">6.64593458175659</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69628238677979</t>
+    <t xml:space="preserve">6.69628190994263</t>
   </si>
   <si>
     <t xml:space="preserve">6.78019523620605</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72984743118286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.629150390625</t>
+    <t xml:space="preserve">6.7298469543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62915086746216</t>
   </si>
   <si>
     <t xml:space="preserve">6.56202030181885</t>
@@ -1169,7 +1169,7 @@
     <t xml:space="preserve">6.66271686553955</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57880353927612</t>
+    <t xml:space="preserve">6.57880306243896</t>
   </si>
   <si>
     <t xml:space="preserve">6.37741088867188</t>
@@ -1181,13 +1181,13 @@
     <t xml:space="preserve">6.22636699676514</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36062908172607</t>
+    <t xml:space="preserve">6.36062955856323</t>
   </si>
   <si>
     <t xml:space="preserve">5.67253875732422</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55506038665771</t>
+    <t xml:space="preserve">5.55506086349487</t>
   </si>
   <si>
     <t xml:space="preserve">5.68932247161865</t>
@@ -1199,13 +1199,13 @@
     <t xml:space="preserve">5.53827810287476</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43758249282837</t>
+    <t xml:space="preserve">5.43758201599121</t>
   </si>
   <si>
     <t xml:space="preserve">5.45436525344849</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60540819168091</t>
+    <t xml:space="preserve">5.60540866851807</t>
   </si>
   <si>
     <t xml:space="preserve">5.5214958190918</t>
@@ -1220,13 +1220,13 @@
     <t xml:space="preserve">5.35366868972778</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37045097351074</t>
+    <t xml:space="preserve">5.3704514503479</t>
   </si>
   <si>
     <t xml:space="preserve">5.42079877853394</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28653860092163</t>
+    <t xml:space="preserve">5.28653812408447</t>
   </si>
   <si>
     <t xml:space="preserve">5.30332088470459</t>
@@ -1241,13 +1241,13 @@
     <t xml:space="preserve">5.32010364532471</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65575695037842</t>
+    <t xml:space="preserve">5.65575647354126</t>
   </si>
   <si>
     <t xml:space="preserve">5.75645303726196</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70610475540161</t>
+    <t xml:space="preserve">5.70610427856445</t>
   </si>
   <si>
     <t xml:space="preserve">5.72288703918457</t>
@@ -1256,7 +1256,7 @@
     <t xml:space="preserve">5.73967027664185</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6389741897583</t>
+    <t xml:space="preserve">5.63897466659546</t>
   </si>
   <si>
     <t xml:space="preserve">5.57184410095215</t>
@@ -1265,7 +1265,7 @@
     <t xml:space="preserve">5.18584156036377</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20262575149536</t>
+    <t xml:space="preserve">5.20262479782104</t>
   </si>
   <si>
     <t xml:space="preserve">5.21940803527832</t>
@@ -1274,10 +1274,10 @@
     <t xml:space="preserve">5.16905975341797</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13549327850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1019287109375</t>
+    <t xml:space="preserve">5.13549375534058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10192918777466</t>
   </si>
   <si>
     <t xml:space="preserve">4.9508843421936</t>
@@ -1289,7 +1289,7 @@
     <t xml:space="preserve">5.15227699279785</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11871194839478</t>
+    <t xml:space="preserve">5.11871147155762</t>
   </si>
   <si>
     <t xml:space="preserve">5.06836318969727</t>
@@ -1298,10 +1298,10 @@
     <t xml:space="preserve">5.08514595031738</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23618984222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25297260284424</t>
+    <t xml:space="preserve">5.23619031906128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2529730796814</t>
   </si>
   <si>
     <t xml:space="preserve">5.33688640594482</t>
@@ -1310,10 +1310,10 @@
     <t xml:space="preserve">5.79001808166504</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77323484420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58862638473511</t>
+    <t xml:space="preserve">5.77323532104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58862590789795</t>
   </si>
   <si>
     <t xml:space="preserve">4.81662321090698</t>
@@ -1325,10 +1325,10 @@
     <t xml:space="preserve">4.59844875335693</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36349201202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31314420700073</t>
+    <t xml:space="preserve">4.36349248886108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31314373016357</t>
   </si>
   <si>
     <t xml:space="preserve">4.19566488265991</t>
@@ -1337,13 +1337,13 @@
     <t xml:space="preserve">4.11175203323364</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02783918380737</t>
+    <t xml:space="preserve">4.02783870697021</t>
   </si>
   <si>
     <t xml:space="preserve">4.17049074172974</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06979560852051</t>
+    <t xml:space="preserve">4.06979608535767</t>
   </si>
   <si>
     <t xml:space="preserve">4.12014293670654</t>
@@ -1355,10 +1355,10 @@
     <t xml:space="preserve">4.17888164520264</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04462051391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15370798110962</t>
+    <t xml:space="preserve">4.04462099075317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15370845794678</t>
   </si>
   <si>
     <t xml:space="preserve">4.26279640197754</t>
@@ -1370,25 +1370,25 @@
     <t xml:space="preserve">4.14531803131104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99427223205566</t>
+    <t xml:space="preserve">3.99427318572998</t>
   </si>
   <si>
     <t xml:space="preserve">4.09496927261353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98588180541992</t>
+    <t xml:space="preserve">3.98588132858276</t>
   </si>
   <si>
     <t xml:space="preserve">4.27957820892334</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22922992706299</t>
+    <t xml:space="preserve">4.22923040390015</t>
   </si>
   <si>
     <t xml:space="preserve">4.21244764328003</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03622961044312</t>
+    <t xml:space="preserve">4.03623008728027</t>
   </si>
   <si>
     <t xml:space="preserve">4.12877893447876</t>
@@ -1400,7 +1400,7 @@
     <t xml:space="preserve">4.07770156860352</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00108432769775</t>
+    <t xml:space="preserve">4.00108480453491</t>
   </si>
   <si>
     <t xml:space="preserve">4.20539569854736</t>
@@ -1409,10 +1409,10 @@
     <t xml:space="preserve">4.37565422058105</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21390867233276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22242116928101</t>
+    <t xml:space="preserve">4.21390914916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22242164611816</t>
   </si>
   <si>
     <t xml:space="preserve">4.25647354125977</t>
@@ -1427,13 +1427,13 @@
     <t xml:space="preserve">4.30755090713501</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23944759368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35862874984741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5118613243103</t>
+    <t xml:space="preserve">4.23944711685181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35862827301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51186227798462</t>
   </si>
   <si>
     <t xml:space="preserve">5.5334153175354</t>
@@ -1445,10 +1445,10 @@
     <t xml:space="preserve">5.8909592628479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73772621154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55044078826904</t>
+    <t xml:space="preserve">5.73772573471069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5504412651062</t>
   </si>
   <si>
     <t xml:space="preserve">5.5844931602478</t>
@@ -1460,7 +1460,7 @@
     <t xml:space="preserve">5.41423416137695</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2610011100769</t>
+    <t xml:space="preserve">5.26100063323975</t>
   </si>
   <si>
     <t xml:space="preserve">5.48233795166016</t>
@@ -1469,7 +1469,7 @@
     <t xml:space="preserve">5.44828605651855</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6015191078186</t>
+    <t xml:space="preserve">5.60151863098145</t>
   </si>
   <si>
     <t xml:space="preserve">5.66962242126465</t>
@@ -1478,13 +1478,13 @@
     <t xml:space="preserve">5.51638984680176</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70367431640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32910442352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27802658081055</t>
+    <t xml:space="preserve">5.70367479324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32910490036011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27802705764771</t>
   </si>
   <si>
     <t xml:space="preserve">5.43126058578491</t>
@@ -1496,7 +1496,7 @@
     <t xml:space="preserve">5.2269492149353</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00561237335205</t>
+    <t xml:space="preserve">5.00561285018921</t>
   </si>
   <si>
     <t xml:space="preserve">4.95453500747681</t>
@@ -1505,7 +1505,7 @@
     <t xml:space="preserve">4.93750905990601</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05668973922729</t>
+    <t xml:space="preserve">5.05669021606445</t>
   </si>
   <si>
     <t xml:space="preserve">5.03966426849365</t>
@@ -1514,7 +1514,7 @@
     <t xml:space="preserve">4.97156095504761</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88643074035645</t>
+    <t xml:space="preserve">4.8864312171936</t>
   </si>
   <si>
     <t xml:space="preserve">5.02263879776001</t>
@@ -1523,10 +1523,10 @@
     <t xml:space="preserve">4.92048263549805</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9034571647644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.852379322052</t>
+    <t xml:space="preserve">4.90345764160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85237979888916</t>
   </si>
   <si>
     <t xml:space="preserve">4.86940479278564</t>
@@ -1538,22 +1538,22 @@
     <t xml:space="preserve">5.24397563934326</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36315679550171</t>
+    <t xml:space="preserve">5.36315631866455</t>
   </si>
   <si>
     <t xml:space="preserve">5.38018321990967</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20992374420166</t>
+    <t xml:space="preserve">5.2099232673645</t>
   </si>
   <si>
     <t xml:space="preserve">5.15884637832642</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10776805877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98858690261841</t>
+    <t xml:space="preserve">5.10776853561401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98858642578125</t>
   </si>
   <si>
     <t xml:space="preserve">5.0907416343689</t>
@@ -1565,7 +1565,7 @@
     <t xml:space="preserve">5.17587184906006</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14181995391846</t>
+    <t xml:space="preserve">5.1418194770813</t>
   </si>
   <si>
     <t xml:space="preserve">5.07371616363525</t>
@@ -1574,28 +1574,28 @@
     <t xml:space="preserve">4.68212080001831</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54591369628906</t>
+    <t xml:space="preserve">4.5459132194519</t>
   </si>
   <si>
     <t xml:space="preserve">4.59699106216431</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57996559143066</t>
+    <t xml:space="preserve">4.57996511459351</t>
   </si>
   <si>
     <t xml:space="preserve">4.63104295730591</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7842755317688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76725006103516</t>
+    <t xml:space="preserve">4.78427600860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.767249584198</t>
   </si>
   <si>
     <t xml:space="preserve">4.8183274269104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80130195617676</t>
+    <t xml:space="preserve">4.8013014793396</t>
   </si>
   <si>
     <t xml:space="preserve">5.39720869064331</t>
@@ -1607,7 +1607,7 @@
     <t xml:space="preserve">5.46531200408936</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4993634223938</t>
+    <t xml:space="preserve">5.49936389923096</t>
   </si>
   <si>
     <t xml:space="preserve">5.63557052612305</t>
@@ -1631,7 +1631,7 @@
     <t xml:space="preserve">6.33363246917725</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29958057403564</t>
+    <t xml:space="preserve">6.2995810508728</t>
   </si>
   <si>
     <t xml:space="preserve">6.35065841674805</t>
@@ -1649,7 +1649,7 @@
     <t xml:space="preserve">6.79333162307739</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15087509155273</t>
+    <t xml:space="preserve">7.15087461471558</t>
   </si>
   <si>
     <t xml:space="preserve">7.08277130126953</t>
@@ -1670,7 +1670,7 @@
     <t xml:space="preserve">6.75927972793579</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5379433631897</t>
+    <t xml:space="preserve">6.53794288635254</t>
   </si>
   <si>
     <t xml:space="preserve">6.72522783279419</t>
@@ -1679,40 +1679,40 @@
     <t xml:space="preserve">6.65712451934814</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91251277923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89548683166504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96359062194824</t>
+    <t xml:space="preserve">6.91251230239868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8954873085022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96359014511108</t>
   </si>
   <si>
     <t xml:space="preserve">7.17302179336548</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05085372924805</t>
+    <t xml:space="preserve">7.05085325241089</t>
   </si>
   <si>
     <t xml:space="preserve">7.12066411972046</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57443189620972</t>
+    <t xml:space="preserve">7.57443237304688</t>
   </si>
   <si>
     <t xml:space="preserve">7.97584199905396</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0281982421875</t>
+    <t xml:space="preserve">8.02819919586182</t>
   </si>
   <si>
     <t xml:space="preserve">8.0631046295166</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99329423904419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0107479095459</t>
+    <t xml:space="preserve">7.99329328536987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01074695587158</t>
   </si>
   <si>
     <t xml:space="preserve">7.94093799591064</t>
@@ -1727,7 +1727,7 @@
     <t xml:space="preserve">8.16782093048096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18527317047119</t>
+    <t xml:space="preserve">8.18527412414551</t>
   </si>
   <si>
     <t xml:space="preserve">8.34234619140625</t>
@@ -1742,7 +1742,7 @@
     <t xml:space="preserve">8.08055782318115</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20272445678711</t>
+    <t xml:space="preserve">8.20272541046143</t>
   </si>
   <si>
     <t xml:space="preserve">7.95838928222656</t>
@@ -1772,7 +1772,7 @@
     <t xml:space="preserve">8.72630405426025</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42960929870605</t>
+    <t xml:space="preserve">8.42961025238037</t>
   </si>
   <si>
     <t xml:space="preserve">8.28998947143555</t>
@@ -1787,13 +1787,13 @@
     <t xml:space="preserve">7.85367345809937</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41215705871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22017860412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44706249237061</t>
+    <t xml:space="preserve">8.41215801239014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22017765045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44706153869629</t>
   </si>
   <si>
     <t xml:space="preserve">8.3597993850708</t>
@@ -1802,19 +1802,19 @@
     <t xml:space="preserve">8.09800910949707</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23763084411621</t>
+    <t xml:space="preserve">8.23762989044189</t>
   </si>
   <si>
     <t xml:space="preserve">8.48196792602539</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62158870697021</t>
+    <t xml:space="preserve">8.6215877532959</t>
   </si>
   <si>
     <t xml:space="preserve">8.55177783966064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65649318695068</t>
+    <t xml:space="preserve">8.656494140625</t>
   </si>
   <si>
     <t xml:space="preserve">8.51687240600586</t>
@@ -1826,13 +1826,13 @@
     <t xml:space="preserve">8.49942016601562</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5692310333252</t>
+    <t xml:space="preserve">8.56923007965088</t>
   </si>
   <si>
     <t xml:space="preserve">9.99161815643311</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59893321990967</t>
+    <t xml:space="preserve">9.59893417358398</t>
   </si>
   <si>
     <t xml:space="preserve">9.77345943450928</t>
@@ -1844,10 +1844,10 @@
     <t xml:space="preserve">9.29351425170898</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46803951263428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55530166625977</t>
+    <t xml:space="preserve">9.46804046630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55530261993408</t>
   </si>
   <si>
     <t xml:space="preserve">9.64256572723389</t>
@@ -1859,7 +1859,7 @@
     <t xml:space="preserve">9.33714580535889</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94798564910889</t>
+    <t xml:space="preserve">9.9479866027832</t>
   </si>
   <si>
     <t xml:space="preserve">9.86072254180908</t>
@@ -1868,10 +1868,10 @@
     <t xml:space="preserve">10.5151968002319</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4279327392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5588283538818</t>
+    <t xml:space="preserve">10.4279317855835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5588274002075</t>
   </si>
   <si>
     <t xml:space="preserve">10.6024589538574</t>
@@ -1883,7 +1883,7 @@
     <t xml:space="preserve">10.7333545684814</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7769861221313</t>
+    <t xml:space="preserve">10.776985168457</t>
   </si>
   <si>
     <t xml:space="preserve">10.2970390319824</t>
@@ -1922,7 +1922,7 @@
     <t xml:space="preserve">11.6496152877808</t>
   </si>
   <si>
-    <t xml:space="preserve">11.562352180481</t>
+    <t xml:space="preserve">11.5623531341553</t>
   </si>
   <si>
     <t xml:space="preserve">11.7805099487305</t>
@@ -1931,13 +1931,13 @@
     <t xml:space="preserve">11.9114046096802</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9550361633301</t>
+    <t xml:space="preserve">11.9550352096558</t>
   </si>
   <si>
     <t xml:space="preserve">11.693247795105</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3040895462036</t>
+    <t xml:space="preserve">12.3040885925293</t>
   </si>
   <si>
     <t xml:space="preserve">12.2604570388794</t>
@@ -1946,7 +1946,7 @@
     <t xml:space="preserve">12.2168254852295</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3913507461548</t>
+    <t xml:space="preserve">12.3913516998291</t>
   </si>
   <si>
     <t xml:space="preserve">11.7368783950806</t>
@@ -1958,13 +1958,13 @@
     <t xml:space="preserve">11.6059837341309</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9515104293823</t>
+    <t xml:space="preserve">10.9515113830566</t>
   </si>
   <si>
     <t xml:space="preserve">12.0422992706299</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3005628585815</t>
+    <t xml:space="preserve">11.3005638122559</t>
   </si>
   <si>
     <t xml:space="preserve">11.3441953659058</t>
@@ -1976,10 +1976,10 @@
     <t xml:space="preserve">10.4715642929077</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9078807830811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4314575195312</t>
+    <t xml:space="preserve">10.9078798294067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4314584732056</t>
   </si>
   <si>
     <t xml:space="preserve">11.0387735366821</t>
@@ -1991,7 +1991,7 @@
     <t xml:space="preserve">11.7456045150757</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5361728668213</t>
+    <t xml:space="preserve">11.5361738204956</t>
   </si>
   <si>
     <t xml:space="preserve">11.5187215805054</t>
@@ -2003,7 +2003,7 @@
     <t xml:space="preserve">11.4489116668701</t>
   </si>
   <si>
-    <t xml:space="preserve">11.64089012146</t>
+    <t xml:space="preserve">11.6408891677856</t>
   </si>
   <si>
     <t xml:space="preserve">11.7281522750854</t>
@@ -2054,10 +2054,10 @@
     <t xml:space="preserve">10.1588106155396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0692253112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0871429443359</t>
+    <t xml:space="preserve">10.0692262649536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0871438980103</t>
   </si>
   <si>
     <t xml:space="preserve">10.4633951187134</t>
@@ -2081,13 +2081,13 @@
     <t xml:space="preserve">10.8754816055298</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6425619125366</t>
+    <t xml:space="preserve">10.6425628662109</t>
   </si>
   <si>
     <t xml:space="preserve">10.5888118743896</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5171461105347</t>
+    <t xml:space="preserve">10.5171451568604</t>
   </si>
   <si>
     <t xml:space="preserve">10.8575649261475</t>
@@ -2102,10 +2102,10 @@
     <t xml:space="preserve">10.6604795455933</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3021440505981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4096441268921</t>
+    <t xml:space="preserve">10.3021450042725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4096450805664</t>
   </si>
   <si>
     <t xml:space="preserve">10.3558940887451</t>
@@ -2117,7 +2117,7 @@
     <t xml:space="preserve">10.4275617599487</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5350618362427</t>
+    <t xml:space="preserve">10.535062789917</t>
   </si>
   <si>
     <t xml:space="preserve">11.1800661087036</t>
@@ -2132,7 +2132,7 @@
     <t xml:space="preserve">11.3771505355835</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7354860305786</t>
+    <t xml:space="preserve">11.7354869842529</t>
   </si>
   <si>
     <t xml:space="preserve">11.9146537780762</t>
@@ -2162,7 +2162,7 @@
     <t xml:space="preserve">12.3984069824219</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2013216018677</t>
+    <t xml:space="preserve">12.201322555542</t>
   </si>
   <si>
     <t xml:space="preserve">11.9863214492798</t>
@@ -2186,16 +2186,16 @@
     <t xml:space="preserve">13.258412361145</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4017457962036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4375801086426</t>
+    <t xml:space="preserve">13.4017467498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4375791549683</t>
   </si>
   <si>
     <t xml:space="preserve">13.6884136199951</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9034156799316</t>
+    <t xml:space="preserve">13.903416633606</t>
   </si>
   <si>
     <t xml:space="preserve">14.6559200286865</t>
@@ -2204,7 +2204,7 @@
     <t xml:space="preserve">14.2438344955444</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6380043029785</t>
+    <t xml:space="preserve">14.6380033493042</t>
   </si>
   <si>
     <t xml:space="preserve">14.92467212677</t>
@@ -2231,13 +2231,13 @@
     <t xml:space="preserve">14.8888387680054</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8171730041504</t>
+    <t xml:space="preserve">14.8171720504761</t>
   </si>
   <si>
     <t xml:space="preserve">14.3871688842773</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7634210586548</t>
+    <t xml:space="preserve">14.7634201049805</t>
   </si>
   <si>
     <t xml:space="preserve">14.6200866699219</t>
@@ -2252,19 +2252,19 @@
     <t xml:space="preserve">15.0321731567383</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7455034255981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0500888824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0680046081543</t>
+    <t xml:space="preserve">14.7455043792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.050087928772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0680055618286</t>
   </si>
   <si>
     <t xml:space="preserve">15.1038408279419</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5305032730103</t>
+    <t xml:space="preserve">14.5305023193359</t>
   </si>
   <si>
     <t xml:space="preserve">14.7096710205078</t>
@@ -2273,7 +2273,7 @@
     <t xml:space="preserve">14.2080001831055</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6167478561401</t>
+    <t xml:space="preserve">13.6167469024658</t>
   </si>
   <si>
     <t xml:space="preserve">13.5092468261719</t>
@@ -2282,10 +2282,10 @@
     <t xml:space="preserve">13.0434112548828</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1688270568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9717435836792</t>
+    <t xml:space="preserve">13.1688280105591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9717426300049</t>
   </si>
   <si>
     <t xml:space="preserve">12.4700746536255</t>
@@ -2309,7 +2309,7 @@
     <t xml:space="preserve">13.2225780487061</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2046613693237</t>
+    <t xml:space="preserve">13.2046604156494</t>
   </si>
   <si>
     <t xml:space="preserve">13.0613269805908</t>
@@ -2318,25 +2318,25 @@
     <t xml:space="preserve">13.0075778961182</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6313257217407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0971612930298</t>
+    <t xml:space="preserve">12.6313247680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0971603393555</t>
   </si>
   <si>
     <t xml:space="preserve">13.0792446136475</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8642435073853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9896593093872</t>
+    <t xml:space="preserve">12.8642425537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9896602630615</t>
   </si>
   <si>
     <t xml:space="preserve">12.9538269042969</t>
   </si>
   <si>
-    <t xml:space="preserve">12.720908164978</t>
+    <t xml:space="preserve">12.7209091186523</t>
   </si>
   <si>
     <t xml:space="preserve">12.5596580505371</t>
@@ -2360,13 +2360,13 @@
     <t xml:space="preserve">12.7925758361816</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5954914093018</t>
+    <t xml:space="preserve">12.5954923629761</t>
   </si>
   <si>
     <t xml:space="preserve">12.5238237380981</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5059080123901</t>
+    <t xml:space="preserve">12.5059070587158</t>
   </si>
   <si>
     <t xml:space="preserve">12.4879894256592</t>
@@ -2399,7 +2399,7 @@
     <t xml:space="preserve">12.4342403411865</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9504880905151</t>
+    <t xml:space="preserve">11.9504871368408</t>
   </si>
   <si>
     <t xml:space="preserve">12.2192401885986</t>
@@ -2411,7 +2411,7 @@
     <t xml:space="preserve">12.1117391586304</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9684038162231</t>
+    <t xml:space="preserve">11.9684047698975</t>
   </si>
   <si>
     <t xml:space="preserve">12.0400714874268</t>
@@ -2423,7 +2423,7 @@
     <t xml:space="preserve">12.255072593689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7388257980347</t>
+    <t xml:space="preserve">12.7388248443604</t>
   </si>
   <si>
     <t xml:space="preserve">13.7421646118164</t>
@@ -2444,13 +2444,13 @@
     <t xml:space="preserve">14.0467500686646</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0646667480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9392499923706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6346635818481</t>
+    <t xml:space="preserve">14.0646657943726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9392490386963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6346645355225</t>
   </si>
   <si>
     <t xml:space="preserve">14.2796678543091</t>
@@ -2477,16 +2477,16 @@
     <t xml:space="preserve">13.1867456436157</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3838291168213</t>
+    <t xml:space="preserve">13.383828163147</t>
   </si>
   <si>
     <t xml:space="preserve">13.5988302230835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7029914855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8429861068726</t>
+    <t xml:space="preserve">12.70299243927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8429870605469</t>
   </si>
   <si>
     <t xml:space="preserve">11.7892360687256</t>
@@ -2507,10 +2507,10 @@
     <t xml:space="preserve">11.3592348098755</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4309024810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3054838180542</t>
+    <t xml:space="preserve">11.4309015274048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3054828643799</t>
   </si>
   <si>
     <t xml:space="preserve">11.2875671386719</t>
@@ -3465,6 +3465,9 @@
   </si>
   <si>
     <t xml:space="preserve">18.5400009155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3799991607666</t>
   </si>
 </sst>
 </file>
@@ -68725,7 +68728,7 @@
     </row>
     <row r="2498">
       <c r="A2498" s="1" t="n">
-        <v>45957.6909722222</v>
+        <v>45957.3333333333</v>
       </c>
       <c r="B2498" t="n">
         <v>15401</v>
@@ -68746,6 +68749,32 @@
         <v>1150</v>
       </c>
       <c r="H2498" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2499">
+      <c r="A2499" s="1" t="n">
+        <v>45958.6911342593</v>
+      </c>
+      <c r="B2499" t="n">
+        <v>22084</v>
+      </c>
+      <c r="C2499" t="n">
+        <v>18.4599990844727</v>
+      </c>
+      <c r="D2499" t="n">
+        <v>18.2199993133545</v>
+      </c>
+      <c r="E2499" t="n">
+        <v>18.3799991607666</v>
+      </c>
+      <c r="F2499" t="n">
+        <v>18.3799991607666</v>
+      </c>
+      <c r="G2499" t="s">
+        <v>1151</v>
+      </c>
+      <c r="H2499" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ORS.MI.xlsx
+++ b/data/ORS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1153" uniqueCount="1153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="1154">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,46 +38,46 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08406352996826</t>
+    <t xml:space="preserve">8.08406257629395</t>
   </si>
   <si>
     <t xml:space="preserve">ORS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98275947570801</t>
+    <t xml:space="preserve">7.98275804519653</t>
   </si>
   <si>
     <t xml:space="preserve">8.06380176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94223642349243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8247241973877</t>
+    <t xml:space="preserve">7.94223737716675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82472467422485</t>
   </si>
   <si>
     <t xml:space="preserve">7.93818521499634</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90171527862549</t>
+    <t xml:space="preserve">7.90171575546265</t>
   </si>
   <si>
     <t xml:space="preserve">8.03948879241943</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92602872848511</t>
+    <t xml:space="preserve">7.92602968215942</t>
   </si>
   <si>
     <t xml:space="preserve">7.86119413375854</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82067203521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93413305282593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02328205108643</t>
+    <t xml:space="preserve">7.82067251205444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93413209915161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02328109741211</t>
   </si>
   <si>
     <t xml:space="preserve">8.08811473846436</t>
@@ -86,31 +86,31 @@
     <t xml:space="preserve">8.14484596252441</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69910717010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80446434020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97465515136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0111255645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01517677307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79230833053589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82877635955811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34745407104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84093332290649</t>
+    <t xml:space="preserve">7.69910764694214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8044638633728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97465562820435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01112365722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01517486572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79230785369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8287787437439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34745311737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84093427658081</t>
   </si>
   <si>
     <t xml:space="preserve">7.90982007980347</t>
@@ -119,43 +119,43 @@
     <t xml:space="preserve">7.85714101791382</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78015089035034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84498643875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9787073135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88550662994385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95034122467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00302028656006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0192289352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91792345046997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10027313232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.104323387146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1853666305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20157623291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11242866516113</t>
+    <t xml:space="preserve">7.7801513671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8449854850769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97870779037476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88550519943237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95034265518188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00301837921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01922798156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91792440414429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1002721786499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10432434082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18536758422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20157527923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11242771148682</t>
   </si>
   <si>
     <t xml:space="preserve">8.07595825195312</t>
@@ -164,10 +164,10 @@
     <t xml:space="preserve">8.03138542175293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09621810913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17726230621338</t>
+    <t xml:space="preserve">8.09622001647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1772632598877</t>
   </si>
   <si>
     <t xml:space="preserve">8.05569839477539</t>
@@ -176,37 +176,37 @@
     <t xml:space="preserve">8.12053203582764</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25830745697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42039108276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67162609100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55816555023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42849731445312</t>
+    <t xml:space="preserve">8.2583065032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42039203643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67162799835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55816650390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42849826812744</t>
   </si>
   <si>
     <t xml:space="preserve">8.52429103851318</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45921897888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50802230834961</t>
+    <t xml:space="preserve">8.45921802520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50802040100098</t>
   </si>
   <si>
     <t xml:space="preserve">8.60562801361084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5324239730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61376190185547</t>
+    <t xml:space="preserve">8.53242492675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61376094818115</t>
   </si>
   <si>
     <t xml:space="preserve">8.67069911956787</t>
@@ -215,10 +215,10 @@
     <t xml:space="preserve">8.87404632568359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79270839691162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90658092498779</t>
+    <t xml:space="preserve">8.7927074432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90657997131348</t>
   </si>
   <si>
     <t xml:space="preserve">8.86591243743896</t>
@@ -236,85 +236,85 @@
     <t xml:space="preserve">8.74390316009521</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91471385955811</t>
+    <t xml:space="preserve">8.91471290588379</t>
   </si>
   <si>
     <t xml:space="preserve">8.92284965515137</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10992908477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07739353179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11806201934814</t>
+    <t xml:space="preserve">9.10992813110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.077392578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11806297302246</t>
   </si>
   <si>
     <t xml:space="preserve">9.1343297958374</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15059852600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15873241424561</t>
+    <t xml:space="preserve">9.15059661865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15873146057129</t>
   </si>
   <si>
     <t xml:space="preserve">8.73576927185059</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67883205413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8577766418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72763442993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70323371887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66256618499756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69510078430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62189674377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80084037780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77643966674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68696689605713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54869079589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54055690765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58122825622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46735286712646</t>
+    <t xml:space="preserve">8.6788330078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85777854919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72763633728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7032356262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66256523132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69510173797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6218957901001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80084133148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77643871307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68696784973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54869174957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54055786132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58122730255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46735191345215</t>
   </si>
   <si>
     <t xml:space="preserve">8.51615619659424</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49988842010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45108509063721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63003063201904</t>
+    <t xml:space="preserve">8.49988746643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45108604431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63003158569336</t>
   </si>
   <si>
     <t xml:space="preserve">8.80897617340088</t>
@@ -332,13 +332,13 @@
     <t xml:space="preserve">9.05299091339111</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30514144897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1017951965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19126510620117</t>
+    <t xml:space="preserve">9.30514049530029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10179424285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1912670135498</t>
   </si>
   <si>
     <t xml:space="preserve">9.35394287109375</t>
@@ -347,28 +347,28 @@
     <t xml:space="preserve">9.4759521484375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54915618896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58982563018799</t>
+    <t xml:space="preserve">9.54915523529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5898265838623</t>
   </si>
   <si>
     <t xml:space="preserve">9.66303157806396</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71996688842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85824298858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0046529769897</t>
+    <t xml:space="preserve">9.71996593475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85824394226074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0046539306641</t>
   </si>
   <si>
     <t xml:space="preserve">10.2405347824097</t>
   </si>
   <si>
-    <t xml:space="preserve">10.24866771698</t>
+    <t xml:space="preserve">10.2486686706543</t>
   </si>
   <si>
     <t xml:space="preserve">10.3381414413452</t>
@@ -380,10 +380,10 @@
     <t xml:space="preserve">10.4276142120361</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4032115936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.525221824646</t>
+    <t xml:space="preserve">10.4032125473022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.525218963623</t>
   </si>
   <si>
     <t xml:space="preserve">10.4601488113403</t>
@@ -395,16 +395,16 @@
     <t xml:space="preserve">10.5821571350098</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7773714065552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9807167053223</t>
+    <t xml:space="preserve">10.7773694992065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9807157516479</t>
   </si>
   <si>
     <t xml:space="preserve">10.8749761581421</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6553621292114</t>
+    <t xml:space="preserve">10.6553630828857</t>
   </si>
   <si>
     <t xml:space="preserve">10.679762840271</t>
@@ -416,10 +416,10 @@
     <t xml:space="preserve">10.5170860290527</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5414896011353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5577564239502</t>
+    <t xml:space="preserve">10.5414886474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5577554702759</t>
   </si>
   <si>
     <t xml:space="preserve">10.5089521408081</t>
@@ -428,19 +428,19 @@
     <t xml:space="preserve">10.818039894104</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6878986358643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.761100769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6472282409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8993787765503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.883111000061</t>
+    <t xml:space="preserve">10.6878967285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7611017227173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6472291946411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.899377822876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8831100463867</t>
   </si>
   <si>
     <t xml:space="preserve">10.6716289520264</t>
@@ -449,25 +449,25 @@
     <t xml:space="preserve">10.7367010116577</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0051174163818</t>
+    <t xml:space="preserve">11.0051183700562</t>
   </si>
   <si>
     <t xml:space="preserve">11.0213861465454</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1840629577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4036769866943</t>
+    <t xml:space="preserve">11.184063911438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4036779403687</t>
   </si>
   <si>
     <t xml:space="preserve">11.395544052124</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3386077880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3223390579224</t>
+    <t xml:space="preserve">11.3386068344116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.322338104248</t>
   </si>
   <si>
     <t xml:space="preserve">11.330472946167</t>
@@ -503,28 +503,28 @@
     <t xml:space="preserve">10.232400894165</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3218727111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3706789016724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3300075531006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3056049346924</t>
+    <t xml:space="preserve">10.321873664856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3706769943237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3300085067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3056058883667</t>
   </si>
   <si>
     <t xml:space="preserve">10.2568035125732</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1835975646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4845504760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3625440597534</t>
+    <t xml:space="preserve">10.1835966110229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4845523834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3625431060791</t>
   </si>
   <si>
     <t xml:space="preserve">10.4438819885254</t>
@@ -536,22 +536,22 @@
     <t xml:space="preserve">10.9237794876099</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0376539230347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0620565414429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.102725982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1433944702148</t>
+    <t xml:space="preserve">11.037654876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0620555877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1027250289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1433935165405</t>
   </si>
   <si>
     <t xml:space="preserve">11.175929069519</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1352605819702</t>
+    <t xml:space="preserve">11.1352615356445</t>
   </si>
   <si>
     <t xml:space="preserve">11.0701904296875</t>
@@ -560,73 +560,73 @@
     <t xml:space="preserve">11.1189937591553</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1515283584595</t>
+    <t xml:space="preserve">11.1515274047852</t>
   </si>
   <si>
     <t xml:space="preserve">11.2247323989868</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0457887649536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5008182525635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1347951889038</t>
+    <t xml:space="preserve">11.0457878112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5008201599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1347961425781</t>
   </si>
   <si>
     <t xml:space="preserve">8.36161231994629</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01999092102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10946369171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39414691925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21520328521729</t>
+    <t xml:space="preserve">8.01998996734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10946178436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39414882659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2152042388916</t>
   </si>
   <si>
     <t xml:space="preserve">8.3372106552124</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31280899047852</t>
+    <t xml:space="preserve">8.3128080368042</t>
   </si>
   <si>
     <t xml:space="preserve">8.18266773223877</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34534549713135</t>
+    <t xml:space="preserve">8.34534454345703</t>
   </si>
   <si>
     <t xml:space="preserve">8.23960494995117</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49175453186035</t>
+    <t xml:space="preserve">8.49175548553467</t>
   </si>
   <si>
     <t xml:space="preserve">8.58936023712158</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76017284393311</t>
+    <t xml:space="preserve">8.76017189025879</t>
   </si>
   <si>
     <t xml:space="preserve">8.29654216766357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25587368011475</t>
+    <t xml:space="preserve">8.25587177276611</t>
   </si>
   <si>
     <t xml:space="preserve">8.17453384399414</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1908016204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23147010803223</t>
+    <t xml:space="preserve">8.19080066680908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23147106170654</t>
   </si>
   <si>
     <t xml:space="preserve">8.2802734375</t>
@@ -635,7 +635,7 @@
     <t xml:space="preserve">8.14199733734131</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15826511383057</t>
+    <t xml:space="preserve">8.15826606750488</t>
   </si>
   <si>
     <t xml:space="preserve">8.16639995574951</t>
@@ -644,13 +644,13 @@
     <t xml:space="preserve">8.12166309356689</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05252552032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89798259735107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85731267929077</t>
+    <t xml:space="preserve">8.05252647399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89798307418823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85731410980225</t>
   </si>
   <si>
     <t xml:space="preserve">7.93051767349243</t>
@@ -659,7 +659,7 @@
     <t xml:space="preserve">7.90611553192139</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93865156173706</t>
+    <t xml:space="preserve">7.93865060806274</t>
   </si>
   <si>
     <t xml:space="preserve">7.84917974472046</t>
@@ -674,271 +674,274 @@
     <t xml:space="preserve">7.57262706756592</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48315525054932</t>
+    <t xml:space="preserve">7.48315572738647</t>
   </si>
   <si>
     <t xml:space="preserve">7.66616678237915</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60516357421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54009342193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52382469177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47908735275269</t>
+    <t xml:space="preserve">7.60516309738159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54009246826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52382373809814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47908592224121</t>
   </si>
   <si>
     <t xml:space="preserve">7.61329698562622</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54822587966919</t>
+    <t xml:space="preserve">7.54822635650635</t>
   </si>
   <si>
     <t xml:space="preserve">7.56449365615845</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50755739212036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46688604354858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4912896156311</t>
+    <t xml:space="preserve">7.50755596160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46688652038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49129009246826</t>
   </si>
   <si>
     <t xml:space="preserve">7.49942207336426</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31234407424927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27980804443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3774151802063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38554859161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36928129196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3204779624939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34488010406494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28794145584106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04392528533936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15780067443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39368295669556</t>
+    <t xml:space="preserve">7.31234359741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27980756759644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37741470336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38554954528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36928081512451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32047700881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34487962722778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28794240951538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04392576217651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15779972076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39368343353271</t>
   </si>
   <si>
     <t xml:space="preserve">7.42621803283691</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40181636810303</t>
+    <t xml:space="preserve">7.40181684494019</t>
   </si>
   <si>
     <t xml:space="preserve">7.3042106628418</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3611478805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20660400390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35301351547241</t>
+    <t xml:space="preserve">7.36114692687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20660352706909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35301303863525</t>
   </si>
   <si>
     <t xml:space="preserve">7.33674573898315</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27167367935181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23100519180298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32861185073853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26354122161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23913908004761</t>
+    <t xml:space="preserve">7.27167463302612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23100471496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32861137390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26354169845581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23913955688477</t>
   </si>
   <si>
     <t xml:space="preserve">7.22287178039551</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24727249145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44248580932617</t>
+    <t xml:space="preserve">7.24727344512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44248676300049</t>
   </si>
   <si>
     <t xml:space="preserve">7.25540733337402</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18220281600952</t>
+    <t xml:space="preserve">7.18220233917236</t>
   </si>
   <si>
     <t xml:space="preserve">7.29607629776001</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16593360900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1415319442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05206060409546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07646226882935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03579235076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01952457427979</t>
+    <t xml:space="preserve">7.16593408584595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14153242111206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0520601272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07646179199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0357928276062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01952505111694</t>
   </si>
   <si>
     <t xml:space="preserve">6.87311458587646</t>
   </si>
   <si>
+    <t xml:space="preserve">6.677903175354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85124778747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93379163742065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26397275924683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14840984344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0988826751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1814284324646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16491794586182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14015579223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21444654464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17317390441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97506475448608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84299325942993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60361194610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62012195587158</t>
+  </si>
+  <si>
     <t xml:space="preserve">6.67790269851685</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85124731063843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93379163742065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26397371292114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14840936660767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0988826751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18142890930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16491985321045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14015579223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21444702148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17317390441895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97506475448608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84299278259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60361194610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62012100219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80997467041016</t>
+    <t xml:space="preserve">6.809974193573</t>
   </si>
   <si>
     <t xml:space="preserve">6.54583024978638</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31470394134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32295846939087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34772253036499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38074064254761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39724922180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47153997421265</t>
+    <t xml:space="preserve">6.31470346450806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32295799255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34772300720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38074016571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39724826812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47153949737549</t>
   </si>
   <si>
     <t xml:space="preserve">6.2816858291626</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22390365600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09183168411255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90197849273682</t>
+    <t xml:space="preserve">6.22390460968018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09183216094971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90197801589966</t>
   </si>
   <si>
     <t xml:space="preserve">5.9597601890564</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9927773475647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20739555358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14135980606079</t>
+    <t xml:space="preserve">5.99277782440186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20739507675171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14135932922363</t>
   </si>
   <si>
     <t xml:space="preserve">6.19088649749756</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14961385726929</t>
+    <t xml:space="preserve">6.14961338043213</t>
   </si>
   <si>
     <t xml:space="preserve">6.07532358169556</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25692319869995</t>
+    <t xml:space="preserve">6.25692224502563</t>
   </si>
   <si>
     <t xml:space="preserve">6.00928783416748</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9845232963562</t>
+    <t xml:space="preserve">5.98452281951904</t>
   </si>
   <si>
     <t xml:space="preserve">6.12485074996948</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13310480117798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27343130111694</t>
+    <t xml:space="preserve">6.13310527801514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2734317779541</t>
   </si>
   <si>
     <t xml:space="preserve">6.44677591323853</t>
@@ -947,22 +950,22 @@
     <t xml:space="preserve">6.55408477783203</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51281261444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36423110961914</t>
+    <t xml:space="preserve">6.51281213760376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3642315864563</t>
   </si>
   <si>
     <t xml:space="preserve">6.24041366577148</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21564960479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23215961456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2486686706543</t>
+    <t xml:space="preserve">6.21565008163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23215913772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24866771697998</t>
   </si>
   <si>
     <t xml:space="preserve">6.11659622192383</t>
@@ -971,7 +974,7 @@
     <t xml:space="preserve">6.10834074020386</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05055999755859</t>
+    <t xml:space="preserve">6.05055952072144</t>
   </si>
   <si>
     <t xml:space="preserve">5.89372396469116</t>
@@ -983,7 +986,7 @@
     <t xml:space="preserve">5.6956148147583</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79467010498047</t>
+    <t xml:space="preserve">5.79466915130615</t>
   </si>
   <si>
     <t xml:space="preserve">5.80292367935181</t>
@@ -992,16 +995,16 @@
     <t xml:space="preserve">5.82768726348877</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7864146232605</t>
+    <t xml:space="preserve">5.78641557693481</t>
   </si>
   <si>
     <t xml:space="preserve">5.73688745498657</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85245084762573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29819536209106</t>
+    <t xml:space="preserve">5.85245132446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29819583892822</t>
   </si>
   <si>
     <t xml:space="preserve">6.18263244628906</t>
@@ -1010,7 +1013,7 @@
     <t xml:space="preserve">6.15786838531494</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03404998779297</t>
+    <t xml:space="preserve">6.03405046463013</t>
   </si>
   <si>
     <t xml:space="preserve">6.08357763290405</t>
@@ -1019,7 +1022,7 @@
     <t xml:space="preserve">5.81943321228027</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91848659515381</t>
+    <t xml:space="preserve">5.91848707199097</t>
   </si>
   <si>
     <t xml:space="preserve">5.86070537567139</t>
@@ -1028,10 +1031,10 @@
     <t xml:space="preserve">5.76165151596069</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75339698791504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81117820739746</t>
+    <t xml:space="preserve">5.75339603424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81117868423462</t>
   </si>
   <si>
     <t xml:space="preserve">5.70387029647827</t>
@@ -1040,61 +1043,61 @@
     <t xml:space="preserve">5.74514198303223</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83594226837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71212434768677</t>
+    <t xml:space="preserve">5.83594179153442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71212482452393</t>
   </si>
   <si>
     <t xml:space="preserve">5.84419631958008</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94325065612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96801424026489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87721586227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88546991348267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93499565124512</t>
+    <t xml:space="preserve">5.94325113296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96801471710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87721490859985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88546943664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93499660491943</t>
   </si>
   <si>
     <t xml:space="preserve">6.02579593658447</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06706857681274</t>
+    <t xml:space="preserve">6.0670690536499</t>
   </si>
   <si>
     <t xml:space="preserve">6.3889946937561</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1991400718689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04230451583862</t>
+    <t xml:space="preserve">6.19914150238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04230499267578</t>
   </si>
   <si>
     <t xml:space="preserve">6.05881452560425</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95150518417358</t>
+    <t xml:space="preserve">5.9515061378479</t>
   </si>
   <si>
     <t xml:space="preserve">6.17437744140625</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1760196685791</t>
+    <t xml:space="preserve">6.17601919174194</t>
   </si>
   <si>
     <t xml:space="preserve">6.29349803924561</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25993204116821</t>
+    <t xml:space="preserve">6.25993251800537</t>
   </si>
   <si>
     <t xml:space="preserve">6.20958423614502</t>
@@ -1106,58 +1109,55 @@
     <t xml:space="preserve">6.10888910293579</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0753231048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14245367050171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05854034423828</t>
+    <t xml:space="preserve">6.14245414733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05854082107544</t>
   </si>
   <si>
     <t xml:space="preserve">6.02497529983521</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97462749481201</t>
+    <t xml:space="preserve">5.97462797164917</t>
   </si>
   <si>
     <t xml:space="preserve">5.95784425735474</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15923643112183</t>
+    <t xml:space="preserve">6.15923738479614</t>
   </si>
   <si>
     <t xml:space="preserve">6.12567138671875</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19280195236206</t>
+    <t xml:space="preserve">6.1928014755249</t>
   </si>
   <si>
     <t xml:space="preserve">6.42775869369507</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71306419372559</t>
+    <t xml:space="preserve">6.7130651473999</t>
   </si>
   <si>
     <t xml:space="preserve">6.64593458175659</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69628238677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78019571304321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7298469543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.629150390625</t>
+    <t xml:space="preserve">6.69628190994263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7801947593689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72984743118286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62915086746216</t>
   </si>
   <si>
     <t xml:space="preserve">6.56202030181885</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54523801803589</t>
+    <t xml:space="preserve">6.54523754119873</t>
   </si>
   <si>
     <t xml:space="preserve">6.67949914932251</t>
@@ -1169,19 +1169,19 @@
     <t xml:space="preserve">6.57880306243896</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37741088867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3438458442688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22636747360229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36062908172607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67253923416138</t>
+    <t xml:space="preserve">6.37741136550903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34384632110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22636795043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36062860488892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67253875732422</t>
   </si>
   <si>
     <t xml:space="preserve">5.55506038665771</t>
@@ -1196,43 +1196,43 @@
     <t xml:space="preserve">5.53827810287476</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43758201599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45436573028564</t>
+    <t xml:space="preserve">5.43758249282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45436525344849</t>
   </si>
   <si>
     <t xml:space="preserve">5.60540819168091</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52149534225464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50471305847168</t>
+    <t xml:space="preserve">5.5214958190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50471258163452</t>
   </si>
   <si>
     <t xml:space="preserve">5.4879298210144</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35366916656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3704514503479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42079925537109</t>
+    <t xml:space="preserve">5.35366821289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37045097351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42079877853394</t>
   </si>
   <si>
     <t xml:space="preserve">5.28653860092163</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30332040786743</t>
+    <t xml:space="preserve">5.30332088470459</t>
   </si>
   <si>
     <t xml:space="preserve">5.26975584030151</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38723421096802</t>
+    <t xml:space="preserve">5.38723468780518</t>
   </si>
   <si>
     <t xml:space="preserve">5.32010364532471</t>
@@ -1250,16 +1250,16 @@
     <t xml:space="preserve">5.72288703918457</t>
   </si>
   <si>
-    <t xml:space="preserve">5.739670753479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63897466659546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57184410095215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18584203720093</t>
+    <t xml:space="preserve">5.73967027664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6389741897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57184457778931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18584156036377</t>
   </si>
   <si>
     <t xml:space="preserve">5.2026252746582</t>
@@ -1268,22 +1268,22 @@
     <t xml:space="preserve">5.21940803527832</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16905975341797</t>
+    <t xml:space="preserve">5.16905927658081</t>
   </si>
   <si>
     <t xml:space="preserve">5.13549375534058</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10192918777466</t>
+    <t xml:space="preserve">5.1019287109375</t>
   </si>
   <si>
     <t xml:space="preserve">4.9508843421936</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03479814529419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15227651596069</t>
+    <t xml:space="preserve">5.03479862213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15227746963501</t>
   </si>
   <si>
     <t xml:space="preserve">5.11871147155762</t>
@@ -1295,7 +1295,7 @@
     <t xml:space="preserve">5.08514642715454</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23618984222412</t>
+    <t xml:space="preserve">5.23619031906128</t>
   </si>
   <si>
     <t xml:space="preserve">5.25297260284424</t>
@@ -1304,28 +1304,28 @@
     <t xml:space="preserve">5.33688640594482</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79001760482788</t>
+    <t xml:space="preserve">5.79001808166504</t>
   </si>
   <si>
     <t xml:space="preserve">5.77323484420776</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58862638473511</t>
+    <t xml:space="preserve">5.58862590789795</t>
   </si>
   <si>
     <t xml:space="preserve">4.81662368774414</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79984092712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59844875335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36349201202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31314420700073</t>
+    <t xml:space="preserve">4.79984140396118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59844827651978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36349153518677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31314373016357</t>
   </si>
   <si>
     <t xml:space="preserve">4.19566488265991</t>
@@ -1337,13 +1337,13 @@
     <t xml:space="preserve">4.02783870697021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17049074172974</t>
+    <t xml:space="preserve">4.17049121856689</t>
   </si>
   <si>
     <t xml:space="preserve">4.06979560852051</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12014245986938</t>
+    <t xml:space="preserve">4.1201434135437</t>
   </si>
   <si>
     <t xml:space="preserve">4.34670877456665</t>
@@ -1358,28 +1358,28 @@
     <t xml:space="preserve">4.15370845794678</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2627968788147</t>
+    <t xml:space="preserve">4.26279592514038</t>
   </si>
   <si>
     <t xml:space="preserve">4.16209983825684</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14531755447388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99427247047424</t>
+    <t xml:space="preserve">4.14531803131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99427270889282</t>
   </si>
   <si>
     <t xml:space="preserve">4.09496927261353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98588180541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27957820892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22923040390015</t>
+    <t xml:space="preserve">3.98588132858276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2795786857605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22922992706299</t>
   </si>
   <si>
     <t xml:space="preserve">4.21244764328003</t>
@@ -1388,10 +1388,10 @@
     <t xml:space="preserve">4.03622961044312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1287784576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16283082962036</t>
+    <t xml:space="preserve">4.12877941131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16283130645752</t>
   </si>
   <si>
     <t xml:space="preserve">4.07770156860352</t>
@@ -1400,28 +1400,28 @@
     <t xml:space="preserve">4.00108480453491</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20539522171021</t>
+    <t xml:space="preserve">4.20539569854736</t>
   </si>
   <si>
     <t xml:space="preserve">4.37565469741821</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21390867233276</t>
+    <t xml:space="preserve">4.21390819549561</t>
   </si>
   <si>
     <t xml:space="preserve">4.22242164611816</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25647306442261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24796056747437</t>
+    <t xml:space="preserve">4.25647354125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24796009063721</t>
   </si>
   <si>
     <t xml:space="preserve">4.32457685470581</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30755043029785</t>
+    <t xml:space="preserve">4.30755090713501</t>
   </si>
   <si>
     <t xml:space="preserve">4.23944759368896</t>
@@ -1430,22 +1430,22 @@
     <t xml:space="preserve">4.35862874984741</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51186180114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5334153175354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9420371055603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8909592628479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73772621154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5504412651062</t>
+    <t xml:space="preserve">4.5118613243103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53341484069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94203662872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89095973968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73772573471069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55044078826904</t>
   </si>
   <si>
     <t xml:space="preserve">5.5844931602478</t>
@@ -1454,13 +1454,13 @@
     <t xml:space="preserve">5.567467212677</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41423416137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26100158691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48233842849731</t>
+    <t xml:space="preserve">5.41423368453979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2610011100769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48233795166016</t>
   </si>
   <si>
     <t xml:space="preserve">5.44828605651855</t>
@@ -1478,22 +1478,22 @@
     <t xml:space="preserve">5.70367431640625</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32910490036011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27802705764771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43126058578491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31207895278931</t>
+    <t xml:space="preserve">5.32910442352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27802658081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43126010894775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31207799911499</t>
   </si>
   <si>
     <t xml:space="preserve">5.2269492149353</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00561237335205</t>
+    <t xml:space="preserve">5.00561285018921</t>
   </si>
   <si>
     <t xml:space="preserve">4.95453500747681</t>
@@ -1511,28 +1511,28 @@
     <t xml:space="preserve">4.97156095504761</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88643074035645</t>
+    <t xml:space="preserve">4.88643169403076</t>
   </si>
   <si>
     <t xml:space="preserve">5.02263832092285</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92048311233521</t>
+    <t xml:space="preserve">4.92048263549805</t>
   </si>
   <si>
     <t xml:space="preserve">4.90345764160156</t>
   </si>
   <si>
-    <t xml:space="preserve">4.852379322052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86940479278564</t>
+    <t xml:space="preserve">4.85237979888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8694052696228</t>
   </si>
   <si>
     <t xml:space="preserve">5.34613084793091</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2439751625061</t>
+    <t xml:space="preserve">5.24397563934326</t>
   </si>
   <si>
     <t xml:space="preserve">5.36315631866455</t>
@@ -1547,13 +1547,13 @@
     <t xml:space="preserve">5.15884590148926</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10776853561401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98858642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0907416343689</t>
+    <t xml:space="preserve">5.10776805877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98858690261841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09074211120605</t>
   </si>
   <si>
     <t xml:space="preserve">5.1928973197937</t>
@@ -1568,16 +1568,16 @@
     <t xml:space="preserve">5.07371616363525</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68212032318115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54591369628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59699153900146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57996559143066</t>
+    <t xml:space="preserve">4.68212080001831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5459132194519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59699106216431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57996511459351</t>
   </si>
   <si>
     <t xml:space="preserve">4.63104295730591</t>
@@ -1589,19 +1589,19 @@
     <t xml:space="preserve">4.76725006103516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8183274269104</t>
+    <t xml:space="preserve">4.81832790374756</t>
   </si>
   <si>
     <t xml:space="preserve">4.80130195617676</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39720821380615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61854457855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46531200408936</t>
+    <t xml:space="preserve">5.39720869064331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6185450553894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4653115272522</t>
   </si>
   <si>
     <t xml:space="preserve">5.49936389923096</t>
@@ -1622,7 +1622,7 @@
     <t xml:space="preserve">5.8739333152771</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3166069984436</t>
+    <t xml:space="preserve">6.31660604476929</t>
   </si>
   <si>
     <t xml:space="preserve">6.33363246917725</t>
@@ -1631,16 +1631,16 @@
     <t xml:space="preserve">6.29958057403564</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35065841674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43578767776489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55496883392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69117641448975</t>
+    <t xml:space="preserve">6.35065793991089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43578720092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55496835708618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69117593765259</t>
   </si>
   <si>
     <t xml:space="preserve">6.79333162307739</t>
@@ -1649,16 +1649,16 @@
     <t xml:space="preserve">7.15087509155273</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08277130126953</t>
+    <t xml:space="preserve">7.08277082443237</t>
   </si>
   <si>
     <t xml:space="preserve">6.87846088409424</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77630567550659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84440946578979</t>
+    <t xml:space="preserve">6.77630519866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84440898895264</t>
   </si>
   <si>
     <t xml:space="preserve">6.70820236206055</t>
@@ -1667,22 +1667,22 @@
     <t xml:space="preserve">6.75927972793579</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5379433631897</t>
+    <t xml:space="preserve">6.53794288635254</t>
   </si>
   <si>
     <t xml:space="preserve">6.72522783279419</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65712404251099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91251230239868</t>
+    <t xml:space="preserve">6.6571249961853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91251277923584</t>
   </si>
   <si>
     <t xml:space="preserve">6.8954873085022</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96359014511108</t>
+    <t xml:space="preserve">6.96359062194824</t>
   </si>
   <si>
     <t xml:space="preserve">7.17302179336548</t>
@@ -1694,13 +1694,13 @@
     <t xml:space="preserve">7.1206636428833</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57443189620972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97584247589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02820014953613</t>
+    <t xml:space="preserve">7.57443284988403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97584199905396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0281982421875</t>
   </si>
   <si>
     <t xml:space="preserve">8.0631046295166</t>
@@ -1712,16 +1712,16 @@
     <t xml:space="preserve">8.0107479095459</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94093656539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13291549682617</t>
+    <t xml:space="preserve">7.94093704223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13291454315186</t>
   </si>
   <si>
     <t xml:space="preserve">8.15036773681641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16781902313232</t>
+    <t xml:space="preserve">8.16782093048096</t>
   </si>
   <si>
     <t xml:space="preserve">8.18527317047119</t>
@@ -1736,16 +1736,16 @@
     <t xml:space="preserve">8.25508308410645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08055782318115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20272445678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95838832855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37725162506104</t>
+    <t xml:space="preserve">8.08055686950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20272541046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95838928222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37725257873535</t>
   </si>
   <si>
     <t xml:space="preserve">8.32489395141602</t>
@@ -1757,7 +1757,7 @@
     <t xml:space="preserve">8.58668231964111</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53432464599609</t>
+    <t xml:space="preserve">8.53432559967041</t>
   </si>
   <si>
     <t xml:space="preserve">8.69139862060547</t>
@@ -1769,34 +1769,34 @@
     <t xml:space="preserve">8.72630405426025</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42961025238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28998851776123</t>
+    <t xml:space="preserve">8.42960929870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28998947143555</t>
   </si>
   <si>
     <t xml:space="preserve">8.30744171142578</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04565238952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85367298126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41215705871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22017860412598</t>
+    <t xml:space="preserve">8.04565334320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85367345809937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41215801239014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22017765045166</t>
   </si>
   <si>
     <t xml:space="preserve">8.44706249237061</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3597993850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09801006317139</t>
+    <t xml:space="preserve">8.35979843139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09800910949707</t>
   </si>
   <si>
     <t xml:space="preserve">8.23763084411621</t>
@@ -1805,25 +1805,25 @@
     <t xml:space="preserve">8.48196697235107</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6215877532959</t>
+    <t xml:space="preserve">8.62158870697021</t>
   </si>
   <si>
     <t xml:space="preserve">8.55177783966064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65649318695068</t>
+    <t xml:space="preserve">8.656494140625</t>
   </si>
   <si>
     <t xml:space="preserve">8.51687240600586</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46451473236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49941921234131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56923007965088</t>
+    <t xml:space="preserve">8.46451377868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49942016601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5692310333252</t>
   </si>
   <si>
     <t xml:space="preserve">9.99161720275879</t>
@@ -1832,7 +1832,7 @@
     <t xml:space="preserve">9.59893417358398</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77346038818359</t>
+    <t xml:space="preserve">9.77345943450928</t>
   </si>
   <si>
     <t xml:space="preserve">9.8170919418335</t>
@@ -1847,19 +1847,19 @@
     <t xml:space="preserve">9.55530261993408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6425666809082</t>
+    <t xml:space="preserve">9.64256572723389</t>
   </si>
   <si>
     <t xml:space="preserve">9.9043550491333</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33714485168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94798564910889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8607234954834</t>
+    <t xml:space="preserve">9.33714580535889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9479866027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86072254180908</t>
   </si>
   <si>
     <t xml:space="preserve">10.5151958465576</t>
@@ -1874,16 +1874,16 @@
     <t xml:space="preserve">10.6024589538574</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8206167221069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7333545684814</t>
+    <t xml:space="preserve">10.8206157684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7333536148071</t>
   </si>
   <si>
     <t xml:space="preserve">10.7769861221313</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2970380783081</t>
+    <t xml:space="preserve">10.2970390319824</t>
   </si>
   <si>
     <t xml:space="preserve">10.3843011856079</t>
@@ -1898,10 +1898,10 @@
     <t xml:space="preserve">10.2534065246582</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0788812637329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51167011260986</t>
+    <t xml:space="preserve">10.0788822174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51167106628418</t>
   </si>
   <si>
     <t xml:space="preserve">9.72982883453369</t>
@@ -1922,49 +1922,49 @@
     <t xml:space="preserve">11.562352180481</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7805109024048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9114036560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9550352096558</t>
+    <t xml:space="preserve">11.7805099487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9114046096802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9550361633301</t>
   </si>
   <si>
     <t xml:space="preserve">11.693247795105</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3040885925293</t>
+    <t xml:space="preserve">12.3040895462036</t>
   </si>
   <si>
     <t xml:space="preserve">12.2604570388794</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2168254852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3913516998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7368793487549</t>
+    <t xml:space="preserve">12.2168245315552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3913507461548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7368783950806</t>
   </si>
   <si>
     <t xml:space="preserve">11.8677730560303</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6059846878052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9515104293823</t>
+    <t xml:space="preserve">11.6059837341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9515113830566</t>
   </si>
   <si>
     <t xml:space="preserve">12.0422992706299</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3005628585815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3441953659058</t>
+    <t xml:space="preserve">11.3005638122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3441944122314</t>
   </si>
   <si>
     <t xml:space="preserve">10.9951429367065</t>
@@ -1973,7 +1973,7 @@
     <t xml:space="preserve">10.4715642929077</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9078798294067</t>
+    <t xml:space="preserve">10.9078807830811</t>
   </si>
   <si>
     <t xml:space="preserve">11.4314584732056</t>
@@ -1982,7 +1982,7 @@
     <t xml:space="preserve">11.0387735366821</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9899415969849</t>
+    <t xml:space="preserve">11.9899406433105</t>
   </si>
   <si>
     <t xml:space="preserve">11.7456045150757</t>
@@ -1991,19 +1991,19 @@
     <t xml:space="preserve">11.5361728668213</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5187206268311</t>
+    <t xml:space="preserve">11.5187215805054</t>
   </si>
   <si>
     <t xml:space="preserve">11.6234359741211</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4489116668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6408891677856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7281522750854</t>
+    <t xml:space="preserve">11.4489107131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.64089012146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7281513214111</t>
   </si>
   <si>
     <t xml:space="preserve">11.9201307296753</t>
@@ -2012,10 +2012,10 @@
     <t xml:space="preserve">11.1173105239868</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0998592376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8031635284424</t>
+    <t xml:space="preserve">11.0998582839966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8031644821167</t>
   </si>
   <si>
     <t xml:space="preserve">10.7508068084717</t>
@@ -2024,7 +2024,7 @@
     <t xml:space="preserve">10.3319435119629</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1050605773926</t>
+    <t xml:space="preserve">10.1050596237183</t>
   </si>
   <si>
     <t xml:space="preserve">9.81839179992676</t>
@@ -2033,7 +2033,7 @@
     <t xml:space="preserve">9.69297409057617</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7108907699585</t>
+    <t xml:space="preserve">9.71089172363281</t>
   </si>
   <si>
     <t xml:space="preserve">10.1408929824829</t>
@@ -2054,19 +2054,19 @@
     <t xml:space="preserve">10.0692253112793</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0871429443359</t>
+    <t xml:space="preserve">10.0871438980103</t>
   </si>
   <si>
     <t xml:space="preserve">10.4633951187134</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7858982086182</t>
+    <t xml:space="preserve">10.7858972549438</t>
   </si>
   <si>
     <t xml:space="preserve">10.5708961486816</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7142295837402</t>
+    <t xml:space="preserve">10.7142305374146</t>
   </si>
   <si>
     <t xml:space="preserve">10.7500638961792</t>
@@ -2078,7 +2078,7 @@
     <t xml:space="preserve">10.8754816055298</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6425619125366</t>
+    <t xml:space="preserve">10.6425628662109</t>
   </si>
   <si>
     <t xml:space="preserve">10.5888118743896</t>
@@ -2087,10 +2087,10 @@
     <t xml:space="preserve">10.5171461105347</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8575649261475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9113149642944</t>
+    <t xml:space="preserve">10.8575639724731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9113159179688</t>
   </si>
   <si>
     <t xml:space="preserve">10.6067295074463</t>
@@ -2102,34 +2102,34 @@
     <t xml:space="preserve">10.3021440505981</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4096441268921</t>
+    <t xml:space="preserve">10.4096450805664</t>
   </si>
   <si>
     <t xml:space="preserve">10.3558940887451</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6783962249756</t>
+    <t xml:space="preserve">10.6783971786499</t>
   </si>
   <si>
     <t xml:space="preserve">10.4275617599487</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5350618362427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1800661087036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9829816818237</t>
+    <t xml:space="preserve">10.535062789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1800651550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9829807281494</t>
   </si>
   <si>
     <t xml:space="preserve">11.4846515655518</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3771505355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7354860305786</t>
+    <t xml:space="preserve">11.3771514892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7354869842529</t>
   </si>
   <si>
     <t xml:space="preserve">11.9146537780762</t>
@@ -2138,7 +2138,7 @@
     <t xml:space="preserve">11.9325704574585</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0221538543701</t>
+    <t xml:space="preserve">12.0221548080444</t>
   </si>
   <si>
     <t xml:space="preserve">11.8788204193115</t>
@@ -2156,10 +2156,10 @@
     <t xml:space="preserve">12.0938215255737</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3984069824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2013216018677</t>
+    <t xml:space="preserve">12.3984079360962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.201322555542</t>
   </si>
   <si>
     <t xml:space="preserve">11.9863214492798</t>
@@ -2174,7 +2174,7 @@
     <t xml:space="preserve">12.8463258743286</t>
   </si>
   <si>
-    <t xml:space="preserve">12.810492515564</t>
+    <t xml:space="preserve">12.8104934692383</t>
   </si>
   <si>
     <t xml:space="preserve">12.9179935455322</t>
@@ -2189,7 +2189,7 @@
     <t xml:space="preserve">13.4375801086426</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6884136199951</t>
+    <t xml:space="preserve">13.6884145736694</t>
   </si>
   <si>
     <t xml:space="preserve">13.9034156799316</t>
@@ -2207,46 +2207,46 @@
     <t xml:space="preserve">14.92467212677</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5125865936279</t>
+    <t xml:space="preserve">14.5125875473022</t>
   </si>
   <si>
     <t xml:space="preserve">14.5663366317749</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7992544174194</t>
+    <t xml:space="preserve">14.7992553710938</t>
   </si>
   <si>
     <t xml:space="preserve">14.5484189987183</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4946699142456</t>
+    <t xml:space="preserve">14.4946689605713</t>
   </si>
   <si>
     <t xml:space="preserve">14.2617511749268</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8888387680054</t>
+    <t xml:space="preserve">14.8888397216797</t>
   </si>
   <si>
     <t xml:space="preserve">14.8171730041504</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3871688842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7634210586548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6200866699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9067544937134</t>
+    <t xml:space="preserve">14.387167930603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7634201049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6200857162476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9067535400391</t>
   </si>
   <si>
     <t xml:space="preserve">15.1217546463013</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0321731567383</t>
+    <t xml:space="preserve">15.032172203064</t>
   </si>
   <si>
     <t xml:space="preserve">14.7455034255981</t>
@@ -2255,16 +2255,16 @@
     <t xml:space="preserve">15.0500888824463</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0680046081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1038408279419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5305032730103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7096710205078</t>
+    <t xml:space="preserve">15.0680055618286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1038398742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5305023193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7096700668335</t>
   </si>
   <si>
     <t xml:space="preserve">14.2080001831055</t>
@@ -2273,7 +2273,7 @@
     <t xml:space="preserve">13.6167478561401</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5092468261719</t>
+    <t xml:space="preserve">13.5092458724976</t>
   </si>
   <si>
     <t xml:space="preserve">13.0434112548828</t>
@@ -2285,7 +2285,7 @@
     <t xml:space="preserve">12.9717435836792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4700746536255</t>
+    <t xml:space="preserve">12.4700736999512</t>
   </si>
   <si>
     <t xml:space="preserve">13.2404947280884</t>
@@ -2303,16 +2303,16 @@
     <t xml:space="preserve">13.4913301467896</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2225780487061</t>
+    <t xml:space="preserve">13.2225790023804</t>
   </si>
   <si>
     <t xml:space="preserve">13.2046613693237</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0613269805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0075778961182</t>
+    <t xml:space="preserve">13.0613279342651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0075769424438</t>
   </si>
   <si>
     <t xml:space="preserve">12.6313257217407</t>
@@ -2324,10 +2324,10 @@
     <t xml:space="preserve">13.0792446136475</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8642435073853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9896593093872</t>
+    <t xml:space="preserve">12.8642425537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9896602630615</t>
   </si>
   <si>
     <t xml:space="preserve">12.9538269042969</t>
@@ -2348,7 +2348,7 @@
     <t xml:space="preserve">13.5271635055542</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3479948043823</t>
+    <t xml:space="preserve">13.3479957580566</t>
   </si>
   <si>
     <t xml:space="preserve">13.276328086853</t>
@@ -2360,19 +2360,19 @@
     <t xml:space="preserve">12.5954914093018</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5238237380981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5059080123901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4879894256592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3088226318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5417413711548</t>
+    <t xml:space="preserve">12.5238246917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5059070587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4879903793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3088216781616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5417404174805</t>
   </si>
   <si>
     <t xml:space="preserve">12.8284091949463</t>
@@ -2399,7 +2399,7 @@
     <t xml:space="preserve">11.9504880905151</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2192401885986</t>
+    <t xml:space="preserve">12.2192392349243</t>
   </si>
   <si>
     <t xml:space="preserve">11.8250703811646</t>
@@ -2411,7 +2411,7 @@
     <t xml:space="preserve">11.9684038162231</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0400714874268</t>
+    <t xml:space="preserve">12.0400705337524</t>
   </si>
   <si>
     <t xml:space="preserve">12.0042381286621</t>
@@ -2432,7 +2432,7 @@
     <t xml:space="preserve">14.0825834274292</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0109167098999</t>
+    <t xml:space="preserve">14.0109176635742</t>
   </si>
   <si>
     <t xml:space="preserve">13.7242479324341</t>
@@ -2447,7 +2447,7 @@
     <t xml:space="preserve">13.9392499923706</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6346635818481</t>
+    <t xml:space="preserve">13.6346645355225</t>
   </si>
   <si>
     <t xml:space="preserve">14.2796678543091</t>
@@ -2459,7 +2459,7 @@
     <t xml:space="preserve">13.9571657180786</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8496646881104</t>
+    <t xml:space="preserve">13.8496656417847</t>
   </si>
   <si>
     <t xml:space="preserve">13.9750833511353</t>
@@ -2477,7 +2477,7 @@
     <t xml:space="preserve">13.3838291168213</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5988302230835</t>
+    <t xml:space="preserve">13.5988311767578</t>
   </si>
   <si>
     <t xml:space="preserve">12.7029914855957</t>
@@ -2489,22 +2489,22 @@
     <t xml:space="preserve">11.7892360687256</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6817359924316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0759048461914</t>
+    <t xml:space="preserve">11.6817350387573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0759038925171</t>
   </si>
   <si>
     <t xml:space="preserve">11.5742359161377</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2159004211426</t>
+    <t xml:space="preserve">11.2158994674683</t>
   </si>
   <si>
     <t xml:space="preserve">11.3592348098755</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4309024810791</t>
+    <t xml:space="preserve">11.4309015274048</t>
   </si>
   <si>
     <t xml:space="preserve">11.3054838180542</t>
@@ -3471,6 +3471,9 @@
   </si>
   <si>
     <t xml:space="preserve">18.1599998474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7999992370605</t>
   </si>
 </sst>
 </file>
@@ -19869,7 +19872,7 @@
         <v>7.97442579269409</v>
       </c>
       <c r="G618" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19895,7 +19898,7 @@
         <v>8.13214015960693</v>
       </c>
       <c r="G619" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19921,7 +19924,7 @@
         <v>7.81671190261841</v>
       </c>
       <c r="G620" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19947,7 +19950,7 @@
         <v>7.81671190261841</v>
       </c>
       <c r="G621" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19973,7 +19976,7 @@
         <v>7.54071187973022</v>
       </c>
       <c r="G622" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19999,7 +20002,7 @@
         <v>7.5505690574646</v>
       </c>
       <c r="G623" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -20025,7 +20028,7 @@
         <v>7.58014106750488</v>
       </c>
       <c r="G624" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -20051,7 +20054,7 @@
         <v>7.61956882476807</v>
       </c>
       <c r="G625" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -20077,7 +20080,7 @@
         <v>7.5505690574646</v>
       </c>
       <c r="G626" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -20103,7 +20106,7 @@
         <v>7.63928318023682</v>
       </c>
       <c r="G627" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -20129,7 +20132,7 @@
         <v>7.72799777984619</v>
       </c>
       <c r="G628" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -20155,7 +20158,7 @@
         <v>7.61956882476807</v>
       </c>
       <c r="G629" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -20181,7 +20184,7 @@
         <v>7.50128316879272</v>
       </c>
       <c r="G630" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -20207,7 +20210,7 @@
         <v>7.4322829246521</v>
       </c>
       <c r="G631" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -20233,7 +20236,7 @@
         <v>7.27456903457642</v>
       </c>
       <c r="G632" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -20259,7 +20262,7 @@
         <v>7.04785490036011</v>
       </c>
       <c r="G633" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -20285,7 +20288,7 @@
         <v>7.11685514450073</v>
       </c>
       <c r="G634" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -20311,7 +20314,7 @@
         <v>7.27456903457642</v>
       </c>
       <c r="G635" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -20337,7 +20340,7 @@
         <v>7.15628290176392</v>
       </c>
       <c r="G636" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -20363,7 +20366,7 @@
         <v>7.41256904602051</v>
       </c>
       <c r="G637" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -20389,7 +20392,7 @@
         <v>7.33371210098267</v>
       </c>
       <c r="G638" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -20415,7 +20418,7 @@
         <v>7.39285516738892</v>
       </c>
       <c r="G639" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -20441,7 +20444,7 @@
         <v>7.33371210098267</v>
       </c>
       <c r="G640" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -20467,7 +20470,7 @@
         <v>7.34356880187988</v>
       </c>
       <c r="G641" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -20493,7 +20496,7 @@
         <v>7.25485515594482</v>
       </c>
       <c r="G642" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -20519,7 +20522,7 @@
         <v>7.47171211242676</v>
       </c>
       <c r="G643" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -20545,7 +20548,7 @@
         <v>7.41256904602051</v>
       </c>
       <c r="G644" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -20571,7 +20574,7 @@
         <v>7.25485515594482</v>
       </c>
       <c r="G645" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -20597,7 +20600,7 @@
         <v>7.17599821090698</v>
       </c>
       <c r="G646" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -20623,7 +20626,7 @@
         <v>7.1464262008667</v>
       </c>
       <c r="G647" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -20649,7 +20652,7 @@
         <v>7.31399822235107</v>
       </c>
       <c r="G648" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -20675,7 +20678,7 @@
         <v>7.17599821090698</v>
       </c>
       <c r="G649" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -20701,7 +20704,7 @@
         <v>7.31399822235107</v>
       </c>
       <c r="G650" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -20727,7 +20730,7 @@
         <v>7.32385492324829</v>
       </c>
       <c r="G651" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -20753,7 +20756,7 @@
         <v>7.49142599105835</v>
       </c>
       <c r="G652" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -20779,7 +20782,7 @@
         <v>7.69842576980591</v>
       </c>
       <c r="G653" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -20805,7 +20808,7 @@
         <v>7.82656908035278</v>
       </c>
       <c r="G654" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -20831,7 +20834,7 @@
         <v>7.77728319168091</v>
       </c>
       <c r="G655" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -20857,7 +20860,7 @@
         <v>7.59985494613647</v>
       </c>
       <c r="G656" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -20883,7 +20886,7 @@
         <v>7.63928318023682</v>
       </c>
       <c r="G657" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -20909,7 +20912,7 @@
         <v>7.61956882476807</v>
       </c>
       <c r="G658" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -20935,7 +20938,7 @@
         <v>7.45199823379517</v>
       </c>
       <c r="G659" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -20961,7 +20964,7 @@
         <v>7.45199823379517</v>
       </c>
       <c r="G660" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -20987,7 +20990,7 @@
         <v>7.34356880187988</v>
       </c>
       <c r="G661" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -21013,7 +21016,7 @@
         <v>7.42242622375488</v>
       </c>
       <c r="G662" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -21039,7 +21042,7 @@
         <v>7.50128316879272</v>
       </c>
       <c r="G663" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -21065,7 +21068,7 @@
         <v>7.44214105606079</v>
       </c>
       <c r="G664" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -21091,7 +21094,7 @@
         <v>7.50128316879272</v>
       </c>
       <c r="G665" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -21117,7 +21120,7 @@
         <v>7.50128316879272</v>
       </c>
       <c r="G666" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -21143,7 +21146,7 @@
         <v>7.46185493469238</v>
       </c>
       <c r="G667" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -21169,7 +21172,7 @@
         <v>7.3041410446167</v>
       </c>
       <c r="G668" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -21195,7 +21198,7 @@
         <v>7.29428291320801</v>
       </c>
       <c r="G669" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -21221,7 +21224,7 @@
         <v>7.22528314590454</v>
       </c>
       <c r="G670" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -21247,7 +21250,7 @@
         <v>7.03799819946289</v>
       </c>
       <c r="G671" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -21273,7 +21276,7 @@
         <v>7.11685514450073</v>
       </c>
       <c r="G672" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -21299,7 +21302,7 @@
         <v>7.15628290176392</v>
       </c>
       <c r="G673" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -21325,7 +21328,7 @@
         <v>7.22528314590454</v>
       </c>
       <c r="G674" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -21351,7 +21354,7 @@
         <v>7.22528314590454</v>
       </c>
       <c r="G675" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -21377,7 +21380,7 @@
         <v>7.17599821090698</v>
       </c>
       <c r="G676" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -21403,7 +21406,7 @@
         <v>6.8999981880188</v>
       </c>
       <c r="G677" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -21429,7 +21432,7 @@
         <v>6.80142593383789</v>
       </c>
       <c r="G678" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -21455,7 +21458,7 @@
         <v>6.91971206665039</v>
       </c>
       <c r="G679" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -21481,7 +21484,7 @@
         <v>6.92956876754761</v>
       </c>
       <c r="G680" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -21507,7 +21510,7 @@
         <v>6.8999981880188</v>
       </c>
       <c r="G681" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -21533,7 +21536,7 @@
         <v>6.8999981880188</v>
       </c>
       <c r="G682" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -21559,7 +21562,7 @@
         <v>6.91971206665039</v>
       </c>
       <c r="G683" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -21585,7 +21588,7 @@
         <v>6.95914077758789</v>
       </c>
       <c r="G684" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -21611,7 +21614,7 @@
         <v>6.90985488891602</v>
       </c>
       <c r="G685" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -21637,7 +21640,7 @@
         <v>6.95914077758789</v>
       </c>
       <c r="G686" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -21663,7 +21666,7 @@
         <v>6.8999981880188</v>
       </c>
       <c r="G687" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -21689,7 +21692,7 @@
         <v>6.85071182250977</v>
       </c>
       <c r="G688" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -21715,7 +21718,7 @@
         <v>6.91971206665039</v>
       </c>
       <c r="G689" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -21741,7 +21744,7 @@
         <v>6.8999981880188</v>
       </c>
       <c r="G690" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -21767,7 +21770,7 @@
         <v>6.92956876754761</v>
       </c>
       <c r="G691" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -21793,7 +21796,7 @@
         <v>6.8999981880188</v>
       </c>
       <c r="G692" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -21819,7 +21822,7 @@
         <v>7.04785490036011</v>
       </c>
       <c r="G693" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -21845,7 +21848,7 @@
         <v>6.8999981880188</v>
       </c>
       <c r="G694" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -21871,7 +21874,7 @@
         <v>6.98871183395386</v>
       </c>
       <c r="G695" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -21897,7 +21900,7 @@
         <v>7.27456903457642</v>
       </c>
       <c r="G696" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -21923,7 +21926,7 @@
         <v>7.29428291320801</v>
       </c>
       <c r="G697" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -21949,7 +21952,7 @@
         <v>7.52099800109863</v>
       </c>
       <c r="G698" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -21975,7 +21978,7 @@
         <v>7.54071187973022</v>
       </c>
       <c r="G699" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -22001,7 +22004,7 @@
         <v>7.45199823379517</v>
       </c>
       <c r="G700" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -22027,7 +22030,7 @@
         <v>7.41256904602051</v>
       </c>
       <c r="G701" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -22053,7 +22056,7 @@
         <v>7.49142599105835</v>
       </c>
       <c r="G702" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -22079,7 +22082,7 @@
         <v>7.39285516738892</v>
       </c>
       <c r="G703" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -22105,7 +22108,7 @@
         <v>7.38299798965454</v>
       </c>
       <c r="G704" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -22131,7 +22134,7 @@
         <v>7.29428291320801</v>
       </c>
       <c r="G705" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -22157,7 +22160,7 @@
         <v>7.35342597961426</v>
       </c>
       <c r="G706" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -22183,7 +22186,7 @@
         <v>7.20556879043579</v>
       </c>
       <c r="G707" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -22209,7 +22212,7 @@
         <v>7.31399822235107</v>
       </c>
       <c r="G708" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -22235,7 +22238,7 @@
         <v>7.26471185684204</v>
       </c>
       <c r="G709" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -22261,7 +22264,7 @@
         <v>6.94928407669067</v>
       </c>
       <c r="G710" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -22287,7 +22290,7 @@
         <v>7.04785490036011</v>
       </c>
       <c r="G711" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -22313,7 +22316,7 @@
         <v>7.0675687789917</v>
       </c>
       <c r="G712" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -22339,7 +22342,7 @@
         <v>6.99856901168823</v>
       </c>
       <c r="G713" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -22365,7 +22368,7 @@
         <v>6.95914077758789</v>
       </c>
       <c r="G714" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -22391,7 +22394,7 @@
         <v>6.91971206665039</v>
       </c>
       <c r="G715" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -22417,7 +22420,7 @@
         <v>6.88028383255005</v>
       </c>
       <c r="G716" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -22443,7 +22446,7 @@
         <v>6.95914077758789</v>
       </c>
       <c r="G717" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -22469,7 +22472,7 @@
         <v>6.87042617797852</v>
       </c>
       <c r="G718" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -22495,7 +22498,7 @@
         <v>6.93942594528198</v>
       </c>
       <c r="G719" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -22521,7 +22524,7 @@
         <v>6.88028383255005</v>
       </c>
       <c r="G720" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -22547,7 +22550,7 @@
         <v>6.81128406524658</v>
       </c>
       <c r="G721" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -22573,7 +22576,7 @@
         <v>6.87042617797852</v>
       </c>
       <c r="G722" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -22599,7 +22602,7 @@
         <v>6.86056900024414</v>
       </c>
       <c r="G723" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -22625,7 +22628,7 @@
         <v>6.94928407669067</v>
       </c>
       <c r="G724" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -22651,7 +22654,7 @@
         <v>6.8999981880188</v>
       </c>
       <c r="G725" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -22677,7 +22680,7 @@
         <v>6.96899795532227</v>
       </c>
       <c r="G726" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -22703,7 +22706,7 @@
         <v>6.88028383255005</v>
       </c>
       <c r="G727" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -22729,7 +22732,7 @@
         <v>6.86056900024414</v>
       </c>
       <c r="G728" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -22755,7 +22758,7 @@
         <v>6.96899795532227</v>
       </c>
       <c r="G729" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -22781,7 +22784,7 @@
         <v>6.8999981880188</v>
       </c>
       <c r="G730" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -22807,7 +22810,7 @@
         <v>6.95914077758789</v>
       </c>
       <c r="G731" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -22833,7 +22836,7 @@
         <v>6.8999981880188</v>
       </c>
       <c r="G732" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -22859,7 +22862,7 @@
         <v>6.87042617797852</v>
       </c>
       <c r="G733" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -22885,7 +22888,7 @@
         <v>6.85071182250977</v>
       </c>
       <c r="G734" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -22911,7 +22914,7 @@
         <v>6.87042617797852</v>
       </c>
       <c r="G735" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -22937,7 +22940,7 @@
         <v>6.8211407661438</v>
       </c>
       <c r="G736" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -22963,7 +22966,7 @@
         <v>6.88028383255005</v>
       </c>
       <c r="G737" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -22989,7 +22992,7 @@
         <v>6.8211407661438</v>
       </c>
       <c r="G738" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -23015,7 +23018,7 @@
         <v>6.80142593383789</v>
       </c>
       <c r="G739" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -23041,7 +23044,7 @@
         <v>6.8999981880188</v>
       </c>
       <c r="G740" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -23067,7 +23070,7 @@
         <v>6.8999981880188</v>
       </c>
       <c r="G741" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -23093,7 +23096,7 @@
         <v>6.93942594528198</v>
       </c>
       <c r="G742" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -23119,7 +23122,7 @@
         <v>6.97885513305664</v>
       </c>
       <c r="G743" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -23145,7 +23148,7 @@
         <v>6.94928407669067</v>
       </c>
       <c r="G744" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -23171,7 +23174,7 @@
         <v>6.98871183395386</v>
       </c>
       <c r="G745" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -23197,7 +23200,7 @@
         <v>7.15628290176392</v>
       </c>
       <c r="G746" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -23223,7 +23226,7 @@
         <v>7.09714078903198</v>
       </c>
       <c r="G747" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -23249,7 +23252,7 @@
         <v>7.11685514450073</v>
       </c>
       <c r="G748" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -23275,7 +23278,7 @@
         <v>7.12671184539795</v>
       </c>
       <c r="G749" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -23301,7 +23304,7 @@
         <v>6.97885513305664</v>
       </c>
       <c r="G750" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -23327,7 +23330,7 @@
         <v>6.99856901168823</v>
       </c>
       <c r="G751" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -23353,7 +23356,7 @@
         <v>6.99856901168823</v>
       </c>
       <c r="G752" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -23379,7 +23382,7 @@
         <v>7.01828384399414</v>
       </c>
       <c r="G753" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -23405,7 +23408,7 @@
         <v>6.99856901168823</v>
       </c>
       <c r="G754" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -23431,7 +23434,7 @@
         <v>6.99856901168823</v>
       </c>
       <c r="G755" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -23457,7 +23460,7 @@
         <v>7.01828384399414</v>
       </c>
       <c r="G756" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -23483,7 +23486,7 @@
         <v>6.99856901168823</v>
       </c>
       <c r="G757" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -23509,7 +23512,7 @@
         <v>6.97885513305664</v>
       </c>
       <c r="G758" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -23535,7 +23538,7 @@
         <v>7.03799819946289</v>
       </c>
       <c r="G759" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -23561,7 +23564,7 @@
         <v>7.02814102172852</v>
       </c>
       <c r="G760" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -23587,7 +23590,7 @@
         <v>7.0675687789917</v>
       </c>
       <c r="G761" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -23613,7 +23616,7 @@
         <v>7.11685514450073</v>
       </c>
       <c r="G762" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -23639,7 +23642,7 @@
         <v>7.34356880187988</v>
       </c>
       <c r="G763" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -23665,7 +23668,7 @@
         <v>7.17599821090698</v>
       </c>
       <c r="G764" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -23691,7 +23694,7 @@
         <v>7.17599821090698</v>
       </c>
       <c r="G765" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -23717,7 +23720,7 @@
         <v>7.17599821090698</v>
       </c>
       <c r="G766" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -23743,7 +23746,7 @@
         <v>7.08728313446045</v>
       </c>
       <c r="G767" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -23769,7 +23772,7 @@
         <v>7.04785490036011</v>
       </c>
       <c r="G768" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -23795,7 +23798,7 @@
         <v>7.1464262008667</v>
       </c>
       <c r="G769" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -23821,7 +23824,7 @@
         <v>7.15628290176392</v>
       </c>
       <c r="G770" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -23847,7 +23850,7 @@
         <v>7.19571208953857</v>
       </c>
       <c r="G771" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -23873,7 +23876,7 @@
         <v>7.1464262008667</v>
       </c>
       <c r="G772" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -23899,7 +23902,7 @@
         <v>7.1464262008667</v>
       </c>
       <c r="G773" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -23925,7 +23928,7 @@
         <v>7.24499797821045</v>
       </c>
       <c r="G774" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -23951,7 +23954,7 @@
         <v>7.39285516738892</v>
       </c>
       <c r="G775" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -23977,7 +23980,7 @@
         <v>7.62942600250244</v>
       </c>
       <c r="G776" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -24003,7 +24006,7 @@
         <v>7.49142599105835</v>
       </c>
       <c r="G777" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -24029,7 +24032,7 @@
         <v>7.41256904602051</v>
       </c>
       <c r="G778" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -24055,7 +24058,7 @@
         <v>7.42242622375488</v>
       </c>
       <c r="G779" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -24081,7 +24084,7 @@
         <v>7.39285516738892</v>
       </c>
       <c r="G780" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -24107,7 +24110,7 @@
         <v>7.34356880187988</v>
       </c>
       <c r="G781" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -24133,7 +24136,7 @@
         <v>7.39285516738892</v>
       </c>
       <c r="G782" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -24159,7 +24162,7 @@
         <v>7.40271186828613</v>
       </c>
       <c r="G783" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -24185,7 +24188,7 @@
         <v>7.39285516738892</v>
       </c>
       <c r="G784" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -24211,7 +24214,7 @@
         <v>7.44214105606079</v>
       </c>
       <c r="G785" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -24237,7 +24240,7 @@
         <v>7.40271186828613</v>
       </c>
       <c r="G786" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -24263,7 +24266,7 @@
         <v>7.39285516738892</v>
       </c>
       <c r="G787" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -24289,7 +24292,7 @@
         <v>7.39285516738892</v>
       </c>
       <c r="G788" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -24315,7 +24318,7 @@
         <v>7.39285516738892</v>
       </c>
       <c r="G789" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -24341,7 +24344,7 @@
         <v>7.38299798965454</v>
       </c>
       <c r="G790" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -24367,7 +24370,7 @@
         <v>7.3041410446167</v>
       </c>
       <c r="G791" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -24393,7 +24396,7 @@
         <v>7.49142599105835</v>
       </c>
       <c r="G792" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -24419,7 +24422,7 @@
         <v>7.38299798965454</v>
       </c>
       <c r="G793" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -24445,7 +24448,7 @@
         <v>7.38299798965454</v>
       </c>
       <c r="G794" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -24471,7 +24474,7 @@
         <v>7.29428291320801</v>
       </c>
       <c r="G795" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -24497,7 +24500,7 @@
         <v>7.24499797821045</v>
       </c>
       <c r="G796" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -24523,7 +24526,7 @@
         <v>7.31399822235107</v>
       </c>
       <c r="G797" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -24549,7 +24552,7 @@
         <v>7.39285516738892</v>
       </c>
       <c r="G798" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -24575,7 +24578,7 @@
         <v>7.33371210098267</v>
       </c>
       <c r="G799" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -24601,7 +24604,7 @@
         <v>7.29428291320801</v>
       </c>
       <c r="G800" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -24627,7 +24630,7 @@
         <v>7.25485515594482</v>
       </c>
       <c r="G801" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -24653,7 +24656,7 @@
         <v>7.19571208953857</v>
       </c>
       <c r="G802" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -24679,7 +24682,7 @@
         <v>7.19571208953857</v>
       </c>
       <c r="G803" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -24705,7 +24708,7 @@
         <v>7.21542596817017</v>
       </c>
       <c r="G804" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -24731,7 +24734,7 @@
         <v>7.39285516738892</v>
       </c>
       <c r="G805" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -24757,7 +24760,7 @@
         <v>7.29428291320801</v>
       </c>
       <c r="G806" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -24783,7 +24786,7 @@
         <v>7.34356880187988</v>
       </c>
       <c r="G807" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -24809,7 +24812,7 @@
         <v>7.19571208953857</v>
       </c>
       <c r="G808" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -24835,7 +24838,7 @@
         <v>7.19571208953857</v>
       </c>
       <c r="G809" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -24861,7 +24864,7 @@
         <v>7.23514080047607</v>
       </c>
       <c r="G810" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -24887,7 +24890,7 @@
         <v>7.23514080047607</v>
       </c>
       <c r="G811" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -24913,7 +24916,7 @@
         <v>7.09714078903198</v>
       </c>
       <c r="G812" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -24939,7 +24942,7 @@
         <v>7.1464262008667</v>
       </c>
       <c r="G813" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -24965,7 +24968,7 @@
         <v>7.15628290176392</v>
       </c>
       <c r="G814" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -24991,7 +24994,7 @@
         <v>7.1464262008667</v>
       </c>
       <c r="G815" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -25017,7 +25020,7 @@
         <v>7.10699796676636</v>
       </c>
       <c r="G816" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -25043,7 +25046,7 @@
         <v>7.1464262008667</v>
       </c>
       <c r="G817" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -25069,7 +25072,7 @@
         <v>7.20556879043579</v>
       </c>
       <c r="G818" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -25095,7 +25098,7 @@
         <v>7.38299798965454</v>
       </c>
       <c r="G819" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -25121,7 +25124,7 @@
         <v>7.54071187973022</v>
       </c>
       <c r="G820" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -25147,7 +25150,7 @@
         <v>7.62942600250244</v>
       </c>
       <c r="G821" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -25173,7 +25176,7 @@
         <v>7.63928318023682</v>
       </c>
       <c r="G822" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -25199,7 +25202,7 @@
         <v>7.41256904602051</v>
       </c>
       <c r="G823" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -25225,7 +25228,7 @@
         <v>7.40271186828613</v>
       </c>
       <c r="G824" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -25251,7 +25254,7 @@
         <v>7.40271186828613</v>
       </c>
       <c r="G825" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -25277,7 +25280,7 @@
         <v>7.34356880187988</v>
       </c>
       <c r="G826" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -25303,7 +25306,7 @@
         <v>7.33371210098267</v>
       </c>
       <c r="G827" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -25329,7 +25332,7 @@
         <v>7.29428291320801</v>
       </c>
       <c r="G828" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -25355,7 +25358,7 @@
         <v>7.39285516738892</v>
       </c>
       <c r="G829" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -25381,7 +25384,7 @@
         <v>7.35342597961426</v>
       </c>
       <c r="G830" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -25407,7 +25410,7 @@
         <v>7.33371210098267</v>
       </c>
       <c r="G831" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -25433,7 +25436,7 @@
         <v>7.37314081192017</v>
       </c>
       <c r="G832" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -25459,7 +25462,7 @@
         <v>7.45199823379517</v>
       </c>
       <c r="G833" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -25485,7 +25488,7 @@
         <v>7.37314081192017</v>
       </c>
       <c r="G834" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -25511,7 +25514,7 @@
         <v>7.39285516738892</v>
       </c>
       <c r="G835" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -25537,7 +25540,7 @@
         <v>7.39285516738892</v>
       </c>
       <c r="G836" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -25563,7 +25566,7 @@
         <v>7.35342597961426</v>
       </c>
       <c r="G837" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -25589,7 +25592,7 @@
         <v>7.37314081192017</v>
       </c>
       <c r="G838" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -25615,7 +25618,7 @@
         <v>7.4322829246521</v>
       </c>
       <c r="G839" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -25641,7 +25644,7 @@
         <v>7.37314081192017</v>
       </c>
       <c r="G840" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -25667,7 +25670,7 @@
         <v>7.4322829246521</v>
       </c>
       <c r="G841" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -25693,7 +25696,7 @@
         <v>7.33371210098267</v>
       </c>
       <c r="G842" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -25719,7 +25722,7 @@
         <v>7.4322829246521</v>
       </c>
       <c r="G843" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -25745,7 +25748,7 @@
         <v>7.49142599105835</v>
       </c>
       <c r="G844" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -25771,7 +25774,7 @@
         <v>7.45199823379517</v>
       </c>
       <c r="G845" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -25797,7 +25800,7 @@
         <v>7.41256904602051</v>
       </c>
       <c r="G846" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -25823,7 +25826,7 @@
         <v>7.25485515594482</v>
       </c>
       <c r="G847" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -25849,7 +25852,7 @@
         <v>7.25485515594482</v>
       </c>
       <c r="G848" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -25875,7 +25878,7 @@
         <v>7.39285516738892</v>
       </c>
       <c r="G849" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -25901,7 +25904,7 @@
         <v>7.39285516738892</v>
       </c>
       <c r="G850" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -25927,7 +25930,7 @@
         <v>7.25485515594482</v>
       </c>
       <c r="G851" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -25953,7 +25956,7 @@
         <v>7.35342597961426</v>
       </c>
       <c r="G852" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -25979,7 +25982,7 @@
         <v>7.35342597961426</v>
       </c>
       <c r="G853" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -26005,7 +26008,7 @@
         <v>7.29428291320801</v>
       </c>
       <c r="G854" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -26031,7 +26034,7 @@
         <v>7.29428291320801</v>
       </c>
       <c r="G855" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -26057,7 +26060,7 @@
         <v>7.15628290176392</v>
       </c>
       <c r="G856" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -26083,7 +26086,7 @@
         <v>7.17599821090698</v>
       </c>
       <c r="G857" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -26109,7 +26112,7 @@
         <v>7.13656902313232</v>
       </c>
       <c r="G858" t="s">
-        <v>364</v>
+        <v>303</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -26161,7 +26164,7 @@
         <v>7.17599821090698</v>
       </c>
       <c r="G860" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -26187,7 +26190,7 @@
         <v>7.15628290176392</v>
       </c>
       <c r="G861" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -26343,7 +26346,7 @@
         <v>7.13656902313232</v>
       </c>
       <c r="G867" t="s">
-        <v>364</v>
+        <v>303</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -26369,7 +26372,7 @@
         <v>7.15628290176392</v>
       </c>
       <c r="G868" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -26447,7 +26450,7 @@
         <v>7.15628290176392</v>
       </c>
       <c r="G871" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -26473,7 +26476,7 @@
         <v>7.13656902313232</v>
       </c>
       <c r="G872" t="s">
-        <v>364</v>
+        <v>303</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -26525,7 +26528,7 @@
         <v>7.39285516738892</v>
       </c>
       <c r="G874" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -26577,7 +26580,7 @@
         <v>7.25485515594482</v>
       </c>
       <c r="G876" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -27669,7 +27672,7 @@
         <v>7.39285516738892</v>
       </c>
       <c r="G918" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -27695,7 +27698,7 @@
         <v>7.29428291320801</v>
       </c>
       <c r="G919" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -27721,7 +27724,7 @@
         <v>7.29428291320801</v>
       </c>
       <c r="G920" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -27747,7 +27750,7 @@
         <v>7.39285516738892</v>
       </c>
       <c r="G921" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -27799,7 +27802,7 @@
         <v>7.29428291320801</v>
       </c>
       <c r="G923" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -27903,7 +27906,7 @@
         <v>7.17599821090698</v>
       </c>
       <c r="G927" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -27929,7 +27932,7 @@
         <v>7.17599821090698</v>
       </c>
       <c r="G928" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -27955,7 +27958,7 @@
         <v>7.17599821090698</v>
       </c>
       <c r="G929" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -28137,7 +28140,7 @@
         <v>7.15628290176392</v>
       </c>
       <c r="G936" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -28163,7 +28166,7 @@
         <v>7.13656902313232</v>
       </c>
       <c r="G937" t="s">
-        <v>364</v>
+        <v>303</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -28189,7 +28192,7 @@
         <v>7.17599821090698</v>
       </c>
       <c r="G938" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -68835,7 +68838,7 @@
     </row>
     <row r="2502">
       <c r="A2502" s="1" t="n">
-        <v>45961.6913078704</v>
+        <v>45961.3333333333</v>
       </c>
       <c r="B2502" t="n">
         <v>21606</v>
@@ -68856,6 +68859,32 @@
         <v>1152</v>
       </c>
       <c r="H2502" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2503">
+      <c r="A2503" s="1" t="n">
+        <v>45964.6910532407</v>
+      </c>
+      <c r="B2503" t="n">
+        <v>47100</v>
+      </c>
+      <c r="C2503" t="n">
+        <v>18.1800003051758</v>
+      </c>
+      <c r="D2503" t="n">
+        <v>17.7000007629395</v>
+      </c>
+      <c r="E2503" t="n">
+        <v>18.1599998474121</v>
+      </c>
+      <c r="F2503" t="n">
+        <v>17.7999992370605</v>
+      </c>
+      <c r="G2503" t="s">
+        <v>1153</v>
+      </c>
+      <c r="H2503" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ORS.MI.xlsx
+++ b/data/ORS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1156" uniqueCount="1156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1157" uniqueCount="1157">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,40 +38,40 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08406352996826</t>
+    <t xml:space="preserve">8.08406257629395</t>
   </si>
   <si>
     <t xml:space="preserve">ORS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98275852203369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06380176544189</t>
+    <t xml:space="preserve">7.98275899887085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06380271911621</t>
   </si>
   <si>
     <t xml:space="preserve">7.94223737716675</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82472515106201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93818426132202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9017162322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03948974609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92602872848511</t>
+    <t xml:space="preserve">7.82472467422485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93818616867065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90171670913696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03948783874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92602968215942</t>
   </si>
   <si>
     <t xml:space="preserve">7.86119413375854</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82067203521729</t>
+    <t xml:space="preserve">7.82067251205444</t>
   </si>
   <si>
     <t xml:space="preserve">7.93413305282593</t>
@@ -80,76 +80,76 @@
     <t xml:space="preserve">8.02328205108643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08811569213867</t>
+    <t xml:space="preserve">8.08811473846436</t>
   </si>
   <si>
     <t xml:space="preserve">8.14484596252441</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69910764694214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80446338653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97465419769287</t>
+    <t xml:space="preserve">7.69910717010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8044638633728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97465372085571</t>
   </si>
   <si>
     <t xml:space="preserve">8.01112365722656</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01517677307129</t>
+    <t xml:space="preserve">8.01517581939697</t>
   </si>
   <si>
     <t xml:space="preserve">7.79230737686157</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82877826690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34745407104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84093427658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90982055664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85714101791382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78015184402466</t>
+    <t xml:space="preserve">7.82877683639526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34745311737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84093332290649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9098219871521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8571400642395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78015089035034</t>
   </si>
   <si>
     <t xml:space="preserve">7.8449854850769</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9787073135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88550853729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95034217834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00302028656006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0192289352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9179253578186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10027313232422</t>
+    <t xml:space="preserve">7.97870588302612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88550615310669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95034074783325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00301933288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01922702789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91792440414429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1002721786499</t>
   </si>
   <si>
     <t xml:space="preserve">8.10432243347168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1853666305542</t>
+    <t xml:space="preserve">8.18536758422852</t>
   </si>
   <si>
     <t xml:space="preserve">8.20157527923584</t>
@@ -158,10 +158,10 @@
     <t xml:space="preserve">8.11242866516113</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07595825195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03138542175293</t>
+    <t xml:space="preserve">8.07595729827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03138446807861</t>
   </si>
   <si>
     <t xml:space="preserve">8.09621906280518</t>
@@ -173,10 +173,10 @@
     <t xml:space="preserve">8.05569744110107</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12053298950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2583065032959</t>
+    <t xml:space="preserve">8.12053394317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25830554962158</t>
   </si>
   <si>
     <t xml:space="preserve">8.4203929901123</t>
@@ -188,7 +188,7 @@
     <t xml:space="preserve">8.55816650390625</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42849636077881</t>
+    <t xml:space="preserve">8.42849826812744</t>
   </si>
   <si>
     <t xml:space="preserve">8.52429008483887</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">8.50802135467529</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60562896728516</t>
+    <t xml:space="preserve">8.60562801361084</t>
   </si>
   <si>
     <t xml:space="preserve">8.5324239730835</t>
@@ -209,22 +209,22 @@
     <t xml:space="preserve">8.61376190185547</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67069911956787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87404632568359</t>
+    <t xml:space="preserve">8.67070007324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87404727935791</t>
   </si>
   <si>
     <t xml:space="preserve">8.79270648956299</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90658092498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86591339111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94724941253662</t>
+    <t xml:space="preserve">8.90657997131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86591148376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94725036621094</t>
   </si>
   <si>
     <t xml:space="preserve">8.93911743164062</t>
@@ -233,46 +233,46 @@
     <t xml:space="preserve">8.78457355499268</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74390316009521</t>
+    <t xml:space="preserve">8.74390411376953</t>
   </si>
   <si>
     <t xml:space="preserve">8.91471385955811</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92285060882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1099271774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07739353179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11806201934814</t>
+    <t xml:space="preserve">8.92284965515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10992813110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.077392578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11806297302246</t>
   </si>
   <si>
     <t xml:space="preserve">9.1343297958374</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15059757232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15873146057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73576927185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67883205413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8577766418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72763538360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7032356262207</t>
+    <t xml:space="preserve">9.15059852600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15873050689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7357702255249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6788330078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85777854919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72763729095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70323371887207</t>
   </si>
   <si>
     <t xml:space="preserve">8.66256523132324</t>
@@ -281,7 +281,7 @@
     <t xml:space="preserve">8.69510078430176</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62189674377441</t>
+    <t xml:space="preserve">8.6218957901001</t>
   </si>
   <si>
     <t xml:space="preserve">8.80084133148193</t>
@@ -293,13 +293,13 @@
     <t xml:space="preserve">8.68696689605713</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54869174957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54055690765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58122825622559</t>
+    <t xml:space="preserve">8.54869270324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54055786132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58122730255127</t>
   </si>
   <si>
     <t xml:space="preserve">8.46735286712646</t>
@@ -311,43 +311,43 @@
     <t xml:space="preserve">8.49988746643066</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45108509063721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63003158569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80897521972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89031410217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93098258972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96351909637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05299091339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30514144897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10179328918457</t>
+    <t xml:space="preserve">8.45108413696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63003063201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80897617340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89031314849854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93098449707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96351718902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05299186706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30514049530029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10179424285889</t>
   </si>
   <si>
     <t xml:space="preserve">9.19126605987549</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35394287109375</t>
+    <t xml:space="preserve">9.35394382476807</t>
   </si>
   <si>
     <t xml:space="preserve">9.4759521484375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54915523529053</t>
+    <t xml:space="preserve">9.54915618896484</t>
   </si>
   <si>
     <t xml:space="preserve">9.58982467651367</t>
@@ -356,10 +356,10 @@
     <t xml:space="preserve">9.66303157806396</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71996784210205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85824394226074</t>
+    <t xml:space="preserve">9.71996688842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85824489593506</t>
   </si>
   <si>
     <t xml:space="preserve">10.0046529769897</t>
@@ -368,28 +368,28 @@
     <t xml:space="preserve">10.240535736084</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2486686706543</t>
+    <t xml:space="preserve">10.2486696243286</t>
   </si>
   <si>
     <t xml:space="preserve">10.3381414413452</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5984258651733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4276142120361</t>
+    <t xml:space="preserve">10.598424911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4276151657104</t>
   </si>
   <si>
     <t xml:space="preserve">10.4032125473022</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5252208709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.460150718689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5658903121948</t>
+    <t xml:space="preserve">10.525218963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4601497650146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5658912658691</t>
   </si>
   <si>
     <t xml:space="preserve">10.5821561813354</t>
@@ -398,13 +398,13 @@
     <t xml:space="preserve">10.7773704528809</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9807186126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8749761581421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6553630828857</t>
+    <t xml:space="preserve">10.9807157516479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8749771118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6553621292114</t>
   </si>
   <si>
     <t xml:space="preserve">10.6797637939453</t>
@@ -413,7 +413,7 @@
     <t xml:space="preserve">10.5740242004395</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5170869827271</t>
+    <t xml:space="preserve">10.5170860290527</t>
   </si>
   <si>
     <t xml:space="preserve">10.5414886474609</t>
@@ -428,10 +428,10 @@
     <t xml:space="preserve">10.8180379867554</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6878976821899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.761100769043</t>
+    <t xml:space="preserve">10.6878967285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7611026763916</t>
   </si>
   <si>
     <t xml:space="preserve">10.6472282409668</t>
@@ -440,10 +440,10 @@
     <t xml:space="preserve">10.8993787765503</t>
   </si>
   <si>
-    <t xml:space="preserve">10.883111000061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.671630859375</t>
+    <t xml:space="preserve">10.8831100463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6716299057007</t>
   </si>
   <si>
     <t xml:space="preserve">10.7367010116577</t>
@@ -452,13 +452,13 @@
     <t xml:space="preserve">11.0051193237305</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0213861465454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1840629577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4036779403687</t>
+    <t xml:space="preserve">11.0213871002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.184063911438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4036769866943</t>
   </si>
   <si>
     <t xml:space="preserve">11.3955430984497</t>
@@ -467,31 +467,31 @@
     <t xml:space="preserve">11.3386068344116</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3223390579224</t>
+    <t xml:space="preserve">11.322338104248</t>
   </si>
   <si>
     <t xml:space="preserve">11.3304738998413</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3630084991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0783233642578</t>
+    <t xml:space="preserve">11.3630094528198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0783224105835</t>
   </si>
   <si>
     <t xml:space="preserve">10.606559753418</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8424415588379</t>
+    <t xml:space="preserve">10.8424425125122</t>
   </si>
   <si>
     <t xml:space="preserve">10.8505744934082</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6390943527222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4113454818726</t>
+    <t xml:space="preserve">10.6390953063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4113464355469</t>
   </si>
   <si>
     <t xml:space="preserve">10.2080011367798</t>
@@ -503,34 +503,34 @@
     <t xml:space="preserve">10.232400894165</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3218746185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3706760406494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3300065994263</t>
+    <t xml:space="preserve">10.321873664856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3706789016724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3300085067749</t>
   </si>
   <si>
     <t xml:space="preserve">10.3056058883667</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2568035125732</t>
+    <t xml:space="preserve">10.2568044662476</t>
   </si>
   <si>
     <t xml:space="preserve">10.1835975646973</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4845514297485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3625431060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4438810348511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8587083816528</t>
+    <t xml:space="preserve">10.4845504760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3625421524048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4438819885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8587093353271</t>
   </si>
   <si>
     <t xml:space="preserve">10.9237794876099</t>
@@ -542,22 +542,22 @@
     <t xml:space="preserve">11.0620565414429</t>
   </si>
   <si>
-    <t xml:space="preserve">11.102725982666</t>
+    <t xml:space="preserve">11.1027250289917</t>
   </si>
   <si>
     <t xml:space="preserve">11.1433944702148</t>
   </si>
   <si>
-    <t xml:space="preserve">11.175929069519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1352596282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0701894760132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1189937591553</t>
+    <t xml:space="preserve">11.1759281158447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1352615356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0701904296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.118992805481</t>
   </si>
   <si>
     <t xml:space="preserve">11.1515283584595</t>
@@ -566,16 +566,16 @@
     <t xml:space="preserve">11.2247323989868</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0457887649536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5008182525635</t>
+    <t xml:space="preserve">11.0457878112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5008192062378</t>
   </si>
   <si>
     <t xml:space="preserve">10.1347951889038</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36161231994629</t>
+    <t xml:space="preserve">8.36161136627197</t>
   </si>
   <si>
     <t xml:space="preserve">8.01999092102051</t>
@@ -596,19 +596,19 @@
     <t xml:space="preserve">8.3128080368042</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18266868591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34534454345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23960494995117</t>
+    <t xml:space="preserve">8.18266773223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34534645080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23960399627686</t>
   </si>
   <si>
     <t xml:space="preserve">8.49175453186035</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58936023712158</t>
+    <t xml:space="preserve">8.5893611907959</t>
   </si>
   <si>
     <t xml:space="preserve">8.76017284393311</t>
@@ -617,10 +617,10 @@
     <t xml:space="preserve">8.29654216766357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25587272644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17453384399414</t>
+    <t xml:space="preserve">8.25587368011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17453289031982</t>
   </si>
   <si>
     <t xml:space="preserve">8.1908016204834</t>
@@ -635,22 +635,22 @@
     <t xml:space="preserve">8.14199829101562</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15826606750488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1663990020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12166213989258</t>
+    <t xml:space="preserve">8.15826511383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16640090942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12166500091553</t>
   </si>
   <si>
     <t xml:space="preserve">8.05252552032471</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89798164367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85731267929077</t>
+    <t xml:space="preserve">7.89798212051392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85731315612793</t>
   </si>
   <si>
     <t xml:space="preserve">7.93051767349243</t>
@@ -659,64 +659,64 @@
     <t xml:space="preserve">7.90611457824707</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93865251541138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84917783737183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80850982666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62956380844116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57262754440308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48315620422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66616678237915</t>
+    <t xml:space="preserve">7.93865156173706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84917879104614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80850887298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62956476211548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57262802124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48315572738647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66616725921631</t>
   </si>
   <si>
     <t xml:space="preserve">7.60516309738159</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54009246826172</t>
+    <t xml:space="preserve">7.54009294509888</t>
   </si>
   <si>
     <t xml:space="preserve">7.52382373809814</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47908735275269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61329793930054</t>
+    <t xml:space="preserve">7.47908687591553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61329746246338</t>
   </si>
   <si>
     <t xml:space="preserve">7.54822540283203</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56449270248413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50755500793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46688604354858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49129009246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49942302703857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31234455108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27980899810791</t>
+    <t xml:space="preserve">7.56449413299561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50755739212036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46688652038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49129056930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49942207336426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31234407424927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27980804443359</t>
   </si>
   <si>
     <t xml:space="preserve">7.37741422653198</t>
@@ -725,43 +725,43 @@
     <t xml:space="preserve">7.38554906845093</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36928081512451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3204779624939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34487915039062</t>
+    <t xml:space="preserve">7.36928129196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32047748565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34487867355347</t>
   </si>
   <si>
     <t xml:space="preserve">7.28794240951538</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04392576217651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15780115127563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39368295669556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42621755599976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40181636810303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30421018600464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36114883422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20660352706909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35301351547241</t>
+    <t xml:space="preserve">7.04392623901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15780067443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39368200302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42621803283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40181732177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3042106628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36114835739136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20660400390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3530125617981</t>
   </si>
   <si>
     <t xml:space="preserve">7.33674573898315</t>
@@ -770,46 +770,46 @@
     <t xml:space="preserve">7.27167463302612</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23100471496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32861185073853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26354122161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23913955688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22287225723267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24727296829224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44248676300049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25540733337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18220186233521</t>
+    <t xml:space="preserve">7.23100519180298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32861137390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26354074478149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23914003372192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22287130355835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24727249145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44248628616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25540685653687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18220138549805</t>
   </si>
   <si>
     <t xml:space="preserve">7.29607582092285</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16593456268311</t>
+    <t xml:space="preserve">7.16593408584595</t>
   </si>
   <si>
     <t xml:space="preserve">7.14153337478638</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0520601272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07646179199219</t>
+    <t xml:space="preserve">7.05205965042114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07646322250366</t>
   </si>
   <si>
     <t xml:space="preserve">7.0357928276062</t>
@@ -821,73 +821,73 @@
     <t xml:space="preserve">6.87311506271362</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67790222167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85124731063843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93379259109497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2639741897583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14841032028198</t>
+    <t xml:space="preserve">6.677903175354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85124778747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93379211425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26397323608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14840984344482</t>
   </si>
   <si>
     <t xml:space="preserve">7.09888315200806</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18142938613892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16491937637329</t>
+    <t xml:space="preserve">7.18142890930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16491842269897</t>
   </si>
   <si>
     <t xml:space="preserve">7.14015579223633</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21444654464722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17317390441895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97506427764893</t>
+    <t xml:space="preserve">7.21444606781006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1731743812561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97506475448608</t>
   </si>
   <si>
     <t xml:space="preserve">6.84299278259277</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6036114692688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62012100219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67790174484253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80997467041016</t>
+    <t xml:space="preserve">6.60361242294312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62012147903442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67790269851685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.809974193573</t>
   </si>
   <si>
     <t xml:space="preserve">6.54583024978638</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31470441818237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32295894622803</t>
+    <t xml:space="preserve">6.31470394134521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32295846939087</t>
   </si>
   <si>
     <t xml:space="preserve">6.34772253036499</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38074064254761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39724969863892</t>
+    <t xml:space="preserve">6.38074016571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3972487449646</t>
   </si>
   <si>
     <t xml:space="preserve">6.4715404510498</t>
@@ -899,247 +899,247 @@
     <t xml:space="preserve">6.22390413284302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09183216094971</t>
+    <t xml:space="preserve">6.09183168411255</t>
   </si>
   <si>
     <t xml:space="preserve">5.90197801589966</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9597601890564</t>
+    <t xml:space="preserve">5.95975971221924</t>
   </si>
   <si>
     <t xml:space="preserve">5.99277782440186</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20739555358887</t>
+    <t xml:space="preserve">6.20739507675171</t>
   </si>
   <si>
     <t xml:space="preserve">6.14135980606079</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19088697433472</t>
+    <t xml:space="preserve">6.19088649749756</t>
   </si>
   <si>
     <t xml:space="preserve">6.14961385726929</t>
   </si>
   <si>
+    <t xml:space="preserve">6.07532358169556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25692272186279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00928735733032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9845232963562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12485027313232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13310480117798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27343082427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44677639007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55408525466919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51281213760376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36423110961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24041366577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21565008163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23215961456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24866819381714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11659622192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10834074020386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05055904388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89372444152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77816104888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69561529159546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79466915130615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80292367935181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82768774032593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78641510009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73688745498657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85245132446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29819583892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18263244628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15786790847778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03405046463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08357763290405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81943368911743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91848707199097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86070585250854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76165199279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75339651107788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81117820739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70387029647827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74514245986938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83594179153442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71212482452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84419727325439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94325065612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96801424026489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8772144317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88546943664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93499660491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02579593658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0670690536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3889946937561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19914054870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04230451583862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05881452560425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95150566101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17437744140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17601919174194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29349803924561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25993204116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20958423614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09210586547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10888910293579</t>
+  </si>
+  <si>
     <t xml:space="preserve">6.0753231048584</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25692272186279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00928783416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9845232963562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12485074996948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13310480117798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27343130111694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44677639007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55408477783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51281213760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3642315864563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24041414260864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21565055847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23215961456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24866819381714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11659622192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10834121704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05055952072144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89372444152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.778160572052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6956148147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79466915130615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80292320251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82768774032593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78641510009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73688793182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85245084762573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29819583892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1826319694519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15786838531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03405046463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08357810974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81943368911743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91848707199097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86070537567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76165199279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75339651107788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81117820739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70387029647827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74514198303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83594226837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71212434768677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84419679641724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94325065612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96801424026489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87721490859985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88546943664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93499660491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02579593658447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0670690536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3889946937561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19914054870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04230499267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05881452560425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95150566101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17437744140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17601919174194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29349803924561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25993251800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20958471298218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09210586547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10888910293579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07532358169556</t>
-  </si>
-  <si>
     <t xml:space="preserve">6.14245367050171</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05854034423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02497482299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97462797164917</t>
+    <t xml:space="preserve">6.05854082107544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02497529983521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97462701797485</t>
   </si>
   <si>
     <t xml:space="preserve">5.95784473419189</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15923643112183</t>
+    <t xml:space="preserve">6.15923690795898</t>
   </si>
   <si>
     <t xml:space="preserve">6.12567138671875</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19280195236206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42775964736938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71306419372559</t>
+    <t xml:space="preserve">6.1928014755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42775917053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7130651473999</t>
   </si>
   <si>
     <t xml:space="preserve">6.64593458175659</t>
@@ -1148,25 +1148,25 @@
     <t xml:space="preserve">6.69628190994263</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78019571304321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7298469543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.629150390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56201982498169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54523801803589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67949867248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66271638870239</t>
+    <t xml:space="preserve">6.78019523620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72984743118286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62915086746216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56202030181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54523706436157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67949962615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66271686553955</t>
   </si>
   <si>
     <t xml:space="preserve">6.57880353927612</t>
@@ -1181,106 +1181,106 @@
     <t xml:space="preserve">6.22636747360229</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36062812805176</t>
+    <t xml:space="preserve">6.36062908172607</t>
   </si>
   <si>
     <t xml:space="preserve">5.67253875732422</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55506038665771</t>
+    <t xml:space="preserve">5.55506086349487</t>
   </si>
   <si>
     <t xml:space="preserve">5.68932247161865</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62219190597534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5382776260376</t>
+    <t xml:space="preserve">5.62219142913818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53827810287476</t>
   </si>
   <si>
     <t xml:space="preserve">5.43758249282837</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45436573028564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60540866851807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5214958190918</t>
+    <t xml:space="preserve">5.45436525344849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60540819168091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52149629592896</t>
   </si>
   <si>
     <t xml:space="preserve">5.50471305847168</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48792934417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35366916656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37045049667358</t>
+    <t xml:space="preserve">5.48793029785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35366868972778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3704514503479</t>
   </si>
   <si>
     <t xml:space="preserve">5.42079925537109</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28653860092163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30332136154175</t>
+    <t xml:space="preserve">5.28653812408447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30332088470459</t>
   </si>
   <si>
     <t xml:space="preserve">5.26975536346436</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38723373413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32010364532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65575695037842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75645351409912</t>
+    <t xml:space="preserve">5.38723421096802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32010316848755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65575647354126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75645303726196</t>
   </si>
   <si>
     <t xml:space="preserve">5.70610475540161</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72288656234741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73967027664185</t>
+    <t xml:space="preserve">5.72288751602173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73966979980469</t>
   </si>
   <si>
     <t xml:space="preserve">5.63897466659546</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57184362411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18584203720093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2026252746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21940755844116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16905975341797</t>
+    <t xml:space="preserve">5.57184410095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18584156036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20262479782104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21940803527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16905927658081</t>
   </si>
   <si>
     <t xml:space="preserve">5.13549375534058</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10192966461182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95088529586792</t>
+    <t xml:space="preserve">5.1019287109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9508843421936</t>
   </si>
   <si>
     <t xml:space="preserve">5.03479814529419</t>
@@ -1289,16 +1289,16 @@
     <t xml:space="preserve">5.15227699279785</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11871147155762</t>
+    <t xml:space="preserve">5.11871099472046</t>
   </si>
   <si>
     <t xml:space="preserve">5.06836318969727</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08514595031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23618984222412</t>
+    <t xml:space="preserve">5.08514642715454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23619031906128</t>
   </si>
   <si>
     <t xml:space="preserve">5.25297260284424</t>
@@ -1307,7 +1307,7 @@
     <t xml:space="preserve">5.33688640594482</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79001760482788</t>
+    <t xml:space="preserve">5.79001808166504</t>
   </si>
   <si>
     <t xml:space="preserve">5.77323532104492</t>
@@ -1322,13 +1322,13 @@
     <t xml:space="preserve">4.79984140396118</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59844875335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36349201202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31314420700073</t>
+    <t xml:space="preserve">4.59844827651978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36349248886108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31314373016357</t>
   </si>
   <si>
     <t xml:space="preserve">4.19566535949707</t>
@@ -1337,58 +1337,58 @@
     <t xml:space="preserve">4.11175155639648</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02783823013306</t>
+    <t xml:space="preserve">4.02783870697021</t>
   </si>
   <si>
     <t xml:space="preserve">4.17049074172974</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06979560852051</t>
+    <t xml:space="preserve">4.06979608535767</t>
   </si>
   <si>
     <t xml:space="preserve">4.12014293670654</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34670877456665</t>
+    <t xml:space="preserve">4.34670925140381</t>
   </si>
   <si>
     <t xml:space="preserve">4.17888164520264</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04462146759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15370798110962</t>
+    <t xml:space="preserve">4.04462099075317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15370845794678</t>
   </si>
   <si>
     <t xml:space="preserve">4.26279640197754</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16210031509399</t>
+    <t xml:space="preserve">4.16209983825684</t>
   </si>
   <si>
     <t xml:space="preserve">4.14531803131104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9942729473114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09496927261353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98588180541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27957820892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22922992706299</t>
+    <t xml:space="preserve">3.99427318572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09496879577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98588132858276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2795786857605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22923040390015</t>
   </si>
   <si>
     <t xml:space="preserve">4.21244812011719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03622961044312</t>
+    <t xml:space="preserve">4.03623008728027</t>
   </si>
   <si>
     <t xml:space="preserve">4.12877893447876</t>
@@ -1400,49 +1400,49 @@
     <t xml:space="preserve">4.07770156860352</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00108480453491</t>
+    <t xml:space="preserve">4.00108432769775</t>
   </si>
   <si>
     <t xml:space="preserve">4.20539569854736</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37565469741821</t>
+    <t xml:space="preserve">4.37565422058105</t>
   </si>
   <si>
     <t xml:space="preserve">4.21390867233276</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22242164611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25647354125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24796009063721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32457637786865</t>
+    <t xml:space="preserve">4.22242116928101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25647401809692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24796056747437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32457685470581</t>
   </si>
   <si>
     <t xml:space="preserve">4.30755090713501</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23944759368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35862874984741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51186180114746</t>
+    <t xml:space="preserve">4.23944711685181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35862827301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51186227798462</t>
   </si>
   <si>
     <t xml:space="preserve">5.5334153175354</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9420371055603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89095878601074</t>
+    <t xml:space="preserve">5.94203662872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8909592628479</t>
   </si>
   <si>
     <t xml:space="preserve">5.73772573471069</t>
@@ -1451,7 +1451,7 @@
     <t xml:space="preserve">5.5504412651062</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5844931602478</t>
+    <t xml:space="preserve">5.58449268341064</t>
   </si>
   <si>
     <t xml:space="preserve">5.567467212677</t>
@@ -1460,49 +1460,49 @@
     <t xml:space="preserve">5.41423368453979</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26100158691406</t>
+    <t xml:space="preserve">5.26100063323975</t>
   </si>
   <si>
     <t xml:space="preserve">5.48233795166016</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44828605651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6015191078186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66962289810181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51638889312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70367431640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32910442352295</t>
+    <t xml:space="preserve">5.4482855796814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60151863098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66962242126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51638984680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70367479324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32910490036011</t>
   </si>
   <si>
     <t xml:space="preserve">5.27802705764771</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43126010894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31207895278931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2269492149353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00561237335205</t>
+    <t xml:space="preserve">5.43126058578491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31207847595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22694873809814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00561285018921</t>
   </si>
   <si>
     <t xml:space="preserve">4.95453500747681</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93750905990601</t>
+    <t xml:space="preserve">4.93750953674316</t>
   </si>
   <si>
     <t xml:space="preserve">5.05669021606445</t>
@@ -1511,28 +1511,28 @@
     <t xml:space="preserve">5.03966426849365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97156095504761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88643169403076</t>
+    <t xml:space="preserve">4.97156143188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8864312171936</t>
   </si>
   <si>
     <t xml:space="preserve">5.02263879776001</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92048358917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9034571647644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.852379322052</t>
+    <t xml:space="preserve">4.92048311233521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90345764160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85237979888916</t>
   </si>
   <si>
     <t xml:space="preserve">4.8694052696228</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34613037109375</t>
+    <t xml:space="preserve">5.34613084793091</t>
   </si>
   <si>
     <t xml:space="preserve">5.2439751625061</t>
@@ -1541,16 +1541,16 @@
     <t xml:space="preserve">5.36315631866455</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38018226623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2099232673645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15884590148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10776805877686</t>
+    <t xml:space="preserve">5.38018321990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20992279052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15884637832642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10776853561401</t>
   </si>
   <si>
     <t xml:space="preserve">4.98858642578125</t>
@@ -1562,37 +1562,37 @@
     <t xml:space="preserve">5.1928973197937</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17587089538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14181995391846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07371616363525</t>
+    <t xml:space="preserve">5.1758713722229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1418194770813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07371664047241</t>
   </si>
   <si>
     <t xml:space="preserve">4.68212080001831</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54591369628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59699153900146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57996559143066</t>
+    <t xml:space="preserve">4.5459132194519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59699106216431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57996511459351</t>
   </si>
   <si>
     <t xml:space="preserve">4.63104295730591</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78427648544312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76725006103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81832790374756</t>
+    <t xml:space="preserve">4.78427600860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.767249584198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8183274269104</t>
   </si>
   <si>
     <t xml:space="preserve">4.80130195617676</t>
@@ -1604,19 +1604,19 @@
     <t xml:space="preserve">5.61854457855225</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46531200408936</t>
+    <t xml:space="preserve">5.4653115272522</t>
   </si>
   <si>
     <t xml:space="preserve">5.49936389923096</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63557100296021</t>
+    <t xml:space="preserve">5.63557004928589</t>
   </si>
   <si>
     <t xml:space="preserve">5.68664836883545</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65259647369385</t>
+    <t xml:space="preserve">5.65259695053101</t>
   </si>
   <si>
     <t xml:space="preserve">5.85690689086914</t>
@@ -1628,13 +1628,13 @@
     <t xml:space="preserve">6.31660652160645</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33363246917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29958057403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35065889358521</t>
+    <t xml:space="preserve">6.3336329460144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2995810508728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35065841674805</t>
   </si>
   <si>
     <t xml:space="preserve">6.43578767776489</t>
@@ -1643,22 +1643,22 @@
     <t xml:space="preserve">6.55496883392334</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69117641448975</t>
+    <t xml:space="preserve">6.69117593765259</t>
   </si>
   <si>
     <t xml:space="preserve">6.79333162307739</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15087461471558</t>
+    <t xml:space="preserve">7.15087509155273</t>
   </si>
   <si>
     <t xml:space="preserve">7.08277082443237</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87846088409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77630567550659</t>
+    <t xml:space="preserve">6.87846040725708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77630519866943</t>
   </si>
   <si>
     <t xml:space="preserve">6.84440898895264</t>
@@ -1670,16 +1670,16 @@
     <t xml:space="preserve">6.75927972793579</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5379433631897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72522783279419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65712451934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91251277923584</t>
+    <t xml:space="preserve">6.53794288635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72522830963135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65712404251099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91251230239868</t>
   </si>
   <si>
     <t xml:space="preserve">6.8954873085022</t>
@@ -1691,52 +1691,52 @@
     <t xml:space="preserve">7.17302179336548</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05085372924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1206636428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57443141937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97584247589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02820014953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06310558319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99329519271851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0107479095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94093656539917</t>
+    <t xml:space="preserve">7.05085277557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12066411972046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57443237304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97584199905396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02819919586182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0631046295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99329423904419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01074695587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94093799591064</t>
   </si>
   <si>
     <t xml:space="preserve">8.13291454315186</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15036869049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16781997680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18527412414551</t>
+    <t xml:space="preserve">8.15036678314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16782093048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18527317047119</t>
   </si>
   <si>
     <t xml:space="preserve">8.34234714508057</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11546230316162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25508308410645</t>
+    <t xml:space="preserve">8.11546325683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25508403778076</t>
   </si>
   <si>
     <t xml:space="preserve">8.08055686950684</t>
@@ -1745,52 +1745,52 @@
     <t xml:space="preserve">8.20272445678711</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95838832855225</t>
+    <t xml:space="preserve">7.95838928222656</t>
   </si>
   <si>
     <t xml:space="preserve">8.37725162506104</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3248929977417</t>
+    <t xml:space="preserve">8.32489395141602</t>
   </si>
   <si>
     <t xml:space="preserve">8.81356716156006</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58668327331543</t>
+    <t xml:space="preserve">8.58668231964111</t>
   </si>
   <si>
     <t xml:space="preserve">8.53432464599609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69139957427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60413551330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72630405426025</t>
+    <t xml:space="preserve">8.69139862060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60413455963135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72630500793457</t>
   </si>
   <si>
     <t xml:space="preserve">8.42960929870605</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28998851776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30744075775146</t>
+    <t xml:space="preserve">8.28998947143555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30744171142578</t>
   </si>
   <si>
     <t xml:space="preserve">8.04565238952637</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85367298126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41215705871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22017860412598</t>
+    <t xml:space="preserve">7.85367345809937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41215801239014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22017765045166</t>
   </si>
   <si>
     <t xml:space="preserve">8.44706249237061</t>
@@ -1799,10 +1799,10 @@
     <t xml:space="preserve">8.3597993850708</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09801006317139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23763084411621</t>
+    <t xml:space="preserve">8.09800910949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23762989044189</t>
   </si>
   <si>
     <t xml:space="preserve">8.48196792602539</t>
@@ -1817,34 +1817,34 @@
     <t xml:space="preserve">8.65649318695068</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51687335968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46451473236084</t>
+    <t xml:space="preserve">8.51687240600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46451377868652</t>
   </si>
   <si>
     <t xml:space="preserve">8.49942016601562</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5692310333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99161720275879</t>
+    <t xml:space="preserve">8.56923007965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99161815643311</t>
   </si>
   <si>
     <t xml:space="preserve">9.59893417358398</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77346038818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81709289550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29351234436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46804046630859</t>
+    <t xml:space="preserve">9.77345943450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81709098815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29351425170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46803951263428</t>
   </si>
   <si>
     <t xml:space="preserve">9.55530261993408</t>
@@ -1853,19 +1853,19 @@
     <t xml:space="preserve">9.64256572723389</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90435600280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33714485168457</t>
+    <t xml:space="preserve">9.9043550491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33714580535889</t>
   </si>
   <si>
     <t xml:space="preserve">9.9479866027832</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8607234954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5151958465576</t>
+    <t xml:space="preserve">9.86072254180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5151968002319</t>
   </si>
   <si>
     <t xml:space="preserve">10.4279327392578</t>
@@ -1877,13 +1877,13 @@
     <t xml:space="preserve">10.6024589538574</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8206176757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7333545684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7769861221313</t>
+    <t xml:space="preserve">10.8206167221069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7333536148071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.776985168457</t>
   </si>
   <si>
     <t xml:space="preserve">10.2970390319824</t>
@@ -1892,40 +1892,40 @@
     <t xml:space="preserve">10.3843011856079</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3406705856323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.209774017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2534074783325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0788803100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51167011260986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72982788085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68619728088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98809432983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42440891265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6496171951294</t>
+    <t xml:space="preserve">10.340669631958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2097749710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2534065246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0788822174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51167106628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72982883453369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68619823455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98809242248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42440795898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6496162414551</t>
   </si>
   <si>
     <t xml:space="preserve">11.562352180481</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7805109024048</t>
+    <t xml:space="preserve">11.7805099487305</t>
   </si>
   <si>
     <t xml:space="preserve">11.9114036560059</t>
@@ -1934,7 +1934,7 @@
     <t xml:space="preserve">11.9550352096558</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6932468414307</t>
+    <t xml:space="preserve">11.693247795105</t>
   </si>
   <si>
     <t xml:space="preserve">12.3040885925293</t>
@@ -1955,16 +1955,16 @@
     <t xml:space="preserve">11.8677730560303</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6059846878052</t>
+    <t xml:space="preserve">11.6059837341309</t>
   </si>
   <si>
     <t xml:space="preserve">10.9515113830566</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0422983169556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3005638122559</t>
+    <t xml:space="preserve">12.0422992706299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3005647659302</t>
   </si>
   <si>
     <t xml:space="preserve">11.3441953659058</t>
@@ -1973,31 +1973,31 @@
     <t xml:space="preserve">10.9951429367065</t>
   </si>
   <si>
-    <t xml:space="preserve">10.471565246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9078798294067</t>
+    <t xml:space="preserve">10.4715642929077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9078807830811</t>
   </si>
   <si>
     <t xml:space="preserve">11.4314584732056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0387725830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9899406433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.74560546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5361728668213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5187215805054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6234369277954</t>
+    <t xml:space="preserve">11.0387735366821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9899415969849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7456045150757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5361738204956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5187206268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6234359741211</t>
   </si>
   <si>
     <t xml:space="preserve">11.4489107131958</t>
@@ -2018,7 +2018,7 @@
     <t xml:space="preserve">11.0998582839966</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8031644821167</t>
+    <t xml:space="preserve">10.803165435791</t>
   </si>
   <si>
     <t xml:space="preserve">10.7508058547974</t>
@@ -2030,13 +2030,13 @@
     <t xml:space="preserve">10.1050596237183</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81839179992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69297409057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71089172363281</t>
+    <t xml:space="preserve">9.81839275360107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69297313690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7108907699585</t>
   </si>
   <si>
     <t xml:space="preserve">10.1408929824829</t>
@@ -2051,16 +2051,16 @@
     <t xml:space="preserve">10.1229763031006</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1588106155396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0692253112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0871438980103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4633951187134</t>
+    <t xml:space="preserve">10.1588096618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0692262649536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0871429443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4633960723877</t>
   </si>
   <si>
     <t xml:space="preserve">10.7858972549438</t>
@@ -2087,13 +2087,13 @@
     <t xml:space="preserve">10.5888118743896</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5171461105347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8575639724731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9113159179688</t>
+    <t xml:space="preserve">10.5171451568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8575649261475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9113149642944</t>
   </si>
   <si>
     <t xml:space="preserve">10.6067295074463</t>
@@ -2102,13 +2102,13 @@
     <t xml:space="preserve">10.6604795455933</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3021440505981</t>
+    <t xml:space="preserve">10.3021450042725</t>
   </si>
   <si>
     <t xml:space="preserve">10.4096450805664</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3558940887451</t>
+    <t xml:space="preserve">10.3558950424194</t>
   </si>
   <si>
     <t xml:space="preserve">10.6783971786499</t>
@@ -2120,16 +2120,16 @@
     <t xml:space="preserve">10.535062789917</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1800651550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9829807281494</t>
+    <t xml:space="preserve">11.1800661087036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9829816818237</t>
   </si>
   <si>
     <t xml:space="preserve">11.4846515655518</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3771514892578</t>
+    <t xml:space="preserve">11.3771505355835</t>
   </si>
   <si>
     <t xml:space="preserve">11.7354869842529</t>
@@ -2150,7 +2150,7 @@
     <t xml:space="preserve">12.2371559143066</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3267402648926</t>
+    <t xml:space="preserve">12.3267393112183</t>
   </si>
   <si>
     <t xml:space="preserve">12.4521570205688</t>
@@ -2159,7 +2159,7 @@
     <t xml:space="preserve">12.0938215255737</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3984079360962</t>
+    <t xml:space="preserve">12.3984069824219</t>
   </si>
   <si>
     <t xml:space="preserve">12.201322555542</t>
@@ -2174,10 +2174,10 @@
     <t xml:space="preserve">12.6134080886841</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8463258743286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8104934692383</t>
+    <t xml:space="preserve">12.8463268280029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.810492515564</t>
   </si>
   <si>
     <t xml:space="preserve">12.9179935455322</t>
@@ -2186,37 +2186,37 @@
     <t xml:space="preserve">13.258412361145</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4017457962036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4375801086426</t>
+    <t xml:space="preserve">13.4017467498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4375791549683</t>
   </si>
   <si>
     <t xml:space="preserve">13.6884145736694</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9034156799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6559200286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2438344955444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6380043029785</t>
+    <t xml:space="preserve">13.903416633606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6559209823608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2438335418701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6380033493042</t>
   </si>
   <si>
     <t xml:space="preserve">14.92467212677</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5125875473022</t>
+    <t xml:space="preserve">14.5125865936279</t>
   </si>
   <si>
     <t xml:space="preserve">14.5663366317749</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7992553710938</t>
+    <t xml:space="preserve">14.7992544174194</t>
   </si>
   <si>
     <t xml:space="preserve">14.5484189987183</t>
@@ -2228,10 +2228,10 @@
     <t xml:space="preserve">14.2617511749268</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8888397216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8171730041504</t>
+    <t xml:space="preserve">14.8888387680054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8171710968018</t>
   </si>
   <si>
     <t xml:space="preserve">14.387167930603</t>
@@ -2240,7 +2240,7 @@
     <t xml:space="preserve">14.7634201049805</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6200857162476</t>
+    <t xml:space="preserve">14.6200866699219</t>
   </si>
   <si>
     <t xml:space="preserve">14.9067535400391</t>
@@ -2249,7 +2249,7 @@
     <t xml:space="preserve">15.1217546463013</t>
   </si>
   <si>
-    <t xml:space="preserve">15.032172203064</t>
+    <t xml:space="preserve">15.0321741104126</t>
   </si>
   <si>
     <t xml:space="preserve">14.7455034255981</t>
@@ -2258,7 +2258,7 @@
     <t xml:space="preserve">15.0500888824463</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0680055618286</t>
+    <t xml:space="preserve">15.0680065155029</t>
   </si>
   <si>
     <t xml:space="preserve">15.1038398742676</t>
@@ -2267,34 +2267,34 @@
     <t xml:space="preserve">14.5305023193359</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7096700668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2080001831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6167478561401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5092458724976</t>
+    <t xml:space="preserve">14.7096710205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2080011367798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6167469024658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5092468261719</t>
   </si>
   <si>
     <t xml:space="preserve">13.0434112548828</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1688270568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9717435836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4700736999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2404947280884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6525812149048</t>
+    <t xml:space="preserve">13.1688280105591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9717426300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4700746536255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2404956817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6525802612305</t>
   </si>
   <si>
     <t xml:space="preserve">13.5809135437012</t>
@@ -2306,19 +2306,19 @@
     <t xml:space="preserve">13.4913301467896</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2225790023804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2046613693237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0613279342651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0075769424438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6313257217407</t>
+    <t xml:space="preserve">13.2225780487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2046604156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0613269805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0075778961182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6313247680664</t>
   </si>
   <si>
     <t xml:space="preserve">13.0971612930298</t>
@@ -2345,7 +2345,7 @@
     <t xml:space="preserve">13.1150779724121</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1509122848511</t>
+    <t xml:space="preserve">13.1509113311768</t>
   </si>
   <si>
     <t xml:space="preserve">13.5271635055542</t>
@@ -2354,13 +2354,13 @@
     <t xml:space="preserve">13.3479957580566</t>
   </si>
   <si>
-    <t xml:space="preserve">13.276328086853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7925758361816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5954914093018</t>
+    <t xml:space="preserve">13.2763290405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7925748825073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5954923629761</t>
   </si>
   <si>
     <t xml:space="preserve">12.5238246917725</t>
@@ -2372,16 +2372,16 @@
     <t xml:space="preserve">12.4879903793335</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3088216781616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5417404174805</t>
+    <t xml:space="preserve">12.3088226318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5417413711548</t>
   </si>
   <si>
     <t xml:space="preserve">12.8284091949463</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3804893493652</t>
+    <t xml:space="preserve">12.3804903030396</t>
   </si>
   <si>
     <t xml:space="preserve">12.6671581268311</t>
@@ -2399,22 +2399,22 @@
     <t xml:space="preserve">12.4342403411865</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9504880905151</t>
+    <t xml:space="preserve">11.9504871368408</t>
   </si>
   <si>
     <t xml:space="preserve">12.2192392349243</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8250703811646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1117391586304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9684038162231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0400705337524</t>
+    <t xml:space="preserve">11.8250694274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1117382049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9684047698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0400714874268</t>
   </si>
   <si>
     <t xml:space="preserve">12.0042381286621</t>
@@ -2423,10 +2423,10 @@
     <t xml:space="preserve">12.255072593689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7388257980347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7421646118164</t>
+    <t xml:space="preserve">12.7388248443604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7421655654907</t>
   </si>
   <si>
     <t xml:space="preserve">13.7063312530518</t>
@@ -2435,7 +2435,7 @@
     <t xml:space="preserve">14.0825834274292</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0109176635742</t>
+    <t xml:space="preserve">14.0109157562256</t>
   </si>
   <si>
     <t xml:space="preserve">13.7242479324341</t>
@@ -2444,10 +2444,10 @@
     <t xml:space="preserve">14.0467500686646</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0646667480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9392499923706</t>
+    <t xml:space="preserve">14.0646657943726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9392490386963</t>
   </si>
   <si>
     <t xml:space="preserve">13.6346645355225</t>
@@ -2474,55 +2474,55 @@
     <t xml:space="preserve">13.4734134674072</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1867456436157</t>
+    <t xml:space="preserve">13.1867446899414</t>
   </si>
   <si>
     <t xml:space="preserve">13.3838291168213</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5988311767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7029914855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8429861068726</t>
+    <t xml:space="preserve">13.5988302230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.70299243927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8429870605469</t>
   </si>
   <si>
     <t xml:space="preserve">11.7892360687256</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6817350387573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0759038925171</t>
+    <t xml:space="preserve">11.6817359924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0759048461914</t>
   </si>
   <si>
     <t xml:space="preserve">11.5742359161377</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2158994674683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3592348098755</t>
+    <t xml:space="preserve">11.2159004211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3592338562012</t>
   </si>
   <si>
     <t xml:space="preserve">11.4309015274048</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3054838180542</t>
+    <t xml:space="preserve">11.3054828643799</t>
   </si>
   <si>
     <t xml:space="preserve">11.2875671386719</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6837844848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5179252624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2783527374268</t>
+    <t xml:space="preserve">11.683783531189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5179262161255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2783517837524</t>
   </si>
   <si>
     <t xml:space="preserve">11.1493520736694</t>
@@ -2534,7 +2534,7 @@
     <t xml:space="preserve">11.0756378173828</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9970712661743</t>
+    <t xml:space="preserve">11.9970722198486</t>
   </si>
   <si>
     <t xml:space="preserve">12.052357673645</t>
@@ -2543,7 +2543,7 @@
     <t xml:space="preserve">12.2735013961792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2182159423828</t>
+    <t xml:space="preserve">12.2182149887085</t>
   </si>
   <si>
     <t xml:space="preserve">12.4025020599365</t>
@@ -2555,7 +2555,7 @@
     <t xml:space="preserve">12.0707864761353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1629295349121</t>
+    <t xml:space="preserve">12.1629285812378</t>
   </si>
   <si>
     <t xml:space="preserve">12.1260719299316</t>
@@ -2570,13 +2570,13 @@
     <t xml:space="preserve">11.7759265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8312139511108</t>
+    <t xml:space="preserve">11.8312129974365</t>
   </si>
   <si>
     <t xml:space="preserve">11.9786424636841</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7206420898438</t>
+    <t xml:space="preserve">11.7206411361694</t>
   </si>
   <si>
     <t xml:space="preserve">11.868070602417</t>
@@ -2591,7 +2591,7 @@
     <t xml:space="preserve">11.4442110061646</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3520679473877</t>
+    <t xml:space="preserve">11.3520669937134</t>
   </si>
   <si>
     <t xml:space="preserve">11.3704957962036</t>
@@ -2609,7 +2609,7 @@
     <t xml:space="preserve">11.7022123336792</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5732126235962</t>
+    <t xml:space="preserve">11.5732116699219</t>
   </si>
   <si>
     <t xml:space="preserve">11.481068611145</t>
@@ -2618,7 +2618,7 @@
     <t xml:space="preserve">11.296781539917</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3152103424072</t>
+    <t xml:space="preserve">11.3152093887329</t>
   </si>
   <si>
     <t xml:space="preserve">11.5547828674316</t>
@@ -2627,7 +2627,7 @@
     <t xml:space="preserve">11.4257822036743</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3336391448975</t>
+    <t xml:space="preserve">11.3336381912231</t>
   </si>
   <si>
     <t xml:space="preserve">11.3889245986938</t>
@@ -2636,7 +2636,7 @@
     <t xml:space="preserve">11.4626398086548</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7943563461304</t>
+    <t xml:space="preserve">11.7943553924561</t>
   </si>
   <si>
     <t xml:space="preserve">12.1076431274414</t>
@@ -2666,7 +2666,7 @@
     <t xml:space="preserve">13.0290775299072</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2502212524414</t>
+    <t xml:space="preserve">13.2502222061157</t>
   </si>
   <si>
     <t xml:space="preserve">13.4160804748535</t>
@@ -2681,7 +2681,7 @@
     <t xml:space="preserve">12.6420755386353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8816471099854</t>
+    <t xml:space="preserve">12.8816480636597</t>
   </si>
   <si>
     <t xml:space="preserve">12.9185056686401</t>
@@ -2690,7 +2690,7 @@
     <t xml:space="preserve">13.194935798645</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1580781936646</t>
+    <t xml:space="preserve">13.1580772399902</t>
   </si>
   <si>
     <t xml:space="preserve">12.8079328536987</t>
@@ -2705,7 +2705,7 @@
     <t xml:space="preserve">12.5499315261841</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0843639373779</t>
+    <t xml:space="preserve">13.0843629837036</t>
   </si>
   <si>
     <t xml:space="preserve">13.3423643112183</t>
@@ -2723,13 +2723,13 @@
     <t xml:space="preserve">13.1027917861938</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3607931137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2133636474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5266523361206</t>
+    <t xml:space="preserve">13.3607940673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2133646011353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5266513824463</t>
   </si>
   <si>
     <t xml:space="preserve">13.6003665924072</t>
@@ -2747,28 +2747,28 @@
     <t xml:space="preserve">13.7846536636353</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0610837936401</t>
+    <t xml:space="preserve">14.0610828399658</t>
   </si>
   <si>
     <t xml:space="preserve">14.2637987136841</t>
   </si>
   <si>
-    <t xml:space="preserve">14.540228843689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6139430999756</t>
+    <t xml:space="preserve">14.5402297973633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6139440536499</t>
   </si>
   <si>
     <t xml:space="preserve">15.3695201873779</t>
   </si>
   <si>
-    <t xml:space="preserve">15.53537940979</t>
+    <t xml:space="preserve">15.5353784561157</t>
   </si>
   <si>
     <t xml:space="preserve">15.6275205612183</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5722341537476</t>
+    <t xml:space="preserve">15.5722360610962</t>
   </si>
   <si>
     <t xml:space="preserve">15.4063768386841</t>
@@ -2780,34 +2780,34 @@
     <t xml:space="preserve">15.295804977417</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2773771286011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4616641998291</t>
+    <t xml:space="preserve">15.2773761749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4616651535034</t>
   </si>
   <si>
     <t xml:space="preserve">15.6459493637085</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4432353973389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.664379119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7012367248535</t>
+    <t xml:space="preserve">15.4432344436646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6643781661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7012376785278</t>
   </si>
   <si>
     <t xml:space="preserve">15.6090936660767</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3326616287231</t>
+    <t xml:space="preserve">15.3326606750488</t>
   </si>
   <si>
     <t xml:space="preserve">15.2036619186401</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1668043136597</t>
+    <t xml:space="preserve">15.1668033599854</t>
   </si>
   <si>
     <t xml:space="preserve">14.8535175323486</t>
@@ -2828,22 +2828,22 @@
     <t xml:space="preserve">15.8302373886108</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7196636199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3879499435425</t>
+    <t xml:space="preserve">15.7196645736694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3879489898682</t>
   </si>
   <si>
     <t xml:space="preserve">15.5906648635864</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6828079223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7565231323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.738094329834</t>
+    <t xml:space="preserve">15.682806968689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7565221786499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7380933761597</t>
   </si>
   <si>
     <t xml:space="preserve">15.1483764648438</t>
@@ -2855,7 +2855,7 @@
     <t xml:space="preserve">15.1299476623535</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4800910949707</t>
+    <t xml:space="preserve">15.480092048645</t>
   </si>
   <si>
     <t xml:space="preserve">15.9223804473877</t>
@@ -2867,22 +2867,22 @@
     <t xml:space="preserve">16.0882377624512</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7749519348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8670930862427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7109384536743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6556520462036</t>
+    <t xml:space="preserve">15.7749509811401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.867094039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7109394073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6556529998779</t>
   </si>
   <si>
     <t xml:space="preserve">13.6372241973877</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1347980499268</t>
+    <t xml:space="preserve">14.1347990036011</t>
   </si>
   <si>
     <t xml:space="preserve">14.4480857849121</t>
@@ -2894,7 +2894,7 @@
     <t xml:space="preserve">14.0242261886597</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0795116424561</t>
+    <t xml:space="preserve">14.0795125961304</t>
   </si>
   <si>
     <t xml:space="preserve">14.0057973861694</t>
@@ -2915,7 +2915,7 @@
     <t xml:space="preserve">13.4897947311401</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6187944412231</t>
+    <t xml:space="preserve">13.6187953948975</t>
   </si>
   <si>
     <t xml:space="preserve">12.8263626098633</t>
@@ -2927,7 +2927,7 @@
     <t xml:space="preserve">13.2686500549316</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9369344711304</t>
+    <t xml:space="preserve">12.9369335174561</t>
   </si>
   <si>
     <t xml:space="preserve">12.9000768661499</t>
@@ -2936,10 +2936,10 @@
     <t xml:space="preserve">12.9922199249268</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0475063323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6973609924316</t>
+    <t xml:space="preserve">13.0475053787231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6973600387573</t>
   </si>
   <si>
     <t xml:space="preserve">12.6052179336548</t>
@@ -2951,7 +2951,7 @@
     <t xml:space="preserve">12.4209308624268</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4762163162231</t>
+    <t xml:space="preserve">12.4762172698975</t>
   </si>
   <si>
     <t xml:space="preserve">12.6236457824707</t>
@@ -3480,6 +3480,9 @@
   </si>
   <si>
     <t xml:space="preserve">17.7199993133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8199996948242</t>
   </si>
 </sst>
 </file>
@@ -68896,7 +68899,7 @@
     </row>
     <row r="2504">
       <c r="A2504" s="1" t="n">
-        <v>45965.6912615741</v>
+        <v>45965.3333333333</v>
       </c>
       <c r="B2504" t="n">
         <v>40711</v>
@@ -68917,6 +68920,32 @@
         <v>1155</v>
       </c>
       <c r="H2504" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2505">
+      <c r="A2505" s="1" t="n">
+        <v>45966.6911111111</v>
+      </c>
+      <c r="B2505" t="n">
+        <v>22443</v>
+      </c>
+      <c r="C2505" t="n">
+        <v>17.9400005340576</v>
+      </c>
+      <c r="D2505" t="n">
+        <v>17.4200000762939</v>
+      </c>
+      <c r="E2505" t="n">
+        <v>17.8999996185303</v>
+      </c>
+      <c r="F2505" t="n">
+        <v>17.8199996948242</v>
+      </c>
+      <c r="G2505" t="s">
+        <v>1156</v>
+      </c>
+      <c r="H2505" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ORS.MI.xlsx
+++ b/data/ORS.MI.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">7.98275899887085</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06380271911621</t>
+    <t xml:space="preserve">8.06380081176758</t>
   </si>
   <si>
     <t xml:space="preserve">7.94223737716675</t>
@@ -56,7 +56,7 @@
     <t xml:space="preserve">7.82472467422485</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93818616867065</t>
+    <t xml:space="preserve">7.93818426132202</t>
   </si>
   <si>
     <t xml:space="preserve">7.90171670913696</t>
@@ -65,34 +65,34 @@
     <t xml:space="preserve">8.03948783874512</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92602968215942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86119413375854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82067251205444</t>
+    <t xml:space="preserve">7.92602872848511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86119508743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82067346572876</t>
   </si>
   <si>
     <t xml:space="preserve">7.93413305282593</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02328205108643</t>
+    <t xml:space="preserve">8.02328014373779</t>
   </si>
   <si>
     <t xml:space="preserve">8.08811473846436</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14484596252441</t>
+    <t xml:space="preserve">8.1448450088501</t>
   </si>
   <si>
     <t xml:space="preserve">7.69910717010498</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8044638633728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97465372085571</t>
+    <t xml:space="preserve">7.80446481704712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97465467453003</t>
   </si>
   <si>
     <t xml:space="preserve">8.01112365722656</t>
@@ -101,52 +101,52 @@
     <t xml:space="preserve">8.01517581939697</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79230737686157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82877683639526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34745311737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84093332290649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9098219871521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8571400642395</t>
+    <t xml:space="preserve">7.79230833053589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82877779006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34745407104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84093236923218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90982007980347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85714197158813</t>
   </si>
   <si>
     <t xml:space="preserve">7.78015089035034</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8449854850769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97870588302612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88550615310669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95034074783325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00301933288574</t>
+    <t xml:space="preserve">7.84498643875122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97870683670044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88550806045532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95034170150757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00301837921143</t>
   </si>
   <si>
     <t xml:space="preserve">8.01922702789307</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91792440414429</t>
+    <t xml:space="preserve">7.9179253578186</t>
   </si>
   <si>
     <t xml:space="preserve">8.1002721786499</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10432243347168</t>
+    <t xml:space="preserve">8.104323387146</t>
   </si>
   <si>
     <t xml:space="preserve">8.18536758422852</t>
@@ -155,46 +155,46 @@
     <t xml:space="preserve">8.20157527923584</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11242866516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07595729827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03138446807861</t>
+    <t xml:space="preserve">8.1124267578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07595920562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0313835144043</t>
   </si>
   <si>
     <t xml:space="preserve">8.09621906280518</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1772632598877</t>
+    <t xml:space="preserve">8.17726230621338</t>
   </si>
   <si>
     <t xml:space="preserve">8.05569744110107</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12053394317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25830554962158</t>
+    <t xml:space="preserve">8.12053203582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2583065032959</t>
   </si>
   <si>
     <t xml:space="preserve">8.4203929901123</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67162609100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55816650390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42849826812744</t>
+    <t xml:space="preserve">8.67162704467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55816555023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42849731445312</t>
   </si>
   <si>
     <t xml:space="preserve">8.52429008483887</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45921993255615</t>
+    <t xml:space="preserve">8.45921897888184</t>
   </si>
   <si>
     <t xml:space="preserve">8.50802135467529</t>
@@ -215,34 +215,34 @@
     <t xml:space="preserve">8.87404727935791</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79270648956299</t>
+    <t xml:space="preserve">8.7927074432373</t>
   </si>
   <si>
     <t xml:space="preserve">8.90657997131348</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86591148376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94725036621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93911743164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78457355499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74390411376953</t>
+    <t xml:space="preserve">8.86591243743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94724941253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93911838531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78457260131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74390506744385</t>
   </si>
   <si>
     <t xml:space="preserve">8.91471385955811</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92284965515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10992813110352</t>
+    <t xml:space="preserve">8.92285060882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10992908477783</t>
   </si>
   <si>
     <t xml:space="preserve">9.077392578125</t>
@@ -254,7 +254,7 @@
     <t xml:space="preserve">9.1343297958374</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15059852600098</t>
+    <t xml:space="preserve">9.15059661865234</t>
   </si>
   <si>
     <t xml:space="preserve">9.15873050689697</t>
@@ -266,91 +266,91 @@
     <t xml:space="preserve">8.6788330078125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85777854919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72763729095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70323371887207</t>
+    <t xml:space="preserve">8.85777759552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72763633728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70323467254639</t>
   </si>
   <si>
     <t xml:space="preserve">8.66256523132324</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69510078430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6218957901001</t>
+    <t xml:space="preserve">8.69510173797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62189483642578</t>
   </si>
   <si>
     <t xml:space="preserve">8.80084133148193</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77643966674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68696689605713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54869270324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54055786132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58122730255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46735286712646</t>
+    <t xml:space="preserve">8.77643871307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68696784973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54869079589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54055690765381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58122825622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46735191345215</t>
   </si>
   <si>
     <t xml:space="preserve">8.51615619659424</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49988746643066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45108413696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63003063201904</t>
+    <t xml:space="preserve">8.49988842010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45108509063721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63002967834473</t>
   </si>
   <si>
     <t xml:space="preserve">8.80897617340088</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89031314849854</t>
+    <t xml:space="preserve">8.89031410217285</t>
   </si>
   <si>
     <t xml:space="preserve">8.93098449707031</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96351718902588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05299186706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30514049530029</t>
+    <t xml:space="preserve">8.9635181427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05299091339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30514144897461</t>
   </si>
   <si>
     <t xml:space="preserve">9.10179424285889</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19126605987549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35394382476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4759521484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54915618896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58982467651367</t>
+    <t xml:space="preserve">9.1912670135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35394287109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47595119476318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54915523529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5898265838623</t>
   </si>
   <si>
     <t xml:space="preserve">9.66303157806396</t>
@@ -362,34 +362,34 @@
     <t xml:space="preserve">9.85824489593506</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0046529769897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.240535736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2486696243286</t>
+    <t xml:space="preserve">10.0046539306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2405347824097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2486705780029</t>
   </si>
   <si>
     <t xml:space="preserve">10.3381414413452</t>
   </si>
   <si>
-    <t xml:space="preserve">10.598424911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4276151657104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4032125473022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.525218963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4601497650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5658912658691</t>
+    <t xml:space="preserve">10.5984258651733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4276142120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4032115936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5252199172974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4601488113403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5658893585205</t>
   </si>
   <si>
     <t xml:space="preserve">10.5821561813354</t>
@@ -404,7 +404,7 @@
     <t xml:space="preserve">10.8749771118164</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6553621292114</t>
+    <t xml:space="preserve">10.6553630828857</t>
   </si>
   <si>
     <t xml:space="preserve">10.6797637939453</t>
@@ -413,25 +413,25 @@
     <t xml:space="preserve">10.5740242004395</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5170860290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5414886474609</t>
+    <t xml:space="preserve">10.5170869827271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5414876937866</t>
   </si>
   <si>
     <t xml:space="preserve">10.5577564239502</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5089530944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8180379867554</t>
+    <t xml:space="preserve">10.5089540481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8180389404297</t>
   </si>
   <si>
     <t xml:space="preserve">10.6878967285156</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7611026763916</t>
+    <t xml:space="preserve">10.7611017227173</t>
   </si>
   <si>
     <t xml:space="preserve">10.6472282409668</t>
@@ -443,13 +443,13 @@
     <t xml:space="preserve">10.8831100463867</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6716299057007</t>
+    <t xml:space="preserve">10.6716289520264</t>
   </si>
   <si>
     <t xml:space="preserve">10.7367010116577</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0051193237305</t>
+    <t xml:space="preserve">11.0051183700562</t>
   </si>
   <si>
     <t xml:space="preserve">11.0213871002197</t>
@@ -458,16 +458,16 @@
     <t xml:space="preserve">11.184063911438</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4036769866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3955430984497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3386068344116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.322338104248</t>
+    <t xml:space="preserve">11.4036779403687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.395544052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3386077880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3223390579224</t>
   </si>
   <si>
     <t xml:space="preserve">11.3304738998413</t>
@@ -476,7 +476,7 @@
     <t xml:space="preserve">11.3630094528198</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0783224105835</t>
+    <t xml:space="preserve">11.0783233642578</t>
   </si>
   <si>
     <t xml:space="preserve">10.606559753418</t>
@@ -488,19 +488,19 @@
     <t xml:space="preserve">10.8505744934082</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6390953063965</t>
+    <t xml:space="preserve">10.6390943527222</t>
   </si>
   <si>
     <t xml:space="preserve">10.4113464355469</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2080011367798</t>
+    <t xml:space="preserve">10.2080001831055</t>
   </si>
   <si>
     <t xml:space="preserve">10.2730703353882</t>
   </si>
   <si>
-    <t xml:space="preserve">10.232400894165</t>
+    <t xml:space="preserve">10.2323999404907</t>
   </si>
   <si>
     <t xml:space="preserve">10.321873664856</t>
@@ -509,22 +509,22 @@
     <t xml:space="preserve">10.3706789016724</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3300085067749</t>
+    <t xml:space="preserve">10.3300075531006</t>
   </si>
   <si>
     <t xml:space="preserve">10.3056058883667</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2568044662476</t>
+    <t xml:space="preserve">10.2568035125732</t>
   </si>
   <si>
     <t xml:space="preserve">10.1835975646973</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4845504760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3625421524048</t>
+    <t xml:space="preserve">10.4845514297485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3625440597534</t>
   </si>
   <si>
     <t xml:space="preserve">10.4438819885254</t>
@@ -536,13 +536,13 @@
     <t xml:space="preserve">10.9237794876099</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0376539230347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0620565414429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1027250289917</t>
+    <t xml:space="preserve">11.037654876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0620555877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.102725982666</t>
   </si>
   <si>
     <t xml:space="preserve">11.1433944702148</t>
@@ -551,10 +551,10 @@
     <t xml:space="preserve">11.1759281158447</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1352615356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0701904296875</t>
+    <t xml:space="preserve">11.1352605819702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0701894760132</t>
   </si>
   <si>
     <t xml:space="preserve">11.118992805481</t>
@@ -569,16 +569,16 @@
     <t xml:space="preserve">11.0457878112793</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5008192062378</t>
+    <t xml:space="preserve">10.5008201599121</t>
   </si>
   <si>
     <t xml:space="preserve">10.1347951889038</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36161136627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01999092102051</t>
+    <t xml:space="preserve">8.36161231994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01998996734619</t>
   </si>
   <si>
     <t xml:space="preserve">8.10946273803711</t>
@@ -587,13 +587,13 @@
     <t xml:space="preserve">8.3941478729248</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21520233154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3372106552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3128080368042</t>
+    <t xml:space="preserve">8.2152042388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33721160888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31280899047852</t>
   </si>
   <si>
     <t xml:space="preserve">8.18266773223877</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">8.34534645080566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23960399627686</t>
+    <t xml:space="preserve">8.23960494995117</t>
   </si>
   <si>
     <t xml:space="preserve">8.49175453186035</t>
@@ -611,13 +611,13 @@
     <t xml:space="preserve">8.5893611907959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76017284393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29654216766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25587368011475</t>
+    <t xml:space="preserve">8.76017093658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29654121398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25587177276611</t>
   </si>
   <si>
     <t xml:space="preserve">8.17453289031982</t>
@@ -632,16 +632,16 @@
     <t xml:space="preserve">8.2802734375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14199829101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15826511383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16640090942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12166500091553</t>
+    <t xml:space="preserve">8.14199924468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15826606750488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16639995574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12166404724121</t>
   </si>
   <si>
     <t xml:space="preserve">8.05252552032471</t>
@@ -662,31 +662,31 @@
     <t xml:space="preserve">7.93865156173706</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84917879104614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80850887298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62956476211548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57262802124023</t>
+    <t xml:space="preserve">7.84917974472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80850982666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62956571578979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57262706756592</t>
   </si>
   <si>
     <t xml:space="preserve">7.48315572738647</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66616725921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60516309738159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54009294509888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52382373809814</t>
+    <t xml:space="preserve">7.66616630554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60516357421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54009246826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5238242149353</t>
   </si>
   <si>
     <t xml:space="preserve">7.47908687591553</t>
@@ -695,151 +695,151 @@
     <t xml:space="preserve">7.61329746246338</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54822540283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56449413299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50755739212036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46688652038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49129056930542</t>
+    <t xml:space="preserve">7.54822635650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56449317932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50755643844604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46688747406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49129009246826</t>
   </si>
   <si>
     <t xml:space="preserve">7.49942207336426</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31234407424927</t>
+    <t xml:space="preserve">7.31234502792358</t>
   </si>
   <si>
     <t xml:space="preserve">7.27980804443359</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37741422653198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38554906845093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36928129196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32047748565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34487867355347</t>
+    <t xml:space="preserve">7.37741470336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38555002212524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36928176879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3204779624939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34488010406494</t>
   </si>
   <si>
     <t xml:space="preserve">7.28794240951538</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04392623901367</t>
+    <t xml:space="preserve">7.04392671585083</t>
   </si>
   <si>
     <t xml:space="preserve">7.15780067443848</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39368200302124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42621803283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40181732177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3042106628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36114835739136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20660400390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3530125617981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33674573898315</t>
+    <t xml:space="preserve">7.39368343353271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4262170791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40181636810303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30420970916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3611478805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20660352706909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35301208496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33674621582031</t>
   </si>
   <si>
     <t xml:space="preserve">7.27167463302612</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23100519180298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32861137390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26354074478149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23914003372192</t>
+    <t xml:space="preserve">7.23100423812866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32861042022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26354169845581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23913955688477</t>
   </si>
   <si>
     <t xml:space="preserve">7.22287130355835</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24727249145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44248628616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25540685653687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18220138549805</t>
+    <t xml:space="preserve">7.24727344512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44248580932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25540733337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18220281600952</t>
   </si>
   <si>
     <t xml:space="preserve">7.29607582092285</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16593408584595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14153337478638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05205965042114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07646322250366</t>
+    <t xml:space="preserve">7.16593456268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1415319442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0520601272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07646226882935</t>
   </si>
   <si>
     <t xml:space="preserve">7.0357928276062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01952457427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87311506271362</t>
+    <t xml:space="preserve">7.0195255279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87311458587646</t>
   </si>
   <si>
     <t xml:space="preserve">6.677903175354</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85124778747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93379211425781</t>
+    <t xml:space="preserve">6.85124731063843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93379163742065</t>
   </si>
   <si>
     <t xml:space="preserve">7.26397323608398</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14840984344482</t>
+    <t xml:space="preserve">7.14841032028198</t>
   </si>
   <si>
     <t xml:space="preserve">7.09888315200806</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18142890930176</t>
+    <t xml:space="preserve">7.18142795562744</t>
   </si>
   <si>
     <t xml:space="preserve">7.16491842269897</t>
@@ -848,31 +848,31 @@
     <t xml:space="preserve">7.14015579223633</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21444606781006</t>
+    <t xml:space="preserve">7.21444654464722</t>
   </si>
   <si>
     <t xml:space="preserve">7.1731743812561</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97506475448608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84299278259277</t>
+    <t xml:space="preserve">6.97506427764893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84299325942993</t>
   </si>
   <si>
     <t xml:space="preserve">6.60361242294312</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62012147903442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67790269851685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.809974193573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54583024978638</t>
+    <t xml:space="preserve">6.62012100219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67790222167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80997467041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54583072662354</t>
   </si>
   <si>
     <t xml:space="preserve">6.31470394134521</t>
@@ -881,22 +881,22 @@
     <t xml:space="preserve">6.32295846939087</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34772253036499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38074016571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3972487449646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4715404510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2816858291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22390413284302</t>
+    <t xml:space="preserve">6.34772300720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38073968887329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39724922180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47153997421265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28168630599976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22390460968018</t>
   </si>
   <si>
     <t xml:space="preserve">6.09183168411255</t>
@@ -905,31 +905,31 @@
     <t xml:space="preserve">5.90197801589966</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95975971221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99277782440186</t>
+    <t xml:space="preserve">5.9597601890564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9927773475647</t>
   </si>
   <si>
     <t xml:space="preserve">6.20739507675171</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14135980606079</t>
+    <t xml:space="preserve">6.14135932922363</t>
   </si>
   <si>
     <t xml:space="preserve">6.19088649749756</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14961385726929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07532358169556</t>
+    <t xml:space="preserve">6.14961338043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07532405853271</t>
   </si>
   <si>
     <t xml:space="preserve">6.25692272186279</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00928735733032</t>
+    <t xml:space="preserve">6.00928783416748</t>
   </si>
   <si>
     <t xml:space="preserve">5.9845232963562</t>
@@ -938,19 +938,19 @@
     <t xml:space="preserve">6.12485027313232</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13310480117798</t>
+    <t xml:space="preserve">6.13310527801514</t>
   </si>
   <si>
     <t xml:space="preserve">6.27343082427979</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44677639007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55408525466919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51281213760376</t>
+    <t xml:space="preserve">6.44677591323853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55408477783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51281261444092</t>
   </si>
   <si>
     <t xml:space="preserve">6.36423110961914</t>
@@ -959,31 +959,31 @@
     <t xml:space="preserve">6.24041366577148</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21565008163452</t>
+    <t xml:space="preserve">6.21564960479736</t>
   </si>
   <si>
     <t xml:space="preserve">6.23215961456299</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24866819381714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11659622192383</t>
+    <t xml:space="preserve">6.24866771697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11659669876099</t>
   </si>
   <si>
     <t xml:space="preserve">6.10834074020386</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05055904388428</t>
+    <t xml:space="preserve">6.05055952072144</t>
   </si>
   <si>
     <t xml:space="preserve">5.89372444152832</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77816104888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69561529159546</t>
+    <t xml:space="preserve">5.778160572052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6956148147583</t>
   </si>
   <si>
     <t xml:space="preserve">5.79466915130615</t>
@@ -995,7 +995,7 @@
     <t xml:space="preserve">5.82768774032593</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78641510009766</t>
+    <t xml:space="preserve">5.78641557693481</t>
   </si>
   <si>
     <t xml:space="preserve">5.73688745498657</t>
@@ -1004,13 +1004,13 @@
     <t xml:space="preserve">5.85245132446289</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29819583892822</t>
+    <t xml:space="preserve">6.29819536209106</t>
   </si>
   <si>
     <t xml:space="preserve">6.18263244628906</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15786790847778</t>
+    <t xml:space="preserve">6.15786838531494</t>
   </si>
   <si>
     <t xml:space="preserve">6.03405046463013</t>
@@ -1019,10 +1019,10 @@
     <t xml:space="preserve">6.08357763290405</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81943368911743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91848707199097</t>
+    <t xml:space="preserve">5.81943416595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91848659515381</t>
   </si>
   <si>
     <t xml:space="preserve">5.86070585250854</t>
@@ -1037,28 +1037,28 @@
     <t xml:space="preserve">5.81117820739746</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70387029647827</t>
+    <t xml:space="preserve">5.70387077331543</t>
   </si>
   <si>
     <t xml:space="preserve">5.74514245986938</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83594179153442</t>
+    <t xml:space="preserve">5.83594226837158</t>
   </si>
   <si>
     <t xml:space="preserve">5.71212482452393</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84419727325439</t>
+    <t xml:space="preserve">5.84419679641724</t>
   </si>
   <si>
     <t xml:space="preserve">5.94325065612793</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96801424026489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8772144317627</t>
+    <t xml:space="preserve">5.96801471710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87721490859985</t>
   </si>
   <si>
     <t xml:space="preserve">5.88546943664551</t>
@@ -1070,13 +1070,13 @@
     <t xml:space="preserve">6.02579593658447</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0670690536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3889946937561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19914054870605</t>
+    <t xml:space="preserve">6.06706857681274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38899517059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19914102554321</t>
   </si>
   <si>
     <t xml:space="preserve">6.04230451583862</t>
@@ -1085,28 +1085,28 @@
     <t xml:space="preserve">6.05881452560425</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95150566101074</t>
+    <t xml:space="preserve">5.95150518417358</t>
   </si>
   <si>
     <t xml:space="preserve">6.17437744140625</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17601919174194</t>
+    <t xml:space="preserve">6.1760196685791</t>
   </si>
   <si>
     <t xml:space="preserve">6.29349803924561</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25993204116821</t>
+    <t xml:space="preserve">6.25993251800537</t>
   </si>
   <si>
     <t xml:space="preserve">6.20958423614502</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09210586547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10888910293579</t>
+    <t xml:space="preserve">6.09210538864136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10888957977295</t>
   </si>
   <si>
     <t xml:space="preserve">6.0753231048584</t>
@@ -1115,13 +1115,13 @@
     <t xml:space="preserve">6.14245367050171</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05854082107544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02497529983521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97462701797485</t>
+    <t xml:space="preserve">6.0585412979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02497482299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97462749481201</t>
   </si>
   <si>
     <t xml:space="preserve">5.95784473419189</t>
@@ -1145,13 +1145,13 @@
     <t xml:space="preserve">6.64593458175659</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69628190994263</t>
+    <t xml:space="preserve">6.69628238677979</t>
   </si>
   <si>
     <t xml:space="preserve">6.78019523620605</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72984743118286</t>
+    <t xml:space="preserve">6.7298469543457</t>
   </si>
   <si>
     <t xml:space="preserve">6.62915086746216</t>
@@ -1160,16 +1160,16 @@
     <t xml:space="preserve">6.56202030181885</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54523706436157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67949962615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66271686553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57880353927612</t>
+    <t xml:space="preserve">6.54523801803589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67949914932251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66271638870239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57880306243896</t>
   </si>
   <si>
     <t xml:space="preserve">6.37741088867188</t>
@@ -1184,10 +1184,10 @@
     <t xml:space="preserve">6.36062908172607</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67253875732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55506086349487</t>
+    <t xml:space="preserve">5.67253923416138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55506038665771</t>
   </si>
   <si>
     <t xml:space="preserve">5.68932247161865</t>
@@ -1208,40 +1208,40 @@
     <t xml:space="preserve">5.60540819168091</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52149629592896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50471305847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48793029785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35366868972778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3704514503479</t>
+    <t xml:space="preserve">5.5214958190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50471258163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48792934417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35366821289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37045097351074</t>
   </si>
   <si>
     <t xml:space="preserve">5.42079925537109</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28653812408447</t>
+    <t xml:space="preserve">5.28653860092163</t>
   </si>
   <si>
     <t xml:space="preserve">5.30332088470459</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26975536346436</t>
+    <t xml:space="preserve">5.26975584030151</t>
   </si>
   <si>
     <t xml:space="preserve">5.38723421096802</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32010316848755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65575647354126</t>
+    <t xml:space="preserve">5.32010364532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65575695037842</t>
   </si>
   <si>
     <t xml:space="preserve">5.75645303726196</t>
@@ -1250,19 +1250,19 @@
     <t xml:space="preserve">5.70610475540161</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72288751602173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73966979980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63897466659546</t>
+    <t xml:space="preserve">5.72288703918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73967027664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63897371292114</t>
   </si>
   <si>
     <t xml:space="preserve">5.57184410095215</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18584156036377</t>
+    <t xml:space="preserve">5.18584203720093</t>
   </si>
   <si>
     <t xml:space="preserve">5.20262479782104</t>
@@ -1271,7 +1271,7 @@
     <t xml:space="preserve">5.21940803527832</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16905927658081</t>
+    <t xml:space="preserve">5.16905975341797</t>
   </si>
   <si>
     <t xml:space="preserve">5.13549375534058</t>
@@ -1280,34 +1280,34 @@
     <t xml:space="preserve">5.1019287109375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9508843421936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03479814529419</t>
+    <t xml:space="preserve">4.95088481903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03479862213135</t>
   </si>
   <si>
     <t xml:space="preserve">5.15227699279785</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11871099472046</t>
+    <t xml:space="preserve">5.11871147155762</t>
   </si>
   <si>
     <t xml:space="preserve">5.06836318969727</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08514642715454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23619031906128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25297260284424</t>
+    <t xml:space="preserve">5.0851469039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23619079589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25297212600708</t>
   </si>
   <si>
     <t xml:space="preserve">5.33688640594482</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79001808166504</t>
+    <t xml:space="preserve">5.79001760482788</t>
   </si>
   <si>
     <t xml:space="preserve">5.77323532104492</t>
@@ -1316,7 +1316,7 @@
     <t xml:space="preserve">5.58862638473511</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81662321090698</t>
+    <t xml:space="preserve">4.81662368774414</t>
   </si>
   <si>
     <t xml:space="preserve">4.79984140396118</t>
@@ -1325,16 +1325,16 @@
     <t xml:space="preserve">4.59844827651978</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36349248886108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31314373016357</t>
+    <t xml:space="preserve">4.36349201202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31314420700073</t>
   </si>
   <si>
     <t xml:space="preserve">4.19566535949707</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11175155639648</t>
+    <t xml:space="preserve">4.11175203323364</t>
   </si>
   <si>
     <t xml:space="preserve">4.02783870697021</t>
@@ -1343,7 +1343,7 @@
     <t xml:space="preserve">4.17049074172974</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06979608535767</t>
+    <t xml:space="preserve">4.06979560852051</t>
   </si>
   <si>
     <t xml:space="preserve">4.12014293670654</t>
@@ -1355,7 +1355,7 @@
     <t xml:space="preserve">4.17888164520264</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04462099075317</t>
+    <t xml:space="preserve">4.04462146759033</t>
   </si>
   <si>
     <t xml:space="preserve">4.15370845794678</t>
@@ -1367,13 +1367,13 @@
     <t xml:space="preserve">4.16209983825684</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14531803131104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99427318572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09496879577637</t>
+    <t xml:space="preserve">4.14531755447388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99427270889282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09496927261353</t>
   </si>
   <si>
     <t xml:space="preserve">3.98588132858276</t>
@@ -1382,19 +1382,19 @@
     <t xml:space="preserve">4.2795786857605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22923040390015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21244812011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03623008728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12877893447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16283082962036</t>
+    <t xml:space="preserve">4.22922992706299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21244764328003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03622961044312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12877941131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16283130645752</t>
   </si>
   <si>
     <t xml:space="preserve">4.07770156860352</t>
@@ -1406,22 +1406,22 @@
     <t xml:space="preserve">4.20539569854736</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37565422058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21390867233276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22242116928101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25647401809692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24796056747437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32457685470581</t>
+    <t xml:space="preserve">4.37565469741821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21390819549561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22242164611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25647354125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24796009063721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32457637786865</t>
   </si>
   <si>
     <t xml:space="preserve">4.30755090713501</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">4.35862827301025</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51186227798462</t>
+    <t xml:space="preserve">4.51186180114746</t>
   </si>
   <si>
     <t xml:space="preserve">5.5334153175354</t>
@@ -1448,28 +1448,28 @@
     <t xml:space="preserve">5.73772573471069</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5504412651062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58449268341064</t>
+    <t xml:space="preserve">5.55044078826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5844931602478</t>
   </si>
   <si>
     <t xml:space="preserve">5.567467212677</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41423368453979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26100063323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48233795166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4482855796814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60151863098145</t>
+    <t xml:space="preserve">5.41423416137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2610011100769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48233842849731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44828605651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6015191078186</t>
   </si>
   <si>
     <t xml:space="preserve">5.66962242126465</t>
@@ -1481,13 +1481,13 @@
     <t xml:space="preserve">5.70367479324341</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32910490036011</t>
+    <t xml:space="preserve">5.32910442352295</t>
   </si>
   <si>
     <t xml:space="preserve">5.27802705764771</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43126058578491</t>
+    <t xml:space="preserve">5.43126010894775</t>
   </si>
   <si>
     <t xml:space="preserve">5.31207847595215</t>
@@ -1496,64 +1496,64 @@
     <t xml:space="preserve">5.22694873809814</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00561285018921</t>
+    <t xml:space="preserve">5.00561237335205</t>
   </si>
   <si>
     <t xml:space="preserve">4.95453500747681</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93750953674316</t>
+    <t xml:space="preserve">4.93750905990601</t>
   </si>
   <si>
     <t xml:space="preserve">5.05669021606445</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03966426849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97156143188477</t>
+    <t xml:space="preserve">5.03966474533081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97156095504761</t>
   </si>
   <si>
     <t xml:space="preserve">4.8864312171936</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02263879776001</t>
+    <t xml:space="preserve">5.02263832092285</t>
   </si>
   <si>
     <t xml:space="preserve">4.92048311233521</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90345764160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85237979888916</t>
+    <t xml:space="preserve">4.9034571647644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.852379322052</t>
   </si>
   <si>
     <t xml:space="preserve">4.8694052696228</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34613084793091</t>
+    <t xml:space="preserve">5.34613037109375</t>
   </si>
   <si>
     <t xml:space="preserve">5.2439751625061</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36315631866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38018321990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20992279052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15884637832642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10776853561401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98858642578125</t>
+    <t xml:space="preserve">5.36315679550171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38018274307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2099232673645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15884590148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10776805877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98858690261841</t>
   </si>
   <si>
     <t xml:space="preserve">5.09074211120605</t>
@@ -1574,19 +1574,19 @@
     <t xml:space="preserve">4.68212080001831</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5459132194519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59699106216431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57996511459351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63104295730591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78427600860596</t>
+    <t xml:space="preserve">4.54591369628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59699153900146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57996559143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63104343414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7842755317688</t>
   </si>
   <si>
     <t xml:space="preserve">4.767249584198</t>
@@ -1595,13 +1595,13 @@
     <t xml:space="preserve">4.8183274269104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80130195617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39720821380615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61854457855225</t>
+    <t xml:space="preserve">4.8013014793396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39720869064331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6185450553894</t>
   </si>
   <si>
     <t xml:space="preserve">5.4653115272522</t>
@@ -1610,7 +1610,7 @@
     <t xml:space="preserve">5.49936389923096</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63557004928589</t>
+    <t xml:space="preserve">5.63557100296021</t>
   </si>
   <si>
     <t xml:space="preserve">5.68664836883545</t>
@@ -1619,31 +1619,31 @@
     <t xml:space="preserve">5.65259695053101</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85690689086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8739333152771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31660652160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3336329460144</t>
+    <t xml:space="preserve">5.8569073677063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87393283843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31660604476929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33363246917725</t>
   </si>
   <si>
     <t xml:space="preserve">6.2995810508728</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35065841674805</t>
+    <t xml:space="preserve">6.35065793991089</t>
   </si>
   <si>
     <t xml:space="preserve">6.43578767776489</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55496883392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69117593765259</t>
+    <t xml:space="preserve">6.55496835708618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69117641448975</t>
   </si>
   <si>
     <t xml:space="preserve">6.79333162307739</t>
@@ -1655,16 +1655,16 @@
     <t xml:space="preserve">7.08277082443237</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87846040725708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77630519866943</t>
+    <t xml:space="preserve">6.87846088409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77630567550659</t>
   </si>
   <si>
     <t xml:space="preserve">6.84440898895264</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70820236206055</t>
+    <t xml:space="preserve">6.70820283889771</t>
   </si>
   <si>
     <t xml:space="preserve">6.75927972793579</t>
@@ -1673,37 +1673,37 @@
     <t xml:space="preserve">6.53794288635254</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72522830963135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65712404251099</t>
+    <t xml:space="preserve">6.72522783279419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6571249961853</t>
   </si>
   <si>
     <t xml:space="preserve">6.91251230239868</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8954873085022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96359062194824</t>
+    <t xml:space="preserve">6.89548683166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96359014511108</t>
   </si>
   <si>
     <t xml:space="preserve">7.17302179336548</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05085277557373</t>
+    <t xml:space="preserve">7.05085325241089</t>
   </si>
   <si>
     <t xml:space="preserve">7.12066411972046</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57443237304688</t>
+    <t xml:space="preserve">7.57443284988403</t>
   </si>
   <si>
     <t xml:space="preserve">7.97584199905396</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02819919586182</t>
+    <t xml:space="preserve">8.0281982421875</t>
   </si>
   <si>
     <t xml:space="preserve">8.0631046295166</t>
@@ -1715,67 +1715,67 @@
     <t xml:space="preserve">8.01074695587158</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94093799591064</t>
+    <t xml:space="preserve">7.94093704223633</t>
   </si>
   <si>
     <t xml:space="preserve">8.13291454315186</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15036678314209</t>
+    <t xml:space="preserve">8.15036869049072</t>
   </si>
   <si>
     <t xml:space="preserve">8.16782093048096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18527317047119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34234714508057</t>
+    <t xml:space="preserve">8.18527412414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34234619140625</t>
   </si>
   <si>
     <t xml:space="preserve">8.11546325683594</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25508403778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08055686950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20272445678711</t>
+    <t xml:space="preserve">8.25508308410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08055782318115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20272541046143</t>
   </si>
   <si>
     <t xml:space="preserve">7.95838928222656</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37725162506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32489395141602</t>
+    <t xml:space="preserve">8.37725257873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3248929977417</t>
   </si>
   <si>
     <t xml:space="preserve">8.81356716156006</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58668231964111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53432464599609</t>
+    <t xml:space="preserve">8.58668327331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53432559967041</t>
   </si>
   <si>
     <t xml:space="preserve">8.69139862060547</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60413455963135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72630500793457</t>
+    <t xml:space="preserve">8.60413646697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72630405426025</t>
   </si>
   <si>
     <t xml:space="preserve">8.42960929870605</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28998947143555</t>
+    <t xml:space="preserve">8.28998851776123</t>
   </si>
   <si>
     <t xml:space="preserve">8.30744171142578</t>
@@ -1793,7 +1793,7 @@
     <t xml:space="preserve">8.22017765045166</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44706249237061</t>
+    <t xml:space="preserve">8.44706153869629</t>
   </si>
   <si>
     <t xml:space="preserve">8.3597993850708</t>
@@ -1802,19 +1802,19 @@
     <t xml:space="preserve">8.09800910949707</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23762989044189</t>
+    <t xml:space="preserve">8.23763084411621</t>
   </si>
   <si>
     <t xml:space="preserve">8.48196792602539</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6215877532959</t>
+    <t xml:space="preserve">8.62158870697021</t>
   </si>
   <si>
     <t xml:space="preserve">8.55177783966064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65649318695068</t>
+    <t xml:space="preserve">8.656494140625</t>
   </si>
   <si>
     <t xml:space="preserve">8.51687240600586</t>
@@ -1829,7 +1829,7 @@
     <t xml:space="preserve">8.56923007965088</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99161815643311</t>
+    <t xml:space="preserve">9.99161720275879</t>
   </si>
   <si>
     <t xml:space="preserve">9.59893417358398</t>
@@ -1838,25 +1838,25 @@
     <t xml:space="preserve">9.77345943450928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81709098815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29351425170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46803951263428</t>
+    <t xml:space="preserve">9.8170919418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29351329803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46804046630859</t>
   </si>
   <si>
     <t xml:space="preserve">9.55530261993408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64256572723389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9043550491333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33714580535889</t>
+    <t xml:space="preserve">9.64256477355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90435600280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33714485168457</t>
   </si>
   <si>
     <t xml:space="preserve">9.9479866027832</t>
@@ -1865,16 +1865,16 @@
     <t xml:space="preserve">9.86072254180908</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5151968002319</t>
+    <t xml:space="preserve">10.5151958465576</t>
   </si>
   <si>
     <t xml:space="preserve">10.4279327392578</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5588274002075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6024589538574</t>
+    <t xml:space="preserve">10.5588283538818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6024580001831</t>
   </si>
   <si>
     <t xml:space="preserve">10.8206167221069</t>
@@ -1883,7 +1883,7 @@
     <t xml:space="preserve">10.7333536148071</t>
   </si>
   <si>
-    <t xml:space="preserve">10.776985168457</t>
+    <t xml:space="preserve">10.7769861221313</t>
   </si>
   <si>
     <t xml:space="preserve">10.2970390319824</t>
@@ -1892,7 +1892,7 @@
     <t xml:space="preserve">10.3843011856079</t>
   </si>
   <si>
-    <t xml:space="preserve">10.340669631958</t>
+    <t xml:space="preserve">10.3406715393066</t>
   </si>
   <si>
     <t xml:space="preserve">10.2097749710083</t>
@@ -1901,7 +1901,7 @@
     <t xml:space="preserve">10.2534065246582</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0788822174072</t>
+    <t xml:space="preserve">10.0788812637329</t>
   </si>
   <si>
     <t xml:space="preserve">9.51167106628418</t>
@@ -1913,7 +1913,7 @@
     <t xml:space="preserve">9.68619823455811</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98809242248535</t>
+    <t xml:space="preserve">8.98809337615967</t>
   </si>
   <si>
     <t xml:space="preserve">9.42440795898438</t>
@@ -1922,28 +1922,28 @@
     <t xml:space="preserve">11.6496162414551</t>
   </si>
   <si>
-    <t xml:space="preserve">11.562352180481</t>
+    <t xml:space="preserve">11.5623531341553</t>
   </si>
   <si>
     <t xml:space="preserve">11.7805099487305</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9114036560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9550352096558</t>
+    <t xml:space="preserve">11.9114046096802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9550361633301</t>
   </si>
   <si>
     <t xml:space="preserve">11.693247795105</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3040885925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2604570388794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2168254852295</t>
+    <t xml:space="preserve">12.3040895462036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2604560852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2168245315552</t>
   </si>
   <si>
     <t xml:space="preserve">12.3913507461548</t>
@@ -1964,10 +1964,10 @@
     <t xml:space="preserve">12.0422992706299</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3005647659302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3441953659058</t>
+    <t xml:space="preserve">11.3005638122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3441944122314</t>
   </si>
   <si>
     <t xml:space="preserve">10.9951429367065</t>
@@ -1976,7 +1976,7 @@
     <t xml:space="preserve">10.4715642929077</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9078807830811</t>
+    <t xml:space="preserve">10.9078798294067</t>
   </si>
   <si>
     <t xml:space="preserve">11.4314584732056</t>
@@ -1997,49 +1997,49 @@
     <t xml:space="preserve">11.5187206268311</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6234359741211</t>
+    <t xml:space="preserve">11.6234369277954</t>
   </si>
   <si>
     <t xml:space="preserve">11.4489107131958</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6408891677856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7281522750854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9201307296753</t>
+    <t xml:space="preserve">11.64089012146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7281513214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.920129776001</t>
   </si>
   <si>
     <t xml:space="preserve">11.1173105239868</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0998582839966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.803165435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7508058547974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3319435119629</t>
+    <t xml:space="preserve">11.0998592376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8031644821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7508068084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3319444656372</t>
   </si>
   <si>
     <t xml:space="preserve">10.1050596237183</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81839275360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69297313690186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7108907699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1408929824829</t>
+    <t xml:space="preserve">9.81839179992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69297409057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71089172363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1408939361572</t>
   </si>
   <si>
     <t xml:space="preserve">10.2663106918335</t>
@@ -2051,19 +2051,19 @@
     <t xml:space="preserve">10.1229763031006</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1588096618652</t>
+    <t xml:space="preserve">10.1588106155396</t>
   </si>
   <si>
     <t xml:space="preserve">10.0692262649536</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0871429443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4633960723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7858972549438</t>
+    <t xml:space="preserve">10.0871438980103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4633951187134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7858963012695</t>
   </si>
   <si>
     <t xml:space="preserve">10.5708961486816</t>
@@ -2072,7 +2072,7 @@
     <t xml:space="preserve">10.7142305374146</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7500638961792</t>
+    <t xml:space="preserve">10.7500629425049</t>
   </si>
   <si>
     <t xml:space="preserve">11.1621494293213</t>
@@ -2081,34 +2081,34 @@
     <t xml:space="preserve">10.8754816055298</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6425628662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5888118743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5171451568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8575649261475</t>
+    <t xml:space="preserve">10.6425638198853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.588812828064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5171461105347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8575639724731</t>
   </si>
   <si>
     <t xml:space="preserve">10.9113149642944</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6067295074463</t>
+    <t xml:space="preserve">10.6067304611206</t>
   </si>
   <si>
     <t xml:space="preserve">10.6604795455933</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3021450042725</t>
+    <t xml:space="preserve">10.3021440505981</t>
   </si>
   <si>
     <t xml:space="preserve">10.4096450805664</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3558950424194</t>
+    <t xml:space="preserve">10.3558940887451</t>
   </si>
   <si>
     <t xml:space="preserve">10.6783971786499</t>
@@ -2120,7 +2120,7 @@
     <t xml:space="preserve">10.535062789917</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1800661087036</t>
+    <t xml:space="preserve">11.1800651550293</t>
   </si>
   <si>
     <t xml:space="preserve">10.9829816818237</t>
@@ -2138,7 +2138,7 @@
     <t xml:space="preserve">11.9146537780762</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9325704574585</t>
+    <t xml:space="preserve">11.9325714111328</t>
   </si>
   <si>
     <t xml:space="preserve">12.0221548080444</t>
@@ -2147,10 +2147,10 @@
     <t xml:space="preserve">11.8788204193115</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2371559143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3267393112183</t>
+    <t xml:space="preserve">12.2371549606323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3267402648926</t>
   </si>
   <si>
     <t xml:space="preserve">12.4521570205688</t>
@@ -2159,7 +2159,7 @@
     <t xml:space="preserve">12.0938215255737</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3984069824219</t>
+    <t xml:space="preserve">12.3984079360962</t>
   </si>
   <si>
     <t xml:space="preserve">12.201322555542</t>
@@ -2186,7 +2186,7 @@
     <t xml:space="preserve">13.258412361145</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4017467498779</t>
+    <t xml:space="preserve">13.4017457962036</t>
   </si>
   <si>
     <t xml:space="preserve">13.4375791549683</t>
@@ -2195,19 +2195,19 @@
     <t xml:space="preserve">13.6884145736694</t>
   </si>
   <si>
-    <t xml:space="preserve">13.903416633606</t>
+    <t xml:space="preserve">13.9034156799316</t>
   </si>
   <si>
     <t xml:space="preserve">14.6559209823608</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2438335418701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6380033493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.92467212677</t>
+    <t xml:space="preserve">14.2438344955444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6380043029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9246711730957</t>
   </si>
   <si>
     <t xml:space="preserve">14.5125865936279</t>
@@ -2228,16 +2228,16 @@
     <t xml:space="preserve">14.2617511749268</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8888387680054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8171710968018</t>
+    <t xml:space="preserve">14.8888397216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8171720504761</t>
   </si>
   <si>
     <t xml:space="preserve">14.387167930603</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7634201049805</t>
+    <t xml:space="preserve">14.7634191513062</t>
   </si>
   <si>
     <t xml:space="preserve">14.6200866699219</t>
@@ -2246,10 +2246,10 @@
     <t xml:space="preserve">14.9067535400391</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1217546463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0321741104126</t>
+    <t xml:space="preserve">15.1217555999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.032172203064</t>
   </si>
   <si>
     <t xml:space="preserve">14.7455034255981</t>
@@ -2288,13 +2288,13 @@
     <t xml:space="preserve">12.9717426300049</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4700746536255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2404956817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6525802612305</t>
+    <t xml:space="preserve">12.4700736999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2404947280884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6525812149048</t>
   </si>
   <si>
     <t xml:space="preserve">13.5809135437012</t>
@@ -2306,22 +2306,22 @@
     <t xml:space="preserve">13.4913301467896</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2225780487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2046604156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0613269805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0075778961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6313247680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0971612930298</t>
+    <t xml:space="preserve">13.2225790023804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2046613693237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0613279342651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0075769424438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6313257217407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0971603393555</t>
   </si>
   <si>
     <t xml:space="preserve">13.0792446136475</t>
@@ -2357,13 +2357,13 @@
     <t xml:space="preserve">13.2763290405273</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7925748825073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5954923629761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5238246917725</t>
+    <t xml:space="preserve">12.7925758361816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5954914093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5238237380981</t>
   </si>
   <si>
     <t xml:space="preserve">12.5059070587158</t>
@@ -2375,10 +2375,10 @@
     <t xml:space="preserve">12.3088226318359</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5417413711548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8284091949463</t>
+    <t xml:space="preserve">12.5417404174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8284101486206</t>
   </si>
   <si>
     <t xml:space="preserve">12.3804903030396</t>
@@ -2396,10 +2396,10 @@
     <t xml:space="preserve">12.7746591567993</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4342403411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9504871368408</t>
+    <t xml:space="preserve">12.4342412948608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9504880905151</t>
   </si>
   <si>
     <t xml:space="preserve">12.2192392349243</t>
@@ -2414,7 +2414,7 @@
     <t xml:space="preserve">11.9684047698975</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0400714874268</t>
+    <t xml:space="preserve">12.0400705337524</t>
   </si>
   <si>
     <t xml:space="preserve">12.0042381286621</t>
@@ -2423,7 +2423,7 @@
     <t xml:space="preserve">12.255072593689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7388248443604</t>
+    <t xml:space="preserve">12.7388257980347</t>
   </si>
   <si>
     <t xml:space="preserve">13.7421655654907</t>
@@ -2432,10 +2432,10 @@
     <t xml:space="preserve">13.7063312530518</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0825834274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0109157562256</t>
+    <t xml:space="preserve">14.0825843811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0109167098999</t>
   </si>
   <si>
     <t xml:space="preserve">13.7242479324341</t>
@@ -2444,10 +2444,10 @@
     <t xml:space="preserve">14.0467500686646</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0646657943726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9392490386963</t>
+    <t xml:space="preserve">14.0646667480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9392499923706</t>
   </si>
   <si>
     <t xml:space="preserve">13.6346645355225</t>
@@ -2471,10 +2471,10 @@
     <t xml:space="preserve">13.5450801849365</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4734134674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1867446899414</t>
+    <t xml:space="preserve">13.4734125137329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1867456436157</t>
   </si>
   <si>
     <t xml:space="preserve">13.3838291168213</t>
@@ -2483,7 +2483,7 @@
     <t xml:space="preserve">13.5988302230835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.70299243927</t>
+    <t xml:space="preserve">12.7029914855957</t>
   </si>
   <si>
     <t xml:space="preserve">11.8429870605469</t>
@@ -2492,16 +2492,16 @@
     <t xml:space="preserve">11.7892360687256</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6817359924316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0759048461914</t>
+    <t xml:space="preserve">11.6817350387573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0759038925171</t>
   </si>
   <si>
     <t xml:space="preserve">11.5742359161377</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2159004211426</t>
+    <t xml:space="preserve">11.2158994674683</t>
   </si>
   <si>
     <t xml:space="preserve">11.3592338562012</t>
@@ -2510,7 +2510,7 @@
     <t xml:space="preserve">11.4309015274048</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3054828643799</t>
+    <t xml:space="preserve">11.3054838180542</t>
   </si>
   <si>
     <t xml:space="preserve">11.2875671386719</t>
@@ -3482,7 +3482,7 @@
     <t xml:space="preserve">17.7199993133545</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8199996948242</t>
+    <t xml:space="preserve">17.6200008392334</t>
   </si>
 </sst>
 </file>
@@ -68925,22 +68925,22 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45966.6911111111</v>
+        <v>45967.693125</v>
       </c>
       <c r="B2505" t="n">
-        <v>22443</v>
+        <v>14956</v>
       </c>
       <c r="C2505" t="n">
-        <v>17.9400005340576</v>
+        <v>17.7999992370605</v>
       </c>
       <c r="D2505" t="n">
-        <v>17.4200000762939</v>
+        <v>17.5400009155273</v>
       </c>
       <c r="E2505" t="n">
-        <v>17.8999996185303</v>
+        <v>17.7800006866455</v>
       </c>
       <c r="F2505" t="n">
-        <v>17.8199996948242</v>
+        <v>17.6200008392334</v>
       </c>
       <c r="G2505" t="s">
         <v>1156</v>

--- a/data/ORS.MI.xlsx
+++ b/data/ORS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1161" uniqueCount="1161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1162" uniqueCount="1162">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08406352996826</t>
+    <t xml:space="preserve">8.08406257629395</t>
   </si>
   <si>
     <t xml:space="preserve">ORS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98275852203369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06380271911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94223785400391</t>
+    <t xml:space="preserve">7.98275899887085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06380176544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94223642349243</t>
   </si>
   <si>
     <t xml:space="preserve">7.82472562789917</t>
@@ -59,25 +59,25 @@
     <t xml:space="preserve">7.93818521499634</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9017162322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03948974609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92602968215942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86119365692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82067394256592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93413400650024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02328109741211</t>
+    <t xml:space="preserve">7.90171575546265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03948879241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92602872848511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86119413375854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82067346572876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93413305282593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02328014373779</t>
   </si>
   <si>
     <t xml:space="preserve">8.08811473846436</t>
@@ -86,37 +86,37 @@
     <t xml:space="preserve">8.14484596252441</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69910669326782</t>
+    <t xml:space="preserve">7.69910764694214</t>
   </si>
   <si>
     <t xml:space="preserve">7.8044638633728</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97465467453003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01112461090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01517677307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79230833053589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82877731323242</t>
+    <t xml:space="preserve">7.97465562820435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01112365722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01517581939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79230880737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82877779006958</t>
   </si>
   <si>
     <t xml:space="preserve">8.34745407104492</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84093379974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90982055664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85714101791382</t>
+    <t xml:space="preserve">7.84093332290649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90982103347778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85714197158813</t>
   </si>
   <si>
     <t xml:space="preserve">7.7801513671875</t>
@@ -128,112 +128,112 @@
     <t xml:space="preserve">7.97870779037476</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88550806045532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95034217834473</t>
+    <t xml:space="preserve">7.88550710678101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95034265518188</t>
   </si>
   <si>
     <t xml:space="preserve">8.00301933288574</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01922798156738</t>
+    <t xml:space="preserve">8.0192289352417</t>
   </si>
   <si>
     <t xml:space="preserve">7.91792440414429</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10027313232422</t>
+    <t xml:space="preserve">8.10027122497559</t>
   </si>
   <si>
     <t xml:space="preserve">8.104323387146</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18536853790283</t>
+    <t xml:space="preserve">8.18536758422852</t>
   </si>
   <si>
     <t xml:space="preserve">8.20157432556152</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11242866516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07595825195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03138446807861</t>
+    <t xml:space="preserve">8.11242771148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07595920562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03138542175293</t>
   </si>
   <si>
     <t xml:space="preserve">8.09622001647949</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1772632598877</t>
+    <t xml:space="preserve">8.17726230621338</t>
   </si>
   <si>
     <t xml:space="preserve">8.05569839477539</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12053298950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2583065032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4203929901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67162799835205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55816555023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42849826812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52429008483887</t>
+    <t xml:space="preserve">8.12053203582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25830745697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42039203643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67162609100342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55816650390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42849731445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52428913116455</t>
   </si>
   <si>
     <t xml:space="preserve">8.45921802520752</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50802135467529</t>
+    <t xml:space="preserve">8.50802040100098</t>
   </si>
   <si>
     <t xml:space="preserve">8.60562896728516</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5324239730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61376094818115</t>
+    <t xml:space="preserve">8.53242588043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61376190185547</t>
   </si>
   <si>
     <t xml:space="preserve">8.67070007324219</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87404632568359</t>
+    <t xml:space="preserve">8.87404727935791</t>
   </si>
   <si>
     <t xml:space="preserve">8.7927074432373</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90658187866211</t>
+    <t xml:space="preserve">8.90658092498779</t>
   </si>
   <si>
     <t xml:space="preserve">8.86591243743896</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94724941253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93911647796631</t>
+    <t xml:space="preserve">8.94725131988525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93911743164062</t>
   </si>
   <si>
     <t xml:space="preserve">8.78457260131836</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74390411376953</t>
+    <t xml:space="preserve">8.74390316009521</t>
   </si>
   <si>
     <t xml:space="preserve">8.91471481323242</t>
@@ -242,55 +242,55 @@
     <t xml:space="preserve">8.92284965515137</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10992813110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07739162445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11806201934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13432884216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15059661865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15873241424561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7357702255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6788330078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85777854919434</t>
+    <t xml:space="preserve">9.1099271774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.077392578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11806297302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1343297958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15059852600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15873146057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73577117919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67883396148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85777950286865</t>
   </si>
   <si>
     <t xml:space="preserve">8.72763633728027</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7032356262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66256523132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69510173797607</t>
+    <t xml:space="preserve">8.70323467254639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66256618499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69510078430176</t>
   </si>
   <si>
     <t xml:space="preserve">8.6218957901001</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80084228515625</t>
+    <t xml:space="preserve">8.80084037780762</t>
   </si>
   <si>
     <t xml:space="preserve">8.77643966674805</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68696784973145</t>
+    <t xml:space="preserve">8.68696689605713</t>
   </si>
   <si>
     <t xml:space="preserve">8.54869174957275</t>
@@ -299,67 +299,67 @@
     <t xml:space="preserve">8.54055690765381</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58122730255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46735286712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51615619659424</t>
+    <t xml:space="preserve">8.58122825622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46735382080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51615524291992</t>
   </si>
   <si>
     <t xml:space="preserve">8.49988746643066</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45108413696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63002967834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80897521972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89031314849854</t>
+    <t xml:space="preserve">8.45108318328857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63003063201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80897617340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89031410217285</t>
   </si>
   <si>
     <t xml:space="preserve">8.930983543396</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96351623535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05299091339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30514049530029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1017951965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1912670135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35394477844238</t>
+    <t xml:space="preserve">8.9635181427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0529899597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30513954162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10179328918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19126605987549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35394382476807</t>
   </si>
   <si>
     <t xml:space="preserve">9.4759521484375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54915714263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58982467651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66303062438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71996593475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85824298858643</t>
+    <t xml:space="preserve">9.54915523529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5898265838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66303157806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71996784210205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85824394226074</t>
   </si>
   <si>
     <t xml:space="preserve">10.0046539306641</t>
@@ -371,10 +371,10 @@
     <t xml:space="preserve">10.2486696243286</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3381423950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.598424911499</t>
+    <t xml:space="preserve">10.3381404876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5984268188477</t>
   </si>
   <si>
     <t xml:space="preserve">10.4276142120361</t>
@@ -386,10 +386,10 @@
     <t xml:space="preserve">10.5252199172974</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4601488113403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5658912658691</t>
+    <t xml:space="preserve">10.4601497650146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5658893585205</t>
   </si>
   <si>
     <t xml:space="preserve">10.5821571350098</t>
@@ -398,28 +398,28 @@
     <t xml:space="preserve">10.7773704528809</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9807176589966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8749761581421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6553621292114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6797637939453</t>
+    <t xml:space="preserve">10.9807167053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8749771118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6553630828857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6797647476196</t>
   </si>
   <si>
     <t xml:space="preserve">10.5740242004395</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5170869827271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5414886474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5577564239502</t>
+    <t xml:space="preserve">10.5170860290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5414876937866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5577554702759</t>
   </si>
   <si>
     <t xml:space="preserve">10.5089530944824</t>
@@ -428,31 +428,31 @@
     <t xml:space="preserve">10.8180389404297</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6878976821899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7611026763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6472282409668</t>
+    <t xml:space="preserve">10.6878967285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7611017227173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6472301483154</t>
   </si>
   <si>
     <t xml:space="preserve">10.8993787765503</t>
   </si>
   <si>
-    <t xml:space="preserve">10.883111000061</t>
+    <t xml:space="preserve">10.8831100463867</t>
   </si>
   <si>
     <t xml:space="preserve">10.6716299057007</t>
   </si>
   <si>
-    <t xml:space="preserve">10.736701965332</t>
+    <t xml:space="preserve">10.7367010116577</t>
   </si>
   <si>
     <t xml:space="preserve">11.0051183700562</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0213871002197</t>
+    <t xml:space="preserve">11.0213861465454</t>
   </si>
   <si>
     <t xml:space="preserve">11.184063911438</t>
@@ -461,10 +461,10 @@
     <t xml:space="preserve">11.4036769866943</t>
   </si>
   <si>
-    <t xml:space="preserve">11.395544052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3386077880859</t>
+    <t xml:space="preserve">11.3955430984497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3386068344116</t>
   </si>
   <si>
     <t xml:space="preserve">11.322338104248</t>
@@ -473,7 +473,7 @@
     <t xml:space="preserve">11.3304738998413</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3630084991455</t>
+    <t xml:space="preserve">11.3630094528198</t>
   </si>
   <si>
     <t xml:space="preserve">11.0783233642578</t>
@@ -482,25 +482,25 @@
     <t xml:space="preserve">10.6065587997437</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8424425125122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8505754470825</t>
+    <t xml:space="preserve">10.8424415588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8505764007568</t>
   </si>
   <si>
     <t xml:space="preserve">10.6390943527222</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4113454818726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2080001831055</t>
+    <t xml:space="preserve">10.4113464355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2080011367798</t>
   </si>
   <si>
     <t xml:space="preserve">10.2730703353882</t>
   </si>
   <si>
-    <t xml:space="preserve">10.232400894165</t>
+    <t xml:space="preserve">10.2323999404907</t>
   </si>
   <si>
     <t xml:space="preserve">10.3218746185303</t>
@@ -509,22 +509,22 @@
     <t xml:space="preserve">10.3706769943237</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3300085067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3056058883667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2568035125732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1835975646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4845504760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3625411987305</t>
+    <t xml:space="preserve">10.3300065994263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.305606842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2568044662476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1835966110229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4845514297485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3625421524048</t>
   </si>
   <si>
     <t xml:space="preserve">10.4438819885254</t>
@@ -539,22 +539,22 @@
     <t xml:space="preserve">11.0376539230347</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0620555877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.102725982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1433935165405</t>
+    <t xml:space="preserve">11.0620565414429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1027250289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1433944702148</t>
   </si>
   <si>
     <t xml:space="preserve">11.1759300231934</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1352596282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0701904296875</t>
+    <t xml:space="preserve">11.1352605819702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0701894760132</t>
   </si>
   <si>
     <t xml:space="preserve">11.118992805481</t>
@@ -563,19 +563,19 @@
     <t xml:space="preserve">11.1515283584595</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2247333526611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0457887649536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5008201599121</t>
+    <t xml:space="preserve">11.2247323989868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0457878112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5008192062378</t>
   </si>
   <si>
     <t xml:space="preserve">10.1347951889038</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36161327362061</t>
+    <t xml:space="preserve">8.36161231994629</t>
   </si>
   <si>
     <t xml:space="preserve">8.01998996734619</t>
@@ -584,16 +584,16 @@
     <t xml:space="preserve">8.10946273803711</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3941478729248</t>
+    <t xml:space="preserve">8.39414691925049</t>
   </si>
   <si>
     <t xml:space="preserve">8.21520233154297</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33721160888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31280899047852</t>
+    <t xml:space="preserve">8.3372106552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3128080368042</t>
   </si>
   <si>
     <t xml:space="preserve">8.18266773223877</t>
@@ -605,55 +605,55 @@
     <t xml:space="preserve">8.23960494995117</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49175643920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5893611907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76017093658447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29654121398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25587368011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17453289031982</t>
+    <t xml:space="preserve">8.49175453186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58936023712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76017284393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29654312133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25587177276611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17453384399414</t>
   </si>
   <si>
     <t xml:space="preserve">8.1908016204834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23147106170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28027248382568</t>
+    <t xml:space="preserve">8.23147010803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2802734375</t>
   </si>
   <si>
     <t xml:space="preserve">8.14199829101562</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1582670211792</t>
+    <t xml:space="preserve">8.15826606750488</t>
   </si>
   <si>
     <t xml:space="preserve">8.16639995574951</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12166309356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05252647399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89798307418823</t>
+    <t xml:space="preserve">8.12166213989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05252552032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89798212051392</t>
   </si>
   <si>
     <t xml:space="preserve">7.85731315612793</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93051624298096</t>
+    <t xml:space="preserve">7.93051671981812</t>
   </si>
   <si>
     <t xml:space="preserve">7.9061164855957</t>
@@ -662,22 +662,22 @@
     <t xml:space="preserve">7.93865251541138</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8491792678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80851030349731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62956428527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57262802124023</t>
+    <t xml:space="preserve">7.84917879104614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80850982666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62956476211548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57262754440308</t>
   </si>
   <si>
     <t xml:space="preserve">7.48315572738647</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66616725921631</t>
+    <t xml:space="preserve">7.66616678237915</t>
   </si>
   <si>
     <t xml:space="preserve">7.60516309738159</t>
@@ -686,28 +686,28 @@
     <t xml:space="preserve">7.54009246826172</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5238242149353</t>
+    <t xml:space="preserve">7.52382373809814</t>
   </si>
   <si>
     <t xml:space="preserve">7.47908687591553</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61329650878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54822540283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56449413299561</t>
+    <t xml:space="preserve">7.61329793930054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54822587966919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56449365615845</t>
   </si>
   <si>
     <t xml:space="preserve">7.50755643844604</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4668869972229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49129009246826</t>
+    <t xml:space="preserve">7.46688604354858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49128866195679</t>
   </si>
   <si>
     <t xml:space="preserve">7.49942350387573</t>
@@ -719,25 +719,25 @@
     <t xml:space="preserve">7.27980804443359</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37741565704346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38554954528809</t>
+    <t xml:space="preserve">7.37741470336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38554859161377</t>
   </si>
   <si>
     <t xml:space="preserve">7.36928081512451</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32047843933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34488010406494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28794193267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04392576217651</t>
+    <t xml:space="preserve">7.32047653198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34487962722778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28794240951538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04392671585083</t>
   </si>
   <si>
     <t xml:space="preserve">7.15780067443848</t>
@@ -746,43 +746,43 @@
     <t xml:space="preserve">7.39368295669556</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42621755599976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40181589126587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30421018600464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3611478805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20660352706909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35301303863525</t>
+    <t xml:space="preserve">7.42621898651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40181636810303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3042106628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36114835739136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20660400390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3530125617981</t>
   </si>
   <si>
     <t xml:space="preserve">7.336745262146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27167415618896</t>
+    <t xml:space="preserve">7.27167463302612</t>
   </si>
   <si>
     <t xml:space="preserve">7.23100423812866</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32861137390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26354122161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23913908004761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22287178039551</t>
+    <t xml:space="preserve">7.32861185073853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26354169845581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23913955688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22287130355835</t>
   </si>
   <si>
     <t xml:space="preserve">7.24727344512939</t>
@@ -791,85 +791,85 @@
     <t xml:space="preserve">7.44248628616333</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25540781021118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18220233917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29607486724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16593503952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14153337478638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0520601272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07646179199219</t>
+    <t xml:space="preserve">7.25540733337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18220090866089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29607534408569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16593456268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14153289794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05205965042114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07646226882935</t>
   </si>
   <si>
     <t xml:space="preserve">7.0357928276062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01952505111694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87311458587646</t>
+    <t xml:space="preserve">7.0195255279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87311506271362</t>
   </si>
   <si>
     <t xml:space="preserve">6.677903175354</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85124778747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93379163742065</t>
+    <t xml:space="preserve">6.85124731063843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93379211425781</t>
   </si>
   <si>
     <t xml:space="preserve">7.26397371292114</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14840888977051</t>
+    <t xml:space="preserve">7.14841032028198</t>
   </si>
   <si>
     <t xml:space="preserve">7.09888315200806</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18142890930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16491985321045</t>
+    <t xml:space="preserve">7.1814284324646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16491842269897</t>
   </si>
   <si>
     <t xml:space="preserve">7.14015579223633</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21444654464722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17317342758179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97506427764893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84299325942993</t>
+    <t xml:space="preserve">7.21444606781006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17317390441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97506475448608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84299278259277</t>
   </si>
   <si>
     <t xml:space="preserve">6.60361194610596</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62012052536011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67790269851685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80997514724731</t>
+    <t xml:space="preserve">6.62012100219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67790222167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.809974193573</t>
   </si>
   <si>
     <t xml:space="preserve">6.54583072662354</t>
@@ -878,13 +878,13 @@
     <t xml:space="preserve">6.31470394134521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32295846939087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34772253036499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38074064254761</t>
+    <t xml:space="preserve">6.32295894622803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34772300720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38074016571045</t>
   </si>
   <si>
     <t xml:space="preserve">6.39724922180176</t>
@@ -893,7 +893,7 @@
     <t xml:space="preserve">6.47153997421265</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28168630599976</t>
+    <t xml:space="preserve">6.2816858291626</t>
   </si>
   <si>
     <t xml:space="preserve">6.22390460968018</t>
@@ -902,16 +902,16 @@
     <t xml:space="preserve">6.09183216094971</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90197849273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9597601890564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9927773475647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20739507675171</t>
+    <t xml:space="preserve">5.90197801589966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95975971221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99277782440186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20739555358887</t>
   </si>
   <si>
     <t xml:space="preserve">6.14135932922363</t>
@@ -920,205 +920,205 @@
     <t xml:space="preserve">6.19088649749756</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14961338043213</t>
+    <t xml:space="preserve">6.14961385726929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0753231048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25692224502563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00928783416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9845232963562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12485027313232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13310480117798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27343082427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44677591323853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55408525466919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51281213760376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36423110961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24041366577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21564960479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23215913772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24866771697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11659574508667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10834074020386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05055952072144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89372444152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.778160572052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69561529159546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79466915130615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80292367935181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82768774032593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78641510009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73688745498657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85245132446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29819583892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18263244628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15786838531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03405046463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08357715606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81943368911743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91848659515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86070537567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76165246963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75339651107788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81117868423462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70387029647827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74514198303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83594226837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71212434768677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84419679641724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94325065612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96801424026489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87721490859985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88546895980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93499612808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02579593658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06706857681274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38899517059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19914102554321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04230499267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05881500244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9515061378479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17437744140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17601871490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29349803924561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25993251800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20958423614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09210586547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10888957977295</t>
   </si>
   <si>
     <t xml:space="preserve">6.07532358169556</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25692319869995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00928735733032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98452281951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12485074996948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13310480117798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27343082427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44677591323853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55408477783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51281261444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36423110961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24041414260864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21565008163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23215913772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24866771697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11659622192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1083402633667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05055952072144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89372396469116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.778160572052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6956148147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79466962814331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80292415618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82768821716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78641510009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73688745498657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85245084762573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29819536209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18263244628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1578688621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03405046463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08357763290405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81943321228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91848659515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86070537567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76165199279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75339698791504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81117820739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70387077331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74514198303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83594226837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71212434768677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84419679641724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94325065612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96801471710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87721490859985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88546991348267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93499612808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02579641342163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06706857681274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3889946937561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19914054870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04230451583862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05881452560425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95150566101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17437744140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17601919174194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29349803924561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25993251800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20958423614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0921049118042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10888910293579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0753231048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14245319366455</t>
+    <t xml:space="preserve">6.14245414733887</t>
   </si>
   <si>
     <t xml:space="preserve">6.05854082107544</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02497529983521</t>
+    <t xml:space="preserve">6.02497482299805</t>
   </si>
   <si>
     <t xml:space="preserve">5.97462749481201</t>
@@ -1127,7 +1127,7 @@
     <t xml:space="preserve">5.95784425735474</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15923690795898</t>
+    <t xml:space="preserve">6.15923738479614</t>
   </si>
   <si>
     <t xml:space="preserve">6.12567138671875</t>
@@ -1136,7 +1136,7 @@
     <t xml:space="preserve">6.19280195236206</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42775869369507</t>
+    <t xml:space="preserve">6.42775964736938</t>
   </si>
   <si>
     <t xml:space="preserve">6.71306467056274</t>
@@ -1148,7 +1148,7 @@
     <t xml:space="preserve">6.69628238677979</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78019571304321</t>
+    <t xml:space="preserve">6.78019523620605</t>
   </si>
   <si>
     <t xml:space="preserve">6.7298469543457</t>
@@ -1157,16 +1157,16 @@
     <t xml:space="preserve">6.629150390625</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56202030181885</t>
+    <t xml:space="preserve">6.56201982498169</t>
   </si>
   <si>
     <t xml:space="preserve">6.54523801803589</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67949867248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66271638870239</t>
+    <t xml:space="preserve">6.67949914932251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66271686553955</t>
   </si>
   <si>
     <t xml:space="preserve">6.57880306243896</t>
@@ -1175,19 +1175,19 @@
     <t xml:space="preserve">6.37741088867188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3438458442688</t>
+    <t xml:space="preserve">6.34384632110596</t>
   </si>
   <si>
     <t xml:space="preserve">6.22636747360229</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36062908172607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67253923416138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55506038665771</t>
+    <t xml:space="preserve">6.36062860488892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67253875732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55506086349487</t>
   </si>
   <si>
     <t xml:space="preserve">5.68932247161865</t>
@@ -1199,28 +1199,28 @@
     <t xml:space="preserve">5.53827810287476</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43758249282837</t>
+    <t xml:space="preserve">5.43758201599121</t>
   </si>
   <si>
     <t xml:space="preserve">5.45436525344849</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60540866851807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52149534225464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50471353530884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48793029785156</t>
+    <t xml:space="preserve">5.60540819168091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5214958190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50471305847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48792934417725</t>
   </si>
   <si>
     <t xml:space="preserve">5.35366868972778</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3704514503479</t>
+    <t xml:space="preserve">5.37045097351074</t>
   </si>
   <si>
     <t xml:space="preserve">5.42079925537109</t>
@@ -1229,7 +1229,7 @@
     <t xml:space="preserve">5.28653860092163</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30332040786743</t>
+    <t xml:space="preserve">5.30332088470459</t>
   </si>
   <si>
     <t xml:space="preserve">5.26975584030151</t>
@@ -1238,19 +1238,19 @@
     <t xml:space="preserve">5.38723421096802</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32010412216187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65575695037842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75645303726196</t>
+    <t xml:space="preserve">5.32010364532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65575647354126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75645351409912</t>
   </si>
   <si>
     <t xml:space="preserve">5.70610475540161</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72288703918457</t>
+    <t xml:space="preserve">5.72288656234741</t>
   </si>
   <si>
     <t xml:space="preserve">5.739670753479</t>
@@ -1259,19 +1259,19 @@
     <t xml:space="preserve">5.6389741897583</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57184362411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18584156036377</t>
+    <t xml:space="preserve">5.57184410095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18584203720093</t>
   </si>
   <si>
     <t xml:space="preserve">5.2026252746582</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21940803527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16905975341797</t>
+    <t xml:space="preserve">5.21940851211548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16906023025513</t>
   </si>
   <si>
     <t xml:space="preserve">5.13549327850342</t>
@@ -1283,16 +1283,16 @@
     <t xml:space="preserve">4.95088481903076</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03479862213135</t>
+    <t xml:space="preserve">5.03479814529419</t>
   </si>
   <si>
     <t xml:space="preserve">5.15227651596069</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11871194839478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06836271286011</t>
+    <t xml:space="preserve">5.11871147155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06836318969727</t>
   </si>
   <si>
     <t xml:space="preserve">5.08514595031738</t>
@@ -1307,16 +1307,16 @@
     <t xml:space="preserve">5.33688640594482</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79001760482788</t>
+    <t xml:space="preserve">5.79001808166504</t>
   </si>
   <si>
     <t xml:space="preserve">5.77323532104492</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58862590789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81662321090698</t>
+    <t xml:space="preserve">5.58862638473511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81662368774414</t>
   </si>
   <si>
     <t xml:space="preserve">4.79984092712402</t>
@@ -1328,7 +1328,7 @@
     <t xml:space="preserve">4.36349201202393</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31314373016357</t>
+    <t xml:space="preserve">4.31314420700073</t>
   </si>
   <si>
     <t xml:space="preserve">4.19566488265991</t>
@@ -1346,7 +1346,7 @@
     <t xml:space="preserve">4.06979560852051</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12014293670654</t>
+    <t xml:space="preserve">4.1201434135437</t>
   </si>
   <si>
     <t xml:space="preserve">4.34670877456665</t>
@@ -1358,61 +1358,61 @@
     <t xml:space="preserve">4.04462099075317</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15370798110962</t>
+    <t xml:space="preserve">4.15370845794678</t>
   </si>
   <si>
     <t xml:space="preserve">4.26279640197754</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16210031509399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14531707763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9942729473114</t>
+    <t xml:space="preserve">4.16209983825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14531755447388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99427223205566</t>
   </si>
   <si>
     <t xml:space="preserve">4.09496927261353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98588156700134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27957820892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22923040390015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21244812011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03623008728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12877893447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16283130645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07770204544067</t>
+    <t xml:space="preserve">3.98588132858276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2795786857605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22922992706299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21244764328003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03622961044312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12877941131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16283082962036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07770156860352</t>
   </si>
   <si>
     <t xml:space="preserve">4.00108480453491</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20539522171021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37565469741821</t>
+    <t xml:space="preserve">4.20539569854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37565422058105</t>
   </si>
   <si>
     <t xml:space="preserve">4.21390867233276</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22242164611816</t>
+    <t xml:space="preserve">4.22242116928101</t>
   </si>
   <si>
     <t xml:space="preserve">4.25647354125977</t>
@@ -1424,7 +1424,7 @@
     <t xml:space="preserve">4.32457685470581</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30755043029785</t>
+    <t xml:space="preserve">4.30755138397217</t>
   </si>
   <si>
     <t xml:space="preserve">4.23944711685181</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">4.35862827301025</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51186180114746</t>
+    <t xml:space="preserve">4.5118613243103</t>
   </si>
   <si>
     <t xml:space="preserve">5.5334153175354</t>
@@ -1445,25 +1445,25 @@
     <t xml:space="preserve">5.8909592628479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73772573471069</t>
+    <t xml:space="preserve">5.73772621154785</t>
   </si>
   <si>
     <t xml:space="preserve">5.5504412651062</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5844931602478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.567467212677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41423463821411</t>
+    <t xml:space="preserve">5.58449268341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56746768951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41423416137695</t>
   </si>
   <si>
     <t xml:space="preserve">5.2610011100769</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48233795166016</t>
+    <t xml:space="preserve">5.482337474823</t>
   </si>
   <si>
     <t xml:space="preserve">5.44828605651855</t>
@@ -1475,7 +1475,7 @@
     <t xml:space="preserve">5.66962242126465</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5163893699646</t>
+    <t xml:space="preserve">5.51638984680176</t>
   </si>
   <si>
     <t xml:space="preserve">5.70367431640625</t>
@@ -1484,13 +1484,13 @@
     <t xml:space="preserve">5.32910490036011</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27802705764771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43126010894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31207847595215</t>
+    <t xml:space="preserve">5.27802658081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43126058578491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31207799911499</t>
   </si>
   <si>
     <t xml:space="preserve">5.2269492149353</t>
@@ -1502,40 +1502,40 @@
     <t xml:space="preserve">4.95453500747681</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93750905990601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05669069290161</t>
+    <t xml:space="preserve">4.93750953674316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05669021606445</t>
   </si>
   <si>
     <t xml:space="preserve">5.03966426849365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97156095504761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8864312171936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02263832092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92048263549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90345764160156</t>
+    <t xml:space="preserve">4.97156143188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88643169403076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02263879776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92048311233521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9034571647644</t>
   </si>
   <si>
     <t xml:space="preserve">4.852379322052</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8694052696228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34613132476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24397563934326</t>
+    <t xml:space="preserve">4.86940479278564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34613084793091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2439751625061</t>
   </si>
   <si>
     <t xml:space="preserve">5.36315631866455</t>
@@ -1544,13 +1544,13 @@
     <t xml:space="preserve">5.38018274307251</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20992279052734</t>
+    <t xml:space="preserve">5.2099232673645</t>
   </si>
   <si>
     <t xml:space="preserve">5.15884590148926</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10776805877686</t>
+    <t xml:space="preserve">5.10776853561401</t>
   </si>
   <si>
     <t xml:space="preserve">4.98858690261841</t>
@@ -1559,10 +1559,10 @@
     <t xml:space="preserve">5.09074211120605</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19289779663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17587184906006</t>
+    <t xml:space="preserve">5.1928973197937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1758713722229</t>
   </si>
   <si>
     <t xml:space="preserve">5.1418194770813</t>
@@ -1571,7 +1571,7 @@
     <t xml:space="preserve">5.07371616363525</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68212080001831</t>
+    <t xml:space="preserve">4.68212032318115</t>
   </si>
   <si>
     <t xml:space="preserve">4.54591369628906</t>
@@ -1580,22 +1580,22 @@
     <t xml:space="preserve">4.59699106216431</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57996511459351</t>
+    <t xml:space="preserve">4.57996559143066</t>
   </si>
   <si>
     <t xml:space="preserve">4.63104295730591</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78427600860596</t>
+    <t xml:space="preserve">4.7842755317688</t>
   </si>
   <si>
     <t xml:space="preserve">4.76725006103516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8183274269104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80130100250244</t>
+    <t xml:space="preserve">4.81832790374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80130195617676</t>
   </si>
   <si>
     <t xml:space="preserve">5.39720869064331</t>
@@ -1604,16 +1604,16 @@
     <t xml:space="preserve">5.6185450553894</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46531248092651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49936389923096</t>
+    <t xml:space="preserve">5.4653115272522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4993634223938</t>
   </si>
   <si>
     <t xml:space="preserve">5.63557052612305</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68664884567261</t>
+    <t xml:space="preserve">5.68664836883545</t>
   </si>
   <si>
     <t xml:space="preserve">5.65259647369385</t>
@@ -1634,73 +1634,73 @@
     <t xml:space="preserve">6.29958057403564</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35065841674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43578767776489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5549693107605</t>
+    <t xml:space="preserve">6.35065889358521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43578720092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55496883392334</t>
   </si>
   <si>
     <t xml:space="preserve">6.69117641448975</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79333114624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15087461471558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08277130126953</t>
+    <t xml:space="preserve">6.79333162307739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15087509155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08277082443237</t>
   </si>
   <si>
     <t xml:space="preserve">6.87846088409424</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77630615234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84440898895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70820283889771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75927972793579</t>
+    <t xml:space="preserve">6.77630519866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84440946578979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70820236206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75928020477295</t>
   </si>
   <si>
     <t xml:space="preserve">6.53794288635254</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72522735595703</t>
+    <t xml:space="preserve">6.72522783279419</t>
   </si>
   <si>
     <t xml:space="preserve">6.65712451934814</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91251277923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8954873085022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96359062194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17302227020264</t>
+    <t xml:space="preserve">6.91251230239868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89548683166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96359014511108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17302179336548</t>
   </si>
   <si>
     <t xml:space="preserve">7.05085325241089</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1206636428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57443189620972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9758415222168</t>
+    <t xml:space="preserve">7.12066411972046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57443237304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97584199905396</t>
   </si>
   <si>
     <t xml:space="preserve">8.02819919586182</t>
@@ -1709,7 +1709,7 @@
     <t xml:space="preserve">8.0631046295166</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99329423904419</t>
+    <t xml:space="preserve">7.99329328536987</t>
   </si>
   <si>
     <t xml:space="preserve">8.01074695587158</t>
@@ -1733,13 +1733,13 @@
     <t xml:space="preserve">8.34234619140625</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11546230316162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25508308410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08055877685547</t>
+    <t xml:space="preserve">8.11546325683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25508403778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08055782318115</t>
   </si>
   <si>
     <t xml:space="preserve">8.20272541046143</t>
@@ -1757,13 +1757,13 @@
     <t xml:space="preserve">8.81356716156006</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58668327331543</t>
+    <t xml:space="preserve">8.58668231964111</t>
   </si>
   <si>
     <t xml:space="preserve">8.53432559967041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69139862060547</t>
+    <t xml:space="preserve">8.69139766693115</t>
   </si>
   <si>
     <t xml:space="preserve">8.60413551330566</t>
@@ -1775,25 +1775,25 @@
     <t xml:space="preserve">8.42961025238037</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28998851776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3074426651001</t>
+    <t xml:space="preserve">8.28998947143555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30744171142578</t>
   </si>
   <si>
     <t xml:space="preserve">8.04565334320068</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85367393493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41215705871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22017860412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44706249237061</t>
+    <t xml:space="preserve">7.85367345809937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41215801239014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22017765045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44706153869629</t>
   </si>
   <si>
     <t xml:space="preserve">8.3597993850708</t>
@@ -1805,7 +1805,7 @@
     <t xml:space="preserve">8.23762989044189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48196697235107</t>
+    <t xml:space="preserve">8.48196792602539</t>
   </si>
   <si>
     <t xml:space="preserve">8.6215877532959</t>
@@ -1814,13 +1814,13 @@
     <t xml:space="preserve">8.55177783966064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65649318695068</t>
+    <t xml:space="preserve">8.656494140625</t>
   </si>
   <si>
     <t xml:space="preserve">8.51687240600586</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46451473236084</t>
+    <t xml:space="preserve">8.46451377868652</t>
   </si>
   <si>
     <t xml:space="preserve">8.49942016601562</t>
@@ -1835,7 +1835,7 @@
     <t xml:space="preserve">9.59893417358398</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77346038818359</t>
+    <t xml:space="preserve">9.77345943450928</t>
   </si>
   <si>
     <t xml:space="preserve">9.8170919418335</t>
@@ -1856,13 +1856,13 @@
     <t xml:space="preserve">9.9043550491333</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33714485168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94798564910889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8607234954834</t>
+    <t xml:space="preserve">9.33714580535889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9479866027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86072254180908</t>
   </si>
   <si>
     <t xml:space="preserve">10.5151968002319</t>
@@ -1871,10 +1871,10 @@
     <t xml:space="preserve">10.4279317855835</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5588283538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6024580001831</t>
+    <t xml:space="preserve">10.5588274002075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6024589538574</t>
   </si>
   <si>
     <t xml:space="preserve">10.8206167221069</t>
@@ -1892,16 +1892,16 @@
     <t xml:space="preserve">10.3843011856079</t>
   </si>
   <si>
-    <t xml:space="preserve">10.340669631958</t>
+    <t xml:space="preserve">10.3406705856323</t>
   </si>
   <si>
     <t xml:space="preserve">10.2097749710083</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2534074783325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0788803100586</t>
+    <t xml:space="preserve">10.2534065246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0788812637329</t>
   </si>
   <si>
     <t xml:space="preserve">9.51167106628418</t>
@@ -1955,7 +1955,7 @@
     <t xml:space="preserve">11.8677730560303</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6059846878052</t>
+    <t xml:space="preserve">11.6059837341309</t>
   </si>
   <si>
     <t xml:space="preserve">10.9515113830566</t>
@@ -1964,7 +1964,7 @@
     <t xml:space="preserve">12.0422992706299</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3005628585815</t>
+    <t xml:space="preserve">11.3005638122559</t>
   </si>
   <si>
     <t xml:space="preserve">11.3441953659058</t>
@@ -1973,22 +1973,22 @@
     <t xml:space="preserve">10.9951429367065</t>
   </si>
   <si>
-    <t xml:space="preserve">10.471565246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9078788757324</t>
+    <t xml:space="preserve">10.4715642929077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9078798294067</t>
   </si>
   <si>
     <t xml:space="preserve">11.4314584732056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0387744903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9899406433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.74560546875</t>
+    <t xml:space="preserve">11.0387735366821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9899415969849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7456045150757</t>
   </si>
   <si>
     <t xml:space="preserve">11.5361738204956</t>
@@ -1997,28 +1997,28 @@
     <t xml:space="preserve">11.5187215805054</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6234369277954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4489107131958</t>
+    <t xml:space="preserve">11.6234359741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4489116668701</t>
   </si>
   <si>
     <t xml:space="preserve">11.6408891677856</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7281513214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9201316833496</t>
+    <t xml:space="preserve">11.7281522750854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9201307296753</t>
   </si>
   <si>
     <t xml:space="preserve">11.1173105239868</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0998601913452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8031635284424</t>
+    <t xml:space="preserve">11.0998592376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8031644821167</t>
   </si>
   <si>
     <t xml:space="preserve">10.7508068084717</t>
@@ -3495,6 +3495,9 @@
   </si>
   <si>
     <t xml:space="preserve">17.7000007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4400005340576</t>
   </si>
 </sst>
 </file>
@@ -69067,7 +69070,7 @@
     </row>
     <row r="2510">
       <c r="A2510" s="1" t="n">
-        <v>45973.6912152778</v>
+        <v>45973.3333333333</v>
       </c>
       <c r="B2510" t="n">
         <v>20844</v>
@@ -69088,6 +69091,32 @@
         <v>1160</v>
       </c>
       <c r="H2510" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2511">
+      <c r="A2511" s="1" t="n">
+        <v>45974.6911805556</v>
+      </c>
+      <c r="B2511" t="n">
+        <v>48787</v>
+      </c>
+      <c r="C2511" t="n">
+        <v>17.7999992370605</v>
+      </c>
+      <c r="D2511" t="n">
+        <v>17.3199996948242</v>
+      </c>
+      <c r="E2511" t="n">
+        <v>17.7199993133545</v>
+      </c>
+      <c r="F2511" t="n">
+        <v>17.4400005340576</v>
+      </c>
+      <c r="G2511" t="s">
+        <v>1161</v>
+      </c>
+      <c r="H2511" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ORS.MI.xlsx
+++ b/data/ORS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1163" uniqueCount="1163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1164" uniqueCount="1164">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,13 +44,13 @@
     <t xml:space="preserve">ORS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98275804519653</t>
+    <t xml:space="preserve">7.98275899887085</t>
   </si>
   <si>
     <t xml:space="preserve">8.06380176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94223833084106</t>
+    <t xml:space="preserve">7.94223642349243</t>
   </si>
   <si>
     <t xml:space="preserve">7.82472467422485</t>
@@ -62,31 +62,31 @@
     <t xml:space="preserve">7.90171527862549</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03948783874512</t>
+    <t xml:space="preserve">8.03948879241943</t>
   </si>
   <si>
     <t xml:space="preserve">7.92602920532227</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86119508743286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82067251205444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93413305282593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02328014373779</t>
+    <t xml:space="preserve">7.86119318008423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82067346572876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93413352966309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02328109741211</t>
   </si>
   <si>
     <t xml:space="preserve">8.08811473846436</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14484596252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69910669326782</t>
+    <t xml:space="preserve">8.1448450088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69910717010498</t>
   </si>
   <si>
     <t xml:space="preserve">7.8044638633728</t>
@@ -95,19 +95,19 @@
     <t xml:space="preserve">7.97465467453003</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01112365722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01517677307129</t>
+    <t xml:space="preserve">8.01112461090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01517581939697</t>
   </si>
   <si>
     <t xml:space="preserve">7.79230785369873</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82877779006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34745311737061</t>
+    <t xml:space="preserve">7.82877731323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34745407104492</t>
   </si>
   <si>
     <t xml:space="preserve">7.84093332290649</t>
@@ -116,34 +116,34 @@
     <t xml:space="preserve">7.90982055664062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85714197158813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78015041351318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8449854850769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97870683670044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88550853729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95034170150757</t>
+    <t xml:space="preserve">7.85714292526245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7801513671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84498500823975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97870779037476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88550567626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95034265518188</t>
   </si>
   <si>
     <t xml:space="preserve">8.00301933288574</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01922798156738</t>
+    <t xml:space="preserve">8.0192289352417</t>
   </si>
   <si>
     <t xml:space="preserve">7.91792488098145</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1002721786499</t>
+    <t xml:space="preserve">8.10027313232422</t>
   </si>
   <si>
     <t xml:space="preserve">8.10432434082031</t>
@@ -152,16 +152,16 @@
     <t xml:space="preserve">8.18536758422852</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20157527923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11242866516113</t>
+    <t xml:space="preserve">8.20157623291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11242961883545</t>
   </si>
   <si>
     <t xml:space="preserve">8.07595920562744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03138446807861</t>
+    <t xml:space="preserve">8.03138542175293</t>
   </si>
   <si>
     <t xml:space="preserve">8.09621906280518</t>
@@ -170,28 +170,28 @@
     <t xml:space="preserve">8.17726230621338</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05569744110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12053203582764</t>
+    <t xml:space="preserve">8.05569839477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12053394317627</t>
   </si>
   <si>
     <t xml:space="preserve">8.2583065032959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4203929901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67162704467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55816555023193</t>
+    <t xml:space="preserve">8.42039203643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67162609100342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55816745758057</t>
   </si>
   <si>
     <t xml:space="preserve">8.42849731445312</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52429103851318</t>
+    <t xml:space="preserve">8.52429008483887</t>
   </si>
   <si>
     <t xml:space="preserve">8.45921993255615</t>
@@ -218,67 +218,67 @@
     <t xml:space="preserve">8.7927074432373</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90657997131348</t>
+    <t xml:space="preserve">8.90658187866211</t>
   </si>
   <si>
     <t xml:space="preserve">8.86591243743896</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94724941253662</t>
+    <t xml:space="preserve">8.94725036621094</t>
   </si>
   <si>
     <t xml:space="preserve">8.93911647796631</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78457355499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74390411376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91471481323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92284965515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10993003845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07739162445068</t>
+    <t xml:space="preserve">8.78457260131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74390506744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91471385955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92285060882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10992813110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.077392578125</t>
   </si>
   <si>
     <t xml:space="preserve">9.11806297302246</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1343297958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15059757232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15873241424561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7357702255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67883205413818</t>
+    <t xml:space="preserve">9.13432884216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15059852600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15873146057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73576927185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6788330078125</t>
   </si>
   <si>
     <t xml:space="preserve">8.85777759552002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72763633728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70323371887207</t>
+    <t xml:space="preserve">8.72763729095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7032356262207</t>
   </si>
   <si>
     <t xml:space="preserve">8.66256618499756</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69510078430176</t>
+    <t xml:space="preserve">8.69510173797607</t>
   </si>
   <si>
     <t xml:space="preserve">8.6218957901001</t>
@@ -287,19 +287,19 @@
     <t xml:space="preserve">8.80084133148193</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77643871307373</t>
+    <t xml:space="preserve">8.77643966674805</t>
   </si>
   <si>
     <t xml:space="preserve">8.68696784973145</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54868984222412</t>
+    <t xml:space="preserve">8.54869174957275</t>
   </si>
   <si>
     <t xml:space="preserve">8.54055690765381</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58122730255127</t>
+    <t xml:space="preserve">8.58122825622559</t>
   </si>
   <si>
     <t xml:space="preserve">8.46735191345215</t>
@@ -317,13 +317,13 @@
     <t xml:space="preserve">8.63003063201904</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80897617340088</t>
+    <t xml:space="preserve">8.80897521972656</t>
   </si>
   <si>
     <t xml:space="preserve">8.89031314849854</t>
   </si>
   <si>
-    <t xml:space="preserve">8.930983543396</t>
+    <t xml:space="preserve">8.93098258972168</t>
   </si>
   <si>
     <t xml:space="preserve">8.9635181427002</t>
@@ -332,43 +332,43 @@
     <t xml:space="preserve">9.05299091339111</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30514240264893</t>
+    <t xml:space="preserve">9.30514144897461</t>
   </si>
   <si>
     <t xml:space="preserve">9.10179424285889</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1912670135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35394382476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47595119476318</t>
+    <t xml:space="preserve">9.19126796722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35394191741943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4759521484375</t>
   </si>
   <si>
     <t xml:space="preserve">9.54915618896484</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58982563018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66303062438965</t>
+    <t xml:space="preserve">9.5898265838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66303157806396</t>
   </si>
   <si>
     <t xml:space="preserve">9.71996688842773</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85824489593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0046529769897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2405338287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2486696243286</t>
+    <t xml:space="preserve">9.85824203491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0046520233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2405347824097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.24866771698</t>
   </si>
   <si>
     <t xml:space="preserve">10.3381414413452</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">10.598424911499</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4276151657104</t>
+    <t xml:space="preserve">10.4276132583618</t>
   </si>
   <si>
     <t xml:space="preserve">10.4032115936279</t>
@@ -392,13 +392,13 @@
     <t xml:space="preserve">10.5658893585205</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5821571350098</t>
+    <t xml:space="preserve">10.5821580886841</t>
   </si>
   <si>
     <t xml:space="preserve">10.7773704528809</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9807167053223</t>
+    <t xml:space="preserve">10.9807176589966</t>
   </si>
   <si>
     <t xml:space="preserve">10.8749771118164</t>
@@ -407,7 +407,7 @@
     <t xml:space="preserve">10.6553640365601</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6797637939453</t>
+    <t xml:space="preserve">10.6797647476196</t>
   </si>
   <si>
     <t xml:space="preserve">10.5740242004395</t>
@@ -416,7 +416,7 @@
     <t xml:space="preserve">10.5170869827271</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5414867401123</t>
+    <t xml:space="preserve">10.5414896011353</t>
   </si>
   <si>
     <t xml:space="preserve">10.5577564239502</t>
@@ -443,22 +443,22 @@
     <t xml:space="preserve">10.8831100463867</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6716289520264</t>
+    <t xml:space="preserve">10.671630859375</t>
   </si>
   <si>
     <t xml:space="preserve">10.7367010116577</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0051193237305</t>
+    <t xml:space="preserve">11.0051202774048</t>
   </si>
   <si>
     <t xml:space="preserve">11.0213871002197</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1840648651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4036779403687</t>
+    <t xml:space="preserve">11.184063911438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4036769866943</t>
   </si>
   <si>
     <t xml:space="preserve">11.395544052124</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">11.3386077880859</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3223390579224</t>
+    <t xml:space="preserve">11.3223400115967</t>
   </si>
   <si>
     <t xml:space="preserve">11.3304738998413</t>
@@ -479,19 +479,19 @@
     <t xml:space="preserve">11.0783233642578</t>
   </si>
   <si>
-    <t xml:space="preserve">10.606559753418</t>
+    <t xml:space="preserve">10.6065607070923</t>
   </si>
   <si>
     <t xml:space="preserve">10.8424415588379</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8505744934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6390933990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4113464355469</t>
+    <t xml:space="preserve">10.8505735397339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6390943527222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4113473892212</t>
   </si>
   <si>
     <t xml:space="preserve">10.2080001831055</t>
@@ -503,19 +503,19 @@
     <t xml:space="preserve">10.2324018478394</t>
   </si>
   <si>
-    <t xml:space="preserve">10.321873664856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.370677947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3300085067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3056049346924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2568035125732</t>
+    <t xml:space="preserve">10.3218746185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3706769943237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3300075531006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3056058883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2568044662476</t>
   </si>
   <si>
     <t xml:space="preserve">10.1835975646973</t>
@@ -524,19 +524,19 @@
     <t xml:space="preserve">10.4845523834229</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3625431060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4438810348511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8587093353271</t>
+    <t xml:space="preserve">10.3625421524048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4438819885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8587102890015</t>
   </si>
   <si>
     <t xml:space="preserve">10.9237794876099</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0376539230347</t>
+    <t xml:space="preserve">11.0376529693604</t>
   </si>
   <si>
     <t xml:space="preserve">11.0620555877686</t>
@@ -548,10 +548,10 @@
     <t xml:space="preserve">11.1433944702148</t>
   </si>
   <si>
-    <t xml:space="preserve">11.175929069519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1352615356445</t>
+    <t xml:space="preserve">11.1759300231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1352605819702</t>
   </si>
   <si>
     <t xml:space="preserve">11.0701894760132</t>
@@ -560,10 +560,10 @@
     <t xml:space="preserve">11.118992805481</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1515293121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2247314453125</t>
+    <t xml:space="preserve">11.1515283584595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2247323989868</t>
   </si>
   <si>
     <t xml:space="preserve">11.0457878112793</t>
@@ -578,7 +578,7 @@
     <t xml:space="preserve">8.36161231994629</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01998901367188</t>
+    <t xml:space="preserve">8.01998996734619</t>
   </si>
   <si>
     <t xml:space="preserve">8.10946273803711</t>
@@ -587,16 +587,16 @@
     <t xml:space="preserve">8.3941478729248</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21520328521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33721160888672</t>
+    <t xml:space="preserve">8.21520233154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33720970153809</t>
   </si>
   <si>
     <t xml:space="preserve">8.31280899047852</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18266773223877</t>
+    <t xml:space="preserve">8.18266677856445</t>
   </si>
   <si>
     <t xml:space="preserve">8.34534549713135</t>
@@ -608,22 +608,22 @@
     <t xml:space="preserve">8.49175453186035</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5893611907959</t>
+    <t xml:space="preserve">8.58936023712158</t>
   </si>
   <si>
     <t xml:space="preserve">8.76017189025879</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29654216766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25587177276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17453289031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19080066680908</t>
+    <t xml:space="preserve">8.29654121398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25587272644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17453384399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1908016204834</t>
   </si>
   <si>
     <t xml:space="preserve">8.23147106170654</t>
@@ -632,7 +632,7 @@
     <t xml:space="preserve">8.2802734375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14199829101562</t>
+    <t xml:space="preserve">8.14199733734131</t>
   </si>
   <si>
     <t xml:space="preserve">8.15826606750488</t>
@@ -641,46 +641,46 @@
     <t xml:space="preserve">8.16639995574951</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12166213989258</t>
+    <t xml:space="preserve">8.12166404724121</t>
   </si>
   <si>
     <t xml:space="preserve">8.05252552032471</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89798355102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85731267929077</t>
+    <t xml:space="preserve">7.89798259735107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85731315612793</t>
   </si>
   <si>
     <t xml:space="preserve">7.93051719665527</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90611553192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93865156173706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8491792678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80851030349731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62956571578979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57262754440308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48315572738647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66616630554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60516357421875</t>
+    <t xml:space="preserve">7.90611600875854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93865251541138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84917879104614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80850982666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62956523895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57262659072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48315620422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66616678237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60516309738159</t>
   </si>
   <si>
     <t xml:space="preserve">7.54009246826172</t>
@@ -689,55 +689,55 @@
     <t xml:space="preserve">7.5238242149353</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47908735275269</t>
+    <t xml:space="preserve">7.47908878326416</t>
   </si>
   <si>
     <t xml:space="preserve">7.61329650878906</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54822635650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56449317932129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50755596160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46688795089722</t>
+    <t xml:space="preserve">7.54822444915771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56449413299561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50755643844604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46688652038574</t>
   </si>
   <si>
     <t xml:space="preserve">7.49128913879395</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49942207336426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31234502792358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27980804443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37741422653198</t>
+    <t xml:space="preserve">7.4994215965271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31234550476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27980852127075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3774151802063</t>
   </si>
   <si>
     <t xml:space="preserve">7.38554906845093</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36928081512451</t>
+    <t xml:space="preserve">7.36928033828735</t>
   </si>
   <si>
     <t xml:space="preserve">7.32047748565674</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34487962722778</t>
+    <t xml:space="preserve">7.34487915039062</t>
   </si>
   <si>
     <t xml:space="preserve">7.28794193267822</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04392623901367</t>
+    <t xml:space="preserve">7.04392576217651</t>
   </si>
   <si>
     <t xml:space="preserve">7.15780019760132</t>
@@ -746,82 +746,82 @@
     <t xml:space="preserve">7.39368295669556</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42621755599976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40181636810303</t>
+    <t xml:space="preserve">7.42621803283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40181589126587</t>
   </si>
   <si>
     <t xml:space="preserve">7.30421018600464</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3611478805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20660352706909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35301208496094</t>
+    <t xml:space="preserve">7.36114835739136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20660448074341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35301303863525</t>
   </si>
   <si>
     <t xml:space="preserve">7.33674621582031</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27167463302612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23100471496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32861137390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26354169845581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23913955688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22287082672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24727344512939</t>
+    <t xml:space="preserve">7.27167510986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23100519180298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32861042022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26354122161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23914003372192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22287130355835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24727296829224</t>
   </si>
   <si>
     <t xml:space="preserve">7.44248533248901</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25540733337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18220233917236</t>
+    <t xml:space="preserve">7.25540781021118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18220186233521</t>
   </si>
   <si>
     <t xml:space="preserve">7.29607582092285</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16593456268311</t>
+    <t xml:space="preserve">7.16593408584595</t>
   </si>
   <si>
     <t xml:space="preserve">7.14153242111206</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0520601272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0764627456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0357928276062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01952505111694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87311458587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.677903175354</t>
+    <t xml:space="preserve">7.05205965042114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07646179199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03579378128052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0195255279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87311410903931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67790269851685</t>
   </si>
   <si>
     <t xml:space="preserve">6.85124778747559</t>
@@ -833,58 +833,58 @@
     <t xml:space="preserve">7.26397323608398</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14841032028198</t>
+    <t xml:space="preserve">7.14840936660767</t>
   </si>
   <si>
     <t xml:space="preserve">7.09888315200806</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18142890930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16491794586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14015626907349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21444654464722</t>
+    <t xml:space="preserve">7.1814284324646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16491937637329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14015674591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21444606781006</t>
   </si>
   <si>
     <t xml:space="preserve">7.1731743812561</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97506475448608</t>
+    <t xml:space="preserve">6.97506427764893</t>
   </si>
   <si>
     <t xml:space="preserve">6.84299325942993</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60361194610596</t>
+    <t xml:space="preserve">6.60361242294312</t>
   </si>
   <si>
     <t xml:space="preserve">6.62012100219727</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67790269851685</t>
+    <t xml:space="preserve">6.67790222167969</t>
   </si>
   <si>
     <t xml:space="preserve">6.80997467041016</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54583072662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31470394134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32295846939087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34772300720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38073968887329</t>
+    <t xml:space="preserve">6.54583024978638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31470441818237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32295799255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34772253036499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38074016571045</t>
   </si>
   <si>
     <t xml:space="preserve">6.39724922180176</t>
@@ -893,7 +893,7 @@
     <t xml:space="preserve">6.47153997421265</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28168630599976</t>
+    <t xml:space="preserve">6.28168535232544</t>
   </si>
   <si>
     <t xml:space="preserve">6.22390413284302</t>
@@ -902,7 +902,7 @@
     <t xml:space="preserve">6.09183216094971</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90197801589966</t>
+    <t xml:space="preserve">5.9019775390625</t>
   </si>
   <si>
     <t xml:space="preserve">5.95976066589355</t>
@@ -914,22 +914,22 @@
     <t xml:space="preserve">6.20739507675171</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14135885238647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19088697433472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14961338043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0753231048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25692272186279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00928783416748</t>
+    <t xml:space="preserve">6.14135932922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19088649749756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14961385726929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07532358169556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25692224502563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00928735733032</t>
   </si>
   <si>
     <t xml:space="preserve">5.98452377319336</t>
@@ -938,7 +938,7 @@
     <t xml:space="preserve">6.12485074996948</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13310480117798</t>
+    <t xml:space="preserve">6.13310432434082</t>
   </si>
   <si>
     <t xml:space="preserve">6.27343130111694</t>
@@ -947,34 +947,34 @@
     <t xml:space="preserve">6.44677639007568</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55408477783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51281261444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36423110961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24041366577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21565008163452</t>
+    <t xml:space="preserve">6.55408525466919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51281213760376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3642315864563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24041414260864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21565055847168</t>
   </si>
   <si>
     <t xml:space="preserve">6.23215961456299</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24866771697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11659669876099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10834074020386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05055952072144</t>
+    <t xml:space="preserve">6.24866819381714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11659574508667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1083402633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05055999755859</t>
   </si>
   <si>
     <t xml:space="preserve">5.89372396469116</t>
@@ -983,46 +983,46 @@
     <t xml:space="preserve">5.77816104888916</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69561433792114</t>
+    <t xml:space="preserve">5.69561529159546</t>
   </si>
   <si>
     <t xml:space="preserve">5.79466962814331</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80292367935181</t>
+    <t xml:space="preserve">5.80292415618896</t>
   </si>
   <si>
     <t xml:space="preserve">5.82768774032593</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78641557693481</t>
+    <t xml:space="preserve">5.78641510009766</t>
   </si>
   <si>
     <t xml:space="preserve">5.73688793182373</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85245132446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29819536209106</t>
+    <t xml:space="preserve">5.85245084762573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29819488525391</t>
   </si>
   <si>
     <t xml:space="preserve">6.18263244628906</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15786838531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03405046463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08357763290405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81943416595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91848707199097</t>
+    <t xml:space="preserve">6.15786790847778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03404998779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08357715606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81943368911743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91848659515381</t>
   </si>
   <si>
     <t xml:space="preserve">5.86070585250854</t>
@@ -1031,40 +1031,40 @@
     <t xml:space="preserve">5.76165199279785</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7533974647522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81117820739746</t>
+    <t xml:space="preserve">5.75339698791504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8111777305603</t>
   </si>
   <si>
     <t xml:space="preserve">5.70387029647827</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74514245986938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83594226837158</t>
+    <t xml:space="preserve">5.74514293670654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83594274520874</t>
   </si>
   <si>
     <t xml:space="preserve">5.71212434768677</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84419631958008</t>
+    <t xml:space="preserve">5.84419679641724</t>
   </si>
   <si>
     <t xml:space="preserve">5.94325065612793</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96801471710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8772144317627</t>
+    <t xml:space="preserve">5.96801424026489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87721490859985</t>
   </si>
   <si>
     <t xml:space="preserve">5.88546943664551</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93499612808228</t>
+    <t xml:space="preserve">5.93499565124512</t>
   </si>
   <si>
     <t xml:space="preserve">6.02579593658447</t>
@@ -1073,7 +1073,7 @@
     <t xml:space="preserve">6.06706857681274</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3889946937561</t>
+    <t xml:space="preserve">6.38899421691895</t>
   </si>
   <si>
     <t xml:space="preserve">6.19914102554321</t>
@@ -1082,7 +1082,7 @@
     <t xml:space="preserve">6.04230451583862</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05881404876709</t>
+    <t xml:space="preserve">6.05881452560425</t>
   </si>
   <si>
     <t xml:space="preserve">5.95150566101074</t>
@@ -1091,28 +1091,28 @@
     <t xml:space="preserve">6.17437744140625</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1760196685791</t>
+    <t xml:space="preserve">6.17602014541626</t>
   </si>
   <si>
     <t xml:space="preserve">6.29349803924561</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25993299484253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20958423614502</t>
+    <t xml:space="preserve">6.25993251800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20958375930786</t>
   </si>
   <si>
     <t xml:space="preserve">6.09210538864136</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10888957977295</t>
+    <t xml:space="preserve">6.10888862609863</t>
   </si>
   <si>
     <t xml:space="preserve">6.14245367050171</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0585412979126</t>
+    <t xml:space="preserve">6.05854177474976</t>
   </si>
   <si>
     <t xml:space="preserve">6.02497529983521</t>
@@ -1130,46 +1130,46 @@
     <t xml:space="preserve">6.12567090988159</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19280195236206</t>
+    <t xml:space="preserve">6.1928014755249</t>
   </si>
   <si>
     <t xml:space="preserve">6.42775917053223</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71306467056274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64593458175659</t>
+    <t xml:space="preserve">6.7130651473999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64593410491943</t>
   </si>
   <si>
     <t xml:space="preserve">6.69628190994263</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78019571304321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72984647750854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62915086746216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56202030181885</t>
+    <t xml:space="preserve">6.78019523620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7298469543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.629150390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56201982498169</t>
   </si>
   <si>
     <t xml:space="preserve">6.54523801803589</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67949867248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66271638870239</t>
+    <t xml:space="preserve">6.67949914932251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66271686553955</t>
   </si>
   <si>
     <t xml:space="preserve">6.57880353927612</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37741136550903</t>
+    <t xml:space="preserve">6.37741088867188</t>
   </si>
   <si>
     <t xml:space="preserve">6.34384632110596</t>
@@ -1181,25 +1181,25 @@
     <t xml:space="preserve">6.36062860488892</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67253923416138</t>
+    <t xml:space="preserve">5.67253875732422</t>
   </si>
   <si>
     <t xml:space="preserve">5.55505990982056</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68932247161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62219142913818</t>
+    <t xml:space="preserve">5.68932199478149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62219190597534</t>
   </si>
   <si>
     <t xml:space="preserve">5.53827810287476</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43758201599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45436573028564</t>
+    <t xml:space="preserve">5.43758249282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45436525344849</t>
   </si>
   <si>
     <t xml:space="preserve">5.60540819168091</t>
@@ -1220,10 +1220,10 @@
     <t xml:space="preserve">5.3704514503479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42079925537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28653860092163</t>
+    <t xml:space="preserve">5.42079973220825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28653764724731</t>
   </si>
   <si>
     <t xml:space="preserve">5.30332088470459</t>
@@ -1238,7 +1238,7 @@
     <t xml:space="preserve">5.32010364532471</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65575742721558</t>
+    <t xml:space="preserve">5.65575695037842</t>
   </si>
   <si>
     <t xml:space="preserve">5.75645303726196</t>
@@ -1247,22 +1247,22 @@
     <t xml:space="preserve">5.70610475540161</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72288703918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73967027664185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6389741897583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57184410095215</t>
+    <t xml:space="preserve">5.72288656234741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.739670753479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63897466659546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57184362411499</t>
   </si>
   <si>
     <t xml:space="preserve">5.18584203720093</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20262432098389</t>
+    <t xml:space="preserve">5.2026252746582</t>
   </si>
   <si>
     <t xml:space="preserve">5.21940803527832</t>
@@ -1271,13 +1271,13 @@
     <t xml:space="preserve">5.16905975341797</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13549423217773</t>
+    <t xml:space="preserve">5.13549327850342</t>
   </si>
   <si>
     <t xml:space="preserve">5.10192918777466</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95088481903076</t>
+    <t xml:space="preserve">4.9508843421936</t>
   </si>
   <si>
     <t xml:space="preserve">5.03479862213135</t>
@@ -1286,37 +1286,37 @@
     <t xml:space="preserve">5.15227699279785</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11871147155762</t>
+    <t xml:space="preserve">5.11871099472046</t>
   </si>
   <si>
     <t xml:space="preserve">5.06836318969727</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0851469039917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23619031906128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25297212600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33688688278198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79001712799072</t>
+    <t xml:space="preserve">5.08514595031738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23618984222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25297260284424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33688640594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79001760482788</t>
   </si>
   <si>
     <t xml:space="preserve">5.77323532104492</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58862590789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81662368774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79984140396118</t>
+    <t xml:space="preserve">5.58862638473511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81662321090698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79984092712402</t>
   </si>
   <si>
     <t xml:space="preserve">4.59844827651978</t>
@@ -1328,13 +1328,13 @@
     <t xml:space="preserve">4.31314373016357</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19566535949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11175155639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02783870697021</t>
+    <t xml:space="preserve">4.19566488265991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11175107955933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02783918380737</t>
   </si>
   <si>
     <t xml:space="preserve">4.17049121856689</t>
@@ -1352,16 +1352,16 @@
     <t xml:space="preserve">4.17888212203979</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04462146759033</t>
+    <t xml:space="preserve">4.04462099075317</t>
   </si>
   <si>
     <t xml:space="preserve">4.15370845794678</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26279640197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16209983825684</t>
+    <t xml:space="preserve">4.26279592514038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16209936141968</t>
   </si>
   <si>
     <t xml:space="preserve">4.14531707763672</t>
@@ -1373,13 +1373,13 @@
     <t xml:space="preserve">4.09496927261353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98588132858276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27957820892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22922992706299</t>
+    <t xml:space="preserve">3.98588180541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2795786857605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22923040390015</t>
   </si>
   <si>
     <t xml:space="preserve">4.21244812011719</t>
@@ -1388,10 +1388,10 @@
     <t xml:space="preserve">4.03622961044312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12877941131592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16283130645752</t>
+    <t xml:space="preserve">4.12877893447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16283082962036</t>
   </si>
   <si>
     <t xml:space="preserve">4.07770156860352</t>
@@ -1403,13 +1403,13 @@
     <t xml:space="preserve">4.20539569854736</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37565469741821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21390819549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22242212295532</t>
+    <t xml:space="preserve">4.37565422058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21390914916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22242116928101</t>
   </si>
   <si>
     <t xml:space="preserve">4.25647354125977</t>
@@ -1418,10 +1418,10 @@
     <t xml:space="preserve">4.24796009063721</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32457637786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30755090713501</t>
+    <t xml:space="preserve">4.32457685470581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30755138397217</t>
   </si>
   <si>
     <t xml:space="preserve">4.23944759368896</t>
@@ -1436,7 +1436,7 @@
     <t xml:space="preserve">5.5334153175354</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94203615188599</t>
+    <t xml:space="preserve">5.94203662872314</t>
   </si>
   <si>
     <t xml:space="preserve">5.8909592628479</t>
@@ -1457,16 +1457,16 @@
     <t xml:space="preserve">5.41423416137695</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2610011100769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48233842849731</t>
+    <t xml:space="preserve">5.26100063323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48233795166016</t>
   </si>
   <si>
     <t xml:space="preserve">5.44828653335571</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6015191078186</t>
+    <t xml:space="preserve">5.60151863098145</t>
   </si>
   <si>
     <t xml:space="preserve">5.66962289810181</t>
@@ -1475,10 +1475,10 @@
     <t xml:space="preserve">5.5163893699646</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70367479324341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32910442352295</t>
+    <t xml:space="preserve">5.70367383956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32910490036011</t>
   </si>
   <si>
     <t xml:space="preserve">5.27802705764771</t>
@@ -1496,19 +1496,19 @@
     <t xml:space="preserve">5.00561285018921</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95453500747681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93750858306885</t>
+    <t xml:space="preserve">4.95453548431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93750953674316</t>
   </si>
   <si>
     <t xml:space="preserve">5.05669069290161</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03966474533081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97156047821045</t>
+    <t xml:space="preserve">5.03966426849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97156095504761</t>
   </si>
   <si>
     <t xml:space="preserve">4.88643074035645</t>
@@ -1517,7 +1517,7 @@
     <t xml:space="preserve">5.02263832092285</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92048311233521</t>
+    <t xml:space="preserve">4.92048358917236</t>
   </si>
   <si>
     <t xml:space="preserve">4.9034571647644</t>
@@ -1526,7 +1526,7 @@
     <t xml:space="preserve">4.852379322052</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86940574645996</t>
+    <t xml:space="preserve">4.8694052696228</t>
   </si>
   <si>
     <t xml:space="preserve">5.34613037109375</t>
@@ -1541,13 +1541,13 @@
     <t xml:space="preserve">5.38018226623535</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2099232673645</t>
+    <t xml:space="preserve">5.20992279052734</t>
   </si>
   <si>
     <t xml:space="preserve">5.1588454246521</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1077675819397</t>
+    <t xml:space="preserve">5.10776853561401</t>
   </si>
   <si>
     <t xml:space="preserve">4.98858690261841</t>
@@ -1562,22 +1562,22 @@
     <t xml:space="preserve">5.1758713722229</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1418194770813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07371664047241</t>
+    <t xml:space="preserve">5.14182043075562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0737156867981</t>
   </si>
   <si>
     <t xml:space="preserve">4.68212080001831</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54591369628906</t>
+    <t xml:space="preserve">4.5459132194519</t>
   </si>
   <si>
     <t xml:space="preserve">4.59699153900146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57996559143066</t>
+    <t xml:space="preserve">4.57996511459351</t>
   </si>
   <si>
     <t xml:space="preserve">4.63104343414307</t>
@@ -1586,19 +1586,19 @@
     <t xml:space="preserve">4.78427600860596</t>
   </si>
   <si>
-    <t xml:space="preserve">4.767249584198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8183274269104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8013014793396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39720869064331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6185450553894</t>
+    <t xml:space="preserve">4.76725053787231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81832790374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80130195617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39720773696899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61854553222656</t>
   </si>
   <si>
     <t xml:space="preserve">5.46531200408936</t>
@@ -1607,58 +1607,58 @@
     <t xml:space="preserve">5.4993634223938</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63557100296021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68664884567261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65259695053101</t>
+    <t xml:space="preserve">5.63557052612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68664789199829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65259647369385</t>
   </si>
   <si>
     <t xml:space="preserve">5.8569073677063</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8739333152771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31660652160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33363199234009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2995810508728</t>
+    <t xml:space="preserve">5.87393283843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3166069984436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33363246917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29958009719849</t>
   </si>
   <si>
     <t xml:space="preserve">6.35065793991089</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43578767776489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55496835708618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69117641448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79333114624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15087509155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08277082443237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87846088409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77630567550659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84440898895264</t>
+    <t xml:space="preserve">6.43578720092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55496883392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69117593765259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79333162307739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15087413787842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08277177810669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8784613609314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77630519866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84440946578979</t>
   </si>
   <si>
     <t xml:space="preserve">6.70820283889771</t>
@@ -1673,7 +1673,7 @@
     <t xml:space="preserve">6.72522783279419</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6571249961853</t>
+    <t xml:space="preserve">6.65712451934814</t>
   </si>
   <si>
     <t xml:space="preserve">6.91251230239868</t>
@@ -1682,10 +1682,10 @@
     <t xml:space="preserve">6.8954873085022</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96359014511108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17302179336548</t>
+    <t xml:space="preserve">6.96359062194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17302131652832</t>
   </si>
   <si>
     <t xml:space="preserve">7.05085372924805</t>
@@ -1694,16 +1694,16 @@
     <t xml:space="preserve">7.1206636428833</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57443237304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97584247589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0281982421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06310367584229</t>
+    <t xml:space="preserve">7.57443141937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9758415222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02819919586182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0631046295166</t>
   </si>
   <si>
     <t xml:space="preserve">7.99329423904419</t>
@@ -1721,34 +1721,34 @@
     <t xml:space="preserve">8.15036869049072</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16782093048096</t>
+    <t xml:space="preserve">8.16781997680664</t>
   </si>
   <si>
     <t xml:space="preserve">8.18527412414551</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34234714508057</t>
+    <t xml:space="preserve">8.34234809875488</t>
   </si>
   <si>
     <t xml:space="preserve">8.11546230316162</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25508308410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08055782318115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20272541046143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95838928222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37725257873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3248929977417</t>
+    <t xml:space="preserve">8.25508403778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08055686950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20272445678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95838832855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37725162506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32489395141602</t>
   </si>
   <si>
     <t xml:space="preserve">8.81356716156006</t>
@@ -1760,22 +1760,22 @@
     <t xml:space="preserve">8.53432559967041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69139862060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60413646697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72630310058594</t>
+    <t xml:space="preserve">8.69139957427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60413551330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72630405426025</t>
   </si>
   <si>
     <t xml:space="preserve">8.42960929870605</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28998756408691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30744171142578</t>
+    <t xml:space="preserve">8.28998851776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30744075775146</t>
   </si>
   <si>
     <t xml:space="preserve">8.04565238952637</t>
@@ -1787,7 +1787,7 @@
     <t xml:space="preserve">8.41215801239014</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22017765045166</t>
+    <t xml:space="preserve">8.22017860412598</t>
   </si>
   <si>
     <t xml:space="preserve">8.44706249237061</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">8.3597993850708</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09800910949707</t>
+    <t xml:space="preserve">8.09801006317139</t>
   </si>
   <si>
     <t xml:space="preserve">8.23763084411621</t>
@@ -1811,13 +1811,13 @@
     <t xml:space="preserve">8.55177688598633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65649318695068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51687240600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46451473236084</t>
+    <t xml:space="preserve">8.65649223327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51687335968018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46451377868652</t>
   </si>
   <si>
     <t xml:space="preserve">8.49942016601562</t>
@@ -1826,13 +1826,13 @@
     <t xml:space="preserve">8.56923007965088</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99161720275879</t>
+    <t xml:space="preserve">9.99161815643311</t>
   </si>
   <si>
     <t xml:space="preserve">9.59893417358398</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77345943450928</t>
+    <t xml:space="preserve">9.77346038818359</t>
   </si>
   <si>
     <t xml:space="preserve">9.8170919418335</t>
@@ -1853,7 +1853,7 @@
     <t xml:space="preserve">9.9043550491333</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33714485168457</t>
+    <t xml:space="preserve">9.33714389801025</t>
   </si>
   <si>
     <t xml:space="preserve">9.94798564910889</t>
@@ -1868,7 +1868,7 @@
     <t xml:space="preserve">10.4279327392578</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5588283538818</t>
+    <t xml:space="preserve">10.5588274002075</t>
   </si>
   <si>
     <t xml:space="preserve">10.6024589538574</t>
@@ -1877,25 +1877,25 @@
     <t xml:space="preserve">10.8206167221069</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7333526611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7769861221313</t>
+    <t xml:space="preserve">10.7333536148071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.776985168457</t>
   </si>
   <si>
     <t xml:space="preserve">10.2970380783081</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3843011856079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3406715393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2097749710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2534065246582</t>
+    <t xml:space="preserve">10.3843002319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3406705856323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.209774017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2534074783325</t>
   </si>
   <si>
     <t xml:space="preserve">10.0788812637329</t>
@@ -1904,13 +1904,13 @@
     <t xml:space="preserve">9.51167011260986</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72982883453369</t>
+    <t xml:space="preserve">9.72982788085938</t>
   </si>
   <si>
     <t xml:space="preserve">9.68619728088379</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98809242248535</t>
+    <t xml:space="preserve">8.98809337615967</t>
   </si>
   <si>
     <t xml:space="preserve">9.42440795898438</t>
@@ -1919,7 +1919,7 @@
     <t xml:space="preserve">11.6496162414551</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5623531341553</t>
+    <t xml:space="preserve">11.562352180481</t>
   </si>
   <si>
     <t xml:space="preserve">11.7805099487305</t>
@@ -1946,7 +1946,7 @@
     <t xml:space="preserve">12.3913516998291</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7368783950806</t>
+    <t xml:space="preserve">11.7368774414062</t>
   </si>
   <si>
     <t xml:space="preserve">11.8677730560303</t>
@@ -1955,7 +1955,7 @@
     <t xml:space="preserve">11.6059837341309</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9515113830566</t>
+    <t xml:space="preserve">10.951512336731</t>
   </si>
   <si>
     <t xml:space="preserve">12.0422992706299</t>
@@ -1970,7 +1970,7 @@
     <t xml:space="preserve">10.9951429367065</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4715633392334</t>
+    <t xml:space="preserve">10.471565246582</t>
   </si>
   <si>
     <t xml:space="preserve">10.9078788757324</t>
@@ -1979,7 +1979,7 @@
     <t xml:space="preserve">11.4314584732056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0387744903564</t>
+    <t xml:space="preserve">11.0387735366821</t>
   </si>
   <si>
     <t xml:space="preserve">11.9899406433105</t>
@@ -1988,28 +1988,28 @@
     <t xml:space="preserve">11.74560546875</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5361728668213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5187206268311</t>
+    <t xml:space="preserve">11.5361738204956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5187215805054</t>
   </si>
   <si>
     <t xml:space="preserve">11.6234369277954</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4489107131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6408891677856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7281513214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9201307296753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1173105239868</t>
+    <t xml:space="preserve">11.4489097595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6408882141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7281522750854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9201316833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1173114776611</t>
   </si>
   <si>
     <t xml:space="preserve">11.0998582839966</t>
@@ -2018,13 +2018,13 @@
     <t xml:space="preserve">10.8031644821167</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7508068084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3319444656372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1050605773926</t>
+    <t xml:space="preserve">10.7508058547974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3319435119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1050596237183</t>
   </si>
   <si>
     <t xml:space="preserve">9.81839179992676</t>
@@ -3501,6 +3501,9 @@
   </si>
   <si>
     <t xml:space="preserve">17.1399993896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1200008392334</t>
   </si>
 </sst>
 </file>
@@ -69177,7 +69180,7 @@
     </row>
     <row r="2514">
       <c r="A2514" s="1" t="n">
-        <v>45979.69125</v>
+        <v>45979.3333333333</v>
       </c>
       <c r="B2514" t="n">
         <v>42392</v>
@@ -69198,6 +69201,32 @@
         <v>1118</v>
       </c>
       <c r="H2514" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2515">
+      <c r="A2515" s="1" t="n">
+        <v>45980.6912962963</v>
+      </c>
+      <c r="B2515" t="n">
+        <v>30216</v>
+      </c>
+      <c r="C2515" t="n">
+        <v>17.2999992370605</v>
+      </c>
+      <c r="D2515" t="n">
+        <v>16.9599990844727</v>
+      </c>
+      <c r="E2515" t="n">
+        <v>17.1000003814697</v>
+      </c>
+      <c r="F2515" t="n">
+        <v>17.1200008392334</v>
+      </c>
+      <c r="G2515" t="s">
+        <v>1163</v>
+      </c>
+      <c r="H2515" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ORS.MI.xlsx
+++ b/data/ORS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1166" uniqueCount="1166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1167" uniqueCount="1167">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,76 +38,76 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08406448364258</t>
+    <t xml:space="preserve">8.08406352996826</t>
   </si>
   <si>
     <t xml:space="preserve">ORS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98275947570801</t>
+    <t xml:space="preserve">7.98275852203369</t>
   </si>
   <si>
     <t xml:space="preserve">8.06380176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94223690032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82472562789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93818521499634</t>
+    <t xml:space="preserve">7.94223833084106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82472515106201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93818616867065</t>
   </si>
   <si>
     <t xml:space="preserve">7.9017162322998</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03948879241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92603015899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86119365692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8206729888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93413162231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02328109741211</t>
+    <t xml:space="preserve">8.03948974609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92602872848511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86119508743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82067203521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93413305282593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02328205108643</t>
   </si>
   <si>
     <t xml:space="preserve">8.08811473846436</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14484596252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69910764694214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80446434020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97465419769287</t>
+    <t xml:space="preserve">8.14484691619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69910669326782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80446338653564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97465324401855</t>
   </si>
   <si>
     <t xml:space="preserve">8.01112461090088</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01517486572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79230785369873</t>
+    <t xml:space="preserve">8.01517581939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79230737686157</t>
   </si>
   <si>
     <t xml:space="preserve">7.82877731323242</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34745311737061</t>
+    <t xml:space="preserve">8.34745407104492</t>
   </si>
   <si>
     <t xml:space="preserve">7.84093332290649</t>
@@ -116,49 +116,49 @@
     <t xml:space="preserve">7.90982055664062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85714101791382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78015041351318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84498500823975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97870683670044</t>
+    <t xml:space="preserve">7.85714197158813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78015184402466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8449854850769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97870635986328</t>
   </si>
   <si>
     <t xml:space="preserve">7.88550758361816</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95034122467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00302028656006</t>
+    <t xml:space="preserve">7.95034265518188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00301933288574</t>
   </si>
   <si>
     <t xml:space="preserve">8.0192289352417</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91792488098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10027313232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.104323387146</t>
+    <t xml:space="preserve">7.91792440414429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1002721786499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10432434082031</t>
   </si>
   <si>
     <t xml:space="preserve">8.18536758422852</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20157527923584</t>
+    <t xml:space="preserve">8.20157432556152</t>
   </si>
   <si>
     <t xml:space="preserve">8.11242866516113</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07595920562744</t>
+    <t xml:space="preserve">8.07595825195312</t>
   </si>
   <si>
     <t xml:space="preserve">8.03138542175293</t>
@@ -167,37 +167,37 @@
     <t xml:space="preserve">8.09621906280518</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1772632598877</t>
+    <t xml:space="preserve">8.17726230621338</t>
   </si>
   <si>
     <t xml:space="preserve">8.05569839477539</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12053394317627</t>
+    <t xml:space="preserve">8.12053203582764</t>
   </si>
   <si>
     <t xml:space="preserve">8.2583065032959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4203929901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67162704467773</t>
+    <t xml:space="preserve">8.42039394378662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67162609100342</t>
   </si>
   <si>
     <t xml:space="preserve">8.55816555023193</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42849636077881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52428913116455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45921993255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50802040100098</t>
+    <t xml:space="preserve">8.42849731445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52429103851318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45921897888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50802135467529</t>
   </si>
   <si>
     <t xml:space="preserve">8.60562896728516</t>
@@ -206,31 +206,31 @@
     <t xml:space="preserve">8.53242492675781</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61376190185547</t>
+    <t xml:space="preserve">8.61376285552979</t>
   </si>
   <si>
     <t xml:space="preserve">8.67069911956787</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87404632568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79270648956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90658092498779</t>
+    <t xml:space="preserve">8.87404537200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7927074432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90658187866211</t>
   </si>
   <si>
     <t xml:space="preserve">8.86591243743896</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94724941253662</t>
+    <t xml:space="preserve">8.94725036621094</t>
   </si>
   <si>
     <t xml:space="preserve">8.93911743164062</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78457260131836</t>
+    <t xml:space="preserve">8.78457355499268</t>
   </si>
   <si>
     <t xml:space="preserve">8.74390316009521</t>
@@ -239,7 +239,7 @@
     <t xml:space="preserve">8.91471481323242</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92285060882568</t>
+    <t xml:space="preserve">8.92284965515137</t>
   </si>
   <si>
     <t xml:space="preserve">9.1099271774292</t>
@@ -248,34 +248,34 @@
     <t xml:space="preserve">9.077392578125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11806297302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1343297958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15059661865234</t>
+    <t xml:space="preserve">9.11806201934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13432884216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15059757232666</t>
   </si>
   <si>
     <t xml:space="preserve">9.15873146057129</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7357702255249</t>
+    <t xml:space="preserve">8.73576927185059</t>
   </si>
   <si>
     <t xml:space="preserve">8.67883205413818</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85777759552002</t>
+    <t xml:space="preserve">8.85777854919434</t>
   </si>
   <si>
     <t xml:space="preserve">8.72763633728027</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7032356262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66256618499756</t>
+    <t xml:space="preserve">8.70323467254639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66256523132324</t>
   </si>
   <si>
     <t xml:space="preserve">8.69510173797607</t>
@@ -284,13 +284,13 @@
     <t xml:space="preserve">8.62189674377441</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80084133148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77643966674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68696880340576</t>
+    <t xml:space="preserve">8.80084037780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77643871307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68696689605713</t>
   </si>
   <si>
     <t xml:space="preserve">8.54869079589844</t>
@@ -302,79 +302,79 @@
     <t xml:space="preserve">8.58122825622559</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46735191345215</t>
+    <t xml:space="preserve">8.46735286712646</t>
   </si>
   <si>
     <t xml:space="preserve">8.51615619659424</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49988746643066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45108604431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63002967834473</t>
+    <t xml:space="preserve">8.49988651275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45108509063721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63003063201904</t>
   </si>
   <si>
     <t xml:space="preserve">8.80897617340088</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89031410217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.930983543396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9635181427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0529899597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30514049530029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1017951965332</t>
+    <t xml:space="preserve">8.89031505584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93098258972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96351909637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05299091339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30514144897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10179424285889</t>
   </si>
   <si>
     <t xml:space="preserve">9.19126605987549</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35394382476807</t>
+    <t xml:space="preserve">9.35394287109375</t>
   </si>
   <si>
     <t xml:space="preserve">9.4759521484375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54915714263916</t>
+    <t xml:space="preserve">9.54915618896484</t>
   </si>
   <si>
     <t xml:space="preserve">9.58982467651367</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66303062438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71996688842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85824203491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0046529769897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.240535736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.24866771698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3381423950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.598424911499</t>
+    <t xml:space="preserve">9.66303157806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71996784210205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85824394226074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0046539306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2405347824097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2486696243286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3381414413452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5984258651733</t>
   </si>
   <si>
     <t xml:space="preserve">10.4276142120361</t>
@@ -398,7 +398,7 @@
     <t xml:space="preserve">10.7773714065552</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9807167053223</t>
+    <t xml:space="preserve">10.9807176589966</t>
   </si>
   <si>
     <t xml:space="preserve">10.8749761581421</t>
@@ -407,22 +407,22 @@
     <t xml:space="preserve">10.6553640365601</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6797647476196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5740242004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5170869827271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5414896011353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5577554702759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5089540481567</t>
+    <t xml:space="preserve">10.6797637939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5740232467651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5170860290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5414886474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5577564239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5089530944824</t>
   </si>
   <si>
     <t xml:space="preserve">10.818039894104</t>
@@ -431,31 +431,31 @@
     <t xml:space="preserve">10.6878976821899</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7611017227173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6472291946411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.899377822876</t>
+    <t xml:space="preserve">10.7611026763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6472282409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8993787765503</t>
   </si>
   <si>
     <t xml:space="preserve">10.883111000061</t>
   </si>
   <si>
-    <t xml:space="preserve">10.671630859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7367000579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0051193237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0213871002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1840648651123</t>
+    <t xml:space="preserve">10.6716289520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7367010116577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0051183700562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0213861465454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.184063911438</t>
   </si>
   <si>
     <t xml:space="preserve">11.4036769866943</t>
@@ -467,19 +467,19 @@
     <t xml:space="preserve">11.3386077880859</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3223400115967</t>
+    <t xml:space="preserve">11.3223390579224</t>
   </si>
   <si>
     <t xml:space="preserve">11.3304738998413</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3630094528198</t>
+    <t xml:space="preserve">11.3630075454712</t>
   </si>
   <si>
     <t xml:space="preserve">11.0783233642578</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6065587997437</t>
+    <t xml:space="preserve">10.6065607070923</t>
   </si>
   <si>
     <t xml:space="preserve">10.8424415588379</t>
@@ -491,46 +491,46 @@
     <t xml:space="preserve">10.6390933990479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4113464355469</t>
+    <t xml:space="preserve">10.4113454818726</t>
   </si>
   <si>
     <t xml:space="preserve">10.2080001831055</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2730712890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2324018478394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.321873664856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3706769943237</t>
+    <t xml:space="preserve">10.2730703353882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2323999404907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3218746185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.370677947998</t>
   </si>
   <si>
     <t xml:space="preserve">10.3300075531006</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3056058883667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2568035125732</t>
+    <t xml:space="preserve">10.3056049346924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2568025588989</t>
   </si>
   <si>
     <t xml:space="preserve">10.1835975646973</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4845514297485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3625421524048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4438810348511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8587093353271</t>
+    <t xml:space="preserve">10.4845523834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3625431060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4438819885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8587083816528</t>
   </si>
   <si>
     <t xml:space="preserve">10.9237794876099</t>
@@ -539,31 +539,31 @@
     <t xml:space="preserve">11.0376539230347</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0620555877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1027250289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1433925628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.175929069519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1352596282959</t>
+    <t xml:space="preserve">11.0620574951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.102725982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1433944702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1759281158447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1352605819702</t>
   </si>
   <si>
     <t xml:space="preserve">11.0701894760132</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1189937591553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1515283584595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2247323989868</t>
+    <t xml:space="preserve">11.118992805481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1515274047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2247333526611</t>
   </si>
   <si>
     <t xml:space="preserve">11.0457878112793</t>
@@ -572,28 +572,28 @@
     <t xml:space="preserve">10.5008182525635</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1347951889038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36161136627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01999187469482</t>
+    <t xml:space="preserve">10.1347942352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36161327362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01999092102051</t>
   </si>
   <si>
     <t xml:space="preserve">8.10946273803711</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3941478729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21520328521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33720970153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31280899047852</t>
+    <t xml:space="preserve">8.39414691925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21520233154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3372106552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3128080368042</t>
   </si>
   <si>
     <t xml:space="preserve">8.18266773223877</t>
@@ -602,40 +602,40 @@
     <t xml:space="preserve">8.34534454345703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23960494995117</t>
+    <t xml:space="preserve">8.23960590362549</t>
   </si>
   <si>
     <t xml:space="preserve">8.49175453186035</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58936214447021</t>
+    <t xml:space="preserve">8.58935928344727</t>
   </si>
   <si>
     <t xml:space="preserve">8.76017189025879</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29654312133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25587272644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17453384399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19080066680908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23147106170654</t>
+    <t xml:space="preserve">8.29654216766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25587177276611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17453479766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1908016204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23147010803223</t>
   </si>
   <si>
     <t xml:space="preserve">8.2802734375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14199829101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15826606750488</t>
+    <t xml:space="preserve">8.14199733734131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15826511383057</t>
   </si>
   <si>
     <t xml:space="preserve">8.16639995574951</t>
@@ -644,28 +644,28 @@
     <t xml:space="preserve">8.12166309356689</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05252552032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89798164367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85731315612793</t>
+    <t xml:space="preserve">8.05252456665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89798259735107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85731267929077</t>
   </si>
   <si>
     <t xml:space="preserve">7.93051719665527</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90611505508423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93865251541138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84917831420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80851030349731</t>
+    <t xml:space="preserve">7.90611553192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93865156173706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84917879104614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80850887298584</t>
   </si>
   <si>
     <t xml:space="preserve">7.62956380844116</t>
@@ -677,46 +677,46 @@
     <t xml:space="preserve">7.48315572738647</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66616630554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60516405105591</t>
+    <t xml:space="preserve">7.66616678237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60516119003296</t>
   </si>
   <si>
     <t xml:space="preserve">7.54009246826172</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52382326126099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.479088306427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61329698562622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54822587966919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56449460983276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50755548477173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4668869972229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4912896156311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49942255020142</t>
+    <t xml:space="preserve">7.52382373809814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47908782958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61329746246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54822540283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56449270248413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50755643844604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46688604354858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49128913879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49942302703857</t>
   </si>
   <si>
     <t xml:space="preserve">7.31234455108643</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27980852127075</t>
+    <t xml:space="preserve">7.27980804443359</t>
   </si>
   <si>
     <t xml:space="preserve">7.37741470336914</t>
@@ -725,28 +725,28 @@
     <t xml:space="preserve">7.38554906845093</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36928081512451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32047700881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34487915039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28794288635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04392623901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15780019760132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39368200302124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42621755599976</t>
+    <t xml:space="preserve">7.36928033828735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3204779624939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34487867355347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28794145584106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04392671585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15780067443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39368343353271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42621850967407</t>
   </si>
   <si>
     <t xml:space="preserve">7.40181684494019</t>
@@ -755,25 +755,25 @@
     <t xml:space="preserve">7.30421018600464</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3611478805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20660352706909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35301303863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.336745262146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27167510986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2310037612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32861232757568</t>
+    <t xml:space="preserve">7.36114835739136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20660305023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3530125617981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33674573898315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27167463302612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23100471496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32861089706421</t>
   </si>
   <si>
     <t xml:space="preserve">7.26354122161865</t>
@@ -782,7 +782,7 @@
     <t xml:space="preserve">7.23913908004761</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22287130355835</t>
+    <t xml:space="preserve">7.22287225723267</t>
   </si>
   <si>
     <t xml:space="preserve">7.24727296829224</t>
@@ -791,76 +791,76 @@
     <t xml:space="preserve">7.44248628616333</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25540733337402</t>
+    <t xml:space="preserve">7.25540781021118</t>
   </si>
   <si>
     <t xml:space="preserve">7.18220233917236</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29607629776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16593503952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14153289794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05206060409546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07646179199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03579378128052</t>
+    <t xml:space="preserve">7.29607582092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16593408584595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14153385162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05205965042114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0764627456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03579330444336</t>
   </si>
   <si>
     <t xml:space="preserve">7.01952505111694</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87311553955078</t>
+    <t xml:space="preserve">6.87311506271362</t>
   </si>
   <si>
     <t xml:space="preserve">6.67790269851685</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85124778747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93379163742065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26397275924683</t>
+    <t xml:space="preserve">6.85124731063843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93379259109497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26397371292114</t>
   </si>
   <si>
     <t xml:space="preserve">7.14841032028198</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09888410568237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18142795562744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16491842269897</t>
+    <t xml:space="preserve">7.09888315200806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18142890930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16491937637329</t>
   </si>
   <si>
     <t xml:space="preserve">7.14015579223633</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2144455909729</t>
+    <t xml:space="preserve">7.21444654464722</t>
   </si>
   <si>
     <t xml:space="preserve">7.17317390441895</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97506427764893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84299373626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60361289978027</t>
+    <t xml:space="preserve">6.97506475448608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84299278259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6036114692688</t>
   </si>
   <si>
     <t xml:space="preserve">6.62012100219727</t>
@@ -869,7 +869,7 @@
     <t xml:space="preserve">6.67790222167969</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80997514724731</t>
+    <t xml:space="preserve">6.80997467041016</t>
   </si>
   <si>
     <t xml:space="preserve">6.54583072662354</t>
@@ -878,259 +878,259 @@
     <t xml:space="preserve">6.31470394134521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32295846939087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34772205352783</t>
+    <t xml:space="preserve">6.32295894622803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34772253036499</t>
   </si>
   <si>
     <t xml:space="preserve">6.38074064254761</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39724922180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4715404510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28168535232544</t>
+    <t xml:space="preserve">6.39724969863892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47153997421265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28168630599976</t>
   </si>
   <si>
     <t xml:space="preserve">6.22390413284302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09183168411255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90197849273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9597601890564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9927773475647</t>
+    <t xml:space="preserve">6.09183216094971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90197801589966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95975971221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99277782440186</t>
   </si>
   <si>
     <t xml:space="preserve">6.20739555358887</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14135932922363</t>
+    <t xml:space="preserve">6.14135980606079</t>
   </si>
   <si>
     <t xml:space="preserve">6.19088649749756</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14961338043213</t>
+    <t xml:space="preserve">6.14961385726929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0753231048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25692272186279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00928783416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9845232963562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12485074996948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13310480117798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27343130111694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44677591323853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55408525466919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51281213760376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36423110961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24041414260864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21565008163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23215961456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24866819381714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11659622192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10834074020386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05055952072144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89372396469116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.778160572052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6956148147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79466915130615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80292320251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82768774032593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7864146232605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73688840866089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85245084762573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29819536209106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18263149261475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15786838531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03404998779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08357763290405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81943368911743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91848707199097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86070537567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76165199279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75339698791504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81117820739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70387029647827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74514198303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83594226837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71212434768677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84419679641724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94325065612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96801424026489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87721538543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88546943664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93499612808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02579593658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0670690536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3889946937561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19914054870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04230451583862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05881404876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95150566101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17437744140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17601919174194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29349803924561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25993251800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20958423614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09210586547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10888910293579</t>
   </si>
   <si>
     <t xml:space="preserve">6.07532358169556</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25692319869995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00928735733032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9845232963562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12485074996948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13310480117798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27343130111694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44677639007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55408573150635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51281261444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3642315864563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24041366577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21565008163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23215913772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24866819381714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11659526824951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1083402633667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05055904388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89372396469116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77816104888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69561529159546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79466962814331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80292320251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82768774032593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78641510009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73688745498657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85245084762573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29819536209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18263244628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15786743164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03404998779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08357763290405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81943368911743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91848659515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86070585250854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76165103912354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75339651107788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8111777305603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70386981964111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74514198303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83594226837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71212434768677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84419679641724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94325065612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96801424026489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87721490859985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88546943664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93499565124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02579593658447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0670690536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3889946937561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19914054870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04230451583862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05881404876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9515061378479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17437744140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17602014541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29349803924561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25993299484253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20958423614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09210538864136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10888862609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0753231048584</t>
-  </si>
-  <si>
     <t xml:space="preserve">6.14245367050171</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05854082107544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02497529983521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97462749481201</t>
+    <t xml:space="preserve">6.05854034423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02497482299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97462797164917</t>
   </si>
   <si>
     <t xml:space="preserve">5.95784425735474</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15923690795898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12567090988159</t>
+    <t xml:space="preserve">6.15923643112183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12567138671875</t>
   </si>
   <si>
     <t xml:space="preserve">6.19280195236206</t>
@@ -1139,37 +1139,37 @@
     <t xml:space="preserve">6.42775964736938</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71306467056274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64593410491943</t>
+    <t xml:space="preserve">6.71306419372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64593458175659</t>
   </si>
   <si>
     <t xml:space="preserve">6.69628190994263</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78019523620605</t>
+    <t xml:space="preserve">6.78019571304321</t>
   </si>
   <si>
     <t xml:space="preserve">6.7298469543457</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62915086746216</t>
+    <t xml:space="preserve">6.629150390625</t>
   </si>
   <si>
     <t xml:space="preserve">6.56202030181885</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54523754119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67949914932251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66271638870239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57880353927612</t>
+    <t xml:space="preserve">6.54523801803589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67949867248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66271686553955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57880306243896</t>
   </si>
   <si>
     <t xml:space="preserve">6.37741088867188</t>
@@ -1178,7 +1178,7 @@
     <t xml:space="preserve">6.34384632110596</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22636795043945</t>
+    <t xml:space="preserve">6.22636747360229</t>
   </si>
   <si>
     <t xml:space="preserve">6.36062860488892</t>
@@ -1187,13 +1187,13 @@
     <t xml:space="preserve">5.67253923416138</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55506038665771</t>
+    <t xml:space="preserve">5.55505990982056</t>
   </si>
   <si>
     <t xml:space="preserve">5.68932247161865</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62219142913818</t>
+    <t xml:space="preserve">5.62219190597534</t>
   </si>
   <si>
     <t xml:space="preserve">5.53827810287476</t>
@@ -1205,7 +1205,7 @@
     <t xml:space="preserve">5.45436525344849</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60540866851807</t>
+    <t xml:space="preserve">5.60540819168091</t>
   </si>
   <si>
     <t xml:space="preserve">5.5214958190918</t>
@@ -1214,28 +1214,28 @@
     <t xml:space="preserve">5.50471258163452</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48792934417725</t>
+    <t xml:space="preserve">5.4879298210144</t>
   </si>
   <si>
     <t xml:space="preserve">5.35366916656494</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3704514503479</t>
+    <t xml:space="preserve">5.37045049667358</t>
   </si>
   <si>
     <t xml:space="preserve">5.42079925537109</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28653764724731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30332040786743</t>
+    <t xml:space="preserve">5.28653860092163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30332088470459</t>
   </si>
   <si>
     <t xml:space="preserve">5.26975584030151</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38723468780518</t>
+    <t xml:space="preserve">5.38723373413086</t>
   </si>
   <si>
     <t xml:space="preserve">5.32010364532471</t>
@@ -1244,7 +1244,7 @@
     <t xml:space="preserve">5.65575647354126</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75645303726196</t>
+    <t xml:space="preserve">5.75645351409912</t>
   </si>
   <si>
     <t xml:space="preserve">5.70610475540161</t>
@@ -1256,49 +1256,49 @@
     <t xml:space="preserve">5.73967027664185</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6389741897583</t>
+    <t xml:space="preserve">5.63897466659546</t>
   </si>
   <si>
     <t xml:space="preserve">5.57184362411499</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18584203720093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2026252746582</t>
+    <t xml:space="preserve">5.18584251403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20262479782104</t>
   </si>
   <si>
     <t xml:space="preserve">5.21940803527832</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16905927658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13549327850342</t>
+    <t xml:space="preserve">5.16905975341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13549423217773</t>
   </si>
   <si>
     <t xml:space="preserve">5.10192918777466</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9508843421936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03479909896851</t>
+    <t xml:space="preserve">4.95088529586792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03479862213135</t>
   </si>
   <si>
     <t xml:space="preserve">5.15227651596069</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11871099472046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06836366653442</t>
+    <t xml:space="preserve">5.11871147155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06836318969727</t>
   </si>
   <si>
     <t xml:space="preserve">5.08514642715454</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23619031906128</t>
+    <t xml:space="preserve">5.23618984222412</t>
   </si>
   <si>
     <t xml:space="preserve">5.25297212600708</t>
@@ -1313,31 +1313,31 @@
     <t xml:space="preserve">5.77323532104492</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58862590789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81662321090698</t>
+    <t xml:space="preserve">5.58862686157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81662368774414</t>
   </si>
   <si>
     <t xml:space="preserve">4.79984092712402</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59844923019409</t>
+    <t xml:space="preserve">4.59844875335693</t>
   </si>
   <si>
     <t xml:space="preserve">4.36349201202393</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31314325332642</t>
+    <t xml:space="preserve">4.31314420700073</t>
   </si>
   <si>
     <t xml:space="preserve">4.19566535949707</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11175155639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02783870697021</t>
+    <t xml:space="preserve">4.11175107955933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02783823013306</t>
   </si>
   <si>
     <t xml:space="preserve">4.17049074172974</t>
@@ -1346,13 +1346,13 @@
     <t xml:space="preserve">4.06979560852051</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12014245986938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34670877456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17888164520264</t>
+    <t xml:space="preserve">4.12014293670654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34670829772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17888212203979</t>
   </si>
   <si>
     <t xml:space="preserve">4.04462146759033</t>
@@ -1364,13 +1364,13 @@
     <t xml:space="preserve">4.26279640197754</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16209936141968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14531755447388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99427270889282</t>
+    <t xml:space="preserve">4.16209983825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14531803131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9942729473114</t>
   </si>
   <si>
     <t xml:space="preserve">4.09496927261353</t>
@@ -1385,7 +1385,7 @@
     <t xml:space="preserve">4.22923040390015</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21244812011719</t>
+    <t xml:space="preserve">4.21244764328003</t>
   </si>
   <si>
     <t xml:space="preserve">4.03622961044312</t>
@@ -1394,19 +1394,19 @@
     <t xml:space="preserve">4.12877893447876</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1628303527832</t>
+    <t xml:space="preserve">4.16283082962036</t>
   </si>
   <si>
     <t xml:space="preserve">4.07770156860352</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00108480453491</t>
+    <t xml:space="preserve">4.00108528137207</t>
   </si>
   <si>
     <t xml:space="preserve">4.20539569854736</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37565517425537</t>
+    <t xml:space="preserve">4.37565469741821</t>
   </si>
   <si>
     <t xml:space="preserve">4.21390867233276</t>
@@ -1415,10 +1415,10 @@
     <t xml:space="preserve">4.22242164611816</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25647354125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24795961380005</t>
+    <t xml:space="preserve">4.25647306442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24796009063721</t>
   </si>
   <si>
     <t xml:space="preserve">4.32457685470581</t>
@@ -1427,13 +1427,13 @@
     <t xml:space="preserve">4.30755090713501</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23944807052612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35862827301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51186227798462</t>
+    <t xml:space="preserve">4.23944759368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35862874984741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51186180114746</t>
   </si>
   <si>
     <t xml:space="preserve">5.5334153175354</t>
@@ -1442,10 +1442,10 @@
     <t xml:space="preserve">5.9420371055603</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8909592628479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73772621154785</t>
+    <t xml:space="preserve">5.89095878601074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73772573471069</t>
   </si>
   <si>
     <t xml:space="preserve">5.5504412651062</t>
@@ -1457,13 +1457,13 @@
     <t xml:space="preserve">5.567467212677</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41423463821411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2610011100769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.482337474823</t>
+    <t xml:space="preserve">5.41423416137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26100158691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48233795166016</t>
   </si>
   <si>
     <t xml:space="preserve">5.44828605651855</t>
@@ -1472,25 +1472,25 @@
     <t xml:space="preserve">5.6015191078186</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66962242126465</t>
+    <t xml:space="preserve">5.66962289810181</t>
   </si>
   <si>
     <t xml:space="preserve">5.5163893699646</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70367383956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32910442352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27802753448486</t>
+    <t xml:space="preserve">5.70367431640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32910490036011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27802705764771</t>
   </si>
   <si>
     <t xml:space="preserve">5.43126010894775</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31207799911499</t>
+    <t xml:space="preserve">5.31207847595215</t>
   </si>
   <si>
     <t xml:space="preserve">5.2269492149353</t>
@@ -1499,7 +1499,7 @@
     <t xml:space="preserve">5.00561237335205</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95453548431396</t>
+    <t xml:space="preserve">4.95453500747681</t>
   </si>
   <si>
     <t xml:space="preserve">4.93750905990601</t>
@@ -1508,37 +1508,37 @@
     <t xml:space="preserve">5.05669069290161</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03966474533081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97156143188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8864312171936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02263879776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92048311233521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90345764160156</t>
+    <t xml:space="preserve">5.03966426849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97156095504761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88643169403076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02263832092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92048358917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9034571647644</t>
   </si>
   <si>
     <t xml:space="preserve">4.852379322052</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86940479278564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34613084793091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2439751625061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36315679550171</t>
+    <t xml:space="preserve">4.8694052696228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34613037109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24397468566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36315631866455</t>
   </si>
   <si>
     <t xml:space="preserve">5.38018226623535</t>
@@ -1547,7 +1547,7 @@
     <t xml:space="preserve">5.2099232673645</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15884590148926</t>
+    <t xml:space="preserve">5.1588454246521</t>
   </si>
   <si>
     <t xml:space="preserve">5.10776805877686</t>
@@ -1559,16 +1559,16 @@
     <t xml:space="preserve">5.09074211120605</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1928973197937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1758713722229</t>
+    <t xml:space="preserve">5.19289779663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17587089538574</t>
   </si>
   <si>
     <t xml:space="preserve">5.14181995391846</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0737156867981</t>
+    <t xml:space="preserve">5.07371616363525</t>
   </si>
   <si>
     <t xml:space="preserve">4.68212080001831</t>
@@ -1580,13 +1580,13 @@
     <t xml:space="preserve">4.59699153900146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57996559143066</t>
+    <t xml:space="preserve">4.57996511459351</t>
   </si>
   <si>
     <t xml:space="preserve">4.63104295730591</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7842755317688</t>
+    <t xml:space="preserve">4.78427600860596</t>
   </si>
   <si>
     <t xml:space="preserve">4.76725006103516</t>
@@ -1601,22 +1601,22 @@
     <t xml:space="preserve">5.39720821380615</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6185450553894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4653115272522</t>
+    <t xml:space="preserve">5.61854457855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46531200408936</t>
   </si>
   <si>
     <t xml:space="preserve">5.49936389923096</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63557052612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68664836883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65259599685669</t>
+    <t xml:space="preserve">5.63557100296021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68664789199829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65259695053101</t>
   </si>
   <si>
     <t xml:space="preserve">5.8569073677063</t>
@@ -1631,28 +1631,28 @@
     <t xml:space="preserve">6.33363246917725</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29958009719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35065793991089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43578767776489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55496835708618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69117593765259</t>
+    <t xml:space="preserve">6.29958057403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35065841674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43578720092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55496883392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69117641448975</t>
   </si>
   <si>
     <t xml:space="preserve">6.79333162307739</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15087461471558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08277130126953</t>
+    <t xml:space="preserve">7.15087413787842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08277082443237</t>
   </si>
   <si>
     <t xml:space="preserve">6.87846088409424</t>
@@ -1670,13 +1670,13 @@
     <t xml:space="preserve">6.75927972793579</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53794288635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72522830963135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65712404251099</t>
+    <t xml:space="preserve">6.5379433631897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72522783279419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65712451934814</t>
   </si>
   <si>
     <t xml:space="preserve">6.91251277923584</t>
@@ -1685,40 +1685,40 @@
     <t xml:space="preserve">6.8954873085022</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96359062194824</t>
+    <t xml:space="preserve">6.96359014511108</t>
   </si>
   <si>
     <t xml:space="preserve">7.17302179336548</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05085325241089</t>
+    <t xml:space="preserve">7.05085372924805</t>
   </si>
   <si>
     <t xml:space="preserve">7.1206636428833</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57443237304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97584247589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02819919586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06310558319092</t>
+    <t xml:space="preserve">7.57443189620972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9758415222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02820014953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0631046295166</t>
   </si>
   <si>
     <t xml:space="preserve">7.99329423904419</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01074695587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94093704223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13291358947754</t>
+    <t xml:space="preserve">8.0107479095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94093656539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13291454315186</t>
   </si>
   <si>
     <t xml:space="preserve">8.15036773681641</t>
@@ -1727,22 +1727,22 @@
     <t xml:space="preserve">8.16781997680664</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18527412414551</t>
+    <t xml:space="preserve">8.18527317047119</t>
   </si>
   <si>
     <t xml:space="preserve">8.34234714508057</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11546325683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25508213043213</t>
+    <t xml:space="preserve">8.11546230316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25508308410645</t>
   </si>
   <si>
     <t xml:space="preserve">8.08055686950684</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20272541046143</t>
+    <t xml:space="preserve">8.20272445678711</t>
   </si>
   <si>
     <t xml:space="preserve">7.95838832855225</t>
@@ -1754,16 +1754,16 @@
     <t xml:space="preserve">8.32489395141602</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81356716156006</t>
+    <t xml:space="preserve">8.81356811523438</t>
   </si>
   <si>
     <t xml:space="preserve">8.58668327331543</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53432369232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69139957427979</t>
+    <t xml:space="preserve">8.53432464599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69139862060547</t>
   </si>
   <si>
     <t xml:space="preserve">8.60413551330566</t>
@@ -1772,7 +1772,7 @@
     <t xml:space="preserve">8.72630405426025</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42961025238037</t>
+    <t xml:space="preserve">8.42960929870605</t>
   </si>
   <si>
     <t xml:space="preserve">8.28998851776123</t>
@@ -1781,7 +1781,7 @@
     <t xml:space="preserve">8.30744171142578</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04565238952637</t>
+    <t xml:space="preserve">8.04565143585205</t>
   </si>
   <si>
     <t xml:space="preserve">7.85367298126221</t>
@@ -1802,7 +1802,7 @@
     <t xml:space="preserve">8.09801006317139</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23763084411621</t>
+    <t xml:space="preserve">8.23763179779053</t>
   </si>
   <si>
     <t xml:space="preserve">8.48196697235107</t>
@@ -1826,13 +1826,13 @@
     <t xml:space="preserve">8.49941921234131</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5692310333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99161815643311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59893417358398</t>
+    <t xml:space="preserve">8.56923007965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99161720275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5989351272583</t>
   </si>
   <si>
     <t xml:space="preserve">9.77346038818359</t>
@@ -1841,28 +1841,28 @@
     <t xml:space="preserve">9.8170919418335</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29351425170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46804046630859</t>
+    <t xml:space="preserve">9.29351329803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46803951263428</t>
   </si>
   <si>
     <t xml:space="preserve">9.55530261993408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64256572723389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90435409545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33714485168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94798564910889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86072254180908</t>
+    <t xml:space="preserve">9.6425666809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9043550491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33714389801025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9479866027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8607234954834</t>
   </si>
   <si>
     <t xml:space="preserve">10.5151958465576</t>
@@ -1874,10 +1874,10 @@
     <t xml:space="preserve">10.5588283538818</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6024580001831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8206176757812</t>
+    <t xml:space="preserve">10.6024589538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8206167221069</t>
   </si>
   <si>
     <t xml:space="preserve">10.7333545684814</t>
@@ -1889,7 +1889,7 @@
     <t xml:space="preserve">10.2970390319824</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3843002319336</t>
+    <t xml:space="preserve">10.3843011856079</t>
   </si>
   <si>
     <t xml:space="preserve">10.3406705856323</t>
@@ -1898,16 +1898,16 @@
     <t xml:space="preserve">10.2097749710083</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2534074783325</t>
+    <t xml:space="preserve">10.2534065246582</t>
   </si>
   <si>
     <t xml:space="preserve">10.0788812637329</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51167106628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72982788085938</t>
+    <t xml:space="preserve">9.51167011260986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72982883453369</t>
   </si>
   <si>
     <t xml:space="preserve">9.68619728088379</t>
@@ -1916,28 +1916,28 @@
     <t xml:space="preserve">8.98809337615967</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42440891265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6496162414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5623531341553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7805099487305</t>
+    <t xml:space="preserve">9.42440795898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6496171951294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.562352180481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7805109024048</t>
   </si>
   <si>
     <t xml:space="preserve">11.9114036560059</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9550361633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6932458877563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3040895462036</t>
+    <t xml:space="preserve">11.9550352096558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6932468414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3040885925293</t>
   </si>
   <si>
     <t xml:space="preserve">12.2604570388794</t>
@@ -1958,10 +1958,10 @@
     <t xml:space="preserve">11.6059846878052</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9515113830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0422992706299</t>
+    <t xml:space="preserve">10.9515104293823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0422983169556</t>
   </si>
   <si>
     <t xml:space="preserve">11.3005638122559</t>
@@ -1970,7 +1970,7 @@
     <t xml:space="preserve">11.3441953659058</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9951438903809</t>
+    <t xml:space="preserve">10.9951429367065</t>
   </si>
   <si>
     <t xml:space="preserve">10.4715642929077</t>
@@ -1979,61 +1979,61 @@
     <t xml:space="preserve">10.9078798294067</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4314575195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0387735366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9899406433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.74560546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5361738204956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5187215805054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6234369277954</t>
+    <t xml:space="preserve">11.4314584732056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0387725830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9899415969849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7456045150757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5361728668213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5187206268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6234359741211</t>
   </si>
   <si>
     <t xml:space="preserve">11.4489107131958</t>
   </si>
   <si>
-    <t xml:space="preserve">11.64089012146</t>
+    <t xml:space="preserve">11.6408891677856</t>
   </si>
   <si>
     <t xml:space="preserve">11.7281522750854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9201307296753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1173114776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0998592376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8031635284424</t>
+    <t xml:space="preserve">11.9201316833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1173105239868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0998582839966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8031644821167</t>
   </si>
   <si>
     <t xml:space="preserve">10.7508058547974</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3319444656372</t>
+    <t xml:space="preserve">10.3319435119629</t>
   </si>
   <si>
     <t xml:space="preserve">10.1050596237183</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81839275360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69297313690186</t>
+    <t xml:space="preserve">9.81839179992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69297409057617</t>
   </si>
   <si>
     <t xml:space="preserve">9.7108907699585</t>
@@ -2051,25 +2051,25 @@
     <t xml:space="preserve">10.1229763031006</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1588096618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0692262649536</t>
+    <t xml:space="preserve">10.1588106155396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0692253112793</t>
   </si>
   <si>
     <t xml:space="preserve">10.0871429443359</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4633960723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7858972549438</t>
+    <t xml:space="preserve">10.4633951187134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7858982086182</t>
   </si>
   <si>
     <t xml:space="preserve">10.5708961486816</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7142305374146</t>
+    <t xml:space="preserve">10.7142295837402</t>
   </si>
   <si>
     <t xml:space="preserve">10.7500638961792</t>
@@ -2081,13 +2081,13 @@
     <t xml:space="preserve">10.8754816055298</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6425628662109</t>
+    <t xml:space="preserve">10.6425619125366</t>
   </si>
   <si>
     <t xml:space="preserve">10.5888118743896</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5171451568604</t>
+    <t xml:space="preserve">10.5171461105347</t>
   </si>
   <si>
     <t xml:space="preserve">10.8575649261475</t>
@@ -2102,22 +2102,22 @@
     <t xml:space="preserve">10.6604795455933</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3021450042725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4096450805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3558950424194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6783971786499</t>
+    <t xml:space="preserve">10.3021440505981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4096441268921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3558940887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6783962249756</t>
   </si>
   <si>
     <t xml:space="preserve">10.4275617599487</t>
   </si>
   <si>
-    <t xml:space="preserve">10.535062789917</t>
+    <t xml:space="preserve">10.5350618362427</t>
   </si>
   <si>
     <t xml:space="preserve">11.1800661087036</t>
@@ -2132,7 +2132,7 @@
     <t xml:space="preserve">11.3771505355835</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7354869842529</t>
+    <t xml:space="preserve">11.7354860305786</t>
   </si>
   <si>
     <t xml:space="preserve">11.9146537780762</t>
@@ -2141,7 +2141,7 @@
     <t xml:space="preserve">11.9325704574585</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0221548080444</t>
+    <t xml:space="preserve">12.0221538543701</t>
   </si>
   <si>
     <t xml:space="preserve">11.8788204193115</t>
@@ -2150,7 +2150,7 @@
     <t xml:space="preserve">12.2371559143066</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3267393112183</t>
+    <t xml:space="preserve">12.3267402648926</t>
   </si>
   <si>
     <t xml:space="preserve">12.4521570205688</t>
@@ -2162,7 +2162,7 @@
     <t xml:space="preserve">12.3984069824219</t>
   </si>
   <si>
-    <t xml:space="preserve">12.201322555542</t>
+    <t xml:space="preserve">12.2013216018677</t>
   </si>
   <si>
     <t xml:space="preserve">11.9863214492798</t>
@@ -2174,7 +2174,7 @@
     <t xml:space="preserve">12.6134080886841</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8463268280029</t>
+    <t xml:space="preserve">12.8463258743286</t>
   </si>
   <si>
     <t xml:space="preserve">12.810492515564</t>
@@ -2186,25 +2186,25 @@
     <t xml:space="preserve">13.258412361145</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4017467498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4375791549683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6884145736694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.903416633606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6559209823608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2438335418701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6380033493042</t>
+    <t xml:space="preserve">13.4017457962036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4375801086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6884136199951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9034156799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6559200286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2438344955444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6380043029785</t>
   </si>
   <si>
     <t xml:space="preserve">14.92467212677</t>
@@ -2222,7 +2222,7 @@
     <t xml:space="preserve">14.5484189987183</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4946689605713</t>
+    <t xml:space="preserve">14.4946699142456</t>
   </si>
   <si>
     <t xml:space="preserve">14.2617511749268</t>
@@ -2231,25 +2231,25 @@
     <t xml:space="preserve">14.8888387680054</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8171710968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.387167930603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7634201049805</t>
+    <t xml:space="preserve">14.8171730041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3871688842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7634210586548</t>
   </si>
   <si>
     <t xml:space="preserve">14.6200866699219</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9067535400391</t>
+    <t xml:space="preserve">14.9067544937134</t>
   </si>
   <si>
     <t xml:space="preserve">15.1217546463013</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0321741104126</t>
+    <t xml:space="preserve">15.0321731567383</t>
   </si>
   <si>
     <t xml:space="preserve">14.7455034255981</t>
@@ -2258,22 +2258,22 @@
     <t xml:space="preserve">15.0500888824463</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0680065155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1038398742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5305023193359</t>
+    <t xml:space="preserve">15.0680046081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1038408279419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5305032730103</t>
   </si>
   <si>
     <t xml:space="preserve">14.7096710205078</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2080011367798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6167469024658</t>
+    <t xml:space="preserve">14.2080001831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6167478561401</t>
   </si>
   <si>
     <t xml:space="preserve">13.5092468261719</t>
@@ -2282,19 +2282,19 @@
     <t xml:space="preserve">13.0434112548828</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1688280105591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9717426300049</t>
+    <t xml:space="preserve">13.1688270568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9717435836792</t>
   </si>
   <si>
     <t xml:space="preserve">12.4700746536255</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2404956817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6525802612305</t>
+    <t xml:space="preserve">13.2404947280884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6525812149048</t>
   </si>
   <si>
     <t xml:space="preserve">13.5809135437012</t>
@@ -2309,7 +2309,7 @@
     <t xml:space="preserve">13.2225780487061</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2046604156494</t>
+    <t xml:space="preserve">13.2046613693237</t>
   </si>
   <si>
     <t xml:space="preserve">13.0613269805908</t>
@@ -2318,7 +2318,7 @@
     <t xml:space="preserve">13.0075778961182</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6313247680664</t>
+    <t xml:space="preserve">12.6313257217407</t>
   </si>
   <si>
     <t xml:space="preserve">13.0971612930298</t>
@@ -2327,10 +2327,10 @@
     <t xml:space="preserve">13.0792446136475</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8642425537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9896602630615</t>
+    <t xml:space="preserve">12.8642435073853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9896593093872</t>
   </si>
   <si>
     <t xml:space="preserve">12.9538269042969</t>
@@ -2345,31 +2345,31 @@
     <t xml:space="preserve">13.1150779724121</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1509113311768</t>
+    <t xml:space="preserve">13.1509122848511</t>
   </si>
   <si>
     <t xml:space="preserve">13.5271635055542</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3479957580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2763290405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7925748825073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5954923629761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5238246917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5059070587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4879903793335</t>
+    <t xml:space="preserve">13.3479948043823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.276328086853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7925758361816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5954914093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5238237380981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5059080123901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4879894256592</t>
   </si>
   <si>
     <t xml:space="preserve">12.3088226318359</t>
@@ -2381,7 +2381,7 @@
     <t xml:space="preserve">12.8284091949463</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3804903030396</t>
+    <t xml:space="preserve">12.3804893493652</t>
   </si>
   <si>
     <t xml:space="preserve">12.6671581268311</t>
@@ -2399,19 +2399,19 @@
     <t xml:space="preserve">12.4342403411865</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9504871368408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2192392349243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8250694274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1117382049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9684047698975</t>
+    <t xml:space="preserve">11.9504880905151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2192401885986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8250703811646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1117391586304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9684038162231</t>
   </si>
   <si>
     <t xml:space="preserve">12.0400714874268</t>
@@ -2423,10 +2423,10 @@
     <t xml:space="preserve">12.255072593689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7388248443604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7421655654907</t>
+    <t xml:space="preserve">12.7388257980347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7421646118164</t>
   </si>
   <si>
     <t xml:space="preserve">13.7063312530518</t>
@@ -2435,7 +2435,7 @@
     <t xml:space="preserve">14.0825834274292</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0109157562256</t>
+    <t xml:space="preserve">14.0109167098999</t>
   </si>
   <si>
     <t xml:space="preserve">13.7242479324341</t>
@@ -2444,13 +2444,13 @@
     <t xml:space="preserve">14.0467500686646</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0646657943726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9392490386963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6346645355225</t>
+    <t xml:space="preserve">14.0646667480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9392499923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6346635818481</t>
   </si>
   <si>
     <t xml:space="preserve">14.2796678543091</t>
@@ -2462,7 +2462,7 @@
     <t xml:space="preserve">13.9571657180786</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8496656417847</t>
+    <t xml:space="preserve">13.8496646881104</t>
   </si>
   <si>
     <t xml:space="preserve">13.9750833511353</t>
@@ -2474,7 +2474,7 @@
     <t xml:space="preserve">13.4734134674072</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1867446899414</t>
+    <t xml:space="preserve">13.1867456436157</t>
   </si>
   <si>
     <t xml:space="preserve">13.3838291168213</t>
@@ -2483,10 +2483,10 @@
     <t xml:space="preserve">13.5988302230835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.70299243927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8429870605469</t>
+    <t xml:space="preserve">12.7029914855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8429861068726</t>
   </si>
   <si>
     <t xml:space="preserve">11.7892360687256</t>
@@ -2504,25 +2504,25 @@
     <t xml:space="preserve">11.2159004211426</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3592338562012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4309015274048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3054828643799</t>
+    <t xml:space="preserve">11.3592348098755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4309024810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3054838180542</t>
   </si>
   <si>
     <t xml:space="preserve">11.2875671386719</t>
   </si>
   <si>
-    <t xml:space="preserve">11.683783531189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5179262161255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2783517837524</t>
+    <t xml:space="preserve">11.6837844848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5179252624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2783527374268</t>
   </si>
   <si>
     <t xml:space="preserve">11.1493520736694</t>
@@ -2534,7 +2534,7 @@
     <t xml:space="preserve">11.0756378173828</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9970722198486</t>
+    <t xml:space="preserve">11.9970712661743</t>
   </si>
   <si>
     <t xml:space="preserve">12.052357673645</t>
@@ -2543,7 +2543,7 @@
     <t xml:space="preserve">12.2735013961792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2182149887085</t>
+    <t xml:space="preserve">12.2182159423828</t>
   </si>
   <si>
     <t xml:space="preserve">12.4025020599365</t>
@@ -2555,7 +2555,7 @@
     <t xml:space="preserve">12.0707864761353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1629285812378</t>
+    <t xml:space="preserve">12.1629295349121</t>
   </si>
   <si>
     <t xml:space="preserve">12.1260719299316</t>
@@ -2570,13 +2570,13 @@
     <t xml:space="preserve">11.7759265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8312129974365</t>
+    <t xml:space="preserve">11.8312139511108</t>
   </si>
   <si>
     <t xml:space="preserve">11.9786424636841</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7206411361694</t>
+    <t xml:space="preserve">11.7206420898438</t>
   </si>
   <si>
     <t xml:space="preserve">11.868070602417</t>
@@ -2591,7 +2591,7 @@
     <t xml:space="preserve">11.4442110061646</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3520669937134</t>
+    <t xml:space="preserve">11.3520679473877</t>
   </si>
   <si>
     <t xml:space="preserve">11.3704957962036</t>
@@ -2609,7 +2609,7 @@
     <t xml:space="preserve">11.7022123336792</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5732116699219</t>
+    <t xml:space="preserve">11.5732126235962</t>
   </si>
   <si>
     <t xml:space="preserve">11.481068611145</t>
@@ -2618,7 +2618,7 @@
     <t xml:space="preserve">11.296781539917</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3152093887329</t>
+    <t xml:space="preserve">11.3152103424072</t>
   </si>
   <si>
     <t xml:space="preserve">11.5547828674316</t>
@@ -2627,7 +2627,7 @@
     <t xml:space="preserve">11.4257822036743</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3336381912231</t>
+    <t xml:space="preserve">11.3336391448975</t>
   </si>
   <si>
     <t xml:space="preserve">11.3889245986938</t>
@@ -2636,7 +2636,7 @@
     <t xml:space="preserve">11.4626398086548</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7943553924561</t>
+    <t xml:space="preserve">11.7943563461304</t>
   </si>
   <si>
     <t xml:space="preserve">12.1076431274414</t>
@@ -2666,7 +2666,7 @@
     <t xml:space="preserve">13.0290775299072</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2502222061157</t>
+    <t xml:space="preserve">13.2502212524414</t>
   </si>
   <si>
     <t xml:space="preserve">13.4160804748535</t>
@@ -2681,7 +2681,7 @@
     <t xml:space="preserve">12.6420755386353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8816480636597</t>
+    <t xml:space="preserve">12.8816471099854</t>
   </si>
   <si>
     <t xml:space="preserve">12.9185056686401</t>
@@ -2690,7 +2690,7 @@
     <t xml:space="preserve">13.194935798645</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1580772399902</t>
+    <t xml:space="preserve">13.1580781936646</t>
   </si>
   <si>
     <t xml:space="preserve">12.8079328536987</t>
@@ -2705,7 +2705,7 @@
     <t xml:space="preserve">12.5499315261841</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0843629837036</t>
+    <t xml:space="preserve">13.0843639373779</t>
   </si>
   <si>
     <t xml:space="preserve">13.3423643112183</t>
@@ -2723,13 +2723,13 @@
     <t xml:space="preserve">13.1027917861938</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3607940673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2133646011353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5266513824463</t>
+    <t xml:space="preserve">13.3607931137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2133636474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5266523361206</t>
   </si>
   <si>
     <t xml:space="preserve">13.6003665924072</t>
@@ -2747,28 +2747,28 @@
     <t xml:space="preserve">13.7846536636353</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0610828399658</t>
+    <t xml:space="preserve">14.0610837936401</t>
   </si>
   <si>
     <t xml:space="preserve">14.2637987136841</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5402297973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6139440536499</t>
+    <t xml:space="preserve">14.540228843689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6139430999756</t>
   </si>
   <si>
     <t xml:space="preserve">15.3695201873779</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5353784561157</t>
+    <t xml:space="preserve">15.53537940979</t>
   </si>
   <si>
     <t xml:space="preserve">15.6275205612183</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5722360610962</t>
+    <t xml:space="preserve">15.5722341537476</t>
   </si>
   <si>
     <t xml:space="preserve">15.4063768386841</t>
@@ -2780,34 +2780,34 @@
     <t xml:space="preserve">15.295804977417</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2773761749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4616651535034</t>
+    <t xml:space="preserve">15.2773771286011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4616641998291</t>
   </si>
   <si>
     <t xml:space="preserve">15.6459493637085</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4432344436646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6643781661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7012376785278</t>
+    <t xml:space="preserve">15.4432353973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.664379119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7012367248535</t>
   </si>
   <si>
     <t xml:space="preserve">15.6090936660767</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3326606750488</t>
+    <t xml:space="preserve">15.3326616287231</t>
   </si>
   <si>
     <t xml:space="preserve">15.2036619186401</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1668033599854</t>
+    <t xml:space="preserve">15.1668043136597</t>
   </si>
   <si>
     <t xml:space="preserve">14.8535175323486</t>
@@ -2828,22 +2828,22 @@
     <t xml:space="preserve">15.8302373886108</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7196645736694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3879489898682</t>
+    <t xml:space="preserve">15.7196636199951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3879499435425</t>
   </si>
   <si>
     <t xml:space="preserve">15.5906648635864</t>
   </si>
   <si>
-    <t xml:space="preserve">15.682806968689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7565221786499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7380933761597</t>
+    <t xml:space="preserve">15.6828079223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7565231323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.738094329834</t>
   </si>
   <si>
     <t xml:space="preserve">15.1483764648438</t>
@@ -2855,7 +2855,7 @@
     <t xml:space="preserve">15.1299476623535</t>
   </si>
   <si>
-    <t xml:space="preserve">15.480092048645</t>
+    <t xml:space="preserve">15.4800910949707</t>
   </si>
   <si>
     <t xml:space="preserve">15.9223804473877</t>
@@ -2867,22 +2867,22 @@
     <t xml:space="preserve">16.0882377624512</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7749509811401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.867094039917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7109394073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6556529998779</t>
+    <t xml:space="preserve">15.7749519348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8670930862427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7109384536743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6556520462036</t>
   </si>
   <si>
     <t xml:space="preserve">13.6372241973877</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1347990036011</t>
+    <t xml:space="preserve">14.1347980499268</t>
   </si>
   <si>
     <t xml:space="preserve">14.4480857849121</t>
@@ -2894,7 +2894,7 @@
     <t xml:space="preserve">14.0242261886597</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0795125961304</t>
+    <t xml:space="preserve">14.0795116424561</t>
   </si>
   <si>
     <t xml:space="preserve">14.0057973861694</t>
@@ -2915,7 +2915,7 @@
     <t xml:space="preserve">13.4897947311401</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6187953948975</t>
+    <t xml:space="preserve">13.6187944412231</t>
   </si>
   <si>
     <t xml:space="preserve">12.8263626098633</t>
@@ -2927,7 +2927,7 @@
     <t xml:space="preserve">13.2686500549316</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9369335174561</t>
+    <t xml:space="preserve">12.9369344711304</t>
   </si>
   <si>
     <t xml:space="preserve">12.9000768661499</t>
@@ -2936,10 +2936,10 @@
     <t xml:space="preserve">12.9922199249268</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0475053787231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6973600387573</t>
+    <t xml:space="preserve">13.0475063323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6973609924316</t>
   </si>
   <si>
     <t xml:space="preserve">12.6052179336548</t>
@@ -2951,7 +2951,7 @@
     <t xml:space="preserve">12.4209308624268</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4762172698975</t>
+    <t xml:space="preserve">12.4762163162231</t>
   </si>
   <si>
     <t xml:space="preserve">12.6236457824707</t>
@@ -3510,6 +3510,9 @@
   </si>
   <si>
     <t xml:space="preserve">17.1599998474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0400009155273</t>
   </si>
 </sst>
 </file>
@@ -69238,7 +69241,7 @@
     </row>
     <row r="2516">
       <c r="A2516" s="1" t="n">
-        <v>45981.6910763889</v>
+        <v>45981.3333333333</v>
       </c>
       <c r="B2516" t="n">
         <v>24207</v>
@@ -69259,6 +69262,32 @@
         <v>1165</v>
       </c>
       <c r="H2516" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2517">
+      <c r="A2517" s="1" t="n">
+        <v>45982.6912152778</v>
+      </c>
+      <c r="B2517" t="n">
+        <v>26030</v>
+      </c>
+      <c r="C2517" t="n">
+        <v>17.0599994659424</v>
+      </c>
+      <c r="D2517" t="n">
+        <v>16.7399997711182</v>
+      </c>
+      <c r="E2517" t="n">
+        <v>17</v>
+      </c>
+      <c r="F2517" t="n">
+        <v>17.0400009155273</v>
+      </c>
+      <c r="G2517" t="s">
+        <v>1166</v>
+      </c>
+      <c r="H2517" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ORS.MI.xlsx
+++ b/data/ORS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1167" uniqueCount="1167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1168" uniqueCount="1168">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,124 +38,124 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08406352996826</t>
+    <t xml:space="preserve">8.08406257629395</t>
   </si>
   <si>
     <t xml:space="preserve">ORS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98275947570801</t>
+    <t xml:space="preserve">7.98275899887085</t>
   </si>
   <si>
     <t xml:space="preserve">8.06380176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94223690032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82472467422485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93818521499634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9017162322998</t>
+    <t xml:space="preserve">7.94223642349243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82472515106201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93818616867065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90171432495117</t>
   </si>
   <si>
     <t xml:space="preserve">8.03948974609375</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92602872848511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86119365692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82067203521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93413400650024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02328109741211</t>
+    <t xml:space="preserve">7.92603015899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86119318008423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82067346572876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93413257598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02328014373779</t>
   </si>
   <si>
     <t xml:space="preserve">8.08811473846436</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14484691619873</t>
+    <t xml:space="preserve">8.1448450088501</t>
   </si>
   <si>
     <t xml:space="preserve">7.69910764694214</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8044638633728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97465372085571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01112461090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01517677307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79230833053589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82877731323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34745407104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84093379974365</t>
+    <t xml:space="preserve">7.80446434020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97465467453003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0111255645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01517581939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79230785369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82877683639526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34745311737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84093332290649</t>
   </si>
   <si>
     <t xml:space="preserve">7.90982055664062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85714197158813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78015232086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8449854850769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97870683670044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88550710678101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95034217834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00302028656006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01922798156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91792440414429</t>
+    <t xml:space="preserve">7.85714149475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78015184402466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84498500823975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97870779037476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88550662994385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95034170150757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00301933288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0192289352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91792488098145</t>
   </si>
   <si>
     <t xml:space="preserve">8.1002721786499</t>
   </si>
   <si>
-    <t xml:space="preserve">8.104323387146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18536758422852</t>
+    <t xml:space="preserve">8.10432434082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1853666305542</t>
   </si>
   <si>
     <t xml:space="preserve">8.20157527923584</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11242866516113</t>
+    <t xml:space="preserve">8.11242961883545</t>
   </si>
   <si>
     <t xml:space="preserve">8.07595920562744</t>
@@ -167,22 +167,22 @@
     <t xml:space="preserve">8.09621906280518</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1772632598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05569839477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12053298950195</t>
+    <t xml:space="preserve">8.17726230621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05569744110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12053394317627</t>
   </si>
   <si>
     <t xml:space="preserve">8.2583065032959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42039203643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67162609100342</t>
+    <t xml:space="preserve">8.4203929901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67162799835205</t>
   </si>
   <si>
     <t xml:space="preserve">8.55816650390625</t>
@@ -191,22 +191,22 @@
     <t xml:space="preserve">8.42849636077881</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52429008483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45921897888184</t>
+    <t xml:space="preserve">8.52429103851318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45921993255615</t>
   </si>
   <si>
     <t xml:space="preserve">8.50802135467529</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60562801361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53242301940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61376094818115</t>
+    <t xml:space="preserve">8.60562896728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5324239730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61376190185547</t>
   </si>
   <si>
     <t xml:space="preserve">8.67070007324219</t>
@@ -215,16 +215,16 @@
     <t xml:space="preserve">8.87404632568359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79270839691162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90658283233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86591148376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94724941253662</t>
+    <t xml:space="preserve">8.7927074432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90658187866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86591243743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94725036621094</t>
   </si>
   <si>
     <t xml:space="preserve">8.93911743164062</t>
@@ -239,34 +239,34 @@
     <t xml:space="preserve">8.91471385955811</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92284965515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10992908477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07739353179932</t>
+    <t xml:space="preserve">8.92285060882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10992813110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.077392578125</t>
   </si>
   <si>
     <t xml:space="preserve">9.11806201934814</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1343297958374</t>
+    <t xml:space="preserve">9.13432884216309</t>
   </si>
   <si>
     <t xml:space="preserve">9.15059852600098</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15873050689697</t>
+    <t xml:space="preserve">9.15873146057129</t>
   </si>
   <si>
     <t xml:space="preserve">8.73576927185059</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6788330078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8577766418457</t>
+    <t xml:space="preserve">8.67883205413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85777759552002</t>
   </si>
   <si>
     <t xml:space="preserve">8.72763633728027</t>
@@ -275,13 +275,13 @@
     <t xml:space="preserve">8.70323467254639</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66256427764893</t>
+    <t xml:space="preserve">8.66256618499756</t>
   </si>
   <si>
     <t xml:space="preserve">8.69510173797607</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62189769744873</t>
+    <t xml:space="preserve">8.62189674377441</t>
   </si>
   <si>
     <t xml:space="preserve">8.80084133148193</t>
@@ -293,43 +293,43 @@
     <t xml:space="preserve">8.68696689605713</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54869079589844</t>
+    <t xml:space="preserve">8.54869174957275</t>
   </si>
   <si>
     <t xml:space="preserve">8.54055786132812</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58122730255127</t>
+    <t xml:space="preserve">8.58122825622559</t>
   </si>
   <si>
     <t xml:space="preserve">8.46735286712646</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51615715026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49988651275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45108509063721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63003063201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80897521972656</t>
+    <t xml:space="preserve">8.51615619659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49988842010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45108413696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63003158569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80897617340088</t>
   </si>
   <si>
     <t xml:space="preserve">8.89031314849854</t>
   </si>
   <si>
-    <t xml:space="preserve">8.930983543396</t>
+    <t xml:space="preserve">8.93098258972168</t>
   </si>
   <si>
     <t xml:space="preserve">8.9635181427002</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05299186706543</t>
+    <t xml:space="preserve">9.05299091339111</t>
   </si>
   <si>
     <t xml:space="preserve">9.30514144897461</t>
@@ -338,19 +338,19 @@
     <t xml:space="preserve">9.10179328918457</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1912670135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35394382476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47595310211182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54915714263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58982563018799</t>
+    <t xml:space="preserve">9.19126796722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35394287109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4759521484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54915618896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5898265838623</t>
   </si>
   <si>
     <t xml:space="preserve">9.66303062438965</t>
@@ -362,100 +362,100 @@
     <t xml:space="preserve">9.85824298858643</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0046529769897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2405347824097</t>
+    <t xml:space="preserve">10.0046520233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.240535736084</t>
   </si>
   <si>
     <t xml:space="preserve">10.2486686706543</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3381414413452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.598424911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4276151657104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4032125473022</t>
+    <t xml:space="preserve">10.3381423950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5984258651733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4276142120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4032115936279</t>
   </si>
   <si>
     <t xml:space="preserve">10.5252208709717</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4601488113403</t>
+    <t xml:space="preserve">10.4601497650146</t>
   </si>
   <si>
     <t xml:space="preserve">10.5658903121948</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5821571350098</t>
+    <t xml:space="preserve">10.5821580886841</t>
   </si>
   <si>
     <t xml:space="preserve">10.7773704528809</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9807167053223</t>
+    <t xml:space="preserve">10.9807176589966</t>
   </si>
   <si>
     <t xml:space="preserve">10.8749761581421</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6553630828857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6797637939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5740242004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5170860290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5414876937866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5577564239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5089521408081</t>
+    <t xml:space="preserve">10.6553640365601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6797647476196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5740251541138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5170869827271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5414896011353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5577573776245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5089540481567</t>
   </si>
   <si>
     <t xml:space="preserve">10.8180389404297</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6878967285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7611026763916</t>
+    <t xml:space="preserve">10.6878976821899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7611017227173</t>
   </si>
   <si>
     <t xml:space="preserve">10.6472282409668</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8993787765503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8831090927124</t>
+    <t xml:space="preserve">10.899377822876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8831100463867</t>
   </si>
   <si>
     <t xml:space="preserve">10.671630859375</t>
   </si>
   <si>
-    <t xml:space="preserve">10.736701965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0051183700562</t>
+    <t xml:space="preserve">10.7367010116577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0051202774048</t>
   </si>
   <si>
     <t xml:space="preserve">11.0213871002197</t>
   </si>
   <si>
-    <t xml:space="preserve">11.184063911438</t>
+    <t xml:space="preserve">11.1840629577637</t>
   </si>
   <si>
     <t xml:space="preserve">11.4036769866943</t>
@@ -464,13 +464,13 @@
     <t xml:space="preserve">11.3955430984497</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3386058807373</t>
+    <t xml:space="preserve">11.3386068344116</t>
   </si>
   <si>
     <t xml:space="preserve">11.3223390579224</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3304738998413</t>
+    <t xml:space="preserve">11.330472946167</t>
   </si>
   <si>
     <t xml:space="preserve">11.3630084991455</t>
@@ -479,61 +479,61 @@
     <t xml:space="preserve">11.0783233642578</t>
   </si>
   <si>
-    <t xml:space="preserve">10.606559753418</t>
+    <t xml:space="preserve">10.6065607070923</t>
   </si>
   <si>
     <t xml:space="preserve">10.8424415588379</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8505744934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6390943527222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4113464355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2079992294312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2730722427368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.232400894165</t>
+    <t xml:space="preserve">10.8505735397339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6390953063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4113473892212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2080001831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2730712890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2324018478394</t>
   </si>
   <si>
     <t xml:space="preserve">10.3218746185303</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3706769943237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3300075531006</t>
+    <t xml:space="preserve">10.370677947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3300085067749</t>
   </si>
   <si>
     <t xml:space="preserve">10.3056058883667</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2568025588989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1835966110229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4845504760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3625421524048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4438829421997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8587083816528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9237804412842</t>
+    <t xml:space="preserve">10.2568044662476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1835985183716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4845523834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3625431060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4438819885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8587093353271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9237794876099</t>
   </si>
   <si>
     <t xml:space="preserve">11.0376539230347</t>
@@ -542,34 +542,34 @@
     <t xml:space="preserve">11.0620555877686</t>
   </si>
   <si>
-    <t xml:space="preserve">11.102725982666</t>
+    <t xml:space="preserve">11.1027240753174</t>
   </si>
   <si>
     <t xml:space="preserve">11.1433935165405</t>
   </si>
   <si>
-    <t xml:space="preserve">11.175929069519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1352605819702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0701913833618</t>
+    <t xml:space="preserve">11.1759300231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1352596282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0701894760132</t>
   </si>
   <si>
     <t xml:space="preserve">11.118992805481</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1515283584595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2247333526611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0457887649536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5008201599121</t>
+    <t xml:space="preserve">11.1515274047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2247323989868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.045786857605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5008192062378</t>
   </si>
   <si>
     <t xml:space="preserve">10.1347951889038</t>
@@ -578,76 +578,76 @@
     <t xml:space="preserve">8.36161231994629</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01998901367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10946178436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39414882659912</t>
+    <t xml:space="preserve">8.01998996734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10946273803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39414691925049</t>
   </si>
   <si>
     <t xml:space="preserve">8.21520233154297</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33721160888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31280994415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18266773223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34534454345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23960399627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49175548553467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58936023712158</t>
+    <t xml:space="preserve">8.33720970153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31280899047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18266677856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34534549713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23960494995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49175453186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5893611907959</t>
   </si>
   <si>
     <t xml:space="preserve">8.76017189025879</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29654216766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25587368011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17453384399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19080066680908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23147201538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28027534484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14199733734131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15826606750488</t>
+    <t xml:space="preserve">8.29654121398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25587272644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17453479766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1908016204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23147106170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2802734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14199829101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1582670211792</t>
   </si>
   <si>
     <t xml:space="preserve">8.16639995574951</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12166213989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05252647399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89798307418823</t>
+    <t xml:space="preserve">8.12166309356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05252552032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89798164367676</t>
   </si>
   <si>
     <t xml:space="preserve">7.85731315612793</t>
@@ -656,130 +656,130 @@
     <t xml:space="preserve">7.93051719665527</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90611457824707</t>
+    <t xml:space="preserve">7.90611600875854</t>
   </si>
   <si>
     <t xml:space="preserve">7.93865156173706</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8491792678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80850839614868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62956571578979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57262849807739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48315477371216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66616725921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60516405105591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54009199142456</t>
+    <t xml:space="preserve">7.84917879104614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80850982666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62956476211548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5726261138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48315572738647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66616630554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60516357421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54009246826172</t>
   </si>
   <si>
     <t xml:space="preserve">7.52382373809814</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47908687591553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61329650878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54822540283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56449317932129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5075569152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46688652038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4912896156311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49942302703857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31234455108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27980709075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37741422653198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38554906845093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36928129196167</t>
+    <t xml:space="preserve">7.47908878326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6132960319519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54822492599487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56449365615845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50755596160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46688604354858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49128913879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4994215965271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31234502792358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27980852127075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3774151802063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38554859161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36928033828735</t>
   </si>
   <si>
     <t xml:space="preserve">7.32047748565674</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34487915039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28794240951538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04392623901367</t>
+    <t xml:space="preserve">7.34487867355347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28794193267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04392576217651</t>
   </si>
   <si>
     <t xml:space="preserve">7.15780067443848</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39368200302124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42621850967407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40181732177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3042106628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3611478805542</t>
+    <t xml:space="preserve">7.39368295669556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4262170791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40181541442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30420970916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36114740371704</t>
   </si>
   <si>
     <t xml:space="preserve">7.20660448074341</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3530125617981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.336745262146</t>
+    <t xml:space="preserve">7.35301303863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33674621582031</t>
   </si>
   <si>
     <t xml:space="preserve">7.27167463302612</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23100519180298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32861137390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26354169845581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23913908004761</t>
+    <t xml:space="preserve">7.23100566864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32861089706421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26354074478149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23913955688477</t>
   </si>
   <si>
     <t xml:space="preserve">7.22287130355835</t>
@@ -788,37 +788,37 @@
     <t xml:space="preserve">7.24727296829224</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44248580932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25540685653687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18220138549805</t>
+    <t xml:space="preserve">7.44248485565186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25540733337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18220281600952</t>
   </si>
   <si>
     <t xml:space="preserve">7.29607582092285</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16593360900879</t>
+    <t xml:space="preserve">7.16593456268311</t>
   </si>
   <si>
     <t xml:space="preserve">7.14153289794922</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05205965042114</t>
+    <t xml:space="preserve">7.0520601272583</t>
   </si>
   <si>
     <t xml:space="preserve">7.07646226882935</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0357928276062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01952457427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87311553955078</t>
+    <t xml:space="preserve">7.03579378128052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01952600479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87311410903931</t>
   </si>
   <si>
     <t xml:space="preserve">6.67790269851685</t>
@@ -827,43 +827,43 @@
     <t xml:space="preserve">6.85124731063843</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93379259109497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26397323608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14840984344482</t>
+    <t xml:space="preserve">6.93379163742065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26397371292114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14840936660767</t>
   </si>
   <si>
     <t xml:space="preserve">7.09888315200806</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18142938613892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16491889953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14015579223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21444702148438</t>
+    <t xml:space="preserve">7.18142890930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16491937637329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14015674591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21444606781006</t>
   </si>
   <si>
     <t xml:space="preserve">7.17317485809326</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97506523132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84299278259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60361242294312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62012147903442</t>
+    <t xml:space="preserve">6.97506427764893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84299325942993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60361194610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62012100219727</t>
   </si>
   <si>
     <t xml:space="preserve">6.67790222167969</t>
@@ -872,79 +872,79 @@
     <t xml:space="preserve">6.80997467041016</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54583072662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31470346450806</t>
+    <t xml:space="preserve">6.54582977294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31470441818237</t>
   </si>
   <si>
     <t xml:space="preserve">6.32295846939087</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34772253036499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38074064254761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39724922180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4715404510498</t>
+    <t xml:space="preserve">6.34772300720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38074016571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39724969863892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47153997421265</t>
   </si>
   <si>
     <t xml:space="preserve">6.2816858291626</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22390365600586</t>
+    <t xml:space="preserve">6.22390460968018</t>
   </si>
   <si>
     <t xml:space="preserve">6.09183216094971</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90197849273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9597601890564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9927773475647</t>
+    <t xml:space="preserve">5.90197801589966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95976066589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99277687072754</t>
   </si>
   <si>
     <t xml:space="preserve">6.20739507675171</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14135932922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19088649749756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14961338043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0753231048584</t>
+    <t xml:space="preserve">6.14135980606079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19088697433472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14961385726929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07532358169556</t>
   </si>
   <si>
     <t xml:space="preserve">6.25692272186279</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00928783416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98452281951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12485074996948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13310527801514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27343082427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44677591323853</t>
+    <t xml:space="preserve">6.00928735733032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9845232963562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12485122680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13310480117798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27343130111694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44677639007568</t>
   </si>
   <si>
     <t xml:space="preserve">6.55408477783203</t>
@@ -956,22 +956,22 @@
     <t xml:space="preserve">6.36423206329346</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24041366577148</t>
+    <t xml:space="preserve">6.24041414260864</t>
   </si>
   <si>
     <t xml:space="preserve">6.21565008163452</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23215913772583</t>
+    <t xml:space="preserve">6.23216009140015</t>
   </si>
   <si>
     <t xml:space="preserve">6.24866819381714</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11659669876099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1083402633667</t>
+    <t xml:space="preserve">6.11659622192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10834074020386</t>
   </si>
   <si>
     <t xml:space="preserve">6.05055952072144</t>
@@ -980,7 +980,7 @@
     <t xml:space="preserve">5.89372396469116</t>
   </si>
   <si>
-    <t xml:space="preserve">5.778160572052</t>
+    <t xml:space="preserve">5.77816104888916</t>
   </si>
   <si>
     <t xml:space="preserve">5.6956148147583</t>
@@ -989,124 +989,124 @@
     <t xml:space="preserve">5.79466915130615</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80292415618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82768821716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7864146232605</t>
+    <t xml:space="preserve">5.80292367935181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82768726348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78641510009766</t>
   </si>
   <si>
     <t xml:space="preserve">5.73688745498657</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85245132446289</t>
+    <t xml:space="preserve">5.85245084762573</t>
   </si>
   <si>
     <t xml:space="preserve">6.29819536209106</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1826319694519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15786838531494</t>
+    <t xml:space="preserve">6.18263244628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15786790847778</t>
   </si>
   <si>
     <t xml:space="preserve">6.03404998779297</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08357810974121</t>
+    <t xml:space="preserve">6.08357715606689</t>
   </si>
   <si>
     <t xml:space="preserve">5.81943321228027</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91848754882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86070585250854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76165199279785</t>
+    <t xml:space="preserve">5.91848659515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86070537567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76165151596069</t>
   </si>
   <si>
     <t xml:space="preserve">5.75339651107788</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81117868423462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70387029647827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74514198303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83594179153442</t>
+    <t xml:space="preserve">5.8111777305603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70386981964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74514245986938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83594274520874</t>
   </si>
   <si>
     <t xml:space="preserve">5.71212434768677</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84419775009155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94325065612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96801471710205</t>
+    <t xml:space="preserve">5.84419679641724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94325113296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96801424026489</t>
   </si>
   <si>
     <t xml:space="preserve">5.87721490859985</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88546991348267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93499660491943</t>
+    <t xml:space="preserve">5.88546943664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93499565124512</t>
   </si>
   <si>
     <t xml:space="preserve">6.02579593658447</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06706857681274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38899421691895</t>
+    <t xml:space="preserve">6.0670690536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38899517059326</t>
   </si>
   <si>
     <t xml:space="preserve">6.19914102554321</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04230499267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05881404876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9515061378479</t>
+    <t xml:space="preserve">6.04230451583862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05881452560425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95150566101074</t>
   </si>
   <si>
     <t xml:space="preserve">6.17437791824341</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17601871490479</t>
+    <t xml:space="preserve">6.1760196685791</t>
   </si>
   <si>
     <t xml:space="preserve">6.29349803924561</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25993204116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20958375930786</t>
+    <t xml:space="preserve">6.25993251800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20958423614502</t>
   </si>
   <si>
     <t xml:space="preserve">6.09210538864136</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10888957977295</t>
+    <t xml:space="preserve">6.10888862609863</t>
   </si>
   <si>
     <t xml:space="preserve">6.14245367050171</t>
@@ -1118,13 +1118,13 @@
     <t xml:space="preserve">6.02497529983521</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97462701797485</t>
+    <t xml:space="preserve">5.97462797164917</t>
   </si>
   <si>
     <t xml:space="preserve">5.95784473419189</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15923690795898</t>
+    <t xml:space="preserve">6.15923643112183</t>
   </si>
   <si>
     <t xml:space="preserve">6.12567138671875</t>
@@ -1133,37 +1133,37 @@
     <t xml:space="preserve">6.19280195236206</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42775869369507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7130651473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64593458175659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69628238677979</t>
+    <t xml:space="preserve">6.42775917053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71306467056274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64593410491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69628143310547</t>
   </si>
   <si>
     <t xml:space="preserve">6.78019571304321</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72984743118286</t>
+    <t xml:space="preserve">6.7298469543457</t>
   </si>
   <si>
     <t xml:space="preserve">6.62915086746216</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56202077865601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54523754119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67949867248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66271638870239</t>
+    <t xml:space="preserve">6.56201982498169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54523801803589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67949914932251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66271686553955</t>
   </si>
   <si>
     <t xml:space="preserve">6.57880353927612</t>
@@ -1172,91 +1172,91 @@
     <t xml:space="preserve">6.37741088867188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3438458442688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22636747360229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36062908172607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67253923416138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55505990982056</t>
+    <t xml:space="preserve">6.34384632110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22636795043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36062860488892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67253875732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55506038665771</t>
   </si>
   <si>
     <t xml:space="preserve">5.68932247161865</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62219190597534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53827810287476</t>
+    <t xml:space="preserve">5.62219142913818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5382776260376</t>
   </si>
   <si>
     <t xml:space="preserve">5.43758249282837</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45436573028564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60540819168091</t>
+    <t xml:space="preserve">5.45436525344849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60540866851807</t>
   </si>
   <si>
     <t xml:space="preserve">5.5214958190918</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50471353530884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48793029785156</t>
+    <t xml:space="preserve">5.50471305847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48792934417725</t>
   </si>
   <si>
     <t xml:space="preserve">5.35366868972778</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3704514503479</t>
+    <t xml:space="preserve">5.37045097351074</t>
   </si>
   <si>
     <t xml:space="preserve">5.42079973220825</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28653860092163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30332040786743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26975536346436</t>
+    <t xml:space="preserve">5.28653812408447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30332088470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26975584030151</t>
   </si>
   <si>
     <t xml:space="preserve">5.38723421096802</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32010316848755</t>
+    <t xml:space="preserve">5.32010364532471</t>
   </si>
   <si>
     <t xml:space="preserve">5.65575695037842</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75645303726196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70610523223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72288703918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.739670753479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6389741897583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57184410095215</t>
+    <t xml:space="preserve">5.75645351409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70610475540161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72288656234741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73967027664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63897466659546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57184362411499</t>
   </si>
   <si>
     <t xml:space="preserve">5.18584156036377</t>
@@ -1265,7 +1265,7 @@
     <t xml:space="preserve">5.2026252746582</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21940755844116</t>
+    <t xml:space="preserve">5.21940803527832</t>
   </si>
   <si>
     <t xml:space="preserve">5.16905975341797</t>
@@ -1274,28 +1274,28 @@
     <t xml:space="preserve">5.13549327850342</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1019287109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9508843421936</t>
+    <t xml:space="preserve">5.10192918777466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95088481903076</t>
   </si>
   <si>
     <t xml:space="preserve">5.03479862213135</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15227651596069</t>
+    <t xml:space="preserve">5.15227699279785</t>
   </si>
   <si>
     <t xml:space="preserve">5.11871147155762</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06836318969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0851469039917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23618984222412</t>
+    <t xml:space="preserve">5.06836366653442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08514547348022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23619031906128</t>
   </si>
   <si>
     <t xml:space="preserve">5.25297260284424</t>
@@ -1313,19 +1313,19 @@
     <t xml:space="preserve">5.58862638473511</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81662368774414</t>
+    <t xml:space="preserve">4.81662321090698</t>
   </si>
   <si>
     <t xml:space="preserve">4.79984140396118</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59844875335693</t>
+    <t xml:space="preserve">4.59844827651978</t>
   </si>
   <si>
     <t xml:space="preserve">4.36349201202393</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31314420700073</t>
+    <t xml:space="preserve">4.31314373016357</t>
   </si>
   <si>
     <t xml:space="preserve">4.19566535949707</t>
@@ -1334,34 +1334,34 @@
     <t xml:space="preserve">4.11175107955933</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02783823013306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17049026489258</t>
+    <t xml:space="preserve">4.02783870697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17049121856689</t>
   </si>
   <si>
     <t xml:space="preserve">4.06979560852051</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1201434135437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34670925140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17888212203979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04462099075317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15370798110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26279592514038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16210031509399</t>
+    <t xml:space="preserve">4.12014293670654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34670877456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17888164520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04462146759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15370845794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26279640197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16209983825684</t>
   </si>
   <si>
     <t xml:space="preserve">4.14531755447388</t>
@@ -1370,22 +1370,22 @@
     <t xml:space="preserve">3.9942729473114</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09496879577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98588156700134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27957820892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2292308807373</t>
+    <t xml:space="preserve">4.09496927261353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98588180541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2795786857605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22923040390015</t>
   </si>
   <si>
     <t xml:space="preserve">4.21244812011719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03623008728027</t>
+    <t xml:space="preserve">4.03622961044312</t>
   </si>
   <si>
     <t xml:space="preserve">4.12877893447876</t>
@@ -1394,22 +1394,22 @@
     <t xml:space="preserve">4.16283082962036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07770156860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00108480453491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20539522171021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37565469741821</t>
+    <t xml:space="preserve">4.07770204544067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00108432769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20539569854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37565422058105</t>
   </si>
   <si>
     <t xml:space="preserve">4.21390867233276</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22242116928101</t>
+    <t xml:space="preserve">4.22242164611816</t>
   </si>
   <si>
     <t xml:space="preserve">4.25647354125977</t>
@@ -1421,7 +1421,7 @@
     <t xml:space="preserve">4.32457685470581</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30755043029785</t>
+    <t xml:space="preserve">4.30755090713501</t>
   </si>
   <si>
     <t xml:space="preserve">4.23944759368896</t>
@@ -1430,16 +1430,16 @@
     <t xml:space="preserve">4.35862827301025</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5118613243103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53341484069824</t>
+    <t xml:space="preserve">4.51186180114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5334153175354</t>
   </si>
   <si>
     <t xml:space="preserve">5.94203662872314</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8909592628479</t>
+    <t xml:space="preserve">5.89095878601074</t>
   </si>
   <si>
     <t xml:space="preserve">5.73772573471069</t>
@@ -1451,7 +1451,7 @@
     <t xml:space="preserve">5.5844931602478</t>
   </si>
   <si>
-    <t xml:space="preserve">5.567467212677</t>
+    <t xml:space="preserve">5.56746673583984</t>
   </si>
   <si>
     <t xml:space="preserve">5.41423416137695</t>
@@ -1460,34 +1460,34 @@
     <t xml:space="preserve">5.26100063323975</t>
   </si>
   <si>
-    <t xml:space="preserve">5.482337474823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44828605651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6015191078186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66962242126465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51638984680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70367431640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32910490036011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27802658081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43126010894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31207847595215</t>
+    <t xml:space="preserve">5.48233795166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44828653335571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60151863098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66962289810181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51638889312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70367336273193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32910442352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27802705764771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4312596321106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31207895278931</t>
   </si>
   <si>
     <t xml:space="preserve">5.2269492149353</t>
@@ -1505,13 +1505,13 @@
     <t xml:space="preserve">5.05669021606445</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03966474533081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97156095504761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88643169403076</t>
+    <t xml:space="preserve">5.03966426849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97156143188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8864312171936</t>
   </si>
   <si>
     <t xml:space="preserve">5.02263879776001</t>
@@ -1532,37 +1532,37 @@
     <t xml:space="preserve">5.34613037109375</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2439751625061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36315679550171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38018274307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20992279052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15884590148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10776805877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98858690261841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09074258804321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19289779663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1758713722229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14181995391846</t>
+    <t xml:space="preserve">5.24397468566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36315631866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38018226623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2099232673645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1588454246521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10776853561401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98858642578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0907416343689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1928973197937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17587089538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14182043075562</t>
   </si>
   <si>
     <t xml:space="preserve">5.07371616363525</t>
@@ -1574,7 +1574,7 @@
     <t xml:space="preserve">4.54591369628906</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59699106216431</t>
+    <t xml:space="preserve">4.59699201583862</t>
   </si>
   <si>
     <t xml:space="preserve">4.57996559143066</t>
@@ -1586,7 +1586,7 @@
     <t xml:space="preserve">4.78427600860596</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76725006103516</t>
+    <t xml:space="preserve">4.76725053787231</t>
   </si>
   <si>
     <t xml:space="preserve">4.8183274269104</t>
@@ -1595,10 +1595,10 @@
     <t xml:space="preserve">4.80130195617676</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39720869064331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61854457855225</t>
+    <t xml:space="preserve">5.39720821380615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6185450553894</t>
   </si>
   <si>
     <t xml:space="preserve">5.46531200408936</t>
@@ -1607,22 +1607,22 @@
     <t xml:space="preserve">5.49936389923096</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63557004928589</t>
+    <t xml:space="preserve">5.63557100296021</t>
   </si>
   <si>
     <t xml:space="preserve">5.68664836883545</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65259695053101</t>
+    <t xml:space="preserve">5.65259647369385</t>
   </si>
   <si>
     <t xml:space="preserve">5.8569073677063</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87393379211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31660604476929</t>
+    <t xml:space="preserve">5.8739333152771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3166069984436</t>
   </si>
   <si>
     <t xml:space="preserve">6.33363246917725</t>
@@ -1634,25 +1634,25 @@
     <t xml:space="preserve">6.35065841674805</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43578767776489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5549693107605</t>
+    <t xml:space="preserve">6.43578720092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55496883392334</t>
   </si>
   <si>
     <t xml:space="preserve">6.69117641448975</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79333162307739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15087509155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08277082443237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87846040725708</t>
+    <t xml:space="preserve">6.79333114624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15087461471558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08277130126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87846088409424</t>
   </si>
   <si>
     <t xml:space="preserve">6.77630567550659</t>
@@ -1664,10 +1664,10 @@
     <t xml:space="preserve">6.70820236206055</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75927925109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53794288635254</t>
+    <t xml:space="preserve">6.75927972793579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5379433631897</t>
   </si>
   <si>
     <t xml:space="preserve">6.72522783279419</t>
@@ -1676,55 +1676,55 @@
     <t xml:space="preserve">6.65712451934814</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91251277923584</t>
+    <t xml:space="preserve">6.91251230239868</t>
   </si>
   <si>
     <t xml:space="preserve">6.8954873085022</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96359062194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17302227020264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05085277557373</t>
+    <t xml:space="preserve">6.9635910987854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17302179336548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05085372924805</t>
   </si>
   <si>
     <t xml:space="preserve">7.1206636428833</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57443189620972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9758415222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02819919586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0631046295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99329471588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01074695587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94093799591064</t>
+    <t xml:space="preserve">7.57443141937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97584247589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02820014953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06310558319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99329519271851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0107479095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94093656539917</t>
   </si>
   <si>
     <t xml:space="preserve">8.13291454315186</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15036678314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16782093048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18527317047119</t>
+    <t xml:space="preserve">8.15036869049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16781997680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18527412414551</t>
   </si>
   <si>
     <t xml:space="preserve">8.34234714508057</t>
@@ -1736,19 +1736,19 @@
     <t xml:space="preserve">8.25508308410645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08055782318115</t>
+    <t xml:space="preserve">8.08055686950684</t>
   </si>
   <si>
     <t xml:space="preserve">8.20272445678711</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95838928222656</t>
+    <t xml:space="preserve">7.95838832855225</t>
   </si>
   <si>
     <t xml:space="preserve">8.37725162506104</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32489395141602</t>
+    <t xml:space="preserve">8.3248929977417</t>
   </si>
   <si>
     <t xml:space="preserve">8.81356716156006</t>
@@ -1763,10 +1763,10 @@
     <t xml:space="preserve">8.69139957427979</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60413455963135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72630500793457</t>
+    <t xml:space="preserve">8.60413551330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72630405426025</t>
   </si>
   <si>
     <t xml:space="preserve">8.42960929870605</t>
@@ -1775,13 +1775,13 @@
     <t xml:space="preserve">8.28998851776123</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3074426651001</t>
+    <t xml:space="preserve">8.30744075775146</t>
   </si>
   <si>
     <t xml:space="preserve">8.04565238952637</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85367393493652</t>
+    <t xml:space="preserve">7.85367298126221</t>
   </si>
   <si>
     <t xml:space="preserve">8.41215705871582</t>
@@ -1790,19 +1790,19 @@
     <t xml:space="preserve">8.22017860412598</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44706344604492</t>
+    <t xml:space="preserve">8.44706249237061</t>
   </si>
   <si>
     <t xml:space="preserve">8.3597993850708</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09800910949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23762989044189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48196697235107</t>
+    <t xml:space="preserve">8.09801006317139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23763084411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48196792602539</t>
   </si>
   <si>
     <t xml:space="preserve">8.6215877532959</t>
@@ -1811,10 +1811,10 @@
     <t xml:space="preserve">8.55177783966064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65649223327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51687240600586</t>
+    <t xml:space="preserve">8.65649318695068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51687335968018</t>
   </si>
   <si>
     <t xml:space="preserve">8.46451473236084</t>
@@ -1823,10 +1823,10 @@
     <t xml:space="preserve">8.49942016601562</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56923007965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99161815643311</t>
+    <t xml:space="preserve">8.5692310333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99161720275879</t>
   </si>
   <si>
     <t xml:space="preserve">9.59893417358398</t>
@@ -1835,13 +1835,13 @@
     <t xml:space="preserve">9.77346038818359</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8170919418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29351425170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46803951263428</t>
+    <t xml:space="preserve">9.81709289550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29351234436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46804046630859</t>
   </si>
   <si>
     <t xml:space="preserve">9.55530261993408</t>
@@ -1850,37 +1850,37 @@
     <t xml:space="preserve">9.64256572723389</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9043550491333</t>
+    <t xml:space="preserve">9.90435600280762</t>
   </si>
   <si>
     <t xml:space="preserve">9.33714485168457</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94798564910889</t>
+    <t xml:space="preserve">9.9479866027832</t>
   </si>
   <si>
     <t xml:space="preserve">9.8607234954834</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5151968002319</t>
+    <t xml:space="preserve">10.5151958465576</t>
   </si>
   <si>
     <t xml:space="preserve">10.4279327392578</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5588283538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6024580001831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8206167221069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7333536148071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.776985168457</t>
+    <t xml:space="preserve">10.5588274002075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6024589538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8206176757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7333545684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7769861221313</t>
   </si>
   <si>
     <t xml:space="preserve">10.2970390319824</t>
@@ -1889,40 +1889,40 @@
     <t xml:space="preserve">10.3843011856079</t>
   </si>
   <si>
-    <t xml:space="preserve">10.340669631958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2097749710083</t>
+    <t xml:space="preserve">10.3406705856323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.209774017334</t>
   </si>
   <si>
     <t xml:space="preserve">10.2534074783325</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0788812637329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51167106628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72982883453369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68619823455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98809242248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42440795898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6496162414551</t>
+    <t xml:space="preserve">10.0788803100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51167011260986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72982788085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68619728088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98809432983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42440891265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6496171951294</t>
   </si>
   <si>
     <t xml:space="preserve">11.562352180481</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7805099487305</t>
+    <t xml:space="preserve">11.7805109024048</t>
   </si>
   <si>
     <t xml:space="preserve">11.9114036560059</t>
@@ -1931,7 +1931,7 @@
     <t xml:space="preserve">11.9550352096558</t>
   </si>
   <si>
-    <t xml:space="preserve">11.693247795105</t>
+    <t xml:space="preserve">11.6932468414307</t>
   </si>
   <si>
     <t xml:space="preserve">12.3040885925293</t>
@@ -1958,7 +1958,7 @@
     <t xml:space="preserve">10.9515113830566</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0422992706299</t>
+    <t xml:space="preserve">12.0422983169556</t>
   </si>
   <si>
     <t xml:space="preserve">11.3005638122559</t>
@@ -1979,7 +1979,7 @@
     <t xml:space="preserve">11.4314584732056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0387744903564</t>
+    <t xml:space="preserve">11.0387725830078</t>
   </si>
   <si>
     <t xml:space="preserve">11.9899406433105</t>
@@ -1988,31 +1988,31 @@
     <t xml:space="preserve">11.74560546875</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5361738204956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5187206268311</t>
+    <t xml:space="preserve">11.5361728668213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5187215805054</t>
   </si>
   <si>
     <t xml:space="preserve">11.6234369277954</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4489097595215</t>
+    <t xml:space="preserve">11.4489107131958</t>
   </si>
   <si>
     <t xml:space="preserve">11.6408891677856</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7281513214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9201316833496</t>
+    <t xml:space="preserve">11.7281522750854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9201307296753</t>
   </si>
   <si>
     <t xml:space="preserve">11.1173105239868</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0998592376709</t>
+    <t xml:space="preserve">11.0998582839966</t>
   </si>
   <si>
     <t xml:space="preserve">10.8031644821167</t>
@@ -2027,13 +2027,13 @@
     <t xml:space="preserve">10.1050596237183</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81839275360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69297313690186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7108907699585</t>
+    <t xml:space="preserve">9.81839179992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69297409057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71089172363281</t>
   </si>
   <si>
     <t xml:space="preserve">10.1408929824829</t>
@@ -2048,16 +2048,16 @@
     <t xml:space="preserve">10.1229763031006</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1588096618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0692262649536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0871429443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4633960723877</t>
+    <t xml:space="preserve">10.1588106155396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0692253112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0871438980103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4633951187134</t>
   </si>
   <si>
     <t xml:space="preserve">10.7858972549438</t>
@@ -2084,13 +2084,13 @@
     <t xml:space="preserve">10.5888118743896</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5171451568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8575649261475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9113149642944</t>
+    <t xml:space="preserve">10.5171461105347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8575639724731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9113159179688</t>
   </si>
   <si>
     <t xml:space="preserve">10.6067295074463</t>
@@ -2099,13 +2099,13 @@
     <t xml:space="preserve">10.6604795455933</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3021450042725</t>
+    <t xml:space="preserve">10.3021440505981</t>
   </si>
   <si>
     <t xml:space="preserve">10.4096450805664</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3558950424194</t>
+    <t xml:space="preserve">10.3558940887451</t>
   </si>
   <si>
     <t xml:space="preserve">10.6783971786499</t>
@@ -2117,16 +2117,16 @@
     <t xml:space="preserve">10.535062789917</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1800661087036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9829816818237</t>
+    <t xml:space="preserve">11.1800651550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9829807281494</t>
   </si>
   <si>
     <t xml:space="preserve">11.4846515655518</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3771505355835</t>
+    <t xml:space="preserve">11.3771514892578</t>
   </si>
   <si>
     <t xml:space="preserve">11.7354869842529</t>
@@ -2147,7 +2147,7 @@
     <t xml:space="preserve">12.2371559143066</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3267393112183</t>
+    <t xml:space="preserve">12.3267402648926</t>
   </si>
   <si>
     <t xml:space="preserve">12.4521570205688</t>
@@ -2156,7 +2156,7 @@
     <t xml:space="preserve">12.0938215255737</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3984069824219</t>
+    <t xml:space="preserve">12.3984079360962</t>
   </si>
   <si>
     <t xml:space="preserve">12.201322555542</t>
@@ -2171,10 +2171,10 @@
     <t xml:space="preserve">12.6134080886841</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8463268280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.810492515564</t>
+    <t xml:space="preserve">12.8463258743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8104934692383</t>
   </si>
   <si>
     <t xml:space="preserve">12.9179935455322</t>
@@ -2183,37 +2183,37 @@
     <t xml:space="preserve">13.258412361145</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4017467498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4375791549683</t>
+    <t xml:space="preserve">13.4017457962036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4375801086426</t>
   </si>
   <si>
     <t xml:space="preserve">13.6884145736694</t>
   </si>
   <si>
-    <t xml:space="preserve">13.903416633606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6559209823608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2438335418701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6380033493042</t>
+    <t xml:space="preserve">13.9034156799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6559200286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2438344955444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6380043029785</t>
   </si>
   <si>
     <t xml:space="preserve">14.92467212677</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5125865936279</t>
+    <t xml:space="preserve">14.5125875473022</t>
   </si>
   <si>
     <t xml:space="preserve">14.5663366317749</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7992544174194</t>
+    <t xml:space="preserve">14.7992553710938</t>
   </si>
   <si>
     <t xml:space="preserve">14.5484189987183</t>
@@ -2225,10 +2225,10 @@
     <t xml:space="preserve">14.2617511749268</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8888387680054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8171710968018</t>
+    <t xml:space="preserve">14.8888397216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8171730041504</t>
   </si>
   <si>
     <t xml:space="preserve">14.387167930603</t>
@@ -2237,7 +2237,7 @@
     <t xml:space="preserve">14.7634201049805</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6200866699219</t>
+    <t xml:space="preserve">14.6200857162476</t>
   </si>
   <si>
     <t xml:space="preserve">14.9067535400391</t>
@@ -2246,7 +2246,7 @@
     <t xml:space="preserve">15.1217546463013</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0321741104126</t>
+    <t xml:space="preserve">15.032172203064</t>
   </si>
   <si>
     <t xml:space="preserve">14.7455034255981</t>
@@ -2255,7 +2255,7 @@
     <t xml:space="preserve">15.0500888824463</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0680065155029</t>
+    <t xml:space="preserve">15.0680055618286</t>
   </si>
   <si>
     <t xml:space="preserve">15.1038398742676</t>
@@ -2264,34 +2264,34 @@
     <t xml:space="preserve">14.5305023193359</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7096710205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2080011367798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6167469024658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5092468261719</t>
+    <t xml:space="preserve">14.7096700668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2080001831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6167478561401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5092458724976</t>
   </si>
   <si>
     <t xml:space="preserve">13.0434112548828</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1688280105591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9717426300049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4700746536255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2404956817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6525802612305</t>
+    <t xml:space="preserve">13.1688270568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9717435836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4700736999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2404947280884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6525812149048</t>
   </si>
   <si>
     <t xml:space="preserve">13.5809135437012</t>
@@ -2303,19 +2303,19 @@
     <t xml:space="preserve">13.4913301467896</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2225780487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2046604156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0613269805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0075778961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6313247680664</t>
+    <t xml:space="preserve">13.2225790023804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2046613693237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0613279342651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0075769424438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6313257217407</t>
   </si>
   <si>
     <t xml:space="preserve">13.0971612930298</t>
@@ -2342,7 +2342,7 @@
     <t xml:space="preserve">13.1150779724121</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1509113311768</t>
+    <t xml:space="preserve">13.1509122848511</t>
   </si>
   <si>
     <t xml:space="preserve">13.5271635055542</t>
@@ -2351,13 +2351,13 @@
     <t xml:space="preserve">13.3479957580566</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2763290405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7925748825073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5954923629761</t>
+    <t xml:space="preserve">13.276328086853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7925758361816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5954914093018</t>
   </si>
   <si>
     <t xml:space="preserve">12.5238246917725</t>
@@ -2369,16 +2369,16 @@
     <t xml:space="preserve">12.4879903793335</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3088226318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5417413711548</t>
+    <t xml:space="preserve">12.3088216781616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5417404174805</t>
   </si>
   <si>
     <t xml:space="preserve">12.8284091949463</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3804903030396</t>
+    <t xml:space="preserve">12.3804893493652</t>
   </si>
   <si>
     <t xml:space="preserve">12.6671581268311</t>
@@ -2396,22 +2396,22 @@
     <t xml:space="preserve">12.4342403411865</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9504871368408</t>
+    <t xml:space="preserve">11.9504880905151</t>
   </si>
   <si>
     <t xml:space="preserve">12.2192392349243</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8250694274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1117382049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9684047698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0400714874268</t>
+    <t xml:space="preserve">11.8250703811646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1117391586304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9684038162231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0400705337524</t>
   </si>
   <si>
     <t xml:space="preserve">12.0042381286621</t>
@@ -2420,10 +2420,10 @@
     <t xml:space="preserve">12.255072593689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7388248443604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7421655654907</t>
+    <t xml:space="preserve">12.7388257980347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7421646118164</t>
   </si>
   <si>
     <t xml:space="preserve">13.7063312530518</t>
@@ -2432,7 +2432,7 @@
     <t xml:space="preserve">14.0825834274292</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0109157562256</t>
+    <t xml:space="preserve">14.0109176635742</t>
   </si>
   <si>
     <t xml:space="preserve">13.7242479324341</t>
@@ -2441,10 +2441,10 @@
     <t xml:space="preserve">14.0467500686646</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0646657943726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9392490386963</t>
+    <t xml:space="preserve">14.0646667480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9392499923706</t>
   </si>
   <si>
     <t xml:space="preserve">13.6346645355225</t>
@@ -2471,55 +2471,55 @@
     <t xml:space="preserve">13.4734134674072</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1867446899414</t>
+    <t xml:space="preserve">13.1867456436157</t>
   </si>
   <si>
     <t xml:space="preserve">13.3838291168213</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5988302230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.70299243927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8429870605469</t>
+    <t xml:space="preserve">13.5988311767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7029914855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8429861068726</t>
   </si>
   <si>
     <t xml:space="preserve">11.7892360687256</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6817359924316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0759048461914</t>
+    <t xml:space="preserve">11.6817350387573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0759038925171</t>
   </si>
   <si>
     <t xml:space="preserve">11.5742359161377</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2159004211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3592338562012</t>
+    <t xml:space="preserve">11.2158994674683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3592348098755</t>
   </si>
   <si>
     <t xml:space="preserve">11.4309015274048</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3054828643799</t>
+    <t xml:space="preserve">11.3054838180542</t>
   </si>
   <si>
     <t xml:space="preserve">11.2875671386719</t>
   </si>
   <si>
-    <t xml:space="preserve">11.683783531189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5179262161255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2783517837524</t>
+    <t xml:space="preserve">11.6837844848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5179252624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2783527374268</t>
   </si>
   <si>
     <t xml:space="preserve">11.1493520736694</t>
@@ -2531,7 +2531,7 @@
     <t xml:space="preserve">11.0756378173828</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9970722198486</t>
+    <t xml:space="preserve">11.9970712661743</t>
   </si>
   <si>
     <t xml:space="preserve">12.052357673645</t>
@@ -2540,7 +2540,7 @@
     <t xml:space="preserve">12.2735013961792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2182149887085</t>
+    <t xml:space="preserve">12.2182159423828</t>
   </si>
   <si>
     <t xml:space="preserve">12.4025020599365</t>
@@ -2552,7 +2552,7 @@
     <t xml:space="preserve">12.0707864761353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1629285812378</t>
+    <t xml:space="preserve">12.1629295349121</t>
   </si>
   <si>
     <t xml:space="preserve">12.1260719299316</t>
@@ -2567,13 +2567,13 @@
     <t xml:space="preserve">11.7759265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8312129974365</t>
+    <t xml:space="preserve">11.8312139511108</t>
   </si>
   <si>
     <t xml:space="preserve">11.9786424636841</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7206411361694</t>
+    <t xml:space="preserve">11.7206420898438</t>
   </si>
   <si>
     <t xml:space="preserve">11.868070602417</t>
@@ -2588,7 +2588,7 @@
     <t xml:space="preserve">11.4442110061646</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3520669937134</t>
+    <t xml:space="preserve">11.3520679473877</t>
   </si>
   <si>
     <t xml:space="preserve">11.3704957962036</t>
@@ -2606,7 +2606,7 @@
     <t xml:space="preserve">11.7022123336792</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5732116699219</t>
+    <t xml:space="preserve">11.5732126235962</t>
   </si>
   <si>
     <t xml:space="preserve">11.481068611145</t>
@@ -2615,7 +2615,7 @@
     <t xml:space="preserve">11.296781539917</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3152093887329</t>
+    <t xml:space="preserve">11.3152103424072</t>
   </si>
   <si>
     <t xml:space="preserve">11.5547828674316</t>
@@ -2624,7 +2624,7 @@
     <t xml:space="preserve">11.4257822036743</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3336381912231</t>
+    <t xml:space="preserve">11.3336391448975</t>
   </si>
   <si>
     <t xml:space="preserve">11.3889245986938</t>
@@ -2633,7 +2633,7 @@
     <t xml:space="preserve">11.4626398086548</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7943553924561</t>
+    <t xml:space="preserve">11.7943563461304</t>
   </si>
   <si>
     <t xml:space="preserve">12.1076431274414</t>
@@ -2663,7 +2663,7 @@
     <t xml:space="preserve">13.0290775299072</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2502222061157</t>
+    <t xml:space="preserve">13.2502212524414</t>
   </si>
   <si>
     <t xml:space="preserve">13.4160804748535</t>
@@ -2678,7 +2678,7 @@
     <t xml:space="preserve">12.6420755386353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8816480636597</t>
+    <t xml:space="preserve">12.8816471099854</t>
   </si>
   <si>
     <t xml:space="preserve">12.9185056686401</t>
@@ -2687,7 +2687,7 @@
     <t xml:space="preserve">13.194935798645</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1580772399902</t>
+    <t xml:space="preserve">13.1580781936646</t>
   </si>
   <si>
     <t xml:space="preserve">12.8079328536987</t>
@@ -2702,7 +2702,7 @@
     <t xml:space="preserve">12.5499315261841</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0843629837036</t>
+    <t xml:space="preserve">13.0843639373779</t>
   </si>
   <si>
     <t xml:space="preserve">13.3423643112183</t>
@@ -2720,13 +2720,13 @@
     <t xml:space="preserve">13.1027917861938</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3607940673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2133646011353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5266513824463</t>
+    <t xml:space="preserve">13.3607931137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2133636474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5266523361206</t>
   </si>
   <si>
     <t xml:space="preserve">13.6003665924072</t>
@@ -2744,28 +2744,28 @@
     <t xml:space="preserve">13.7846536636353</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0610828399658</t>
+    <t xml:space="preserve">14.0610837936401</t>
   </si>
   <si>
     <t xml:space="preserve">14.2637987136841</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5402297973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6139440536499</t>
+    <t xml:space="preserve">14.540228843689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6139430999756</t>
   </si>
   <si>
     <t xml:space="preserve">15.3695201873779</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5353784561157</t>
+    <t xml:space="preserve">15.53537940979</t>
   </si>
   <si>
     <t xml:space="preserve">15.6275205612183</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5722360610962</t>
+    <t xml:space="preserve">15.5722341537476</t>
   </si>
   <si>
     <t xml:space="preserve">15.4063768386841</t>
@@ -2777,34 +2777,34 @@
     <t xml:space="preserve">15.295804977417</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2773761749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4616651535034</t>
+    <t xml:space="preserve">15.2773771286011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4616641998291</t>
   </si>
   <si>
     <t xml:space="preserve">15.6459493637085</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4432344436646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6643781661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7012376785278</t>
+    <t xml:space="preserve">15.4432353973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.664379119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7012367248535</t>
   </si>
   <si>
     <t xml:space="preserve">15.6090936660767</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3326606750488</t>
+    <t xml:space="preserve">15.3326616287231</t>
   </si>
   <si>
     <t xml:space="preserve">15.2036619186401</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1668033599854</t>
+    <t xml:space="preserve">15.1668043136597</t>
   </si>
   <si>
     <t xml:space="preserve">14.8535175323486</t>
@@ -2825,22 +2825,22 @@
     <t xml:space="preserve">15.8302373886108</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7196645736694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3879489898682</t>
+    <t xml:space="preserve">15.7196636199951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3879499435425</t>
   </si>
   <si>
     <t xml:space="preserve">15.5906648635864</t>
   </si>
   <si>
-    <t xml:space="preserve">15.682806968689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7565221786499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7380933761597</t>
+    <t xml:space="preserve">15.6828079223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7565231323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.738094329834</t>
   </si>
   <si>
     <t xml:space="preserve">15.1483764648438</t>
@@ -2852,7 +2852,7 @@
     <t xml:space="preserve">15.1299476623535</t>
   </si>
   <si>
-    <t xml:space="preserve">15.480092048645</t>
+    <t xml:space="preserve">15.4800910949707</t>
   </si>
   <si>
     <t xml:space="preserve">15.9223804473877</t>
@@ -2864,22 +2864,22 @@
     <t xml:space="preserve">16.0882377624512</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7749509811401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.867094039917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7109394073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6556529998779</t>
+    <t xml:space="preserve">15.7749519348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8670930862427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7109384536743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6556520462036</t>
   </si>
   <si>
     <t xml:space="preserve">13.6372241973877</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1347990036011</t>
+    <t xml:space="preserve">14.1347980499268</t>
   </si>
   <si>
     <t xml:space="preserve">14.4480857849121</t>
@@ -2891,7 +2891,7 @@
     <t xml:space="preserve">14.0242261886597</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0795125961304</t>
+    <t xml:space="preserve">14.0795116424561</t>
   </si>
   <si>
     <t xml:space="preserve">14.0057973861694</t>
@@ -2912,7 +2912,7 @@
     <t xml:space="preserve">13.4897947311401</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6187953948975</t>
+    <t xml:space="preserve">13.6187944412231</t>
   </si>
   <si>
     <t xml:space="preserve">12.8263626098633</t>
@@ -2924,7 +2924,7 @@
     <t xml:space="preserve">13.2686500549316</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9369335174561</t>
+    <t xml:space="preserve">12.9369344711304</t>
   </si>
   <si>
     <t xml:space="preserve">12.9000768661499</t>
@@ -2933,10 +2933,10 @@
     <t xml:space="preserve">12.9922199249268</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0475053787231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6973600387573</t>
+    <t xml:space="preserve">13.0475063323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6973609924316</t>
   </si>
   <si>
     <t xml:space="preserve">12.6052179336548</t>
@@ -2948,7 +2948,7 @@
     <t xml:space="preserve">12.4209308624268</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4762172698975</t>
+    <t xml:space="preserve">12.4762163162231</t>
   </si>
   <si>
     <t xml:space="preserve">12.6236457824707</t>
@@ -3513,6 +3513,9 @@
   </si>
   <si>
     <t xml:space="preserve">17.1000003814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2800006866455</t>
   </si>
 </sst>
 </file>
@@ -69293,7 +69296,7 @@
     </row>
     <row r="2518">
       <c r="A2518" s="1" t="n">
-        <v>45985.6911226852</v>
+        <v>45985.3333333333</v>
       </c>
       <c r="B2518" t="n">
         <v>28119</v>
@@ -69314,6 +69317,32 @@
         <v>1166</v>
       </c>
       <c r="H2518" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2519">
+      <c r="A2519" s="1" t="n">
+        <v>45986.6913078704</v>
+      </c>
+      <c r="B2519" t="n">
+        <v>25559</v>
+      </c>
+      <c r="C2519" t="n">
+        <v>17.2800006866455</v>
+      </c>
+      <c r="D2519" t="n">
+        <v>17</v>
+      </c>
+      <c r="E2519" t="n">
+        <v>17.2600002288818</v>
+      </c>
+      <c r="F2519" t="n">
+        <v>17.2800006866455</v>
+      </c>
+      <c r="G2519" t="s">
+        <v>1167</v>
+      </c>
+      <c r="H2519" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ORS.MI.xlsx
+++ b/data/ORS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1168" uniqueCount="1168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1169" uniqueCount="1169">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08406257629395</t>
+    <t xml:space="preserve">8.08406352996826</t>
   </si>
   <si>
     <t xml:space="preserve">ORS.MI</t>
@@ -47,43 +47,43 @@
     <t xml:space="preserve">7.98275899887085</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06380176544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94223642349243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82472515106201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93818616867065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90171432495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03948974609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92603015899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86119318008423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82067346572876</t>
+    <t xml:space="preserve">8.06380271911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94223690032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82472467422485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93818521499634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90171527862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03948879241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92602968215942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86119508743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8206729888916</t>
   </si>
   <si>
     <t xml:space="preserve">7.93413257598877</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02328014373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08811473846436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1448450088501</t>
+    <t xml:space="preserve">8.02328109741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08811569213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14484596252441</t>
   </si>
   <si>
     <t xml:space="preserve">7.69910764694214</t>
@@ -92,19 +92,19 @@
     <t xml:space="preserve">7.80446434020996</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97465467453003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0111255645752</t>
+    <t xml:space="preserve">7.97465562820435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01112461090088</t>
   </si>
   <si>
     <t xml:space="preserve">8.01517581939697</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79230785369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82877683639526</t>
+    <t xml:space="preserve">7.79230833053589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82877826690674</t>
   </si>
   <si>
     <t xml:space="preserve">8.34745311737061</t>
@@ -113,40 +113,40 @@
     <t xml:space="preserve">7.84093332290649</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90982055664062</t>
+    <t xml:space="preserve">7.90982103347778</t>
   </si>
   <si>
     <t xml:space="preserve">7.85714149475098</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78015184402466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84498500823975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97870779037476</t>
+    <t xml:space="preserve">7.78015232086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84498596191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97870635986328</t>
   </si>
   <si>
     <t xml:space="preserve">7.88550662994385</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95034170150757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00301933288574</t>
+    <t xml:space="preserve">7.95034217834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00302028656006</t>
   </si>
   <si>
     <t xml:space="preserve">8.0192289352417</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91792488098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1002721786499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10432434082031</t>
+    <t xml:space="preserve">7.91792440414429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10027313232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.104323387146</t>
   </si>
   <si>
     <t xml:space="preserve">8.1853666305542</t>
@@ -161,10 +161,10 @@
     <t xml:space="preserve">8.07595920562744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03138637542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09621906280518</t>
+    <t xml:space="preserve">8.03138446807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09622097015381</t>
   </si>
   <si>
     <t xml:space="preserve">8.17726230621338</t>
@@ -173,43 +173,43 @@
     <t xml:space="preserve">8.05569744110107</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12053394317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2583065032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4203929901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67162799835205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55816650390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42849636077881</t>
+    <t xml:space="preserve">8.12053298950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25830745697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42039203643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67162609100342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55816555023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42849731445312</t>
   </si>
   <si>
     <t xml:space="preserve">8.52429103851318</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45921993255615</t>
+    <t xml:space="preserve">8.45921802520752</t>
   </si>
   <si>
     <t xml:space="preserve">8.50802135467529</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60562896728516</t>
+    <t xml:space="preserve">8.60562801361084</t>
   </si>
   <si>
     <t xml:space="preserve">8.5324239730835</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61376190185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67070007324219</t>
+    <t xml:space="preserve">8.61376094818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67069911956787</t>
   </si>
   <si>
     <t xml:space="preserve">8.87404632568359</t>
@@ -218,7 +218,7 @@
     <t xml:space="preserve">8.7927074432373</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90658187866211</t>
+    <t xml:space="preserve">8.90657997131348</t>
   </si>
   <si>
     <t xml:space="preserve">8.86591243743896</t>
@@ -227,10 +227,10 @@
     <t xml:space="preserve">8.94725036621094</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93911743164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78457260131836</t>
+    <t xml:space="preserve">8.93911552429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78457355499268</t>
   </si>
   <si>
     <t xml:space="preserve">8.74390411376953</t>
@@ -239,13 +239,13 @@
     <t xml:space="preserve">8.91471385955811</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92285060882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10992813110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.077392578125</t>
+    <t xml:space="preserve">8.92284870147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10992908477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07739162445068</t>
   </si>
   <si>
     <t xml:space="preserve">9.11806201934814</t>
@@ -254,13 +254,13 @@
     <t xml:space="preserve">9.13432884216309</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15059852600098</t>
+    <t xml:space="preserve">9.15059757232666</t>
   </si>
   <si>
     <t xml:space="preserve">9.15873146057129</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73576927185059</t>
+    <t xml:space="preserve">8.7357702255249</t>
   </si>
   <si>
     <t xml:space="preserve">8.67883205413818</t>
@@ -272,13 +272,13 @@
     <t xml:space="preserve">8.72763633728027</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70323467254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66256618499756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69510173797607</t>
+    <t xml:space="preserve">8.7032356262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66256713867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69510078430176</t>
   </si>
   <si>
     <t xml:space="preserve">8.62189674377441</t>
@@ -287,19 +287,19 @@
     <t xml:space="preserve">8.80084133148193</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77643966674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68696689605713</t>
+    <t xml:space="preserve">8.77643871307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68696784973145</t>
   </si>
   <si>
     <t xml:space="preserve">8.54869174957275</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54055786132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58122825622559</t>
+    <t xml:space="preserve">8.54055595397949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58122730255127</t>
   </si>
   <si>
     <t xml:space="preserve">8.46735286712646</t>
@@ -308,13 +308,13 @@
     <t xml:space="preserve">8.51615619659424</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49988842010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45108413696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63003158569336</t>
+    <t xml:space="preserve">8.49988746643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45108318328857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63003063201904</t>
   </si>
   <si>
     <t xml:space="preserve">8.80897617340088</t>
@@ -323,34 +323,34 @@
     <t xml:space="preserve">8.89031314849854</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93098258972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9635181427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05299091339111</t>
+    <t xml:space="preserve">8.930983543396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96351718902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0529899597168</t>
   </si>
   <si>
     <t xml:space="preserve">9.30514144897461</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10179328918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19126796722412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35394287109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4759521484375</t>
+    <t xml:space="preserve">9.10179424285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1912670135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35394382476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47595119476318</t>
   </si>
   <si>
     <t xml:space="preserve">9.54915618896484</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5898265838623</t>
+    <t xml:space="preserve">9.58982467651367</t>
   </si>
   <si>
     <t xml:space="preserve">9.66303062438965</t>
@@ -362,43 +362,43 @@
     <t xml:space="preserve">9.85824298858643</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0046520233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.240535736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2486686706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3381423950195</t>
+    <t xml:space="preserve">10.0046539306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2405347824097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2486696243286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3381414413452</t>
   </si>
   <si>
     <t xml:space="preserve">10.5984258651733</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4276142120361</t>
+    <t xml:space="preserve">10.4276151657104</t>
   </si>
   <si>
     <t xml:space="preserve">10.4032115936279</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5252208709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4601497650146</t>
+    <t xml:space="preserve">10.525218963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4601488113403</t>
   </si>
   <si>
     <t xml:space="preserve">10.5658903121948</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5821580886841</t>
+    <t xml:space="preserve">10.5821571350098</t>
   </si>
   <si>
     <t xml:space="preserve">10.7773704528809</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9807176589966</t>
+    <t xml:space="preserve">10.9807167053223</t>
   </si>
   <si>
     <t xml:space="preserve">10.8749761581421</t>
@@ -407,64 +407,64 @@
     <t xml:space="preserve">10.6553640365601</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6797647476196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5740251541138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5170869827271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5414896011353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5577573776245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5089540481567</t>
+    <t xml:space="preserve">10.6797637939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5740242004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5170879364014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5414886474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5577564239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5089521408081</t>
   </si>
   <si>
     <t xml:space="preserve">10.8180389404297</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6878976821899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7611017227173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6472282409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.899377822876</t>
+    <t xml:space="preserve">10.6878967285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7611026763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6472291946411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8993787765503</t>
   </si>
   <si>
     <t xml:space="preserve">10.8831100463867</t>
   </si>
   <si>
-    <t xml:space="preserve">10.671630859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7367010116577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0051202774048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0213871002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1840629577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4036769866943</t>
+    <t xml:space="preserve">10.6716289520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7367029190063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0051193237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0213861465454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.184063911438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4036779403687</t>
   </si>
   <si>
     <t xml:space="preserve">11.3955430984497</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3386068344116</t>
+    <t xml:space="preserve">11.3386058807373</t>
   </si>
   <si>
     <t xml:space="preserve">11.3223390579224</t>
@@ -473,13 +473,13 @@
     <t xml:space="preserve">11.330472946167</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3630084991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0783233642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6065607070923</t>
+    <t xml:space="preserve">11.3630075454712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0783243179321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6065587997437</t>
   </si>
   <si>
     <t xml:space="preserve">10.8424415588379</t>
@@ -488,10 +488,10 @@
     <t xml:space="preserve">10.8505735397339</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6390953063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4113473892212</t>
+    <t xml:space="preserve">10.6390943527222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4113464355469</t>
   </si>
   <si>
     <t xml:space="preserve">10.2080001831055</t>
@@ -500,25 +500,25 @@
     <t xml:space="preserve">10.2730712890625</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2324018478394</t>
+    <t xml:space="preserve">10.232400894165</t>
   </si>
   <si>
     <t xml:space="preserve">10.3218746185303</t>
   </si>
   <si>
-    <t xml:space="preserve">10.370677947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3300085067749</t>
+    <t xml:space="preserve">10.3706760406494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3300075531006</t>
   </si>
   <si>
     <t xml:space="preserve">10.3056058883667</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2568044662476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1835985183716</t>
+    <t xml:space="preserve">10.2568035125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1835975646973</t>
   </si>
   <si>
     <t xml:space="preserve">10.4845523834229</t>
@@ -527,49 +527,49 @@
     <t xml:space="preserve">10.3625431060791</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4438819885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8587093353271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9237794876099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0376539230347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0620555877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1027240753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1433935165405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1759300231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1352596282959</t>
+    <t xml:space="preserve">10.4438810348511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8587074279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9237804412842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0376529693604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0620565414429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.102725982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1433944702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.175929069519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1352615356445</t>
   </si>
   <si>
     <t xml:space="preserve">11.0701894760132</t>
   </si>
   <si>
-    <t xml:space="preserve">11.118992805481</t>
+    <t xml:space="preserve">11.1189937591553</t>
   </si>
   <si>
     <t xml:space="preserve">11.1515274047852</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2247323989868</t>
+    <t xml:space="preserve">11.2247333526611</t>
   </si>
   <si>
     <t xml:space="preserve">11.045786857605</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5008192062378</t>
+    <t xml:space="preserve">10.5008182525635</t>
   </si>
   <si>
     <t xml:space="preserve">10.1347951889038</t>
@@ -578,19 +578,19 @@
     <t xml:space="preserve">8.36161231994629</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01998996734619</t>
+    <t xml:space="preserve">8.01998901367188</t>
   </si>
   <si>
     <t xml:space="preserve">8.10946273803711</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39414691925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21520233154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33720970153809</t>
+    <t xml:space="preserve">8.3941478729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21520328521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3372106552124</t>
   </si>
   <si>
     <t xml:space="preserve">8.31280899047852</t>
@@ -602,22 +602,22 @@
     <t xml:space="preserve">8.34534549713135</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23960494995117</t>
+    <t xml:space="preserve">8.23960399627686</t>
   </si>
   <si>
     <t xml:space="preserve">8.49175453186035</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5893611907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76017189025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29654121398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25587272644043</t>
+    <t xml:space="preserve">8.58936023712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76017093658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29654216766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25587177276611</t>
   </si>
   <si>
     <t xml:space="preserve">8.17453479766846</t>
@@ -626,58 +626,58 @@
     <t xml:space="preserve">8.1908016204834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23147106170654</t>
+    <t xml:space="preserve">8.23147201538086</t>
   </si>
   <si>
     <t xml:space="preserve">8.2802734375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14199829101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1582670211792</t>
+    <t xml:space="preserve">8.14199733734131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15826511383057</t>
   </si>
   <si>
     <t xml:space="preserve">8.16639995574951</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12166309356689</t>
+    <t xml:space="preserve">8.12166404724121</t>
   </si>
   <si>
     <t xml:space="preserve">8.05252552032471</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89798164367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85731315612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93051719665527</t>
+    <t xml:space="preserve">7.89798259735107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85731363296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93051767349243</t>
   </si>
   <si>
     <t xml:space="preserve">7.90611600875854</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93865156173706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84917879104614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80850982666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62956476211548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5726261138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48315572738647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66616630554199</t>
+    <t xml:space="preserve">7.93865060806274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84918022155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80851030349731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62956523895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57262659072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48315477371216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66616678237915</t>
   </si>
   <si>
     <t xml:space="preserve">7.60516357421875</t>
@@ -686,97 +686,97 @@
     <t xml:space="preserve">7.54009246826172</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52382373809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47908878326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6132960319519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54822492599487</t>
+    <t xml:space="preserve">7.5238242149353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47908735275269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61329698562622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54822635650635</t>
   </si>
   <si>
     <t xml:space="preserve">7.56449365615845</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50755596160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46688604354858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49128913879395</t>
+    <t xml:space="preserve">7.50755643844604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46688747406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49129009246826</t>
   </si>
   <si>
     <t xml:space="preserve">7.4994215965271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31234502792358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27980852127075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3774151802063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38554859161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36928033828735</t>
+    <t xml:space="preserve">7.31234407424927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27980804443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37741470336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38554906845093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36928081512451</t>
   </si>
   <si>
     <t xml:space="preserve">7.32047748565674</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34487867355347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28794193267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04392576217651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15780067443848</t>
+    <t xml:space="preserve">7.34487915039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28794240951538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04392623901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15780019760132</t>
   </si>
   <si>
     <t xml:space="preserve">7.39368295669556</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4262170791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40181541442871</t>
+    <t xml:space="preserve">7.42621850967407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40181684494019</t>
   </si>
   <si>
     <t xml:space="preserve">7.30420970916748</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36114740371704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20660448074341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35301303863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33674621582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27167463302612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23100566864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32861089706421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26354074478149</t>
+    <t xml:space="preserve">7.36114692687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20660352706909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3530125617981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33674573898315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27167510986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23100471496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32861137390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26354169845581</t>
   </si>
   <si>
     <t xml:space="preserve">7.23913955688477</t>
@@ -785,109 +785,109 @@
     <t xml:space="preserve">7.22287130355835</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24727296829224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44248485565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25540733337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18220281600952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29607582092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16593456268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14153289794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0520601272583</t>
+    <t xml:space="preserve">7.24727439880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44248580932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25540828704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18220233917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29607629776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16593408584595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1415319442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05206060409546</t>
   </si>
   <si>
     <t xml:space="preserve">7.07646226882935</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03579378128052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01952600479126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87311410903931</t>
+    <t xml:space="preserve">7.0357928276062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01952505111694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87311458587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.677903175354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85124731063843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93379211425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26397323608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14841032028198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09888315200806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1814284324646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16491842269897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14015626907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21444702148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17317390441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97506475448608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84299278259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60361289978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62012100219727</t>
   </si>
   <si>
     <t xml:space="preserve">6.67790269851685</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85124731063843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93379163742065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26397371292114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14840936660767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09888315200806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18142890930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16491937637329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14015674591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21444606781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17317485809326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97506427764893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84299325942993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60361194610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62012100219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67790222167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80997467041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54582977294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31470441818237</t>
+    <t xml:space="preserve">6.80997514724731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54583024978638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31470394134521</t>
   </si>
   <si>
     <t xml:space="preserve">6.32295846939087</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34772300720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38074016571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39724969863892</t>
+    <t xml:space="preserve">6.34772253036499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38074064254761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3972487449646</t>
   </si>
   <si>
     <t xml:space="preserve">6.47153997421265</t>
@@ -896,19 +896,19 @@
     <t xml:space="preserve">6.2816858291626</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22390460968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09183216094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90197801589966</t>
+    <t xml:space="preserve">6.22390413284302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09183168411255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9019775390625</t>
   </si>
   <si>
     <t xml:space="preserve">5.95976066589355</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99277687072754</t>
+    <t xml:space="preserve">5.99277782440186</t>
   </si>
   <si>
     <t xml:space="preserve">6.20739507675171</t>
@@ -917,10 +917,10 @@
     <t xml:space="preserve">6.14135980606079</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19088697433472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14961385726929</t>
+    <t xml:space="preserve">6.19088649749756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14961338043213</t>
   </si>
   <si>
     <t xml:space="preserve">6.07532358169556</t>
@@ -935,13 +935,13 @@
     <t xml:space="preserve">5.9845232963562</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12485122680664</t>
+    <t xml:space="preserve">6.12485074996948</t>
   </si>
   <si>
     <t xml:space="preserve">6.13310480117798</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27343130111694</t>
+    <t xml:space="preserve">6.2734317779541</t>
   </si>
   <si>
     <t xml:space="preserve">6.44677639007568</t>
@@ -953,16 +953,16 @@
     <t xml:space="preserve">6.51281213760376</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36423206329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24041414260864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21565008163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23216009140015</t>
+    <t xml:space="preserve">6.36423110961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24041318893433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21564960479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23215913772583</t>
   </si>
   <si>
     <t xml:space="preserve">6.24866819381714</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">6.10834074020386</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05055952072144</t>
+    <t xml:space="preserve">6.05055999755859</t>
   </si>
   <si>
     <t xml:space="preserve">5.89372396469116</t>
@@ -983,16 +983,16 @@
     <t xml:space="preserve">5.77816104888916</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6956148147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79466915130615</t>
+    <t xml:space="preserve">5.69561433792114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79466962814331</t>
   </si>
   <si>
     <t xml:space="preserve">5.80292367935181</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82768726348877</t>
+    <t xml:space="preserve">5.82768774032593</t>
   </si>
   <si>
     <t xml:space="preserve">5.78641510009766</t>
@@ -1007,25 +1007,25 @@
     <t xml:space="preserve">6.29819536209106</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18263244628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15786790847778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03404998779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08357715606689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81943321228027</t>
+    <t xml:space="preserve">6.1826319694519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15786838531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03405046463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08357763290405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81943368911743</t>
   </si>
   <si>
     <t xml:space="preserve">5.91848659515381</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86070537567139</t>
+    <t xml:space="preserve">5.86070585250854</t>
   </si>
   <si>
     <t xml:space="preserve">5.76165151596069</t>
@@ -1034,10 +1034,10 @@
     <t xml:space="preserve">5.75339651107788</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8111777305603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70386981964111</t>
+    <t xml:space="preserve">5.81117820739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70387029647827</t>
   </si>
   <si>
     <t xml:space="preserve">5.74514245986938</t>
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">5.83594274520874</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71212434768677</t>
+    <t xml:space="preserve">5.71212482452393</t>
   </si>
   <si>
     <t xml:space="preserve">5.84419679641724</t>
@@ -1055,40 +1055,40 @@
     <t xml:space="preserve">5.94325113296509</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96801424026489</t>
+    <t xml:space="preserve">5.96801471710205</t>
   </si>
   <si>
     <t xml:space="preserve">5.87721490859985</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88546943664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93499565124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02579593658447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0670690536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38899517059326</t>
+    <t xml:space="preserve">5.88546991348267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93499612808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02579545974731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06706857681274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3889946937561</t>
   </si>
   <si>
     <t xml:space="preserve">6.19914102554321</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04230451583862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05881452560425</t>
+    <t xml:space="preserve">6.04230499267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05881404876709</t>
   </si>
   <si>
     <t xml:space="preserve">5.95150566101074</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17437791824341</t>
+    <t xml:space="preserve">6.17437744140625</t>
   </si>
   <si>
     <t xml:space="preserve">6.1760196685791</t>
@@ -1103,22 +1103,22 @@
     <t xml:space="preserve">6.20958423614502</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09210538864136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10888862609863</t>
+    <t xml:space="preserve">6.09210586547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10888910293579</t>
   </si>
   <si>
     <t xml:space="preserve">6.14245367050171</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05854082107544</t>
+    <t xml:space="preserve">6.0585412979126</t>
   </si>
   <si>
     <t xml:space="preserve">6.02497529983521</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97462797164917</t>
+    <t xml:space="preserve">5.97462749481201</t>
   </si>
   <si>
     <t xml:space="preserve">5.95784473419189</t>
@@ -1127,34 +1127,34 @@
     <t xml:space="preserve">6.15923643112183</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12567138671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19280195236206</t>
+    <t xml:space="preserve">6.12567090988159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1928014755249</t>
   </si>
   <si>
     <t xml:space="preserve">6.42775917053223</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71306467056274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64593410491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69628143310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78019571304321</t>
+    <t xml:space="preserve">6.7130651473999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64593458175659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69628190994263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7801947593689</t>
   </si>
   <si>
     <t xml:space="preserve">6.7298469543457</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62915086746216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56201982498169</t>
+    <t xml:space="preserve">6.629150390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56202030181885</t>
   </si>
   <si>
     <t xml:space="preserve">6.54523801803589</t>
@@ -1163,16 +1163,16 @@
     <t xml:space="preserve">6.67949914932251</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66271686553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57880353927612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37741088867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34384632110596</t>
+    <t xml:space="preserve">6.66271638870239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57880306243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37741136550903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3438458442688</t>
   </si>
   <si>
     <t xml:space="preserve">6.22636795043945</t>
@@ -1193,10 +1193,10 @@
     <t xml:space="preserve">5.62219142913818</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5382776260376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43758249282837</t>
+    <t xml:space="preserve">5.53827810287476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43758201599121</t>
   </si>
   <si>
     <t xml:space="preserve">5.45436525344849</t>
@@ -1208,22 +1208,22 @@
     <t xml:space="preserve">5.5214958190918</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50471305847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48792934417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35366868972778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37045097351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42079973220825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28653812408447</t>
+    <t xml:space="preserve">5.50471210479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4879298210144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35366821289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3704514503479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42079925537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28653764724731</t>
   </si>
   <si>
     <t xml:space="preserve">5.30332088470459</t>
@@ -1232,7 +1232,7 @@
     <t xml:space="preserve">5.26975584030151</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38723421096802</t>
+    <t xml:space="preserve">5.38723468780518</t>
   </si>
   <si>
     <t xml:space="preserve">5.32010364532471</t>
@@ -1241,34 +1241,34 @@
     <t xml:space="preserve">5.65575695037842</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75645351409912</t>
+    <t xml:space="preserve">5.75645303726196</t>
   </si>
   <si>
     <t xml:space="preserve">5.70610475540161</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72288656234741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73967027664185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63897466659546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57184362411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18584156036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2026252746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21940803527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16905975341797</t>
+    <t xml:space="preserve">5.72288703918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.739670753479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6389741897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57184410095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18584203720093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20262479782104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21940755844116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16905927658081</t>
   </si>
   <si>
     <t xml:space="preserve">5.13549327850342</t>
@@ -1277,25 +1277,25 @@
     <t xml:space="preserve">5.10192918777466</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95088481903076</t>
+    <t xml:space="preserve">4.9508843421936</t>
   </si>
   <si>
     <t xml:space="preserve">5.03479862213135</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15227699279785</t>
+    <t xml:space="preserve">5.15227746963501</t>
   </si>
   <si>
     <t xml:space="preserve">5.11871147155762</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06836366653442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08514547348022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23619031906128</t>
+    <t xml:space="preserve">5.06836318969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0851469039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23619079589844</t>
   </si>
   <si>
     <t xml:space="preserve">5.25297260284424</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">5.33688640594482</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79001760482788</t>
+    <t xml:space="preserve">5.79001712799072</t>
   </si>
   <si>
     <t xml:space="preserve">5.77323532104492</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">5.58862638473511</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81662321090698</t>
+    <t xml:space="preserve">4.81662368774414</t>
   </si>
   <si>
     <t xml:space="preserve">4.79984140396118</t>
@@ -1325,10 +1325,10 @@
     <t xml:space="preserve">4.36349201202393</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31314373016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19566535949707</t>
+    <t xml:space="preserve">4.31314420700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19566488265991</t>
   </si>
   <si>
     <t xml:space="preserve">4.11175107955933</t>
@@ -1337,7 +1337,7 @@
     <t xml:space="preserve">4.02783870697021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17049121856689</t>
+    <t xml:space="preserve">4.17049074172974</t>
   </si>
   <si>
     <t xml:space="preserve">4.06979560852051</t>
@@ -1349,16 +1349,16 @@
     <t xml:space="preserve">4.34670877456665</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17888164520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04462146759033</t>
+    <t xml:space="preserve">4.17888212203979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04462099075317</t>
   </si>
   <si>
     <t xml:space="preserve">4.15370845794678</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26279640197754</t>
+    <t xml:space="preserve">4.26279592514038</t>
   </si>
   <si>
     <t xml:space="preserve">4.16209983825684</t>
@@ -1367,22 +1367,22 @@
     <t xml:space="preserve">4.14531755447388</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9942729473114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09496927261353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98588180541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2795786857605</t>
+    <t xml:space="preserve">3.99427270889282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09496974945068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98588132858276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27957820892334</t>
   </si>
   <si>
     <t xml:space="preserve">4.22923040390015</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21244812011719</t>
+    <t xml:space="preserve">4.21244764328003</t>
   </si>
   <si>
     <t xml:space="preserve">4.03622961044312</t>
@@ -1394,19 +1394,19 @@
     <t xml:space="preserve">4.16283082962036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07770204544067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00108432769775</t>
+    <t xml:space="preserve">4.07770109176636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00108480453491</t>
   </si>
   <si>
     <t xml:space="preserve">4.20539569854736</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37565422058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21390867233276</t>
+    <t xml:space="preserve">4.37565469741821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21390819549561</t>
   </si>
   <si>
     <t xml:space="preserve">4.22242164611816</t>
@@ -1415,19 +1415,19 @@
     <t xml:space="preserve">4.25647354125977</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24796009063721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32457685470581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30755090713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23944759368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35862827301025</t>
+    <t xml:space="preserve">4.24795961380005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32457637786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30755043029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23944807052612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35862874984741</t>
   </si>
   <si>
     <t xml:space="preserve">4.51186180114746</t>
@@ -1439,7 +1439,7 @@
     <t xml:space="preserve">5.94203662872314</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89095878601074</t>
+    <t xml:space="preserve">5.8909592628479</t>
   </si>
   <si>
     <t xml:space="preserve">5.73772573471069</t>
@@ -1457,25 +1457,25 @@
     <t xml:space="preserve">5.41423416137695</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26100063323975</t>
+    <t xml:space="preserve">5.2610011100769</t>
   </si>
   <si>
     <t xml:space="preserve">5.48233795166016</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44828653335571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60151863098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66962289810181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51638889312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70367336273193</t>
+    <t xml:space="preserve">5.44828605651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6015191078186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66962194442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5163893699646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70367479324341</t>
   </si>
   <si>
     <t xml:space="preserve">5.32910442352295</t>
@@ -1484,22 +1484,22 @@
     <t xml:space="preserve">5.27802705764771</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4312596321106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31207895278931</t>
+    <t xml:space="preserve">5.43126010894775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31207847595215</t>
   </si>
   <si>
     <t xml:space="preserve">5.2269492149353</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00561237335205</t>
+    <t xml:space="preserve">5.00561285018921</t>
   </si>
   <si>
     <t xml:space="preserve">4.95453548431396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93750953674316</t>
+    <t xml:space="preserve">4.93750858306885</t>
   </si>
   <si>
     <t xml:space="preserve">5.05669021606445</t>
@@ -1511,34 +1511,34 @@
     <t xml:space="preserve">4.97156143188477</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8864312171936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02263879776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92048311233521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9034571647644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.852379322052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8694052696228</t>
+    <t xml:space="preserve">4.88643169403076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02263832092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92048263549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90345764160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85237979888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86940574645996</t>
   </si>
   <si>
     <t xml:space="preserve">5.34613037109375</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24397468566895</t>
+    <t xml:space="preserve">5.2439751625061</t>
   </si>
   <si>
     <t xml:space="preserve">5.36315631866455</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38018226623535</t>
+    <t xml:space="preserve">5.38018274307251</t>
   </si>
   <si>
     <t xml:space="preserve">5.2099232673645</t>
@@ -1547,22 +1547,22 @@
     <t xml:space="preserve">5.1588454246521</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10776853561401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98858642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0907416343689</t>
+    <t xml:space="preserve">5.10776805877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98858737945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09074211120605</t>
   </si>
   <si>
     <t xml:space="preserve">5.1928973197937</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17587089538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14182043075562</t>
+    <t xml:space="preserve">5.1758713722229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14181995391846</t>
   </si>
   <si>
     <t xml:space="preserve">5.07371616363525</t>
@@ -1574,7 +1574,7 @@
     <t xml:space="preserve">4.54591369628906</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59699201583862</t>
+    <t xml:space="preserve">4.59699106216431</t>
   </si>
   <si>
     <t xml:space="preserve">4.57996559143066</t>
@@ -1583,19 +1583,19 @@
     <t xml:space="preserve">4.63104295730591</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78427600860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76725053787231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8183274269104</t>
+    <t xml:space="preserve">4.7842755317688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.767249584198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81832790374756</t>
   </si>
   <si>
     <t xml:space="preserve">4.80130195617676</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39720821380615</t>
+    <t xml:space="preserve">5.39720869064331</t>
   </si>
   <si>
     <t xml:space="preserve">5.6185450553894</t>
@@ -1607,22 +1607,22 @@
     <t xml:space="preserve">5.49936389923096</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63557100296021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68664836883545</t>
+    <t xml:space="preserve">5.63557052612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68664884567261</t>
   </si>
   <si>
     <t xml:space="preserve">5.65259647369385</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8569073677063</t>
+    <t xml:space="preserve">5.85690784454346</t>
   </si>
   <si>
     <t xml:space="preserve">5.8739333152771</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3166069984436</t>
+    <t xml:space="preserve">6.31660652160645</t>
   </si>
   <si>
     <t xml:space="preserve">6.33363246917725</t>
@@ -1631,58 +1631,58 @@
     <t xml:space="preserve">6.29958057403564</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35065841674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43578720092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55496883392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69117641448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79333114624023</t>
+    <t xml:space="preserve">6.35065793991089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43578767776489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55496835708618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69117593765259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79333162307739</t>
   </si>
   <si>
     <t xml:space="preserve">7.15087461471558</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08277130126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87846088409424</t>
+    <t xml:space="preserve">7.08277082443237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8784613609314</t>
   </si>
   <si>
     <t xml:space="preserve">6.77630567550659</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84440946578979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70820236206055</t>
+    <t xml:space="preserve">6.84440898895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70820188522339</t>
   </si>
   <si>
     <t xml:space="preserve">6.75927972793579</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5379433631897</t>
+    <t xml:space="preserve">6.53794288635254</t>
   </si>
   <si>
     <t xml:space="preserve">6.72522783279419</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65712451934814</t>
+    <t xml:space="preserve">6.6571249961853</t>
   </si>
   <si>
     <t xml:space="preserve">6.91251230239868</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8954873085022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9635910987854</t>
+    <t xml:space="preserve">6.89548778533936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96359062194824</t>
   </si>
   <si>
     <t xml:space="preserve">7.17302179336548</t>
@@ -1694,19 +1694,19 @@
     <t xml:space="preserve">7.1206636428833</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57443141937256</t>
+    <t xml:space="preserve">7.57443237304688</t>
   </si>
   <si>
     <t xml:space="preserve">7.97584247589111</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02820014953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06310558319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99329519271851</t>
+    <t xml:space="preserve">8.02819919586182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0631046295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99329423904419</t>
   </si>
   <si>
     <t xml:space="preserve">8.0107479095459</t>
@@ -1724,7 +1724,7 @@
     <t xml:space="preserve">8.16781997680664</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18527412414551</t>
+    <t xml:space="preserve">8.18527317047119</t>
   </si>
   <si>
     <t xml:space="preserve">8.34234714508057</t>
@@ -1739,19 +1739,19 @@
     <t xml:space="preserve">8.08055686950684</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20272445678711</t>
+    <t xml:space="preserve">8.20272541046143</t>
   </si>
   <si>
     <t xml:space="preserve">7.95838832855225</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37725162506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3248929977417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81356716156006</t>
+    <t xml:space="preserve">8.37725257873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32489395141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81356811523438</t>
   </si>
   <si>
     <t xml:space="preserve">8.58668327331543</t>
@@ -1775,25 +1775,25 @@
     <t xml:space="preserve">8.28998851776123</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30744075775146</t>
+    <t xml:space="preserve">8.30744171142578</t>
   </si>
   <si>
     <t xml:space="preserve">8.04565238952637</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85367298126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41215705871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22017860412598</t>
+    <t xml:space="preserve">7.85367345809937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41215801239014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22017765045166</t>
   </si>
   <si>
     <t xml:space="preserve">8.44706249237061</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3597993850708</t>
+    <t xml:space="preserve">8.35979843139648</t>
   </si>
   <si>
     <t xml:space="preserve">8.09801006317139</t>
@@ -1802,7 +1802,7 @@
     <t xml:space="preserve">8.23763084411621</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48196792602539</t>
+    <t xml:space="preserve">8.48196697235107</t>
   </si>
   <si>
     <t xml:space="preserve">8.6215877532959</t>
@@ -1814,7 +1814,7 @@
     <t xml:space="preserve">8.65649318695068</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51687335968018</t>
+    <t xml:space="preserve">8.51687240600586</t>
   </si>
   <si>
     <t xml:space="preserve">8.46451473236084</t>
@@ -1832,16 +1832,16 @@
     <t xml:space="preserve">9.59893417358398</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77346038818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81709289550781</t>
+    <t xml:space="preserve">9.77345943450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8170919418335</t>
   </si>
   <si>
     <t xml:space="preserve">9.29351234436035</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46804046630859</t>
+    <t xml:space="preserve">9.46803951263428</t>
   </si>
   <si>
     <t xml:space="preserve">9.55530261993408</t>
@@ -1850,7 +1850,7 @@
     <t xml:space="preserve">9.64256572723389</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90435600280762</t>
+    <t xml:space="preserve">9.9043550491333</t>
   </si>
   <si>
     <t xml:space="preserve">9.33714485168457</t>
@@ -1868,22 +1868,22 @@
     <t xml:space="preserve">10.4279327392578</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5588274002075</t>
+    <t xml:space="preserve">10.5588283538818</t>
   </si>
   <si>
     <t xml:space="preserve">10.6024589538574</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8206176757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7333545684814</t>
+    <t xml:space="preserve">10.8206167221069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7333536148071</t>
   </si>
   <si>
     <t xml:space="preserve">10.7769861221313</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2970390319824</t>
+    <t xml:space="preserve">10.2970380783081</t>
   </si>
   <si>
     <t xml:space="preserve">10.3843011856079</t>
@@ -1892,19 +1892,19 @@
     <t xml:space="preserve">10.3406705856323</t>
   </si>
   <si>
-    <t xml:space="preserve">10.209774017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2534074783325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0788803100586</t>
+    <t xml:space="preserve">10.2097749710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2534065246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0788812637329</t>
   </si>
   <si>
     <t xml:space="preserve">9.51167011260986</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72982788085938</t>
+    <t xml:space="preserve">9.72982883453369</t>
   </si>
   <si>
     <t xml:space="preserve">9.68619728088379</t>
@@ -1913,13 +1913,13 @@
     <t xml:space="preserve">8.98809432983398</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42440891265869</t>
+    <t xml:space="preserve">9.42440795898438</t>
   </si>
   <si>
     <t xml:space="preserve">11.6496171951294</t>
   </si>
   <si>
-    <t xml:space="preserve">11.562352180481</t>
+    <t xml:space="preserve">11.5623531341553</t>
   </si>
   <si>
     <t xml:space="preserve">11.7805109024048</t>
@@ -1931,7 +1931,7 @@
     <t xml:space="preserve">11.9550352096558</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6932468414307</t>
+    <t xml:space="preserve">11.693247795105</t>
   </si>
   <si>
     <t xml:space="preserve">12.3040885925293</t>
@@ -1940,13 +1940,13 @@
     <t xml:space="preserve">12.2604570388794</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2168254852295</t>
+    <t xml:space="preserve">12.2168245315552</t>
   </si>
   <si>
     <t xml:space="preserve">12.3913507461548</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7368783950806</t>
+    <t xml:space="preserve">11.7368793487549</t>
   </si>
   <si>
     <t xml:space="preserve">11.8677730560303</t>
@@ -1958,34 +1958,34 @@
     <t xml:space="preserve">10.9515113830566</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0422983169556</t>
+    <t xml:space="preserve">12.0422992706299</t>
   </si>
   <si>
     <t xml:space="preserve">11.3005638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3441953659058</t>
+    <t xml:space="preserve">11.3441944122314</t>
   </si>
   <si>
     <t xml:space="preserve">10.9951429367065</t>
   </si>
   <si>
-    <t xml:space="preserve">10.471565246582</t>
+    <t xml:space="preserve">10.4715642929077</t>
   </si>
   <si>
     <t xml:space="preserve">10.9078798294067</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4314584732056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0387725830078</t>
+    <t xml:space="preserve">11.4314594268799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0387735366821</t>
   </si>
   <si>
     <t xml:space="preserve">11.9899406433105</t>
   </si>
   <si>
-    <t xml:space="preserve">11.74560546875</t>
+    <t xml:space="preserve">11.7456045150757</t>
   </si>
   <si>
     <t xml:space="preserve">11.5361728668213</t>
@@ -1994,7 +1994,7 @@
     <t xml:space="preserve">11.5187215805054</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6234369277954</t>
+    <t xml:space="preserve">11.6234359741211</t>
   </si>
   <si>
     <t xml:space="preserve">11.4489107131958</t>
@@ -2003,7 +2003,7 @@
     <t xml:space="preserve">11.6408891677856</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7281522750854</t>
+    <t xml:space="preserve">11.7281513214111</t>
   </si>
   <si>
     <t xml:space="preserve">11.9201307296753</t>
@@ -2024,7 +2024,7 @@
     <t xml:space="preserve">10.3319435119629</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1050596237183</t>
+    <t xml:space="preserve">10.1050605773926</t>
   </si>
   <si>
     <t xml:space="preserve">9.81839179992676</t>
@@ -3516,6 +3516,9 @@
   </si>
   <si>
     <t xml:space="preserve">17.2800006866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3799991607666</t>
   </si>
 </sst>
 </file>
@@ -69322,7 +69325,7 @@
     </row>
     <row r="2519">
       <c r="A2519" s="1" t="n">
-        <v>45986.6913078704</v>
+        <v>45986.3333333333</v>
       </c>
       <c r="B2519" t="n">
         <v>25559</v>
@@ -69343,6 +69346,32 @@
         <v>1167</v>
       </c>
       <c r="H2519" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2520">
+      <c r="A2520" s="1" t="n">
+        <v>45987.6911111111</v>
+      </c>
+      <c r="B2520" t="n">
+        <v>32123</v>
+      </c>
+      <c r="C2520" t="n">
+        <v>17.3999996185303</v>
+      </c>
+      <c r="D2520" t="n">
+        <v>17.1800003051758</v>
+      </c>
+      <c r="E2520" t="n">
+        <v>17.2999992370605</v>
+      </c>
+      <c r="F2520" t="n">
+        <v>17.3799991607666</v>
+      </c>
+      <c r="G2520" t="s">
+        <v>1168</v>
+      </c>
+      <c r="H2520" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ORS.MI.xlsx
+++ b/data/ORS.MI.xlsx
@@ -50,46 +50,46 @@
     <t xml:space="preserve">8.06380176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94223833084106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82472515106201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93818521499634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90171527862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03948974609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92602920532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8611946105957</t>
+    <t xml:space="preserve">7.94223642349243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82472467422485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93818712234497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90171575546265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03948879241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92602872848511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86119508743286</t>
   </si>
   <si>
     <t xml:space="preserve">7.82067251205444</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93413352966309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02327919006348</t>
+    <t xml:space="preserve">7.93413305282593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02328109741211</t>
   </si>
   <si>
     <t xml:space="preserve">8.08811473846436</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14484596252441</t>
+    <t xml:space="preserve">8.1448450088501</t>
   </si>
   <si>
     <t xml:space="preserve">7.69910764694214</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80446338653564</t>
+    <t xml:space="preserve">7.8044638633728</t>
   </si>
   <si>
     <t xml:space="preserve">7.97465467453003</t>
@@ -98,76 +98,76 @@
     <t xml:space="preserve">8.01112461090088</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01517581939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79230880737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82877683639526</t>
+    <t xml:space="preserve">8.01517486572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79230737686157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82877779006958</t>
   </si>
   <si>
     <t xml:space="preserve">8.34745311737061</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84093332290649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90982055664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85714149475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78015184402466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84498596191406</t>
+    <t xml:space="preserve">7.84093427658081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90982103347778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85714101791382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7801513671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8449854850769</t>
   </si>
   <si>
     <t xml:space="preserve">7.97870683670044</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88550662994385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95034170150757</t>
+    <t xml:space="preserve">7.88550615310669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95034265518188</t>
   </si>
   <si>
     <t xml:space="preserve">8.00301933288574</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0192289352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91792392730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10027313232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10432434082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1853666305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20157527923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11242961883545</t>
+    <t xml:space="preserve">8.01922798156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91792440414429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1002721786499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.104323387146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18536758422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20157432556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11242771148682</t>
   </si>
   <si>
     <t xml:space="preserve">8.07595825195312</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03138637542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09621906280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17726230621338</t>
+    <t xml:space="preserve">8.03138446807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09622001647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1772632598877</t>
   </si>
   <si>
     <t xml:space="preserve">8.05569744110107</t>
@@ -182,28 +182,28 @@
     <t xml:space="preserve">8.4203929901123</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67162799835205</t>
+    <t xml:space="preserve">8.67162704467773</t>
   </si>
   <si>
     <t xml:space="preserve">8.55816650390625</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42849731445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52429103851318</t>
+    <t xml:space="preserve">8.42849826812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52429008483887</t>
   </si>
   <si>
     <t xml:space="preserve">8.45921897888184</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50802230834961</t>
+    <t xml:space="preserve">8.50802135467529</t>
   </si>
   <si>
     <t xml:space="preserve">8.60562896728516</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5324239730835</t>
+    <t xml:space="preserve">8.53242492675781</t>
   </si>
   <si>
     <t xml:space="preserve">8.61376190185547</t>
@@ -221,10 +221,10 @@
     <t xml:space="preserve">8.90657997131348</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86591148376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94725036621094</t>
+    <t xml:space="preserve">8.86591243743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94725131988525</t>
   </si>
   <si>
     <t xml:space="preserve">8.93911838531494</t>
@@ -233,10 +233,10 @@
     <t xml:space="preserve">8.78457355499268</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74390411376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91471481323242</t>
+    <t xml:space="preserve">8.74390316009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91471385955811</t>
   </si>
   <si>
     <t xml:space="preserve">8.92284965515137</t>
@@ -245,25 +245,25 @@
     <t xml:space="preserve">9.10992908477783</t>
   </si>
   <si>
-    <t xml:space="preserve">9.077392578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11806201934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13432788848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15059852600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15873241424561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7357702255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67883396148682</t>
+    <t xml:space="preserve">9.07739162445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11806297302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1343297958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15059757232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15873050689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73576927185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6788330078125</t>
   </si>
   <si>
     <t xml:space="preserve">8.85777759552002</t>
@@ -272,10 +272,10 @@
     <t xml:space="preserve">8.72763633728027</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70323467254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66256618499756</t>
+    <t xml:space="preserve">8.7032356262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66256523132324</t>
   </si>
   <si>
     <t xml:space="preserve">8.69510173797607</t>
@@ -287,34 +287,34 @@
     <t xml:space="preserve">8.80084037780762</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77643966674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68696689605713</t>
+    <t xml:space="preserve">8.77644062042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68696784973145</t>
   </si>
   <si>
     <t xml:space="preserve">8.54869174957275</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54055786132812</t>
+    <t xml:space="preserve">8.54055690765381</t>
   </si>
   <si>
     <t xml:space="preserve">8.58122825622559</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46735191345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51615619659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49988842010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45108509063721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63003158569336</t>
+    <t xml:space="preserve">8.46735382080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51615524291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49988746643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45108413696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63003063201904</t>
   </si>
   <si>
     <t xml:space="preserve">8.80897617340088</t>
@@ -323,76 +323,76 @@
     <t xml:space="preserve">8.89031505584717</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93098258972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96351909637451</t>
+    <t xml:space="preserve">8.930983543396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9635181427002</t>
   </si>
   <si>
     <t xml:space="preserve">9.0529899597168</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30514144897461</t>
+    <t xml:space="preserve">9.30514049530029</t>
   </si>
   <si>
     <t xml:space="preserve">9.10179424285889</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1912670135498</t>
+    <t xml:space="preserve">9.19126605987549</t>
   </si>
   <si>
     <t xml:space="preserve">9.35394382476807</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47595119476318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54915618896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58982563018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66302967071533</t>
+    <t xml:space="preserve">9.4759521484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54915523529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5898265838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66303253173828</t>
   </si>
   <si>
     <t xml:space="preserve">9.71996688842773</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85824489593506</t>
+    <t xml:space="preserve">9.85824394226074</t>
   </si>
   <si>
     <t xml:space="preserve">10.0046539306641</t>
   </si>
   <si>
-    <t xml:space="preserve">10.240535736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2486686706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3381414413452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.598424911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4276161193848</t>
+    <t xml:space="preserve">10.2405338287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2486705780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3381404876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5984258651733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4276151657104</t>
   </si>
   <si>
     <t xml:space="preserve">10.4032115936279</t>
   </si>
   <si>
-    <t xml:space="preserve">10.525221824646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4601488113403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5658912658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5821580886841</t>
+    <t xml:space="preserve">10.525218963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.460150718689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5658903121948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5821571350098</t>
   </si>
   <si>
     <t xml:space="preserve">10.7773704528809</t>
@@ -407,19 +407,19 @@
     <t xml:space="preserve">10.6553640365601</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6797637939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5740251541138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5170879364014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5414886474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5577564239502</t>
+    <t xml:space="preserve">10.679762840271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5740242004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5170860290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5414876937866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5577554702759</t>
   </si>
   <si>
     <t xml:space="preserve">10.5089530944824</t>
@@ -428,37 +428,37 @@
     <t xml:space="preserve">10.818039894104</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6878976821899</t>
+    <t xml:space="preserve">10.6878967285156</t>
   </si>
   <si>
     <t xml:space="preserve">10.7611017227173</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6472282409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.899377822876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8831100463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.671630859375</t>
+    <t xml:space="preserve">10.6472291946411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8993787765503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8831090927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6716289520264</t>
   </si>
   <si>
     <t xml:space="preserve">10.7367010116577</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0051193237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0213871002197</t>
+    <t xml:space="preserve">11.0051183700562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0213861465454</t>
   </si>
   <si>
     <t xml:space="preserve">11.184063911438</t>
   </si>
   <si>
-    <t xml:space="preserve">11.40367603302</t>
+    <t xml:space="preserve">11.4036779403687</t>
   </si>
   <si>
     <t xml:space="preserve">11.3955430984497</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">11.3386068344116</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3223390579224</t>
+    <t xml:space="preserve">11.322338104248</t>
   </si>
   <si>
     <t xml:space="preserve">11.330472946167</t>
@@ -482,19 +482,19 @@
     <t xml:space="preserve">10.606559753418</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8424415588379</t>
+    <t xml:space="preserve">10.8424406051636</t>
   </si>
   <si>
     <t xml:space="preserve">10.8505744934082</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6390953063965</t>
+    <t xml:space="preserve">10.6390943527222</t>
   </si>
   <si>
     <t xml:space="preserve">10.4113464355469</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2080011367798</t>
+    <t xml:space="preserve">10.2080001831055</t>
   </si>
   <si>
     <t xml:space="preserve">10.2730712890625</t>
@@ -503,28 +503,28 @@
     <t xml:space="preserve">10.232400894165</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3218746185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.370677947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3300085067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3056049346924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2568035125732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1835975646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4845523834229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3625431060791</t>
+    <t xml:space="preserve">10.321873664856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3706769943237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3300075531006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.305606842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2568044662476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1835966110229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4845514297485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3625421524048</t>
   </si>
   <si>
     <t xml:space="preserve">10.4438819885254</t>
@@ -533,55 +533,55 @@
     <t xml:space="preserve">10.8587083816528</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9237804412842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0376539230347</t>
+    <t xml:space="preserve">10.9237794876099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0376529693604</t>
   </si>
   <si>
     <t xml:space="preserve">11.0620555877686</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1027240753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1433935165405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1759300231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1352596282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0701885223389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1189918518066</t>
+    <t xml:space="preserve">11.1027250289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1433954238892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1759281158447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1352605819702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0701904296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1189937591553</t>
   </si>
   <si>
     <t xml:space="preserve">11.1515274047852</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2247323989868</t>
+    <t xml:space="preserve">11.2247314453125</t>
   </si>
   <si>
     <t xml:space="preserve">11.0457878112793</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5008192062378</t>
+    <t xml:space="preserve">10.5008182525635</t>
   </si>
   <si>
     <t xml:space="preserve">10.1347951889038</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36161231994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01998996734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10946273803711</t>
+    <t xml:space="preserve">8.36161327362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01999092102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10946178436279</t>
   </si>
   <si>
     <t xml:space="preserve">8.3941478729248</t>
@@ -590,7 +590,7 @@
     <t xml:space="preserve">8.21520328521729</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33720970153809</t>
+    <t xml:space="preserve">8.3372106552124</t>
   </si>
   <si>
     <t xml:space="preserve">8.31280899047852</t>
@@ -602,37 +602,37 @@
     <t xml:space="preserve">8.34534549713135</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23960494995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49175548553467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58936214447021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76017189025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29654216766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25587272644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17453479766846</t>
+    <t xml:space="preserve">8.23960590362549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49175453186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58936023712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76017093658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29654312133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25587177276611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17453384399414</t>
   </si>
   <si>
     <t xml:space="preserve">8.1908016204834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23147106170654</t>
+    <t xml:space="preserve">8.23147010803223</t>
   </si>
   <si>
     <t xml:space="preserve">8.2802734375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14199829101562</t>
+    <t xml:space="preserve">8.14199924468994</t>
   </si>
   <si>
     <t xml:space="preserve">8.15826606750488</t>
@@ -644,19 +644,19 @@
     <t xml:space="preserve">8.12166404724121</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05252552032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89798259735107</t>
+    <t xml:space="preserve">8.05252647399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89798402786255</t>
   </si>
   <si>
     <t xml:space="preserve">7.85731315612793</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93051815032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90611505508423</t>
+    <t xml:space="preserve">7.93051671981812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90611553192139</t>
   </si>
   <si>
     <t xml:space="preserve">7.93865156173706</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">7.84917974472046</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80850887298584</t>
+    <t xml:space="preserve">7.80850982666016</t>
   </si>
   <si>
     <t xml:space="preserve">7.62956476211548</t>
@@ -677,13 +677,13 @@
     <t xml:space="preserve">7.48315572738647</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66616725921631</t>
+    <t xml:space="preserve">7.66616678237915</t>
   </si>
   <si>
     <t xml:space="preserve">7.60516262054443</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54009246826172</t>
+    <t xml:space="preserve">7.54009342193604</t>
   </si>
   <si>
     <t xml:space="preserve">7.52382373809814</t>
@@ -692,106 +692,106 @@
     <t xml:space="preserve">7.47908687591553</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61329793930054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54822492599487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56449460983276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50755596160889</t>
+    <t xml:space="preserve">7.61329746246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54822540283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56449365615845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5075569152832</t>
   </si>
   <si>
     <t xml:space="preserve">7.4668869972229</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49128913879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49942064285278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31234407424927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27980804443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3774151802063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38554859161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36928081512451</t>
+    <t xml:space="preserve">7.4912896156311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49942255020142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31234455108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27980709075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37741422653198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38555002212524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36928129196167</t>
   </si>
   <si>
     <t xml:space="preserve">7.32047748565674</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34487867355347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28794193267822</t>
+    <t xml:space="preserve">7.34487915039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28794240951538</t>
   </si>
   <si>
     <t xml:space="preserve">7.04392671585083</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15780067443848</t>
+    <t xml:space="preserve">7.15780019760132</t>
   </si>
   <si>
     <t xml:space="preserve">7.39368200302124</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4262170791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40181636810303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30420970916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36114740371704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20660400390625</t>
+    <t xml:space="preserve">7.42621803283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40181541442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30421161651611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36114835739136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20660352706909</t>
   </si>
   <si>
     <t xml:space="preserve">7.3530125617981</t>
   </si>
   <si>
-    <t xml:space="preserve">7.336745262146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27167510986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23100519180298</t>
+    <t xml:space="preserve">7.33674621582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27167367935181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23100423812866</t>
   </si>
   <si>
     <t xml:space="preserve">7.32861185073853</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26354122161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23913955688477</t>
+    <t xml:space="preserve">7.26354074478149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23913908004761</t>
   </si>
   <si>
     <t xml:space="preserve">7.22287178039551</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24727344512939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44248485565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25540733337402</t>
+    <t xml:space="preserve">7.24727296829224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44248580932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25540685653687</t>
   </si>
   <si>
     <t xml:space="preserve">7.18220233917236</t>
@@ -800,28 +800,28 @@
     <t xml:space="preserve">7.29607534408569</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16593456268311</t>
+    <t xml:space="preserve">7.16593503952026</t>
   </si>
   <si>
     <t xml:space="preserve">7.14153289794922</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05206108093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07646226882935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03579330444336</t>
+    <t xml:space="preserve">7.05205965042114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07646179199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03579235076904</t>
   </si>
   <si>
     <t xml:space="preserve">7.0195255279541</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87311458587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67790269851685</t>
+    <t xml:space="preserve">6.87311410903931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67790222167969</t>
   </si>
   <si>
     <t xml:space="preserve">6.85124731063843</t>
@@ -830,7 +830,7 @@
     <t xml:space="preserve">6.93379163742065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26397371292114</t>
+    <t xml:space="preserve">7.26397323608398</t>
   </si>
   <si>
     <t xml:space="preserve">7.14841032028198</t>
@@ -839,40 +839,40 @@
     <t xml:space="preserve">7.0988826751709</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18142890930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16491889953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14015626907349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21444654464722</t>
+    <t xml:space="preserve">7.1814284324646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16491842269897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14015531539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2144455909729</t>
   </si>
   <si>
     <t xml:space="preserve">7.1731743812561</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97506475448608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84299278259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60361242294312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62012052536011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80997467041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54582977294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31470394134521</t>
+    <t xml:space="preserve">6.97506427764893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84299325942993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60361194610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62012147903442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.809974193573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54583024978638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31470346450806</t>
   </si>
   <si>
     <t xml:space="preserve">6.32295894622803</t>
@@ -881,49 +881,49 @@
     <t xml:space="preserve">6.34772300720215</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38074016571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39724969863892</t>
+    <t xml:space="preserve">6.38073968887329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3972487449646</t>
   </si>
   <si>
     <t xml:space="preserve">6.47153997421265</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2816858291626</t>
+    <t xml:space="preserve">6.28168630599976</t>
   </si>
   <si>
     <t xml:space="preserve">6.22390413284302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09183168411255</t>
+    <t xml:space="preserve">6.09183216094971</t>
   </si>
   <si>
     <t xml:space="preserve">5.90197801589966</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9597601890564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9927773475647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20739507675171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14135932922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19088697433472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14961385726929</t>
+    <t xml:space="preserve">5.95975971221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99277830123901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20739555358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14135980606079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1908860206604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14961338043213</t>
   </si>
   <si>
     <t xml:space="preserve">6.07532358169556</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25692272186279</t>
+    <t xml:space="preserve">6.25692224502563</t>
   </si>
   <si>
     <t xml:space="preserve">6.00928783416748</t>
@@ -932,22 +932,22 @@
     <t xml:space="preserve">5.9845232963562</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12485122680664</t>
+    <t xml:space="preserve">6.12485027313232</t>
   </si>
   <si>
     <t xml:space="preserve">6.13310480117798</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2734317779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44677639007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55408477783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51281213760376</t>
+    <t xml:space="preserve">6.27343082427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44677591323853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55408525466919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51281261444092</t>
   </si>
   <si>
     <t xml:space="preserve">6.3642315864563</t>
@@ -956,22 +956,22 @@
     <t xml:space="preserve">6.24041414260864</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21565008163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23215961456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24866819381714</t>
+    <t xml:space="preserve">6.21564960479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23215866088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24866771697998</t>
   </si>
   <si>
     <t xml:space="preserve">6.11659622192383</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10834121704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05055952072144</t>
+    <t xml:space="preserve">6.1083402633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05055904388428</t>
   </si>
   <si>
     <t xml:space="preserve">5.89372396469116</t>
@@ -983,49 +983,49 @@
     <t xml:space="preserve">5.6956148147583</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79466915130615</t>
+    <t xml:space="preserve">5.79466962814331</t>
   </si>
   <si>
     <t xml:space="preserve">5.80292367935181</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82768726348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7864146232605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73688745498657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85245084762573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29819583892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1826319694519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15786790847778</t>
+    <t xml:space="preserve">5.82768821716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78641557693481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73688793182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85245132446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29819536209106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18263244628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15786838531494</t>
   </si>
   <si>
     <t xml:space="preserve">6.03405046463013</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08357810974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81943368911743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91848659515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86070585250854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76165103912354</t>
+    <t xml:space="preserve">6.08357715606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81943416595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91848707199097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86070537567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76165199279785</t>
   </si>
   <si>
     <t xml:space="preserve">5.75339651107788</t>
@@ -1037,7 +1037,7 @@
     <t xml:space="preserve">5.70387029647827</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74514198303223</t>
+    <t xml:space="preserve">5.74514245986938</t>
   </si>
   <si>
     <t xml:space="preserve">5.83594226837158</t>
@@ -1049,7 +1049,7 @@
     <t xml:space="preserve">5.84419679641724</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94325065612793</t>
+    <t xml:space="preserve">5.94325113296509</t>
   </si>
   <si>
     <t xml:space="preserve">5.96801424026489</t>
@@ -1058,79 +1058,79 @@
     <t xml:space="preserve">5.87721490859985</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88546991348267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93499660491943</t>
+    <t xml:space="preserve">5.88546943664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93499612808228</t>
   </si>
   <si>
     <t xml:space="preserve">6.02579593658447</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0670690536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38899517059326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19914150238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04230499267578</t>
+    <t xml:space="preserve">6.06706857681274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38899421691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19914102554321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04230403900146</t>
   </si>
   <si>
     <t xml:space="preserve">6.05881452560425</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95150518417358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17437791824341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1760196685791</t>
+    <t xml:space="preserve">5.9515061378479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17437744140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17601919174194</t>
   </si>
   <si>
     <t xml:space="preserve">6.29349803924561</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25993251800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20958471298218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09210538864136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10888910293579</t>
+    <t xml:space="preserve">6.25993204116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20958423614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09210586547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10888862609863</t>
   </si>
   <si>
     <t xml:space="preserve">6.14245367050171</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05854034423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02497529983521</t>
+    <t xml:space="preserve">6.05854082107544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02497482299805</t>
   </si>
   <si>
     <t xml:space="preserve">5.97462797164917</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95784473419189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15923643112183</t>
+    <t xml:space="preserve">5.95784425735474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15923690795898</t>
   </si>
   <si>
     <t xml:space="preserve">6.12567138671875</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1928014755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42775917053223</t>
+    <t xml:space="preserve">6.19280195236206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42775964736938</t>
   </si>
   <si>
     <t xml:space="preserve">6.71306467056274</t>
@@ -1142,37 +1142,37 @@
     <t xml:space="preserve">6.69628190994263</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78019571304321</t>
+    <t xml:space="preserve">6.78019523620605</t>
   </si>
   <si>
     <t xml:space="preserve">6.7298469543457</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62915086746216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56201982498169</t>
+    <t xml:space="preserve">6.629150390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56202030181885</t>
   </si>
   <si>
     <t xml:space="preserve">6.54523801803589</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67949867248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66271638870239</t>
+    <t xml:space="preserve">6.67949914932251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66271734237671</t>
   </si>
   <si>
     <t xml:space="preserve">6.57880306243896</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37741136550903</t>
+    <t xml:space="preserve">6.37741088867188</t>
   </si>
   <si>
     <t xml:space="preserve">6.34384632110596</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22636795043945</t>
+    <t xml:space="preserve">6.22636747360229</t>
   </si>
   <si>
     <t xml:space="preserve">6.36062860488892</t>
@@ -1181,64 +1181,64 @@
     <t xml:space="preserve">5.67253875732422</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55506038665771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68932294845581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62219142913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5382776260376</t>
+    <t xml:space="preserve">5.55505990982056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68932199478149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62219190597534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53827810287476</t>
   </si>
   <si>
     <t xml:space="preserve">5.43758249282837</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45436573028564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60540866851807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5214958190918</t>
+    <t xml:space="preserve">5.45436525344849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60540819168091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52149629592896</t>
   </si>
   <si>
     <t xml:space="preserve">5.50471258163452</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48792934417725</t>
+    <t xml:space="preserve">5.4879298210144</t>
   </si>
   <si>
     <t xml:space="preserve">5.35366868972778</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37045097351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42079973220825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28653812408447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30332136154175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26975536346436</t>
+    <t xml:space="preserve">5.37045049667358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42079877853394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28653860092163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30332088470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26975584030151</t>
   </si>
   <si>
     <t xml:space="preserve">5.38723421096802</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32010364532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65575695037842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75645351409912</t>
+    <t xml:space="preserve">5.32010316848755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65575647354126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75645303726196</t>
   </si>
   <si>
     <t xml:space="preserve">5.70610475540161</t>
@@ -1256,22 +1256,22 @@
     <t xml:space="preserve">5.57184410095215</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18584203720093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20262479782104</t>
+    <t xml:space="preserve">5.18584156036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2026252746582</t>
   </si>
   <si>
     <t xml:space="preserve">5.21940803527832</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16905975341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13549375534058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10192918777466</t>
+    <t xml:space="preserve">5.16906023025513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13549327850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1019287109375</t>
   </si>
   <si>
     <t xml:space="preserve">4.95088481903076</t>
@@ -1286,13 +1286,13 @@
     <t xml:space="preserve">5.11871147155762</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06836366653442</t>
+    <t xml:space="preserve">5.06836318969727</t>
   </si>
   <si>
     <t xml:space="preserve">5.08514642715454</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23619031906128</t>
+    <t xml:space="preserve">5.23618984222412</t>
   </si>
   <si>
     <t xml:space="preserve">5.25297260284424</t>
@@ -1301,25 +1301,25 @@
     <t xml:space="preserve">5.33688640594482</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79001712799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77323484420776</t>
+    <t xml:space="preserve">5.79001760482788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77323532104492</t>
   </si>
   <si>
     <t xml:space="preserve">5.58862638473511</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81662368774414</t>
+    <t xml:space="preserve">4.81662321090698</t>
   </si>
   <si>
     <t xml:space="preserve">4.79984140396118</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59844827651978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36349153518677</t>
+    <t xml:space="preserve">4.59844875335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36349201202393</t>
   </si>
   <si>
     <t xml:space="preserve">4.31314373016357</t>
@@ -1331,16 +1331,16 @@
     <t xml:space="preserve">4.11175203323364</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02783870697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17049121856689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06979560852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12014293670654</t>
+    <t xml:space="preserve">4.02783823013306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17049074172974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06979513168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1201434135437</t>
   </si>
   <si>
     <t xml:space="preserve">4.34670877456665</t>
@@ -1349,28 +1349,28 @@
     <t xml:space="preserve">4.17888164520264</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04462146759033</t>
+    <t xml:space="preserve">4.04462099075317</t>
   </si>
   <si>
     <t xml:space="preserve">4.15370845794678</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26279640197754</t>
+    <t xml:space="preserve">4.26279592514038</t>
   </si>
   <si>
     <t xml:space="preserve">4.16209983825684</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14531755447388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9942729473114</t>
+    <t xml:space="preserve">4.14531803131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99427270889282</t>
   </si>
   <si>
     <t xml:space="preserve">4.09496927261353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98588132858276</t>
+    <t xml:space="preserve">3.98588180541992</t>
   </si>
   <si>
     <t xml:space="preserve">4.2795786857605</t>
@@ -1391,10 +1391,10 @@
     <t xml:space="preserve">4.16283130645752</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07770204544067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00108432769775</t>
+    <t xml:space="preserve">4.07770156860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00108480453491</t>
   </si>
   <si>
     <t xml:space="preserve">4.20539569854736</t>
@@ -1403,22 +1403,22 @@
     <t xml:space="preserve">4.37565422058105</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21390819549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22242212295532</t>
+    <t xml:space="preserve">4.21390867233276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22242164611816</t>
   </si>
   <si>
     <t xml:space="preserve">4.25647354125977</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24796009063721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32457637786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30755090713501</t>
+    <t xml:space="preserve">4.24796056747437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32457685470581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30755138397217</t>
   </si>
   <si>
     <t xml:space="preserve">4.23944759368896</t>
@@ -1436,13 +1436,13 @@
     <t xml:space="preserve">5.94203662872314</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89095878601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73772621154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5504412651062</t>
+    <t xml:space="preserve">5.8909592628479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73772573471069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55044078826904</t>
   </si>
   <si>
     <t xml:space="preserve">5.5844931602478</t>
@@ -1457,37 +1457,37 @@
     <t xml:space="preserve">5.2610011100769</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48233842849731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44828653335571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60151863098145</t>
+    <t xml:space="preserve">5.482337474823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4482855796814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6015191078186</t>
   </si>
   <si>
     <t xml:space="preserve">5.66962289810181</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51638889312744</t>
+    <t xml:space="preserve">5.5163893699646</t>
   </si>
   <si>
     <t xml:space="preserve">5.70367431640625</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32910442352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27802705764771</t>
+    <t xml:space="preserve">5.32910490036011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27802658081055</t>
   </si>
   <si>
     <t xml:space="preserve">5.43126010894775</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31207895278931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22694873809814</t>
+    <t xml:space="preserve">5.31207847595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2269492149353</t>
   </si>
   <si>
     <t xml:space="preserve">5.00561237335205</t>
@@ -1526,28 +1526,28 @@
     <t xml:space="preserve">4.8694052696228</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34613037109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2439751625061</t>
+    <t xml:space="preserve">5.34613084793091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24397563934326</t>
   </si>
   <si>
     <t xml:space="preserve">5.36315631866455</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38018226623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2099232673645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1588454246521</t>
+    <t xml:space="preserve">5.38018274307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20992374420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15884637832642</t>
   </si>
   <si>
     <t xml:space="preserve">5.10776805877686</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98858642578125</t>
+    <t xml:space="preserve">4.98858737945557</t>
   </si>
   <si>
     <t xml:space="preserve">5.09074211120605</t>
@@ -1556,13 +1556,13 @@
     <t xml:space="preserve">5.1928973197937</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17587089538574</t>
+    <t xml:space="preserve">5.1758713722229</t>
   </si>
   <si>
     <t xml:space="preserve">5.1418194770813</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07371664047241</t>
+    <t xml:space="preserve">5.07371616363525</t>
   </si>
   <si>
     <t xml:space="preserve">4.68212080001831</t>
@@ -1571,13 +1571,13 @@
     <t xml:space="preserve">4.54591369628906</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59699153900146</t>
+    <t xml:space="preserve">4.59699058532715</t>
   </si>
   <si>
     <t xml:space="preserve">4.57996559143066</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63104295730591</t>
+    <t xml:space="preserve">4.63104248046875</t>
   </si>
   <si>
     <t xml:space="preserve">4.78427600860596</t>
@@ -1586,19 +1586,19 @@
     <t xml:space="preserve">4.76725006103516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8183274269104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8013014793396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39720869064331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6185450553894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46531200408936</t>
+    <t xml:space="preserve">4.81832790374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80130195617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39720821380615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61854457855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4653115272522</t>
   </si>
   <si>
     <t xml:space="preserve">5.49936389923096</t>
@@ -1607,25 +1607,25 @@
     <t xml:space="preserve">5.63557100296021</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68664836883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65259695053101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85690689086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8739333152771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31660604476929</t>
+    <t xml:space="preserve">5.68664789199829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65259647369385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8569073677063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87393283843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31660652160645</t>
   </si>
   <si>
     <t xml:space="preserve">6.33363246917725</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2995810508728</t>
+    <t xml:space="preserve">6.29958057403564</t>
   </si>
   <si>
     <t xml:space="preserve">6.35065841674805</t>
@@ -1640,13 +1640,13 @@
     <t xml:space="preserve">6.69117641448975</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79333114624023</t>
+    <t xml:space="preserve">6.79333162307739</t>
   </si>
   <si>
     <t xml:space="preserve">7.15087461471558</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08277130126953</t>
+    <t xml:space="preserve">7.08277082443237</t>
   </si>
   <si>
     <t xml:space="preserve">6.87846088409424</t>
@@ -1658,13 +1658,13 @@
     <t xml:space="preserve">6.84440898895264</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70820283889771</t>
+    <t xml:space="preserve">6.70820236206055</t>
   </si>
   <si>
     <t xml:space="preserve">6.75927972793579</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5379433631897</t>
+    <t xml:space="preserve">6.53794288635254</t>
   </si>
   <si>
     <t xml:space="preserve">6.72522783279419</t>
@@ -1673,16 +1673,16 @@
     <t xml:space="preserve">6.6571249961853</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91251230239868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8954873085022</t>
+    <t xml:space="preserve">6.91251277923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89548683166504</t>
   </si>
   <si>
     <t xml:space="preserve">6.96359062194824</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17302227020264</t>
+    <t xml:space="preserve">7.17302179336548</t>
   </si>
   <si>
     <t xml:space="preserve">7.05085372924805</t>
@@ -1691,70 +1691,70 @@
     <t xml:space="preserve">7.1206636428833</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57443237304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97584247589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02820014953613</t>
+    <t xml:space="preserve">7.57443284988403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97584199905396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0281982421875</t>
   </si>
   <si>
     <t xml:space="preserve">8.0631046295166</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99329519271851</t>
+    <t xml:space="preserve">7.99329423904419</t>
   </si>
   <si>
     <t xml:space="preserve">8.0107479095459</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94093656539917</t>
+    <t xml:space="preserve">7.94093704223633</t>
   </si>
   <si>
     <t xml:space="preserve">8.13291454315186</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15036869049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16781997680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18527412414551</t>
+    <t xml:space="preserve">8.15036773681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16782093048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18527317047119</t>
   </si>
   <si>
     <t xml:space="preserve">8.34234714508057</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11546230316162</t>
+    <t xml:space="preserve">8.11546325683594</t>
   </si>
   <si>
     <t xml:space="preserve">8.25508308410645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08055782318115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20272445678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95838832855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37725162506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3248929977417</t>
+    <t xml:space="preserve">8.08055686950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20272541046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95838928222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37725257873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32489395141602</t>
   </si>
   <si>
     <t xml:space="preserve">8.81356716156006</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58668327331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53432464599609</t>
+    <t xml:space="preserve">8.58668231964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53432559967041</t>
   </si>
   <si>
     <t xml:space="preserve">8.69139862060547</t>
@@ -1766,22 +1766,22 @@
     <t xml:space="preserve">8.72630405426025</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42961025238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28998756408691</t>
+    <t xml:space="preserve">8.42960929870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28998947143555</t>
   </si>
   <si>
     <t xml:space="preserve">8.30744171142578</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04565238952637</t>
+    <t xml:space="preserve">8.04565334320068</t>
   </si>
   <si>
     <t xml:space="preserve">7.85367345809937</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41215705871582</t>
+    <t xml:space="preserve">8.41215801239014</t>
   </si>
   <si>
     <t xml:space="preserve">8.22017765045166</t>
@@ -1793,28 +1793,28 @@
     <t xml:space="preserve">8.35979843139648</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09801006317139</t>
+    <t xml:space="preserve">8.09800910949707</t>
   </si>
   <si>
     <t xml:space="preserve">8.23763084411621</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48196792602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6215877532959</t>
+    <t xml:space="preserve">8.48196697235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62158870697021</t>
   </si>
   <si>
     <t xml:space="preserve">8.55177783966064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65649318695068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51687335968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46451473236084</t>
+    <t xml:space="preserve">8.656494140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51687240600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46451377868652</t>
   </si>
   <si>
     <t xml:space="preserve">8.49942016601562</t>
@@ -1829,16 +1829,16 @@
     <t xml:space="preserve">9.59893417358398</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77346038818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81709289550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29351234436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46804046630859</t>
+    <t xml:space="preserve">9.77345943450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8170919418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29351329803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46803951263428</t>
   </si>
   <si>
     <t xml:space="preserve">9.55530261993408</t>
@@ -1847,7 +1847,7 @@
     <t xml:space="preserve">9.64256572723389</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90435600280762</t>
+    <t xml:space="preserve">9.9043550491333</t>
   </si>
   <si>
     <t xml:space="preserve">9.33714580535889</t>
@@ -1856,7 +1856,7 @@
     <t xml:space="preserve">9.9479866027832</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8607234954834</t>
+    <t xml:space="preserve">9.86072254180908</t>
   </si>
   <si>
     <t xml:space="preserve">10.5151958465576</t>
@@ -1868,13 +1868,13 @@
     <t xml:space="preserve">10.5588283538818</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6024580001831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8206176757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7333545684814</t>
+    <t xml:space="preserve">10.6024589538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8206157684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7333536148071</t>
   </si>
   <si>
     <t xml:space="preserve">10.7769861221313</t>
@@ -1895,37 +1895,37 @@
     <t xml:space="preserve">10.2534065246582</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0788812637329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51167011260986</t>
+    <t xml:space="preserve">10.0788822174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51167106628418</t>
   </si>
   <si>
     <t xml:space="preserve">9.72982883453369</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68619728088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98809432983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42440891265869</t>
+    <t xml:space="preserve">9.68619823455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98809337615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42440795898438</t>
   </si>
   <si>
     <t xml:space="preserve">11.6496162414551</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5623531341553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7805109024048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9114036560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9550352096558</t>
+    <t xml:space="preserve">11.562352180481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7805099487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9114046096802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9550361633301</t>
   </si>
   <si>
     <t xml:space="preserve">11.693247795105</t>
@@ -1937,10 +1937,10 @@
     <t xml:space="preserve">12.2604570388794</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2168254852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3913516998291</t>
+    <t xml:space="preserve">12.2168245315552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3913507461548</t>
   </si>
   <si>
     <t xml:space="preserve">11.7368783950806</t>
@@ -1949,7 +1949,7 @@
     <t xml:space="preserve">11.8677730560303</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6059846878052</t>
+    <t xml:space="preserve">11.6059837341309</t>
   </si>
   <si>
     <t xml:space="preserve">10.9515113830566</t>
@@ -1964,13 +1964,13 @@
     <t xml:space="preserve">11.3441944122314</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9951419830322</t>
+    <t xml:space="preserve">10.9951429367065</t>
   </si>
   <si>
     <t xml:space="preserve">10.4715642929077</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9078798294067</t>
+    <t xml:space="preserve">10.9078807830811</t>
   </si>
   <si>
     <t xml:space="preserve">11.4314584732056</t>
@@ -1988,10 +1988,10 @@
     <t xml:space="preserve">11.5361728668213</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5187206268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6234369277954</t>
+    <t xml:space="preserve">11.5187215805054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6234359741211</t>
   </si>
   <si>
     <t xml:space="preserve">11.4489107131958</t>
@@ -2000,10 +2000,10 @@
     <t xml:space="preserve">11.64089012146</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7281522750854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.920129776001</t>
+    <t xml:space="preserve">11.7281513214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9201307296753</t>
   </si>
   <si>
     <t xml:space="preserve">11.1173105239868</t>
@@ -2015,10 +2015,10 @@
     <t xml:space="preserve">10.8031644821167</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7508058547974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3319444656372</t>
+    <t xml:space="preserve">10.7508068084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3319435119629</t>
   </si>
   <si>
     <t xml:space="preserve">10.1050596237183</t>
@@ -69377,7 +69377,7 @@
     </row>
     <row r="2521">
       <c r="A2521" s="1" t="n">
-        <v>45988.6910185185</v>
+        <v>45988.3333333333</v>
       </c>
       <c r="B2521" t="n">
         <v>27855</v>
@@ -69398,6 +69398,32 @@
         <v>1168</v>
       </c>
       <c r="H2521" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2522">
+      <c r="A2522" s="1" t="n">
+        <v>45989.6909722222</v>
+      </c>
+      <c r="B2522" t="n">
+        <v>17799</v>
+      </c>
+      <c r="C2522" t="n">
+        <v>17.6200008392334</v>
+      </c>
+      <c r="D2522" t="n">
+        <v>17.3400001525879</v>
+      </c>
+      <c r="E2522" t="n">
+        <v>17.3400001525879</v>
+      </c>
+      <c r="F2522" t="n">
+        <v>17.6200008392334</v>
+      </c>
+      <c r="G2522" t="s">
+        <v>1155</v>
+      </c>
+      <c r="H2522" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ORS.MI.xlsx
+++ b/data/ORS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1173" uniqueCount="1173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1174" uniqueCount="1174">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,43 +38,43 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08406448364258</t>
+    <t xml:space="preserve">8.08406352996826</t>
   </si>
   <si>
     <t xml:space="preserve">ORS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98275804519653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06380176544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94223785400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8247241973877</t>
+    <t xml:space="preserve">7.98275995254517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06380271911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94223880767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82472562789917</t>
   </si>
   <si>
     <t xml:space="preserve">7.93818616867065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90171432495117</t>
+    <t xml:space="preserve">7.9017162322998</t>
   </si>
   <si>
     <t xml:space="preserve">8.03948879241943</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92602872848511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8611946105957</t>
+    <t xml:space="preserve">7.92603063583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86119413375854</t>
   </si>
   <si>
     <t xml:space="preserve">7.82067203521729</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9341344833374</t>
+    <t xml:space="preserve">7.93413352966309</t>
   </si>
   <si>
     <t xml:space="preserve">8.02328109741211</t>
@@ -86,58 +86,58 @@
     <t xml:space="preserve">8.14484596252441</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69910764694214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8044638633728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97465372085571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0111255645752</t>
+    <t xml:space="preserve">7.69910669326782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80446529388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97465467453003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01112365722656</t>
   </si>
   <si>
     <t xml:space="preserve">8.01517677307129</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79230785369873</t>
+    <t xml:space="preserve">7.79230737686157</t>
   </si>
   <si>
     <t xml:space="preserve">7.82877826690674</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34745216369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84093332290649</t>
+    <t xml:space="preserve">8.34745311737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84093236923218</t>
   </si>
   <si>
     <t xml:space="preserve">7.90982103347778</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85714197158813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78015089035034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84498500823975</t>
+    <t xml:space="preserve">7.85714054107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7801513671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84498596191406</t>
   </si>
   <si>
     <t xml:space="preserve">7.97870635986328</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88550758361816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95034313201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00301933288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0192289352417</t>
+    <t xml:space="preserve">7.88550662994385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95034217834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00302124023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01922798156738</t>
   </si>
   <si>
     <t xml:space="preserve">7.91792440414429</t>
@@ -146,13 +146,13 @@
     <t xml:space="preserve">8.1002721786499</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10432243347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1853666305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20157527923584</t>
+    <t xml:space="preserve">8.10432434082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18536567687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20157623291016</t>
   </si>
   <si>
     <t xml:space="preserve">8.11242866516113</t>
@@ -167,16 +167,16 @@
     <t xml:space="preserve">8.09621906280518</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17726135253906</t>
+    <t xml:space="preserve">8.17726230621338</t>
   </si>
   <si>
     <t xml:space="preserve">8.05569744110107</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12053394317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25830745697021</t>
+    <t xml:space="preserve">8.12053203582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2583065032959</t>
   </si>
   <si>
     <t xml:space="preserve">8.42039203643799</t>
@@ -185,37 +185,37 @@
     <t xml:space="preserve">8.67162609100342</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55816555023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42849636077881</t>
+    <t xml:space="preserve">8.55816650390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42849731445312</t>
   </si>
   <si>
     <t xml:space="preserve">8.52429008483887</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45921897888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50802135467529</t>
+    <t xml:space="preserve">8.45921993255615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50802230834961</t>
   </si>
   <si>
     <t xml:space="preserve">8.60562801361084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53242492675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61376190185547</t>
+    <t xml:space="preserve">8.53242301940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61376094818115</t>
   </si>
   <si>
     <t xml:space="preserve">8.67069911956787</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87404632568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79270648956299</t>
+    <t xml:space="preserve">8.87404537200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7927074432373</t>
   </si>
   <si>
     <t xml:space="preserve">8.90658092498779</t>
@@ -230,40 +230,40 @@
     <t xml:space="preserve">8.93911647796631</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78457355499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74390316009521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91471481323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92284965515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10992813110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07739162445068</t>
+    <t xml:space="preserve">8.78457260131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74390411376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91471576690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92284870147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10992908477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.077392578125</t>
   </si>
   <si>
     <t xml:space="preserve">9.11806201934814</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13432884216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15059852600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15873241424561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7357702255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67883205413818</t>
+    <t xml:space="preserve">9.1343297958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15059757232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15873146057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73576927185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67883110046387</t>
   </si>
   <si>
     <t xml:space="preserve">8.85777759552002</t>
@@ -275,10 +275,10 @@
     <t xml:space="preserve">8.70323467254639</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66256523132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69510078430176</t>
+    <t xml:space="preserve">8.66256618499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69510173797607</t>
   </si>
   <si>
     <t xml:space="preserve">8.62189674377441</t>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">8.80084133148193</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77643966674805</t>
+    <t xml:space="preserve">8.77643871307373</t>
   </si>
   <si>
     <t xml:space="preserve">8.68696784973145</t>
@@ -296,43 +296,43 @@
     <t xml:space="preserve">8.54869174957275</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54055690765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58122825622559</t>
+    <t xml:space="preserve">8.54055595397949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58122730255127</t>
   </si>
   <si>
     <t xml:space="preserve">8.46735286712646</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51615524291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49988651275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45108413696289</t>
+    <t xml:space="preserve">8.51615619659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49988842010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45108318328857</t>
   </si>
   <si>
     <t xml:space="preserve">8.63003063201904</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80897617340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89031410217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93098258972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96351718902588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05299091339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30514144897461</t>
+    <t xml:space="preserve">8.80897521972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89031505584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93098449707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9635181427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0529899597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30514049530029</t>
   </si>
   <si>
     <t xml:space="preserve">9.10179424285889</t>
@@ -341,7 +341,7 @@
     <t xml:space="preserve">9.19126605987549</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35394382476807</t>
+    <t xml:space="preserve">9.35394287109375</t>
   </si>
   <si>
     <t xml:space="preserve">9.47595119476318</t>
@@ -353,22 +353,22 @@
     <t xml:space="preserve">9.58982563018799</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66303062438965</t>
+    <t xml:space="preserve">9.66303157806396</t>
   </si>
   <si>
     <t xml:space="preserve">9.71996688842773</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85824203491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0046548843384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2405338287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2486686706543</t>
+    <t xml:space="preserve">9.85824298858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0046539306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.240535736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2486696243286</t>
   </si>
   <si>
     <t xml:space="preserve">10.3381414413452</t>
@@ -377,10 +377,10 @@
     <t xml:space="preserve">10.5984258651733</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4276132583618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4032115936279</t>
+    <t xml:space="preserve">10.4276142120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4032125473022</t>
   </si>
   <si>
     <t xml:space="preserve">10.5252199172974</t>
@@ -395,13 +395,13 @@
     <t xml:space="preserve">10.5821571350098</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7773704528809</t>
+    <t xml:space="preserve">10.7773694992065</t>
   </si>
   <si>
     <t xml:space="preserve">10.9807167053223</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8749761581421</t>
+    <t xml:space="preserve">10.8749771118164</t>
   </si>
   <si>
     <t xml:space="preserve">10.6553630828857</t>
@@ -410,7 +410,7 @@
     <t xml:space="preserve">10.6797637939453</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5740251541138</t>
+    <t xml:space="preserve">10.5740232467651</t>
   </si>
   <si>
     <t xml:space="preserve">10.5170869827271</t>
@@ -422,28 +422,28 @@
     <t xml:space="preserve">10.5577554702759</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5089540481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.818039894104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6878986358643</t>
+    <t xml:space="preserve">10.5089511871338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8180389404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6878967285156</t>
   </si>
   <si>
     <t xml:space="preserve">10.7611017227173</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6472282409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.899377822876</t>
+    <t xml:space="preserve">10.6472291946411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8993787765503</t>
   </si>
   <si>
     <t xml:space="preserve">10.8831100463867</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6716289520264</t>
+    <t xml:space="preserve">10.6716299057007</t>
   </si>
   <si>
     <t xml:space="preserve">10.736701965332</t>
@@ -458,10 +458,10 @@
     <t xml:space="preserve">11.184063911438</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4036769866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3955421447754</t>
+    <t xml:space="preserve">11.4036779403687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3955430984497</t>
   </si>
   <si>
     <t xml:space="preserve">11.3386068344116</t>
@@ -473,22 +473,22 @@
     <t xml:space="preserve">11.3304738998413</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3630094528198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0783233642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.606559753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8424415588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8505754470825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6390933990479</t>
+    <t xml:space="preserve">11.3630084991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0783243179321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6065587997437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8424425125122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8505744934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6390943527222</t>
   </si>
   <si>
     <t xml:space="preserve">10.4113464355469</t>
@@ -497,25 +497,25 @@
     <t xml:space="preserve">10.2080011367798</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2730712890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2324018478394</t>
+    <t xml:space="preserve">10.2730703353882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2323999404907</t>
   </si>
   <si>
     <t xml:space="preserve">10.3218746185303</t>
   </si>
   <si>
-    <t xml:space="preserve">10.370677947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3300075531006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3056058883667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2568044662476</t>
+    <t xml:space="preserve">10.3706760406494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3300085067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3056049346924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2568035125732</t>
   </si>
   <si>
     <t xml:space="preserve">10.1835985183716</t>
@@ -527,19 +527,19 @@
     <t xml:space="preserve">10.3625431060791</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4438810348511</t>
+    <t xml:space="preserve">10.4438819885254</t>
   </si>
   <si>
     <t xml:space="preserve">10.8587083816528</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9237794876099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0376539230347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0620555877686</t>
+    <t xml:space="preserve">10.9237813949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.037652015686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0620565414429</t>
   </si>
   <si>
     <t xml:space="preserve">11.1027250289917</t>
@@ -548,58 +548,58 @@
     <t xml:space="preserve">11.1433944702148</t>
   </si>
   <si>
-    <t xml:space="preserve">11.175929069519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1352596282959</t>
+    <t xml:space="preserve">11.1759281158447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1352605819702</t>
   </si>
   <si>
     <t xml:space="preserve">11.0701904296875</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1189937591553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1515283584595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2247323989868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0457878112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5008192062378</t>
+    <t xml:space="preserve">11.118992805481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1515274047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2247333526611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.045786857605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5008182525635</t>
   </si>
   <si>
     <t xml:space="preserve">10.1347951889038</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36161136627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01998901367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10946273803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3941478729248</t>
+    <t xml:space="preserve">8.36161231994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01999092102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10946369171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39414691925049</t>
   </si>
   <si>
     <t xml:space="preserve">8.21520328521729</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3372106552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31280899047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18266582489014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34534549713135</t>
+    <t xml:space="preserve">8.33720970153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31281089782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18266677856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34534454345703</t>
   </si>
   <si>
     <t xml:space="preserve">8.23960494995117</t>
@@ -608,31 +608,31 @@
     <t xml:space="preserve">8.49175453186035</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58936023712158</t>
+    <t xml:space="preserve">8.58935928344727</t>
   </si>
   <si>
     <t xml:space="preserve">8.76017189025879</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29654216766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25587177276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17453384399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1908016204834</t>
+    <t xml:space="preserve">8.29654121398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25587368011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17453479766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19080066680908</t>
   </si>
   <si>
     <t xml:space="preserve">8.23147106170654</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28027439117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14199829101562</t>
+    <t xml:space="preserve">8.2802734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14199733734131</t>
   </si>
   <si>
     <t xml:space="preserve">8.15826511383057</t>
@@ -641,82 +641,82 @@
     <t xml:space="preserve">8.16640090942383</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12166309356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05252647399902</t>
+    <t xml:space="preserve">8.12166404724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05252456665039</t>
   </si>
   <si>
     <t xml:space="preserve">7.89798259735107</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85731267929077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93051671981812</t>
+    <t xml:space="preserve">7.85731363296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93051767349243</t>
   </si>
   <si>
     <t xml:space="preserve">7.90611553192139</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93865251541138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84917974472046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80850982666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62956571578979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57262754440308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48315572738647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66616725921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60516405105591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54009199142456</t>
+    <t xml:space="preserve">7.93865156173706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84917879104614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80851030349731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62956476211548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57262706756592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48315525054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66616678237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60516357421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54009294509888</t>
   </si>
   <si>
     <t xml:space="preserve">7.52382373809814</t>
   </si>
   <si>
-    <t xml:space="preserve">7.479088306427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6132960319519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54822540283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56449365615845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50755548477173</t>
+    <t xml:space="preserve">7.47908735275269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61329746246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54822587966919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56449413299561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5075569152832</t>
   </si>
   <si>
     <t xml:space="preserve">7.4668869972229</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4912896156311</t>
+    <t xml:space="preserve">7.49129009246826</t>
   </si>
   <si>
     <t xml:space="preserve">7.49942207336426</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31234502792358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27980852127075</t>
+    <t xml:space="preserve">7.31234455108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27980899810791</t>
   </si>
   <si>
     <t xml:space="preserve">7.3774151802063</t>
@@ -725,22 +725,22 @@
     <t xml:space="preserve">7.38554859161377</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36928033828735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3204779624939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34487962722778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28794240951538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04392576217651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15780067443848</t>
+    <t xml:space="preserve">7.36928129196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32047748565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34487915039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28794193267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04392528533936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15780162811279</t>
   </si>
   <si>
     <t xml:space="preserve">7.3936824798584</t>
@@ -755,10 +755,10 @@
     <t xml:space="preserve">7.3042106628418</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3611478805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20660352706909</t>
+    <t xml:space="preserve">7.36114740371704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20660400390625</t>
   </si>
   <si>
     <t xml:space="preserve">7.35301351547241</t>
@@ -767,13 +767,13 @@
     <t xml:space="preserve">7.33674573898315</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27167367935181</t>
+    <t xml:space="preserve">7.27167320251465</t>
   </si>
   <si>
     <t xml:space="preserve">7.23100519180298</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32861185073853</t>
+    <t xml:space="preserve">7.32861137390137</t>
   </si>
   <si>
     <t xml:space="preserve">7.26354074478149</t>
@@ -782,22 +782,22 @@
     <t xml:space="preserve">7.23913908004761</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22287130355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24727296829224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44248533248901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25540685653687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18220186233521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29607629776001</t>
+    <t xml:space="preserve">7.22287225723267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24727249145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44248628616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25540828704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18220233917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29607582092285</t>
   </si>
   <si>
     <t xml:space="preserve">7.16593408584595</t>
@@ -806,31 +806,31 @@
     <t xml:space="preserve">7.14153242111206</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0520601272583</t>
+    <t xml:space="preserve">7.05205965042114</t>
   </si>
   <si>
     <t xml:space="preserve">7.07646226882935</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03579235076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0195255279541</t>
+    <t xml:space="preserve">7.0357928276062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01952457427979</t>
   </si>
   <si>
     <t xml:space="preserve">6.87311458587646</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67790365219116</t>
+    <t xml:space="preserve">6.677903175354</t>
   </si>
   <si>
     <t xml:space="preserve">6.85124731063843</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93379163742065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26397323608398</t>
+    <t xml:space="preserve">6.93379211425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2639741897583</t>
   </si>
   <si>
     <t xml:space="preserve">7.14840936660767</t>
@@ -842,10 +842,10 @@
     <t xml:space="preserve">7.1814284324646</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16491937637329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14015579223633</t>
+    <t xml:space="preserve">7.16491889953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14015626907349</t>
   </si>
   <si>
     <t xml:space="preserve">7.21444606781006</t>
@@ -854,7 +854,7 @@
     <t xml:space="preserve">7.17317342758179</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97506427764893</t>
+    <t xml:space="preserve">6.97506475448608</t>
   </si>
   <si>
     <t xml:space="preserve">6.84299325942993</t>
@@ -866,22 +866,22 @@
     <t xml:space="preserve">6.62012100219727</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67790269851685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80997467041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54582977294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31470394134521</t>
+    <t xml:space="preserve">6.67790222167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80997514724731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54583024978638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31470441818237</t>
   </si>
   <si>
     <t xml:space="preserve">6.32295846939087</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34772253036499</t>
+    <t xml:space="preserve">6.34772205352783</t>
   </si>
   <si>
     <t xml:space="preserve">6.38074016571045</t>
@@ -890,7 +890,7 @@
     <t xml:space="preserve">6.39724922180176</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47154092788696</t>
+    <t xml:space="preserve">6.4715404510498</t>
   </si>
   <si>
     <t xml:space="preserve">6.2816858291626</t>
@@ -899,46 +899,46 @@
     <t xml:space="preserve">6.22390365600586</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09183263778687</t>
+    <t xml:space="preserve">6.09183216094971</t>
   </si>
   <si>
     <t xml:space="preserve">5.90197801589966</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95976066589355</t>
+    <t xml:space="preserve">5.9597601890564</t>
   </si>
   <si>
     <t xml:space="preserve">5.9927773475647</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20739555358887</t>
+    <t xml:space="preserve">6.20739507675171</t>
   </si>
   <si>
     <t xml:space="preserve">6.14135980606079</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1908860206604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14961338043213</t>
+    <t xml:space="preserve">6.19088649749756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14961385726929</t>
   </si>
   <si>
     <t xml:space="preserve">6.07532358169556</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25692272186279</t>
+    <t xml:space="preserve">6.25692319869995</t>
   </si>
   <si>
     <t xml:space="preserve">6.00928688049316</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9845232963562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12485074996948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13310432434082</t>
+    <t xml:space="preserve">5.98452377319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12485027313232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13310480117798</t>
   </si>
   <si>
     <t xml:space="preserve">6.27343130111694</t>
@@ -947,7 +947,7 @@
     <t xml:space="preserve">6.44677591323853</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55408525466919</t>
+    <t xml:space="preserve">6.55408477783203</t>
   </si>
   <si>
     <t xml:space="preserve">6.51281213760376</t>
@@ -956,25 +956,25 @@
     <t xml:space="preserve">6.3642315864563</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24041414260864</t>
+    <t xml:space="preserve">6.24041366577148</t>
   </si>
   <si>
     <t xml:space="preserve">6.21564960479736</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23215913772583</t>
+    <t xml:space="preserve">6.23215961456299</t>
   </si>
   <si>
     <t xml:space="preserve">6.24866819381714</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11659622192383</t>
+    <t xml:space="preserve">6.11659574508667</t>
   </si>
   <si>
     <t xml:space="preserve">6.10834074020386</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05055952072144</t>
+    <t xml:space="preserve">6.05055904388428</t>
   </si>
   <si>
     <t xml:space="preserve">5.89372396469116</t>
@@ -983,25 +983,25 @@
     <t xml:space="preserve">5.77816104888916</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69561529159546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79466915130615</t>
+    <t xml:space="preserve">5.6956148147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79466962814331</t>
   </si>
   <si>
     <t xml:space="preserve">5.80292320251465</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82768774032593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7864146232605</t>
+    <t xml:space="preserve">5.82768821716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78641510009766</t>
   </si>
   <si>
     <t xml:space="preserve">5.73688745498657</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85245180130005</t>
+    <t xml:space="preserve">5.85245132446289</t>
   </si>
   <si>
     <t xml:space="preserve">6.29819536209106</t>
@@ -1010,10 +1010,10 @@
     <t xml:space="preserve">6.1826319694519</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15786838531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03405094146729</t>
+    <t xml:space="preserve">6.1578688621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03404998779297</t>
   </si>
   <si>
     <t xml:space="preserve">6.08357763290405</t>
@@ -1028,10 +1028,10 @@
     <t xml:space="preserve">5.86070537567139</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76165246963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75339651107788</t>
+    <t xml:space="preserve">5.76165199279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75339698791504</t>
   </si>
   <si>
     <t xml:space="preserve">5.8111777305603</t>
@@ -1049,16 +1049,16 @@
     <t xml:space="preserve">5.71212482452393</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84419727325439</t>
+    <t xml:space="preserve">5.84419679641724</t>
   </si>
   <si>
     <t xml:space="preserve">5.94325113296509</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96801471710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87721538543701</t>
+    <t xml:space="preserve">5.96801424026489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8772144317627</t>
   </si>
   <si>
     <t xml:space="preserve">5.88546943664551</t>
@@ -1067,7 +1067,7 @@
     <t xml:space="preserve">5.93499612808228</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02579545974731</t>
+    <t xml:space="preserve">6.02579641342163</t>
   </si>
   <si>
     <t xml:space="preserve">6.06706857681274</t>
@@ -1076,16 +1076,16 @@
     <t xml:space="preserve">6.3889946937561</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19914102554321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04230499267578</t>
+    <t xml:space="preserve">6.19914054870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04230451583862</t>
   </si>
   <si>
     <t xml:space="preserve">6.05881452560425</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95150566101074</t>
+    <t xml:space="preserve">5.9515061378479</t>
   </si>
   <si>
     <t xml:space="preserve">6.17437744140625</t>
@@ -1094,10 +1094,10 @@
     <t xml:space="preserve">6.1760196685791</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29349756240845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25993251800537</t>
+    <t xml:space="preserve">6.29349803924561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25993299484253</t>
   </si>
   <si>
     <t xml:space="preserve">6.20958423614502</t>
@@ -1112,16 +1112,16 @@
     <t xml:space="preserve">6.0753231048584</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14245367050171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0585412979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02497482299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97462797164917</t>
+    <t xml:space="preserve">6.14245319366455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05854082107544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02497529983521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97462701797485</t>
   </si>
   <si>
     <t xml:space="preserve">5.95784425735474</t>
@@ -1130,10 +1130,10 @@
     <t xml:space="preserve">6.15923690795898</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12567090988159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19280242919922</t>
+    <t xml:space="preserve">6.12567186355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19280195236206</t>
   </si>
   <si>
     <t xml:space="preserve">6.42775917053223</t>
@@ -1148,49 +1148,49 @@
     <t xml:space="preserve">6.69628190994263</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78019523620605</t>
+    <t xml:space="preserve">6.7801947593689</t>
   </si>
   <si>
     <t xml:space="preserve">6.7298469543457</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62915086746216</t>
+    <t xml:space="preserve">6.629150390625</t>
   </si>
   <si>
     <t xml:space="preserve">6.56202030181885</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54523754119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67949867248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66271686553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57880401611328</t>
+    <t xml:space="preserve">6.54523801803589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67949914932251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66271638870239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57880353927612</t>
   </si>
   <si>
     <t xml:space="preserve">6.37741088867188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34384679794312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22636795043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36062860488892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67253923416138</t>
+    <t xml:space="preserve">6.34384632110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22636747360229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36062908172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67253875732422</t>
   </si>
   <si>
     <t xml:space="preserve">5.55506038665771</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68932199478149</t>
+    <t xml:space="preserve">5.68932247161865</t>
   </si>
   <si>
     <t xml:space="preserve">5.62219142913818</t>
@@ -1202,43 +1202,43 @@
     <t xml:space="preserve">5.43758249282837</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45436573028564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60540819168091</t>
+    <t xml:space="preserve">5.45436477661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60540866851807</t>
   </si>
   <si>
     <t xml:space="preserve">5.52149534225464</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50471258163452</t>
+    <t xml:space="preserve">5.50471305847168</t>
   </si>
   <si>
     <t xml:space="preserve">5.4879298210144</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35366868972778</t>
+    <t xml:space="preserve">5.35366916656494</t>
   </si>
   <si>
     <t xml:space="preserve">5.3704514503479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42079973220825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28653764724731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30332088470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26975536346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38723421096802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32010364532471</t>
+    <t xml:space="preserve">5.42079925537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28653812408447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30332040786743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26975584030151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38723468780518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32010412216187</t>
   </si>
   <si>
     <t xml:space="preserve">5.65575647354126</t>
@@ -1253,16 +1253,16 @@
     <t xml:space="preserve">5.72288703918457</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73967027664185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6389741897583</t>
+    <t xml:space="preserve">5.739670753479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63897466659546</t>
   </si>
   <si>
     <t xml:space="preserve">5.57184410095215</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18584203720093</t>
+    <t xml:space="preserve">5.18584156036377</t>
   </si>
   <si>
     <t xml:space="preserve">5.20262479782104</t>
@@ -1274,40 +1274,40 @@
     <t xml:space="preserve">5.16905975341797</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13549375534058</t>
+    <t xml:space="preserve">5.13549327850342</t>
   </si>
   <si>
     <t xml:space="preserve">5.10192918777466</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95088481903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03479909896851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15227651596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11871099472046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06836366653442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08514595031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23618984222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25297260284424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33688688278198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79001808166504</t>
+    <t xml:space="preserve">4.95088386535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03479814529419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15227699279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11871147155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06836318969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08514642715454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23619031906128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2529730796814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33688640594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79001760482788</t>
   </si>
   <si>
     <t xml:space="preserve">5.77323532104492</t>
@@ -1316,16 +1316,16 @@
     <t xml:space="preserve">5.58862590789795</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81662368774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79984140396118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59844827651978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36349201202393</t>
+    <t xml:space="preserve">4.81662321090698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79984092712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59844923019409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36349248886108</t>
   </si>
   <si>
     <t xml:space="preserve">4.31314373016357</t>
@@ -1334,43 +1334,43 @@
     <t xml:space="preserve">4.19566488265991</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11175107955933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02783870697021</t>
+    <t xml:space="preserve">4.11175155639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02783918380737</t>
   </si>
   <si>
     <t xml:space="preserve">4.17049074172974</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06979560852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12014293670654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34670877456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17888212203979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04462146759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15370845794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26279592514038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16209983825684</t>
+    <t xml:space="preserve">4.06979608535767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12014245986938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34670925140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17888164520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04462099075317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15370798110962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26279640197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16209936141968</t>
   </si>
   <si>
     <t xml:space="preserve">4.14531755447388</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99427247047424</t>
+    <t xml:space="preserve">3.99427318572998</t>
   </si>
   <si>
     <t xml:space="preserve">4.09496927261353</t>
@@ -1379,31 +1379,31 @@
     <t xml:space="preserve">3.98588132858276</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2795786857605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22922992706299</t>
+    <t xml:space="preserve">4.27957820892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22923040390015</t>
   </si>
   <si>
     <t xml:space="preserve">4.21244812011719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03622961044312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12877941131592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1628303527832</t>
+    <t xml:space="preserve">4.03623008728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1287784576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16283130645752</t>
   </si>
   <si>
     <t xml:space="preserve">4.07770156860352</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00108528137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20539522171021</t>
+    <t xml:space="preserve">4.00108480453491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20539569854736</t>
   </si>
   <si>
     <t xml:space="preserve">4.37565469741821</t>
@@ -1418,46 +1418,46 @@
     <t xml:space="preserve">4.25647354125977</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24795961380005</t>
+    <t xml:space="preserve">4.24796009063721</t>
   </si>
   <si>
     <t xml:space="preserve">4.32457685470581</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30755138397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23944759368896</t>
+    <t xml:space="preserve">4.30755043029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23944711685181</t>
   </si>
   <si>
     <t xml:space="preserve">4.35862827301025</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5118613243103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53341579437256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9420371055603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89095878601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73772573471069</t>
+    <t xml:space="preserve">4.51186227798462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5334153175354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94203662872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8909592628479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73772621154785</t>
   </si>
   <si>
     <t xml:space="preserve">5.5504412651062</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58449268341064</t>
+    <t xml:space="preserve">5.58449363708496</t>
   </si>
   <si>
     <t xml:space="preserve">5.567467212677</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41423416137695</t>
+    <t xml:space="preserve">5.41423463821411</t>
   </si>
   <si>
     <t xml:space="preserve">5.2610011100769</t>
@@ -1472,19 +1472,19 @@
     <t xml:space="preserve">5.60151863098145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66962242126465</t>
+    <t xml:space="preserve">5.66962194442749</t>
   </si>
   <si>
     <t xml:space="preserve">5.5163893699646</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70367383956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32910442352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27802658081055</t>
+    <t xml:space="preserve">5.70367479324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32910490036011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27802705764771</t>
   </si>
   <si>
     <t xml:space="preserve">5.43126010894775</t>
@@ -1493,7 +1493,7 @@
     <t xml:space="preserve">5.31207847595215</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22694969177246</t>
+    <t xml:space="preserve">5.2269492149353</t>
   </si>
   <si>
     <t xml:space="preserve">5.00561285018921</t>
@@ -1505,10 +1505,10 @@
     <t xml:space="preserve">4.93750905990601</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05669069290161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03966474533081</t>
+    <t xml:space="preserve">5.05669021606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03966426849365</t>
   </si>
   <si>
     <t xml:space="preserve">4.97156095504761</t>
@@ -1517,28 +1517,28 @@
     <t xml:space="preserve">4.88643074035645</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02263832092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92048358917236</t>
+    <t xml:space="preserve">5.02263879776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92048263549805</t>
   </si>
   <si>
     <t xml:space="preserve">4.90345764160156</t>
   </si>
   <si>
-    <t xml:space="preserve">4.852379322052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8694052696228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34613084793091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24397468566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36315679550171</t>
+    <t xml:space="preserve">4.85237979888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86940479278564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34613132476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24397563934326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36315631866455</t>
   </si>
   <si>
     <t xml:space="preserve">5.38018274307251</t>
@@ -1547,13 +1547,13 @@
     <t xml:space="preserve">5.2099232673645</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1588454246521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1077675819397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98858690261841</t>
+    <t xml:space="preserve">5.15884590148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10776805877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98858642578125</t>
   </si>
   <si>
     <t xml:space="preserve">5.09074211120605</t>
@@ -1562,13 +1562,13 @@
     <t xml:space="preserve">5.1928973197937</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1758713722229</t>
+    <t xml:space="preserve">5.17587184906006</t>
   </si>
   <si>
     <t xml:space="preserve">5.14181995391846</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07371664047241</t>
+    <t xml:space="preserve">5.0737156867981</t>
   </si>
   <si>
     <t xml:space="preserve">4.68212080001831</t>
@@ -1583,13 +1583,13 @@
     <t xml:space="preserve">4.57996511459351</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63104295730591</t>
+    <t xml:space="preserve">4.63104248046875</t>
   </si>
   <si>
     <t xml:space="preserve">4.78427600860596</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76725006103516</t>
+    <t xml:space="preserve">4.767249584198</t>
   </si>
   <si>
     <t xml:space="preserve">4.81832790374756</t>
@@ -1598,61 +1598,61 @@
     <t xml:space="preserve">4.8013014793396</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39720821380615</t>
+    <t xml:space="preserve">5.39720869064331</t>
   </si>
   <si>
     <t xml:space="preserve">5.6185450553894</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46531200408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4993634223938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63557100296021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68664836883545</t>
+    <t xml:space="preserve">5.46531248092651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49936389923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63557052612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68664884567261</t>
   </si>
   <si>
     <t xml:space="preserve">5.65259647369385</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8569073677063</t>
+    <t xml:space="preserve">5.85690784454346</t>
   </si>
   <si>
     <t xml:space="preserve">5.8739333152771</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3166069984436</t>
+    <t xml:space="preserve">6.31660652160645</t>
   </si>
   <si>
     <t xml:space="preserve">6.33363246917725</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29958009719849</t>
+    <t xml:space="preserve">6.2995810508728</t>
   </si>
   <si>
     <t xml:space="preserve">6.35065793991089</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43578720092773</t>
+    <t xml:space="preserve">6.43578767776489</t>
   </si>
   <si>
     <t xml:space="preserve">6.55496883392334</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69117641448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79333162307739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15087509155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08277177810669</t>
+    <t xml:space="preserve">6.69117593765259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79333114624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15087461471558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08277130126953</t>
   </si>
   <si>
     <t xml:space="preserve">6.87846088409424</t>
@@ -1661,22 +1661,22 @@
     <t xml:space="preserve">6.77630567550659</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84440946578979</t>
+    <t xml:space="preserve">6.84440851211548</t>
   </si>
   <si>
     <t xml:space="preserve">6.70820236206055</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75928020477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5379433631897</t>
+    <t xml:space="preserve">6.75927972793579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53794288635254</t>
   </si>
   <si>
     <t xml:space="preserve">6.72522783279419</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65712404251099</t>
+    <t xml:space="preserve">6.65712451934814</t>
   </si>
   <si>
     <t xml:space="preserve">6.91251230239868</t>
@@ -1685,37 +1685,37 @@
     <t xml:space="preserve">6.8954873085022</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96359062194824</t>
+    <t xml:space="preserve">6.96359014511108</t>
   </si>
   <si>
     <t xml:space="preserve">7.17302179336548</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05085372924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1206636428833</t>
+    <t xml:space="preserve">7.05085325241089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12066411972046</t>
   </si>
   <si>
     <t xml:space="preserve">7.57443237304688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97584247589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0281982421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06310558319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99329423904419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0107479095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94093656539917</t>
+    <t xml:space="preserve">7.97584199905396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02819919586182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0631046295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99329328536987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01074695587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94093799591064</t>
   </si>
   <si>
     <t xml:space="preserve">8.13291454315186</t>
@@ -1724,28 +1724,28 @@
     <t xml:space="preserve">8.15036773681641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16781997680664</t>
+    <t xml:space="preserve">8.16782093048096</t>
   </si>
   <si>
     <t xml:space="preserve">8.18527412414551</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34234809875488</t>
+    <t xml:space="preserve">8.34234619140625</t>
   </si>
   <si>
     <t xml:space="preserve">8.11546325683594</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25508308410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08055686950684</t>
+    <t xml:space="preserve">8.25508403778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08055782318115</t>
   </si>
   <si>
     <t xml:space="preserve">8.20272541046143</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95838832855225</t>
+    <t xml:space="preserve">7.95838928222656</t>
   </si>
   <si>
     <t xml:space="preserve">8.37725162506104</t>
@@ -1757,31 +1757,31 @@
     <t xml:space="preserve">8.81356716156006</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58668327331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53432464599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69139957427979</t>
+    <t xml:space="preserve">8.58668231964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53432559967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69139766693115</t>
   </si>
   <si>
     <t xml:space="preserve">8.60413551330566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72630310058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42960929870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28998851776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30744075775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04565238952637</t>
+    <t xml:space="preserve">8.72630405426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42961025238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28998947143555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30744171142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04565334320068</t>
   </si>
   <si>
     <t xml:space="preserve">7.85367345809937</t>
@@ -1793,37 +1793,37 @@
     <t xml:space="preserve">8.22017765045166</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44706249237061</t>
+    <t xml:space="preserve">8.44706153869629</t>
   </si>
   <si>
     <t xml:space="preserve">8.3597993850708</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09801006317139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23763084411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48196697235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62158870697021</t>
+    <t xml:space="preserve">8.09800910949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23762989044189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48196792602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6215877532959</t>
   </si>
   <si>
     <t xml:space="preserve">8.55177783966064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65649318695068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51687335968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46451473236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49941921234131</t>
+    <t xml:space="preserve">8.656494140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51687240600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46451377868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49942016601562</t>
   </si>
   <si>
     <t xml:space="preserve">8.56923007965088</t>
@@ -1841,7 +1841,7 @@
     <t xml:space="preserve">9.8170919418335</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29351329803467</t>
+    <t xml:space="preserve">9.29351425170898</t>
   </si>
   <si>
     <t xml:space="preserve">9.46804046630859</t>
@@ -1856,19 +1856,19 @@
     <t xml:space="preserve">9.9043550491333</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33714485168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94798564910889</t>
+    <t xml:space="preserve">9.33714580535889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9479866027832</t>
   </si>
   <si>
     <t xml:space="preserve">9.86072254180908</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5151958465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4279327392578</t>
+    <t xml:space="preserve">10.5151968002319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4279317855835</t>
   </si>
   <si>
     <t xml:space="preserve">10.5588274002075</t>
@@ -1880,37 +1880,37 @@
     <t xml:space="preserve">10.8206167221069</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7333536148071</t>
+    <t xml:space="preserve">10.7333545684814</t>
   </si>
   <si>
     <t xml:space="preserve">10.776985168457</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2970380783081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3843002319336</t>
+    <t xml:space="preserve">10.2970390319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3843011856079</t>
   </si>
   <si>
     <t xml:space="preserve">10.3406705856323</t>
   </si>
   <si>
-    <t xml:space="preserve">10.209774017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2534074783325</t>
+    <t xml:space="preserve">10.2097749710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2534065246582</t>
   </si>
   <si>
     <t xml:space="preserve">10.0788812637329</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51167011260986</t>
+    <t xml:space="preserve">9.51167106628418</t>
   </si>
   <si>
     <t xml:space="preserve">9.72982788085938</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68619728088379</t>
+    <t xml:space="preserve">9.68619823455811</t>
   </si>
   <si>
     <t xml:space="preserve">8.98809337615967</t>
@@ -1919,22 +1919,22 @@
     <t xml:space="preserve">9.42440795898438</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6496162414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.562352180481</t>
+    <t xml:space="preserve">11.6496152877808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5623531341553</t>
   </si>
   <si>
     <t xml:space="preserve">11.7805099487305</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9114036560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9550361633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6932468414307</t>
+    <t xml:space="preserve">11.9114046096802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9550352096558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.693247795105</t>
   </si>
   <si>
     <t xml:space="preserve">12.3040885925293</t>
@@ -1967,7 +1967,7 @@
     <t xml:space="preserve">11.3005638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3441944122314</t>
+    <t xml:space="preserve">11.3441953659058</t>
   </si>
   <si>
     <t xml:space="preserve">10.9951429367065</t>
@@ -1979,28 +1979,28 @@
     <t xml:space="preserve">10.9078798294067</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4314575195312</t>
+    <t xml:space="preserve">11.4314584732056</t>
   </si>
   <si>
     <t xml:space="preserve">11.0387735366821</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9899406433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.74560546875</t>
+    <t xml:space="preserve">11.9899415969849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7456045150757</t>
   </si>
   <si>
     <t xml:space="preserve">11.5361738204956</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5187206268311</t>
+    <t xml:space="preserve">11.5187215805054</t>
   </si>
   <si>
     <t xml:space="preserve">11.6234359741211</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4489107131958</t>
+    <t xml:space="preserve">11.4489116668701</t>
   </si>
   <si>
     <t xml:space="preserve">11.6408891677856</t>
@@ -2012,7 +2012,7 @@
     <t xml:space="preserve">11.9201307296753</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1173114776611</t>
+    <t xml:space="preserve">11.1173105239868</t>
   </si>
   <si>
     <t xml:space="preserve">11.0998592376709</t>
@@ -2021,13 +2021,13 @@
     <t xml:space="preserve">10.8031644821167</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7508058547974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3319444656372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1050605773926</t>
+    <t xml:space="preserve">10.7508068084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3319435119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1050596237183</t>
   </si>
   <si>
     <t xml:space="preserve">9.81839179992676</t>
@@ -2036,7 +2036,7 @@
     <t xml:space="preserve">9.69297409057617</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71089172363281</t>
+    <t xml:space="preserve">9.7108907699585</t>
   </si>
   <si>
     <t xml:space="preserve">10.1408929824829</t>
@@ -2045,10 +2045,10 @@
     <t xml:space="preserve">10.2663106918335</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3738107681274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1229772567749</t>
+    <t xml:space="preserve">10.3738117218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1229763031006</t>
   </si>
   <si>
     <t xml:space="preserve">10.1588106155396</t>
@@ -2063,13 +2063,13 @@
     <t xml:space="preserve">10.4633951187134</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7858963012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.570897102356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7142305374146</t>
+    <t xml:space="preserve">10.7858982086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5708961486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7142295837402</t>
   </si>
   <si>
     <t xml:space="preserve">10.7500638961792</t>
@@ -2081,16 +2081,16 @@
     <t xml:space="preserve">10.8754816055298</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6425638198853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.588812828064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5171461105347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8575639724731</t>
+    <t xml:space="preserve">10.6425628662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5888118743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5171451568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8575649261475</t>
   </si>
   <si>
     <t xml:space="preserve">10.9113149642944</t>
@@ -2102,16 +2102,16 @@
     <t xml:space="preserve">10.6604795455933</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3021440505981</t>
+    <t xml:space="preserve">10.3021450042725</t>
   </si>
   <si>
     <t xml:space="preserve">10.4096450805664</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3558950424194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6783971786499</t>
+    <t xml:space="preserve">10.3558940887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6783962249756</t>
   </si>
   <si>
     <t xml:space="preserve">10.4275617599487</t>
@@ -2120,10 +2120,10 @@
     <t xml:space="preserve">10.535062789917</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1800651550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.982982635498</t>
+    <t xml:space="preserve">11.1800661087036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9829816818237</t>
   </si>
   <si>
     <t xml:space="preserve">11.4846515655518</t>
@@ -2132,16 +2132,16 @@
     <t xml:space="preserve">11.3771505355835</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7354860305786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9146547317505</t>
+    <t xml:space="preserve">11.7354869842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9146537780762</t>
   </si>
   <si>
     <t xml:space="preserve">11.9325704574585</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0221548080444</t>
+    <t xml:space="preserve">12.0221538543701</t>
   </si>
   <si>
     <t xml:space="preserve">11.8788204193115</t>
@@ -2162,7 +2162,7 @@
     <t xml:space="preserve">12.3984069824219</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2013216018677</t>
+    <t xml:space="preserve">12.201322555542</t>
   </si>
   <si>
     <t xml:space="preserve">11.9863214492798</t>
@@ -2174,13 +2174,13 @@
     <t xml:space="preserve">12.6134080886841</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8463268280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8104934692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9179925918579</t>
+    <t xml:space="preserve">12.8463258743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.810492515564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9179935455322</t>
   </si>
   <si>
     <t xml:space="preserve">13.258412361145</t>
@@ -2192,16 +2192,16 @@
     <t xml:space="preserve">13.4375791549683</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6884145736694</t>
+    <t xml:space="preserve">13.6884136199951</t>
   </si>
   <si>
     <t xml:space="preserve">13.903416633606</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6559209823608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2438335418701</t>
+    <t xml:space="preserve">14.6559200286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2438344955444</t>
   </si>
   <si>
     <t xml:space="preserve">14.6380033493042</t>
@@ -2219,10 +2219,10 @@
     <t xml:space="preserve">14.7992544174194</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5484199523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4946689605713</t>
+    <t xml:space="preserve">14.5484189987183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4946699142456</t>
   </si>
   <si>
     <t xml:space="preserve">14.2617511749268</t>
@@ -2231,10 +2231,10 @@
     <t xml:space="preserve">14.8888387680054</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8171710968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.387167930603</t>
+    <t xml:space="preserve">14.8171720504761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3871688842773</t>
   </si>
   <si>
     <t xml:space="preserve">14.7634201049805</t>
@@ -2243,25 +2243,25 @@
     <t xml:space="preserve">14.6200866699219</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9067535400391</t>
+    <t xml:space="preserve">14.9067544937134</t>
   </si>
   <si>
     <t xml:space="preserve">15.1217546463013</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0321741104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7455034255981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0500888824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0680065155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1038398742676</t>
+    <t xml:space="preserve">15.0321731567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7455043792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.050087928772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0680055618286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1038408279419</t>
   </si>
   <si>
     <t xml:space="preserve">14.5305023193359</t>
@@ -2270,7 +2270,7 @@
     <t xml:space="preserve">14.7096710205078</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2080011367798</t>
+    <t xml:space="preserve">14.2080001831055</t>
   </si>
   <si>
     <t xml:space="preserve">13.6167469024658</t>
@@ -2306,10 +2306,10 @@
     <t xml:space="preserve">13.4913301467896</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2225790023804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2046613693237</t>
+    <t xml:space="preserve">13.2225780487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2046604156494</t>
   </si>
   <si>
     <t xml:space="preserve">13.0613269805908</t>
@@ -2321,10 +2321,10 @@
     <t xml:space="preserve">12.6313247680664</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0971612930298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0792436599731</t>
+    <t xml:space="preserve">13.0971603393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0792446136475</t>
   </si>
   <si>
     <t xml:space="preserve">12.8642425537109</t>
@@ -2336,7 +2336,7 @@
     <t xml:space="preserve">12.9538269042969</t>
   </si>
   <si>
-    <t xml:space="preserve">12.720908164978</t>
+    <t xml:space="preserve">12.7209091186523</t>
   </si>
   <si>
     <t xml:space="preserve">12.5596580505371</t>
@@ -2345,22 +2345,22 @@
     <t xml:space="preserve">13.1150779724121</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1509103775024</t>
+    <t xml:space="preserve">13.1509122848511</t>
   </si>
   <si>
     <t xml:space="preserve">13.5271635055542</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3479957580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2763290405273</t>
+    <t xml:space="preserve">13.3479948043823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.276328086853</t>
   </si>
   <si>
     <t xml:space="preserve">12.7925758361816</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5954914093018</t>
+    <t xml:space="preserve">12.5954923629761</t>
   </si>
   <si>
     <t xml:space="preserve">12.5238237380981</t>
@@ -2369,10 +2369,10 @@
     <t xml:space="preserve">12.5059070587158</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4879903793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3088235855103</t>
+    <t xml:space="preserve">12.4879894256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3088226318359</t>
   </si>
   <si>
     <t xml:space="preserve">12.5417413711548</t>
@@ -2381,7 +2381,7 @@
     <t xml:space="preserve">12.8284091949463</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3804903030396</t>
+    <t xml:space="preserve">12.3804893493652</t>
   </si>
   <si>
     <t xml:space="preserve">12.6671581268311</t>
@@ -2393,28 +2393,28 @@
     <t xml:space="preserve">12.6492414474487</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7746601104736</t>
+    <t xml:space="preserve">12.7746591567993</t>
   </si>
   <si>
     <t xml:space="preserve">12.4342403411865</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9504880905151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2192392349243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8250694274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1117382049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9684038162231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0400705337524</t>
+    <t xml:space="preserve">11.9504871368408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2192401885986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8250703811646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1117391586304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9684047698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0400714874268</t>
   </si>
   <si>
     <t xml:space="preserve">12.0042381286621</t>
@@ -2423,19 +2423,19 @@
     <t xml:space="preserve">12.255072593689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7388257980347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7421655654907</t>
+    <t xml:space="preserve">12.7388248443604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7421646118164</t>
   </si>
   <si>
     <t xml:space="preserve">13.7063312530518</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0825843811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0109157562256</t>
+    <t xml:space="preserve">14.0825834274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0109167098999</t>
   </si>
   <si>
     <t xml:space="preserve">13.7242479324341</t>
@@ -2444,7 +2444,7 @@
     <t xml:space="preserve">14.0467500686646</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0646667480469</t>
+    <t xml:space="preserve">14.0646657943726</t>
   </si>
   <si>
     <t xml:space="preserve">13.9392490386963</t>
@@ -2462,22 +2462,22 @@
     <t xml:space="preserve">13.9571657180786</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8496656417847</t>
+    <t xml:space="preserve">13.8496646881104</t>
   </si>
   <si>
     <t xml:space="preserve">13.9750833511353</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5450792312622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4734125137329</t>
+    <t xml:space="preserve">13.5450801849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4734134674072</t>
   </si>
   <si>
     <t xml:space="preserve">13.1867456436157</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3838291168213</t>
+    <t xml:space="preserve">13.383828163147</t>
   </si>
   <si>
     <t xml:space="preserve">13.5988302230835</t>
@@ -2498,16 +2498,16 @@
     <t xml:space="preserve">12.0759048461914</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5742349624634</t>
+    <t xml:space="preserve">11.5742359161377</t>
   </si>
   <si>
     <t xml:space="preserve">11.2159004211426</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3592338562012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4309024810791</t>
+    <t xml:space="preserve">11.3592348098755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4309015274048</t>
   </si>
   <si>
     <t xml:space="preserve">11.3054828643799</t>
@@ -2516,13 +2516,13 @@
     <t xml:space="preserve">11.2875671386719</t>
   </si>
   <si>
-    <t xml:space="preserve">11.683783531189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5179262161255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2783517837524</t>
+    <t xml:space="preserve">11.6837844848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5179252624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2783527374268</t>
   </si>
   <si>
     <t xml:space="preserve">11.1493520736694</t>
@@ -2534,7 +2534,7 @@
     <t xml:space="preserve">11.0756378173828</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9970722198486</t>
+    <t xml:space="preserve">11.9970712661743</t>
   </si>
   <si>
     <t xml:space="preserve">12.052357673645</t>
@@ -2543,7 +2543,7 @@
     <t xml:space="preserve">12.2735013961792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2182149887085</t>
+    <t xml:space="preserve">12.2182159423828</t>
   </si>
   <si>
     <t xml:space="preserve">12.4025020599365</t>
@@ -2555,7 +2555,7 @@
     <t xml:space="preserve">12.0707864761353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1629285812378</t>
+    <t xml:space="preserve">12.1629295349121</t>
   </si>
   <si>
     <t xml:space="preserve">12.1260719299316</t>
@@ -2570,13 +2570,13 @@
     <t xml:space="preserve">11.7759265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8312129974365</t>
+    <t xml:space="preserve">11.8312139511108</t>
   </si>
   <si>
     <t xml:space="preserve">11.9786424636841</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7206411361694</t>
+    <t xml:space="preserve">11.7206420898438</t>
   </si>
   <si>
     <t xml:space="preserve">11.868070602417</t>
@@ -2591,7 +2591,7 @@
     <t xml:space="preserve">11.4442110061646</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3520669937134</t>
+    <t xml:space="preserve">11.3520679473877</t>
   </si>
   <si>
     <t xml:space="preserve">11.3704957962036</t>
@@ -2609,7 +2609,7 @@
     <t xml:space="preserve">11.7022123336792</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5732116699219</t>
+    <t xml:space="preserve">11.5732126235962</t>
   </si>
   <si>
     <t xml:space="preserve">11.481068611145</t>
@@ -2618,7 +2618,7 @@
     <t xml:space="preserve">11.296781539917</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3152093887329</t>
+    <t xml:space="preserve">11.3152103424072</t>
   </si>
   <si>
     <t xml:space="preserve">11.5547828674316</t>
@@ -2627,7 +2627,7 @@
     <t xml:space="preserve">11.4257822036743</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3336381912231</t>
+    <t xml:space="preserve">11.3336391448975</t>
   </si>
   <si>
     <t xml:space="preserve">11.3889245986938</t>
@@ -2636,7 +2636,7 @@
     <t xml:space="preserve">11.4626398086548</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7943553924561</t>
+    <t xml:space="preserve">11.7943563461304</t>
   </si>
   <si>
     <t xml:space="preserve">12.1076431274414</t>
@@ -2666,7 +2666,7 @@
     <t xml:space="preserve">13.0290775299072</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2502222061157</t>
+    <t xml:space="preserve">13.2502212524414</t>
   </si>
   <si>
     <t xml:space="preserve">13.4160804748535</t>
@@ -2681,7 +2681,7 @@
     <t xml:space="preserve">12.6420755386353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8816480636597</t>
+    <t xml:space="preserve">12.8816471099854</t>
   </si>
   <si>
     <t xml:space="preserve">12.9185056686401</t>
@@ -2690,7 +2690,7 @@
     <t xml:space="preserve">13.194935798645</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1580772399902</t>
+    <t xml:space="preserve">13.1580781936646</t>
   </si>
   <si>
     <t xml:space="preserve">12.8079328536987</t>
@@ -2705,7 +2705,7 @@
     <t xml:space="preserve">12.5499315261841</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0843629837036</t>
+    <t xml:space="preserve">13.0843639373779</t>
   </si>
   <si>
     <t xml:space="preserve">13.3423643112183</t>
@@ -2723,13 +2723,13 @@
     <t xml:space="preserve">13.1027917861938</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3607940673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2133646011353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5266513824463</t>
+    <t xml:space="preserve">13.3607931137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2133636474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5266523361206</t>
   </si>
   <si>
     <t xml:space="preserve">13.6003665924072</t>
@@ -2747,28 +2747,28 @@
     <t xml:space="preserve">13.7846536636353</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0610828399658</t>
+    <t xml:space="preserve">14.0610837936401</t>
   </si>
   <si>
     <t xml:space="preserve">14.2637987136841</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5402297973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6139440536499</t>
+    <t xml:space="preserve">14.540228843689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6139430999756</t>
   </si>
   <si>
     <t xml:space="preserve">15.3695201873779</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5353784561157</t>
+    <t xml:space="preserve">15.53537940979</t>
   </si>
   <si>
     <t xml:space="preserve">15.6275205612183</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5722360610962</t>
+    <t xml:space="preserve">15.5722341537476</t>
   </si>
   <si>
     <t xml:space="preserve">15.4063768386841</t>
@@ -2780,34 +2780,34 @@
     <t xml:space="preserve">15.295804977417</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2773761749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4616651535034</t>
+    <t xml:space="preserve">15.2773771286011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4616641998291</t>
   </si>
   <si>
     <t xml:space="preserve">15.6459493637085</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4432344436646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6643781661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7012376785278</t>
+    <t xml:space="preserve">15.4432353973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.664379119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7012367248535</t>
   </si>
   <si>
     <t xml:space="preserve">15.6090936660767</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3326606750488</t>
+    <t xml:space="preserve">15.3326616287231</t>
   </si>
   <si>
     <t xml:space="preserve">15.2036619186401</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1668033599854</t>
+    <t xml:space="preserve">15.1668043136597</t>
   </si>
   <si>
     <t xml:space="preserve">14.8535175323486</t>
@@ -2828,22 +2828,22 @@
     <t xml:space="preserve">15.8302373886108</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7196645736694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3879489898682</t>
+    <t xml:space="preserve">15.7196636199951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3879499435425</t>
   </si>
   <si>
     <t xml:space="preserve">15.5906648635864</t>
   </si>
   <si>
-    <t xml:space="preserve">15.682806968689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7565221786499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7380933761597</t>
+    <t xml:space="preserve">15.6828079223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7565231323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.738094329834</t>
   </si>
   <si>
     <t xml:space="preserve">15.1483764648438</t>
@@ -2855,7 +2855,7 @@
     <t xml:space="preserve">15.1299476623535</t>
   </si>
   <si>
-    <t xml:space="preserve">15.480092048645</t>
+    <t xml:space="preserve">15.4800910949707</t>
   </si>
   <si>
     <t xml:space="preserve">15.9223804473877</t>
@@ -2867,22 +2867,22 @@
     <t xml:space="preserve">16.0882377624512</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7749509811401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.867094039917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7109394073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6556529998779</t>
+    <t xml:space="preserve">15.7749519348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8670930862427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7109384536743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6556520462036</t>
   </si>
   <si>
     <t xml:space="preserve">13.6372241973877</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1347990036011</t>
+    <t xml:space="preserve">14.1347980499268</t>
   </si>
   <si>
     <t xml:space="preserve">14.4480857849121</t>
@@ -2894,7 +2894,7 @@
     <t xml:space="preserve">14.0242261886597</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0795125961304</t>
+    <t xml:space="preserve">14.0795116424561</t>
   </si>
   <si>
     <t xml:space="preserve">14.0057973861694</t>
@@ -2915,7 +2915,7 @@
     <t xml:space="preserve">13.4897947311401</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6187953948975</t>
+    <t xml:space="preserve">13.6187944412231</t>
   </si>
   <si>
     <t xml:space="preserve">12.8263626098633</t>
@@ -2927,7 +2927,7 @@
     <t xml:space="preserve">13.2686500549316</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9369335174561</t>
+    <t xml:space="preserve">12.9369344711304</t>
   </si>
   <si>
     <t xml:space="preserve">12.9000768661499</t>
@@ -2936,10 +2936,10 @@
     <t xml:space="preserve">12.9922199249268</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0475053787231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6973600387573</t>
+    <t xml:space="preserve">13.0475063323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6973609924316</t>
   </si>
   <si>
     <t xml:space="preserve">12.6052179336548</t>
@@ -2951,7 +2951,7 @@
     <t xml:space="preserve">12.4209308624268</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4762172698975</t>
+    <t xml:space="preserve">12.4762163162231</t>
   </si>
   <si>
     <t xml:space="preserve">12.6236457824707</t>
@@ -3531,6 +3531,9 @@
   </si>
   <si>
     <t xml:space="preserve">17.7600002288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2199993133545</t>
   </si>
 </sst>
 </file>
@@ -69467,7 +69470,7 @@
     </row>
     <row r="2524">
       <c r="A2524" s="1" t="n">
-        <v>45993.6912152778</v>
+        <v>45993.3333333333</v>
       </c>
       <c r="B2524" t="n">
         <v>29711</v>
@@ -69488,6 +69491,32 @@
         <v>1172</v>
       </c>
       <c r="H2524" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2525">
+      <c r="A2525" s="1" t="n">
+        <v>45994.691099537</v>
+      </c>
+      <c r="B2525" t="n">
+        <v>35568</v>
+      </c>
+      <c r="C2525" t="n">
+        <v>17.8199996948242</v>
+      </c>
+      <c r="D2525" t="n">
+        <v>17.2199993133545</v>
+      </c>
+      <c r="E2525" t="n">
+        <v>17.5400009155273</v>
+      </c>
+      <c r="F2525" t="n">
+        <v>17.2199993133545</v>
+      </c>
+      <c r="G2525" t="s">
+        <v>1173</v>
+      </c>
+      <c r="H2525" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ORS.MI.xlsx
+++ b/data/ORS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1174" uniqueCount="1174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1175" uniqueCount="1175">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,112 +44,112 @@
     <t xml:space="preserve">ORS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98275995254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06380271911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94223880767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82472562789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93818616867065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9017162322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03948879241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92603063583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86119413375854</t>
+    <t xml:space="preserve">7.98275852203369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06380176544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94223785400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82472467422485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93818521499634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90171432495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03948974609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92602872848511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8611946105957</t>
   </si>
   <si>
     <t xml:space="preserve">7.82067203521729</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93413352966309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02328109741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08811569213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14484596252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69910669326782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80446529388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97465467453003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01112365722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01517677307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79230737686157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82877826690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34745311737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84093236923218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90982103347778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85714054107666</t>
+    <t xml:space="preserve">7.93413305282593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02328205108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08811473846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14484691619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69910717010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80446290969849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97465372085571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01112461090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01517772674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79230642318726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82877731323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34745216369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84093284606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90982055664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85714197158813</t>
   </si>
   <si>
     <t xml:space="preserve">7.7801513671875</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84498596191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97870635986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88550662994385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95034217834473</t>
+    <t xml:space="preserve">7.8449854850769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97870779037476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88550710678101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95034122467041</t>
   </si>
   <si>
     <t xml:space="preserve">8.00302124023438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01922798156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91792440414429</t>
+    <t xml:space="preserve">8.0192289352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9179253578186</t>
   </si>
   <si>
     <t xml:space="preserve">8.1002721786499</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10432434082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18536567687988</t>
+    <t xml:space="preserve">8.104323387146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18536758422852</t>
   </si>
   <si>
     <t xml:space="preserve">8.20157623291016</t>
@@ -164,16 +164,16 @@
     <t xml:space="preserve">8.03138542175293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09621906280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17726230621338</t>
+    <t xml:space="preserve">8.09622097015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1772632598877</t>
   </si>
   <si>
     <t xml:space="preserve">8.05569744110107</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12053203582764</t>
+    <t xml:space="preserve">8.12053394317627</t>
   </si>
   <si>
     <t xml:space="preserve">8.2583065032959</t>
@@ -185,19 +185,19 @@
     <t xml:space="preserve">8.67162609100342</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55816650390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42849731445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52429008483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45921993255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50802230834961</t>
+    <t xml:space="preserve">8.55816555023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42849826812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52429103851318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45921802520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50802135467529</t>
   </si>
   <si>
     <t xml:space="preserve">8.60562801361084</t>
@@ -206,7 +206,7 @@
     <t xml:space="preserve">8.53242301940918</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61376094818115</t>
+    <t xml:space="preserve">8.61376190185547</t>
   </si>
   <si>
     <t xml:space="preserve">8.67069911956787</t>
@@ -215,10 +215,10 @@
     <t xml:space="preserve">8.87404537200928</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7927074432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90658092498779</t>
+    <t xml:space="preserve">8.79270648956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90657997131348</t>
   </si>
   <si>
     <t xml:space="preserve">8.86591243743896</t>
@@ -230,58 +230,58 @@
     <t xml:space="preserve">8.93911647796631</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78457260131836</t>
+    <t xml:space="preserve">8.78457355499268</t>
   </si>
   <si>
     <t xml:space="preserve">8.74390411376953</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91471576690674</t>
+    <t xml:space="preserve">8.91471385955811</t>
   </si>
   <si>
     <t xml:space="preserve">8.92284870147705</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10992908477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.077392578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11806201934814</t>
+    <t xml:space="preserve">9.10992813110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07739162445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11806392669678</t>
   </si>
   <si>
     <t xml:space="preserve">9.1343297958374</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15059757232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15873146057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73576927185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67883110046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85777759552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72763538360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70323467254639</t>
+    <t xml:space="preserve">9.15059661865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15873241424561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7357702255249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6788330078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8577766418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72763633728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7032356262207</t>
   </si>
   <si>
     <t xml:space="preserve">8.66256618499756</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69510173797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62189674377441</t>
+    <t xml:space="preserve">8.69510078430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6218957901001</t>
   </si>
   <si>
     <t xml:space="preserve">8.80084133148193</t>
@@ -290,13 +290,13 @@
     <t xml:space="preserve">8.77643871307373</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68696784973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54869174957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54055595397949</t>
+    <t xml:space="preserve">8.68696689605713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54869079589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54055786132812</t>
   </si>
   <si>
     <t xml:space="preserve">8.58122730255127</t>
@@ -305,7 +305,7 @@
     <t xml:space="preserve">8.46735286712646</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51615619659424</t>
+    <t xml:space="preserve">8.51615715026855</t>
   </si>
   <si>
     <t xml:space="preserve">8.49988842010498</t>
@@ -320,37 +320,37 @@
     <t xml:space="preserve">8.80897521972656</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89031505584717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93098449707031</t>
+    <t xml:space="preserve">8.89031314849854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.930983543396</t>
   </si>
   <si>
     <t xml:space="preserve">8.9635181427002</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0529899597168</t>
+    <t xml:space="preserve">9.05299091339111</t>
   </si>
   <si>
     <t xml:space="preserve">9.30514049530029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10179424285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19126605987549</t>
+    <t xml:space="preserve">9.1017951965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1912670135498</t>
   </si>
   <si>
     <t xml:space="preserve">9.35394287109375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47595119476318</t>
+    <t xml:space="preserve">9.4759521484375</t>
   </si>
   <si>
     <t xml:space="preserve">9.54915618896484</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58982563018799</t>
+    <t xml:space="preserve">9.58982467651367</t>
   </si>
   <si>
     <t xml:space="preserve">9.66303157806396</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">9.85824298858643</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0046539306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.240535736084</t>
+    <t xml:space="preserve">10.0046520233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2405347824097</t>
   </si>
   <si>
     <t xml:space="preserve">10.2486696243286</t>
@@ -377,25 +377,25 @@
     <t xml:space="preserve">10.5984258651733</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4276142120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4032125473022</t>
+    <t xml:space="preserve">10.4276151657104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4032115936279</t>
   </si>
   <si>
     <t xml:space="preserve">10.5252199172974</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4601488113403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5658903121948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5821571350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7773694992065</t>
+    <t xml:space="preserve">10.4601497650146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5658893585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5821580886841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7773704528809</t>
   </si>
   <si>
     <t xml:space="preserve">10.9807167053223</t>
@@ -407,37 +407,37 @@
     <t xml:space="preserve">10.6553630828857</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6797637939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5740232467651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5170869827271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5414886474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5577554702759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5089511871338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8180389404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6878967285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7611017227173</t>
+    <t xml:space="preserve">10.679762840271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5740242004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5170860290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5414876937866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5577564239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5089521408081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.818039894104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6878976821899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7611026763916</t>
   </si>
   <si>
     <t xml:space="preserve">10.6472291946411</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8993787765503</t>
+    <t xml:space="preserve">10.899377822876</t>
   </si>
   <si>
     <t xml:space="preserve">10.8831100463867</t>
@@ -446,31 +446,31 @@
     <t xml:space="preserve">10.6716299057007</t>
   </si>
   <si>
-    <t xml:space="preserve">10.736701965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0051193237305</t>
+    <t xml:space="preserve">10.7367010116577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0051183700562</t>
   </si>
   <si>
     <t xml:space="preserve">11.0213871002197</t>
   </si>
   <si>
-    <t xml:space="preserve">11.184063911438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4036779403687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3955430984497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3386068344116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3223400115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3304738998413</t>
+    <t xml:space="preserve">11.1840629577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4036769866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.395544052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3386077880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3223390579224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.330472946167</t>
   </si>
   <si>
     <t xml:space="preserve">11.3630084991455</t>
@@ -479,13 +479,13 @@
     <t xml:space="preserve">11.0783243179321</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6065587997437</t>
+    <t xml:space="preserve">10.606559753418</t>
   </si>
   <si>
     <t xml:space="preserve">10.8424425125122</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8505744934082</t>
+    <t xml:space="preserve">10.8505754470825</t>
   </si>
   <si>
     <t xml:space="preserve">10.6390943527222</t>
@@ -494,34 +494,34 @@
     <t xml:space="preserve">10.4113464355469</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2080011367798</t>
+    <t xml:space="preserve">10.2080001831055</t>
   </si>
   <si>
     <t xml:space="preserve">10.2730703353882</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2323999404907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3218746185303</t>
+    <t xml:space="preserve">10.232400894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.321873664856</t>
   </si>
   <si>
     <t xml:space="preserve">10.3706760406494</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3300085067749</t>
+    <t xml:space="preserve">10.3300075531006</t>
   </si>
   <si>
     <t xml:space="preserve">10.3056049346924</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2568035125732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1835985183716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4845514297485</t>
+    <t xml:space="preserve">10.2568044662476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1835975646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4845523834229</t>
   </si>
   <si>
     <t xml:space="preserve">10.3625431060791</t>
@@ -533,10 +533,10 @@
     <t xml:space="preserve">10.8587083816528</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9237813949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.037652015686</t>
+    <t xml:space="preserve">10.9237804412842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0376539230347</t>
   </si>
   <si>
     <t xml:space="preserve">11.0620565414429</t>
@@ -548,10 +548,10 @@
     <t xml:space="preserve">11.1433944702148</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1759281158447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1352605819702</t>
+    <t xml:space="preserve">11.1759309768677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1352596282959</t>
   </si>
   <si>
     <t xml:space="preserve">11.0701904296875</t>
@@ -563,16 +563,16 @@
     <t xml:space="preserve">11.1515274047852</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2247333526611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.045786857605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5008182525635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1347951889038</t>
+    <t xml:space="preserve">11.2247323989868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0457878112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5008192062378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1347932815552</t>
   </si>
   <si>
     <t xml:space="preserve">8.36161231994629</t>
@@ -581,22 +581,22 @@
     <t xml:space="preserve">8.01999092102051</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10946369171143</t>
+    <t xml:space="preserve">8.10946273803711</t>
   </si>
   <si>
     <t xml:space="preserve">8.39414691925049</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21520328521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33720970153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31281089782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18266677856445</t>
+    <t xml:space="preserve">8.21520137786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33721160888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3128080368042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18266773223877</t>
   </si>
   <si>
     <t xml:space="preserve">8.34534454345703</t>
@@ -608,52 +608,52 @@
     <t xml:space="preserve">8.49175453186035</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58935928344727</t>
+    <t xml:space="preserve">8.5893611907959</t>
   </si>
   <si>
     <t xml:space="preserve">8.76017189025879</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29654121398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25587368011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17453479766846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19080066680908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23147106170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2802734375</t>
+    <t xml:space="preserve">8.29654216766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25587272644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17453384399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1908016204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23147010803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28027439117432</t>
   </si>
   <si>
     <t xml:space="preserve">8.14199733734131</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15826511383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16640090942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12166404724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05252456665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89798259735107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85731363296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93051767349243</t>
+    <t xml:space="preserve">8.1582670211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16639995574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12166118621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05252647399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89798212051392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85731220245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93051719665527</t>
   </si>
   <si>
     <t xml:space="preserve">7.90611553192139</t>
@@ -662,7 +662,7 @@
     <t xml:space="preserve">7.93865156173706</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84917879104614</t>
+    <t xml:space="preserve">7.8491792678833</t>
   </si>
   <si>
     <t xml:space="preserve">7.80851030349731</t>
@@ -671,103 +671,103 @@
     <t xml:space="preserve">7.62956476211548</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57262706756592</t>
+    <t xml:space="preserve">7.57262802124023</t>
   </si>
   <si>
     <t xml:space="preserve">7.48315525054932</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66616678237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60516357421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54009294509888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52382373809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47908735275269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61329746246338</t>
+    <t xml:space="preserve">7.66616773605347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60516452789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54009342193604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5238242149353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.479088306427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61329650878906</t>
   </si>
   <si>
     <t xml:space="preserve">7.54822587966919</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56449413299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5075569152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4668869972229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49129009246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49942207336426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31234455108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27980899810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3774151802063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38554859161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36928129196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32047748565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34487915039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28794193267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04392528533936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15780162811279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3936824798584</t>
+    <t xml:space="preserve">7.56449460983276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50755643844604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46688604354858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4912896156311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49942255020142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31234359741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27980804443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37741422653198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38554954528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36928176879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32047891616821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34488010406494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28794145584106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04392623901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15780019760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39368295669556</t>
   </si>
   <si>
     <t xml:space="preserve">7.42621850967407</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40181684494019</t>
+    <t xml:space="preserve">7.40181732177734</t>
   </si>
   <si>
     <t xml:space="preserve">7.3042106628418</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36114740371704</t>
+    <t xml:space="preserve">7.36114835739136</t>
   </si>
   <si>
     <t xml:space="preserve">7.20660400390625</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35301351547241</t>
+    <t xml:space="preserve">7.35301303863525</t>
   </si>
   <si>
     <t xml:space="preserve">7.33674573898315</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27167320251465</t>
+    <t xml:space="preserve">7.27167415618896</t>
   </si>
   <si>
     <t xml:space="preserve">7.23100519180298</t>
@@ -782,34 +782,34 @@
     <t xml:space="preserve">7.23913908004761</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22287225723267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24727249145508</t>
+    <t xml:space="preserve">7.22287178039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24727296829224</t>
   </si>
   <si>
     <t xml:space="preserve">7.44248628616333</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25540828704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18220233917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29607582092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16593408584595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14153242111206</t>
+    <t xml:space="preserve">7.25540733337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18220329284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29607486724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16593503952026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14153289794922</t>
   </si>
   <si>
     <t xml:space="preserve">7.05205965042114</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07646226882935</t>
+    <t xml:space="preserve">7.07646083831787</t>
   </si>
   <si>
     <t xml:space="preserve">7.0357928276062</t>
@@ -818,10 +818,10 @@
     <t xml:space="preserve">7.01952457427979</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87311458587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.677903175354</t>
+    <t xml:space="preserve">6.87311410903931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67790269851685</t>
   </si>
   <si>
     <t xml:space="preserve">6.85124731063843</t>
@@ -830,31 +830,31 @@
     <t xml:space="preserve">6.93379211425781</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2639741897583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14840936660767</t>
+    <t xml:space="preserve">7.26397275924683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14841032028198</t>
   </si>
   <si>
     <t xml:space="preserve">7.09888315200806</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1814284324646</t>
+    <t xml:space="preserve">7.18142747879028</t>
   </si>
   <si>
     <t xml:space="preserve">7.16491889953613</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14015626907349</t>
+    <t xml:space="preserve">7.14015579223633</t>
   </si>
   <si>
     <t xml:space="preserve">7.21444606781006</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17317342758179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97506475448608</t>
+    <t xml:space="preserve">7.17317390441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97506427764893</t>
   </si>
   <si>
     <t xml:space="preserve">6.84299325942993</t>
@@ -869,70 +869,70 @@
     <t xml:space="preserve">6.67790222167969</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80997514724731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54583024978638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31470441818237</t>
+    <t xml:space="preserve">6.80997467041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54583120346069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31470394134521</t>
   </si>
   <si>
     <t xml:space="preserve">6.32295846939087</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34772205352783</t>
+    <t xml:space="preserve">6.34772253036499</t>
   </si>
   <si>
     <t xml:space="preserve">6.38074016571045</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39724922180176</t>
+    <t xml:space="preserve">6.3972487449646</t>
   </si>
   <si>
     <t xml:space="preserve">6.4715404510498</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2816858291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22390365600586</t>
+    <t xml:space="preserve">6.28168535232544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22390413284302</t>
   </si>
   <si>
     <t xml:space="preserve">6.09183216094971</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90197801589966</t>
+    <t xml:space="preserve">5.9019775390625</t>
   </si>
   <si>
     <t xml:space="preserve">5.9597601890564</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9927773475647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20739507675171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14135980606079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19088649749756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14961385726929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07532358169556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25692319869995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00928688049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98452377319336</t>
+    <t xml:space="preserve">5.99277782440186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20739555358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14135932922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19088697433472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14961338043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07532453536987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25692272186279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00928735733032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9845232963562</t>
   </si>
   <si>
     <t xml:space="preserve">6.12485027313232</t>
@@ -944,22 +944,22 @@
     <t xml:space="preserve">6.27343130111694</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44677591323853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55408477783203</t>
+    <t xml:space="preserve">6.44677639007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55408525466919</t>
   </si>
   <si>
     <t xml:space="preserve">6.51281213760376</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3642315864563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24041366577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21564960479736</t>
+    <t xml:space="preserve">6.36423110961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24041414260864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21565008163452</t>
   </si>
   <si>
     <t xml:space="preserve">6.23215961456299</t>
@@ -968,19 +968,19 @@
     <t xml:space="preserve">6.24866819381714</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11659574508667</t>
+    <t xml:space="preserve">6.11659622192383</t>
   </si>
   <si>
     <t xml:space="preserve">6.10834074020386</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05055904388428</t>
+    <t xml:space="preserve">6.05055952072144</t>
   </si>
   <si>
     <t xml:space="preserve">5.89372396469116</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77816104888916</t>
+    <t xml:space="preserve">5.778160572052</t>
   </si>
   <si>
     <t xml:space="preserve">5.6956148147583</t>
@@ -989,10 +989,10 @@
     <t xml:space="preserve">5.79466962814331</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80292320251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82768821716309</t>
+    <t xml:space="preserve">5.80292415618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82768774032593</t>
   </si>
   <si>
     <t xml:space="preserve">5.78641510009766</t>
@@ -1010,16 +1010,16 @@
     <t xml:space="preserve">6.1826319694519</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1578688621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03404998779297</t>
+    <t xml:space="preserve">6.15786838531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03405046463013</t>
   </si>
   <si>
     <t xml:space="preserve">6.08357763290405</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81943368911743</t>
+    <t xml:space="preserve">5.81943321228027</t>
   </si>
   <si>
     <t xml:space="preserve">5.91848659515381</t>
@@ -1028,7 +1028,7 @@
     <t xml:space="preserve">5.86070537567139</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76165199279785</t>
+    <t xml:space="preserve">5.76165246963501</t>
   </si>
   <si>
     <t xml:space="preserve">5.75339698791504</t>
@@ -1043,40 +1043,40 @@
     <t xml:space="preserve">5.74514245986938</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83594274520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71212482452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84419679641724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94325113296509</t>
+    <t xml:space="preserve">5.83594226837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71212434768677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84419727325439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94325017929077</t>
   </si>
   <si>
     <t xml:space="preserve">5.96801424026489</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8772144317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88546943664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93499612808228</t>
+    <t xml:space="preserve">5.87721538543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88546991348267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93499565124512</t>
   </si>
   <si>
     <t xml:space="preserve">6.02579641342163</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06706857681274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3889946937561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19914054870605</t>
+    <t xml:space="preserve">6.0670690536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38899421691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19914102554321</t>
   </si>
   <si>
     <t xml:space="preserve">6.04230451583862</t>
@@ -1085,19 +1085,19 @@
     <t xml:space="preserve">6.05881452560425</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9515061378479</t>
+    <t xml:space="preserve">5.95150518417358</t>
   </si>
   <si>
     <t xml:space="preserve">6.17437744140625</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1760196685791</t>
+    <t xml:space="preserve">6.17601919174194</t>
   </si>
   <si>
     <t xml:space="preserve">6.29349803924561</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25993299484253</t>
+    <t xml:space="preserve">6.25993251800537</t>
   </si>
   <si>
     <t xml:space="preserve">6.20958423614502</t>
@@ -1106,22 +1106,22 @@
     <t xml:space="preserve">6.09210538864136</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10888862609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0753231048584</t>
+    <t xml:space="preserve">6.10888957977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07532405853271</t>
   </si>
   <si>
     <t xml:space="preserve">6.14245319366455</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05854082107544</t>
+    <t xml:space="preserve">6.05854034423828</t>
   </si>
   <si>
     <t xml:space="preserve">6.02497529983521</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97462701797485</t>
+    <t xml:space="preserve">5.97462797164917</t>
   </si>
   <si>
     <t xml:space="preserve">5.95784425735474</t>
@@ -1136,10 +1136,10 @@
     <t xml:space="preserve">6.19280195236206</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42775917053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71306467056274</t>
+    <t xml:space="preserve">6.42775964736938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71306419372559</t>
   </si>
   <si>
     <t xml:space="preserve">6.64593458175659</t>
@@ -1148,25 +1148,25 @@
     <t xml:space="preserve">6.69628190994263</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7801947593689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7298469543457</t>
+    <t xml:space="preserve">6.78019571304321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72984743118286</t>
   </si>
   <si>
     <t xml:space="preserve">6.629150390625</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56202030181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54523801803589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67949914932251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66271638870239</t>
+    <t xml:space="preserve">6.56202077865601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54523754119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67949867248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66271686553955</t>
   </si>
   <si>
     <t xml:space="preserve">6.57880353927612</t>
@@ -1181,19 +1181,19 @@
     <t xml:space="preserve">6.22636747360229</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36062908172607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67253875732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55506038665771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68932247161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62219142913818</t>
+    <t xml:space="preserve">6.36062860488892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67253923416138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55505990982056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68932199478149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6221923828125</t>
   </si>
   <si>
     <t xml:space="preserve">5.53827810287476</t>
@@ -1202,49 +1202,49 @@
     <t xml:space="preserve">5.43758249282837</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45436477661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60540866851807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52149534225464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50471305847168</t>
+    <t xml:space="preserve">5.45436525344849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60540819168091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5214958190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50471258163452</t>
   </si>
   <si>
     <t xml:space="preserve">5.4879298210144</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35366916656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3704514503479</t>
+    <t xml:space="preserve">5.35366868972778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37045097351074</t>
   </si>
   <si>
     <t xml:space="preserve">5.42079925537109</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28653812408447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30332040786743</t>
+    <t xml:space="preserve">5.28653860092163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30332088470459</t>
   </si>
   <si>
     <t xml:space="preserve">5.26975584030151</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38723468780518</t>
+    <t xml:space="preserve">5.38723373413086</t>
   </si>
   <si>
     <t xml:space="preserve">5.32010412216187</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65575647354126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75645303726196</t>
+    <t xml:space="preserve">5.65575695037842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75645351409912</t>
   </si>
   <si>
     <t xml:space="preserve">5.70610475540161</t>
@@ -1253,43 +1253,43 @@
     <t xml:space="preserve">5.72288703918457</t>
   </si>
   <si>
-    <t xml:space="preserve">5.739670753479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63897466659546</t>
+    <t xml:space="preserve">5.73967027664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6389741897583</t>
   </si>
   <si>
     <t xml:space="preserve">5.57184410095215</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18584156036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20262479782104</t>
+    <t xml:space="preserve">5.18584203720093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2026252746582</t>
   </si>
   <si>
     <t xml:space="preserve">5.21940803527832</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16905975341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13549327850342</t>
+    <t xml:space="preserve">5.16906023025513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13549375534058</t>
   </si>
   <si>
     <t xml:space="preserve">5.10192918777466</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95088386535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03479814529419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15227699279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11871147155762</t>
+    <t xml:space="preserve">4.95088529586792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03479862213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15227651596069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11871194839478</t>
   </si>
   <si>
     <t xml:space="preserve">5.06836318969727</t>
@@ -1298,10 +1298,10 @@
     <t xml:space="preserve">5.08514642715454</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23619031906128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2529730796814</t>
+    <t xml:space="preserve">5.23618984222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25297212600708</t>
   </si>
   <si>
     <t xml:space="preserve">5.33688640594482</t>
@@ -1313,76 +1313,76 @@
     <t xml:space="preserve">5.77323532104492</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58862590789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81662321090698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79984092712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59844923019409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36349248886108</t>
+    <t xml:space="preserve">5.58862638473511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81662368774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79984140396118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59844875335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36349153518677</t>
   </si>
   <si>
     <t xml:space="preserve">4.31314373016357</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19566488265991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11175155639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02783918380737</t>
+    <t xml:space="preserve">4.19566535949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11175107955933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02783823013306</t>
   </si>
   <si>
     <t xml:space="preserve">4.17049074172974</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06979608535767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12014245986938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34670925140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17888164520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04462099075317</t>
+    <t xml:space="preserve">4.06979560852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1201434135437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34670877456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17888212203979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04462146759033</t>
   </si>
   <si>
     <t xml:space="preserve">4.15370798110962</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26279640197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16209936141968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14531755447388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99427318572998</t>
+    <t xml:space="preserve">4.26279592514038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16210031509399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14531803131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9942729473114</t>
   </si>
   <si>
     <t xml:space="preserve">4.09496927261353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98588132858276</t>
+    <t xml:space="preserve">3.9858820438385</t>
   </si>
   <si>
     <t xml:space="preserve">4.27957820892334</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22923040390015</t>
+    <t xml:space="preserve">4.22922992706299</t>
   </si>
   <si>
     <t xml:space="preserve">4.21244812011719</t>
@@ -1391,10 +1391,10 @@
     <t xml:space="preserve">4.03623008728027</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1287784576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16283130645752</t>
+    <t xml:space="preserve">4.12877941131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16283082962036</t>
   </si>
   <si>
     <t xml:space="preserve">4.07770156860352</t>
@@ -1409,13 +1409,13 @@
     <t xml:space="preserve">4.37565469741821</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21390867233276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22242212295532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25647354125977</t>
+    <t xml:space="preserve">4.21390819549561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22242116928101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25647306442261</t>
   </si>
   <si>
     <t xml:space="preserve">4.24796009063721</t>
@@ -1424,61 +1424,61 @@
     <t xml:space="preserve">4.32457685470581</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30755043029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23944711685181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35862827301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51186227798462</t>
+    <t xml:space="preserve">4.30755090713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23944759368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35862874984741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5118613243103</t>
   </si>
   <si>
     <t xml:space="preserve">5.5334153175354</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94203662872314</t>
+    <t xml:space="preserve">5.9420371055603</t>
   </si>
   <si>
     <t xml:space="preserve">5.8909592628479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73772621154785</t>
+    <t xml:space="preserve">5.73772573471069</t>
   </si>
   <si>
     <t xml:space="preserve">5.5504412651062</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58449363708496</t>
+    <t xml:space="preserve">5.5844931602478</t>
   </si>
   <si>
     <t xml:space="preserve">5.567467212677</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41423463821411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2610011100769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.482337474823</t>
+    <t xml:space="preserve">5.41423368453979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26100158691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48233795166016</t>
   </si>
   <si>
     <t xml:space="preserve">5.44828605651855</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60151863098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66962194442749</t>
+    <t xml:space="preserve">5.6015191078186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66962289810181</t>
   </si>
   <si>
     <t xml:space="preserve">5.5163893699646</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70367479324341</t>
+    <t xml:space="preserve">5.70367431640625</t>
   </si>
   <si>
     <t xml:space="preserve">5.32910490036011</t>
@@ -1496,7 +1496,7 @@
     <t xml:space="preserve">5.2269492149353</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00561285018921</t>
+    <t xml:space="preserve">5.00561237335205</t>
   </si>
   <si>
     <t xml:space="preserve">4.95453500747681</t>
@@ -1505,7 +1505,7 @@
     <t xml:space="preserve">4.93750905990601</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05669021606445</t>
+    <t xml:space="preserve">5.05669069290161</t>
   </si>
   <si>
     <t xml:space="preserve">5.03966426849365</t>
@@ -1514,28 +1514,28 @@
     <t xml:space="preserve">4.97156095504761</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88643074035645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02263879776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92048263549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90345764160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85237979888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86940479278564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34613132476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24397563934326</t>
+    <t xml:space="preserve">4.88643169403076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02263832092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92048358917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90345668792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.852379322052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86940574645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34613037109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24397468566895</t>
   </si>
   <si>
     <t xml:space="preserve">5.36315631866455</t>
@@ -1550,25 +1550,25 @@
     <t xml:space="preserve">5.15884590148926</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10776805877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98858642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09074211120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1928973197937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17587184906006</t>
+    <t xml:space="preserve">5.1077675819397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98858737945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09074258804321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19289779663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1758713722229</t>
   </si>
   <si>
     <t xml:space="preserve">5.14181995391846</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0737156867981</t>
+    <t xml:space="preserve">5.07371616363525</t>
   </si>
   <si>
     <t xml:space="preserve">4.68212080001831</t>
@@ -1580,31 +1580,31 @@
     <t xml:space="preserve">4.59699106216431</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57996511459351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63104248046875</t>
+    <t xml:space="preserve">4.57996559143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63104295730591</t>
   </si>
   <si>
     <t xml:space="preserve">4.78427600860596</t>
   </si>
   <si>
-    <t xml:space="preserve">4.767249584198</t>
+    <t xml:space="preserve">4.76725006103516</t>
   </si>
   <si>
     <t xml:space="preserve">4.81832790374756</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8013014793396</t>
+    <t xml:space="preserve">4.80130195617676</t>
   </si>
   <si>
     <t xml:space="preserve">5.39720869064331</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6185450553894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46531248092651</t>
+    <t xml:space="preserve">5.61854457855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46531200408936</t>
   </si>
   <si>
     <t xml:space="preserve">5.49936389923096</t>
@@ -1613,13 +1613,13 @@
     <t xml:space="preserve">5.63557052612305</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68664884567261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65259647369385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85690784454346</t>
+    <t xml:space="preserve">5.68664836883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65259695053101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8569073677063</t>
   </si>
   <si>
     <t xml:space="preserve">5.8739333152771</t>
@@ -1631,28 +1631,28 @@
     <t xml:space="preserve">6.33363246917725</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2995810508728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35065793991089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43578767776489</t>
+    <t xml:space="preserve">6.29958057403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35065841674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43578720092773</t>
   </si>
   <si>
     <t xml:space="preserve">6.55496883392334</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69117593765259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79333114624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15087461471558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08277130126953</t>
+    <t xml:space="preserve">6.69117641448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79333209991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15087413787842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08277082443237</t>
   </si>
   <si>
     <t xml:space="preserve">6.87846088409424</t>
@@ -1661,7 +1661,7 @@
     <t xml:space="preserve">6.77630567550659</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84440851211548</t>
+    <t xml:space="preserve">6.84440898895264</t>
   </si>
   <si>
     <t xml:space="preserve">6.70820236206055</t>
@@ -1679,13 +1679,13 @@
     <t xml:space="preserve">6.65712451934814</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91251230239868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8954873085022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96359014511108</t>
+    <t xml:space="preserve">6.91251277923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89548683166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96359062194824</t>
   </si>
   <si>
     <t xml:space="preserve">7.17302179336548</t>
@@ -1694,31 +1694,31 @@
     <t xml:space="preserve">7.05085325241089</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12066411972046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57443237304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97584199905396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02819919586182</t>
+    <t xml:space="preserve">7.1206636428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57443141937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9758415222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02820014953613</t>
   </si>
   <si>
     <t xml:space="preserve">8.0631046295166</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99329328536987</t>
+    <t xml:space="preserve">7.99329423904419</t>
   </si>
   <si>
     <t xml:space="preserve">8.01074695587158</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94093799591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13291454315186</t>
+    <t xml:space="preserve">7.94093704223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13291358947754</t>
   </si>
   <si>
     <t xml:space="preserve">8.15036773681641</t>
@@ -1727,25 +1727,25 @@
     <t xml:space="preserve">8.16782093048096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18527412414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34234619140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11546325683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25508403778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08055782318115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20272541046143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95838928222656</t>
+    <t xml:space="preserve">8.18527317047119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34234714508057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11546230316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25508308410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08055686950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20272445678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95838832855225</t>
   </si>
   <si>
     <t xml:space="preserve">8.37725162506104</t>
@@ -1757,13 +1757,13 @@
     <t xml:space="preserve">8.81356716156006</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58668231964111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53432559967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69139766693115</t>
+    <t xml:space="preserve">8.58668422698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53432464599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69139862060547</t>
   </si>
   <si>
     <t xml:space="preserve">8.60413551330566</t>
@@ -1772,58 +1772,58 @@
     <t xml:space="preserve">8.72630405426025</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42961025238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28998947143555</t>
+    <t xml:space="preserve">8.42960929870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28998851776123</t>
   </si>
   <si>
     <t xml:space="preserve">8.30744171142578</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04565334320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85367345809937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41215801239014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22017765045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44706153869629</t>
+    <t xml:space="preserve">8.04565238952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85367298126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41215705871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22017860412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44706249237061</t>
   </si>
   <si>
     <t xml:space="preserve">8.3597993850708</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09800910949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23762989044189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48196792602539</t>
+    <t xml:space="preserve">8.09801006317139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23763084411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48196697235107</t>
   </si>
   <si>
     <t xml:space="preserve">8.6215877532959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55177783966064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.656494140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51687240600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46451377868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49942016601562</t>
+    <t xml:space="preserve">8.55177688598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65649318695068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51687335968018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46451568603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49941921234131</t>
   </si>
   <si>
     <t xml:space="preserve">8.56923007965088</t>
@@ -1835,7 +1835,7 @@
     <t xml:space="preserve">9.59893417358398</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77345943450928</t>
+    <t xml:space="preserve">9.77346038818359</t>
   </si>
   <si>
     <t xml:space="preserve">9.8170919418335</t>
@@ -1856,7 +1856,7 @@
     <t xml:space="preserve">9.9043550491333</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33714580535889</t>
+    <t xml:space="preserve">9.33714389801025</t>
   </si>
   <si>
     <t xml:space="preserve">9.9479866027832</t>
@@ -1868,13 +1868,13 @@
     <t xml:space="preserve">10.5151968002319</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4279317855835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5588274002075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6024589538574</t>
+    <t xml:space="preserve">10.4279327392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5588283538818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6024580001831</t>
   </si>
   <si>
     <t xml:space="preserve">10.8206167221069</t>
@@ -1883,10 +1883,10 @@
     <t xml:space="preserve">10.7333545684814</t>
   </si>
   <si>
-    <t xml:space="preserve">10.776985168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2970390319824</t>
+    <t xml:space="preserve">10.7769861221313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2970399856567</t>
   </si>
   <si>
     <t xml:space="preserve">10.3843011856079</t>
@@ -1901,16 +1901,16 @@
     <t xml:space="preserve">10.2534065246582</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0788812637329</t>
+    <t xml:space="preserve">10.0788803100586</t>
   </si>
   <si>
     <t xml:space="preserve">9.51167106628418</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72982788085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68619823455811</t>
+    <t xml:space="preserve">9.72982883453369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68619728088379</t>
   </si>
   <si>
     <t xml:space="preserve">8.98809337615967</t>
@@ -1919,22 +1919,22 @@
     <t xml:space="preserve">9.42440795898438</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6496152877808</t>
+    <t xml:space="preserve">11.6496162414551</t>
   </si>
   <si>
     <t xml:space="preserve">11.5623531341553</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7805099487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9114046096802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9550352096558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.693247795105</t>
+    <t xml:space="preserve">11.7805109024048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9114036560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9550361633301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6932458877563</t>
   </si>
   <si>
     <t xml:space="preserve">12.3040885925293</t>
@@ -1946,16 +1946,16 @@
     <t xml:space="preserve">12.2168254852295</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3913516998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7368783950806</t>
+    <t xml:space="preserve">12.3913507461548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7368774414062</t>
   </si>
   <si>
     <t xml:space="preserve">11.8677730560303</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6059837341309</t>
+    <t xml:space="preserve">11.6059846878052</t>
   </si>
   <si>
     <t xml:space="preserve">10.9515113830566</t>
@@ -1967,16 +1967,16 @@
     <t xml:space="preserve">11.3005638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3441953659058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9951429367065</t>
+    <t xml:space="preserve">11.3441963195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9951438903809</t>
   </si>
   <si>
     <t xml:space="preserve">10.4715642929077</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9078798294067</t>
+    <t xml:space="preserve">10.9078788757324</t>
   </si>
   <si>
     <t xml:space="preserve">11.4314584732056</t>
@@ -1985,22 +1985,22 @@
     <t xml:space="preserve">11.0387735366821</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9899415969849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7456045150757</t>
+    <t xml:space="preserve">11.9899406433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.74560546875</t>
   </si>
   <si>
     <t xml:space="preserve">11.5361738204956</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5187215805054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6234359741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4489116668701</t>
+    <t xml:space="preserve">11.5187206268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6234369277954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4489097595215</t>
   </si>
   <si>
     <t xml:space="preserve">11.6408891677856</t>
@@ -2009,10 +2009,10 @@
     <t xml:space="preserve">11.7281522750854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9201307296753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1173105239868</t>
+    <t xml:space="preserve">11.9201316833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1173114776611</t>
   </si>
   <si>
     <t xml:space="preserve">11.0998592376709</t>
@@ -2021,13 +2021,13 @@
     <t xml:space="preserve">10.8031644821167</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7508068084717</t>
+    <t xml:space="preserve">10.7508058547974</t>
   </si>
   <si>
     <t xml:space="preserve">10.3319435119629</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1050596237183</t>
+    <t xml:space="preserve">10.1050586700439</t>
   </si>
   <si>
     <t xml:space="preserve">9.81839179992676</t>
@@ -3534,6 +3534,9 @@
   </si>
   <si>
     <t xml:space="preserve">17.2199993133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2600002288818</t>
   </si>
 </sst>
 </file>
@@ -69496,7 +69499,7 @@
     </row>
     <row r="2525">
       <c r="A2525" s="1" t="n">
-        <v>45994.691099537</v>
+        <v>45994.3333333333</v>
       </c>
       <c r="B2525" t="n">
         <v>35568</v>
@@ -69517,6 +69520,32 @@
         <v>1173</v>
       </c>
       <c r="H2525" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2526">
+      <c r="A2526" s="1" t="n">
+        <v>45995.6910416667</v>
+      </c>
+      <c r="B2526" t="n">
+        <v>16226</v>
+      </c>
+      <c r="C2526" t="n">
+        <v>17.5799999237061</v>
+      </c>
+      <c r="D2526" t="n">
+        <v>17.1000003814697</v>
+      </c>
+      <c r="E2526" t="n">
+        <v>17.5799999237061</v>
+      </c>
+      <c r="F2526" t="n">
+        <v>17.2600002288818</v>
+      </c>
+      <c r="G2526" t="s">
+        <v>1174</v>
+      </c>
+      <c r="H2526" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ORS.MI.xlsx
+++ b/data/ORS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1176" uniqueCount="1176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1177" uniqueCount="1177">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -53,7 +53,7 @@
     <t xml:space="preserve">7.94223690032959</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8247241973877</t>
+    <t xml:space="preserve">7.82472562789917</t>
   </si>
   <si>
     <t xml:space="preserve">7.93818521499634</t>
@@ -68,91 +68,91 @@
     <t xml:space="preserve">7.92602968215942</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8611946105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82067203521729</t>
+    <t xml:space="preserve">7.86119508743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8206729888916</t>
   </si>
   <si>
     <t xml:space="preserve">7.93413257598877</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02328109741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08811569213867</t>
+    <t xml:space="preserve">8.02328205108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08811473846436</t>
   </si>
   <si>
     <t xml:space="preserve">8.14484596252441</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69910669326782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8044638633728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97465562820435</t>
+    <t xml:space="preserve">7.69910764694214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80446434020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97465467453003</t>
   </si>
   <si>
     <t xml:space="preserve">8.0111255645752</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01517772674561</t>
+    <t xml:space="preserve">8.01517486572266</t>
   </si>
   <si>
     <t xml:space="preserve">7.79230785369873</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82877731323242</t>
+    <t xml:space="preserve">7.82877826690674</t>
   </si>
   <si>
     <t xml:space="preserve">8.34745311737061</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84093427658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90982103347778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85714197158813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78015184402466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84498596191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97870635986328</t>
+    <t xml:space="preserve">7.84093236923218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9098219871521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85714101791382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78015279769897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8449854850769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9787073135376</t>
   </si>
   <si>
     <t xml:space="preserve">7.88550662994385</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95034217834473</t>
+    <t xml:space="preserve">7.95034313201904</t>
   </si>
   <si>
     <t xml:space="preserve">8.00302028656006</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01922798156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91792631149292</t>
+    <t xml:space="preserve">8.0192289352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91792345046997</t>
   </si>
   <si>
     <t xml:space="preserve">8.1002721786499</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10432243347168</t>
+    <t xml:space="preserve">8.104323387146</t>
   </si>
   <si>
     <t xml:space="preserve">8.18536758422852</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20157623291016</t>
+    <t xml:space="preserve">8.20157527923584</t>
   </si>
   <si>
     <t xml:space="preserve">8.11242866516113</t>
@@ -170,40 +170,40 @@
     <t xml:space="preserve">8.17726230621338</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05569744110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12053298950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25830745697021</t>
+    <t xml:space="preserve">8.05569839477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12053203582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2583065032959</t>
   </si>
   <si>
     <t xml:space="preserve">8.4203929901123</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67162609100342</t>
+    <t xml:space="preserve">8.6716251373291</t>
   </si>
   <si>
     <t xml:space="preserve">8.55816555023193</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42849731445312</t>
+    <t xml:space="preserve">8.42849826812744</t>
   </si>
   <si>
     <t xml:space="preserve">8.52429008483887</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45921897888184</t>
+    <t xml:space="preserve">8.45921802520752</t>
   </si>
   <si>
     <t xml:space="preserve">8.50802135467529</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60562801361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5324239730835</t>
+    <t xml:space="preserve">8.60562896728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53242492675781</t>
   </si>
   <si>
     <t xml:space="preserve">8.61376190185547</t>
@@ -212,7 +212,7 @@
     <t xml:space="preserve">8.67069911956787</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87404727935791</t>
+    <t xml:space="preserve">8.87404632568359</t>
   </si>
   <si>
     <t xml:space="preserve">8.7927074432373</t>
@@ -221,10 +221,10 @@
     <t xml:space="preserve">8.90658092498779</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86591148376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94725036621094</t>
+    <t xml:space="preserve">8.86591243743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94725131988525</t>
   </si>
   <si>
     <t xml:space="preserve">8.93911647796631</t>
@@ -236,55 +236,55 @@
     <t xml:space="preserve">8.74390316009521</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91471481323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92285060882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10992908477783</t>
+    <t xml:space="preserve">8.91471672058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92284870147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1099271774292</t>
   </si>
   <si>
     <t xml:space="preserve">9.077392578125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11806297302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1343297958374</t>
+    <t xml:space="preserve">9.11806201934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13432884216309</t>
   </si>
   <si>
     <t xml:space="preserve">9.15059852600098</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15873241424561</t>
+    <t xml:space="preserve">9.15873146057129</t>
   </si>
   <si>
     <t xml:space="preserve">8.7357702255249</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6788330078125</t>
+    <t xml:space="preserve">8.67883205413818</t>
   </si>
   <si>
     <t xml:space="preserve">8.85777759552002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72763729095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70323467254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66256523132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69510078430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6218957901001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80084133148193</t>
+    <t xml:space="preserve">8.72763538360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7032356262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66256618499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69510173797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62189674377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80084037780762</t>
   </si>
   <si>
     <t xml:space="preserve">8.77643966674805</t>
@@ -293,37 +293,37 @@
     <t xml:space="preserve">8.68696689605713</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54869079589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54055595397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58122730255127</t>
+    <t xml:space="preserve">8.54869174957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54055690765381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58122825622559</t>
   </si>
   <si>
     <t xml:space="preserve">8.46735382080078</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51615619659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49988651275635</t>
+    <t xml:space="preserve">8.51615524291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49988746643066</t>
   </si>
   <si>
     <t xml:space="preserve">8.45108413696289</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63003063201904</t>
+    <t xml:space="preserve">8.63002967834473</t>
   </si>
   <si>
     <t xml:space="preserve">8.80897617340088</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89031410217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93098258972168</t>
+    <t xml:space="preserve">8.89031600952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93098449707031</t>
   </si>
   <si>
     <t xml:space="preserve">8.96351718902588</t>
@@ -344,22 +344,22 @@
     <t xml:space="preserve">9.35394382476807</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47595119476318</t>
+    <t xml:space="preserve">9.4759521484375</t>
   </si>
   <si>
     <t xml:space="preserve">9.54915618896484</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58982467651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66303157806396</t>
+    <t xml:space="preserve">9.58982563018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66303062438965</t>
   </si>
   <si>
     <t xml:space="preserve">9.71996688842773</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85824298858643</t>
+    <t xml:space="preserve">9.85824203491211</t>
   </si>
   <si>
     <t xml:space="preserve">10.0046529769897</t>
@@ -368,13 +368,13 @@
     <t xml:space="preserve">10.2405347824097</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2486686706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3381423950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5984268188477</t>
+    <t xml:space="preserve">10.2486696243286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3381414413452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5984258651733</t>
   </si>
   <si>
     <t xml:space="preserve">10.4276151657104</t>
@@ -383,52 +383,52 @@
     <t xml:space="preserve">10.4032115936279</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5252208709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.460150718689</t>
+    <t xml:space="preserve">10.525218963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4601488113403</t>
   </si>
   <si>
     <t xml:space="preserve">10.5658903121948</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5821571350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7773694992065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9807157516479</t>
+    <t xml:space="preserve">10.5821580886841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7773704528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9807167053223</t>
   </si>
   <si>
     <t xml:space="preserve">10.8749771118164</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6553621292114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.679762840271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5740242004395</t>
+    <t xml:space="preserve">10.6553630828857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6797647476196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5740232467651</t>
   </si>
   <si>
     <t xml:space="preserve">10.5170860290527</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5414896011353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5577564239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5089540481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8180379867554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6878967285156</t>
+    <t xml:space="preserve">10.5414886474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5577554702759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5089530944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.818039894104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6878976821899</t>
   </si>
   <si>
     <t xml:space="preserve">10.7611017227173</t>
@@ -443,7 +443,7 @@
     <t xml:space="preserve">10.8831090927124</t>
   </si>
   <si>
-    <t xml:space="preserve">10.671630859375</t>
+    <t xml:space="preserve">10.6716289520264</t>
   </si>
   <si>
     <t xml:space="preserve">10.7367010116577</t>
@@ -452,37 +452,37 @@
     <t xml:space="preserve">11.0051183700562</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0213861465454</t>
+    <t xml:space="preserve">11.0213871002197</t>
   </si>
   <si>
     <t xml:space="preserve">11.184063911438</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4036769866943</t>
+    <t xml:space="preserve">11.40367603302</t>
   </si>
   <si>
     <t xml:space="preserve">11.395544052124</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3386058807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3223400115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3304738998413</t>
+    <t xml:space="preserve">11.3386068344116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3223390579224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.330472946167</t>
   </si>
   <si>
     <t xml:space="preserve">11.3630094528198</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0783243179321</t>
+    <t xml:space="preserve">11.0783233642578</t>
   </si>
   <si>
     <t xml:space="preserve">10.606559753418</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8424415588379</t>
+    <t xml:space="preserve">10.8424406051636</t>
   </si>
   <si>
     <t xml:space="preserve">10.8505744934082</t>
@@ -500,13 +500,13 @@
     <t xml:space="preserve">10.2730712890625</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2324018478394</t>
+    <t xml:space="preserve">10.232400894165</t>
   </si>
   <si>
     <t xml:space="preserve">10.3218746185303</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3706769943237</t>
+    <t xml:space="preserve">10.370677947998</t>
   </si>
   <si>
     <t xml:space="preserve">10.3300075531006</t>
@@ -518,10 +518,10 @@
     <t xml:space="preserve">10.2568035125732</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1835985183716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4845514297485</t>
+    <t xml:space="preserve">10.1835966110229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4845523834229</t>
   </si>
   <si>
     <t xml:space="preserve">10.3625431060791</t>
@@ -533,7 +533,7 @@
     <t xml:space="preserve">10.8587074279785</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9237804412842</t>
+    <t xml:space="preserve">10.9237794876099</t>
   </si>
   <si>
     <t xml:space="preserve">11.0376539230347</t>
@@ -542,10 +542,10 @@
     <t xml:space="preserve">11.0620555877686</t>
   </si>
   <si>
-    <t xml:space="preserve">11.102725982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1433925628662</t>
+    <t xml:space="preserve">11.1027250289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1433954238892</t>
   </si>
   <si>
     <t xml:space="preserve">11.1759281158447</t>
@@ -554,43 +554,43 @@
     <t xml:space="preserve">11.1352605819702</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0701904296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1189937591553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1515293121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2247323989868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.045786857605</t>
+    <t xml:space="preserve">11.0701894760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.118992805481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1515274047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2247333526611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0457878112793</t>
   </si>
   <si>
     <t xml:space="preserve">10.5008182525635</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1347951889038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36161136627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01998996734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10946369171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39414882659912</t>
+    <t xml:space="preserve">10.1347961425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36161231994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01999092102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10946273803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39414691925049</t>
   </si>
   <si>
     <t xml:space="preserve">8.21520328521729</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33720874786377</t>
+    <t xml:space="preserve">8.33720970153809</t>
   </si>
   <si>
     <t xml:space="preserve">8.31280899047852</t>
@@ -602,61 +602,61 @@
     <t xml:space="preserve">8.34534549713135</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23960399627686</t>
+    <t xml:space="preserve">8.23960494995117</t>
   </si>
   <si>
     <t xml:space="preserve">8.49175453186035</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5893611907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76017284393311</t>
+    <t xml:space="preserve">8.58936023712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76017189025879</t>
   </si>
   <si>
     <t xml:space="preserve">8.29654121398926</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25587272644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17453384399414</t>
+    <t xml:space="preserve">8.25587177276611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17453479766846</t>
   </si>
   <si>
     <t xml:space="preserve">8.1908016204834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23147201538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28027439117432</t>
+    <t xml:space="preserve">8.23147010803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2802734375</t>
   </si>
   <si>
     <t xml:space="preserve">8.14199829101562</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15826511383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16640090942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12166404724121</t>
+    <t xml:space="preserve">8.15826606750488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16639995574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12166309356689</t>
   </si>
   <si>
     <t xml:space="preserve">8.05252552032471</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89798164367676</t>
+    <t xml:space="preserve">7.89798259735107</t>
   </si>
   <si>
     <t xml:space="preserve">7.85731267929077</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93051671981812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90611553192139</t>
+    <t xml:space="preserve">7.93051767349243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90611600875854</t>
   </si>
   <si>
     <t xml:space="preserve">7.93865251541138</t>
@@ -665,211 +665,214 @@
     <t xml:space="preserve">7.84917879104614</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80850887298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62956571578979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57262659072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48315572738647</t>
+    <t xml:space="preserve">7.80850982666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62956380844116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57262754440308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48315525054932</t>
   </si>
   <si>
     <t xml:space="preserve">7.66616630554199</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60516309738159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54009199142456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5238242149353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47908782958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6132960319519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54822540283203</t>
+    <t xml:space="preserve">7.60516214370728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5400915145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52382326126099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47908687591553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61329746246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54822587966919</t>
   </si>
   <si>
     <t xml:space="preserve">7.56449365615845</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50755643844604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46688747406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4912896156311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49942207336426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31234502792358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27980804443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37741327285767</t>
+    <t xml:space="preserve">7.50755548477173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46688652038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49128913879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49942302703857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31234455108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27980852127075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37741470336914</t>
   </si>
   <si>
     <t xml:space="preserve">7.38554906845093</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36928129196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3204779624939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34487915039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28794240951538</t>
+    <t xml:space="preserve">7.36928176879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32047700881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34487962722778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28794145584106</t>
   </si>
   <si>
     <t xml:space="preserve">7.04392671585083</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15780067443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39368200302124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42621803283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40181684494019</t>
+    <t xml:space="preserve">7.15780115127563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39368295669556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42621850967407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40181589126587</t>
   </si>
   <si>
     <t xml:space="preserve">7.30421018600464</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36114740371704</t>
+    <t xml:space="preserve">7.36114835739136</t>
   </si>
   <si>
     <t xml:space="preserve">7.20660352706909</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35301303863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33674573898315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27167415618896</t>
+    <t xml:space="preserve">7.3530125617981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33674478530884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27167510986328</t>
   </si>
   <si>
     <t xml:space="preserve">7.23100423812866</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32861089706421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26354169845581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23914003372192</t>
+    <t xml:space="preserve">7.32861137390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26354074478149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23913955688477</t>
   </si>
   <si>
     <t xml:space="preserve">7.22287178039551</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24727344512939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44248485565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25540685653687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18220186233521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29607582092285</t>
+    <t xml:space="preserve">7.24727392196655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44248628616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25540781021118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18220043182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29607486724854</t>
   </si>
   <si>
     <t xml:space="preserve">7.16593456268311</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14153337478638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05205917358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0764627456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0357928276062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01952505111694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87311553955078</t>
+    <t xml:space="preserve">7.14153289794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05205965042114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07646226882935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03579235076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01952600479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87311458587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.677903175354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85124731063843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93379259109497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26397371292114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14841079711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09888315200806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1814284324646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16491842269897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14015626907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21444654464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17317390441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97506427764893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84299278259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60361194610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62012052536011</t>
   </si>
   <si>
     <t xml:space="preserve">6.67790269851685</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85124778747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93379163742065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26397323608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14841032028198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09888315200806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18142890930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16491842269897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14015579223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21444702148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17317342758179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97506523132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84299278259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60361289978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62012100219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.809974193573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54582977294922</t>
+    <t xml:space="preserve">6.80997467041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54583072662354</t>
   </si>
   <si>
     <t xml:space="preserve">6.31470394134521</t>
@@ -878,49 +881,49 @@
     <t xml:space="preserve">6.32295846939087</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34772253036499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38074016571045</t>
+    <t xml:space="preserve">6.34772205352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38074064254761</t>
   </si>
   <si>
     <t xml:space="preserve">6.39724922180176</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47154092788696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2816858291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22390365600586</t>
+    <t xml:space="preserve">6.47153997421265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28168630599976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22390460968018</t>
   </si>
   <si>
     <t xml:space="preserve">6.09183216094971</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90197849273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95976066589355</t>
+    <t xml:space="preserve">5.9019775390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95975971221924</t>
   </si>
   <si>
     <t xml:space="preserve">5.99277782440186</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20739555358887</t>
+    <t xml:space="preserve">6.20739603042603</t>
   </si>
   <si>
     <t xml:space="preserve">6.14135932922363</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1908860206604</t>
+    <t xml:space="preserve">6.19088649749756</t>
   </si>
   <si>
     <t xml:space="preserve">6.14961385726929</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07532358169556</t>
+    <t xml:space="preserve">6.0753231048584</t>
   </si>
   <si>
     <t xml:space="preserve">6.25692272186279</t>
@@ -932,16 +935,16 @@
     <t xml:space="preserve">5.9845232963562</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12485027313232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13310480117798</t>
+    <t xml:space="preserve">6.12485074996948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13310432434082</t>
   </si>
   <si>
     <t xml:space="preserve">6.27343130111694</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44677591323853</t>
+    <t xml:space="preserve">6.44677543640137</t>
   </si>
   <si>
     <t xml:space="preserve">6.55408525466919</t>
@@ -953,34 +956,34 @@
     <t xml:space="preserve">6.3642315864563</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24041414260864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21564960479736</t>
+    <t xml:space="preserve">6.24041318893433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21565008163452</t>
   </si>
   <si>
     <t xml:space="preserve">6.23215913772583</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24866819381714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11659669876099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1083402633667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05055952072144</t>
+    <t xml:space="preserve">6.24866771697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11659574508667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10834074020386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05055999755859</t>
   </si>
   <si>
     <t xml:space="preserve">5.89372396469116</t>
   </si>
   <si>
-    <t xml:space="preserve">5.778160572052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69561529159546</t>
+    <t xml:space="preserve">5.77816104888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6956148147583</t>
   </si>
   <si>
     <t xml:space="preserve">5.79466915130615</t>
@@ -989,16 +992,16 @@
     <t xml:space="preserve">5.80292320251465</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82768774032593</t>
+    <t xml:space="preserve">5.82768821716309</t>
   </si>
   <si>
     <t xml:space="preserve">5.7864146232605</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73688745498657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85245180130005</t>
+    <t xml:space="preserve">5.73688793182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85245132446289</t>
   </si>
   <si>
     <t xml:space="preserve">6.29819536209106</t>
@@ -1013,13 +1016,13 @@
     <t xml:space="preserve">6.03405094146729</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08357810974121</t>
+    <t xml:space="preserve">6.08357715606689</t>
   </si>
   <si>
     <t xml:space="preserve">5.81943368911743</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91848659515381</t>
+    <t xml:space="preserve">5.91848707199097</t>
   </si>
   <si>
     <t xml:space="preserve">5.86070537567139</t>
@@ -1028,40 +1031,40 @@
     <t xml:space="preserve">5.76165246963501</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75339651107788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8111777305603</t>
+    <t xml:space="preserve">5.75339698791504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81117820739746</t>
   </si>
   <si>
     <t xml:space="preserve">5.70387029647827</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74514245986938</t>
+    <t xml:space="preserve">5.74514198303223</t>
   </si>
   <si>
     <t xml:space="preserve">5.83594274520874</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71212482452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84419727325439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94325113296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96801471710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87721538543701</t>
+    <t xml:space="preserve">5.71212434768677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84419679641724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94325160980225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96801424026489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87721490859985</t>
   </si>
   <si>
     <t xml:space="preserve">5.88546943664551</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93499612808228</t>
+    <t xml:space="preserve">5.93499660491943</t>
   </si>
   <si>
     <t xml:space="preserve">6.02579593658447</t>
@@ -1070,34 +1073,34 @@
     <t xml:space="preserve">6.06706857681274</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3889946937561</t>
+    <t xml:space="preserve">6.38899517059326</t>
   </si>
   <si>
     <t xml:space="preserve">6.19914102554321</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04230499267578</t>
+    <t xml:space="preserve">6.04230546951294</t>
   </si>
   <si>
     <t xml:space="preserve">6.05881404876709</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95150566101074</t>
+    <t xml:space="preserve">5.95150518417358</t>
   </si>
   <si>
     <t xml:space="preserve">6.17437744140625</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1760196685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29349756240845</t>
+    <t xml:space="preserve">6.17601919174194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29349803924561</t>
   </si>
   <si>
     <t xml:space="preserve">6.25993204116821</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20958375930786</t>
+    <t xml:space="preserve">6.20958423614502</t>
   </si>
   <si>
     <t xml:space="preserve">6.09210586547852</t>
@@ -1106,19 +1109,16 @@
     <t xml:space="preserve">6.10888910293579</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0753231048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14245367050171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0585412979126</t>
+    <t xml:space="preserve">6.14245414733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05854034423828</t>
   </si>
   <si>
     <t xml:space="preserve">6.02497482299805</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97462797164917</t>
+    <t xml:space="preserve">5.97462749481201</t>
   </si>
   <si>
     <t xml:space="preserve">5.95784425735474</t>
@@ -1136,7 +1136,7 @@
     <t xml:space="preserve">6.42775917053223</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7130651473999</t>
+    <t xml:space="preserve">6.71306419372559</t>
   </si>
   <si>
     <t xml:space="preserve">6.64593458175659</t>
@@ -1145,37 +1145,37 @@
     <t xml:space="preserve">6.69628238677979</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78019523620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7298469543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62915086746216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56202030181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54523754119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67949867248535</t>
+    <t xml:space="preserve">6.78019571304321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72984647750854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.629150390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56201982498169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54523801803589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67949914932251</t>
   </si>
   <si>
     <t xml:space="preserve">6.66271686553955</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57880401611328</t>
+    <t xml:space="preserve">6.57880306243896</t>
   </si>
   <si>
     <t xml:space="preserve">6.37741088867188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34384679794312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22636747360229</t>
+    <t xml:space="preserve">6.3438458442688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22636795043945</t>
   </si>
   <si>
     <t xml:space="preserve">6.36062860488892</t>
@@ -1184,7 +1184,7 @@
     <t xml:space="preserve">5.67253923416138</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55506086349487</t>
+    <t xml:space="preserve">5.55506038665771</t>
   </si>
   <si>
     <t xml:space="preserve">5.68932247161865</t>
@@ -1193,13 +1193,13 @@
     <t xml:space="preserve">5.62219142913818</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53827857971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43758249282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45436573028564</t>
+    <t xml:space="preserve">5.53827810287476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43758201599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45436525344849</t>
   </si>
   <si>
     <t xml:space="preserve">5.60540819168091</t>
@@ -1208,22 +1208,22 @@
     <t xml:space="preserve">5.5214958190918</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50471305847168</t>
+    <t xml:space="preserve">5.50471258163452</t>
   </si>
   <si>
     <t xml:space="preserve">5.4879298210144</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35366868972778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3704514503479</t>
+    <t xml:space="preserve">5.35366916656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37045097351074</t>
   </si>
   <si>
     <t xml:space="preserve">5.42079973220825</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28653812408447</t>
+    <t xml:space="preserve">5.28653860092163</t>
   </si>
   <si>
     <t xml:space="preserve">5.30332040786743</t>
@@ -1235,34 +1235,34 @@
     <t xml:space="preserve">5.38723421096802</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32010316848755</t>
+    <t xml:space="preserve">5.32010364532471</t>
   </si>
   <si>
     <t xml:space="preserve">5.65575647354126</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75645303726196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70610523223877</t>
+    <t xml:space="preserve">5.75645351409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70610475540161</t>
   </si>
   <si>
     <t xml:space="preserve">5.72288703918457</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73967027664185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6389741897583</t>
+    <t xml:space="preserve">5.739670753479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63897466659546</t>
   </si>
   <si>
     <t xml:space="preserve">5.57184410095215</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18584203720093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20262479782104</t>
+    <t xml:space="preserve">5.18584251403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2026252746582</t>
   </si>
   <si>
     <t xml:space="preserve">5.21940803527832</t>
@@ -1292,10 +1292,10 @@
     <t xml:space="preserve">5.06836318969727</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08514595031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23618984222412</t>
+    <t xml:space="preserve">5.08514642715454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23619031906128</t>
   </si>
   <si>
     <t xml:space="preserve">5.25297260284424</t>
@@ -1304,25 +1304,25 @@
     <t xml:space="preserve">5.33688640594482</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79001808166504</t>
+    <t xml:space="preserve">5.79001760482788</t>
   </si>
   <si>
     <t xml:space="preserve">5.77323532104492</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58862590789795</t>
+    <t xml:space="preserve">5.58862638473511</t>
   </si>
   <si>
     <t xml:space="preserve">4.81662368774414</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79984140396118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59844827651978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36349201202393</t>
+    <t xml:space="preserve">4.79984092712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59844875335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36349153518677</t>
   </si>
   <si>
     <t xml:space="preserve">4.31314420700073</t>
@@ -1331,10 +1331,10 @@
     <t xml:space="preserve">4.19566488265991</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11175107955933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02783870697021</t>
+    <t xml:space="preserve">4.11175155639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02783823013306</t>
   </si>
   <si>
     <t xml:space="preserve">4.17049074172974</t>
@@ -1346,19 +1346,19 @@
     <t xml:space="preserve">4.12014293670654</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34670925140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17888212203979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04462099075317</t>
+    <t xml:space="preserve">4.34670829772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17888164520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04462146759033</t>
   </si>
   <si>
     <t xml:space="preserve">4.15370845794678</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26279592514038</t>
+    <t xml:space="preserve">4.2627968788147</t>
   </si>
   <si>
     <t xml:space="preserve">4.16209983825684</t>
@@ -1373,22 +1373,22 @@
     <t xml:space="preserve">4.09496927261353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98588132858276</t>
+    <t xml:space="preserve">3.98588180541992</t>
   </si>
   <si>
     <t xml:space="preserve">4.2795786857605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22922992706299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21244812011719</t>
+    <t xml:space="preserve">4.22923040390015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21244764328003</t>
   </si>
   <si>
     <t xml:space="preserve">4.03622961044312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12877941131592</t>
+    <t xml:space="preserve">4.1287784576416</t>
   </si>
   <si>
     <t xml:space="preserve">4.16283082962036</t>
@@ -1397,10 +1397,10 @@
     <t xml:space="preserve">4.07770156860352</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00108528137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20539569854736</t>
+    <t xml:space="preserve">4.00108480453491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20539522171021</t>
   </si>
   <si>
     <t xml:space="preserve">4.37565469741821</t>
@@ -1409,19 +1409,19 @@
     <t xml:space="preserve">4.21390867233276</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22242212295532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25647401809692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24796009063721</t>
+    <t xml:space="preserve">4.22242164611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25647306442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24796056747437</t>
   </si>
   <si>
     <t xml:space="preserve">4.32457685470581</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30755138397217</t>
+    <t xml:space="preserve">4.30755090713501</t>
   </si>
   <si>
     <t xml:space="preserve">4.23944759368896</t>
@@ -1430,61 +1430,61 @@
     <t xml:space="preserve">4.35862827301025</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5118613243103</t>
+    <t xml:space="preserve">4.51186180114746</t>
   </si>
   <si>
     <t xml:space="preserve">5.5334153175354</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94203662872314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89095878601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73772573471069</t>
+    <t xml:space="preserve">5.9420371055603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8909592628479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73772621154785</t>
   </si>
   <si>
     <t xml:space="preserve">5.5504412651062</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58449268341064</t>
+    <t xml:space="preserve">5.5844931602478</t>
   </si>
   <si>
     <t xml:space="preserve">5.567467212677</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41423368453979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26100063323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.482337474823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4482855796814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60151863098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66962194442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5163893699646</t>
+    <t xml:space="preserve">5.41423416137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26100158691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48233795166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44828605651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6015191078186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66962242126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51638889312744</t>
   </si>
   <si>
     <t xml:space="preserve">5.70367431640625</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32910442352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27802658081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43126010894775</t>
+    <t xml:space="preserve">5.32910490036011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27802705764771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43126058578491</t>
   </si>
   <si>
     <t xml:space="preserve">5.31207847595215</t>
@@ -1493,25 +1493,25 @@
     <t xml:space="preserve">5.2269492149353</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00561285018921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95453500747681</t>
+    <t xml:space="preserve">5.00561237335205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95453548431396</t>
   </si>
   <si>
     <t xml:space="preserve">4.93750905990601</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05669021606445</t>
+    <t xml:space="preserve">5.05669069290161</t>
   </si>
   <si>
     <t xml:space="preserve">5.03966426849365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97156047821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88643074035645</t>
+    <t xml:space="preserve">4.97156143188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8864312171936</t>
   </si>
   <si>
     <t xml:space="preserve">5.02263832092285</t>
@@ -1520,13 +1520,13 @@
     <t xml:space="preserve">4.92048358917236</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9034571647644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85237884521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8694052696228</t>
+    <t xml:space="preserve">4.90345764160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.852379322052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86940479278564</t>
   </si>
   <si>
     <t xml:space="preserve">5.34613037109375</t>
@@ -1538,34 +1538,34 @@
     <t xml:space="preserve">5.36315631866455</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38018274307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20992279052734</t>
+    <t xml:space="preserve">5.38018226623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2099232673645</t>
   </si>
   <si>
     <t xml:space="preserve">5.1588454246521</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1077675819397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98858690261841</t>
+    <t xml:space="preserve">5.10776853561401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98858642578125</t>
   </si>
   <si>
     <t xml:space="preserve">5.09074211120605</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19289684295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1758713722229</t>
+    <t xml:space="preserve">5.1928973197937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17587089538574</t>
   </si>
   <si>
     <t xml:space="preserve">5.14181995391846</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07371664047241</t>
+    <t xml:space="preserve">5.07371616363525</t>
   </si>
   <si>
     <t xml:space="preserve">4.68212032318115</t>
@@ -1574,10 +1574,10 @@
     <t xml:space="preserve">4.54591369628906</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59699058532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57996511459351</t>
+    <t xml:space="preserve">4.59699153900146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57996559143066</t>
   </si>
   <si>
     <t xml:space="preserve">4.63104295730591</t>
@@ -1586,13 +1586,13 @@
     <t xml:space="preserve">4.78427600860596</t>
   </si>
   <si>
-    <t xml:space="preserve">4.767249584198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8183274269104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8013014793396</t>
+    <t xml:space="preserve">4.76725006103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81832790374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80130195617676</t>
   </si>
   <si>
     <t xml:space="preserve">5.39720821380615</t>
@@ -1601,16 +1601,16 @@
     <t xml:space="preserve">5.61854457855225</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46531200408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49936294555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63557052612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68664836883545</t>
+    <t xml:space="preserve">5.4653115272522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49936389923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63557100296021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68664789199829</t>
   </si>
   <si>
     <t xml:space="preserve">5.65259647369385</t>
@@ -1622,16 +1622,16 @@
     <t xml:space="preserve">5.8739333152771</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31660652160645</t>
+    <t xml:space="preserve">6.3166069984436</t>
   </si>
   <si>
     <t xml:space="preserve">6.33363246917725</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29958009719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35065793991089</t>
+    <t xml:space="preserve">6.29958057403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35065841674805</t>
   </si>
   <si>
     <t xml:space="preserve">6.43578720092773</t>
@@ -1640,19 +1640,19 @@
     <t xml:space="preserve">6.55496883392334</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69117641448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79333114624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15087509155273</t>
+    <t xml:space="preserve">6.6911768913269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79333162307739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15087461471558</t>
   </si>
   <si>
     <t xml:space="preserve">7.08277082443237</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87846040725708</t>
+    <t xml:space="preserve">6.87846088409424</t>
   </si>
   <si>
     <t xml:space="preserve">6.77630567550659</t>
@@ -1661,19 +1661,19 @@
     <t xml:space="preserve">6.84440946578979</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70820188522339</t>
+    <t xml:space="preserve">6.70820236206055</t>
   </si>
   <si>
     <t xml:space="preserve">6.75927972793579</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53794288635254</t>
+    <t xml:space="preserve">6.5379433631897</t>
   </si>
   <si>
     <t xml:space="preserve">6.72522783279419</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65712404251099</t>
+    <t xml:space="preserve">6.65712451934814</t>
   </si>
   <si>
     <t xml:space="preserve">6.91251230239868</t>
@@ -1682,37 +1682,37 @@
     <t xml:space="preserve">6.8954873085022</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96359062194824</t>
+    <t xml:space="preserve">6.96359014511108</t>
   </si>
   <si>
     <t xml:space="preserve">7.17302179336548</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05085325241089</t>
+    <t xml:space="preserve">7.05085372924805</t>
   </si>
   <si>
     <t xml:space="preserve">7.1206636428833</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57443237304688</t>
+    <t xml:space="preserve">7.57443189620972</t>
   </si>
   <si>
     <t xml:space="preserve">7.97584247589111</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02819919586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06310558319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99329519271851</t>
+    <t xml:space="preserve">8.02820014953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0631046295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99329423904419</t>
   </si>
   <si>
     <t xml:space="preserve">8.0107479095459</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94093751907349</t>
+    <t xml:space="preserve">7.94093656539917</t>
   </si>
   <si>
     <t xml:space="preserve">8.13291549682617</t>
@@ -1721,28 +1721,28 @@
     <t xml:space="preserve">8.15036773681641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16782093048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18527412414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34234809875488</t>
+    <t xml:space="preserve">8.16781902313232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18527317047119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34234714508057</t>
   </si>
   <si>
     <t xml:space="preserve">8.11546325683594</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25508403778076</t>
+    <t xml:space="preserve">8.25508308410645</t>
   </si>
   <si>
     <t xml:space="preserve">8.08055782318115</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20272541046143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95838928222656</t>
+    <t xml:space="preserve">8.20272445678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95838832855225</t>
   </si>
   <si>
     <t xml:space="preserve">8.37725162506104</t>
@@ -1754,13 +1754,13 @@
     <t xml:space="preserve">8.81356716156006</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58668327331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53432559967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69139957427979</t>
+    <t xml:space="preserve">8.58668231964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53432464599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69139862060547</t>
   </si>
   <si>
     <t xml:space="preserve">8.60413551330566</t>
@@ -1769,7 +1769,7 @@
     <t xml:space="preserve">8.72630405426025</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42960929870605</t>
+    <t xml:space="preserve">8.42961025238037</t>
   </si>
   <si>
     <t xml:space="preserve">8.28998851776123</t>
@@ -1781,16 +1781,16 @@
     <t xml:space="preserve">8.04565238952637</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85367345809937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41215801239014</t>
+    <t xml:space="preserve">7.85367298126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41215705871582</t>
   </si>
   <si>
     <t xml:space="preserve">8.22017860412598</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44706344604492</t>
+    <t xml:space="preserve">8.44706249237061</t>
   </si>
   <si>
     <t xml:space="preserve">8.3597993850708</t>
@@ -1802,25 +1802,25 @@
     <t xml:space="preserve">8.23763084411621</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48196792602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62158966064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55177879333496</t>
+    <t xml:space="preserve">8.48196697235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6215877532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55177783966064</t>
   </si>
   <si>
     <t xml:space="preserve">8.65649318695068</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51687335968018</t>
+    <t xml:space="preserve">8.51687240600586</t>
   </si>
   <si>
     <t xml:space="preserve">8.46451473236084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49942016601562</t>
+    <t xml:space="preserve">8.49941921234131</t>
   </si>
   <si>
     <t xml:space="preserve">8.56923007965088</t>
@@ -1829,10 +1829,10 @@
     <t xml:space="preserve">9.99161720275879</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59893321990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77345943450928</t>
+    <t xml:space="preserve">9.59893417358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77346038818359</t>
   </si>
   <si>
     <t xml:space="preserve">9.8170919418335</t>
@@ -1841,61 +1841,61 @@
     <t xml:space="preserve">9.29351329803467</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46804046630859</t>
+    <t xml:space="preserve">9.46803951263428</t>
   </si>
   <si>
     <t xml:space="preserve">9.55530261993408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64256572723389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90435600280762</t>
+    <t xml:space="preserve">9.6425666809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9043550491333</t>
   </si>
   <si>
     <t xml:space="preserve">9.33714485168457</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94798469543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86072254180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5151968002319</t>
+    <t xml:space="preserve">9.94798564910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8607234954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5151958465576</t>
   </si>
   <si>
     <t xml:space="preserve">10.4279327392578</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5588264465332</t>
+    <t xml:space="preserve">10.5588283538818</t>
   </si>
   <si>
     <t xml:space="preserve">10.6024589538574</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8206157684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7333526611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.776985168457</t>
+    <t xml:space="preserve">10.8206167221069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7333545684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7769861221313</t>
   </si>
   <si>
     <t xml:space="preserve">10.2970380783081</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3843002319336</t>
+    <t xml:space="preserve">10.3843011856079</t>
   </si>
   <si>
     <t xml:space="preserve">10.3406705856323</t>
   </si>
   <si>
-    <t xml:space="preserve">10.209774017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2534074783325</t>
+    <t xml:space="preserve">10.2097749710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2534065246582</t>
   </si>
   <si>
     <t xml:space="preserve">10.0788812637329</t>
@@ -1907,13 +1907,13 @@
     <t xml:space="preserve">9.72982883453369</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68619728088379</t>
+    <t xml:space="preserve">9.68619823455811</t>
   </si>
   <si>
     <t xml:space="preserve">8.98809337615967</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42440700531006</t>
+    <t xml:space="preserve">9.42440795898438</t>
   </si>
   <si>
     <t xml:space="preserve">11.6496162414551</t>
@@ -1922,16 +1922,16 @@
     <t xml:space="preserve">11.562352180481</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7805099487305</t>
+    <t xml:space="preserve">11.7805109024048</t>
   </si>
   <si>
     <t xml:space="preserve">11.9114036560059</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9550361633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6932468414307</t>
+    <t xml:space="preserve">11.9550352096558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.693247795105</t>
   </si>
   <si>
     <t xml:space="preserve">12.3040885925293</t>
@@ -1946,28 +1946,28 @@
     <t xml:space="preserve">12.3913516998291</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7368783950806</t>
+    <t xml:space="preserve">11.7368793487549</t>
   </si>
   <si>
     <t xml:space="preserve">11.8677730560303</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6059837341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9515113830566</t>
+    <t xml:space="preserve">11.6059846878052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9515104293823</t>
   </si>
   <si>
     <t xml:space="preserve">12.0422992706299</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3005638122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3441944122314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9951419830322</t>
+    <t xml:space="preserve">11.3005628585815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3441953659058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9951429367065</t>
   </si>
   <si>
     <t xml:space="preserve">10.4715642929077</t>
@@ -1976,34 +1976,34 @@
     <t xml:space="preserve">10.9078798294067</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4314575195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0387744903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9899406433105</t>
+    <t xml:space="preserve">11.4314584732056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0387735366821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9899415969849</t>
   </si>
   <si>
     <t xml:space="preserve">11.7456045150757</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5361738204956</t>
+    <t xml:space="preserve">11.5361728668213</t>
   </si>
   <si>
     <t xml:space="preserve">11.5187206268311</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6234350204468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4489097595215</t>
+    <t xml:space="preserve">11.6234359741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4489116668701</t>
   </si>
   <si>
     <t xml:space="preserve">11.6408891677856</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7281513214111</t>
+    <t xml:space="preserve">11.7281522750854</t>
   </si>
   <si>
     <t xml:space="preserve">11.9201307296753</t>
@@ -2012,19 +2012,19 @@
     <t xml:space="preserve">11.1173105239868</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0998582839966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8031644821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7508058547974</t>
+    <t xml:space="preserve">11.0998592376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8031635284424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7508068084717</t>
   </si>
   <si>
     <t xml:space="preserve">10.3319435119629</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1050596237183</t>
+    <t xml:space="preserve">10.1050605773926</t>
   </si>
   <si>
     <t xml:space="preserve">9.81839179992676</t>
@@ -2033,7 +2033,7 @@
     <t xml:space="preserve">9.69297409057617</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71089172363281</t>
+    <t xml:space="preserve">9.7108907699585</t>
   </si>
   <si>
     <t xml:space="preserve">10.1408929824829</t>
@@ -2042,31 +2042,31 @@
     <t xml:space="preserve">10.2663106918335</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3738107681274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1229772567749</t>
+    <t xml:space="preserve">10.3738117218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1229763031006</t>
   </si>
   <si>
     <t xml:space="preserve">10.1588106155396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0692262649536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0871438980103</t>
+    <t xml:space="preserve">10.0692253112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0871429443359</t>
   </si>
   <si>
     <t xml:space="preserve">10.4633951187134</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7858963012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.570897102356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7142305374146</t>
+    <t xml:space="preserve">10.7858982086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5708961486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7142295837402</t>
   </si>
   <si>
     <t xml:space="preserve">10.7500638961792</t>
@@ -2078,16 +2078,16 @@
     <t xml:space="preserve">10.8754816055298</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6425638198853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.588812828064</t>
+    <t xml:space="preserve">10.6425619125366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5888118743896</t>
   </si>
   <si>
     <t xml:space="preserve">10.5171461105347</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8575639724731</t>
+    <t xml:space="preserve">10.8575649261475</t>
   </si>
   <si>
     <t xml:space="preserve">10.9113149642944</t>
@@ -2102,25 +2102,25 @@
     <t xml:space="preserve">10.3021440505981</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4096450805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3558950424194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6783971786499</t>
+    <t xml:space="preserve">10.4096441268921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3558940887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6783962249756</t>
   </si>
   <si>
     <t xml:space="preserve">10.4275617599487</t>
   </si>
   <si>
-    <t xml:space="preserve">10.535062789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1800651550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.982982635498</t>
+    <t xml:space="preserve">10.5350618362427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1800661087036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9829816818237</t>
   </si>
   <si>
     <t xml:space="preserve">11.4846515655518</t>
@@ -2132,13 +2132,13 @@
     <t xml:space="preserve">11.7354860305786</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9146547317505</t>
+    <t xml:space="preserve">11.9146537780762</t>
   </si>
   <si>
     <t xml:space="preserve">11.9325704574585</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0221548080444</t>
+    <t xml:space="preserve">12.0221538543701</t>
   </si>
   <si>
     <t xml:space="preserve">11.8788204193115</t>
@@ -2171,37 +2171,37 @@
     <t xml:space="preserve">12.6134080886841</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8463268280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8104934692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9179925918579</t>
+    <t xml:space="preserve">12.8463258743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.810492515564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9179935455322</t>
   </si>
   <si>
     <t xml:space="preserve">13.258412361145</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4017467498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4375791549683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6884145736694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.903416633606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6559209823608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2438335418701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6380033493042</t>
+    <t xml:space="preserve">13.4017457962036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4375801086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6884136199951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9034156799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6559200286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2438344955444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6380043029785</t>
   </si>
   <si>
     <t xml:space="preserve">14.92467212677</t>
@@ -2216,10 +2216,10 @@
     <t xml:space="preserve">14.7992544174194</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5484199523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4946689605713</t>
+    <t xml:space="preserve">14.5484189987183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4946699142456</t>
   </si>
   <si>
     <t xml:space="preserve">14.2617511749268</t>
@@ -2228,25 +2228,25 @@
     <t xml:space="preserve">14.8888387680054</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8171710968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.387167930603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7634201049805</t>
+    <t xml:space="preserve">14.8171730041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3871688842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7634210586548</t>
   </si>
   <si>
     <t xml:space="preserve">14.6200866699219</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9067535400391</t>
+    <t xml:space="preserve">14.9067544937134</t>
   </si>
   <si>
     <t xml:space="preserve">15.1217546463013</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0321741104126</t>
+    <t xml:space="preserve">15.0321731567383</t>
   </si>
   <si>
     <t xml:space="preserve">14.7455034255981</t>
@@ -2255,22 +2255,22 @@
     <t xml:space="preserve">15.0500888824463</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0680065155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1038398742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5305023193359</t>
+    <t xml:space="preserve">15.0680046081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1038408279419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5305032730103</t>
   </si>
   <si>
     <t xml:space="preserve">14.7096710205078</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2080011367798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6167469024658</t>
+    <t xml:space="preserve">14.2080001831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6167478561401</t>
   </si>
   <si>
     <t xml:space="preserve">13.5092468261719</t>
@@ -2279,10 +2279,10 @@
     <t xml:space="preserve">13.0434112548828</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1688280105591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9717426300049</t>
+    <t xml:space="preserve">13.1688270568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9717435836792</t>
   </si>
   <si>
     <t xml:space="preserve">12.4700746536255</t>
@@ -2303,7 +2303,7 @@
     <t xml:space="preserve">13.4913301467896</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2225790023804</t>
+    <t xml:space="preserve">13.2225780487061</t>
   </si>
   <si>
     <t xml:space="preserve">13.2046613693237</t>
@@ -2315,19 +2315,19 @@
     <t xml:space="preserve">13.0075778961182</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6313247680664</t>
+    <t xml:space="preserve">12.6313257217407</t>
   </si>
   <si>
     <t xml:space="preserve">13.0971612930298</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0792436599731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8642425537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9896602630615</t>
+    <t xml:space="preserve">13.0792446136475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8642435073853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9896593093872</t>
   </si>
   <si>
     <t xml:space="preserve">12.9538269042969</t>
@@ -2342,16 +2342,16 @@
     <t xml:space="preserve">13.1150779724121</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1509103775024</t>
+    <t xml:space="preserve">13.1509122848511</t>
   </si>
   <si>
     <t xml:space="preserve">13.5271635055542</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3479957580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2763290405273</t>
+    <t xml:space="preserve">13.3479948043823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.276328086853</t>
   </si>
   <si>
     <t xml:space="preserve">12.7925758361816</t>
@@ -2363,13 +2363,13 @@
     <t xml:space="preserve">12.5238237380981</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5059070587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4879903793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3088235855103</t>
+    <t xml:space="preserve">12.5059080123901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4879894256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3088226318359</t>
   </si>
   <si>
     <t xml:space="preserve">12.5417413711548</t>
@@ -2378,7 +2378,7 @@
     <t xml:space="preserve">12.8284091949463</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3804903030396</t>
+    <t xml:space="preserve">12.3804893493652</t>
   </si>
   <si>
     <t xml:space="preserve">12.6671581268311</t>
@@ -2390,7 +2390,7 @@
     <t xml:space="preserve">12.6492414474487</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7746601104736</t>
+    <t xml:space="preserve">12.7746591567993</t>
   </si>
   <si>
     <t xml:space="preserve">12.4342403411865</t>
@@ -2399,19 +2399,19 @@
     <t xml:space="preserve">11.9504880905151</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2192392349243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8250694274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1117382049561</t>
+    <t xml:space="preserve">12.2192401885986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8250703811646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1117391586304</t>
   </si>
   <si>
     <t xml:space="preserve">11.9684038162231</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0400705337524</t>
+    <t xml:space="preserve">12.0400714874268</t>
   </si>
   <si>
     <t xml:space="preserve">12.0042381286621</t>
@@ -2423,16 +2423,16 @@
     <t xml:space="preserve">12.7388257980347</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7421655654907</t>
+    <t xml:space="preserve">13.7421646118164</t>
   </si>
   <si>
     <t xml:space="preserve">13.7063312530518</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0825843811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0109157562256</t>
+    <t xml:space="preserve">14.0825834274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0109167098999</t>
   </si>
   <si>
     <t xml:space="preserve">13.7242479324341</t>
@@ -2444,10 +2444,10 @@
     <t xml:space="preserve">14.0646667480469</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9392490386963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6346645355225</t>
+    <t xml:space="preserve">13.9392499923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6346635818481</t>
   </si>
   <si>
     <t xml:space="preserve">14.2796678543091</t>
@@ -2459,16 +2459,16 @@
     <t xml:space="preserve">13.9571657180786</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8496656417847</t>
+    <t xml:space="preserve">13.8496646881104</t>
   </si>
   <si>
     <t xml:space="preserve">13.9750833511353</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5450792312622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4734125137329</t>
+    <t xml:space="preserve">13.5450801849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4734134674072</t>
   </si>
   <si>
     <t xml:space="preserve">13.1867456436157</t>
@@ -2480,10 +2480,10 @@
     <t xml:space="preserve">13.5988302230835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.70299243927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8429870605469</t>
+    <t xml:space="preserve">12.7029914855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8429861068726</t>
   </si>
   <si>
     <t xml:space="preserve">11.7892360687256</t>
@@ -2495,31 +2495,31 @@
     <t xml:space="preserve">12.0759048461914</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5742349624634</t>
+    <t xml:space="preserve">11.5742359161377</t>
   </si>
   <si>
     <t xml:space="preserve">11.2159004211426</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3592338562012</t>
+    <t xml:space="preserve">11.3592348098755</t>
   </si>
   <si>
     <t xml:space="preserve">11.4309024810791</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3054828643799</t>
+    <t xml:space="preserve">11.3054838180542</t>
   </si>
   <si>
     <t xml:space="preserve">11.2875671386719</t>
   </si>
   <si>
-    <t xml:space="preserve">11.683783531189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5179262161255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2783517837524</t>
+    <t xml:space="preserve">11.6837844848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5179252624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2783527374268</t>
   </si>
   <si>
     <t xml:space="preserve">11.1493520736694</t>
@@ -2531,7 +2531,7 @@
     <t xml:space="preserve">11.0756378173828</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9970722198486</t>
+    <t xml:space="preserve">11.9970712661743</t>
   </si>
   <si>
     <t xml:space="preserve">12.052357673645</t>
@@ -2540,7 +2540,7 @@
     <t xml:space="preserve">12.2735013961792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2182149887085</t>
+    <t xml:space="preserve">12.2182159423828</t>
   </si>
   <si>
     <t xml:space="preserve">12.4025020599365</t>
@@ -2552,7 +2552,7 @@
     <t xml:space="preserve">12.0707864761353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1629285812378</t>
+    <t xml:space="preserve">12.1629295349121</t>
   </si>
   <si>
     <t xml:space="preserve">12.1260719299316</t>
@@ -2567,13 +2567,13 @@
     <t xml:space="preserve">11.7759265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8312129974365</t>
+    <t xml:space="preserve">11.8312139511108</t>
   </si>
   <si>
     <t xml:space="preserve">11.9786424636841</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7206411361694</t>
+    <t xml:space="preserve">11.7206420898438</t>
   </si>
   <si>
     <t xml:space="preserve">11.868070602417</t>
@@ -2588,7 +2588,7 @@
     <t xml:space="preserve">11.4442110061646</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3520669937134</t>
+    <t xml:space="preserve">11.3520679473877</t>
   </si>
   <si>
     <t xml:space="preserve">11.3704957962036</t>
@@ -2606,7 +2606,7 @@
     <t xml:space="preserve">11.7022123336792</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5732116699219</t>
+    <t xml:space="preserve">11.5732126235962</t>
   </si>
   <si>
     <t xml:space="preserve">11.481068611145</t>
@@ -2615,7 +2615,7 @@
     <t xml:space="preserve">11.296781539917</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3152093887329</t>
+    <t xml:space="preserve">11.3152103424072</t>
   </si>
   <si>
     <t xml:space="preserve">11.5547828674316</t>
@@ -2624,7 +2624,7 @@
     <t xml:space="preserve">11.4257822036743</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3336381912231</t>
+    <t xml:space="preserve">11.3336391448975</t>
   </si>
   <si>
     <t xml:space="preserve">11.3889245986938</t>
@@ -2633,7 +2633,7 @@
     <t xml:space="preserve">11.4626398086548</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7943553924561</t>
+    <t xml:space="preserve">11.7943563461304</t>
   </si>
   <si>
     <t xml:space="preserve">12.1076431274414</t>
@@ -2663,7 +2663,7 @@
     <t xml:space="preserve">13.0290775299072</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2502222061157</t>
+    <t xml:space="preserve">13.2502212524414</t>
   </si>
   <si>
     <t xml:space="preserve">13.4160804748535</t>
@@ -2678,7 +2678,7 @@
     <t xml:space="preserve">12.6420755386353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8816480636597</t>
+    <t xml:space="preserve">12.8816471099854</t>
   </si>
   <si>
     <t xml:space="preserve">12.9185056686401</t>
@@ -2687,7 +2687,7 @@
     <t xml:space="preserve">13.194935798645</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1580772399902</t>
+    <t xml:space="preserve">13.1580781936646</t>
   </si>
   <si>
     <t xml:space="preserve">12.8079328536987</t>
@@ -2702,7 +2702,7 @@
     <t xml:space="preserve">12.5499315261841</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0843629837036</t>
+    <t xml:space="preserve">13.0843639373779</t>
   </si>
   <si>
     <t xml:space="preserve">13.3423643112183</t>
@@ -2720,13 +2720,13 @@
     <t xml:space="preserve">13.1027917861938</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3607940673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2133646011353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5266513824463</t>
+    <t xml:space="preserve">13.3607931137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2133636474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5266523361206</t>
   </si>
   <si>
     <t xml:space="preserve">13.6003665924072</t>
@@ -2744,28 +2744,28 @@
     <t xml:space="preserve">13.7846536636353</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0610828399658</t>
+    <t xml:space="preserve">14.0610837936401</t>
   </si>
   <si>
     <t xml:space="preserve">14.2637987136841</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5402297973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6139440536499</t>
+    <t xml:space="preserve">14.540228843689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6139430999756</t>
   </si>
   <si>
     <t xml:space="preserve">15.3695201873779</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5353784561157</t>
+    <t xml:space="preserve">15.53537940979</t>
   </si>
   <si>
     <t xml:space="preserve">15.6275205612183</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5722360610962</t>
+    <t xml:space="preserve">15.5722341537476</t>
   </si>
   <si>
     <t xml:space="preserve">15.4063768386841</t>
@@ -2777,34 +2777,34 @@
     <t xml:space="preserve">15.295804977417</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2773761749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4616651535034</t>
+    <t xml:space="preserve">15.2773771286011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4616641998291</t>
   </si>
   <si>
     <t xml:space="preserve">15.6459493637085</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4432344436646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6643781661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7012376785278</t>
+    <t xml:space="preserve">15.4432353973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.664379119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7012367248535</t>
   </si>
   <si>
     <t xml:space="preserve">15.6090936660767</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3326606750488</t>
+    <t xml:space="preserve">15.3326616287231</t>
   </si>
   <si>
     <t xml:space="preserve">15.2036619186401</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1668033599854</t>
+    <t xml:space="preserve">15.1668043136597</t>
   </si>
   <si>
     <t xml:space="preserve">14.8535175323486</t>
@@ -2825,22 +2825,22 @@
     <t xml:space="preserve">15.8302373886108</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7196645736694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3879489898682</t>
+    <t xml:space="preserve">15.7196636199951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3879499435425</t>
   </si>
   <si>
     <t xml:space="preserve">15.5906648635864</t>
   </si>
   <si>
-    <t xml:space="preserve">15.682806968689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7565221786499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7380933761597</t>
+    <t xml:space="preserve">15.6828079223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7565231323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.738094329834</t>
   </si>
   <si>
     <t xml:space="preserve">15.1483764648438</t>
@@ -2852,7 +2852,7 @@
     <t xml:space="preserve">15.1299476623535</t>
   </si>
   <si>
-    <t xml:space="preserve">15.480092048645</t>
+    <t xml:space="preserve">15.4800910949707</t>
   </si>
   <si>
     <t xml:space="preserve">15.9223804473877</t>
@@ -2864,22 +2864,22 @@
     <t xml:space="preserve">16.0882377624512</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7749509811401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.867094039917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7109394073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6556529998779</t>
+    <t xml:space="preserve">15.7749519348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8670930862427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7109384536743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6556520462036</t>
   </si>
   <si>
     <t xml:space="preserve">13.6372241973877</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1347990036011</t>
+    <t xml:space="preserve">14.1347980499268</t>
   </si>
   <si>
     <t xml:space="preserve">14.4480857849121</t>
@@ -2891,7 +2891,7 @@
     <t xml:space="preserve">14.0242261886597</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0795125961304</t>
+    <t xml:space="preserve">14.0795116424561</t>
   </si>
   <si>
     <t xml:space="preserve">14.0057973861694</t>
@@ -2912,7 +2912,7 @@
     <t xml:space="preserve">13.4897947311401</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6187953948975</t>
+    <t xml:space="preserve">13.6187944412231</t>
   </si>
   <si>
     <t xml:space="preserve">12.8263626098633</t>
@@ -2924,7 +2924,7 @@
     <t xml:space="preserve">13.2686500549316</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9369335174561</t>
+    <t xml:space="preserve">12.9369344711304</t>
   </si>
   <si>
     <t xml:space="preserve">12.9000768661499</t>
@@ -2933,10 +2933,10 @@
     <t xml:space="preserve">12.9922199249268</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0475053787231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6973600387573</t>
+    <t xml:space="preserve">13.0475063323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6973609924316</t>
   </si>
   <si>
     <t xml:space="preserve">12.6052179336548</t>
@@ -2948,7 +2948,7 @@
     <t xml:space="preserve">12.4209308624268</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4762172698975</t>
+    <t xml:space="preserve">12.4762163162231</t>
   </si>
   <si>
     <t xml:space="preserve">12.6236457824707</t>
@@ -3540,6 +3540,9 @@
   </si>
   <si>
     <t xml:space="preserve">17.3600006103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4599990844727</t>
   </si>
 </sst>
 </file>
@@ -19938,7 +19941,7 @@
         <v>7.97442579269409</v>
       </c>
       <c r="G618" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19964,7 +19967,7 @@
         <v>8.13214015960693</v>
       </c>
       <c r="G619" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19990,7 +19993,7 @@
         <v>7.81671190261841</v>
       </c>
       <c r="G620" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -20016,7 +20019,7 @@
         <v>7.81671190261841</v>
       </c>
       <c r="G621" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -20042,7 +20045,7 @@
         <v>7.54071187973022</v>
       </c>
       <c r="G622" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -20068,7 +20071,7 @@
         <v>7.5505690574646</v>
       </c>
       <c r="G623" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -20094,7 +20097,7 @@
         <v>7.58014106750488</v>
       </c>
       <c r="G624" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -20120,7 +20123,7 @@
         <v>7.61956882476807</v>
       </c>
       <c r="G625" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -20146,7 +20149,7 @@
         <v>7.5505690574646</v>
       </c>
       <c r="G626" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -20172,7 +20175,7 @@
         <v>7.63928318023682</v>
       </c>
       <c r="G627" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -20198,7 +20201,7 @@
         <v>7.72799777984619</v>
       </c>
       <c r="G628" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -20224,7 +20227,7 @@
         <v>7.61956882476807</v>
       </c>
       <c r="G629" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -20250,7 +20253,7 @@
         <v>7.50128316879272</v>
       </c>
       <c r="G630" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -20276,7 +20279,7 @@
         <v>7.4322829246521</v>
       </c>
       <c r="G631" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -20302,7 +20305,7 @@
         <v>7.27456903457642</v>
       </c>
       <c r="G632" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -20328,7 +20331,7 @@
         <v>7.04785490036011</v>
       </c>
       <c r="G633" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -20354,7 +20357,7 @@
         <v>7.11685514450073</v>
       </c>
       <c r="G634" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -20380,7 +20383,7 @@
         <v>7.27456903457642</v>
       </c>
       <c r="G635" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -20406,7 +20409,7 @@
         <v>7.15628290176392</v>
       </c>
       <c r="G636" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -20432,7 +20435,7 @@
         <v>7.41256904602051</v>
       </c>
       <c r="G637" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -20458,7 +20461,7 @@
         <v>7.33371210098267</v>
       </c>
       <c r="G638" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -20484,7 +20487,7 @@
         <v>7.39285516738892</v>
       </c>
       <c r="G639" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -20510,7 +20513,7 @@
         <v>7.33371210098267</v>
       </c>
       <c r="G640" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -20536,7 +20539,7 @@
         <v>7.34356880187988</v>
       </c>
       <c r="G641" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -20562,7 +20565,7 @@
         <v>7.25485515594482</v>
       </c>
       <c r="G642" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -20588,7 +20591,7 @@
         <v>7.47171211242676</v>
       </c>
       <c r="G643" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -20614,7 +20617,7 @@
         <v>7.41256904602051</v>
       </c>
       <c r="G644" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -20640,7 +20643,7 @@
         <v>7.25485515594482</v>
       </c>
       <c r="G645" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -20666,7 +20669,7 @@
         <v>7.17599821090698</v>
       </c>
       <c r="G646" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -20692,7 +20695,7 @@
         <v>7.1464262008667</v>
       </c>
       <c r="G647" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -20718,7 +20721,7 @@
         <v>7.31399822235107</v>
       </c>
       <c r="G648" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -20744,7 +20747,7 @@
         <v>7.17599821090698</v>
       </c>
       <c r="G649" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -20770,7 +20773,7 @@
         <v>7.31399822235107</v>
       </c>
       <c r="G650" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -20796,7 +20799,7 @@
         <v>7.32385492324829</v>
       </c>
       <c r="G651" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -20822,7 +20825,7 @@
         <v>7.49142599105835</v>
       </c>
       <c r="G652" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -20848,7 +20851,7 @@
         <v>7.69842576980591</v>
       </c>
       <c r="G653" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -20874,7 +20877,7 @@
         <v>7.82656908035278</v>
       </c>
       <c r="G654" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -20900,7 +20903,7 @@
         <v>7.77728319168091</v>
       </c>
       <c r="G655" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -20926,7 +20929,7 @@
         <v>7.59985494613647</v>
       </c>
       <c r="G656" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -20952,7 +20955,7 @@
         <v>7.63928318023682</v>
       </c>
       <c r="G657" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -20978,7 +20981,7 @@
         <v>7.61956882476807</v>
       </c>
       <c r="G658" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -21004,7 +21007,7 @@
         <v>7.45199823379517</v>
       </c>
       <c r="G659" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -21030,7 +21033,7 @@
         <v>7.45199823379517</v>
       </c>
       <c r="G660" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -21056,7 +21059,7 @@
         <v>7.34356880187988</v>
       </c>
       <c r="G661" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -21082,7 +21085,7 @@
         <v>7.42242622375488</v>
       </c>
       <c r="G662" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -21108,7 +21111,7 @@
         <v>7.50128316879272</v>
       </c>
       <c r="G663" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -21134,7 +21137,7 @@
         <v>7.44214105606079</v>
       </c>
       <c r="G664" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -21160,7 +21163,7 @@
         <v>7.50128316879272</v>
       </c>
       <c r="G665" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -21186,7 +21189,7 @@
         <v>7.50128316879272</v>
       </c>
       <c r="G666" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -21212,7 +21215,7 @@
         <v>7.46185493469238</v>
       </c>
       <c r="G667" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -21238,7 +21241,7 @@
         <v>7.3041410446167</v>
       </c>
       <c r="G668" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -21264,7 +21267,7 @@
         <v>7.29428291320801</v>
       </c>
       <c r="G669" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -21290,7 +21293,7 @@
         <v>7.22528314590454</v>
       </c>
       <c r="G670" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -21316,7 +21319,7 @@
         <v>7.03799819946289</v>
       </c>
       <c r="G671" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -21342,7 +21345,7 @@
         <v>7.11685514450073</v>
       </c>
       <c r="G672" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -21368,7 +21371,7 @@
         <v>7.15628290176392</v>
       </c>
       <c r="G673" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -21394,7 +21397,7 @@
         <v>7.22528314590454</v>
       </c>
       <c r="G674" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -21420,7 +21423,7 @@
         <v>7.22528314590454</v>
       </c>
       <c r="G675" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -21446,7 +21449,7 @@
         <v>7.17599821090698</v>
       </c>
       <c r="G676" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -21472,7 +21475,7 @@
         <v>6.8999981880188</v>
       </c>
       <c r="G677" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -21498,7 +21501,7 @@
         <v>6.80142593383789</v>
       </c>
       <c r="G678" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -21524,7 +21527,7 @@
         <v>6.91971206665039</v>
       </c>
       <c r="G679" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -21550,7 +21553,7 @@
         <v>6.92956876754761</v>
       </c>
       <c r="G680" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -21576,7 +21579,7 @@
         <v>6.8999981880188</v>
       </c>
       <c r="G681" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -21602,7 +21605,7 @@
         <v>6.8999981880188</v>
       </c>
       <c r="G682" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -21628,7 +21631,7 @@
         <v>6.91971206665039</v>
       </c>
       <c r="G683" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -21654,7 +21657,7 @@
         <v>6.95914077758789</v>
       </c>
       <c r="G684" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -21680,7 +21683,7 @@
         <v>6.90985488891602</v>
       </c>
       <c r="G685" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -21706,7 +21709,7 @@
         <v>6.95914077758789</v>
       </c>
       <c r="G686" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -21732,7 +21735,7 @@
         <v>6.8999981880188</v>
       </c>
       <c r="G687" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -21758,7 +21761,7 @@
         <v>6.85071182250977</v>
       </c>
       <c r="G688" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -21784,7 +21787,7 @@
         <v>6.91971206665039</v>
       </c>
       <c r="G689" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -21810,7 +21813,7 @@
         <v>6.8999981880188</v>
       </c>
       <c r="G690" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -21836,7 +21839,7 @@
         <v>6.92956876754761</v>
       </c>
       <c r="G691" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -21862,7 +21865,7 @@
         <v>6.8999981880188</v>
       </c>
       <c r="G692" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -21888,7 +21891,7 @@
         <v>7.04785490036011</v>
       </c>
       <c r="G693" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -21914,7 +21917,7 @@
         <v>6.8999981880188</v>
       </c>
       <c r="G694" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -21940,7 +21943,7 @@
         <v>6.98871183395386</v>
       </c>
       <c r="G695" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -21966,7 +21969,7 @@
         <v>7.27456903457642</v>
       </c>
       <c r="G696" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -21992,7 +21995,7 @@
         <v>7.29428291320801</v>
       </c>
       <c r="G697" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -22018,7 +22021,7 @@
         <v>7.52099800109863</v>
       </c>
       <c r="G698" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -22044,7 +22047,7 @@
         <v>7.54071187973022</v>
       </c>
       <c r="G699" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -22070,7 +22073,7 @@
         <v>7.45199823379517</v>
       </c>
       <c r="G700" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -22096,7 +22099,7 @@
         <v>7.41256904602051</v>
       </c>
       <c r="G701" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -22122,7 +22125,7 @@
         <v>7.49142599105835</v>
       </c>
       <c r="G702" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -22148,7 +22151,7 @@
         <v>7.39285516738892</v>
       </c>
       <c r="G703" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -22174,7 +22177,7 @@
         <v>7.38299798965454</v>
       </c>
       <c r="G704" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -22200,7 +22203,7 @@
         <v>7.29428291320801</v>
       </c>
       <c r="G705" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -22226,7 +22229,7 @@
         <v>7.35342597961426</v>
       </c>
       <c r="G706" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -22252,7 +22255,7 @@
         <v>7.20556879043579</v>
       </c>
       <c r="G707" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -22278,7 +22281,7 @@
         <v>7.31399822235107</v>
       </c>
       <c r="G708" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -22304,7 +22307,7 @@
         <v>7.26471185684204</v>
       </c>
       <c r="G709" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -22330,7 +22333,7 @@
         <v>6.94928407669067</v>
       </c>
       <c r="G710" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -22356,7 +22359,7 @@
         <v>7.04785490036011</v>
       </c>
       <c r="G711" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -22382,7 +22385,7 @@
         <v>7.0675687789917</v>
       </c>
       <c r="G712" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -22408,7 +22411,7 @@
         <v>6.99856901168823</v>
       </c>
       <c r="G713" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -22434,7 +22437,7 @@
         <v>6.95914077758789</v>
       </c>
       <c r="G714" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -22460,7 +22463,7 @@
         <v>6.91971206665039</v>
       </c>
       <c r="G715" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -22486,7 +22489,7 @@
         <v>6.88028383255005</v>
       </c>
       <c r="G716" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -22512,7 +22515,7 @@
         <v>6.95914077758789</v>
       </c>
       <c r="G717" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -22538,7 +22541,7 @@
         <v>6.87042617797852</v>
       </c>
       <c r="G718" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -22564,7 +22567,7 @@
         <v>6.93942594528198</v>
       </c>
       <c r="G719" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -22590,7 +22593,7 @@
         <v>6.88028383255005</v>
       </c>
       <c r="G720" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -22616,7 +22619,7 @@
         <v>6.81128406524658</v>
       </c>
       <c r="G721" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -22642,7 +22645,7 @@
         <v>6.87042617797852</v>
       </c>
       <c r="G722" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -22668,7 +22671,7 @@
         <v>6.86056900024414</v>
       </c>
       <c r="G723" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -22694,7 +22697,7 @@
         <v>6.94928407669067</v>
       </c>
       <c r="G724" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -22720,7 +22723,7 @@
         <v>6.8999981880188</v>
       </c>
       <c r="G725" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -22746,7 +22749,7 @@
         <v>6.96899795532227</v>
       </c>
       <c r="G726" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -22772,7 +22775,7 @@
         <v>6.88028383255005</v>
       </c>
       <c r="G727" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -22798,7 +22801,7 @@
         <v>6.86056900024414</v>
       </c>
       <c r="G728" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -22824,7 +22827,7 @@
         <v>6.96899795532227</v>
       </c>
       <c r="G729" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -22850,7 +22853,7 @@
         <v>6.8999981880188</v>
       </c>
       <c r="G730" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -22876,7 +22879,7 @@
         <v>6.95914077758789</v>
       </c>
       <c r="G731" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -22902,7 +22905,7 @@
         <v>6.8999981880188</v>
       </c>
       <c r="G732" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -22928,7 +22931,7 @@
         <v>6.87042617797852</v>
       </c>
       <c r="G733" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -22954,7 +22957,7 @@
         <v>6.85071182250977</v>
       </c>
       <c r="G734" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -22980,7 +22983,7 @@
         <v>6.87042617797852</v>
       </c>
       <c r="G735" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -23006,7 +23009,7 @@
         <v>6.8211407661438</v>
       </c>
       <c r="G736" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -23032,7 +23035,7 @@
         <v>6.88028383255005</v>
       </c>
       <c r="G737" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -23058,7 +23061,7 @@
         <v>6.8211407661438</v>
       </c>
       <c r="G738" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -23084,7 +23087,7 @@
         <v>6.80142593383789</v>
       </c>
       <c r="G739" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -23110,7 +23113,7 @@
         <v>6.8999981880188</v>
       </c>
       <c r="G740" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -23136,7 +23139,7 @@
         <v>6.8999981880188</v>
       </c>
       <c r="G741" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -23162,7 +23165,7 @@
         <v>6.93942594528198</v>
       </c>
       <c r="G742" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -23188,7 +23191,7 @@
         <v>6.97885513305664</v>
       </c>
       <c r="G743" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -23214,7 +23217,7 @@
         <v>6.94928407669067</v>
       </c>
       <c r="G744" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -23240,7 +23243,7 @@
         <v>6.98871183395386</v>
       </c>
       <c r="G745" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -23266,7 +23269,7 @@
         <v>7.15628290176392</v>
       </c>
       <c r="G746" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -23292,7 +23295,7 @@
         <v>7.09714078903198</v>
       </c>
       <c r="G747" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -23318,7 +23321,7 @@
         <v>7.11685514450073</v>
       </c>
       <c r="G748" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -23344,7 +23347,7 @@
         <v>7.12671184539795</v>
       </c>
       <c r="G749" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -23370,7 +23373,7 @@
         <v>6.97885513305664</v>
       </c>
       <c r="G750" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -23396,7 +23399,7 @@
         <v>6.99856901168823</v>
       </c>
       <c r="G751" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -23422,7 +23425,7 @@
         <v>6.99856901168823</v>
       </c>
       <c r="G752" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -23448,7 +23451,7 @@
         <v>7.01828384399414</v>
       </c>
       <c r="G753" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -23474,7 +23477,7 @@
         <v>6.99856901168823</v>
       </c>
       <c r="G754" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -23500,7 +23503,7 @@
         <v>6.99856901168823</v>
       </c>
       <c r="G755" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -23526,7 +23529,7 @@
         <v>7.01828384399414</v>
       </c>
       <c r="G756" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -23552,7 +23555,7 @@
         <v>6.99856901168823</v>
       </c>
       <c r="G757" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -23578,7 +23581,7 @@
         <v>6.97885513305664</v>
       </c>
       <c r="G758" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -23604,7 +23607,7 @@
         <v>7.03799819946289</v>
       </c>
       <c r="G759" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -23630,7 +23633,7 @@
         <v>7.02814102172852</v>
       </c>
       <c r="G760" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -23656,7 +23659,7 @@
         <v>7.0675687789917</v>
       </c>
       <c r="G761" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -23682,7 +23685,7 @@
         <v>7.11685514450073</v>
       </c>
       <c r="G762" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -23708,7 +23711,7 @@
         <v>7.34356880187988</v>
       </c>
       <c r="G763" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -23734,7 +23737,7 @@
         <v>7.17599821090698</v>
       </c>
       <c r="G764" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -23760,7 +23763,7 @@
         <v>7.17599821090698</v>
       </c>
       <c r="G765" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -23786,7 +23789,7 @@
         <v>7.17599821090698</v>
       </c>
       <c r="G766" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -23812,7 +23815,7 @@
         <v>7.08728313446045</v>
       </c>
       <c r="G767" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -23838,7 +23841,7 @@
         <v>7.04785490036011</v>
       </c>
       <c r="G768" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -23864,7 +23867,7 @@
         <v>7.1464262008667</v>
       </c>
       <c r="G769" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -23890,7 +23893,7 @@
         <v>7.15628290176392</v>
       </c>
       <c r="G770" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -23916,7 +23919,7 @@
         <v>7.19571208953857</v>
       </c>
       <c r="G771" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -23942,7 +23945,7 @@
         <v>7.1464262008667</v>
       </c>
       <c r="G772" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -23968,7 +23971,7 @@
         <v>7.1464262008667</v>
       </c>
       <c r="G773" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -23994,7 +23997,7 @@
         <v>7.24499797821045</v>
       </c>
       <c r="G774" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -24020,7 +24023,7 @@
         <v>7.39285516738892</v>
       </c>
       <c r="G775" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -24046,7 +24049,7 @@
         <v>7.62942600250244</v>
       </c>
       <c r="G776" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -24072,7 +24075,7 @@
         <v>7.49142599105835</v>
       </c>
       <c r="G777" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -24098,7 +24101,7 @@
         <v>7.41256904602051</v>
       </c>
       <c r="G778" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -24124,7 +24127,7 @@
         <v>7.42242622375488</v>
       </c>
       <c r="G779" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -24150,7 +24153,7 @@
         <v>7.39285516738892</v>
       </c>
       <c r="G780" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -24176,7 +24179,7 @@
         <v>7.34356880187988</v>
       </c>
       <c r="G781" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -24202,7 +24205,7 @@
         <v>7.39285516738892</v>
       </c>
       <c r="G782" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -24228,7 +24231,7 @@
         <v>7.40271186828613</v>
       </c>
       <c r="G783" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -24254,7 +24257,7 @@
         <v>7.39285516738892</v>
       </c>
       <c r="G784" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -24280,7 +24283,7 @@
         <v>7.44214105606079</v>
       </c>
       <c r="G785" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -24306,7 +24309,7 @@
         <v>7.40271186828613</v>
       </c>
       <c r="G786" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -24332,7 +24335,7 @@
         <v>7.39285516738892</v>
       </c>
       <c r="G787" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -24358,7 +24361,7 @@
         <v>7.39285516738892</v>
       </c>
       <c r="G788" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -24384,7 +24387,7 @@
         <v>7.39285516738892</v>
       </c>
       <c r="G789" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -24410,7 +24413,7 @@
         <v>7.38299798965454</v>
       </c>
       <c r="G790" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -24436,7 +24439,7 @@
         <v>7.3041410446167</v>
       </c>
       <c r="G791" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -24462,7 +24465,7 @@
         <v>7.49142599105835</v>
       </c>
       <c r="G792" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -24488,7 +24491,7 @@
         <v>7.38299798965454</v>
       </c>
       <c r="G793" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -24514,7 +24517,7 @@
         <v>7.38299798965454</v>
       </c>
       <c r="G794" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -24540,7 +24543,7 @@
         <v>7.29428291320801</v>
       </c>
       <c r="G795" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -24566,7 +24569,7 @@
         <v>7.24499797821045</v>
       </c>
       <c r="G796" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -24592,7 +24595,7 @@
         <v>7.31399822235107</v>
       </c>
       <c r="G797" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -24618,7 +24621,7 @@
         <v>7.39285516738892</v>
       </c>
       <c r="G798" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -24644,7 +24647,7 @@
         <v>7.33371210098267</v>
       </c>
       <c r="G799" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -24670,7 +24673,7 @@
         <v>7.29428291320801</v>
       </c>
       <c r="G800" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -24696,7 +24699,7 @@
         <v>7.25485515594482</v>
       </c>
       <c r="G801" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -24722,7 +24725,7 @@
         <v>7.19571208953857</v>
       </c>
       <c r="G802" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -24748,7 +24751,7 @@
         <v>7.19571208953857</v>
       </c>
       <c r="G803" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -24774,7 +24777,7 @@
         <v>7.21542596817017</v>
       </c>
       <c r="G804" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -24800,7 +24803,7 @@
         <v>7.39285516738892</v>
       </c>
       <c r="G805" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -24826,7 +24829,7 @@
         <v>7.29428291320801</v>
       </c>
       <c r="G806" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -24852,7 +24855,7 @@
         <v>7.34356880187988</v>
       </c>
       <c r="G807" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -24878,7 +24881,7 @@
         <v>7.19571208953857</v>
       </c>
       <c r="G808" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -24904,7 +24907,7 @@
         <v>7.19571208953857</v>
       </c>
       <c r="G809" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -24930,7 +24933,7 @@
         <v>7.23514080047607</v>
       </c>
       <c r="G810" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -24956,7 +24959,7 @@
         <v>7.23514080047607</v>
       </c>
       <c r="G811" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -24982,7 +24985,7 @@
         <v>7.09714078903198</v>
       </c>
       <c r="G812" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -25008,7 +25011,7 @@
         <v>7.1464262008667</v>
       </c>
       <c r="G813" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -25034,7 +25037,7 @@
         <v>7.15628290176392</v>
       </c>
       <c r="G814" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -25060,7 +25063,7 @@
         <v>7.1464262008667</v>
       </c>
       <c r="G815" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -25086,7 +25089,7 @@
         <v>7.10699796676636</v>
       </c>
       <c r="G816" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -25112,7 +25115,7 @@
         <v>7.1464262008667</v>
       </c>
       <c r="G817" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -25138,7 +25141,7 @@
         <v>7.20556879043579</v>
       </c>
       <c r="G818" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -25164,7 +25167,7 @@
         <v>7.38299798965454</v>
       </c>
       <c r="G819" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -25190,7 +25193,7 @@
         <v>7.54071187973022</v>
       </c>
       <c r="G820" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -25216,7 +25219,7 @@
         <v>7.62942600250244</v>
       </c>
       <c r="G821" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -25242,7 +25245,7 @@
         <v>7.63928318023682</v>
       </c>
       <c r="G822" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -25268,7 +25271,7 @@
         <v>7.41256904602051</v>
       </c>
       <c r="G823" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -25294,7 +25297,7 @@
         <v>7.40271186828613</v>
       </c>
       <c r="G824" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -25320,7 +25323,7 @@
         <v>7.40271186828613</v>
       </c>
       <c r="G825" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -25346,7 +25349,7 @@
         <v>7.34356880187988</v>
       </c>
       <c r="G826" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -25372,7 +25375,7 @@
         <v>7.33371210098267</v>
       </c>
       <c r="G827" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -25398,7 +25401,7 @@
         <v>7.29428291320801</v>
       </c>
       <c r="G828" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -25424,7 +25427,7 @@
         <v>7.39285516738892</v>
       </c>
       <c r="G829" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -25450,7 +25453,7 @@
         <v>7.35342597961426</v>
       </c>
       <c r="G830" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -25476,7 +25479,7 @@
         <v>7.33371210098267</v>
       </c>
       <c r="G831" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -25502,7 +25505,7 @@
         <v>7.37314081192017</v>
       </c>
       <c r="G832" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -25528,7 +25531,7 @@
         <v>7.45199823379517</v>
       </c>
       <c r="G833" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -25554,7 +25557,7 @@
         <v>7.37314081192017</v>
       </c>
       <c r="G834" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -25580,7 +25583,7 @@
         <v>7.39285516738892</v>
       </c>
       <c r="G835" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -25606,7 +25609,7 @@
         <v>7.39285516738892</v>
       </c>
       <c r="G836" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -25632,7 +25635,7 @@
         <v>7.35342597961426</v>
       </c>
       <c r="G837" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -25658,7 +25661,7 @@
         <v>7.37314081192017</v>
       </c>
       <c r="G838" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -25684,7 +25687,7 @@
         <v>7.4322829246521</v>
       </c>
       <c r="G839" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -25710,7 +25713,7 @@
         <v>7.37314081192017</v>
       </c>
       <c r="G840" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -25736,7 +25739,7 @@
         <v>7.4322829246521</v>
       </c>
       <c r="G841" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -25762,7 +25765,7 @@
         <v>7.33371210098267</v>
       </c>
       <c r="G842" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -25788,7 +25791,7 @@
         <v>7.4322829246521</v>
       </c>
       <c r="G843" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -25814,7 +25817,7 @@
         <v>7.49142599105835</v>
       </c>
       <c r="G844" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -25840,7 +25843,7 @@
         <v>7.45199823379517</v>
       </c>
       <c r="G845" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -25866,7 +25869,7 @@
         <v>7.41256904602051</v>
       </c>
       <c r="G846" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -25892,7 +25895,7 @@
         <v>7.25485515594482</v>
       </c>
       <c r="G847" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -25918,7 +25921,7 @@
         <v>7.25485515594482</v>
       </c>
       <c r="G848" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -25944,7 +25947,7 @@
         <v>7.39285516738892</v>
       </c>
       <c r="G849" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -25970,7 +25973,7 @@
         <v>7.39285516738892</v>
       </c>
       <c r="G850" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -25996,7 +25999,7 @@
         <v>7.25485515594482</v>
       </c>
       <c r="G851" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -26022,7 +26025,7 @@
         <v>7.35342597961426</v>
       </c>
       <c r="G852" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -26048,7 +26051,7 @@
         <v>7.35342597961426</v>
       </c>
       <c r="G853" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -26074,7 +26077,7 @@
         <v>7.29428291320801</v>
       </c>
       <c r="G854" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -26100,7 +26103,7 @@
         <v>7.29428291320801</v>
       </c>
       <c r="G855" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -26126,7 +26129,7 @@
         <v>7.15628290176392</v>
       </c>
       <c r="G856" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -26152,7 +26155,7 @@
         <v>7.17599821090698</v>
       </c>
       <c r="G857" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -26178,7 +26181,7 @@
         <v>7.13656902313232</v>
       </c>
       <c r="G858" t="s">
-        <v>364</v>
+        <v>303</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -26230,7 +26233,7 @@
         <v>7.17599821090698</v>
       </c>
       <c r="G860" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -26256,7 +26259,7 @@
         <v>7.15628290176392</v>
       </c>
       <c r="G861" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -26412,7 +26415,7 @@
         <v>7.13656902313232</v>
       </c>
       <c r="G867" t="s">
-        <v>364</v>
+        <v>303</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -26438,7 +26441,7 @@
         <v>7.15628290176392</v>
       </c>
       <c r="G868" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -26516,7 +26519,7 @@
         <v>7.15628290176392</v>
       </c>
       <c r="G871" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -26542,7 +26545,7 @@
         <v>7.13656902313232</v>
       </c>
       <c r="G872" t="s">
-        <v>364</v>
+        <v>303</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -26594,7 +26597,7 @@
         <v>7.39285516738892</v>
       </c>
       <c r="G874" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -26646,7 +26649,7 @@
         <v>7.25485515594482</v>
       </c>
       <c r="G876" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -27738,7 +27741,7 @@
         <v>7.39285516738892</v>
       </c>
       <c r="G918" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -27764,7 +27767,7 @@
         <v>7.29428291320801</v>
       </c>
       <c r="G919" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -27790,7 +27793,7 @@
         <v>7.29428291320801</v>
       </c>
       <c r="G920" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -27816,7 +27819,7 @@
         <v>7.39285516738892</v>
       </c>
       <c r="G921" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -27868,7 +27871,7 @@
         <v>7.29428291320801</v>
       </c>
       <c r="G923" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -27972,7 +27975,7 @@
         <v>7.17599821090698</v>
       </c>
       <c r="G927" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -27998,7 +28001,7 @@
         <v>7.17599821090698</v>
       </c>
       <c r="G928" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -28024,7 +28027,7 @@
         <v>7.17599821090698</v>
       </c>
       <c r="G929" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -28206,7 +28209,7 @@
         <v>7.15628290176392</v>
       </c>
       <c r="G936" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -28232,7 +28235,7 @@
         <v>7.13656902313232</v>
       </c>
       <c r="G937" t="s">
-        <v>364</v>
+        <v>303</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -28258,7 +28261,7 @@
         <v>7.17599821090698</v>
       </c>
       <c r="G938" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -69606,7 +69609,7 @@
     </row>
     <row r="2529">
       <c r="A2529" s="1" t="n">
-        <v>46000.6910648148</v>
+        <v>46000.3333333333</v>
       </c>
       <c r="B2529" t="n">
         <v>10130</v>
@@ -69627,6 +69630,32 @@
         <v>1175</v>
       </c>
       <c r="H2529" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2530">
+      <c r="A2530" s="1" t="n">
+        <v>46001.6912268518</v>
+      </c>
+      <c r="B2530" t="n">
+        <v>15158</v>
+      </c>
+      <c r="C2530" t="n">
+        <v>17.4799995422363</v>
+      </c>
+      <c r="D2530" t="n">
+        <v>17.2000007629395</v>
+      </c>
+      <c r="E2530" t="n">
+        <v>17.2600002288818</v>
+      </c>
+      <c r="F2530" t="n">
+        <v>17.4599990844727</v>
+      </c>
+      <c r="G2530" t="s">
+        <v>1176</v>
+      </c>
+      <c r="H2530" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ORS.MI.xlsx
+++ b/data/ORS.MI.xlsx
@@ -38,28 +38,28 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08406352996826</t>
+    <t xml:space="preserve">8.08406257629395</t>
   </si>
   <si>
     <t xml:space="preserve">ORS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98275804519653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06380271911621</t>
+    <t xml:space="preserve">7.98275899887085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06380176544189</t>
   </si>
   <si>
     <t xml:space="preserve">7.94223833084106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82472562789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93818426132202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9017162322998</t>
+    <t xml:space="preserve">7.82472467422485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93818616867065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90171527862549</t>
   </si>
   <si>
     <t xml:space="preserve">8.03948974609375</t>
@@ -74,16 +74,16 @@
     <t xml:space="preserve">7.82067251205444</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93413305282593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02328205108643</t>
+    <t xml:space="preserve">7.93413400650024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02328014373779</t>
   </si>
   <si>
     <t xml:space="preserve">8.08811473846436</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1448450088501</t>
+    <t xml:space="preserve">8.14484691619873</t>
   </si>
   <si>
     <t xml:space="preserve">7.69910669326782</t>
@@ -95,22 +95,22 @@
     <t xml:space="preserve">7.97465467453003</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01112365722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01517677307129</t>
+    <t xml:space="preserve">8.01112461090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01517581939697</t>
   </si>
   <si>
     <t xml:space="preserve">7.79230785369873</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82877779006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34745407104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84093332290649</t>
+    <t xml:space="preserve">7.8287787437439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34745311737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84093427658081</t>
   </si>
   <si>
     <t xml:space="preserve">7.90982055664062</t>
@@ -125,19 +125,19 @@
     <t xml:space="preserve">7.84498453140259</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97870683670044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88550758361816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95034170150757</t>
+    <t xml:space="preserve">7.97870492935181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88550853729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95034265518188</t>
   </si>
   <si>
     <t xml:space="preserve">8.00301933288574</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01922798156738</t>
+    <t xml:space="preserve">8.0192289352417</t>
   </si>
   <si>
     <t xml:space="preserve">7.91792488098145</t>
@@ -146,58 +146,58 @@
     <t xml:space="preserve">8.1002721786499</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10432243347168</t>
+    <t xml:space="preserve">8.104323387146</t>
   </si>
   <si>
     <t xml:space="preserve">8.18536758422852</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20157527923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11242961883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07595729827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03138446807861</t>
+    <t xml:space="preserve">8.20157623291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11242866516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07595920562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03138637542725</t>
   </si>
   <si>
     <t xml:space="preserve">8.09621906280518</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17726421356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05569839477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12053298950195</t>
+    <t xml:space="preserve">8.17726230621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05569744110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12053394317627</t>
   </si>
   <si>
     <t xml:space="preserve">8.2583065032959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4203929901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67162799835205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55816650390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42849636077881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52428913116455</t>
+    <t xml:space="preserve">8.42039203643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67162609100342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55816555023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42849826812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52429103851318</t>
   </si>
   <si>
     <t xml:space="preserve">8.45921993255615</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50802135467529</t>
+    <t xml:space="preserve">8.50802326202393</t>
   </si>
   <si>
     <t xml:space="preserve">8.60562896728516</t>
@@ -209,28 +209,28 @@
     <t xml:space="preserve">8.61376190185547</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67069911956787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87404632568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7927074432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90658187866211</t>
+    <t xml:space="preserve">8.67069816589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87404537200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79270839691162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90658092498779</t>
   </si>
   <si>
     <t xml:space="preserve">8.86591243743896</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94724941253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93911552429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78457260131836</t>
+    <t xml:space="preserve">8.94725036621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93911743164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78457355499268</t>
   </si>
   <si>
     <t xml:space="preserve">8.74390316009521</t>
@@ -239,13 +239,13 @@
     <t xml:space="preserve">8.91471385955811</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92285060882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10992813110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.077392578125</t>
+    <t xml:space="preserve">8.92284965515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10992908477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07739353179932</t>
   </si>
   <si>
     <t xml:space="preserve">9.11806201934814</t>
@@ -254,25 +254,25 @@
     <t xml:space="preserve">9.1343297958374</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15059757232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15873146057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7357702255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67883205413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85777759552002</t>
+    <t xml:space="preserve">9.15059852600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15873050689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73577117919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67883396148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85777854919434</t>
   </si>
   <si>
     <t xml:space="preserve">8.72763633728027</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7032356262207</t>
+    <t xml:space="preserve">8.70323467254639</t>
   </si>
   <si>
     <t xml:space="preserve">8.66256523132324</t>
@@ -281,7 +281,7 @@
     <t xml:space="preserve">8.69510078430176</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6218957901001</t>
+    <t xml:space="preserve">8.62189674377441</t>
   </si>
   <si>
     <t xml:space="preserve">8.80084037780762</t>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">8.77643871307373</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68696689605713</t>
+    <t xml:space="preserve">8.68696784973145</t>
   </si>
   <si>
     <t xml:space="preserve">8.54869079589844</t>
@@ -302,19 +302,19 @@
     <t xml:space="preserve">8.58122825622559</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46735286712646</t>
+    <t xml:space="preserve">8.46735191345215</t>
   </si>
   <si>
     <t xml:space="preserve">8.51615619659424</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49988746643066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45108413696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63003158569336</t>
+    <t xml:space="preserve">8.49988651275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45108604431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63003063201904</t>
   </si>
   <si>
     <t xml:space="preserve">8.80897617340088</t>
@@ -323,34 +323,34 @@
     <t xml:space="preserve">8.89031410217285</t>
   </si>
   <si>
-    <t xml:space="preserve">8.930983543396</t>
+    <t xml:space="preserve">8.93098258972168</t>
   </si>
   <si>
     <t xml:space="preserve">8.9635181427002</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05299091339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30514144897461</t>
+    <t xml:space="preserve">9.05299186706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30514240264893</t>
   </si>
   <si>
     <t xml:space="preserve">9.10179424285889</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19126510620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35394382476807</t>
+    <t xml:space="preserve">9.1912670135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35394477844238</t>
   </si>
   <si>
     <t xml:space="preserve">9.47595310211182</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54915523529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58982467651367</t>
+    <t xml:space="preserve">9.54915714263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58982563018799</t>
   </si>
   <si>
     <t xml:space="preserve">9.66303062438965</t>
@@ -359,10 +359,10 @@
     <t xml:space="preserve">9.71996688842773</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85824394226074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0046520233154</t>
+    <t xml:space="preserve">9.85824298858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0046529769897</t>
   </si>
   <si>
     <t xml:space="preserve">10.240535736084</t>
@@ -371,31 +371,31 @@
     <t xml:space="preserve">10.2486686706543</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3381423950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5984258651733</t>
+    <t xml:space="preserve">10.3381414413452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.598424911499</t>
   </si>
   <si>
     <t xml:space="preserve">10.4276142120361</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4032115936279</t>
+    <t xml:space="preserve">10.4032125473022</t>
   </si>
   <si>
     <t xml:space="preserve">10.5252208709717</t>
   </si>
   <si>
-    <t xml:space="preserve">10.460150718689</t>
+    <t xml:space="preserve">10.4601497650146</t>
   </si>
   <si>
     <t xml:space="preserve">10.5658893585205</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5821561813354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7773704528809</t>
+    <t xml:space="preserve">10.5821571350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7773694992065</t>
   </si>
   <si>
     <t xml:space="preserve">10.9807176589966</t>
@@ -404,28 +404,28 @@
     <t xml:space="preserve">10.8749752044678</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6553640365601</t>
+    <t xml:space="preserve">10.6553630828857</t>
   </si>
   <si>
     <t xml:space="preserve">10.6797637939453</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5740242004395</t>
+    <t xml:space="preserve">10.5740251541138</t>
   </si>
   <si>
     <t xml:space="preserve">10.5170860290527</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5414876937866</t>
+    <t xml:space="preserve">10.5414886474609</t>
   </si>
   <si>
     <t xml:space="preserve">10.5577573776245</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5089521408081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8180379867554</t>
+    <t xml:space="preserve">10.5089530944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8180389404297</t>
   </si>
   <si>
     <t xml:space="preserve">10.6878976821899</t>
@@ -446,7 +446,7 @@
     <t xml:space="preserve">10.671630859375</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7367010116577</t>
+    <t xml:space="preserve">10.736701965332</t>
   </si>
   <si>
     <t xml:space="preserve">11.0051183700562</t>
@@ -458,31 +458,31 @@
     <t xml:space="preserve">11.184063911438</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4036779403687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3955430984497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3386068344116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.322338104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3304748535156</t>
+    <t xml:space="preserve">11.4036769866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.395544052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3386058807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3223400115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3304738998413</t>
   </si>
   <si>
     <t xml:space="preserve">11.3630084991455</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0783243179321</t>
+    <t xml:space="preserve">11.0783224105835</t>
   </si>
   <si>
     <t xml:space="preserve">10.606559753418</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8424406051636</t>
+    <t xml:space="preserve">10.8424415588379</t>
   </si>
   <si>
     <t xml:space="preserve">10.8505744934082</t>
@@ -491,34 +491,34 @@
     <t xml:space="preserve">10.6390943527222</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4113454818726</t>
+    <t xml:space="preserve">10.4113464355469</t>
   </si>
   <si>
     <t xml:space="preserve">10.2080011367798</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2730703353882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.232400894165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3218746185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3706760406494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3300075531006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.305606842041</t>
+    <t xml:space="preserve">10.2730712890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2324018478394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.321873664856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3706769943237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3300085067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3056058883667</t>
   </si>
   <si>
     <t xml:space="preserve">10.2568035125732</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1835985183716</t>
+    <t xml:space="preserve">10.1835975646973</t>
   </si>
   <si>
     <t xml:space="preserve">10.4845514297485</t>
@@ -527,7 +527,7 @@
     <t xml:space="preserve">10.3625431060791</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4438810348511</t>
+    <t xml:space="preserve">10.4438819885254</t>
   </si>
   <si>
     <t xml:space="preserve">10.8587093353271</t>
@@ -539,58 +539,58 @@
     <t xml:space="preserve">11.0376539230347</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0620555877686</t>
+    <t xml:space="preserve">11.0620565414429</t>
   </si>
   <si>
     <t xml:space="preserve">11.1027250289917</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1433935165405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.175929069519</t>
+    <t xml:space="preserve">11.1433944702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1759281158447</t>
   </si>
   <si>
     <t xml:space="preserve">11.1352615356445</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0701894760132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1189937591553</t>
+    <t xml:space="preserve">11.0701913833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.118992805481</t>
   </si>
   <si>
     <t xml:space="preserve">11.1515283584595</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2247314453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0457878112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5008192062378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1347951889038</t>
+    <t xml:space="preserve">11.2247323989868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.045786857605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5008201599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1347961425781</t>
   </si>
   <si>
     <t xml:space="preserve">8.36161231994629</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01999092102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10946369171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39414596557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21520328521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33720970153809</t>
+    <t xml:space="preserve">8.01998996734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10946273803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3941478729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21520233154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3372106552124</t>
   </si>
   <si>
     <t xml:space="preserve">8.31280899047852</t>
@@ -605,46 +605,46 @@
     <t xml:space="preserve">8.23960304260254</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49175453186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58936023712158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76017284393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29654121398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25587177276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17453384399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1908016204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23147010803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28027248382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14199733734131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1582670211792</t>
+    <t xml:space="preserve">8.49175357818604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58935928344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76017189025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29654312133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25587368011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17453479766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19080066680908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23147106170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28027439117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14199829101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15826511383057</t>
   </si>
   <si>
     <t xml:space="preserve">8.16639995574951</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12166404724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05252742767334</t>
+    <t xml:space="preserve">8.12166309356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05252552032471</t>
   </si>
   <si>
     <t xml:space="preserve">7.89798259735107</t>
@@ -656,7 +656,7 @@
     <t xml:space="preserve">7.93051719665527</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90611553192139</t>
+    <t xml:space="preserve">7.90611362457275</t>
   </si>
   <si>
     <t xml:space="preserve">7.93865251541138</t>
@@ -668,10 +668,10 @@
     <t xml:space="preserve">7.808509349823</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62956428527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57262802124023</t>
+    <t xml:space="preserve">7.62956571578979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57262754440308</t>
   </si>
   <si>
     <t xml:space="preserve">7.48315525054932</t>
@@ -683,94 +683,94 @@
     <t xml:space="preserve">7.60516405105591</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54009294509888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52382326126099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47908782958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61329793930054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54822587966919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56449317932129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50755548477173</t>
+    <t xml:space="preserve">7.54009199142456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5238242149353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47908735275269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61329698562622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54822492599487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56449270248413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50755596160889</t>
   </si>
   <si>
     <t xml:space="preserve">7.46688652038574</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49128913879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49942207336426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31234407424927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27980947494507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37741422653198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38554906845093</t>
+    <t xml:space="preserve">7.4912896156311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49942302703857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31234455108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27980709075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37741470336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38554859161377</t>
   </si>
   <si>
     <t xml:space="preserve">7.36928081512451</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32047748565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34487867355347</t>
+    <t xml:space="preserve">7.32047700881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34487962722778</t>
   </si>
   <si>
     <t xml:space="preserve">7.28794240951538</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04392576217651</t>
+    <t xml:space="preserve">7.04392623901367</t>
   </si>
   <si>
     <t xml:space="preserve">7.15780019760132</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39368295669556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42621755599976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40181589126587</t>
+    <t xml:space="preserve">7.39368200302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42621850967407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4018177986145</t>
   </si>
   <si>
     <t xml:space="preserve">7.30421113967896</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36114835739136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20660352706909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35301351547241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33674573898315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27167510986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23100471496582</t>
+    <t xml:space="preserve">7.3611478805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20660400390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35301303863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33674478530884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27167463302612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23100519180298</t>
   </si>
   <si>
     <t xml:space="preserve">7.32861185073853</t>
@@ -782,16 +782,16 @@
     <t xml:space="preserve">7.23913955688477</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22287225723267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24727344512939</t>
+    <t xml:space="preserve">7.22287130355835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24727249145508</t>
   </si>
   <si>
     <t xml:space="preserve">7.44248580932617</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25540781021118</t>
+    <t xml:space="preserve">7.25540685653687</t>
   </si>
   <si>
     <t xml:space="preserve">7.18220138549805</t>
@@ -800,16 +800,16 @@
     <t xml:space="preserve">7.29607534408569</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16593503952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14153289794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0520601272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07646179199219</t>
+    <t xml:space="preserve">7.16593360900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14153337478638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05205965042114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07646226882935</t>
   </si>
   <si>
     <t xml:space="preserve">7.03579235076904</t>
@@ -821,55 +821,55 @@
     <t xml:space="preserve">6.87311506271362</t>
   </si>
   <si>
+    <t xml:space="preserve">6.677903175354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85124778747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93379211425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26397275924683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14841032028198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09888315200806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18142938613892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16491794586182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14015626907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21444702148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1731743812561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97506523132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84299325942993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60361194610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62012100219727</t>
+  </si>
+  <si>
     <t xml:space="preserve">6.67790269851685</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85124731063843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93379163742065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26397371292114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14841032028198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09888362884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18142938613892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16491842269897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14015626907349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21444606781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17317342758179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97506475448608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84299325942993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60361242294312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62012100219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67790222167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.809974193573</t>
+    <t xml:space="preserve">6.80997467041016</t>
   </si>
   <si>
     <t xml:space="preserve">6.54583072662354</t>
@@ -878,10 +878,10 @@
     <t xml:space="preserve">6.31470441818237</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32295894622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34772253036499</t>
+    <t xml:space="preserve">6.32295846939087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34772300720215</t>
   </si>
   <si>
     <t xml:space="preserve">6.38074016571045</t>
@@ -890,13 +890,13 @@
     <t xml:space="preserve">6.39724922180176</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47153997421265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2816858291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22390460968018</t>
+    <t xml:space="preserve">6.4715404510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28168630599976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22390413284302</t>
   </si>
   <si>
     <t xml:space="preserve">6.09183216094971</t>
@@ -905,244 +905,244 @@
     <t xml:space="preserve">5.90197801589966</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9597601890564</t>
+    <t xml:space="preserve">5.95976066589355</t>
   </si>
   <si>
     <t xml:space="preserve">5.99277782440186</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20739603042603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14135932922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19088649749756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14961338043213</t>
+    <t xml:space="preserve">6.20739507675171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14135885238647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19088697433472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14961385726929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07532262802124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25692272186279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00928735733032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98452377319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12485074996948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13310480117798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27343130111694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44677639007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55408525466919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51281261444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36423110961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24041366577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21565008163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23215913772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24866819381714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11659669876099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1083402633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05055952072144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89372396469116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77816104888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69561433792114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79466962814331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80292320251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82768774032593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78641510009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73688793182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85245132446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29819536209106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18263244628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15786790847778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03404998779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08357763290405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81943368911743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91848754882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86070585250854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76165199279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7533974647522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81117820739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70386981964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74514245986938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83594179153442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71212387084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84419679641724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94325065612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96801471710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8772144317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88546943664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93499612808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02579641342163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06706857681274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38899421691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19914054870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04230451583862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05881452560425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9515061378479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17437744140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17601919174194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29349803924561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25993251800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20958375930786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09210586547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10888910293579</t>
   </si>
   <si>
     <t xml:space="preserve">6.0753231048584</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25692319869995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00928735733032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98452377319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12485074996948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13310384750366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27343130111694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44677591323853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55408477783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51281261444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36423110961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24041414260864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21564960479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23215961456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24866771697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11659574508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10834121704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05055999755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89372396469116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77816104888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6956148147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79466962814331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80292320251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82768726348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78641510009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73688793182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85245132446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29819536209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1826319694519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15786790847778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03405046463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08357763290405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81943368911743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91848707199097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86070489883423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76165199279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75339698791504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81117820739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70386981964111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74514293670654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83594274520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71212434768677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84419631958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94325065612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96801471710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87721538543701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88546943664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93499660491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02579641342163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06706857681274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38899421691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19914102554321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04230451583862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05881404876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95150566101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17437744140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17601919174194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29349756240845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25993204116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20958423614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09210586547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10888910293579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07532358169556</t>
-  </si>
-  <si>
     <t xml:space="preserve">6.14245367050171</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05854082107544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02497482299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97462797164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95784378051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15923643112183</t>
+    <t xml:space="preserve">6.0585412979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02497529983521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97462749481201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95784473419189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15923690795898</t>
   </si>
   <si>
     <t xml:space="preserve">6.12567138671875</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19280242919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42775964736938</t>
+    <t xml:space="preserve">6.19280195236206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42775917053223</t>
   </si>
   <si>
     <t xml:space="preserve">6.71306467056274</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64593458175659</t>
+    <t xml:space="preserve">6.64593410491943</t>
   </si>
   <si>
     <t xml:space="preserve">6.69628190994263</t>
@@ -1151,16 +1151,16 @@
     <t xml:space="preserve">6.78019571304321</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72984647750854</t>
+    <t xml:space="preserve">6.7298469543457</t>
   </si>
   <si>
     <t xml:space="preserve">6.62915086746216</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56201982498169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54523849487305</t>
+    <t xml:space="preserve">6.56202077865601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54523754119873</t>
   </si>
   <si>
     <t xml:space="preserve">6.67949867248535</t>
@@ -1169,13 +1169,13 @@
     <t xml:space="preserve">6.66271686553955</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57880353927612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37741088867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34384679794312</t>
+    <t xml:space="preserve">6.57880401611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37741136550903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34384632110596</t>
   </si>
   <si>
     <t xml:space="preserve">6.22636795043945</t>
@@ -1187,10 +1187,10 @@
     <t xml:space="preserve">5.67253923416138</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55506038665771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68932199478149</t>
+    <t xml:space="preserve">5.55505990982056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68932247161865</t>
   </si>
   <si>
     <t xml:space="preserve">5.62219142913818</t>
@@ -1202,7 +1202,7 @@
     <t xml:space="preserve">5.43758249282837</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45436525344849</t>
+    <t xml:space="preserve">5.45436573028564</t>
   </si>
   <si>
     <t xml:space="preserve">5.60540819168091</t>
@@ -1211,7 +1211,7 @@
     <t xml:space="preserve">5.5214958190918</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50471258163452</t>
+    <t xml:space="preserve">5.50471353530884</t>
   </si>
   <si>
     <t xml:space="preserve">5.4879298210144</t>
@@ -1220,40 +1220,40 @@
     <t xml:space="preserve">5.35366868972778</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37045097351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42079973220825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28653764724731</t>
+    <t xml:space="preserve">5.3704514503479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42079925537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28653812408447</t>
   </si>
   <si>
     <t xml:space="preserve">5.30332088470459</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26975536346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38723373413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32010364532471</t>
+    <t xml:space="preserve">5.26975584030151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38723421096802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32010316848755</t>
   </si>
   <si>
     <t xml:space="preserve">5.65575695037842</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75645351409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70610475540161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72288656234741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73967027664185</t>
+    <t xml:space="preserve">5.7564525604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70610523223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72288703918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.739670753479</t>
   </si>
   <si>
     <t xml:space="preserve">5.63897466659546</t>
@@ -1262,13 +1262,13 @@
     <t xml:space="preserve">5.57184410095215</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18584251403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2026252746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21940803527832</t>
+    <t xml:space="preserve">5.18584156036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20262479782104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21940755844116</t>
   </si>
   <si>
     <t xml:space="preserve">5.16905975341797</t>
@@ -1277,10 +1277,10 @@
     <t xml:space="preserve">5.13549375534058</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10192966461182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95088481903076</t>
+    <t xml:space="preserve">5.10192918777466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9508843421936</t>
   </si>
   <si>
     <t xml:space="preserve">5.03479862213135</t>
@@ -1289,10 +1289,10 @@
     <t xml:space="preserve">5.15227651596069</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11871147155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06836366653442</t>
+    <t xml:space="preserve">5.11871099472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06836318969727</t>
   </si>
   <si>
     <t xml:space="preserve">5.08514642715454</t>
@@ -1301,13 +1301,13 @@
     <t xml:space="preserve">5.23618984222412</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25297260284424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33688688278198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79001760482788</t>
+    <t xml:space="preserve">5.25297212600708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33688640594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79001712799072</t>
   </si>
   <si>
     <t xml:space="preserve">5.77323532104492</t>
@@ -1316,22 +1316,22 @@
     <t xml:space="preserve">5.58862590789795</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81662321090698</t>
+    <t xml:space="preserve">4.81662368774414</t>
   </si>
   <si>
     <t xml:space="preserve">4.79984140396118</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59844827651978</t>
+    <t xml:space="preserve">4.59844875335693</t>
   </si>
   <si>
     <t xml:space="preserve">4.36349201202393</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31314420700073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19566488265991</t>
+    <t xml:space="preserve">4.31314373016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19566535949707</t>
   </si>
   <si>
     <t xml:space="preserve">4.11175107955933</t>
@@ -1340,7 +1340,7 @@
     <t xml:space="preserve">4.02783823013306</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17049026489258</t>
+    <t xml:space="preserve">4.17049074172974</t>
   </si>
   <si>
     <t xml:space="preserve">4.06979560852051</t>
@@ -1349,16 +1349,16 @@
     <t xml:space="preserve">4.12014293670654</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34670877456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17888212203979</t>
+    <t xml:space="preserve">4.34670925140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17888259887695</t>
   </si>
   <si>
     <t xml:space="preserve">4.04462099075317</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15370798110962</t>
+    <t xml:space="preserve">4.15370845794678</t>
   </si>
   <si>
     <t xml:space="preserve">4.26279592514038</t>
@@ -1367,43 +1367,43 @@
     <t xml:space="preserve">4.16209983825684</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14531755447388</t>
+    <t xml:space="preserve">4.14531707763672</t>
   </si>
   <si>
     <t xml:space="preserve">3.9942729473114</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09496927261353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98588132858276</t>
+    <t xml:space="preserve">4.09496879577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98588180541992</t>
   </si>
   <si>
     <t xml:space="preserve">4.27957820892334</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22922992706299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21244812011719</t>
+    <t xml:space="preserve">4.22923040390015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21244859695435</t>
   </si>
   <si>
     <t xml:space="preserve">4.03622961044312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12877893447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16283130645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07770156860352</t>
+    <t xml:space="preserve">4.12877941131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1628303527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07770109176636</t>
   </si>
   <si>
     <t xml:space="preserve">4.00108528137207</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20539522171021</t>
+    <t xml:space="preserve">4.20539569854736</t>
   </si>
   <si>
     <t xml:space="preserve">4.37565469741821</t>
@@ -1415,16 +1415,16 @@
     <t xml:space="preserve">4.22242164611816</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25647306442261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24796009063721</t>
+    <t xml:space="preserve">4.25647354125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24796056747437</t>
   </si>
   <si>
     <t xml:space="preserve">4.32457637786865</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30755138397217</t>
+    <t xml:space="preserve">4.30755043029785</t>
   </si>
   <si>
     <t xml:space="preserve">4.23944759368896</t>
@@ -1436,19 +1436,19 @@
     <t xml:space="preserve">4.51186180114746</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53341579437256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9420371055603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89095878601074</t>
+    <t xml:space="preserve">5.53341484069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94203615188599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8909592628479</t>
   </si>
   <si>
     <t xml:space="preserve">5.73772573471069</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5504412651062</t>
+    <t xml:space="preserve">5.55044078826904</t>
   </si>
   <si>
     <t xml:space="preserve">5.58449268341064</t>
@@ -1457,28 +1457,28 @@
     <t xml:space="preserve">5.567467212677</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41423368453979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2610011100769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.482337474823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4482855796814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60151863098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66962289810181</t>
+    <t xml:space="preserve">5.41423416137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26100063323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48233795166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44828605651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6015191078186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66962242126465</t>
   </si>
   <si>
     <t xml:space="preserve">5.5163893699646</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70367431640625</t>
+    <t xml:space="preserve">5.70367479324341</t>
   </si>
   <si>
     <t xml:space="preserve">5.32910490036011</t>
@@ -1490,7 +1490,7 @@
     <t xml:space="preserve">5.43126010894775</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31207895278931</t>
+    <t xml:space="preserve">5.31207847595215</t>
   </si>
   <si>
     <t xml:space="preserve">5.22694969177246</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve">4.95453548431396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93750905990601</t>
+    <t xml:space="preserve">4.93750953674316</t>
   </si>
   <si>
     <t xml:space="preserve">5.05669069290161</t>
@@ -1520,7 +1520,7 @@
     <t xml:space="preserve">5.02263879776001</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92048406600952</t>
+    <t xml:space="preserve">4.92048358917236</t>
   </si>
   <si>
     <t xml:space="preserve">4.9034571647644</t>
@@ -1532,28 +1532,28 @@
     <t xml:space="preserve">4.8694052696228</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34613084793091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24397468566895</t>
+    <t xml:space="preserve">5.34613037109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2439751625061</t>
   </si>
   <si>
     <t xml:space="preserve">5.36315679550171</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38018274307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20992279052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15884590148926</t>
+    <t xml:space="preserve">5.38018226623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2099232673645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1588454246521</t>
   </si>
   <si>
     <t xml:space="preserve">5.1077675819397</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98858690261841</t>
+    <t xml:space="preserve">4.98858642578125</t>
   </si>
   <si>
     <t xml:space="preserve">5.09074211120605</t>
@@ -1571,7 +1571,7 @@
     <t xml:space="preserve">5.07371664047241</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68212127685547</t>
+    <t xml:space="preserve">4.68212032318115</t>
   </si>
   <si>
     <t xml:space="preserve">4.54591369628906</t>
@@ -1592,13 +1592,13 @@
     <t xml:space="preserve">4.76725006103516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8183274269104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8013014793396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39720869064331</t>
+    <t xml:space="preserve">4.81832790374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80130195617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39720821380615</t>
   </si>
   <si>
     <t xml:space="preserve">5.6185450553894</t>
@@ -1610,7 +1610,7 @@
     <t xml:space="preserve">5.4993634223938</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63557100296021</t>
+    <t xml:space="preserve">5.63557052612305</t>
   </si>
   <si>
     <t xml:space="preserve">5.68664836883545</t>
@@ -1625,7 +1625,7 @@
     <t xml:space="preserve">5.87393379211426</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31660652160645</t>
+    <t xml:space="preserve">6.3166069984436</t>
   </si>
   <si>
     <t xml:space="preserve">6.33363199234009</t>
@@ -1634,22 +1634,22 @@
     <t xml:space="preserve">6.29958057403564</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35065841674805</t>
+    <t xml:space="preserve">6.35065793991089</t>
   </si>
   <si>
     <t xml:space="preserve">6.43578767776489</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5549693107605</t>
+    <t xml:space="preserve">6.55496883392334</t>
   </si>
   <si>
     <t xml:space="preserve">6.69117641448975</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79333209991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15087509155273</t>
+    <t xml:space="preserve">6.79333114624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15087556838989</t>
   </si>
   <si>
     <t xml:space="preserve">7.08277082443237</t>
@@ -1658,7 +1658,7 @@
     <t xml:space="preserve">6.87846088409424</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77630567550659</t>
+    <t xml:space="preserve">6.77630519866943</t>
   </si>
   <si>
     <t xml:space="preserve">6.84440946578979</t>
@@ -1667,13 +1667,13 @@
     <t xml:space="preserve">6.70820236206055</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75927972793579</t>
+    <t xml:space="preserve">6.75927925109863</t>
   </si>
   <si>
     <t xml:space="preserve">6.5379433631897</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72522783279419</t>
+    <t xml:space="preserve">6.72522830963135</t>
   </si>
   <si>
     <t xml:space="preserve">6.65712451934814</t>
@@ -1685,7 +1685,7 @@
     <t xml:space="preserve">6.8954873085022</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96359014511108</t>
+    <t xml:space="preserve">6.96359062194824</t>
   </si>
   <si>
     <t xml:space="preserve">7.17302179336548</t>
@@ -1697,19 +1697,19 @@
     <t xml:space="preserve">7.1206636428833</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57443237304688</t>
+    <t xml:space="preserve">7.57443141937256</t>
   </si>
   <si>
     <t xml:space="preserve">7.97584247589111</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02819919586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06310558319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99329519271851</t>
+    <t xml:space="preserve">8.0281982421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0631046295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99329423904419</t>
   </si>
   <si>
     <t xml:space="preserve">8.0107479095459</t>
@@ -1727,16 +1727,16 @@
     <t xml:space="preserve">8.16782093048096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18527412414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34234809875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11546325683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25508403778076</t>
+    <t xml:space="preserve">8.18527317047119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34234714508057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11546230316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25508308410645</t>
   </si>
   <si>
     <t xml:space="preserve">8.08055782318115</t>
@@ -1745,16 +1745,16 @@
     <t xml:space="preserve">8.20272541046143</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95838928222656</t>
+    <t xml:space="preserve">7.95838832855225</t>
   </si>
   <si>
     <t xml:space="preserve">8.37725162506104</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32489395141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81356716156006</t>
+    <t xml:space="preserve">8.3248929977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81356620788574</t>
   </si>
   <si>
     <t xml:space="preserve">8.58668327331543</t>
@@ -1763,13 +1763,13 @@
     <t xml:space="preserve">8.53432559967041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69139957427979</t>
+    <t xml:space="preserve">8.69139862060547</t>
   </si>
   <si>
     <t xml:space="preserve">8.60413551330566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72630405426025</t>
+    <t xml:space="preserve">8.72630310058594</t>
   </si>
   <si>
     <t xml:space="preserve">8.42960929870605</t>
@@ -1781,13 +1781,13 @@
     <t xml:space="preserve">8.30744171142578</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04565238952637</t>
+    <t xml:space="preserve">8.04565143585205</t>
   </si>
   <si>
     <t xml:space="preserve">7.85367345809937</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41215801239014</t>
+    <t xml:space="preserve">8.41215705871582</t>
   </si>
   <si>
     <t xml:space="preserve">8.22017860412598</t>
@@ -1799,22 +1799,22 @@
     <t xml:space="preserve">8.3597993850708</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09801006317139</t>
+    <t xml:space="preserve">8.09800910949707</t>
   </si>
   <si>
     <t xml:space="preserve">8.23763084411621</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48196792602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62158966064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55177879333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65649318695068</t>
+    <t xml:space="preserve">8.48196697235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62158870697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55177783966064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65649223327637</t>
   </si>
   <si>
     <t xml:space="preserve">8.51687335968018</t>
@@ -1832,7 +1832,7 @@
     <t xml:space="preserve">9.99161720275879</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59893321990967</t>
+    <t xml:space="preserve">9.59893417358398</t>
   </si>
   <si>
     <t xml:space="preserve">9.77345943450928</t>
@@ -1844,16 +1844,16 @@
     <t xml:space="preserve">9.29351329803467</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46804046630859</t>
+    <t xml:space="preserve">9.46803951263428</t>
   </si>
   <si>
     <t xml:space="preserve">9.55530261993408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64256572723389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90435600280762</t>
+    <t xml:space="preserve">9.6425666809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9043550491333</t>
   </si>
   <si>
     <t xml:space="preserve">9.33714485168457</t>
@@ -1862,7 +1862,7 @@
     <t xml:space="preserve">9.94798469543457</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86072254180908</t>
+    <t xml:space="preserve">9.8607234954834</t>
   </si>
   <si>
     <t xml:space="preserve">10.5151968002319</t>
@@ -1871,13 +1871,13 @@
     <t xml:space="preserve">10.4279327392578</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5588264465332</t>
+    <t xml:space="preserve">10.5588274002075</t>
   </si>
   <si>
     <t xml:space="preserve">10.6024589538574</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8206157684326</t>
+    <t xml:space="preserve">10.8206167221069</t>
   </si>
   <si>
     <t xml:space="preserve">10.7333526611328</t>
@@ -1886,16 +1886,16 @@
     <t xml:space="preserve">10.776985168457</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2970380783081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3843002319336</t>
+    <t xml:space="preserve">10.2970390319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3843011856079</t>
   </si>
   <si>
     <t xml:space="preserve">10.3406705856323</t>
   </si>
   <si>
-    <t xml:space="preserve">10.209774017334</t>
+    <t xml:space="preserve">10.2097749710083</t>
   </si>
   <si>
     <t xml:space="preserve">10.2534074783325</t>
@@ -1904,7 +1904,7 @@
     <t xml:space="preserve">10.0788812637329</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51167011260986</t>
+    <t xml:space="preserve">9.51167106628418</t>
   </si>
   <si>
     <t xml:space="preserve">9.72982883453369</t>
@@ -1913,16 +1913,16 @@
     <t xml:space="preserve">9.68619728088379</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98809337615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42440700531006</t>
+    <t xml:space="preserve">8.98809242248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42440795898438</t>
   </si>
   <si>
     <t xml:space="preserve">11.6496162414551</t>
   </si>
   <si>
-    <t xml:space="preserve">11.562352180481</t>
+    <t xml:space="preserve">11.5623531341553</t>
   </si>
   <si>
     <t xml:space="preserve">11.7805099487305</t>
@@ -1940,7 +1940,7 @@
     <t xml:space="preserve">12.3040885925293</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2604570388794</t>
+    <t xml:space="preserve">12.2604579925537</t>
   </si>
   <si>
     <t xml:space="preserve">12.2168254852295</t>
@@ -1970,7 +1970,7 @@
     <t xml:space="preserve">11.3441944122314</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9951419830322</t>
+    <t xml:space="preserve">10.9951429367065</t>
   </si>
   <si>
     <t xml:space="preserve">10.4715642929077</t>
@@ -1985,10 +1985,10 @@
     <t xml:space="preserve">11.0387744903564</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9899406433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7456045150757</t>
+    <t xml:space="preserve">11.9899415969849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.74560546875</t>
   </si>
   <si>
     <t xml:space="preserve">11.5361738204956</t>
@@ -1997,10 +1997,10 @@
     <t xml:space="preserve">11.5187206268311</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6234350204468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4489097595215</t>
+    <t xml:space="preserve">11.6234359741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4489107131958</t>
   </si>
   <si>
     <t xml:space="preserve">11.6408891677856</t>
@@ -2009,7 +2009,7 @@
     <t xml:space="preserve">11.7281513214111</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9201307296753</t>
+    <t xml:space="preserve">11.9201316833496</t>
   </si>
   <si>
     <t xml:space="preserve">11.1173105239868</t>
@@ -2021,7 +2021,7 @@
     <t xml:space="preserve">10.8031644821167</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7508058547974</t>
+    <t xml:space="preserve">10.7508068084717</t>
   </si>
   <si>
     <t xml:space="preserve">10.3319435119629</t>
@@ -69664,13 +69664,13 @@
     </row>
     <row r="2531">
       <c r="A2531" s="1" t="n">
-        <v>46002.6910185185</v>
+        <v>46002.3333333333</v>
       </c>
       <c r="B2531" t="n">
         <v>9848</v>
       </c>
       <c r="C2531" t="n">
-        <v>17.4799995422363</v>
+        <v>17.5200004577637</v>
       </c>
       <c r="D2531" t="n">
         <v>17.2600002288818</v>
@@ -69685,6 +69685,32 @@
         <v>1162</v>
       </c>
       <c r="H2531" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2532">
+      <c r="A2532" s="1" t="n">
+        <v>46003.6911805556</v>
+      </c>
+      <c r="B2532" t="n">
+        <v>16036</v>
+      </c>
+      <c r="C2532" t="n">
+        <v>17.5400009155273</v>
+      </c>
+      <c r="D2532" t="n">
+        <v>17.3199996948242</v>
+      </c>
+      <c r="E2532" t="n">
+        <v>17.5200004577637</v>
+      </c>
+      <c r="F2532" t="n">
+        <v>17.3600006103516</v>
+      </c>
+      <c r="G2532" t="s">
+        <v>1176</v>
+      </c>
+      <c r="H2532" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ORS.MI.xlsx
+++ b/data/ORS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1178" uniqueCount="1178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1179" uniqueCount="1179">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,58 +38,58 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08406257629395</t>
+    <t xml:space="preserve">8.08406448364258</t>
   </si>
   <si>
     <t xml:space="preserve">ORS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98275899887085</t>
+    <t xml:space="preserve">7.98275995254517</t>
   </si>
   <si>
     <t xml:space="preserve">8.06380176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94223833084106</t>
+    <t xml:space="preserve">7.94223690032959</t>
   </si>
   <si>
     <t xml:space="preserve">7.82472467422485</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93818616867065</t>
+    <t xml:space="preserve">7.93818521499634</t>
   </si>
   <si>
     <t xml:space="preserve">7.90171527862549</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03948974609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92602920532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86119413375854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82067251205444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93413400650024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02328014373779</t>
+    <t xml:space="preserve">8.03948783874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92602968215942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86119365692139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82067203521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9341344833374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02328109741211</t>
   </si>
   <si>
     <t xml:space="preserve">8.08811473846436</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14484691619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69910669326782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8044638633728</t>
+    <t xml:space="preserve">8.14484596252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69910764694214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80446481704712</t>
   </si>
   <si>
     <t xml:space="preserve">7.97465467453003</t>
@@ -98,61 +98,61 @@
     <t xml:space="preserve">8.01112461090088</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01517581939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79230785369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8287787437439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34745311737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84093427658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90982055664062</t>
+    <t xml:space="preserve">8.01517677307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79230880737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82877683639526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34745407104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84093284606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90982007980347</t>
   </si>
   <si>
     <t xml:space="preserve">7.85714197158813</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7801513671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84498453140259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97870492935181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88550853729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95034265518188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00301933288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0192289352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91792488098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1002721786499</t>
+    <t xml:space="preserve">7.78015184402466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84498500823975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9787073135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88550662994385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95034217834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00302028656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01922798156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91792440414429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10027122497559</t>
   </si>
   <si>
     <t xml:space="preserve">8.104323387146</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18536758422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20157623291016</t>
+    <t xml:space="preserve">8.1853666305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20157527923584</t>
   </si>
   <si>
     <t xml:space="preserve">8.11242866516113</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">8.07595920562744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03138637542725</t>
+    <t xml:space="preserve">8.03138542175293</t>
   </si>
   <si>
     <t xml:space="preserve">8.09621906280518</t>
@@ -170,55 +170,55 @@
     <t xml:space="preserve">8.17726230621338</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05569744110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12053394317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2583065032959</t>
+    <t xml:space="preserve">8.05569839477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12053203582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25830745697021</t>
   </si>
   <si>
     <t xml:space="preserve">8.42039203643799</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67162609100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55816555023193</t>
+    <t xml:space="preserve">8.6716251373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55816650390625</t>
   </si>
   <si>
     <t xml:space="preserve">8.42849826812744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52429103851318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45921993255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50802326202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60562896728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5324239730835</t>
+    <t xml:space="preserve">8.52429008483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45921897888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50802230834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60562801361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53242301940918</t>
   </si>
   <si>
     <t xml:space="preserve">8.61376190185547</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67069816589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87404537200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79270839691162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90658092498779</t>
+    <t xml:space="preserve">8.67069911956787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87404632568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7927074432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90657997131348</t>
   </si>
   <si>
     <t xml:space="preserve">8.86591243743896</t>
@@ -227,67 +227,67 @@
     <t xml:space="preserve">8.94725036621094</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93911743164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78457355499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74390316009521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91471385955811</t>
+    <t xml:space="preserve">8.93911647796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78457260131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74390411376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91471576690674</t>
   </si>
   <si>
     <t xml:space="preserve">8.92284965515137</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10992908477783</t>
+    <t xml:space="preserve">9.10992813110352</t>
   </si>
   <si>
     <t xml:space="preserve">9.07739353179932</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11806201934814</t>
+    <t xml:space="preserve">9.11806106567383</t>
   </si>
   <si>
     <t xml:space="preserve">9.1343297958374</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15059852600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15873050689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73577117919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67883396148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85777854919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72763633728027</t>
+    <t xml:space="preserve">9.15059757232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15873146057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7357702255249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67883205413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85777759552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72763538360596</t>
   </si>
   <si>
     <t xml:space="preserve">8.70323467254639</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66256523132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69510078430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62189674377441</t>
+    <t xml:space="preserve">8.66256618499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69510173797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6218957901001</t>
   </si>
   <si>
     <t xml:space="preserve">8.80084037780762</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77643871307373</t>
+    <t xml:space="preserve">8.77643966674805</t>
   </si>
   <si>
     <t xml:space="preserve">8.68696784973145</t>
@@ -299,19 +299,19 @@
     <t xml:space="preserve">8.54055690765381</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58122825622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46735191345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51615619659424</t>
+    <t xml:space="preserve">8.58122730255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46735286712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51615715026855</t>
   </si>
   <si>
     <t xml:space="preserve">8.49988651275635</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45108604431152</t>
+    <t xml:space="preserve">8.45108413696289</t>
   </si>
   <si>
     <t xml:space="preserve">8.63003063201904</t>
@@ -320,40 +320,40 @@
     <t xml:space="preserve">8.80897617340088</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89031410217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93098258972168</t>
+    <t xml:space="preserve">8.89031505584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.930983543396</t>
   </si>
   <si>
     <t xml:space="preserve">8.9635181427002</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05299186706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30514240264893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10179424285889</t>
+    <t xml:space="preserve">9.05299091339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30514049530029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1017951965332</t>
   </si>
   <si>
     <t xml:space="preserve">9.1912670135498</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35394477844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47595310211182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54915714263916</t>
+    <t xml:space="preserve">9.35394287109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47595119476318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54915618896484</t>
   </si>
   <si>
     <t xml:space="preserve">9.58982563018799</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66303062438965</t>
+    <t xml:space="preserve">9.66303157806396</t>
   </si>
   <si>
     <t xml:space="preserve">9.71996688842773</t>
@@ -362,31 +362,31 @@
     <t xml:space="preserve">9.85824298858643</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0046529769897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.240535736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2486686706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3381414413452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.598424911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4276142120361</t>
+    <t xml:space="preserve">10.0046510696411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2405347824097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2486696243286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3381423950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5984258651733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4276151657104</t>
   </si>
   <si>
     <t xml:space="preserve">10.4032125473022</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5252208709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4601497650146</t>
+    <t xml:space="preserve">10.5252199172974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4601488113403</t>
   </si>
   <si>
     <t xml:space="preserve">10.5658893585205</t>
@@ -395,34 +395,34 @@
     <t xml:space="preserve">10.5821571350098</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7773694992065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9807176589966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8749752044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6553630828857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6797637939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5740251541138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5170860290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5414886474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5577573776245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5089530944824</t>
+    <t xml:space="preserve">10.7773704528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9807167053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8749771118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6553621292114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.679762840271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5740242004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5170879364014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5414896011353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5577564239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5089511871338</t>
   </si>
   <si>
     <t xml:space="preserve">10.8180389404297</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">10.8993787765503</t>
   </si>
   <si>
-    <t xml:space="preserve">10.883111000061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.671630859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.736701965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0051183700562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0213861465454</t>
+    <t xml:space="preserve">10.8831100463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6716299057007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7367010116577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0051193237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0213871002197</t>
   </si>
   <si>
     <t xml:space="preserve">11.184063911438</t>
@@ -461,28 +461,28 @@
     <t xml:space="preserve">11.4036769866943</t>
   </si>
   <si>
-    <t xml:space="preserve">11.395544052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3386058807373</t>
+    <t xml:space="preserve">11.3955430984497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3386068344116</t>
   </si>
   <si>
     <t xml:space="preserve">11.3223400115967</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3304738998413</t>
+    <t xml:space="preserve">11.3304719924927</t>
   </si>
   <si>
     <t xml:space="preserve">11.3630084991455</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0783224105835</t>
+    <t xml:space="preserve">11.0783243179321</t>
   </si>
   <si>
     <t xml:space="preserve">10.606559753418</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8424415588379</t>
+    <t xml:space="preserve">10.8424425125122</t>
   </si>
   <si>
     <t xml:space="preserve">10.8505744934082</t>
@@ -491,16 +491,16 @@
     <t xml:space="preserve">10.6390943527222</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4113464355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2080011367798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2730712890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2324018478394</t>
+    <t xml:space="preserve">10.4113454818726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2080001831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2730693817139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.232400894165</t>
   </si>
   <si>
     <t xml:space="preserve">10.321873664856</t>
@@ -509,7 +509,7 @@
     <t xml:space="preserve">10.3706769943237</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3300085067749</t>
+    <t xml:space="preserve">10.3300075531006</t>
   </si>
   <si>
     <t xml:space="preserve">10.3056058883667</t>
@@ -530,121 +530,121 @@
     <t xml:space="preserve">10.4438819885254</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8587093353271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9237794876099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0376539230347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0620565414429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1027250289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1433944702148</t>
+    <t xml:space="preserve">10.8587074279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9237804412842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.037652015686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0620555877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.102725982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1433954238892</t>
   </si>
   <si>
     <t xml:space="preserve">11.1759281158447</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1352615356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0701913833618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.118992805481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1515283584595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2247323989868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.045786857605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5008201599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1347961425781</t>
+    <t xml:space="preserve">11.1352596282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0701894760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1189937591553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1515274047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2247333526611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0457878112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5008182525635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1347951889038</t>
   </si>
   <si>
     <t xml:space="preserve">8.36161231994629</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01998996734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10946273803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3941478729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21520233154297</t>
+    <t xml:space="preserve">8.01999092102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10946369171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39414882659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2152042388916</t>
   </si>
   <si>
     <t xml:space="preserve">8.3372106552124</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31280899047852</t>
+    <t xml:space="preserve">8.31280994415283</t>
   </si>
   <si>
     <t xml:space="preserve">8.18266773223877</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34534549713135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23960304260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49175357818604</t>
+    <t xml:space="preserve">8.34534454345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23960399627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49175453186035</t>
   </si>
   <si>
     <t xml:space="preserve">8.58935928344727</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76017189025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29654312133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25587368011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17453479766846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19080066680908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23147106170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28027439117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14199829101562</t>
+    <t xml:space="preserve">8.76017093658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29654121398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25587272644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17453384399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1908016204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23147010803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28027248382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14199733734131</t>
   </si>
   <si>
     <t xml:space="preserve">8.15826511383057</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16639995574951</t>
+    <t xml:space="preserve">8.16640090942383</t>
   </si>
   <si>
     <t xml:space="preserve">8.12166309356689</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05252552032471</t>
+    <t xml:space="preserve">8.05252456665039</t>
   </si>
   <si>
     <t xml:space="preserve">7.89798259735107</t>
@@ -653,121 +653,121 @@
     <t xml:space="preserve">7.85731363296509</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93051719665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90611362457275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93865251541138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84917831420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.808509349823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62956571578979</t>
+    <t xml:space="preserve">7.93051767349243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90611600875854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93865156173706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84917879104614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80850982666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62956476211548</t>
   </si>
   <si>
     <t xml:space="preserve">7.57262754440308</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48315525054932</t>
+    <t xml:space="preserve">7.48315572738647</t>
   </si>
   <si>
     <t xml:space="preserve">7.66616630554199</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60516405105591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54009199142456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5238242149353</t>
+    <t xml:space="preserve">7.60516309738159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54009246826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52382373809814</t>
   </si>
   <si>
     <t xml:space="preserve">7.47908735275269</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61329698562622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54822492599487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56449270248413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50755596160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46688652038574</t>
+    <t xml:space="preserve">7.61329746246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54822587966919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56449365615845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50755643844604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4668869972229</t>
   </si>
   <si>
     <t xml:space="preserve">7.4912896156311</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49942302703857</t>
+    <t xml:space="preserve">7.49942207336426</t>
   </si>
   <si>
     <t xml:space="preserve">7.31234455108643</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27980709075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37741470336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38554859161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36928081512451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32047700881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34487962722778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28794240951538</t>
+    <t xml:space="preserve">7.27980852127075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3774151802063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38554811477661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36928129196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32047748565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34487915039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28794097900391</t>
   </si>
   <si>
     <t xml:space="preserve">7.04392623901367</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15780019760132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39368200302124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42621850967407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4018177986145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30421113967896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3611478805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20660400390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35301303863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33674478530884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27167463302612</t>
+    <t xml:space="preserve">7.15780115127563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39368343353271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42621803283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40181589126587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3042106628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36114692687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20660448074341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35301351547241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33674573898315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27167415618896</t>
   </si>
   <si>
     <t xml:space="preserve">7.23100519180298</t>
@@ -776,37 +776,37 @@
     <t xml:space="preserve">7.32861185073853</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26354169845581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23913955688477</t>
+    <t xml:space="preserve">7.26354122161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23913908004761</t>
   </si>
   <si>
     <t xml:space="preserve">7.22287130355835</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24727249145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44248580932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25540685653687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18220138549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29607534408569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16593360900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14153337478638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05205965042114</t>
+    <t xml:space="preserve">7.24727439880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44248676300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25540781021118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18220186233521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29607582092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16593456268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1415319442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05205917358398</t>
   </si>
   <si>
     <t xml:space="preserve">7.07646226882935</t>
@@ -815,58 +815,58 @@
     <t xml:space="preserve">7.03579235076904</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01952457427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87311506271362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.677903175354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85124778747559</t>
+    <t xml:space="preserve">7.01952505111694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87311458587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67790269851685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85124731063843</t>
   </si>
   <si>
     <t xml:space="preserve">6.93379211425781</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26397275924683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14841032028198</t>
+    <t xml:space="preserve">7.26397371292114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14840936660767</t>
   </si>
   <si>
     <t xml:space="preserve">7.09888315200806</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18142938613892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16491794586182</t>
+    <t xml:space="preserve">7.18142890930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16491889953613</t>
   </si>
   <si>
     <t xml:space="preserve">7.14015626907349</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21444702148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1731743812561</t>
+    <t xml:space="preserve">7.21444606781006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17317342758179</t>
   </si>
   <si>
     <t xml:space="preserve">6.97506523132324</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84299325942993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60361194610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62012100219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67790269851685</t>
+    <t xml:space="preserve">6.84299278259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60361242294312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62012147903442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67790222167969</t>
   </si>
   <si>
     <t xml:space="preserve">6.80997467041016</t>
@@ -875,88 +875,88 @@
     <t xml:space="preserve">6.54583072662354</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31470441818237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32295846939087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34772300720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38074016571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39724922180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4715404510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28168630599976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22390413284302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09183216094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90197801589966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95976066589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99277782440186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20739507675171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14135885238647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19088697433472</t>
+    <t xml:space="preserve">6.31470394134521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32295799255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34772253036499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38074064254761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3972487449646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47153997421265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28168535232544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22390365600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09183263778687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90197849273682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95975971221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9927773475647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20739555358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14135932922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19088649749756</t>
   </si>
   <si>
     <t xml:space="preserve">6.14961385726929</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07532262802124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25692272186279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00928735733032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98452377319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12485074996948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13310480117798</t>
+    <t xml:space="preserve">6.0753231048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25692319869995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00928783416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9845232963562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12484979629517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13310527801514</t>
   </si>
   <si>
     <t xml:space="preserve">6.27343130111694</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44677639007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55408525466919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51281261444092</t>
+    <t xml:space="preserve">6.44677495956421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55408477783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51281213760376</t>
   </si>
   <si>
     <t xml:space="preserve">6.36423110961914</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24041366577148</t>
+    <t xml:space="preserve">6.24041318893433</t>
   </si>
   <si>
     <t xml:space="preserve">6.21565008163452</t>
@@ -968,13 +968,13 @@
     <t xml:space="preserve">6.24866819381714</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11659669876099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1083402633667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05055952072144</t>
+    <t xml:space="preserve">6.11659526824951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10834074020386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05055999755859</t>
   </si>
   <si>
     <t xml:space="preserve">5.89372396469116</t>
@@ -983,16 +983,16 @@
     <t xml:space="preserve">5.77816104888916</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69561433792114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79466962814331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80292320251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82768774032593</t>
+    <t xml:space="preserve">5.69561529159546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79466915130615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80292415618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82768821716309</t>
   </si>
   <si>
     <t xml:space="preserve">5.78641510009766</t>
@@ -1004,7 +1004,7 @@
     <t xml:space="preserve">5.85245132446289</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29819536209106</t>
+    <t xml:space="preserve">6.29819583892822</t>
   </si>
   <si>
     <t xml:space="preserve">6.18263244628906</t>
@@ -1013,70 +1013,70 @@
     <t xml:space="preserve">6.15786790847778</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03404998779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08357763290405</t>
+    <t xml:space="preserve">6.03405046463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08357715606689</t>
   </si>
   <si>
     <t xml:space="preserve">5.81943368911743</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91848754882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86070585250854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76165199279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7533974647522</t>
+    <t xml:space="preserve">5.91848611831665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86070537567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76165151596069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75339651107788</t>
   </si>
   <si>
     <t xml:space="preserve">5.81117820739746</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70386981964111</t>
+    <t xml:space="preserve">5.70387029647827</t>
   </si>
   <si>
     <t xml:space="preserve">5.74514245986938</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83594179153442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71212387084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84419679641724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94325065612793</t>
+    <t xml:space="preserve">5.83594226837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71212434768677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84419727325439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94325113296509</t>
   </si>
   <si>
     <t xml:space="preserve">5.96801471710205</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8772144317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88546943664551</t>
+    <t xml:space="preserve">5.87721490859985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88546991348267</t>
   </si>
   <si>
     <t xml:space="preserve">5.93499612808228</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02579641342163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06706857681274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38899421691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19914054870605</t>
+    <t xml:space="preserve">6.02579593658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0670690536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3889946937561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1991400718689</t>
   </si>
   <si>
     <t xml:space="preserve">6.04230451583862</t>
@@ -1085,10 +1085,10 @@
     <t xml:space="preserve">6.05881452560425</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9515061378479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17437744140625</t>
+    <t xml:space="preserve">5.95150566101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17437791824341</t>
   </si>
   <si>
     <t xml:space="preserve">6.17601919174194</t>
@@ -1097,34 +1097,34 @@
     <t xml:space="preserve">6.29349803924561</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25993251800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20958375930786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09210586547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10888910293579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0753231048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14245367050171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0585412979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02497529983521</t>
+    <t xml:space="preserve">6.25993204116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20958423614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09210538864136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10888957977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07532358169556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14245319366455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05854034423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02497577667236</t>
   </si>
   <si>
     <t xml:space="preserve">5.97462749481201</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95784473419189</t>
+    <t xml:space="preserve">5.95784425735474</t>
   </si>
   <si>
     <t xml:space="preserve">6.15923690795898</t>
@@ -1133,73 +1133,73 @@
     <t xml:space="preserve">6.12567138671875</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19280195236206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42775917053223</t>
+    <t xml:space="preserve">6.19280242919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42775869369507</t>
   </si>
   <si>
     <t xml:space="preserve">6.71306467056274</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64593410491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69628190994263</t>
+    <t xml:space="preserve">6.64593458175659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69628238677979</t>
   </si>
   <si>
     <t xml:space="preserve">6.78019571304321</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7298469543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62915086746216</t>
+    <t xml:space="preserve">6.72984743118286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.629150390625</t>
   </si>
   <si>
     <t xml:space="preserve">6.56202077865601</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54523754119873</t>
+    <t xml:space="preserve">6.54523801803589</t>
   </si>
   <si>
     <t xml:space="preserve">6.67949867248535</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66271686553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57880401611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37741136550903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34384632110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22636795043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36062860488892</t>
+    <t xml:space="preserve">6.66271638870239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57880306243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37741088867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3438458442688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22636699676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36062908172607</t>
   </si>
   <si>
     <t xml:space="preserve">5.67253923416138</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55505990982056</t>
+    <t xml:space="preserve">5.55506038665771</t>
   </si>
   <si>
     <t xml:space="preserve">5.68932247161865</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62219142913818</t>
+    <t xml:space="preserve">5.62219190597534</t>
   </si>
   <si>
     <t xml:space="preserve">5.53827810287476</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43758249282837</t>
+    <t xml:space="preserve">5.43758201599121</t>
   </si>
   <si>
     <t xml:space="preserve">5.45436573028564</t>
@@ -1208,7 +1208,7 @@
     <t xml:space="preserve">5.60540819168091</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5214958190918</t>
+    <t xml:space="preserve">5.52149534225464</t>
   </si>
   <si>
     <t xml:space="preserve">5.50471353530884</t>
@@ -1226,10 +1226,10 @@
     <t xml:space="preserve">5.42079925537109</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28653812408447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30332088470459</t>
+    <t xml:space="preserve">5.28653860092163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30332040786743</t>
   </si>
   <si>
     <t xml:space="preserve">5.26975584030151</t>
@@ -1238,25 +1238,25 @@
     <t xml:space="preserve">5.38723421096802</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32010316848755</t>
+    <t xml:space="preserve">5.32010364532471</t>
   </si>
   <si>
     <t xml:space="preserve">5.65575695037842</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7564525604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70610523223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72288703918457</t>
+    <t xml:space="preserve">5.75645303726196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70610475540161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72288656234741</t>
   </si>
   <si>
     <t xml:space="preserve">5.739670753479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63897466659546</t>
+    <t xml:space="preserve">5.6389741897583</t>
   </si>
   <si>
     <t xml:space="preserve">5.57184410095215</t>
@@ -1265,16 +1265,16 @@
     <t xml:space="preserve">5.18584156036377</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20262479782104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21940755844116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16905975341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13549375534058</t>
+    <t xml:space="preserve">5.2026252746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21940803527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16906023025513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13549327850342</t>
   </si>
   <si>
     <t xml:space="preserve">5.10192918777466</t>
@@ -1283,13 +1283,13 @@
     <t xml:space="preserve">4.9508843421936</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03479862213135</t>
+    <t xml:space="preserve">5.03479814529419</t>
   </si>
   <si>
     <t xml:space="preserve">5.15227651596069</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11871099472046</t>
+    <t xml:space="preserve">5.11871194839478</t>
   </si>
   <si>
     <t xml:space="preserve">5.06836318969727</t>
@@ -1301,25 +1301,25 @@
     <t xml:space="preserve">5.23618984222412</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25297212600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33688640594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79001712799072</t>
+    <t xml:space="preserve">5.25297260284424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33688688278198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79001808166504</t>
   </si>
   <si>
     <t xml:space="preserve">5.77323532104492</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58862590789795</t>
+    <t xml:space="preserve">5.58862638473511</t>
   </si>
   <si>
     <t xml:space="preserve">4.81662368774414</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79984140396118</t>
+    <t xml:space="preserve">4.79984092712402</t>
   </si>
   <si>
     <t xml:space="preserve">4.59844875335693</t>
@@ -1328,22 +1328,22 @@
     <t xml:space="preserve">4.36349201202393</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31314373016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19566535949707</t>
+    <t xml:space="preserve">4.31314420700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19566488265991</t>
   </si>
   <si>
     <t xml:space="preserve">4.11175107955933</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02783823013306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17049074172974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06979560852051</t>
+    <t xml:space="preserve">4.02783870697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17049026489258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06979513168335</t>
   </si>
   <si>
     <t xml:space="preserve">4.12014293670654</t>
@@ -1352,76 +1352,76 @@
     <t xml:space="preserve">4.34670925140381</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17888259887695</t>
+    <t xml:space="preserve">4.17888212203979</t>
   </si>
   <si>
     <t xml:space="preserve">4.04462099075317</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15370845794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26279592514038</t>
+    <t xml:space="preserve">4.15370798110962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26279640197754</t>
   </si>
   <si>
     <t xml:space="preserve">4.16209983825684</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14531707763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9942729473114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09496879577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98588180541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27957820892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22923040390015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21244859695435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03622961044312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12877941131592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1628303527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07770109176636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00108528137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20539569854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37565469741821</t>
+    <t xml:space="preserve">4.14531755447388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99427247047424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09496927261353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98588156700134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27957773208618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22922992706299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21244764328003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03623008728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12877893447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16283082962036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07770204544067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00108432769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20539522171021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37565422058105</t>
   </si>
   <si>
     <t xml:space="preserve">4.21390867233276</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22242164611816</t>
+    <t xml:space="preserve">4.22242116928101</t>
   </si>
   <si>
     <t xml:space="preserve">4.25647354125977</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24796056747437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32457637786865</t>
+    <t xml:space="preserve">4.24796009063721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32457685470581</t>
   </si>
   <si>
     <t xml:space="preserve">4.30755043029785</t>
@@ -1430,28 +1430,28 @@
     <t xml:space="preserve">4.23944759368896</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35862827301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51186180114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53341484069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94203615188599</t>
+    <t xml:space="preserve">4.35862874984741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5118613243103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5334153175354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94203662872314</t>
   </si>
   <si>
     <t xml:space="preserve">5.8909592628479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73772573471069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55044078826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58449268341064</t>
+    <t xml:space="preserve">5.73772621154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5504412651062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5844931602478</t>
   </si>
   <si>
     <t xml:space="preserve">5.567467212677</t>
@@ -1460,7 +1460,7 @@
     <t xml:space="preserve">5.41423416137695</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26100063323975</t>
+    <t xml:space="preserve">5.2610011100769</t>
   </si>
   <si>
     <t xml:space="preserve">5.48233795166016</t>
@@ -1475,10 +1475,10 @@
     <t xml:space="preserve">5.66962242126465</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5163893699646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70367479324341</t>
+    <t xml:space="preserve">5.51638984680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70367431640625</t>
   </si>
   <si>
     <t xml:space="preserve">5.32910490036011</t>
@@ -1493,34 +1493,34 @@
     <t xml:space="preserve">5.31207847595215</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22694969177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00561285018921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95453548431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93750953674316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05669069290161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03966474533081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97156047821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88643074035645</t>
+    <t xml:space="preserve">5.2269492149353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00561189651489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95453500747681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93750905990601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05669021606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03966426849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97156095504761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8864312171936</t>
   </si>
   <si>
     <t xml:space="preserve">5.02263879776001</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92048358917236</t>
+    <t xml:space="preserve">4.92048263549805</t>
   </si>
   <si>
     <t xml:space="preserve">4.9034571647644</t>
@@ -1532,46 +1532,46 @@
     <t xml:space="preserve">4.8694052696228</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34613037109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2439751625061</t>
+    <t xml:space="preserve">5.34613084793091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24397563934326</t>
   </si>
   <si>
     <t xml:space="preserve">5.36315679550171</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38018226623535</t>
+    <t xml:space="preserve">5.38018321990967</t>
   </si>
   <si>
     <t xml:space="preserve">5.2099232673645</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1588454246521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1077675819397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98858642578125</t>
+    <t xml:space="preserve">5.15884637832642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10776805877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98858690261841</t>
   </si>
   <si>
     <t xml:space="preserve">5.09074211120605</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1928973197937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1758713722229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14181995391846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07371664047241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68212032318115</t>
+    <t xml:space="preserve">5.19289779663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17587184906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1418194770813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07371616363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68212080001831</t>
   </si>
   <si>
     <t xml:space="preserve">4.54591369628906</t>
@@ -1580,31 +1580,31 @@
     <t xml:space="preserve">4.59699106216431</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57996511459351</t>
+    <t xml:space="preserve">4.57996559143066</t>
   </si>
   <si>
     <t xml:space="preserve">4.63104295730591</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78427600860596</t>
+    <t xml:space="preserve">4.7842755317688</t>
   </si>
   <si>
     <t xml:space="preserve">4.76725006103516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81832790374756</t>
+    <t xml:space="preserve">4.8183274269104</t>
   </si>
   <si>
     <t xml:space="preserve">4.80130195617676</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39720821380615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6185450553894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46531200408936</t>
+    <t xml:space="preserve">5.39720869064331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61854457855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46531248092651</t>
   </si>
   <si>
     <t xml:space="preserve">5.4993634223938</t>
@@ -1613,10 +1613,10 @@
     <t xml:space="preserve">5.63557052612305</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68664836883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65259647369385</t>
+    <t xml:space="preserve">5.68664884567261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65259695053101</t>
   </si>
   <si>
     <t xml:space="preserve">5.8569073677063</t>
@@ -1625,7 +1625,7 @@
     <t xml:space="preserve">5.87393379211426</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3166069984436</t>
+    <t xml:space="preserve">6.31660652160645</t>
   </si>
   <si>
     <t xml:space="preserve">6.33363199234009</t>
@@ -1634,7 +1634,7 @@
     <t xml:space="preserve">6.29958057403564</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35065793991089</t>
+    <t xml:space="preserve">6.35065889358521</t>
   </si>
   <si>
     <t xml:space="preserve">6.43578767776489</t>
@@ -1643,40 +1643,40 @@
     <t xml:space="preserve">6.55496883392334</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69117641448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79333114624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15087556838989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08277082443237</t>
+    <t xml:space="preserve">6.69117593765259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79333162307739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15087509155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08277130126953</t>
   </si>
   <si>
     <t xml:space="preserve">6.87846088409424</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77630519866943</t>
+    <t xml:space="preserve">6.77630567550659</t>
   </si>
   <si>
     <t xml:space="preserve">6.84440946578979</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70820236206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75927925109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5379433631897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72522830963135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65712451934814</t>
+    <t xml:space="preserve">6.70820283889771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75927972793579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53794288635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72522783279419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65712404251099</t>
   </si>
   <si>
     <t xml:space="preserve">6.91251277923584</t>
@@ -1685,10 +1685,10 @@
     <t xml:space="preserve">6.8954873085022</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96359062194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17302179336548</t>
+    <t xml:space="preserve">6.96359014511108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17302227020264</t>
   </si>
   <si>
     <t xml:space="preserve">7.05085325241089</t>
@@ -1697,13 +1697,13 @@
     <t xml:space="preserve">7.1206636428833</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57443141937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97584247589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0281982421875</t>
+    <t xml:space="preserve">7.57443189620972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9758415222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02819919586182</t>
   </si>
   <si>
     <t xml:space="preserve">8.0631046295166</t>
@@ -1712,13 +1712,13 @@
     <t xml:space="preserve">7.99329423904419</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0107479095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94093751907349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13291549682617</t>
+    <t xml:space="preserve">8.01074695587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94093799591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13291454315186</t>
   </si>
   <si>
     <t xml:space="preserve">8.15036773681641</t>
@@ -1727,10 +1727,10 @@
     <t xml:space="preserve">8.16782093048096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18527317047119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34234714508057</t>
+    <t xml:space="preserve">8.18527412414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34234619140625</t>
   </si>
   <si>
     <t xml:space="preserve">8.11546230316162</t>
@@ -1739,22 +1739,22 @@
     <t xml:space="preserve">8.25508308410645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08055782318115</t>
+    <t xml:space="preserve">8.08055877685547</t>
   </si>
   <si>
     <t xml:space="preserve">8.20272541046143</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95838832855225</t>
+    <t xml:space="preserve">7.95838928222656</t>
   </si>
   <si>
     <t xml:space="preserve">8.37725162506104</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3248929977417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81356620788574</t>
+    <t xml:space="preserve">8.32489395141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81356716156006</t>
   </si>
   <si>
     <t xml:space="preserve">8.58668327331543</t>
@@ -1769,22 +1769,22 @@
     <t xml:space="preserve">8.60413551330566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72630310058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42960929870605</t>
+    <t xml:space="preserve">8.72630405426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42961025238037</t>
   </si>
   <si>
     <t xml:space="preserve">8.28998851776123</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30744171142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04565143585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85367345809937</t>
+    <t xml:space="preserve">8.3074426651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04565334320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85367393493652</t>
   </si>
   <si>
     <t xml:space="preserve">8.41215705871582</t>
@@ -1793,7 +1793,7 @@
     <t xml:space="preserve">8.22017860412598</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44706344604492</t>
+    <t xml:space="preserve">8.44706249237061</t>
   </si>
   <si>
     <t xml:space="preserve">8.3597993850708</t>
@@ -1802,22 +1802,22 @@
     <t xml:space="preserve">8.09800910949707</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23763084411621</t>
+    <t xml:space="preserve">8.23762989044189</t>
   </si>
   <si>
     <t xml:space="preserve">8.48196697235107</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62158870697021</t>
+    <t xml:space="preserve">8.6215877532959</t>
   </si>
   <si>
     <t xml:space="preserve">8.55177783966064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65649223327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51687335968018</t>
+    <t xml:space="preserve">8.65649318695068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51687240600586</t>
   </si>
   <si>
     <t xml:space="preserve">8.46451473236084</t>
@@ -1829,28 +1829,28 @@
     <t xml:space="preserve">8.56923007965088</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99161720275879</t>
+    <t xml:space="preserve">9.99161815643311</t>
   </si>
   <si>
     <t xml:space="preserve">9.59893417358398</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77345943450928</t>
+    <t xml:space="preserve">9.77346038818359</t>
   </si>
   <si>
     <t xml:space="preserve">9.8170919418335</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29351329803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46803951263428</t>
+    <t xml:space="preserve">9.29351425170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46804046630859</t>
   </si>
   <si>
     <t xml:space="preserve">9.55530261993408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6425666809082</t>
+    <t xml:space="preserve">9.64256572723389</t>
   </si>
   <si>
     <t xml:space="preserve">9.9043550491333</t>
@@ -1859,7 +1859,7 @@
     <t xml:space="preserve">9.33714485168457</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94798469543457</t>
+    <t xml:space="preserve">9.94798564910889</t>
   </si>
   <si>
     <t xml:space="preserve">9.8607234954834</t>
@@ -1868,19 +1868,19 @@
     <t xml:space="preserve">10.5151968002319</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4279327392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5588274002075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6024589538574</t>
+    <t xml:space="preserve">10.4279317855835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5588283538818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6024580001831</t>
   </si>
   <si>
     <t xml:space="preserve">10.8206167221069</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7333526611328</t>
+    <t xml:space="preserve">10.7333545684814</t>
   </si>
   <si>
     <t xml:space="preserve">10.776985168457</t>
@@ -1892,7 +1892,7 @@
     <t xml:space="preserve">10.3843011856079</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3406705856323</t>
+    <t xml:space="preserve">10.340669631958</t>
   </si>
   <si>
     <t xml:space="preserve">10.2097749710083</t>
@@ -1901,25 +1901,25 @@
     <t xml:space="preserve">10.2534074783325</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0788812637329</t>
+    <t xml:space="preserve">10.0788803100586</t>
   </si>
   <si>
     <t xml:space="preserve">9.51167106628418</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72982883453369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68619728088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98809242248535</t>
+    <t xml:space="preserve">9.72982788085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68619823455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98809337615967</t>
   </si>
   <si>
     <t xml:space="preserve">9.42440795898438</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6496162414551</t>
+    <t xml:space="preserve">11.6496152877808</t>
   </si>
   <si>
     <t xml:space="preserve">11.5623531341553</t>
@@ -1928,19 +1928,19 @@
     <t xml:space="preserve">11.7805099487305</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9114036560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9550361633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6932468414307</t>
+    <t xml:space="preserve">11.9114046096802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9550352096558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.693247795105</t>
   </si>
   <si>
     <t xml:space="preserve">12.3040885925293</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2604579925537</t>
+    <t xml:space="preserve">12.2604570388794</t>
   </si>
   <si>
     <t xml:space="preserve">12.2168254852295</t>
@@ -1955,7 +1955,7 @@
     <t xml:space="preserve">11.8677730560303</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6059837341309</t>
+    <t xml:space="preserve">11.6059846878052</t>
   </si>
   <si>
     <t xml:space="preserve">10.9515113830566</t>
@@ -1964,28 +1964,28 @@
     <t xml:space="preserve">12.0422992706299</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3005638122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3441944122314</t>
+    <t xml:space="preserve">11.3005628585815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3441953659058</t>
   </si>
   <si>
     <t xml:space="preserve">10.9951429367065</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4715642929077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9078798294067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4314575195312</t>
+    <t xml:space="preserve">10.471565246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9078788757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4314584732056</t>
   </si>
   <si>
     <t xml:space="preserve">11.0387744903564</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9899415969849</t>
+    <t xml:space="preserve">11.9899406433105</t>
   </si>
   <si>
     <t xml:space="preserve">11.74560546875</t>
@@ -1994,10 +1994,10 @@
     <t xml:space="preserve">11.5361738204956</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5187206268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6234359741211</t>
+    <t xml:space="preserve">11.5187215805054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6234369277954</t>
   </si>
   <si>
     <t xml:space="preserve">11.4489107131958</t>
@@ -2015,10 +2015,10 @@
     <t xml:space="preserve">11.1173105239868</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0998582839966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8031644821167</t>
+    <t xml:space="preserve">11.0998601913452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8031635284424</t>
   </si>
   <si>
     <t xml:space="preserve">10.7508068084717</t>
@@ -2036,7 +2036,7 @@
     <t xml:space="preserve">9.69297409057617</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71089172363281</t>
+    <t xml:space="preserve">9.7108907699585</t>
   </si>
   <si>
     <t xml:space="preserve">10.1408929824829</t>
@@ -2045,10 +2045,10 @@
     <t xml:space="preserve">10.2663106918335</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3738107681274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1229772567749</t>
+    <t xml:space="preserve">10.3738117218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1229763031006</t>
   </si>
   <si>
     <t xml:space="preserve">10.1588106155396</t>
@@ -2063,13 +2063,13 @@
     <t xml:space="preserve">10.4633951187134</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7858963012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.570897102356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7142305374146</t>
+    <t xml:space="preserve">10.7858982086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5708961486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7142295837402</t>
   </si>
   <si>
     <t xml:space="preserve">10.7500638961792</t>
@@ -2081,16 +2081,16 @@
     <t xml:space="preserve">10.8754816055298</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6425638198853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.588812828064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5171461105347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8575639724731</t>
+    <t xml:space="preserve">10.6425628662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5888118743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5171451568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8575649261475</t>
   </si>
   <si>
     <t xml:space="preserve">10.9113149642944</t>
@@ -2102,16 +2102,16 @@
     <t xml:space="preserve">10.6604795455933</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3021440505981</t>
+    <t xml:space="preserve">10.3021450042725</t>
   </si>
   <si>
     <t xml:space="preserve">10.4096450805664</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3558950424194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6783971786499</t>
+    <t xml:space="preserve">10.3558940887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6783962249756</t>
   </si>
   <si>
     <t xml:space="preserve">10.4275617599487</t>
@@ -2120,10 +2120,10 @@
     <t xml:space="preserve">10.535062789917</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1800651550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.982982635498</t>
+    <t xml:space="preserve">11.1800661087036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9829816818237</t>
   </si>
   <si>
     <t xml:space="preserve">11.4846515655518</t>
@@ -2132,16 +2132,16 @@
     <t xml:space="preserve">11.3771505355835</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7354860305786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9146547317505</t>
+    <t xml:space="preserve">11.7354869842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9146537780762</t>
   </si>
   <si>
     <t xml:space="preserve">11.9325704574585</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0221548080444</t>
+    <t xml:space="preserve">12.0221538543701</t>
   </si>
   <si>
     <t xml:space="preserve">11.8788204193115</t>
@@ -2162,7 +2162,7 @@
     <t xml:space="preserve">12.3984069824219</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2013216018677</t>
+    <t xml:space="preserve">12.201322555542</t>
   </si>
   <si>
     <t xml:space="preserve">11.9863214492798</t>
@@ -2174,13 +2174,13 @@
     <t xml:space="preserve">12.6134080886841</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8463268280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8104934692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9179925918579</t>
+    <t xml:space="preserve">12.8463258743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.810492515564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9179935455322</t>
   </si>
   <si>
     <t xml:space="preserve">13.258412361145</t>
@@ -2192,16 +2192,16 @@
     <t xml:space="preserve">13.4375791549683</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6884145736694</t>
+    <t xml:space="preserve">13.6884136199951</t>
   </si>
   <si>
     <t xml:space="preserve">13.903416633606</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6559209823608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2438335418701</t>
+    <t xml:space="preserve">14.6559200286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2438344955444</t>
   </si>
   <si>
     <t xml:space="preserve">14.6380033493042</t>
@@ -2219,10 +2219,10 @@
     <t xml:space="preserve">14.7992544174194</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5484199523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4946689605713</t>
+    <t xml:space="preserve">14.5484189987183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4946699142456</t>
   </si>
   <si>
     <t xml:space="preserve">14.2617511749268</t>
@@ -2231,10 +2231,10 @@
     <t xml:space="preserve">14.8888387680054</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8171710968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.387167930603</t>
+    <t xml:space="preserve">14.8171720504761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3871688842773</t>
   </si>
   <si>
     <t xml:space="preserve">14.7634201049805</t>
@@ -2243,25 +2243,25 @@
     <t xml:space="preserve">14.6200866699219</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9067535400391</t>
+    <t xml:space="preserve">14.9067544937134</t>
   </si>
   <si>
     <t xml:space="preserve">15.1217546463013</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0321741104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7455034255981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0500888824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0680065155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1038398742676</t>
+    <t xml:space="preserve">15.0321731567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7455043792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.050087928772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0680055618286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1038408279419</t>
   </si>
   <si>
     <t xml:space="preserve">14.5305023193359</t>
@@ -2270,7 +2270,7 @@
     <t xml:space="preserve">14.7096710205078</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2080011367798</t>
+    <t xml:space="preserve">14.2080001831055</t>
   </si>
   <si>
     <t xml:space="preserve">13.6167469024658</t>
@@ -2306,10 +2306,10 @@
     <t xml:space="preserve">13.4913301467896</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2225790023804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2046613693237</t>
+    <t xml:space="preserve">13.2225780487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2046604156494</t>
   </si>
   <si>
     <t xml:space="preserve">13.0613269805908</t>
@@ -2321,10 +2321,10 @@
     <t xml:space="preserve">12.6313247680664</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0971612930298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0792436599731</t>
+    <t xml:space="preserve">13.0971603393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0792446136475</t>
   </si>
   <si>
     <t xml:space="preserve">12.8642425537109</t>
@@ -2336,7 +2336,7 @@
     <t xml:space="preserve">12.9538269042969</t>
   </si>
   <si>
-    <t xml:space="preserve">12.720908164978</t>
+    <t xml:space="preserve">12.7209091186523</t>
   </si>
   <si>
     <t xml:space="preserve">12.5596580505371</t>
@@ -2345,22 +2345,22 @@
     <t xml:space="preserve">13.1150779724121</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1509103775024</t>
+    <t xml:space="preserve">13.1509122848511</t>
   </si>
   <si>
     <t xml:space="preserve">13.5271635055542</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3479957580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2763290405273</t>
+    <t xml:space="preserve">13.3479948043823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.276328086853</t>
   </si>
   <si>
     <t xml:space="preserve">12.7925758361816</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5954914093018</t>
+    <t xml:space="preserve">12.5954923629761</t>
   </si>
   <si>
     <t xml:space="preserve">12.5238237380981</t>
@@ -2369,10 +2369,10 @@
     <t xml:space="preserve">12.5059070587158</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4879903793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3088235855103</t>
+    <t xml:space="preserve">12.4879894256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3088226318359</t>
   </si>
   <si>
     <t xml:space="preserve">12.5417413711548</t>
@@ -2381,7 +2381,7 @@
     <t xml:space="preserve">12.8284091949463</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3804903030396</t>
+    <t xml:space="preserve">12.3804893493652</t>
   </si>
   <si>
     <t xml:space="preserve">12.6671581268311</t>
@@ -2393,28 +2393,28 @@
     <t xml:space="preserve">12.6492414474487</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7746601104736</t>
+    <t xml:space="preserve">12.7746591567993</t>
   </si>
   <si>
     <t xml:space="preserve">12.4342403411865</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9504880905151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2192392349243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8250694274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1117382049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9684038162231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0400705337524</t>
+    <t xml:space="preserve">11.9504871368408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2192401885986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8250703811646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1117391586304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9684047698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0400714874268</t>
   </si>
   <si>
     <t xml:space="preserve">12.0042381286621</t>
@@ -2423,19 +2423,19 @@
     <t xml:space="preserve">12.255072593689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7388257980347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7421655654907</t>
+    <t xml:space="preserve">12.7388248443604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7421646118164</t>
   </si>
   <si>
     <t xml:space="preserve">13.7063312530518</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0825843811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0109157562256</t>
+    <t xml:space="preserve">14.0825834274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0109167098999</t>
   </si>
   <si>
     <t xml:space="preserve">13.7242479324341</t>
@@ -2444,7 +2444,7 @@
     <t xml:space="preserve">14.0467500686646</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0646667480469</t>
+    <t xml:space="preserve">14.0646657943726</t>
   </si>
   <si>
     <t xml:space="preserve">13.9392490386963</t>
@@ -2462,22 +2462,22 @@
     <t xml:space="preserve">13.9571657180786</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8496656417847</t>
+    <t xml:space="preserve">13.8496646881104</t>
   </si>
   <si>
     <t xml:space="preserve">13.9750833511353</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5450792312622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4734125137329</t>
+    <t xml:space="preserve">13.5450801849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4734134674072</t>
   </si>
   <si>
     <t xml:space="preserve">13.1867456436157</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3838291168213</t>
+    <t xml:space="preserve">13.383828163147</t>
   </si>
   <si>
     <t xml:space="preserve">13.5988302230835</t>
@@ -2498,16 +2498,16 @@
     <t xml:space="preserve">12.0759048461914</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5742349624634</t>
+    <t xml:space="preserve">11.5742359161377</t>
   </si>
   <si>
     <t xml:space="preserve">11.2159004211426</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3592338562012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4309024810791</t>
+    <t xml:space="preserve">11.3592348098755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4309015274048</t>
   </si>
   <si>
     <t xml:space="preserve">11.3054828643799</t>
@@ -2516,13 +2516,13 @@
     <t xml:space="preserve">11.2875671386719</t>
   </si>
   <si>
-    <t xml:space="preserve">11.683783531189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5179262161255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2783517837524</t>
+    <t xml:space="preserve">11.6837844848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5179252624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2783527374268</t>
   </si>
   <si>
     <t xml:space="preserve">11.1493520736694</t>
@@ -2534,7 +2534,7 @@
     <t xml:space="preserve">11.0756378173828</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9970722198486</t>
+    <t xml:space="preserve">11.9970712661743</t>
   </si>
   <si>
     <t xml:space="preserve">12.052357673645</t>
@@ -2543,7 +2543,7 @@
     <t xml:space="preserve">12.2735013961792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2182149887085</t>
+    <t xml:space="preserve">12.2182159423828</t>
   </si>
   <si>
     <t xml:space="preserve">12.4025020599365</t>
@@ -2555,7 +2555,7 @@
     <t xml:space="preserve">12.0707864761353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1629285812378</t>
+    <t xml:space="preserve">12.1629295349121</t>
   </si>
   <si>
     <t xml:space="preserve">12.1260719299316</t>
@@ -2570,13 +2570,13 @@
     <t xml:space="preserve">11.7759265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8312129974365</t>
+    <t xml:space="preserve">11.8312139511108</t>
   </si>
   <si>
     <t xml:space="preserve">11.9786424636841</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7206411361694</t>
+    <t xml:space="preserve">11.7206420898438</t>
   </si>
   <si>
     <t xml:space="preserve">11.868070602417</t>
@@ -2591,7 +2591,7 @@
     <t xml:space="preserve">11.4442110061646</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3520669937134</t>
+    <t xml:space="preserve">11.3520679473877</t>
   </si>
   <si>
     <t xml:space="preserve">11.3704957962036</t>
@@ -2609,7 +2609,7 @@
     <t xml:space="preserve">11.7022123336792</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5732116699219</t>
+    <t xml:space="preserve">11.5732126235962</t>
   </si>
   <si>
     <t xml:space="preserve">11.481068611145</t>
@@ -2618,7 +2618,7 @@
     <t xml:space="preserve">11.296781539917</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3152093887329</t>
+    <t xml:space="preserve">11.3152103424072</t>
   </si>
   <si>
     <t xml:space="preserve">11.5547828674316</t>
@@ -2627,7 +2627,7 @@
     <t xml:space="preserve">11.4257822036743</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3336381912231</t>
+    <t xml:space="preserve">11.3336391448975</t>
   </si>
   <si>
     <t xml:space="preserve">11.3889245986938</t>
@@ -2636,7 +2636,7 @@
     <t xml:space="preserve">11.4626398086548</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7943553924561</t>
+    <t xml:space="preserve">11.7943563461304</t>
   </si>
   <si>
     <t xml:space="preserve">12.1076431274414</t>
@@ -2666,7 +2666,7 @@
     <t xml:space="preserve">13.0290775299072</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2502222061157</t>
+    <t xml:space="preserve">13.2502212524414</t>
   </si>
   <si>
     <t xml:space="preserve">13.4160804748535</t>
@@ -2681,7 +2681,7 @@
     <t xml:space="preserve">12.6420755386353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8816480636597</t>
+    <t xml:space="preserve">12.8816471099854</t>
   </si>
   <si>
     <t xml:space="preserve">12.9185056686401</t>
@@ -2690,7 +2690,7 @@
     <t xml:space="preserve">13.194935798645</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1580772399902</t>
+    <t xml:space="preserve">13.1580781936646</t>
   </si>
   <si>
     <t xml:space="preserve">12.8079328536987</t>
@@ -2705,7 +2705,7 @@
     <t xml:space="preserve">12.5499315261841</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0843629837036</t>
+    <t xml:space="preserve">13.0843639373779</t>
   </si>
   <si>
     <t xml:space="preserve">13.3423643112183</t>
@@ -2723,13 +2723,13 @@
     <t xml:space="preserve">13.1027917861938</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3607940673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2133646011353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5266513824463</t>
+    <t xml:space="preserve">13.3607931137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2133636474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5266523361206</t>
   </si>
   <si>
     <t xml:space="preserve">13.6003665924072</t>
@@ -2747,28 +2747,28 @@
     <t xml:space="preserve">13.7846536636353</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0610828399658</t>
+    <t xml:space="preserve">14.0610837936401</t>
   </si>
   <si>
     <t xml:space="preserve">14.2637987136841</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5402297973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6139440536499</t>
+    <t xml:space="preserve">14.540228843689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6139430999756</t>
   </si>
   <si>
     <t xml:space="preserve">15.3695201873779</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5353784561157</t>
+    <t xml:space="preserve">15.53537940979</t>
   </si>
   <si>
     <t xml:space="preserve">15.6275205612183</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5722360610962</t>
+    <t xml:space="preserve">15.5722341537476</t>
   </si>
   <si>
     <t xml:space="preserve">15.4063768386841</t>
@@ -2780,34 +2780,34 @@
     <t xml:space="preserve">15.295804977417</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2773761749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4616651535034</t>
+    <t xml:space="preserve">15.2773771286011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4616641998291</t>
   </si>
   <si>
     <t xml:space="preserve">15.6459493637085</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4432344436646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6643781661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7012376785278</t>
+    <t xml:space="preserve">15.4432353973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.664379119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7012367248535</t>
   </si>
   <si>
     <t xml:space="preserve">15.6090936660767</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3326606750488</t>
+    <t xml:space="preserve">15.3326616287231</t>
   </si>
   <si>
     <t xml:space="preserve">15.2036619186401</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1668033599854</t>
+    <t xml:space="preserve">15.1668043136597</t>
   </si>
   <si>
     <t xml:space="preserve">14.8535175323486</t>
@@ -2828,22 +2828,22 @@
     <t xml:space="preserve">15.8302373886108</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7196645736694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3879489898682</t>
+    <t xml:space="preserve">15.7196636199951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3879499435425</t>
   </si>
   <si>
     <t xml:space="preserve">15.5906648635864</t>
   </si>
   <si>
-    <t xml:space="preserve">15.682806968689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7565221786499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7380933761597</t>
+    <t xml:space="preserve">15.6828079223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7565231323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.738094329834</t>
   </si>
   <si>
     <t xml:space="preserve">15.1483764648438</t>
@@ -2855,7 +2855,7 @@
     <t xml:space="preserve">15.1299476623535</t>
   </si>
   <si>
-    <t xml:space="preserve">15.480092048645</t>
+    <t xml:space="preserve">15.4800910949707</t>
   </si>
   <si>
     <t xml:space="preserve">15.9223804473877</t>
@@ -2867,22 +2867,22 @@
     <t xml:space="preserve">16.0882377624512</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7749509811401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.867094039917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7109394073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6556529998779</t>
+    <t xml:space="preserve">15.7749519348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8670930862427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7109384536743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6556520462036</t>
   </si>
   <si>
     <t xml:space="preserve">13.6372241973877</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1347990036011</t>
+    <t xml:space="preserve">14.1347980499268</t>
   </si>
   <si>
     <t xml:space="preserve">14.4480857849121</t>
@@ -2894,7 +2894,7 @@
     <t xml:space="preserve">14.0242261886597</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0795125961304</t>
+    <t xml:space="preserve">14.0795116424561</t>
   </si>
   <si>
     <t xml:space="preserve">14.0057973861694</t>
@@ -2915,7 +2915,7 @@
     <t xml:space="preserve">13.4897947311401</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6187953948975</t>
+    <t xml:space="preserve">13.6187944412231</t>
   </si>
   <si>
     <t xml:space="preserve">12.8263626098633</t>
@@ -2927,7 +2927,7 @@
     <t xml:space="preserve">13.2686500549316</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9369335174561</t>
+    <t xml:space="preserve">12.9369344711304</t>
   </si>
   <si>
     <t xml:space="preserve">12.9000768661499</t>
@@ -2936,10 +2936,10 @@
     <t xml:space="preserve">12.9922199249268</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0475053787231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6973600387573</t>
+    <t xml:space="preserve">13.0475063323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6973609924316</t>
   </si>
   <si>
     <t xml:space="preserve">12.6052179336548</t>
@@ -2951,7 +2951,7 @@
     <t xml:space="preserve">12.4209308624268</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4762172698975</t>
+    <t xml:space="preserve">12.4762163162231</t>
   </si>
   <si>
     <t xml:space="preserve">12.6236457824707</t>
@@ -3546,6 +3546,9 @@
   </si>
   <si>
     <t xml:space="preserve">17.4599990844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6000003814697</t>
   </si>
 </sst>
 </file>
@@ -69690,7 +69693,7 @@
     </row>
     <row r="2532">
       <c r="A2532" s="1" t="n">
-        <v>46003.6911805556</v>
+        <v>46003.3333333333</v>
       </c>
       <c r="B2532" t="n">
         <v>16036</v>
@@ -69711,6 +69714,32 @@
         <v>1176</v>
       </c>
       <c r="H2532" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2533">
+      <c r="A2533" s="1" t="n">
+        <v>46006.6911458333</v>
+      </c>
+      <c r="B2533" t="n">
+        <v>31403</v>
+      </c>
+      <c r="C2533" t="n">
+        <v>17.6599998474121</v>
+      </c>
+      <c r="D2533" t="n">
+        <v>17.3199996948242</v>
+      </c>
+      <c r="E2533" t="n">
+        <v>17.3600006103516</v>
+      </c>
+      <c r="F2533" t="n">
+        <v>17.6000003814697</v>
+      </c>
+      <c r="G2533" t="s">
+        <v>1178</v>
+      </c>
+      <c r="H2533" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ORS.MI.xlsx
+++ b/data/ORS.MI.xlsx
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08406448364258</t>
+    <t xml:space="preserve">8.08406352996826</t>
   </si>
   <si>
     <t xml:space="preserve">ORS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98275995254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06380176544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94223690032959</t>
+    <t xml:space="preserve">7.98275947570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06380271911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94223785400391</t>
   </si>
   <si>
     <t xml:space="preserve">7.82472467422485</t>
@@ -62,19 +62,19 @@
     <t xml:space="preserve">7.90171527862549</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03948783874512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92602968215942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86119365692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82067203521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9341344833374</t>
+    <t xml:space="preserve">8.03948879241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92603015899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86119556427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82067394256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93413352966309</t>
   </si>
   <si>
     <t xml:space="preserve">8.02328109741211</t>
@@ -89,61 +89,61 @@
     <t xml:space="preserve">7.69910764694214</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80446481704712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97465467453003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01112461090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01517677307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79230880737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82877683639526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34745407104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84093284606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90982007980347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85714197158813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78015184402466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84498500823975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9787073135376</t>
+    <t xml:space="preserve">7.80446434020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9746561050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01112365722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01517581939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79230737686157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82877826690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34745311737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84093332290649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90982151031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85714101791382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7801513671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84498596191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97870683670044</t>
   </si>
   <si>
     <t xml:space="preserve">7.88550662994385</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95034217834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00302028656006</t>
+    <t xml:space="preserve">7.95034122467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00301933288574</t>
   </si>
   <si>
     <t xml:space="preserve">8.01922798156738</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91792440414429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10027122497559</t>
+    <t xml:space="preserve">7.91792392730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1002721786499</t>
   </si>
   <si>
     <t xml:space="preserve">8.104323387146</t>
@@ -161,52 +161,52 @@
     <t xml:space="preserve">8.07595920562744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03138542175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09621906280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17726230621338</t>
+    <t xml:space="preserve">8.03138446807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09622097015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1772632598877</t>
   </si>
   <si>
     <t xml:space="preserve">8.05569839477539</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12053203582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25830745697021</t>
+    <t xml:space="preserve">8.12053298950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25830554962158</t>
   </si>
   <si>
     <t xml:space="preserve">8.42039203643799</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6716251373291</t>
+    <t xml:space="preserve">8.67162799835205</t>
   </si>
   <si>
     <t xml:space="preserve">8.55816650390625</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42849826812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52429008483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45921897888184</t>
+    <t xml:space="preserve">8.42849731445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52429103851318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45921802520752</t>
   </si>
   <si>
     <t xml:space="preserve">8.50802230834961</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60562801361084</t>
+    <t xml:space="preserve">8.60562705993652</t>
   </si>
   <si>
     <t xml:space="preserve">8.53242301940918</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61376190185547</t>
+    <t xml:space="preserve">8.61376094818115</t>
   </si>
   <si>
     <t xml:space="preserve">8.67069911956787</t>
@@ -218,73 +218,73 @@
     <t xml:space="preserve">8.7927074432373</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90657997131348</t>
+    <t xml:space="preserve">8.90658092498779</t>
   </si>
   <si>
     <t xml:space="preserve">8.86591243743896</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94725036621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93911647796631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78457260131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74390411376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91471576690674</t>
+    <t xml:space="preserve">8.94724941253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93911743164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78457355499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74390316009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91471385955811</t>
   </si>
   <si>
     <t xml:space="preserve">8.92284965515137</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10992813110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07739353179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11806106567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1343297958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15059757232666</t>
+    <t xml:space="preserve">9.10992908477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07739162445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11806201934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13432884216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15059661865234</t>
   </si>
   <si>
     <t xml:space="preserve">9.15873146057129</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7357702255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67883205413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85777759552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72763538360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70323467254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66256618499756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69510173797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6218957901001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80084037780762</t>
+    <t xml:space="preserve">8.73576927185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67883110046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85777854919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72763729095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7032356262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66256523132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69510078430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62189674377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80084133148193</t>
   </si>
   <si>
     <t xml:space="preserve">8.77643966674805</t>
@@ -293,10 +293,10 @@
     <t xml:space="preserve">8.68696784973145</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54869079589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54055690765381</t>
+    <t xml:space="preserve">8.54868984222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54055595397949</t>
   </si>
   <si>
     <t xml:space="preserve">8.58122730255127</t>
@@ -305,19 +305,19 @@
     <t xml:space="preserve">8.46735286712646</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51615715026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49988651275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45108413696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63003063201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80897617340088</t>
+    <t xml:space="preserve">8.51615619659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49988842010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45108509063721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63003158569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80897521972656</t>
   </si>
   <si>
     <t xml:space="preserve">8.89031505584717</t>
@@ -326,16 +326,16 @@
     <t xml:space="preserve">8.930983543396</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9635181427002</t>
+    <t xml:space="preserve">8.96351909637451</t>
   </si>
   <si>
     <t xml:space="preserve">9.05299091339111</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30514049530029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1017951965332</t>
+    <t xml:space="preserve">9.30514144897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10179424285889</t>
   </si>
   <si>
     <t xml:space="preserve">9.1912670135498</t>
@@ -344,31 +344,31 @@
     <t xml:space="preserve">9.35394287109375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47595119476318</t>
+    <t xml:space="preserve">9.47595310211182</t>
   </si>
   <si>
     <t xml:space="preserve">9.54915618896484</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58982563018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66303157806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71996688842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85824298858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0046510696411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2405347824097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2486696243286</t>
+    <t xml:space="preserve">9.58982467651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66303062438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71996593475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85824394226074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0046529769897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.240535736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2486686706543</t>
   </si>
   <si>
     <t xml:space="preserve">10.3381423950195</t>
@@ -377,10 +377,10 @@
     <t xml:space="preserve">10.5984258651733</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4276151657104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4032125473022</t>
+    <t xml:space="preserve">10.4276142120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4032115936279</t>
   </si>
   <si>
     <t xml:space="preserve">10.5252199172974</t>
@@ -392,19 +392,19 @@
     <t xml:space="preserve">10.5658893585205</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5821571350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7773704528809</t>
+    <t xml:space="preserve">10.5821580886841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7773714065552</t>
   </si>
   <si>
     <t xml:space="preserve">10.9807167053223</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8749771118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6553621292114</t>
+    <t xml:space="preserve">10.8749761581421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6553630828857</t>
   </si>
   <si>
     <t xml:space="preserve">10.679762840271</t>
@@ -413,37 +413,37 @@
     <t xml:space="preserve">10.5740242004395</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5170879364014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5414896011353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5577564239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5089511871338</t>
+    <t xml:space="preserve">10.5170869827271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5414876937866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5577554702759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5089530944824</t>
   </si>
   <si>
     <t xml:space="preserve">10.8180389404297</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6878976821899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7611026763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6472282409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8993787765503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8831100463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6716299057007</t>
+    <t xml:space="preserve">10.6878967285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7611017227173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6472301483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8993768692017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.883111000061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6716289520264</t>
   </si>
   <si>
     <t xml:space="preserve">10.7367010116577</t>
@@ -455,13 +455,13 @@
     <t xml:space="preserve">11.0213871002197</t>
   </si>
   <si>
-    <t xml:space="preserve">11.184063911438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4036769866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3955430984497</t>
+    <t xml:space="preserve">11.1840648651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4036779403687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.395544052124</t>
   </si>
   <si>
     <t xml:space="preserve">11.3386068344116</t>
@@ -470,22 +470,22 @@
     <t xml:space="preserve">11.3223400115967</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3304719924927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3630084991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0783243179321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.606559753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8424425125122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8505744934082</t>
+    <t xml:space="preserve">11.3304738998413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3630094528198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0783233642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6065587997437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8424406051636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8505754470825</t>
   </si>
   <si>
     <t xml:space="preserve">10.6390943527222</t>
@@ -497,22 +497,22 @@
     <t xml:space="preserve">10.2080001831055</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2730693817139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.232400894165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.321873664856</t>
+    <t xml:space="preserve">10.2730712890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2323989868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3218746185303</t>
   </si>
   <si>
     <t xml:space="preserve">10.3706769943237</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3300075531006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3056058883667</t>
+    <t xml:space="preserve">10.3300085067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3056049346924</t>
   </si>
   <si>
     <t xml:space="preserve">10.2568035125732</t>
@@ -521,52 +521,52 @@
     <t xml:space="preserve">10.1835975646973</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4845514297485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3625431060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4438819885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8587074279785</t>
+    <t xml:space="preserve">10.4845523834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3625421524048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4438829421997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8587093353271</t>
   </si>
   <si>
     <t xml:space="preserve">10.9237804412842</t>
   </si>
   <si>
-    <t xml:space="preserve">11.037652015686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0620555877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.102725982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1433954238892</t>
+    <t xml:space="preserve">11.0376539230347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0620565414429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1027240753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1433935165405</t>
   </si>
   <si>
     <t xml:space="preserve">11.1759281158447</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1352596282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0701894760132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1189937591553</t>
+    <t xml:space="preserve">11.1352605819702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0701904296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.118992805481</t>
   </si>
   <si>
     <t xml:space="preserve">11.1515274047852</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2247333526611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0457878112793</t>
+    <t xml:space="preserve">11.2247323989868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.045786857605</t>
   </si>
   <si>
     <t xml:space="preserve">10.5008182525635</t>
@@ -575,49 +575,49 @@
     <t xml:space="preserve">10.1347951889038</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36161231994629</t>
+    <t xml:space="preserve">8.36161327362061</t>
   </si>
   <si>
     <t xml:space="preserve">8.01999092102051</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10946369171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39414882659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2152042388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3372106552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31280994415283</t>
+    <t xml:space="preserve">8.10946273803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3941478729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21520519256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33720970153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3128080368042</t>
   </si>
   <si>
     <t xml:space="preserve">8.18266773223877</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34534454345703</t>
+    <t xml:space="preserve">8.34534549713135</t>
   </si>
   <si>
     <t xml:space="preserve">8.23960399627686</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49175453186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58935928344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76017093658447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29654121398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25587272644043</t>
+    <t xml:space="preserve">8.49175548553467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58936023712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76017284393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29654216766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25587177276611</t>
   </si>
   <si>
     <t xml:space="preserve">8.17453384399414</t>
@@ -626,37 +626,37 @@
     <t xml:space="preserve">8.1908016204834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23147010803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28027248382568</t>
+    <t xml:space="preserve">8.23147106170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2802734375</t>
   </si>
   <si>
     <t xml:space="preserve">8.14199733734131</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15826511383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16640090942383</t>
+    <t xml:space="preserve">8.15826606750488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16639995574951</t>
   </si>
   <si>
     <t xml:space="preserve">8.12166309356689</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05252456665039</t>
+    <t xml:space="preserve">8.05252647399902</t>
   </si>
   <si>
     <t xml:space="preserve">7.89798259735107</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85731363296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93051767349243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90611600875854</t>
+    <t xml:space="preserve">7.85731315612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93051815032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90611696243286</t>
   </si>
   <si>
     <t xml:space="preserve">7.93865156173706</t>
@@ -665,67 +665,67 @@
     <t xml:space="preserve">7.84917879104614</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80850982666016</t>
+    <t xml:space="preserve">7.808509349823</t>
   </si>
   <si>
     <t xml:space="preserve">7.62956476211548</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57262754440308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48315572738647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66616630554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60516309738159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54009246826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52382373809814</t>
+    <t xml:space="preserve">7.57262706756592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48315525054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66616582870483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60516405105591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54009342193604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5238242149353</t>
   </si>
   <si>
     <t xml:space="preserve">7.47908735275269</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61329746246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54822587966919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56449365615845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50755643844604</t>
+    <t xml:space="preserve">7.61329698562622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54822540283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56449413299561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50755596160889</t>
   </si>
   <si>
     <t xml:space="preserve">7.4668869972229</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4912896156311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49942207336426</t>
+    <t xml:space="preserve">7.49129009246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4994215965271</t>
   </si>
   <si>
     <t xml:space="preserve">7.31234455108643</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27980852127075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3774151802063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38554811477661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36928129196167</t>
+    <t xml:space="preserve">7.27980756759644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37741470336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38554906845093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36928033828735</t>
   </si>
   <si>
     <t xml:space="preserve">7.32047748565674</t>
@@ -734,141 +734,141 @@
     <t xml:space="preserve">7.34487915039062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28794097900391</t>
+    <t xml:space="preserve">7.28794193267822</t>
   </si>
   <si>
     <t xml:space="preserve">7.04392623901367</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15780115127563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39368343353271</t>
+    <t xml:space="preserve">7.15780019760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39368295669556</t>
   </si>
   <si>
     <t xml:space="preserve">7.42621803283691</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40181589126587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3042106628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36114692687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20660448074341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35301351547241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33674573898315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27167415618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23100519180298</t>
+    <t xml:space="preserve">7.40181684494019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30421018600464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36114740371704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20660305023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3530125617981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.336745262146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27167463302612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23100471496582</t>
   </si>
   <si>
     <t xml:space="preserve">7.32861185073853</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26354122161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23913908004761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22287130355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24727439880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44248676300049</t>
+    <t xml:space="preserve">7.26354169845581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23913955688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22287178039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24727392196655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44248580932617</t>
   </si>
   <si>
     <t xml:space="preserve">7.25540781021118</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18220186233521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29607582092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16593456268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1415319442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05205917358398</t>
+    <t xml:space="preserve">7.18220281600952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29607677459717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16593408584595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14153242111206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0520601272583</t>
   </si>
   <si>
     <t xml:space="preserve">7.07646226882935</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03579235076904</t>
+    <t xml:space="preserve">7.0357928276062</t>
   </si>
   <si>
     <t xml:space="preserve">7.01952505111694</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87311458587646</t>
+    <t xml:space="preserve">6.87311506271362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.677903175354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85124778747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93379211425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26397323608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14840984344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09888315200806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18142890930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16491794586182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14015626907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21444654464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17317390441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97506475448608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84299325942993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60361289978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62012100219727</t>
   </si>
   <si>
     <t xml:space="preserve">6.67790269851685</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85124731063843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93379211425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26397371292114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14840936660767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09888315200806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18142890930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16491889953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14015626907349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21444606781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17317342758179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97506523132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84299278259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60361242294312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62012147903442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67790222167969</t>
-  </si>
-  <si>
     <t xml:space="preserve">6.80997467041016</t>
   </si>
   <si>
@@ -878,16 +878,16 @@
     <t xml:space="preserve">6.31470394134521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32295799255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34772253036499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38074064254761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3972487449646</t>
+    <t xml:space="preserve">6.32295846939087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34772300720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38074016571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39724922180176</t>
   </si>
   <si>
     <t xml:space="preserve">6.47153997421265</t>
@@ -899,67 +899,67 @@
     <t xml:space="preserve">6.22390365600586</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09183263778687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90197849273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95975971221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9927773475647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20739555358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14135932922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19088649749756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14961385726929</t>
+    <t xml:space="preserve">6.09183216094971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90197801589966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95976066589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99277687072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20739507675171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14135885238647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19088697433472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14961290359497</t>
   </si>
   <si>
     <t xml:space="preserve">6.0753231048584</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25692319869995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00928783416748</t>
+    <t xml:space="preserve">6.25692272186279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00928735733032</t>
   </si>
   <si>
     <t xml:space="preserve">5.9845232963562</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12484979629517</t>
+    <t xml:space="preserve">6.12485122680664</t>
   </si>
   <si>
     <t xml:space="preserve">6.13310527801514</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27343130111694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44677495956421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55408477783203</t>
+    <t xml:space="preserve">6.2734317779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44677591323853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55408525466919</t>
   </si>
   <si>
     <t xml:space="preserve">6.51281213760376</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36423110961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24041318893433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21565008163452</t>
+    <t xml:space="preserve">6.3642315864563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24041366577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21564960479736</t>
   </si>
   <si>
     <t xml:space="preserve">6.23215913772583</t>
@@ -968,16 +968,16 @@
     <t xml:space="preserve">6.24866819381714</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11659526824951</t>
+    <t xml:space="preserve">6.11659622192383</t>
   </si>
   <si>
     <t xml:space="preserve">6.10834074020386</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05055999755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89372396469116</t>
+    <t xml:space="preserve">6.05055952072144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89372444152832</t>
   </si>
   <si>
     <t xml:space="preserve">5.77816104888916</t>
@@ -986,25 +986,25 @@
     <t xml:space="preserve">5.69561529159546</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79466915130615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80292415618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82768821716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78641510009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73688793182373</t>
+    <t xml:space="preserve">5.79466962814331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80292367935181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82768726348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78641557693481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73688745498657</t>
   </si>
   <si>
     <t xml:space="preserve">5.85245132446289</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29819583892822</t>
+    <t xml:space="preserve">6.29819536209106</t>
   </si>
   <si>
     <t xml:space="preserve">6.18263244628906</t>
@@ -1022,10 +1022,10 @@
     <t xml:space="preserve">5.81943368911743</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91848611831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86070537567139</t>
+    <t xml:space="preserve">5.91848659515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86070585250854</t>
   </si>
   <si>
     <t xml:space="preserve">5.76165151596069</t>
@@ -1046,13 +1046,13 @@
     <t xml:space="preserve">5.83594226837158</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71212434768677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84419727325439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94325113296509</t>
+    <t xml:space="preserve">5.71212482452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84419679641724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94325065612793</t>
   </si>
   <si>
     <t xml:space="preserve">5.96801471710205</t>
@@ -1067,28 +1067,28 @@
     <t xml:space="preserve">5.93499612808228</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02579593658447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0670690536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3889946937561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1991400718689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04230451583862</t>
+    <t xml:space="preserve">6.02579641342163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06706857681274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38899421691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19914150238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04230499267578</t>
   </si>
   <si>
     <t xml:space="preserve">6.05881452560425</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95150566101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17437791824341</t>
+    <t xml:space="preserve">5.9515061378479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17437744140625</t>
   </si>
   <si>
     <t xml:space="preserve">6.17601919174194</t>
@@ -1097,7 +1097,7 @@
     <t xml:space="preserve">6.29349803924561</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25993204116821</t>
+    <t xml:space="preserve">6.25993251800537</t>
   </si>
   <si>
     <t xml:space="preserve">6.20958423614502</t>
@@ -1106,25 +1106,25 @@
     <t xml:space="preserve">6.09210538864136</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10888957977295</t>
+    <t xml:space="preserve">6.10888862609863</t>
   </si>
   <si>
     <t xml:space="preserve">6.07532358169556</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14245319366455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05854034423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02497577667236</t>
+    <t xml:space="preserve">6.14245367050171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0585412979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02497482299805</t>
   </si>
   <si>
     <t xml:space="preserve">5.97462749481201</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95784425735474</t>
+    <t xml:space="preserve">5.95784473419189</t>
   </si>
   <si>
     <t xml:space="preserve">6.15923690795898</t>
@@ -1133,58 +1133,58 @@
     <t xml:space="preserve">6.12567138671875</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19280242919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42775869369507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71306467056274</t>
+    <t xml:space="preserve">6.19280195236206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42775917053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7130651473999</t>
   </si>
   <si>
     <t xml:space="preserve">6.64593458175659</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69628238677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78019571304321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72984743118286</t>
+    <t xml:space="preserve">6.69628190994263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7801947593689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7298469543457</t>
   </si>
   <si>
     <t xml:space="preserve">6.629150390625</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56202077865601</t>
+    <t xml:space="preserve">6.56202030181885</t>
   </si>
   <si>
     <t xml:space="preserve">6.54523801803589</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67949867248535</t>
+    <t xml:space="preserve">6.67949914932251</t>
   </si>
   <si>
     <t xml:space="preserve">6.66271638870239</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57880306243896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37741088867188</t>
+    <t xml:space="preserve">6.57880353927612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37741136550903</t>
   </si>
   <si>
     <t xml:space="preserve">6.3438458442688</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22636699676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36062908172607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67253923416138</t>
+    <t xml:space="preserve">6.22636842727661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36062860488892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67253875732422</t>
   </si>
   <si>
     <t xml:space="preserve">5.55506038665771</t>
@@ -1193,25 +1193,25 @@
     <t xml:space="preserve">5.68932247161865</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62219190597534</t>
+    <t xml:space="preserve">5.62219095230103</t>
   </si>
   <si>
     <t xml:space="preserve">5.53827810287476</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43758201599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45436573028564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60540819168091</t>
+    <t xml:space="preserve">5.43758249282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45436477661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60540866851807</t>
   </si>
   <si>
     <t xml:space="preserve">5.52149534225464</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50471353530884</t>
+    <t xml:space="preserve">5.50471258163452</t>
   </si>
   <si>
     <t xml:space="preserve">5.4879298210144</t>
@@ -1220,13 +1220,13 @@
     <t xml:space="preserve">5.35366868972778</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3704514503479</t>
+    <t xml:space="preserve">5.37045097351074</t>
   </si>
   <si>
     <t xml:space="preserve">5.42079925537109</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28653860092163</t>
+    <t xml:space="preserve">5.28653812408447</t>
   </si>
   <si>
     <t xml:space="preserve">5.30332040786743</t>
@@ -1235,7 +1235,7 @@
     <t xml:space="preserve">5.26975584030151</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38723421096802</t>
+    <t xml:space="preserve">5.38723468780518</t>
   </si>
   <si>
     <t xml:space="preserve">5.32010364532471</t>
@@ -1250,28 +1250,28 @@
     <t xml:space="preserve">5.70610475540161</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72288656234741</t>
+    <t xml:space="preserve">5.72288751602173</t>
   </si>
   <si>
     <t xml:space="preserve">5.739670753479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6389741897583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57184410095215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18584156036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2026252746582</t>
+    <t xml:space="preserve">5.63897466659546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57184457778931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18584203720093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20262479782104</t>
   </si>
   <si>
     <t xml:space="preserve">5.21940803527832</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16906023025513</t>
+    <t xml:space="preserve">5.16905927658081</t>
   </si>
   <si>
     <t xml:space="preserve">5.13549327850342</t>
@@ -1283,49 +1283,49 @@
     <t xml:space="preserve">4.9508843421936</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03479814529419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15227651596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11871194839478</t>
+    <t xml:space="preserve">5.03479862213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15227699279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11871147155762</t>
   </si>
   <si>
     <t xml:space="preserve">5.06836318969727</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08514642715454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23618984222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25297260284424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33688688278198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79001808166504</t>
+    <t xml:space="preserve">5.0851469039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23619031906128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2529730796814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33688640594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79001760482788</t>
   </si>
   <si>
     <t xml:space="preserve">5.77323532104492</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58862638473511</t>
+    <t xml:space="preserve">5.58862590789795</t>
   </si>
   <si>
     <t xml:space="preserve">4.81662368774414</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79984092712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59844875335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36349201202393</t>
+    <t xml:space="preserve">4.79984140396118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59844827651978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36349153518677</t>
   </si>
   <si>
     <t xml:space="preserve">4.31314420700073</t>
@@ -1340,16 +1340,16 @@
     <t xml:space="preserve">4.02783870697021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17049026489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06979513168335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12014293670654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34670925140381</t>
+    <t xml:space="preserve">4.17049121856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06979608535767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12014245986938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34670877456665</t>
   </si>
   <si>
     <t xml:space="preserve">4.17888212203979</t>
@@ -1358,10 +1358,10 @@
     <t xml:space="preserve">4.04462099075317</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15370798110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26279640197754</t>
+    <t xml:space="preserve">4.15370845794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26279592514038</t>
   </si>
   <si>
     <t xml:space="preserve">4.16209983825684</t>
@@ -1370,58 +1370,58 @@
     <t xml:space="preserve">4.14531755447388</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99427247047424</t>
+    <t xml:space="preserve">3.99427318572998</t>
   </si>
   <si>
     <t xml:space="preserve">4.09496927261353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98588156700134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27957773208618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22922992706299</t>
+    <t xml:space="preserve">3.98588132858276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27957820892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22923040390015</t>
   </si>
   <si>
     <t xml:space="preserve">4.21244764328003</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03623008728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12877893447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16283082962036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07770204544067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00108432769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20539522171021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37565422058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21390867233276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22242116928101</t>
+    <t xml:space="preserve">4.03622961044312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1287784576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16283130645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07770109176636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00108480453491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20539569854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37565469741821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21390771865845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22242212295532</t>
   </si>
   <si>
     <t xml:space="preserve">4.25647354125977</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24796009063721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32457685470581</t>
+    <t xml:space="preserve">4.24795961380005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32457637786865</t>
   </si>
   <si>
     <t xml:space="preserve">4.30755043029785</t>
@@ -1442,13 +1442,13 @@
     <t xml:space="preserve">5.94203662872314</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8909592628479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73772621154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5504412651062</t>
+    <t xml:space="preserve">5.89095973968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73772573471069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55044078826904</t>
   </si>
   <si>
     <t xml:space="preserve">5.5844931602478</t>
@@ -1460,7 +1460,7 @@
     <t xml:space="preserve">5.41423416137695</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2610011100769</t>
+    <t xml:space="preserve">5.26100158691406</t>
   </si>
   <si>
     <t xml:space="preserve">5.48233795166016</t>
@@ -1469,19 +1469,19 @@
     <t xml:space="preserve">5.44828605651855</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6015191078186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66962242126465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51638984680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70367431640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32910490036011</t>
+    <t xml:space="preserve">5.60151863098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66962194442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5163893699646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70367479324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32910442352295</t>
   </si>
   <si>
     <t xml:space="preserve">5.27802658081055</t>
@@ -1490,13 +1490,13 @@
     <t xml:space="preserve">5.43126010894775</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31207847595215</t>
+    <t xml:space="preserve">5.31207799911499</t>
   </si>
   <si>
     <t xml:space="preserve">5.2269492149353</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00561189651489</t>
+    <t xml:space="preserve">5.00561285018921</t>
   </si>
   <si>
     <t xml:space="preserve">4.95453500747681</t>
@@ -1514,7 +1514,7 @@
     <t xml:space="preserve">4.97156095504761</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8864312171936</t>
+    <t xml:space="preserve">4.88643169403076</t>
   </si>
   <si>
     <t xml:space="preserve">5.02263879776001</t>
@@ -1523,10 +1523,10 @@
     <t xml:space="preserve">4.92048263549805</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9034571647644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.852379322052</t>
+    <t xml:space="preserve">4.90345764160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85237979888916</t>
   </si>
   <si>
     <t xml:space="preserve">4.8694052696228</t>
@@ -1538,16 +1538,16 @@
     <t xml:space="preserve">5.24397563934326</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36315679550171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38018321990967</t>
+    <t xml:space="preserve">5.36315631866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38018226623535</t>
   </si>
   <si>
     <t xml:space="preserve">5.2099232673645</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15884637832642</t>
+    <t xml:space="preserve">5.1588454246521</t>
   </si>
   <si>
     <t xml:space="preserve">5.10776805877686</t>
@@ -1559,13 +1559,13 @@
     <t xml:space="preserve">5.09074211120605</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19289779663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17587184906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1418194770813</t>
+    <t xml:space="preserve">5.19289684295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1758713722229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14181995391846</t>
   </si>
   <si>
     <t xml:space="preserve">5.07371616363525</t>
@@ -1589,10 +1589,10 @@
     <t xml:space="preserve">4.7842755317688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76725006103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8183274269104</t>
+    <t xml:space="preserve">4.767249584198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81832790374756</t>
   </si>
   <si>
     <t xml:space="preserve">4.80130195617676</t>
@@ -1601,46 +1601,46 @@
     <t xml:space="preserve">5.39720869064331</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61854457855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46531248092651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4993634223938</t>
+    <t xml:space="preserve">5.6185450553894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46531200408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49936389923096</t>
   </si>
   <si>
     <t xml:space="preserve">5.63557052612305</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68664884567261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65259695053101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8569073677063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87393379211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31660652160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33363199234009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29958057403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35065889358521</t>
+    <t xml:space="preserve">5.68664836883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65259647369385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85690784454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8739333152771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31660604476929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33363246917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2995810508728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35065793991089</t>
   </si>
   <si>
     <t xml:space="preserve">6.43578767776489</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55496883392334</t>
+    <t xml:space="preserve">6.55496788024902</t>
   </si>
   <si>
     <t xml:space="preserve">6.69117593765259</t>
@@ -1652,19 +1652,19 @@
     <t xml:space="preserve">7.15087509155273</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08277130126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87846088409424</t>
+    <t xml:space="preserve">7.08277082443237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8784613609314</t>
   </si>
   <si>
     <t xml:space="preserve">6.77630567550659</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84440946578979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70820283889771</t>
+    <t xml:space="preserve">6.84440898895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70820236206055</t>
   </si>
   <si>
     <t xml:space="preserve">6.75927972793579</t>
@@ -1676,34 +1676,34 @@
     <t xml:space="preserve">6.72522783279419</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65712404251099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91251277923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8954873085022</t>
+    <t xml:space="preserve">6.6571249961853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91251230239868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89548778533936</t>
   </si>
   <si>
     <t xml:space="preserve">6.96359014511108</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17302227020264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05085325241089</t>
+    <t xml:space="preserve">7.17302179336548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05085372924805</t>
   </si>
   <si>
     <t xml:space="preserve">7.1206636428833</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57443189620972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9758415222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02819919586182</t>
+    <t xml:space="preserve">7.57443284988403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97584199905396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0281982421875</t>
   </si>
   <si>
     <t xml:space="preserve">8.0631046295166</t>
@@ -1712,10 +1712,10 @@
     <t xml:space="preserve">7.99329423904419</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01074695587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94093799591064</t>
+    <t xml:space="preserve">8.0107479095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94093704223633</t>
   </si>
   <si>
     <t xml:space="preserve">8.13291454315186</t>
@@ -1727,19 +1727,19 @@
     <t xml:space="preserve">8.16782093048096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18527412414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34234619140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11546230316162</t>
+    <t xml:space="preserve">8.18527317047119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34234714508057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11546325683594</t>
   </si>
   <si>
     <t xml:space="preserve">8.25508308410645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08055877685547</t>
+    <t xml:space="preserve">8.08055686950684</t>
   </si>
   <si>
     <t xml:space="preserve">8.20272541046143</t>
@@ -1748,7 +1748,7 @@
     <t xml:space="preserve">7.95838928222656</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37725162506104</t>
+    <t xml:space="preserve">8.37725257873535</t>
   </si>
   <si>
     <t xml:space="preserve">8.32489395141602</t>
@@ -1757,7 +1757,7 @@
     <t xml:space="preserve">8.81356716156006</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58668327331543</t>
+    <t xml:space="preserve">8.58668231964111</t>
   </si>
   <si>
     <t xml:space="preserve">8.53432559967041</t>
@@ -1772,79 +1772,79 @@
     <t xml:space="preserve">8.72630405426025</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42961025238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28998851776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3074426651001</t>
+    <t xml:space="preserve">8.42960929870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28998947143555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30744171142578</t>
   </si>
   <si>
     <t xml:space="preserve">8.04565334320068</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85367393493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41215705871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22017860412598</t>
+    <t xml:space="preserve">7.85367345809937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41215801239014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22017765045166</t>
   </si>
   <si>
     <t xml:space="preserve">8.44706249237061</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3597993850708</t>
+    <t xml:space="preserve">8.35979843139648</t>
   </si>
   <si>
     <t xml:space="preserve">8.09800910949707</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23762989044189</t>
+    <t xml:space="preserve">8.23763084411621</t>
   </si>
   <si>
     <t xml:space="preserve">8.48196697235107</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6215877532959</t>
+    <t xml:space="preserve">8.62158870697021</t>
   </si>
   <si>
     <t xml:space="preserve">8.55177783966064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65649318695068</t>
+    <t xml:space="preserve">8.656494140625</t>
   </si>
   <si>
     <t xml:space="preserve">8.51687240600586</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46451473236084</t>
+    <t xml:space="preserve">8.46451377868652</t>
   </si>
   <si>
     <t xml:space="preserve">8.49942016601562</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56923007965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99161815643311</t>
+    <t xml:space="preserve">8.5692310333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99161720275879</t>
   </si>
   <si>
     <t xml:space="preserve">9.59893417358398</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77346038818359</t>
+    <t xml:space="preserve">9.77345943450928</t>
   </si>
   <si>
     <t xml:space="preserve">9.8170919418335</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29351425170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46804046630859</t>
+    <t xml:space="preserve">9.29351329803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46803951263428</t>
   </si>
   <si>
     <t xml:space="preserve">9.55530261993408</t>
@@ -1856,34 +1856,34 @@
     <t xml:space="preserve">9.9043550491333</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33714485168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94798564910889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8607234954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5151968002319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4279317855835</t>
+    <t xml:space="preserve">9.33714580535889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9479866027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86072254180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5151958465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4279327392578</t>
   </si>
   <si>
     <t xml:space="preserve">10.5588283538818</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6024580001831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8206167221069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7333545684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.776985168457</t>
+    <t xml:space="preserve">10.6024589538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8206157684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7333536148071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7769861221313</t>
   </si>
   <si>
     <t xml:space="preserve">10.2970390319824</t>
@@ -1892,22 +1892,22 @@
     <t xml:space="preserve">10.3843011856079</t>
   </si>
   <si>
-    <t xml:space="preserve">10.340669631958</t>
+    <t xml:space="preserve">10.3406705856323</t>
   </si>
   <si>
     <t xml:space="preserve">10.2097749710083</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2534074783325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0788803100586</t>
+    <t xml:space="preserve">10.2534065246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0788822174072</t>
   </si>
   <si>
     <t xml:space="preserve">9.51167106628418</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72982788085938</t>
+    <t xml:space="preserve">9.72982883453369</t>
   </si>
   <si>
     <t xml:space="preserve">9.68619823455811</t>
@@ -1919,10 +1919,10 @@
     <t xml:space="preserve">9.42440795898438</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6496152877808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5623531341553</t>
+    <t xml:space="preserve">11.6496162414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.562352180481</t>
   </si>
   <si>
     <t xml:space="preserve">11.7805099487305</t>
@@ -1931,22 +1931,22 @@
     <t xml:space="preserve">11.9114046096802</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9550352096558</t>
+    <t xml:space="preserve">11.9550361633301</t>
   </si>
   <si>
     <t xml:space="preserve">11.693247795105</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3040885925293</t>
+    <t xml:space="preserve">12.3040895462036</t>
   </si>
   <si>
     <t xml:space="preserve">12.2604570388794</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2168254852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3913516998291</t>
+    <t xml:space="preserve">12.2168245315552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3913507461548</t>
   </si>
   <si>
     <t xml:space="preserve">11.7368783950806</t>
@@ -1955,7 +1955,7 @@
     <t xml:space="preserve">11.8677730560303</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6059846878052</t>
+    <t xml:space="preserve">11.6059837341309</t>
   </si>
   <si>
     <t xml:space="preserve">10.9515113830566</t>
@@ -1964,61 +1964,61 @@
     <t xml:space="preserve">12.0422992706299</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3005628585815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3441953659058</t>
+    <t xml:space="preserve">11.3005638122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3441944122314</t>
   </si>
   <si>
     <t xml:space="preserve">10.9951429367065</t>
   </si>
   <si>
-    <t xml:space="preserve">10.471565246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9078788757324</t>
+    <t xml:space="preserve">10.4715642929077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9078807830811</t>
   </si>
   <si>
     <t xml:space="preserve">11.4314584732056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0387744903564</t>
+    <t xml:space="preserve">11.0387735366821</t>
   </si>
   <si>
     <t xml:space="preserve">11.9899406433105</t>
   </si>
   <si>
-    <t xml:space="preserve">11.74560546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5361738204956</t>
+    <t xml:space="preserve">11.7456045150757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5361728668213</t>
   </si>
   <si>
     <t xml:space="preserve">11.5187215805054</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6234369277954</t>
+    <t xml:space="preserve">11.6234359741211</t>
   </si>
   <si>
     <t xml:space="preserve">11.4489107131958</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6408891677856</t>
+    <t xml:space="preserve">11.64089012146</t>
   </si>
   <si>
     <t xml:space="preserve">11.7281513214111</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9201316833496</t>
+    <t xml:space="preserve">11.9201307296753</t>
   </si>
   <si>
     <t xml:space="preserve">11.1173105239868</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0998601913452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8031635284424</t>
+    <t xml:space="preserve">11.0998582839966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8031644821167</t>
   </si>
   <si>
     <t xml:space="preserve">10.7508068084717</t>
@@ -2036,7 +2036,7 @@
     <t xml:space="preserve">9.69297409057617</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7108907699585</t>
+    <t xml:space="preserve">9.71089172363281</t>
   </si>
   <si>
     <t xml:space="preserve">10.1408929824829</t>
@@ -2054,7 +2054,7 @@
     <t xml:space="preserve">10.1588106155396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0692262649536</t>
+    <t xml:space="preserve">10.0692253112793</t>
   </si>
   <si>
     <t xml:space="preserve">10.0871438980103</t>
@@ -2063,13 +2063,13 @@
     <t xml:space="preserve">10.4633951187134</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7858982086182</t>
+    <t xml:space="preserve">10.7858972549438</t>
   </si>
   <si>
     <t xml:space="preserve">10.5708961486816</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7142295837402</t>
+    <t xml:space="preserve">10.7142305374146</t>
   </si>
   <si>
     <t xml:space="preserve">10.7500638961792</t>
@@ -2087,13 +2087,13 @@
     <t xml:space="preserve">10.5888118743896</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5171451568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8575649261475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9113149642944</t>
+    <t xml:space="preserve">10.5171461105347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8575639724731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9113159179688</t>
   </si>
   <si>
     <t xml:space="preserve">10.6067295074463</t>
@@ -2102,7 +2102,7 @@
     <t xml:space="preserve">10.6604795455933</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3021450042725</t>
+    <t xml:space="preserve">10.3021440505981</t>
   </si>
   <si>
     <t xml:space="preserve">10.4096450805664</t>
@@ -2111,7 +2111,7 @@
     <t xml:space="preserve">10.3558940887451</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6783962249756</t>
+    <t xml:space="preserve">10.6783971786499</t>
   </si>
   <si>
     <t xml:space="preserve">10.4275617599487</t>
@@ -2120,16 +2120,16 @@
     <t xml:space="preserve">10.535062789917</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1800661087036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9829816818237</t>
+    <t xml:space="preserve">11.1800651550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9829807281494</t>
   </si>
   <si>
     <t xml:space="preserve">11.4846515655518</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3771505355835</t>
+    <t xml:space="preserve">11.3771514892578</t>
   </si>
   <si>
     <t xml:space="preserve">11.7354869842529</t>
@@ -2141,7 +2141,7 @@
     <t xml:space="preserve">11.9325704574585</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0221538543701</t>
+    <t xml:space="preserve">12.0221548080444</t>
   </si>
   <si>
     <t xml:space="preserve">11.8788204193115</t>
@@ -2159,7 +2159,7 @@
     <t xml:space="preserve">12.0938215255737</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3984069824219</t>
+    <t xml:space="preserve">12.3984079360962</t>
   </si>
   <si>
     <t xml:space="preserve">12.201322555542</t>
@@ -2177,7 +2177,7 @@
     <t xml:space="preserve">12.8463258743286</t>
   </si>
   <si>
-    <t xml:space="preserve">12.810492515564</t>
+    <t xml:space="preserve">12.8104934692383</t>
   </si>
   <si>
     <t xml:space="preserve">12.9179935455322</t>
@@ -2186,16 +2186,16 @@
     <t xml:space="preserve">13.258412361145</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4017467498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4375791549683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6884136199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.903416633606</t>
+    <t xml:space="preserve">13.4017457962036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4375801086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6884145736694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9034156799316</t>
   </si>
   <si>
     <t xml:space="preserve">14.6559200286865</t>
@@ -2204,91 +2204,91 @@
     <t xml:space="preserve">14.2438344955444</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6380033493042</t>
+    <t xml:space="preserve">14.6380043029785</t>
   </si>
   <si>
     <t xml:space="preserve">14.92467212677</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5125865936279</t>
+    <t xml:space="preserve">14.5125875473022</t>
   </si>
   <si>
     <t xml:space="preserve">14.5663366317749</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7992544174194</t>
+    <t xml:space="preserve">14.7992553710938</t>
   </si>
   <si>
     <t xml:space="preserve">14.5484189987183</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4946699142456</t>
+    <t xml:space="preserve">14.4946689605713</t>
   </si>
   <si>
     <t xml:space="preserve">14.2617511749268</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8888387680054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8171720504761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3871688842773</t>
+    <t xml:space="preserve">14.8888397216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8171730041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.387167930603</t>
   </si>
   <si>
     <t xml:space="preserve">14.7634201049805</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6200866699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9067544937134</t>
+    <t xml:space="preserve">14.6200857162476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9067535400391</t>
   </si>
   <si>
     <t xml:space="preserve">15.1217546463013</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0321731567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7455043792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.050087928772</t>
+    <t xml:space="preserve">15.032172203064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7455034255981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0500888824463</t>
   </si>
   <si>
     <t xml:space="preserve">15.0680055618286</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1038408279419</t>
+    <t xml:space="preserve">15.1038398742676</t>
   </si>
   <si>
     <t xml:space="preserve">14.5305023193359</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7096710205078</t>
+    <t xml:space="preserve">14.7096700668335</t>
   </si>
   <si>
     <t xml:space="preserve">14.2080001831055</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6167469024658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5092468261719</t>
+    <t xml:space="preserve">13.6167478561401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5092458724976</t>
   </si>
   <si>
     <t xml:space="preserve">13.0434112548828</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1688280105591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9717426300049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4700746536255</t>
+    <t xml:space="preserve">13.1688270568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9717435836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4700736999512</t>
   </si>
   <si>
     <t xml:space="preserve">13.2404947280884</t>
@@ -2306,22 +2306,22 @@
     <t xml:space="preserve">13.4913301467896</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2225780487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2046604156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0613269805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0075778961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6313247680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0971603393555</t>
+    <t xml:space="preserve">13.2225790023804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2046613693237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0613279342651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0075769424438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6313257217407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0971612930298</t>
   </si>
   <si>
     <t xml:space="preserve">13.0792446136475</t>
@@ -2336,7 +2336,7 @@
     <t xml:space="preserve">12.9538269042969</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7209091186523</t>
+    <t xml:space="preserve">12.720908164978</t>
   </si>
   <si>
     <t xml:space="preserve">12.5596580505371</t>
@@ -2351,7 +2351,7 @@
     <t xml:space="preserve">13.5271635055542</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3479948043823</t>
+    <t xml:space="preserve">13.3479957580566</t>
   </si>
   <si>
     <t xml:space="preserve">13.276328086853</t>
@@ -2360,22 +2360,22 @@
     <t xml:space="preserve">12.7925758361816</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5954923629761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5238237380981</t>
+    <t xml:space="preserve">12.5954914093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5238246917725</t>
   </si>
   <si>
     <t xml:space="preserve">12.5059070587158</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4879894256592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3088226318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5417413711548</t>
+    <t xml:space="preserve">12.4879903793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3088216781616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5417404174805</t>
   </si>
   <si>
     <t xml:space="preserve">12.8284091949463</t>
@@ -2399,10 +2399,10 @@
     <t xml:space="preserve">12.4342403411865</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9504871368408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2192401885986</t>
+    <t xml:space="preserve">11.9504880905151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2192392349243</t>
   </si>
   <si>
     <t xml:space="preserve">11.8250703811646</t>
@@ -2411,10 +2411,10 @@
     <t xml:space="preserve">12.1117391586304</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9684047698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0400714874268</t>
+    <t xml:space="preserve">11.9684038162231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0400705337524</t>
   </si>
   <si>
     <t xml:space="preserve">12.0042381286621</t>
@@ -2423,7 +2423,7 @@
     <t xml:space="preserve">12.255072593689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7388248443604</t>
+    <t xml:space="preserve">12.7388257980347</t>
   </si>
   <si>
     <t xml:space="preserve">13.7421646118164</t>
@@ -2435,7 +2435,7 @@
     <t xml:space="preserve">14.0825834274292</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0109167098999</t>
+    <t xml:space="preserve">14.0109176635742</t>
   </si>
   <si>
     <t xml:space="preserve">13.7242479324341</t>
@@ -2444,10 +2444,10 @@
     <t xml:space="preserve">14.0467500686646</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0646657943726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9392490386963</t>
+    <t xml:space="preserve">14.0646667480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9392499923706</t>
   </si>
   <si>
     <t xml:space="preserve">13.6346645355225</t>
@@ -2462,7 +2462,7 @@
     <t xml:space="preserve">13.9571657180786</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8496646881104</t>
+    <t xml:space="preserve">13.8496656417847</t>
   </si>
   <si>
     <t xml:space="preserve">13.9750833511353</t>
@@ -2477,31 +2477,31 @@
     <t xml:space="preserve">13.1867456436157</t>
   </si>
   <si>
-    <t xml:space="preserve">13.383828163147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5988302230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.70299243927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8429870605469</t>
+    <t xml:space="preserve">13.3838291168213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5988311767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7029914855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8429861068726</t>
   </si>
   <si>
     <t xml:space="preserve">11.7892360687256</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6817359924316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0759048461914</t>
+    <t xml:space="preserve">11.6817350387573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0759038925171</t>
   </si>
   <si>
     <t xml:space="preserve">11.5742359161377</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2159004211426</t>
+    <t xml:space="preserve">11.2158994674683</t>
   </si>
   <si>
     <t xml:space="preserve">11.3592348098755</t>
@@ -2510,7 +2510,7 @@
     <t xml:space="preserve">11.4309015274048</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3054828643799</t>
+    <t xml:space="preserve">11.3054838180542</t>
   </si>
   <si>
     <t xml:space="preserve">11.2875671386719</t>
@@ -69719,7 +69719,7 @@
     </row>
     <row r="2533">
       <c r="A2533" s="1" t="n">
-        <v>46006.6911458333</v>
+        <v>46006.3333333333</v>
       </c>
       <c r="B2533" t="n">
         <v>31403</v>
@@ -69740,6 +69740,32 @@
         <v>1178</v>
       </c>
       <c r="H2533" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2534">
+      <c r="A2534" s="1" t="n">
+        <v>46007.6912615741</v>
+      </c>
+      <c r="B2534" t="n">
+        <v>47016</v>
+      </c>
+      <c r="C2534" t="n">
+        <v>17.9599990844727</v>
+      </c>
+      <c r="D2534" t="n">
+        <v>17.4400005340576</v>
+      </c>
+      <c r="E2534" t="n">
+        <v>17.5599994659424</v>
+      </c>
+      <c r="F2534" t="n">
+        <v>17.7600002288818</v>
+      </c>
+      <c r="G2534" t="s">
+        <v>1172</v>
+      </c>
+      <c r="H2534" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ORS.MI.xlsx
+++ b/data/ORS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1179" uniqueCount="1179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="1180">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,40 +44,40 @@
     <t xml:space="preserve">ORS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98275852203369</t>
+    <t xml:space="preserve">7.98276090621948</t>
   </si>
   <si>
     <t xml:space="preserve">8.06380176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94223642349243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8247241973877</t>
+    <t xml:space="preserve">7.94223594665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82472562789917</t>
   </si>
   <si>
     <t xml:space="preserve">7.93818521499634</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90171527862549</t>
+    <t xml:space="preserve">7.90171432495117</t>
   </si>
   <si>
     <t xml:space="preserve">8.03948974609375</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92602872848511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86119413375854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82067203521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93413305282593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02328205108643</t>
+    <t xml:space="preserve">7.92602968215942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86119508743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8206729888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93413352966309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02328109741211</t>
   </si>
   <si>
     <t xml:space="preserve">8.08811473846436</t>
@@ -86,37 +86,37 @@
     <t xml:space="preserve">8.14484596252441</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69910621643066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80446338653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97465419769287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01112651824951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01517677307129</t>
+    <t xml:space="preserve">7.69910669326782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80446434020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97465467453003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01112365722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01517581939697</t>
   </si>
   <si>
     <t xml:space="preserve">7.79230737686157</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82877731323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34745216369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84093332290649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90982055664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85714197158813</t>
+    <t xml:space="preserve">7.82877826690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34745407104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84093379974365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90982103347778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85714244842529</t>
   </si>
   <si>
     <t xml:space="preserve">7.78015089035034</t>
@@ -125,13 +125,13 @@
     <t xml:space="preserve">7.8449854850769</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97870826721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88550758361816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95034122467041</t>
+    <t xml:space="preserve">7.9787073135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88550662994385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95034217834473</t>
   </si>
   <si>
     <t xml:space="preserve">8.00301933288574</t>
@@ -143,64 +143,64 @@
     <t xml:space="preserve">7.91792440414429</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10027313232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.104323387146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1853666305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20157527923584</t>
+    <t xml:space="preserve">8.1002721786499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10432243347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18536758422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20157623291016</t>
   </si>
   <si>
     <t xml:space="preserve">8.11242866516113</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07595825195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03138637542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09621906280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1772632598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05569744110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12053298950195</t>
+    <t xml:space="preserve">8.07595920562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03138542175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09622097015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17726135253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05569839477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12053203582764</t>
   </si>
   <si>
     <t xml:space="preserve">8.25830554962158</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42039108276367</t>
+    <t xml:space="preserve">8.4203929901123</t>
   </si>
   <si>
     <t xml:space="preserve">8.67162609100342</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55816555023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42849731445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52429103851318</t>
+    <t xml:space="preserve">8.55816650390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42849636077881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52429008483887</t>
   </si>
   <si>
     <t xml:space="preserve">8.45921897888184</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50802135467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60562801361084</t>
+    <t xml:space="preserve">8.50802230834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60562705993652</t>
   </si>
   <si>
     <t xml:space="preserve">8.5324239730835</t>
@@ -212,40 +212,40 @@
     <t xml:space="preserve">8.67069911956787</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87404632568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79270648956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90658187866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86591339111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94725131988525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93911743164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78457164764404</t>
+    <t xml:space="preserve">8.87404537200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7927074432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90657997131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86591243743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94725036621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93911647796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78457355499268</t>
   </si>
   <si>
     <t xml:space="preserve">8.74390411376953</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91471385955811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92284965515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1099271774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07739353179932</t>
+    <t xml:space="preserve">8.91471481323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92284870147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10992813110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.077392578125</t>
   </si>
   <si>
     <t xml:space="preserve">9.11806201934814</t>
@@ -254,19 +254,19 @@
     <t xml:space="preserve">9.13432884216309</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15059852600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15873241424561</t>
+    <t xml:space="preserve">9.15059757232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15873146057129</t>
   </si>
   <si>
     <t xml:space="preserve">8.7357702255249</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6788330078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8577766418457</t>
+    <t xml:space="preserve">8.67883205413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85777759552002</t>
   </si>
   <si>
     <t xml:space="preserve">8.72763538360596</t>
@@ -275,13 +275,13 @@
     <t xml:space="preserve">8.70323467254639</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66256713867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69510173797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62189674377441</t>
+    <t xml:space="preserve">8.66256618499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69510078430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6218957901001</t>
   </si>
   <si>
     <t xml:space="preserve">8.80084133148193</t>
@@ -290,19 +290,19 @@
     <t xml:space="preserve">8.77643966674805</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68696784973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54869174957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54055690765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58122825622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46735382080078</t>
+    <t xml:space="preserve">8.68696594238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54869079589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54055595397949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58122730255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46735286712646</t>
   </si>
   <si>
     <t xml:space="preserve">8.51615619659424</t>
@@ -311,22 +311,22 @@
     <t xml:space="preserve">8.49988746643066</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45108413696289</t>
+    <t xml:space="preserve">8.45108509063721</t>
   </si>
   <si>
     <t xml:space="preserve">8.63003063201904</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80897617340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89031410217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.930983543396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96351718902588</t>
+    <t xml:space="preserve">8.80897426605225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89031505584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93098449707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9635181427002</t>
   </si>
   <si>
     <t xml:space="preserve">9.05299091339111</t>
@@ -335,37 +335,37 @@
     <t xml:space="preserve">9.30514144897461</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10179424285889</t>
+    <t xml:space="preserve">9.10179328918457</t>
   </si>
   <si>
     <t xml:space="preserve">9.19126605987549</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35394287109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47595310211182</t>
+    <t xml:space="preserve">9.35394382476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4759521484375</t>
   </si>
   <si>
     <t xml:space="preserve">9.54915618896484</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58982563018799</t>
+    <t xml:space="preserve">9.58982467651367</t>
   </si>
   <si>
     <t xml:space="preserve">9.66303062438965</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71996784210205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85824203491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0046539306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2405338287354</t>
+    <t xml:space="preserve">9.71996688842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85824394226074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0046529769897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2405347824097</t>
   </si>
   <si>
     <t xml:space="preserve">10.24866771698</t>
@@ -374,61 +374,61 @@
     <t xml:space="preserve">10.3381414413452</t>
   </si>
   <si>
-    <t xml:space="preserve">10.598424911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4276142120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4032125473022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5252208709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4601488113403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5658893585205</t>
+    <t xml:space="preserve">10.5984258651733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4276151657104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4032115936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.525218963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4601497650146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5658903121948</t>
   </si>
   <si>
     <t xml:space="preserve">10.5821571350098</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7773714065552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9807176589966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8749761581421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6553621292114</t>
+    <t xml:space="preserve">10.7773694992065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9807167053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8749771118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6553640365601</t>
   </si>
   <si>
     <t xml:space="preserve">10.6797637939453</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5740232467651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5170860290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5414896011353</t>
+    <t xml:space="preserve">10.5740242004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5170879364014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5414876937866</t>
   </si>
   <si>
     <t xml:space="preserve">10.5577564239502</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5089530944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.818039894104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6878986358643</t>
+    <t xml:space="preserve">10.5089521408081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8180389404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6878967285156</t>
   </si>
   <si>
     <t xml:space="preserve">10.761100769043</t>
@@ -437,7 +437,7 @@
     <t xml:space="preserve">10.6472282409668</t>
   </si>
   <si>
-    <t xml:space="preserve">10.899377822876</t>
+    <t xml:space="preserve">10.8993787765503</t>
   </si>
   <si>
     <t xml:space="preserve">10.883111000061</t>
@@ -446,7 +446,7 @@
     <t xml:space="preserve">10.6716289520264</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7367010116577</t>
+    <t xml:space="preserve">10.736701965332</t>
   </si>
   <si>
     <t xml:space="preserve">11.0051193237305</t>
@@ -455,7 +455,7 @@
     <t xml:space="preserve">11.0213871002197</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1840629577637</t>
+    <t xml:space="preserve">11.1840648651123</t>
   </si>
   <si>
     <t xml:space="preserve">11.4036779403687</t>
@@ -464,10 +464,10 @@
     <t xml:space="preserve">11.3955430984497</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3386077880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.322338104248</t>
+    <t xml:space="preserve">11.3386068344116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3223400115967</t>
   </si>
   <si>
     <t xml:space="preserve">11.330472946167</t>
@@ -479,13 +479,13 @@
     <t xml:space="preserve">11.0783233642578</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6065607070923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8424406051636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8505744934082</t>
+    <t xml:space="preserve">10.6065587997437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8424415588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8505754470825</t>
   </si>
   <si>
     <t xml:space="preserve">10.6390943527222</t>
@@ -506,7 +506,7 @@
     <t xml:space="preserve">10.321873664856</t>
   </si>
   <si>
-    <t xml:space="preserve">10.370677947998</t>
+    <t xml:space="preserve">10.3706769943237</t>
   </si>
   <si>
     <t xml:space="preserve">10.3300075531006</t>
@@ -518,7 +518,7 @@
     <t xml:space="preserve">10.2568035125732</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1835975646973</t>
+    <t xml:space="preserve">10.1835985183716</t>
   </si>
   <si>
     <t xml:space="preserve">10.4845514297485</t>
@@ -533,25 +533,25 @@
     <t xml:space="preserve">10.8587083816528</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9237785339355</t>
+    <t xml:space="preserve">10.9237804412842</t>
   </si>
   <si>
     <t xml:space="preserve">11.0376539230347</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0620565414429</t>
+    <t xml:space="preserve">11.0620546340942</t>
   </si>
   <si>
     <t xml:space="preserve">11.1027250289917</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1433954238892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1759300231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1352596282959</t>
+    <t xml:space="preserve">11.1433944702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.175929069519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1352605819702</t>
   </si>
   <si>
     <t xml:space="preserve">11.0701894760132</t>
@@ -560,16 +560,16 @@
     <t xml:space="preserve">11.1189937591553</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1515283584595</t>
+    <t xml:space="preserve">11.1515274047852</t>
   </si>
   <si>
     <t xml:space="preserve">11.2247323989868</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0457878112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5008192062378</t>
+    <t xml:space="preserve">11.0457859039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5008182525635</t>
   </si>
   <si>
     <t xml:space="preserve">10.1347961425781</t>
@@ -578,43 +578,43 @@
     <t xml:space="preserve">8.36161136627197</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01999187469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10946273803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39414691925049</t>
+    <t xml:space="preserve">8.01998996734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10946369171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3941478729248</t>
   </si>
   <si>
     <t xml:space="preserve">8.21520328521729</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3372106552124</t>
+    <t xml:space="preserve">8.33720970153809</t>
   </si>
   <si>
     <t xml:space="preserve">8.3128080368042</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18266773223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34534549713135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23960494995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49175453186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58936023712158</t>
+    <t xml:space="preserve">8.18266677856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34534454345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23960399627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49175548553467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5893611907959</t>
   </si>
   <si>
     <t xml:space="preserve">8.76017189025879</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29654216766357</t>
+    <t xml:space="preserve">8.29654121398926</t>
   </si>
   <si>
     <t xml:space="preserve">8.25587177276611</t>
@@ -623,16 +623,16 @@
     <t xml:space="preserve">8.17453479766846</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19080066680908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23147010803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2802734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14199733734131</t>
+    <t xml:space="preserve">8.1908016204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23147106170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28027248382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14199829101562</t>
   </si>
   <si>
     <t xml:space="preserve">8.15826606750488</t>
@@ -641,91 +641,91 @@
     <t xml:space="preserve">8.16639995574951</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12166213989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05252456665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89798164367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85731172561646</t>
+    <t xml:space="preserve">8.12166404724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05252647399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89798259735107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85731315612793</t>
   </si>
   <si>
     <t xml:space="preserve">7.93051862716675</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9061164855957</t>
+    <t xml:space="preserve">7.90611553192139</t>
   </si>
   <si>
     <t xml:space="preserve">7.93865156173706</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84917974472046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80850982666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62956476211548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5726261138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48315620422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66616773605347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60516357421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54009342193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52382373809814</t>
+    <t xml:space="preserve">7.84918022155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.808509349823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62956523895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57262754440308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48315525054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66616725921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60516309738159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54009199142456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52382326126099</t>
   </si>
   <si>
     <t xml:space="preserve">7.47908735275269</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61329698562622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54822492599487</t>
+    <t xml:space="preserve">7.61329793930054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54822587966919</t>
   </si>
   <si>
     <t xml:space="preserve">7.56449365615845</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50755548477173</t>
+    <t xml:space="preserve">7.50755500793457</t>
   </si>
   <si>
     <t xml:space="preserve">7.4668869972229</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4912896156311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49942207336426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31234455108643</t>
+    <t xml:space="preserve">7.49128913879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4994215965271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31234550476074</t>
   </si>
   <si>
     <t xml:space="preserve">7.27980804443359</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37741565704346</t>
+    <t xml:space="preserve">7.37741470336914</t>
   </si>
   <si>
     <t xml:space="preserve">7.38554859161377</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3692798614502</t>
+    <t xml:space="preserve">7.36928033828735</t>
   </si>
   <si>
     <t xml:space="preserve">7.32047748565674</t>
@@ -734,70 +734,70 @@
     <t xml:space="preserve">7.34487962722778</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28794193267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04392528533936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15779972076416</t>
+    <t xml:space="preserve">7.28794145584106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04392623901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15780067443848</t>
   </si>
   <si>
     <t xml:space="preserve">7.39368295669556</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42621898651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40181636810303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3042106628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3611478805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20660400390625</t>
+    <t xml:space="preserve">7.42621850967407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40181684494019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30421018600464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36114740371704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20660352706909</t>
   </si>
   <si>
     <t xml:space="preserve">7.3530125617981</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33674669265747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27167510986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23100519180298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32861089706421</t>
+    <t xml:space="preserve">7.336745262146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27167463302612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23100423812866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32861185073853</t>
   </si>
   <si>
     <t xml:space="preserve">7.26354122161865</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23913908004761</t>
+    <t xml:space="preserve">7.23913860321045</t>
   </si>
   <si>
     <t xml:space="preserve">7.22287178039551</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24727249145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44248580932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25540637969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18220186233521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29607534408569</t>
+    <t xml:space="preserve">7.24727344512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44248628616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25540685653687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18220233917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29607582092285</t>
   </si>
   <si>
     <t xml:space="preserve">7.16593456268311</t>
@@ -806,19 +806,19 @@
     <t xml:space="preserve">7.14153289794922</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05206108093262</t>
+    <t xml:space="preserve">7.05206060409546</t>
   </si>
   <si>
     <t xml:space="preserve">7.07646226882935</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03579235076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0195255279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87311410903931</t>
+    <t xml:space="preserve">7.0357928276062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01952505111694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87311553955078</t>
   </si>
   <si>
     <t xml:space="preserve">6.67790269851685</t>
@@ -827,13 +827,13 @@
     <t xml:space="preserve">6.85124731063843</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93379163742065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26397275924683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14840936660767</t>
+    <t xml:space="preserve">6.93379211425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26397323608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14840984344482</t>
   </si>
   <si>
     <t xml:space="preserve">7.09888315200806</t>
@@ -845,37 +845,34 @@
     <t xml:space="preserve">7.16491889953613</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14015579223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21444606781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1731743812561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97506427764893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84299373626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60361194610596</t>
+    <t xml:space="preserve">7.14015626907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21444654464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17317390441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97506523132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84299278259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60361289978027</t>
   </si>
   <si>
     <t xml:space="preserve">6.62012100219727</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67790222167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80997514724731</t>
+    <t xml:space="preserve">6.80997467041016</t>
   </si>
   <si>
     <t xml:space="preserve">6.54583024978638</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31470394134521</t>
+    <t xml:space="preserve">6.31470346450806</t>
   </si>
   <si>
     <t xml:space="preserve">6.32295846939087</t>
@@ -887,19 +884,19 @@
     <t xml:space="preserve">6.38074016571045</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39724969863892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4715404510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28168535232544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22390365600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09183216094971</t>
+    <t xml:space="preserve">6.3972487449646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47153997421265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2816858291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22390413284302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09183120727539</t>
   </si>
   <si>
     <t xml:space="preserve">5.9019775390625</t>
@@ -908,40 +905,40 @@
     <t xml:space="preserve">5.95976066589355</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9927773475647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20739555358887</t>
+    <t xml:space="preserve">5.99277782440186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20739507675171</t>
   </si>
   <si>
     <t xml:space="preserve">6.14135980606079</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1908860206604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14961338043213</t>
+    <t xml:space="preserve">6.19088697433472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14961385726929</t>
   </si>
   <si>
     <t xml:space="preserve">6.0753231048584</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25692272186279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00928735733032</t>
+    <t xml:space="preserve">6.25692319869995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00928783416748</t>
   </si>
   <si>
     <t xml:space="preserve">5.9845232963562</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12485074996948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13310480117798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27343130111694</t>
+    <t xml:space="preserve">6.12485027313232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13310432434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2734317779541</t>
   </si>
   <si>
     <t xml:space="preserve">6.44677591323853</t>
@@ -953,13 +950,13 @@
     <t xml:space="preserve">6.51281213760376</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3642315864563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24041414260864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21565055847168</t>
+    <t xml:space="preserve">6.36423110961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24041366577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21565008163452</t>
   </si>
   <si>
     <t xml:space="preserve">6.23215961456299</t>
@@ -977,52 +974,52 @@
     <t xml:space="preserve">6.05055952072144</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89372444152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.778160572052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6956148147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79466962814331</t>
+    <t xml:space="preserve">5.89372396469116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77816104888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69561529159546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79466915130615</t>
   </si>
   <si>
     <t xml:space="preserve">5.80292367935181</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82768774032593</t>
+    <t xml:space="preserve">5.82768726348877</t>
   </si>
   <si>
     <t xml:space="preserve">5.78641510009766</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73688745498657</t>
+    <t xml:space="preserve">5.73688840866089</t>
   </si>
   <si>
     <t xml:space="preserve">5.85245084762573</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29819583892822</t>
+    <t xml:space="preserve">6.29819536209106</t>
   </si>
   <si>
     <t xml:space="preserve">6.18263244628906</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15786790847778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03404998779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08357763290405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81943321228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91848659515381</t>
+    <t xml:space="preserve">6.15786838531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03405094146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08357715606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81943368911743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91848707199097</t>
   </si>
   <si>
     <t xml:space="preserve">5.86070537567139</t>
@@ -1034,70 +1031,70 @@
     <t xml:space="preserve">5.75339698791504</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8111777305603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70386981964111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74514150619507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83594274520874</t>
+    <t xml:space="preserve">5.81117820739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70387029647827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74514293670654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83594179153442</t>
   </si>
   <si>
     <t xml:space="preserve">5.71212482452393</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84419631958008</t>
+    <t xml:space="preserve">5.84419679641724</t>
   </si>
   <si>
     <t xml:space="preserve">5.94325113296509</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96801424026489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87721490859985</t>
+    <t xml:space="preserve">5.96801471710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8772144317627</t>
   </si>
   <si>
     <t xml:space="preserve">5.88546943664551</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93499565124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02579641342163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0670690536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38899421691895</t>
+    <t xml:space="preserve">5.93499660491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02579593658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06706857681274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3889946937561</t>
   </si>
   <si>
     <t xml:space="preserve">6.19914102554321</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04230499267578</t>
+    <t xml:space="preserve">6.04230546951294</t>
   </si>
   <si>
     <t xml:space="preserve">6.05881404876709</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95150518417358</t>
+    <t xml:space="preserve">5.95150566101074</t>
   </si>
   <si>
     <t xml:space="preserve">6.17437744140625</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1760196685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29349756240845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25993204116821</t>
+    <t xml:space="preserve">6.17601919174194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29349851608276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25993251800537</t>
   </si>
   <si>
     <t xml:space="preserve">6.20958423614502</t>
@@ -1106,10 +1103,13 @@
     <t xml:space="preserve">6.09210586547852</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10888862609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14245367050171</t>
+    <t xml:space="preserve">6.10888957977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07532358169556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14245414733887</t>
   </si>
   <si>
     <t xml:space="preserve">6.0585412979126</t>
@@ -1118,10 +1118,10 @@
     <t xml:space="preserve">6.02497529983521</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97462749481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95784473419189</t>
+    <t xml:space="preserve">5.97462701797485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95784425735474</t>
   </si>
   <si>
     <t xml:space="preserve">6.15923643112183</t>
@@ -1130,22 +1130,22 @@
     <t xml:space="preserve">6.12567138671875</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19280195236206</t>
+    <t xml:space="preserve">6.19280099868774</t>
   </si>
   <si>
     <t xml:space="preserve">6.42775917053223</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71306467056274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64593458175659</t>
+    <t xml:space="preserve">6.7130651473999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64593410491943</t>
   </si>
   <si>
     <t xml:space="preserve">6.69628190994263</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78019571304321</t>
+    <t xml:space="preserve">6.78019523620605</t>
   </si>
   <si>
     <t xml:space="preserve">6.7298469543457</t>
@@ -1154,10 +1154,10 @@
     <t xml:space="preserve">6.62915086746216</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56201982498169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54523801803589</t>
+    <t xml:space="preserve">6.56202030181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54523754119873</t>
   </si>
   <si>
     <t xml:space="preserve">6.67949914932251</t>
@@ -1178,13 +1178,13 @@
     <t xml:space="preserve">6.22636747360229</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36062860488892</t>
+    <t xml:space="preserve">6.36062908172607</t>
   </si>
   <si>
     <t xml:space="preserve">5.67253923416138</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55505990982056</t>
+    <t xml:space="preserve">5.55506038665771</t>
   </si>
   <si>
     <t xml:space="preserve">5.68932247161865</t>
@@ -1196,7 +1196,7 @@
     <t xml:space="preserve">5.53827810287476</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43758249282837</t>
+    <t xml:space="preserve">5.43758201599121</t>
   </si>
   <si>
     <t xml:space="preserve">5.45436525344849</t>
@@ -1205,19 +1205,19 @@
     <t xml:space="preserve">5.60540866851807</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52149534225464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50471305847168</t>
+    <t xml:space="preserve">5.5214958190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50471258163452</t>
   </si>
   <si>
     <t xml:space="preserve">5.4879298210144</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35366916656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37045097351074</t>
+    <t xml:space="preserve">5.35366821289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3704514503479</t>
   </si>
   <si>
     <t xml:space="preserve">5.42079973220825</t>
@@ -1226,40 +1226,40 @@
     <t xml:space="preserve">5.28653812408447</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30332040786743</t>
+    <t xml:space="preserve">5.30332088470459</t>
   </si>
   <si>
     <t xml:space="preserve">5.26975584030151</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38723421096802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32010364532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65575647354126</t>
+    <t xml:space="preserve">5.38723468780518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32010316848755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65575695037842</t>
   </si>
   <si>
     <t xml:space="preserve">5.75645303726196</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70610475540161</t>
+    <t xml:space="preserve">5.70610427856445</t>
   </si>
   <si>
     <t xml:space="preserve">5.72288703918457</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73967027664185</t>
+    <t xml:space="preserve">5.73966979980469</t>
   </si>
   <si>
     <t xml:space="preserve">5.63897466659546</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57184362411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18584203720093</t>
+    <t xml:space="preserve">5.57184410095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18584251403809</t>
   </si>
   <si>
     <t xml:space="preserve">5.20262479782104</t>
@@ -1268,31 +1268,31 @@
     <t xml:space="preserve">5.21940803527832</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16905927658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13549423217773</t>
+    <t xml:space="preserve">5.16905975341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13549375534058</t>
   </si>
   <si>
     <t xml:space="preserve">5.10192918777466</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95088481903076</t>
+    <t xml:space="preserve">4.95088529586792</t>
   </si>
   <si>
     <t xml:space="preserve">5.03479862213135</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15227651596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11871099472046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06836366653442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08514595031738</t>
+    <t xml:space="preserve">5.15227699279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11871147155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06836318969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08514642715454</t>
   </si>
   <si>
     <t xml:space="preserve">5.23619031906128</t>
@@ -1304,10 +1304,10 @@
     <t xml:space="preserve">5.33688640594482</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79001760482788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77323532104492</t>
+    <t xml:space="preserve">5.79001808166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77323484420776</t>
   </si>
   <si>
     <t xml:space="preserve">5.58862638473511</t>
@@ -1316,7 +1316,7 @@
     <t xml:space="preserve">4.81662368774414</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79984092712402</t>
+    <t xml:space="preserve">4.79984140396118</t>
   </si>
   <si>
     <t xml:space="preserve">4.59844827651978</t>
@@ -1331,55 +1331,55 @@
     <t xml:space="preserve">4.19566535949707</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11175155639648</t>
+    <t xml:space="preserve">4.11175203323364</t>
   </si>
   <si>
     <t xml:space="preserve">4.02783870697021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17049121856689</t>
+    <t xml:space="preserve">4.17049074172974</t>
   </si>
   <si>
     <t xml:space="preserve">4.06979560852051</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12014245986938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34670829772949</t>
+    <t xml:space="preserve">4.1201434135437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34670925140381</t>
   </si>
   <si>
     <t xml:space="preserve">4.17888164520264</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04462146759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15370845794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2627968788147</t>
+    <t xml:space="preserve">4.04462099075317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15370893478394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26279592514038</t>
   </si>
   <si>
     <t xml:space="preserve">4.16209983825684</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14531707763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9942729473114</t>
+    <t xml:space="preserve">4.14531803131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99427270889282</t>
   </si>
   <si>
     <t xml:space="preserve">4.09496927261353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98588180541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2795786857605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22923040390015</t>
+    <t xml:space="preserve">3.98588132858276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27957820892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22922992706299</t>
   </si>
   <si>
     <t xml:space="preserve">4.21244764328003</t>
@@ -1391,19 +1391,19 @@
     <t xml:space="preserve">4.12877893447876</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16283082962036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07770204544067</t>
+    <t xml:space="preserve">4.16283130645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07770156860352</t>
   </si>
   <si>
     <t xml:space="preserve">4.00108480453491</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20539522171021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37565469741821</t>
+    <t xml:space="preserve">4.20539617538452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37565422058105</t>
   </si>
   <si>
     <t xml:space="preserve">4.21390867233276</t>
@@ -1418,13 +1418,13 @@
     <t xml:space="preserve">4.24796009063721</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32457685470581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30755043029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23944759368896</t>
+    <t xml:space="preserve">4.32457637786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30755090713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23944711685181</t>
   </si>
   <si>
     <t xml:space="preserve">4.35862874984741</t>
@@ -1433,19 +1433,19 @@
     <t xml:space="preserve">4.51186180114746</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5334153175354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9420371055603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8909592628479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73772573471069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5504412651062</t>
+    <t xml:space="preserve">5.53341484069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94203662872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89095973968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73772525787354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55044078826904</t>
   </si>
   <si>
     <t xml:space="preserve">5.58449268341064</t>
@@ -1472,19 +1472,19 @@
     <t xml:space="preserve">5.66962289810181</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51638889312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70367383956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32910490036011</t>
+    <t xml:space="preserve">5.5163893699646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70367479324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32910442352295</t>
   </si>
   <si>
     <t xml:space="preserve">5.27802705764771</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43126010894775</t>
+    <t xml:space="preserve">5.43126058578491</t>
   </si>
   <si>
     <t xml:space="preserve">5.31207799911499</t>
@@ -1493,7 +1493,7 @@
     <t xml:space="preserve">5.2269492149353</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00561237335205</t>
+    <t xml:space="preserve">5.00561285018921</t>
   </si>
   <si>
     <t xml:space="preserve">4.95453500747681</t>
@@ -1505,49 +1505,49 @@
     <t xml:space="preserve">5.05669069290161</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03966426849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97156143188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88643169403076</t>
+    <t xml:space="preserve">5.03966474533081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97156095504761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8864312171936</t>
   </si>
   <si>
     <t xml:space="preserve">5.02263879776001</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92048358917236</t>
+    <t xml:space="preserve">4.92048263549805</t>
   </si>
   <si>
     <t xml:space="preserve">4.90345764160156</t>
   </si>
   <si>
-    <t xml:space="preserve">4.852379322052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86940479278564</t>
+    <t xml:space="preserve">4.85237979888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8694052696228</t>
   </si>
   <si>
     <t xml:space="preserve">5.34613037109375</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24397468566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36315679550171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38018226623535</t>
+    <t xml:space="preserve">5.24397563934326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36315631866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38018274307251</t>
   </si>
   <si>
     <t xml:space="preserve">5.2099232673645</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1588454246521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10776853561401</t>
+    <t xml:space="preserve">5.15884590148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10776805877686</t>
   </si>
   <si>
     <t xml:space="preserve">4.98858690261841</t>
@@ -1556,37 +1556,37 @@
     <t xml:space="preserve">5.09074211120605</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19289779663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17587089538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14181995391846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07371616363525</t>
+    <t xml:space="preserve">5.19289684295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1758713722229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1418194770813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07371664047241</t>
   </si>
   <si>
     <t xml:space="preserve">4.68212080001831</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54591369628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59699153900146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57996511459351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63104295730591</t>
+    <t xml:space="preserve">4.5459132194519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59699106216431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57996559143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63104343414307</t>
   </si>
   <si>
     <t xml:space="preserve">4.78427600860596</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76725006103516</t>
+    <t xml:space="preserve">4.767249584198</t>
   </si>
   <si>
     <t xml:space="preserve">4.81832790374756</t>
@@ -1595,7 +1595,7 @@
     <t xml:space="preserve">4.80130195617676</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39720773696899</t>
+    <t xml:space="preserve">5.39720821380615</t>
   </si>
   <si>
     <t xml:space="preserve">5.61854457855225</t>
@@ -1607,10 +1607,10 @@
     <t xml:space="preserve">5.49936389923096</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63557100296021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68664789199829</t>
+    <t xml:space="preserve">5.63557052612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68664836883545</t>
   </si>
   <si>
     <t xml:space="preserve">5.65259695053101</t>
@@ -1619,7 +1619,7 @@
     <t xml:space="preserve">5.8569073677063</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87393283843994</t>
+    <t xml:space="preserve">5.8739333152771</t>
   </si>
   <si>
     <t xml:space="preserve">6.31660652160645</t>
@@ -1631,31 +1631,31 @@
     <t xml:space="preserve">6.2995810508728</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35065793991089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43578720092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55496883392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69117593765259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79333114624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15087413787842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08277130126953</t>
+    <t xml:space="preserve">6.35065841674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43578767776489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55496835708618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69117641448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79333162307739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15087509155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08277082443237</t>
   </si>
   <si>
     <t xml:space="preserve">6.87846088409424</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77630567550659</t>
+    <t xml:space="preserve">6.77630519866943</t>
   </si>
   <si>
     <t xml:space="preserve">6.84440946578979</t>
@@ -1667,13 +1667,13 @@
     <t xml:space="preserve">6.75927972793579</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5379433631897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72522783279419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65712404251099</t>
+    <t xml:space="preserve">6.53794288635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72522830963135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65712451934814</t>
   </si>
   <si>
     <t xml:space="preserve">6.91251230239868</t>
@@ -1688,19 +1688,19 @@
     <t xml:space="preserve">7.17302179336548</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05085372924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1206636428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57443189620972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9758415222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02820014953613</t>
+    <t xml:space="preserve">7.05085325241089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12066411972046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57443284988403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97584199905396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0281982421875</t>
   </si>
   <si>
     <t xml:space="preserve">8.0631046295166</t>
@@ -1709,61 +1709,61 @@
     <t xml:space="preserve">7.99329423904419</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0107479095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94093656539917</t>
+    <t xml:space="preserve">8.01074695587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94093704223633</t>
   </si>
   <si>
     <t xml:space="preserve">8.13291454315186</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15036773681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16781997680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18527317047119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34234714508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11546230316162</t>
+    <t xml:space="preserve">8.15036869049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16782093048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18527412414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34234619140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11546325683594</t>
   </si>
   <si>
     <t xml:space="preserve">8.25508308410645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08055686950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20272445678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95838832855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37725162506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32489395141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81356811523438</t>
+    <t xml:space="preserve">8.08055782318115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20272541046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95838928222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37725257873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3248929977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81356716156006</t>
   </si>
   <si>
     <t xml:space="preserve">8.58668327331543</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53432464599609</t>
+    <t xml:space="preserve">8.53432559967041</t>
   </si>
   <si>
     <t xml:space="preserve">8.69139862060547</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60413551330566</t>
+    <t xml:space="preserve">8.60413646697998</t>
   </si>
   <si>
     <t xml:space="preserve">8.72630405426025</t>
@@ -1778,49 +1778,49 @@
     <t xml:space="preserve">8.30744171142578</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04565143585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85367298126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41215705871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22017860412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44706249237061</t>
+    <t xml:space="preserve">8.04565238952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85367345809937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41215801239014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22017765045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44706153869629</t>
   </si>
   <si>
     <t xml:space="preserve">8.3597993850708</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09801006317139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23763179779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48196697235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6215877532959</t>
+    <t xml:space="preserve">8.09800910949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23763084411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48196792602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62158870697021</t>
   </si>
   <si>
     <t xml:space="preserve">8.55177783966064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65649318695068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51687335968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46451473236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49941921234131</t>
+    <t xml:space="preserve">8.656494140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51687240600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46451377868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49942016601562</t>
   </si>
   <si>
     <t xml:space="preserve">8.56923007965088</t>
@@ -1829,10 +1829,10 @@
     <t xml:space="preserve">9.99161720275879</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5989351272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77346038818359</t>
+    <t xml:space="preserve">9.59893417358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77345943450928</t>
   </si>
   <si>
     <t xml:space="preserve">9.8170919418335</t>
@@ -1841,25 +1841,25 @@
     <t xml:space="preserve">9.29351329803467</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46803951263428</t>
+    <t xml:space="preserve">9.46804046630859</t>
   </si>
   <si>
     <t xml:space="preserve">9.55530261993408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6425666809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9043550491333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33714389801025</t>
+    <t xml:space="preserve">9.64256477355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90435600280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33714485168457</t>
   </si>
   <si>
     <t xml:space="preserve">9.9479866027832</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8607234954834</t>
+    <t xml:space="preserve">9.86072254180908</t>
   </si>
   <si>
     <t xml:space="preserve">10.5151958465576</t>
@@ -1871,13 +1871,13 @@
     <t xml:space="preserve">10.5588283538818</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6024589538574</t>
+    <t xml:space="preserve">10.6024580001831</t>
   </si>
   <si>
     <t xml:space="preserve">10.8206167221069</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7333545684814</t>
+    <t xml:space="preserve">10.7333536148071</t>
   </si>
   <si>
     <t xml:space="preserve">10.7769861221313</t>
@@ -1889,7 +1889,7 @@
     <t xml:space="preserve">10.3843011856079</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3406705856323</t>
+    <t xml:space="preserve">10.3406715393066</t>
   </si>
   <si>
     <t xml:space="preserve">10.2097749710083</t>
@@ -1901,13 +1901,13 @@
     <t xml:space="preserve">10.0788812637329</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51167011260986</t>
+    <t xml:space="preserve">9.51167106628418</t>
   </si>
   <si>
     <t xml:space="preserve">9.72982883453369</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68619728088379</t>
+    <t xml:space="preserve">9.68619823455811</t>
   </si>
   <si>
     <t xml:space="preserve">8.98809337615967</t>
@@ -1916,31 +1916,31 @@
     <t xml:space="preserve">9.42440795898438</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6496171951294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.562352180481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7805109024048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9114036560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9550352096558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6932468414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3040885925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2604570388794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2168254852295</t>
+    <t xml:space="preserve">11.6496162414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5623531341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7805099487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9114046096802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9550361633301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.693247795105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3040895462036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2604560852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2168245315552</t>
   </si>
   <si>
     <t xml:space="preserve">12.3913507461548</t>
@@ -1952,19 +1952,19 @@
     <t xml:space="preserve">11.8677730560303</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6059846878052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9515104293823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0422983169556</t>
+    <t xml:space="preserve">11.6059837341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9515113830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0422992706299</t>
   </si>
   <si>
     <t xml:space="preserve">11.3005638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3441953659058</t>
+    <t xml:space="preserve">11.3441944122314</t>
   </si>
   <si>
     <t xml:space="preserve">10.9951429367065</t>
@@ -1979,7 +1979,7 @@
     <t xml:space="preserve">11.4314584732056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0387725830078</t>
+    <t xml:space="preserve">11.0387735366821</t>
   </si>
   <si>
     <t xml:space="preserve">11.9899415969849</t>
@@ -1988,40 +1988,40 @@
     <t xml:space="preserve">11.7456045150757</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5361728668213</t>
+    <t xml:space="preserve">11.5361738204956</t>
   </si>
   <si>
     <t xml:space="preserve">11.5187206268311</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6234359741211</t>
+    <t xml:space="preserve">11.6234369277954</t>
   </si>
   <si>
     <t xml:space="preserve">11.4489107131958</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6408891677856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7281522750854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9201316833496</t>
+    <t xml:space="preserve">11.64089012146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7281513214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.920129776001</t>
   </si>
   <si>
     <t xml:space="preserve">11.1173105239868</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0998582839966</t>
+    <t xml:space="preserve">11.0998592376709</t>
   </si>
   <si>
     <t xml:space="preserve">10.8031644821167</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7508058547974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3319435119629</t>
+    <t xml:space="preserve">10.7508068084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3319444656372</t>
   </si>
   <si>
     <t xml:space="preserve">10.1050596237183</t>
@@ -2033,10 +2033,10 @@
     <t xml:space="preserve">9.69297409057617</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7108907699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1408929824829</t>
+    <t xml:space="preserve">9.71089172363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1408939361572</t>
   </si>
   <si>
     <t xml:space="preserve">10.2663106918335</t>
@@ -2051,25 +2051,25 @@
     <t xml:space="preserve">10.1588106155396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0692253112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0871429443359</t>
+    <t xml:space="preserve">10.0692262649536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0871438980103</t>
   </si>
   <si>
     <t xml:space="preserve">10.4633951187134</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7858982086182</t>
+    <t xml:space="preserve">10.7858963012695</t>
   </si>
   <si>
     <t xml:space="preserve">10.5708961486816</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7142295837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7500638961792</t>
+    <t xml:space="preserve">10.7142305374146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7500629425049</t>
   </si>
   <si>
     <t xml:space="preserve">11.1621494293213</t>
@@ -2078,22 +2078,22 @@
     <t xml:space="preserve">10.8754816055298</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6425619125366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5888118743896</t>
+    <t xml:space="preserve">10.6425638198853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.588812828064</t>
   </si>
   <si>
     <t xml:space="preserve">10.5171461105347</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8575649261475</t>
+    <t xml:space="preserve">10.8575639724731</t>
   </si>
   <si>
     <t xml:space="preserve">10.9113149642944</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6067295074463</t>
+    <t xml:space="preserve">10.6067304611206</t>
   </si>
   <si>
     <t xml:space="preserve">10.6604795455933</t>
@@ -2102,22 +2102,22 @@
     <t xml:space="preserve">10.3021440505981</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4096441268921</t>
+    <t xml:space="preserve">10.4096450805664</t>
   </si>
   <si>
     <t xml:space="preserve">10.3558940887451</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6783962249756</t>
+    <t xml:space="preserve">10.6783971786499</t>
   </si>
   <si>
     <t xml:space="preserve">10.4275617599487</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5350618362427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1800661087036</t>
+    <t xml:space="preserve">10.535062789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1800651550293</t>
   </si>
   <si>
     <t xml:space="preserve">10.9829816818237</t>
@@ -2129,22 +2129,22 @@
     <t xml:space="preserve">11.3771505355835</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7354860305786</t>
+    <t xml:space="preserve">11.7354869842529</t>
   </si>
   <si>
     <t xml:space="preserve">11.9146537780762</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9325704574585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0221538543701</t>
+    <t xml:space="preserve">11.9325714111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0221548080444</t>
   </si>
   <si>
     <t xml:space="preserve">11.8788204193115</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2371559143066</t>
+    <t xml:space="preserve">12.2371549606323</t>
   </si>
   <si>
     <t xml:space="preserve">12.3267402648926</t>
@@ -2156,10 +2156,10 @@
     <t xml:space="preserve">12.0938215255737</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3984069824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2013216018677</t>
+    <t xml:space="preserve">12.3984079360962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.201322555542</t>
   </si>
   <si>
     <t xml:space="preserve">11.9863214492798</t>
@@ -2171,7 +2171,7 @@
     <t xml:space="preserve">12.6134080886841</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8463258743286</t>
+    <t xml:space="preserve">12.8463268280029</t>
   </si>
   <si>
     <t xml:space="preserve">12.810492515564</t>
@@ -2186,16 +2186,16 @@
     <t xml:space="preserve">13.4017457962036</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4375801086426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6884136199951</t>
+    <t xml:space="preserve">13.4375791549683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6884145736694</t>
   </si>
   <si>
     <t xml:space="preserve">13.9034156799316</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6559200286865</t>
+    <t xml:space="preserve">14.6559209823608</t>
   </si>
   <si>
     <t xml:space="preserve">14.2438344955444</t>
@@ -2204,7 +2204,7 @@
     <t xml:space="preserve">14.6380043029785</t>
   </si>
   <si>
-    <t xml:space="preserve">14.92467212677</t>
+    <t xml:space="preserve">14.9246711730957</t>
   </si>
   <si>
     <t xml:space="preserve">14.5125865936279</t>
@@ -2219,34 +2219,34 @@
     <t xml:space="preserve">14.5484189987183</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4946699142456</t>
+    <t xml:space="preserve">14.4946689605713</t>
   </si>
   <si>
     <t xml:space="preserve">14.2617511749268</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8888387680054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8171730041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3871688842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7634210586548</t>
+    <t xml:space="preserve">14.8888397216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8171720504761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.387167930603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7634191513062</t>
   </si>
   <si>
     <t xml:space="preserve">14.6200866699219</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9067544937134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1217546463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0321731567383</t>
+    <t xml:space="preserve">14.9067535400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1217555999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.032172203064</t>
   </si>
   <si>
     <t xml:space="preserve">14.7455034255981</t>
@@ -2255,22 +2255,22 @@
     <t xml:space="preserve">15.0500888824463</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0680046081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1038408279419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5305032730103</t>
+    <t xml:space="preserve">15.0680065155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1038398742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5305023193359</t>
   </si>
   <si>
     <t xml:space="preserve">14.7096710205078</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2080001831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6167478561401</t>
+    <t xml:space="preserve">14.2080011367798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6167469024658</t>
   </si>
   <si>
     <t xml:space="preserve">13.5092468261719</t>
@@ -2279,13 +2279,13 @@
     <t xml:space="preserve">13.0434112548828</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1688270568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9717435836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4700746536255</t>
+    <t xml:space="preserve">13.1688280105591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9717426300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4700736999512</t>
   </si>
   <si>
     <t xml:space="preserve">13.2404947280884</t>
@@ -2303,31 +2303,31 @@
     <t xml:space="preserve">13.4913301467896</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2225780487061</t>
+    <t xml:space="preserve">13.2225790023804</t>
   </si>
   <si>
     <t xml:space="preserve">13.2046613693237</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0613269805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0075778961182</t>
+    <t xml:space="preserve">13.0613279342651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0075769424438</t>
   </si>
   <si>
     <t xml:space="preserve">12.6313257217407</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0971612930298</t>
+    <t xml:space="preserve">13.0971603393555</t>
   </si>
   <si>
     <t xml:space="preserve">13.0792446136475</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8642435073853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9896593093872</t>
+    <t xml:space="preserve">12.8642425537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9896602630615</t>
   </si>
   <si>
     <t xml:space="preserve">12.9538269042969</t>
@@ -2342,16 +2342,16 @@
     <t xml:space="preserve">13.1150779724121</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1509122848511</t>
+    <t xml:space="preserve">13.1509113311768</t>
   </si>
   <si>
     <t xml:space="preserve">13.5271635055542</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3479948043823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.276328086853</t>
+    <t xml:space="preserve">13.3479957580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2763290405273</t>
   </si>
   <si>
     <t xml:space="preserve">12.7925758361816</t>
@@ -2363,22 +2363,22 @@
     <t xml:space="preserve">12.5238237380981</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5059080123901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4879894256592</t>
+    <t xml:space="preserve">12.5059070587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4879903793335</t>
   </si>
   <si>
     <t xml:space="preserve">12.3088226318359</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5417413711548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8284091949463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3804893493652</t>
+    <t xml:space="preserve">12.5417404174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8284101486206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3804903030396</t>
   </si>
   <si>
     <t xml:space="preserve">12.6671581268311</t>
@@ -2393,25 +2393,25 @@
     <t xml:space="preserve">12.7746591567993</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4342403411865</t>
+    <t xml:space="preserve">12.4342412948608</t>
   </si>
   <si>
     <t xml:space="preserve">11.9504880905151</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2192401885986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8250703811646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1117391586304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9684038162231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0400714874268</t>
+    <t xml:space="preserve">12.2192392349243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8250694274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1117382049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9684047698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0400705337524</t>
   </si>
   <si>
     <t xml:space="preserve">12.0042381286621</t>
@@ -2423,13 +2423,13 @@
     <t xml:space="preserve">12.7388257980347</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7421646118164</t>
+    <t xml:space="preserve">13.7421655654907</t>
   </si>
   <si>
     <t xml:space="preserve">13.7063312530518</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0825834274292</t>
+    <t xml:space="preserve">14.0825843811035</t>
   </si>
   <si>
     <t xml:space="preserve">14.0109167098999</t>
@@ -2447,7 +2447,7 @@
     <t xml:space="preserve">13.9392499923706</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6346635818481</t>
+    <t xml:space="preserve">13.6346645355225</t>
   </si>
   <si>
     <t xml:space="preserve">14.2796678543091</t>
@@ -2459,7 +2459,7 @@
     <t xml:space="preserve">13.9571657180786</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8496646881104</t>
+    <t xml:space="preserve">13.8496656417847</t>
   </si>
   <si>
     <t xml:space="preserve">13.9750833511353</t>
@@ -2468,7 +2468,7 @@
     <t xml:space="preserve">13.5450801849365</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4734134674072</t>
+    <t xml:space="preserve">13.4734125137329</t>
   </si>
   <si>
     <t xml:space="preserve">13.1867456436157</t>
@@ -2483,28 +2483,28 @@
     <t xml:space="preserve">12.7029914855957</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8429861068726</t>
+    <t xml:space="preserve">11.8429870605469</t>
   </si>
   <si>
     <t xml:space="preserve">11.7892360687256</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6817359924316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0759048461914</t>
+    <t xml:space="preserve">11.6817350387573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0759038925171</t>
   </si>
   <si>
     <t xml:space="preserve">11.5742359161377</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2159004211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3592348098755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4309024810791</t>
+    <t xml:space="preserve">11.2158994674683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3592338562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4309015274048</t>
   </si>
   <si>
     <t xml:space="preserve">11.3054838180542</t>
@@ -2513,13 +2513,13 @@
     <t xml:space="preserve">11.2875671386719</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6837844848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5179252624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2783527374268</t>
+    <t xml:space="preserve">11.683783531189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5179262161255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2783517837524</t>
   </si>
   <si>
     <t xml:space="preserve">11.1493520736694</t>
@@ -2531,7 +2531,7 @@
     <t xml:space="preserve">11.0756378173828</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9970712661743</t>
+    <t xml:space="preserve">11.9970722198486</t>
   </si>
   <si>
     <t xml:space="preserve">12.052357673645</t>
@@ -2540,7 +2540,7 @@
     <t xml:space="preserve">12.2735013961792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2182159423828</t>
+    <t xml:space="preserve">12.2182149887085</t>
   </si>
   <si>
     <t xml:space="preserve">12.4025020599365</t>
@@ -2552,7 +2552,7 @@
     <t xml:space="preserve">12.0707864761353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1629295349121</t>
+    <t xml:space="preserve">12.1629285812378</t>
   </si>
   <si>
     <t xml:space="preserve">12.1260719299316</t>
@@ -2567,13 +2567,13 @@
     <t xml:space="preserve">11.7759265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8312139511108</t>
+    <t xml:space="preserve">11.8312129974365</t>
   </si>
   <si>
     <t xml:space="preserve">11.9786424636841</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7206420898438</t>
+    <t xml:space="preserve">11.7206411361694</t>
   </si>
   <si>
     <t xml:space="preserve">11.868070602417</t>
@@ -2588,7 +2588,7 @@
     <t xml:space="preserve">11.4442110061646</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3520679473877</t>
+    <t xml:space="preserve">11.35206699371